--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -833,8 +833,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="721"/>
-    <col width="12.59765625" customWidth="1" style="5" min="722" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="724"/>
+    <col width="12.59765625" customWidth="1" style="5" min="725" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>16.2</v>
+        <v>19.7</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>9.99</v>
+        <v>11.4</v>
       </c>
       <c r="R2" s="50" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>14.7</v>
+        <v>18.9</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="50" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>14.8</v>
+        <v>16.5</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="50" t="inlineStr">
@@ -1482,13 +1482,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>5.1</v>
+        <v>-1.9</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>15.8</v>
+        <v>13.5</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>9.81</v>
+        <v>5.29</v>
       </c>
       <c r="R6" s="52" t="inlineStr">
         <is>
@@ -1694,13 +1694,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>10.6</v>
+        <v>3.3</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>14.75</v>
+        <v>10.69</v>
       </c>
       <c r="R8" s="50" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1807,13 +1807,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>8.1</v>
+        <v>4.5</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>19.9</v>
+        <v>18.9</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>12.5</v>
+        <v>10.69</v>
       </c>
       <c r="R9" s="50" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>8.06</v>
+        <v>8.16</v>
       </c>
       <c r="R10" s="50" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>-1.1</v>
+        <v>0.6</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>13.8</v>
+        <v>11.4</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>6.25</v>
+        <v>5.59</v>
       </c>
       <c r="R11" s="50" t="inlineStr">
         <is>
@@ -2162,13 +2162,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>8.460000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="R12" s="50" t="inlineStr">
         <is>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>-3.9</v>
+        <v>-3.1</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>5.16</v>
+        <v>5.36</v>
       </c>
       <c r="R13" s="50" t="inlineStr">
         <is>
@@ -2400,13 +2400,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>10.1</v>
+        <v>8.9</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>21.2</v>
+        <v>14.6</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>14.95</v>
+        <v>11.21</v>
       </c>
       <c r="R14" s="50" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2521,13 +2521,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>20.5</v>
+        <v>13.2</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>11.07</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R15" s="50" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2821,7 +2821,9 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O18" s="31" t="n"/>
+      <c r="O18" s="31" t="n">
+        <v>-7.4</v>
+      </c>
       <c r="P18" s="31" t="n"/>
       <c r="Q18" s="31" t="n"/>
       <c r="R18" s="50" t="n"/>
@@ -4133,12 +4135,8 @@
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
-      <c r="O32" s="31" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P32" s="31" t="n">
-        <v>13</v>
-      </c>
+      <c r="O32" s="31" t="n"/>
+      <c r="P32" s="31" t="n"/>
       <c r="Q32" s="31" t="n"/>
       <c r="R32" s="50" t="n"/>
       <c r="S32" s="22" t="n"/>
@@ -9272,13 +9270,13 @@
         </is>
       </c>
       <c r="O88" s="31" t="n">
-        <v>-3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P88" s="31" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="Q88" s="31" t="n">
-        <v>5.85</v>
+        <v>10.16</v>
       </c>
       <c r="R88" s="50" t="inlineStr">
         <is>
@@ -9706,13 +9704,13 @@
         </is>
       </c>
       <c r="O92" s="31" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="P92" s="31" t="n">
-        <v>17.1</v>
+        <v>10.9</v>
       </c>
       <c r="Q92" s="31" t="n">
-        <v>9.85</v>
+        <v>5.56</v>
       </c>
       <c r="R92" s="50" t="n"/>
       <c r="S92" s="22" t="inlineStr">
@@ -9828,13 +9826,13 @@
         </is>
       </c>
       <c r="O93" s="31" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>17.1</v>
+        <v>10.7</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>8.789999999999999</v>
+        <v>5.31</v>
       </c>
       <c r="R93" s="50" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -10048,13 +10046,13 @@
         </is>
       </c>
       <c r="O95" s="31" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="P95" s="31" t="n">
-        <v>18.8</v>
+        <v>14.5</v>
       </c>
       <c r="Q95" s="31" t="n">
-        <v>9.82</v>
+        <v>8.74</v>
       </c>
       <c r="R95" s="50" t="n"/>
       <c r="S95" s="22" t="inlineStr">
@@ -10268,13 +10266,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="31" t="n">
-        <v>5.9</v>
+        <v>8.1</v>
       </c>
       <c r="P97" s="31" t="n">
-        <v>17.1</v>
+        <v>19.4</v>
       </c>
       <c r="Q97" s="31" t="n">
-        <v>10.77</v>
+        <v>12.38</v>
       </c>
       <c r="R97" s="50" t="n"/>
       <c r="S97" s="22" t="inlineStr">
@@ -10496,13 +10494,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="31" t="n">
-        <v>3.1</v>
+        <v>-1</v>
       </c>
       <c r="P99" s="31" t="n">
-        <v>13.1</v>
+        <v>16.2</v>
       </c>
       <c r="Q99" s="31" t="n">
-        <v>7.89</v>
+        <v>7.15</v>
       </c>
       <c r="R99" s="50" t="inlineStr">
         <is>
@@ -11021,13 +11019,13 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="31" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="P104" s="31" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="Q104" s="31" t="n">
-        <v>14.55</v>
+        <v>12.97</v>
       </c>
       <c r="R104" s="50" t="n"/>
       <c r="S104" s="22" t="inlineStr">
@@ -11134,13 +11132,13 @@
       </c>
       <c r="N105" s="2" t="n"/>
       <c r="O105" s="31" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="P105" s="31" t="n">
-        <v>30.3</v>
+        <v>29.2</v>
       </c>
       <c r="Q105" s="31" t="n">
-        <v>21.6</v>
+        <v>20.8</v>
       </c>
       <c r="R105" s="50" t="n"/>
       <c r="S105" s="22" t="inlineStr">
@@ -11373,10 +11371,10 @@
         <v>18.1</v>
       </c>
       <c r="P107" s="31" t="n">
-        <v>29.1</v>
+        <v>28.7</v>
       </c>
       <c r="Q107" s="31" t="n">
-        <v>23.39</v>
+        <v>22.89</v>
       </c>
       <c r="R107" s="50" t="n"/>
       <c r="S107" s="22" t="inlineStr">
@@ -11495,13 +11493,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="31" t="n">
-        <v>11.7</v>
+        <v>16.3</v>
       </c>
       <c r="P108" s="31" t="n">
-        <v>26.6</v>
+        <v>28</v>
       </c>
       <c r="Q108" s="31" t="n">
-        <v>19.24</v>
+        <v>22.61</v>
       </c>
       <c r="R108" s="50" t="n"/>
       <c r="S108" s="22" t="inlineStr">
@@ -12056,13 +12054,13 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="31" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="P113" s="31" t="n">
-        <v>24.7</v>
+        <v>14.5</v>
       </c>
       <c r="Q113" s="31" t="n">
-        <v>11.7</v>
+        <v>10.29</v>
       </c>
       <c r="R113" s="50" t="n"/>
       <c r="S113" s="22" t="inlineStr">
@@ -12395,13 +12393,13 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>28</v>
+        <v>23.3</v>
       </c>
       <c r="Q116" s="31" t="n">
-        <v>14.98</v>
+        <v>13.64</v>
       </c>
       <c r="R116" s="50" t="n"/>
       <c r="S116" s="22" t="inlineStr">
@@ -13689,13 +13687,13 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>26.3</v>
+        <v>23.3</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>34.4</v>
+        <v>32</v>
       </c>
       <c r="Q128" s="31" t="n">
-        <v>29.88</v>
+        <v>27.44</v>
       </c>
       <c r="R128" s="50" t="n"/>
       <c r="S128" s="22" t="inlineStr">
@@ -13806,13 +13804,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>14.7</v>
+        <v>12.2</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q129" s="31" t="n">
-        <v>18.51</v>
+        <v>17.5</v>
       </c>
       <c r="R129" s="50" t="n"/>
       <c r="S129" s="22" t="inlineStr">
@@ -14034,13 +14032,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>10.9</v>
+        <v>12.1</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="Q131" s="31" t="n">
-        <v>16.91</v>
+        <v>16.76</v>
       </c>
       <c r="R131" s="50" t="n"/>
       <c r="S131" s="22" t="inlineStr">
@@ -14159,13 +14157,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="31" t="n">
-        <v>18</v>
+        <v>20.5</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>31</v>
+        <v>28.6</v>
       </c>
       <c r="Q132" s="31" t="n">
-        <v>23.31</v>
+        <v>24.12</v>
       </c>
       <c r="R132" s="50" t="n"/>
       <c r="S132" s="22" t="inlineStr">
@@ -14272,13 +14270,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>11.7</v>
+        <v>13.6</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>27.3</v>
+        <v>28.3</v>
       </c>
       <c r="Q133" s="31" t="n">
-        <v>18.26</v>
+        <v>19.77</v>
       </c>
       <c r="R133" s="50" t="n"/>
       <c r="S133" s="22" t="inlineStr">
@@ -14393,13 +14391,13 @@
       </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="31" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>26.2</v>
+        <v>24.8</v>
       </c>
       <c r="Q134" s="31" t="n">
-        <v>18.43</v>
+        <v>17.64</v>
       </c>
       <c r="R134" s="50" t="n"/>
       <c r="S134" s="22" t="inlineStr">
@@ -14514,13 +14512,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="31" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="P135" s="31" t="n">
-        <v>20.4</v>
+        <v>23.1</v>
       </c>
       <c r="Q135" s="31" t="n">
-        <v>11.03</v>
+        <v>14.38</v>
       </c>
       <c r="R135" s="50" t="n"/>
       <c r="S135" s="22" t="inlineStr">
@@ -14635,13 +14633,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
-        <v>20.8</v>
+        <v>19.3</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="Q136" s="31" t="n">
-        <v>25.25</v>
+        <v>24.54</v>
       </c>
       <c r="R136" s="50" t="n"/>
       <c r="S136" s="22" t="inlineStr">
@@ -14752,13 +14750,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>19.8</v>
+        <v>17.9</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>25.1</v>
+        <v>27.7</v>
       </c>
       <c r="Q137" s="31" t="n">
-        <v>22.36</v>
+        <v>23.16</v>
       </c>
       <c r="R137" s="50" t="n"/>
       <c r="S137" s="22" t="inlineStr">
@@ -14869,13 +14867,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>27</v>
+        <v>23.7</v>
       </c>
       <c r="Q138" s="31" t="n">
-        <v>22.02</v>
+        <v>20.07</v>
       </c>
       <c r="R138" s="50" t="n"/>
       <c r="S138" s="22" t="inlineStr">
@@ -15093,13 +15091,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>25.3</v>
+        <v>22.8</v>
       </c>
       <c r="Q140" s="31" t="n">
-        <v>21.48</v>
+        <v>20.57</v>
       </c>
       <c r="R140" s="50" t="n"/>
       <c r="S140" s="22" t="inlineStr">
@@ -15210,13 +15208,13 @@
       </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="31" t="n">
-        <v>23.9</v>
+        <v>22</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="Q141" s="31" t="n">
-        <v>27.69</v>
+        <v>26.59</v>
       </c>
       <c r="R141" s="50" t="n"/>
       <c r="S141" s="22" t="inlineStr">
@@ -15330,10 +15328,10 @@
         <v>18.8</v>
       </c>
       <c r="P142" s="31" t="n">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
       <c r="Q142" s="31" t="n">
-        <v>19.91</v>
+        <v>20.92</v>
       </c>
       <c r="R142" s="50" t="n"/>
       <c r="S142" s="22" t="inlineStr">
@@ -15444,13 +15442,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>20.9</v>
+        <v>20.2</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>25.4</v>
+        <v>24.9</v>
       </c>
       <c r="Q143" s="31" t="n">
-        <v>23.26</v>
+        <v>22.09</v>
       </c>
       <c r="R143" s="50" t="n"/>
       <c r="S143" s="22" t="inlineStr">
@@ -15561,13 +15559,13 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>20.9</v>
+        <v>24.1</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>30.1</v>
+        <v>31.2</v>
       </c>
       <c r="Q144" s="31" t="n">
-        <v>25.35</v>
+        <v>27.22</v>
       </c>
       <c r="R144" s="50" t="n"/>
       <c r="S144" s="22" t="inlineStr">
@@ -15781,13 +15779,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="31" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="P146" s="31" t="n">
-        <v>32.1</v>
+        <v>33.5</v>
       </c>
       <c r="Q146" s="31" t="n">
-        <v>26.35</v>
+        <v>27.12</v>
       </c>
       <c r="R146" s="50" t="n"/>
       <c r="S146" s="22" t="inlineStr">
@@ -15898,13 +15896,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>24.4</v>
+        <v>25</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>33.7</v>
+        <v>34.4</v>
       </c>
       <c r="Q147" s="31" t="n">
-        <v>27.76</v>
+        <v>28.3</v>
       </c>
       <c r="R147" s="50" t="n"/>
       <c r="S147" s="22" t="inlineStr">
@@ -16217,13 +16215,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>25.7</v>
+        <v>25.2</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>30.6</v>
+        <v>32.2</v>
       </c>
       <c r="Q150" s="31" t="n">
-        <v>28.34</v>
+        <v>28.51</v>
       </c>
       <c r="R150" s="50" t="n"/>
       <c r="S150" s="22" t="inlineStr">
@@ -16326,13 +16324,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>32.8</v>
+        <v>33.4</v>
       </c>
       <c r="Q151" s="31" t="n">
-        <v>28.16</v>
+        <v>28.74</v>
       </c>
       <c r="R151" s="50" t="n"/>
       <c r="S151" s="22" t="inlineStr">
@@ -16443,13 +16441,13 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>16.4</v>
+        <v>16.9</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>25.1</v>
+        <v>26.5</v>
       </c>
       <c r="Q152" s="31" t="n">
-        <v>20.14</v>
+        <v>20.8</v>
       </c>
       <c r="R152" s="50" t="n"/>
       <c r="S152" s="22" t="inlineStr">
@@ -16560,13 +16558,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="31" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P153" s="31" t="n">
-        <v>27.4</v>
+        <v>28</v>
       </c>
       <c r="Q153" s="31" t="n">
-        <v>22.75</v>
+        <v>22.7</v>
       </c>
       <c r="R153" s="50" t="n"/>
       <c r="S153" s="22" t="inlineStr">
@@ -16677,13 +16675,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>20.4</v>
+        <v>21.3</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q154" s="31" t="n">
-        <v>21.31</v>
+        <v>22.04</v>
       </c>
       <c r="R154" s="50" t="n"/>
       <c r="S154" s="22" t="inlineStr">
@@ -16885,13 +16883,13 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="31" t="n">
-        <v>19.7</v>
+        <v>20.4</v>
       </c>
       <c r="P156" s="31" t="n">
-        <v>25.4</v>
+        <v>23.1</v>
       </c>
       <c r="Q156" s="31" t="n">
-        <v>21.91</v>
+        <v>21.28</v>
       </c>
       <c r="R156" s="50" t="n"/>
       <c r="S156" s="22" t="inlineStr">
@@ -17006,13 +17004,13 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="31" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P157" s="31" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q157" s="31" t="n">
-        <v>14.24</v>
+        <v>13.93</v>
       </c>
       <c r="R157" s="50" t="n"/>
       <c r="S157" s="22" t="inlineStr">
@@ -17594,13 +17592,13 @@
       </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="31" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="P163" s="31" t="n">
         <v>11.7</v>
       </c>
       <c r="Q163" s="31" t="n">
-        <v>4.47</v>
+        <v>5.11</v>
       </c>
       <c r="R163" s="50" t="n"/>
       <c r="S163" s="22" t="inlineStr">
@@ -17711,13 +17709,13 @@
         </is>
       </c>
       <c r="O164" s="31" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="P164" s="31" t="n">
-        <v>9.4</v>
+        <v>13.1</v>
       </c>
       <c r="Q164" s="31" t="n">
-        <v>2.84</v>
+        <v>4.89</v>
       </c>
       <c r="R164" s="50" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -17824,13 +17822,13 @@
       </c>
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P165" s="31" t="n">
-        <v>32.5</v>
+        <v>27.7</v>
       </c>
       <c r="Q165" s="31" t="n">
-        <v>25.54</v>
+        <v>23.59</v>
       </c>
       <c r="R165" s="50" t="n"/>
       <c r="S165" s="22" t="inlineStr">
@@ -17929,13 +17927,13 @@
       </c>
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="31" t="n">
-        <v>22.5</v>
+        <v>24.8</v>
       </c>
       <c r="P166" s="31" t="n">
-        <v>30</v>
+        <v>29.6</v>
       </c>
       <c r="Q166" s="31" t="n">
-        <v>26.01</v>
+        <v>26.38</v>
       </c>
       <c r="R166" s="50" t="n"/>
       <c r="S166" s="22" t="inlineStr">
@@ -18038,13 +18036,13 @@
       </c>
       <c r="N167" s="2" t="n"/>
       <c r="O167" s="31" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P167" s="31" t="n">
-        <v>26.2</v>
+        <v>28.4</v>
       </c>
       <c r="Q167" s="31" t="n">
-        <v>17.07</v>
+        <v>21.05</v>
       </c>
       <c r="R167" s="50" t="n"/>
       <c r="S167" s="22" t="inlineStr">
@@ -18282,13 +18280,13 @@
         </is>
       </c>
       <c r="O169" s="31" t="n">
-        <v>-1.3</v>
+        <v>-4.1</v>
       </c>
       <c r="P169" s="31" t="n">
-        <v>5.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q169" s="31" t="n">
-        <v>1.26</v>
+        <v>0.02</v>
       </c>
       <c r="R169" s="50" t="n"/>
       <c r="S169" s="22" t="inlineStr">
@@ -18403,13 +18401,13 @@
       </c>
       <c r="N170" s="2" t="n"/>
       <c r="O170" s="31" t="n">
-        <v>1.4</v>
+        <v>-3</v>
       </c>
       <c r="P170" s="31" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="Q170" s="31" t="n">
-        <v>7.55</v>
+        <v>6.67</v>
       </c>
       <c r="R170" s="50" t="n"/>
       <c r="S170" s="22" t="inlineStr">
@@ -18524,13 +18522,13 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="31" t="n">
-        <v>18.2</v>
+        <v>19.1</v>
       </c>
       <c r="P171" s="31" t="n">
-        <v>30.1</v>
+        <v>27.4</v>
       </c>
       <c r="Q171" s="31" t="n">
-        <v>24.09</v>
+        <v>22.4</v>
       </c>
       <c r="R171" s="50" t="n"/>
       <c r="S171" s="22" t="inlineStr">
@@ -18637,13 +18635,13 @@
       </c>
       <c r="N172" s="2" t="n"/>
       <c r="O172" s="31" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="P172" s="31" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="Q172" s="31" t="n">
-        <v>20.74</v>
+        <v>19.84</v>
       </c>
       <c r="R172" s="50" t="n"/>
       <c r="S172" s="22" t="inlineStr">
@@ -18754,13 +18752,13 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="31" t="n">
-        <v>24.1</v>
+        <v>25.3</v>
       </c>
       <c r="P173" s="31" t="n">
-        <v>35.4</v>
+        <v>33.8</v>
       </c>
       <c r="Q173" s="31" t="n">
-        <v>28.55</v>
+        <v>27.94</v>
       </c>
       <c r="R173" s="50" t="n"/>
       <c r="S173" s="22" t="inlineStr">
@@ -18867,13 +18865,13 @@
       </c>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="31" t="n">
-        <v>11</v>
+        <v>13.1</v>
       </c>
       <c r="P174" s="31" t="n">
-        <v>20.5</v>
+        <v>19.1</v>
       </c>
       <c r="Q174" s="31" t="n">
-        <v>14.34</v>
+        <v>15.47</v>
       </c>
       <c r="R174" s="50" t="n"/>
       <c r="S174" s="22" t="inlineStr">
@@ -19075,13 +19073,13 @@
         </is>
       </c>
       <c r="O176" s="31" t="n">
-        <v>-7.8</v>
+        <v>-8.1</v>
       </c>
       <c r="P176" s="31" t="n">
-        <v>1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="Q176" s="31" t="n">
-        <v>-4.5</v>
+        <v>-5.8</v>
       </c>
       <c r="R176" s="50" t="n"/>
       <c r="S176" s="22" t="inlineStr">
@@ -19184,12 +19182,14 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="31" t="n">
-        <v>-4.4</v>
+        <v>-6.3</v>
       </c>
       <c r="P177" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q177" s="31" t="n"/>
+        <v>-3</v>
+      </c>
+      <c r="Q177" s="31" t="n">
+        <v>-5.2</v>
+      </c>
       <c r="R177" s="50" t="n"/>
       <c r="S177" s="22" t="inlineStr">
         <is>
@@ -19290,12 +19290,8 @@
         </is>
       </c>
       <c r="N178" s="2" t="n"/>
-      <c r="O178" s="31" t="n">
-        <v>-8</v>
-      </c>
-      <c r="P178" s="31" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="O178" s="31" t="n"/>
+      <c r="P178" s="31" t="n"/>
       <c r="Q178" s="31" t="n"/>
       <c r="R178" s="50" t="n"/>
       <c r="S178" s="22" t="n"/>
@@ -19501,14 +19497,12 @@
       </c>
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="31" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="P180" s="31" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="Q180" s="31" t="n">
-        <v>12.61</v>
-      </c>
+        <v>21.9</v>
+      </c>
+      <c r="Q180" s="31" t="n"/>
       <c r="R180" s="50" t="inlineStr">
         <is>
           <t>2010-01-05</t>
@@ -19614,10 +19608,10 @@
       </c>
       <c r="N181" s="2" t="n"/>
       <c r="O181" s="31" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="P181" s="31" t="n">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="Q181" s="31" t="n"/>
       <c r="R181" s="50" t="n"/>
@@ -19720,8 +19714,12 @@
         </is>
       </c>
       <c r="N182" s="3" t="n"/>
-      <c r="O182" s="31" t="n"/>
-      <c r="P182" s="31" t="n"/>
+      <c r="O182" s="31" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="P182" s="31" t="n">
+        <v>17.9</v>
+      </c>
       <c r="Q182" s="31" t="n"/>
       <c r="R182" s="50" t="n"/>
       <c r="S182" s="22" t="inlineStr">
@@ -19832,13 +19830,13 @@
         </is>
       </c>
       <c r="O183" s="31" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="P183" s="31" t="n">
         <v>11.4</v>
       </c>
       <c r="Q183" s="31" t="n">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="R183" s="50" t="n"/>
       <c r="S183" s="22" t="inlineStr">
@@ -20766,8 +20764,12 @@
         </is>
       </c>
       <c r="N192" s="2" t="n"/>
-      <c r="O192" s="31" t="n"/>
-      <c r="P192" s="31" t="n"/>
+      <c r="O192" s="31" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="P192" s="31" t="n">
+        <v>20</v>
+      </c>
       <c r="Q192" s="31" t="n"/>
       <c r="R192" s="50" t="n"/>
       <c r="S192" s="22" t="inlineStr">
@@ -20874,10 +20876,10 @@
         </is>
       </c>
       <c r="O193" s="31" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="P193" s="31" t="n">
-        <v>25.9</v>
+        <v>18.6</v>
       </c>
       <c r="Q193" s="31" t="n"/>
       <c r="R193" s="50" t="n"/>
@@ -21301,12 +21303,8 @@
           <t>⚡🧊</t>
         </is>
       </c>
-      <c r="O197" s="31" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="P197" s="31" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="O197" s="31" t="n"/>
+      <c r="P197" s="31" t="n"/>
       <c r="Q197" s="31" t="n"/>
       <c r="R197" s="50" t="n"/>
       <c r="S197" s="22" t="inlineStr">
@@ -21528,10 +21526,10 @@
       </c>
       <c r="N199" s="2" t="n"/>
       <c r="O199" s="31" t="n">
-        <v>-2.9</v>
+        <v>-5.2</v>
       </c>
       <c r="P199" s="31" t="n">
-        <v>13.3</v>
+        <v>16.3</v>
       </c>
       <c r="Q199" s="31" t="n"/>
       <c r="R199" s="50" t="n"/>
@@ -21637,7 +21635,7 @@
       </c>
       <c r="N200" s="2" t="n"/>
       <c r="O200" s="31" t="n">
-        <v>-29</v>
+        <v>-37.6</v>
       </c>
       <c r="P200" s="31" t="n"/>
       <c r="Q200" s="31" t="n"/>
@@ -21814,7 +21812,7 @@
       <c r="L202" s="2" t="n"/>
       <c r="M202" s="16" t="inlineStr">
         <is>
-          <t>卡通铁列克</t>
+          <t>Karatyurek</t>
         </is>
       </c>
       <c r="N202" s="2" t="n"/>
@@ -22200,11 +22198,21 @@
         </is>
       </c>
       <c r="N206" s="2" t="n"/>
-      <c r="O206" s="31" t="n"/>
-      <c r="P206" s="31" t="n"/>
-      <c r="Q206" s="31" t="n"/>
+      <c r="O206" s="31" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P206" s="31" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Q206" s="31" t="n">
+        <v>18.51</v>
+      </c>
       <c r="R206" s="50" t="n"/>
-      <c r="S206" s="22" t="n"/>
+      <c r="S206" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T206" s="36" t="n"/>
       <c r="U206" s="40" t="inlineStr">
         <is>
@@ -22594,11 +22602,21 @@
         </is>
       </c>
       <c r="N210" s="2" t="n"/>
-      <c r="O210" s="31" t="n"/>
-      <c r="P210" s="31" t="n"/>
-      <c r="Q210" s="31" t="n"/>
+      <c r="O210" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P210" s="31" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Q210" s="31" t="n">
+        <v>11.28</v>
+      </c>
       <c r="R210" s="50" t="n"/>
-      <c r="S210" s="22" t="n"/>
+      <c r="S210" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T210" s="36" t="n"/>
       <c r="U210" s="40" t="inlineStr">
         <is>
@@ -22794,11 +22812,21 @@
         </is>
       </c>
       <c r="N212" s="2" t="n"/>
-      <c r="O212" s="31" t="n"/>
-      <c r="P212" s="31" t="n"/>
-      <c r="Q212" s="31" t="n"/>
+      <c r="O212" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P212" s="31" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="Q212" s="31" t="n">
+        <v>11.24</v>
+      </c>
       <c r="R212" s="50" t="n"/>
-      <c r="S212" s="22" t="n"/>
+      <c r="S212" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T212" s="36" t="n"/>
       <c r="U212" s="40" t="inlineStr">
         <is>
@@ -23190,11 +23218,21 @@
         </is>
       </c>
       <c r="N216" s="2" t="n"/>
-      <c r="O216" s="31" t="n"/>
-      <c r="P216" s="31" t="n"/>
-      <c r="Q216" s="31" t="n"/>
+      <c r="O216" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P216" s="31" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Q216" s="31" t="n">
+        <v>10.15</v>
+      </c>
       <c r="R216" s="50" t="n"/>
-      <c r="S216" s="22" t="n"/>
+      <c r="S216" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T216" s="36" t="n"/>
       <c r="U216" s="40" t="inlineStr">
         <is>
@@ -23483,11 +23521,21 @@
         </is>
       </c>
       <c r="N219" s="2" t="n"/>
-      <c r="O219" s="31" t="n"/>
-      <c r="P219" s="31" t="n"/>
-      <c r="Q219" s="31" t="n"/>
+      <c r="O219" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P219" s="31" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Q219" s="31" t="n">
+        <v>12.5</v>
+      </c>
       <c r="R219" s="50" t="n"/>
-      <c r="S219" s="22" t="n"/>
+      <c r="S219" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T219" s="36" t="n"/>
       <c r="U219" s="40" t="inlineStr">
         <is>
@@ -23586,11 +23634,21 @@
         </is>
       </c>
       <c r="N220" s="2" t="n"/>
-      <c r="O220" s="31" t="n"/>
-      <c r="P220" s="31" t="n"/>
-      <c r="Q220" s="31" t="n"/>
+      <c r="O220" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P220" s="31" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="Q220" s="31" t="n">
+        <v>12.8</v>
+      </c>
       <c r="R220" s="50" t="n"/>
-      <c r="S220" s="22" t="n"/>
+      <c r="S220" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T220" s="36" t="n"/>
       <c r="U220" s="40" t="inlineStr">
         <is>
@@ -23976,15 +24034,25 @@
           <t>♦️</t>
         </is>
       </c>
-      <c r="O224" s="31" t="n"/>
-      <c r="P224" s="31" t="n"/>
-      <c r="Q224" s="31" t="n"/>
+      <c r="O224" s="31" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="P224" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q224" s="31" t="n">
+        <v>-1.18</v>
+      </c>
       <c r="R224" s="50" t="n"/>
-      <c r="S224" s="22" t="n"/>
+      <c r="S224" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T224" s="36" t="n"/>
       <c r="U224" s="40" t="inlineStr">
         <is>
-          <t>通古斯卡河支流</t>
+          <t>通古斯卡河支流&lt;br&gt;克拉斯诺亚尔斯克</t>
         </is>
       </c>
       <c r="V224" s="2" t="inlineStr">
@@ -24158,7 +24226,9 @@
         </is>
       </c>
       <c r="N226" s="2" t="n"/>
-      <c r="O226" s="31" t="n"/>
+      <c r="O226" s="31" t="n">
+        <v>-10.4</v>
+      </c>
       <c r="P226" s="31" t="n"/>
       <c r="Q226" s="31" t="n"/>
       <c r="R226" s="50" t="n"/>
@@ -26209,15 +26279,25 @@
         </is>
       </c>
       <c r="N248" s="2" t="n"/>
-      <c r="O248" s="31" t="n"/>
-      <c r="P248" s="31" t="n"/>
-      <c r="Q248" s="31" t="n"/>
+      <c r="O248" s="31" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="P248" s="31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Q248" s="31" t="n">
+        <v>2.52</v>
+      </c>
       <c r="R248" s="50" t="n"/>
-      <c r="S248" s="22" t="n"/>
+      <c r="S248" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T248" s="36" t="n"/>
       <c r="U248" s="40" t="inlineStr">
         <is>
-          <t>奥伊米亚康</t>
+          <t>奥伊米亚康&lt;br&gt;萨哈</t>
         </is>
       </c>
       <c r="V248" s="2" t="inlineStr">
@@ -26693,15 +26773,23 @@
         </is>
       </c>
       <c r="N253" s="2" t="n"/>
-      <c r="O253" s="31" t="n"/>
-      <c r="P253" s="31" t="n"/>
+      <c r="O253" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P253" s="31" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="Q253" s="31" t="n"/>
       <c r="R253" s="50" t="n"/>
-      <c r="S253" s="22" t="n"/>
+      <c r="S253" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T253" s="36" t="n"/>
       <c r="U253" s="40" t="inlineStr">
         <is>
-          <t>外兴安岭</t>
+          <t>外兴安岭&lt;br&gt;萨哈</t>
         </is>
       </c>
       <c r="V253" s="2" t="inlineStr">
@@ -27067,10 +27155,10 @@
       </c>
       <c r="N257" s="2" t="n"/>
       <c r="O257" s="31" t="n">
-        <v>-73.90000000000001</v>
+        <v>-75.2</v>
       </c>
       <c r="P257" s="31" t="n">
-        <v>-66.2</v>
+        <v>-68.2</v>
       </c>
       <c r="Q257" s="31" t="n"/>
       <c r="R257" s="50" t="n"/>
@@ -27167,7 +27255,9 @@
         </is>
       </c>
       <c r="N258" s="2" t="n"/>
-      <c r="O258" s="31" t="n"/>
+      <c r="O258" s="31" t="n">
+        <v>-80.2</v>
+      </c>
       <c r="P258" s="31" t="n"/>
       <c r="Q258" s="31" t="n"/>
       <c r="R258" s="50" t="n"/>
@@ -32341,12 +32431,8 @@
         </is>
       </c>
       <c r="N310" s="2" t="n"/>
-      <c r="O310" s="31" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="P310" s="31" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="O310" s="31" t="n"/>
+      <c r="P310" s="31" t="n"/>
       <c r="Q310" s="31" t="n"/>
       <c r="R310" s="50" t="n"/>
       <c r="S310" s="22" t="inlineStr">
@@ -34077,15 +34163,9 @@
         </is>
       </c>
       <c r="N328" s="2" t="n"/>
-      <c r="O328" s="31" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="P328" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q328" s="31" t="n">
-        <v>5.02</v>
-      </c>
+      <c r="O328" s="31" t="n"/>
+      <c r="P328" s="31" t="n"/>
+      <c r="Q328" s="31" t="n"/>
       <c r="R328" s="50" t="n"/>
       <c r="S328" s="22" t="inlineStr">
         <is>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -830,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="726"/>
-    <col width="12.59765625" customWidth="1" style="5" min="727" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="728"/>
+    <col width="12.59765625" customWidth="1" style="5" min="729" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>8.1</v>
+        <v>3.2</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>22.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>13.64</v>
+        <v>12.39</v>
       </c>
       <c r="R2" s="49" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="49" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="49" t="inlineStr">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>-6.7</v>
+        <v>-6.3</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>16.5</v>
+        <v>18.9</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>4.65</v>
+        <v>6.19</v>
       </c>
       <c r="R6" s="51" t="inlineStr">
         <is>
@@ -1691,13 +1691,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>21.1</v>
+        <v>20.1</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>11.25</v>
+        <v>12.34</v>
       </c>
       <c r="R8" s="49" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1804,13 +1804,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>19.7</v>
+        <v>21.5</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>12.19</v>
+        <v>12.25</v>
       </c>
       <c r="R9" s="49" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>-1.2</v>
+        <v>-2.5</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>9.09</v>
+        <v>9.35</v>
       </c>
       <c r="R10" s="49" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>-6.6</v>
+        <v>-5.9</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>15.7</v>
+        <v>18.6</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>5.61</v>
+        <v>7.06</v>
       </c>
       <c r="R11" s="49" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>-2.1</v>
+        <v>-1.6</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>18</v>
+        <v>21.1</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>7.01</v>
+        <v>8.42</v>
       </c>
       <c r="R12" s="49" t="inlineStr">
         <is>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>-1.9</v>
+        <v>-3.6</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>10.2</v>
+        <v>18.9</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>5.09</v>
+        <v>6.79</v>
       </c>
       <c r="R13" s="49" t="inlineStr">
         <is>
@@ -2397,13 +2397,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>17.5</v>
+        <v>20.7</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>10.03</v>
+        <v>12.7</v>
       </c>
       <c r="R14" s="49" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2518,13 +2518,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>-3.5</v>
+        <v>-1.3</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>14.8</v>
+        <v>20.3</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>5.16</v>
+        <v>12.7</v>
       </c>
       <c r="R15" s="49" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2628,9 +2628,15 @@
         </is>
       </c>
       <c r="N16" s="2" t="n"/>
-      <c r="O16" s="31" t="n"/>
-      <c r="P16" s="31" t="n"/>
-      <c r="Q16" s="31" t="n"/>
+      <c r="O16" s="31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P16" s="31" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q16" s="31" t="n">
+        <v>12.7</v>
+      </c>
       <c r="R16" s="49" t="n"/>
       <c r="S16" s="22" t="n"/>
       <c r="T16" s="35" t="n"/>
@@ -2819,7 +2825,7 @@
         </is>
       </c>
       <c r="O18" s="31" t="n">
-        <v>-11.5</v>
+        <v>-10</v>
       </c>
       <c r="P18" s="31" t="n"/>
       <c r="Q18" s="31" t="n"/>
@@ -9267,13 +9273,13 @@
         </is>
       </c>
       <c r="O88" s="31" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="P88" s="31" t="n">
-        <v>23.1</v>
+        <v>19.6</v>
       </c>
       <c r="Q88" s="31" t="n">
-        <v>14.74</v>
+        <v>7.65</v>
       </c>
       <c r="R88" s="49" t="inlineStr">
         <is>
@@ -9701,13 +9707,13 @@
         </is>
       </c>
       <c r="O92" s="31" t="n">
-        <v>-7.4</v>
+        <v>-8.1</v>
       </c>
       <c r="P92" s="31" t="n">
-        <v>10.7</v>
+        <v>12.9</v>
       </c>
       <c r="Q92" s="31" t="n">
-        <v>1.79</v>
+        <v>1.27</v>
       </c>
       <c r="R92" s="49" t="n"/>
       <c r="S92" s="22" t="inlineStr">
@@ -9823,13 +9829,13 @@
         </is>
       </c>
       <c r="O93" s="31" t="n">
-        <v>-6.2</v>
+        <v>-1.5</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>9.9</v>
+        <v>10.8</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>1.35</v>
+        <v>3.46</v>
       </c>
       <c r="R93" s="49" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -10043,13 +10049,13 @@
         </is>
       </c>
       <c r="O95" s="31" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="P95" s="31" t="n">
-        <v>11.2</v>
+        <v>16</v>
       </c>
       <c r="Q95" s="31" t="n">
-        <v>6.27</v>
+        <v>8.9</v>
       </c>
       <c r="R95" s="49" t="n"/>
       <c r="S95" s="22" t="inlineStr">
@@ -10263,13 +10269,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="31" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="P97" s="31" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="Q97" s="31" t="n">
-        <v>14.9</v>
+        <v>13.14</v>
       </c>
       <c r="R97" s="49" t="n"/>
       <c r="S97" s="22" t="inlineStr">
@@ -10491,13 +10497,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="31" t="n">
-        <v>-2.1</v>
+        <v>1.4</v>
       </c>
       <c r="P99" s="31" t="n">
-        <v>20.4</v>
+        <v>19.6</v>
       </c>
       <c r="Q99" s="31" t="n">
-        <v>8.69</v>
+        <v>10.5</v>
       </c>
       <c r="R99" s="49" t="inlineStr">
         <is>
@@ -11015,15 +11021,9 @@
         </is>
       </c>
       <c r="N104" s="2" t="n"/>
-      <c r="O104" s="31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P104" s="31" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="Q104" s="31" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="O104" s="31" t="n"/>
+      <c r="P104" s="31" t="n"/>
+      <c r="Q104" s="31" t="n"/>
       <c r="R104" s="49" t="n"/>
       <c r="S104" s="22" t="inlineStr">
         <is>
@@ -11129,14 +11129,12 @@
       </c>
       <c r="N105" s="2" t="n"/>
       <c r="O105" s="31" t="n">
-        <v>13.3</v>
+        <v>15.9</v>
       </c>
       <c r="P105" s="31" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Q105" s="31" t="n">
-        <v>20.36</v>
-      </c>
+        <v>23.5</v>
+      </c>
+      <c r="Q105" s="31" t="n"/>
       <c r="R105" s="49" t="n"/>
       <c r="S105" s="22" t="inlineStr">
         <is>
@@ -11365,14 +11363,12 @@
       </c>
       <c r="N107" s="2" t="n"/>
       <c r="O107" s="31" t="n">
-        <v>15.6</v>
+        <v>11.8</v>
       </c>
       <c r="P107" s="31" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Q107" s="31" t="n">
-        <v>21.91</v>
-      </c>
+        <v>22.1</v>
+      </c>
+      <c r="Q107" s="31" t="n"/>
       <c r="R107" s="49" t="n"/>
       <c r="S107" s="22" t="inlineStr">
         <is>
@@ -11490,14 +11486,12 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="31" t="n">
-        <v>12.4</v>
+        <v>10.5</v>
       </c>
       <c r="P108" s="31" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q108" s="31" t="n">
-        <v>19.85</v>
-      </c>
+        <v>22.8</v>
+      </c>
+      <c r="Q108" s="31" t="n"/>
       <c r="R108" s="49" t="n"/>
       <c r="S108" s="22" t="inlineStr">
         <is>
@@ -12051,14 +12045,12 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="31" t="n">
-        <v>0.9</v>
+        <v>-6</v>
       </c>
       <c r="P113" s="31" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="Q113" s="31" t="n">
-        <v>4.56</v>
-      </c>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q113" s="31" t="n"/>
       <c r="R113" s="49" t="n"/>
       <c r="S113" s="22" t="inlineStr">
         <is>
@@ -12270,9 +12262,15 @@
         </is>
       </c>
       <c r="N115" s="2" t="n"/>
-      <c r="O115" s="31" t="n"/>
-      <c r="P115" s="31" t="n"/>
-      <c r="Q115" s="31" t="n"/>
+      <c r="O115" s="31" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="P115" s="31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q115" s="31" t="n">
+        <v>1.78</v>
+      </c>
       <c r="R115" s="49" t="n"/>
       <c r="S115" s="22" t="n"/>
       <c r="T115" s="35" t="inlineStr">
@@ -12390,14 +12388,12 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>6.3</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="Q116" s="31" t="n">
-        <v>8.56</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="Q116" s="31" t="n"/>
       <c r="R116" s="49" t="n"/>
       <c r="S116" s="22" t="inlineStr">
         <is>
@@ -13684,14 +13680,12 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>18.6</v>
+        <v>21.1</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="Q128" s="31" t="n">
-        <v>26.82</v>
-      </c>
+        <v>33.7</v>
+      </c>
+      <c r="Q128" s="31" t="n"/>
       <c r="R128" s="49" t="n"/>
       <c r="S128" s="22" t="inlineStr">
         <is>
@@ -13801,14 +13795,12 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>13.9</v>
+        <v>18.3</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="Q129" s="31" t="n">
-        <v>20.14</v>
-      </c>
+        <v>29.1</v>
+      </c>
+      <c r="Q129" s="31" t="n"/>
       <c r="R129" s="49" t="n"/>
       <c r="S129" s="22" t="inlineStr">
         <is>
@@ -14029,14 +14021,12 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="Q131" s="31" t="n">
-        <v>15.65</v>
-      </c>
+        <v>21.3</v>
+      </c>
+      <c r="Q131" s="31" t="n"/>
       <c r="R131" s="49" t="n"/>
       <c r="S131" s="22" t="inlineStr">
         <is>
@@ -14154,14 +14144,12 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="31" t="n">
-        <v>19.4</v>
+        <v>21</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="Q132" s="31" t="n">
-        <v>23.72</v>
-      </c>
+        <v>28.1</v>
+      </c>
+      <c r="Q132" s="31" t="n"/>
       <c r="R132" s="49" t="n"/>
       <c r="S132" s="22" t="inlineStr">
         <is>
@@ -14267,14 +14255,12 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>14.3</v>
+        <v>16.3</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="Q133" s="31" t="n">
-        <v>18.05</v>
-      </c>
+        <v>21.9</v>
+      </c>
+      <c r="Q133" s="31" t="n"/>
       <c r="R133" s="49" t="n"/>
       <c r="S133" s="22" t="inlineStr">
         <is>
@@ -14388,14 +14374,12 @@
       </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="31" t="n">
-        <v>12.2</v>
+        <v>16.5</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="Q134" s="31" t="n">
-        <v>18.65</v>
-      </c>
+        <v>26.7</v>
+      </c>
+      <c r="Q134" s="31" t="n"/>
       <c r="R134" s="49" t="n"/>
       <c r="S134" s="22" t="inlineStr">
         <is>
@@ -14509,14 +14493,12 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="P135" s="31" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Q135" s="31" t="n">
-        <v>10.65</v>
-      </c>
+        <v>14.9</v>
+      </c>
+      <c r="Q135" s="31" t="n"/>
       <c r="R135" s="49" t="n"/>
       <c r="S135" s="22" t="inlineStr">
         <is>
@@ -14630,14 +14612,12 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
-        <v>19.7</v>
+        <v>21.2</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="Q136" s="31" t="n">
-        <v>24.96</v>
-      </c>
+        <v>28.7</v>
+      </c>
+      <c r="Q136" s="31" t="n"/>
       <c r="R136" s="49" t="n"/>
       <c r="S136" s="22" t="inlineStr">
         <is>
@@ -14747,14 +14727,12 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>19.4</v>
+        <v>21.8</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Q137" s="31" t="n">
-        <v>23.68</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q137" s="31" t="n"/>
       <c r="R137" s="49" t="n"/>
       <c r="S137" s="22" t="inlineStr">
         <is>
@@ -14864,14 +14842,12 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>16.8</v>
+        <v>18.7</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="Q138" s="31" t="n">
-        <v>19.9</v>
-      </c>
+        <v>21.4</v>
+      </c>
+      <c r="Q138" s="31" t="n"/>
       <c r="R138" s="49" t="n"/>
       <c r="S138" s="22" t="inlineStr">
         <is>
@@ -15088,14 +15064,12 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>20.6</v>
+        <v>21.4</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="Q140" s="31" t="n">
-        <v>22.51</v>
-      </c>
+        <v>29.5</v>
+      </c>
+      <c r="Q140" s="31" t="n"/>
       <c r="R140" s="49" t="n"/>
       <c r="S140" s="22" t="inlineStr">
         <is>
@@ -15205,14 +15179,12 @@
       </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="31" t="n">
-        <v>23.9</v>
+        <v>25.4</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="Q141" s="31" t="n">
-        <v>27.32</v>
-      </c>
+        <v>33.8</v>
+      </c>
+      <c r="Q141" s="31" t="n"/>
       <c r="R141" s="49" t="n"/>
       <c r="S141" s="22" t="inlineStr">
         <is>
@@ -15322,14 +15294,12 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="31" t="n">
-        <v>19.6</v>
+        <v>23</v>
       </c>
       <c r="P142" s="31" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="Q142" s="31" t="n">
-        <v>23.75</v>
-      </c>
+        <v>27.4</v>
+      </c>
+      <c r="Q142" s="31" t="n"/>
       <c r="R142" s="49" t="n"/>
       <c r="S142" s="22" t="inlineStr">
         <is>
@@ -15439,14 +15409,12 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Q143" s="31" t="n">
-        <v>24.11</v>
-      </c>
+        <v>25.5</v>
+      </c>
+      <c r="Q143" s="31" t="n"/>
       <c r="R143" s="49" t="n"/>
       <c r="S143" s="22" t="inlineStr">
         <is>
@@ -15556,14 +15524,12 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="Q144" s="31" t="n">
-        <v>26.95</v>
-      </c>
+        <v>27.4</v>
+      </c>
+      <c r="Q144" s="31" t="n"/>
       <c r="R144" s="49" t="n"/>
       <c r="S144" s="22" t="inlineStr">
         <is>
@@ -15776,14 +15742,12 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="31" t="n">
-        <v>23.7</v>
+        <v>26.5</v>
       </c>
       <c r="P146" s="31" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="Q146" s="31" t="n">
-        <v>28.24</v>
-      </c>
+        <v>33.9</v>
+      </c>
+      <c r="Q146" s="31" t="n"/>
       <c r="R146" s="49" t="n"/>
       <c r="S146" s="22" t="inlineStr">
         <is>
@@ -15893,14 +15857,12 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="Q147" s="31" t="n">
-        <v>28.64</v>
-      </c>
+        <v>35.7</v>
+      </c>
+      <c r="Q147" s="31" t="n"/>
       <c r="R147" s="49" t="n"/>
       <c r="S147" s="22" t="inlineStr">
         <is>
@@ -16212,14 +16174,12 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>26.3</v>
+        <v>25.2</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="Q150" s="31" t="n">
-        <v>28.49</v>
-      </c>
+        <v>33.2</v>
+      </c>
+      <c r="Q150" s="31" t="n"/>
       <c r="R150" s="49" t="n"/>
       <c r="S150" s="22" t="inlineStr">
         <is>
@@ -16321,14 +16281,12 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="Q151" s="31" t="n">
-        <v>29.51</v>
-      </c>
+        <v>35.1</v>
+      </c>
+      <c r="Q151" s="31" t="n"/>
       <c r="R151" s="49" t="n"/>
       <c r="S151" s="22" t="inlineStr">
         <is>
@@ -16438,14 +16396,12 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>18.3</v>
+        <v>14.1</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="Q152" s="31" t="n">
-        <v>20.32</v>
-      </c>
+        <v>26.3</v>
+      </c>
+      <c r="Q152" s="31" t="n"/>
       <c r="R152" s="49" t="n"/>
       <c r="S152" s="22" t="inlineStr">
         <is>
@@ -16555,14 +16511,12 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="31" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="P153" s="31" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="Q153" s="31" t="n">
-        <v>24.25</v>
-      </c>
+        <v>31.3</v>
+      </c>
+      <c r="Q153" s="31" t="n"/>
       <c r="R153" s="49" t="n"/>
       <c r="S153" s="22" t="inlineStr">
         <is>
@@ -16672,14 +16626,12 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>21.1</v>
+        <v>23.1</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="Q154" s="31" t="n">
-        <v>23.77</v>
-      </c>
+        <v>26.4</v>
+      </c>
+      <c r="Q154" s="31" t="n"/>
       <c r="R154" s="49" t="n"/>
       <c r="S154" s="22" t="inlineStr">
         <is>
@@ -16880,14 +16832,12 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="31" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="P156" s="31" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="Q156" s="31" t="n">
-        <v>20.75</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="Q156" s="31" t="n"/>
       <c r="R156" s="49" t="n"/>
       <c r="S156" s="22" t="inlineStr">
         <is>
@@ -17001,7 +16951,7 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="P157" s="31" t="n">
         <v>21.7</v>
@@ -17587,12 +17537,14 @@
       </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="31" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="P163" s="31" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Q163" s="31" t="n"/>
+        <v>8.9</v>
+      </c>
+      <c r="Q163" s="31" t="n">
+        <v>2.89</v>
+      </c>
       <c r="R163" s="49" t="n"/>
       <c r="S163" s="22" t="inlineStr">
         <is>
@@ -17702,13 +17654,13 @@
         </is>
       </c>
       <c r="O164" s="31" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="P164" s="31" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="Q164" s="31" t="n">
-        <v>4.25</v>
+        <v>5.04</v>
       </c>
       <c r="R164" s="49" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -17815,13 +17767,13 @@
       </c>
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="31" t="n">
-        <v>18.3</v>
+        <v>20.4</v>
       </c>
       <c r="P165" s="31" t="n">
-        <v>28.9</v>
+        <v>28.2</v>
       </c>
       <c r="Q165" s="31" t="n">
-        <v>23.16</v>
+        <v>23.51</v>
       </c>
       <c r="R165" s="49" t="n"/>
       <c r="S165" s="22" t="inlineStr">
@@ -17920,13 +17872,13 @@
       </c>
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="31" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="P166" s="31" t="n">
-        <v>28.9</v>
+        <v>29.4</v>
       </c>
       <c r="Q166" s="31" t="n">
-        <v>25.54</v>
+        <v>26.49</v>
       </c>
       <c r="R166" s="49" t="n"/>
       <c r="S166" s="22" t="inlineStr">
@@ -18029,13 +17981,13 @@
       </c>
       <c r="N167" s="2" t="n"/>
       <c r="O167" s="31" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="P167" s="31" t="n">
-        <v>23.6</v>
+        <v>20.3</v>
       </c>
       <c r="Q167" s="31" t="n">
-        <v>16.09</v>
+        <v>16.1</v>
       </c>
       <c r="R167" s="49" t="n"/>
       <c r="S167" s="22" t="inlineStr">
@@ -18273,13 +18225,13 @@
         </is>
       </c>
       <c r="O169" s="31" t="n">
-        <v>-1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="P169" s="31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q169" s="31" t="n">
-        <v>0.82</v>
+        <v>1.96</v>
       </c>
       <c r="R169" s="49" t="n"/>
       <c r="S169" s="22" t="inlineStr">
@@ -18394,13 +18346,13 @@
       </c>
       <c r="N170" s="2" t="n"/>
       <c r="O170" s="31" t="n">
-        <v>-2.5</v>
+        <v>-0.3</v>
       </c>
       <c r="P170" s="31" t="n">
         <v>18</v>
       </c>
       <c r="Q170" s="31" t="n">
-        <v>7.64</v>
+        <v>8.15</v>
       </c>
       <c r="R170" s="49" t="n"/>
       <c r="S170" s="22" t="inlineStr">
@@ -18515,13 +18467,13 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P171" s="31" t="n">
-        <v>28.3</v>
+        <v>29</v>
       </c>
       <c r="Q171" s="31" t="n">
-        <v>23.52</v>
+        <v>24.31</v>
       </c>
       <c r="R171" s="49" t="n"/>
       <c r="S171" s="22" t="inlineStr">
@@ -18628,13 +18580,13 @@
       </c>
       <c r="N172" s="2" t="n"/>
       <c r="O172" s="31" t="n">
-        <v>20.4</v>
+        <v>22.4</v>
       </c>
       <c r="P172" s="31" t="n">
-        <v>27.4</v>
+        <v>26</v>
       </c>
       <c r="Q172" s="31" t="n">
-        <v>22.85</v>
+        <v>23.74</v>
       </c>
       <c r="R172" s="49" t="n"/>
       <c r="S172" s="22" t="inlineStr">
@@ -18745,13 +18697,13 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="31" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="P173" s="31" t="n">
-        <v>33.7</v>
+        <v>36</v>
       </c>
       <c r="Q173" s="31" t="n">
-        <v>27.63</v>
+        <v>28.29</v>
       </c>
       <c r="R173" s="49" t="n"/>
       <c r="S173" s="22" t="inlineStr">
@@ -18858,13 +18810,13 @@
       </c>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="31" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="P174" s="31" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="Q174" s="31" t="n">
-        <v>16.11</v>
+        <v>15.75</v>
       </c>
       <c r="R174" s="49" t="n"/>
       <c r="S174" s="22" t="inlineStr">
@@ -19066,13 +19018,13 @@
         </is>
       </c>
       <c r="O176" s="31" t="n">
-        <v>-8.1</v>
+        <v>-7.5</v>
       </c>
       <c r="P176" s="31" t="n">
-        <v>-1.2</v>
+        <v>0.8</v>
       </c>
       <c r="Q176" s="31" t="n">
-        <v>-5.3</v>
+        <v>-4</v>
       </c>
       <c r="R176" s="49" t="n"/>
       <c r="S176" s="22" t="inlineStr">
@@ -19175,14 +19127,12 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="31" t="n">
-        <v>-6.9</v>
+        <v>-6.4</v>
       </c>
       <c r="P177" s="31" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="Q177" s="31" t="n">
-        <v>-4.9</v>
-      </c>
+        <v>4.7</v>
+      </c>
+      <c r="Q177" s="31" t="n"/>
       <c r="R177" s="49" t="n"/>
       <c r="S177" s="22" t="inlineStr">
         <is>
@@ -19490,14 +19440,12 @@
       </c>
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="31" t="n">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
       <c r="P180" s="31" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q180" s="31" t="n">
-        <v>12.06</v>
-      </c>
+        <v>19.6</v>
+      </c>
+      <c r="Q180" s="31" t="n"/>
       <c r="R180" s="49" t="inlineStr">
         <is>
           <t>2010-01-05</t>
@@ -19603,10 +19551,10 @@
       </c>
       <c r="N181" s="2" t="n"/>
       <c r="O181" s="31" t="n">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="P181" s="31" t="n">
-        <v>18.4</v>
+        <v>12</v>
       </c>
       <c r="Q181" s="31" t="n"/>
       <c r="R181" s="49" t="n"/>
@@ -19709,12 +19657,8 @@
         </is>
       </c>
       <c r="N182" s="3" t="n"/>
-      <c r="O182" s="31" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="P182" s="31" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="O182" s="31" t="n"/>
+      <c r="P182" s="31" t="n"/>
       <c r="Q182" s="31" t="n"/>
       <c r="R182" s="49" t="n"/>
       <c r="S182" s="22" t="inlineStr">
@@ -19825,13 +19769,13 @@
         </is>
       </c>
       <c r="O183" s="31" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="P183" s="31" t="n">
-        <v>12.3</v>
+        <v>10.4</v>
       </c>
       <c r="Q183" s="31" t="n">
-        <v>8.16</v>
+        <v>5.89</v>
       </c>
       <c r="R183" s="49" t="n"/>
       <c r="S183" s="22" t="inlineStr">
@@ -20760,12 +20704,14 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="31" t="n">
-        <v>-5</v>
+        <v>-12.7</v>
       </c>
       <c r="P192" s="31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q192" s="31" t="n"/>
+        <v>11.3</v>
+      </c>
+      <c r="Q192" s="31" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="R192" s="49" t="n"/>
       <c r="S192" s="22" t="inlineStr">
         <is>
@@ -20871,10 +20817,10 @@
         </is>
       </c>
       <c r="O193" s="31" t="n">
-        <v>-2.5</v>
+        <v>-8.1</v>
       </c>
       <c r="P193" s="31" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="Q193" s="31" t="n"/>
       <c r="R193" s="49" t="n"/>
@@ -20982,10 +20928,10 @@
       </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="31" t="n">
-        <v>-3.4</v>
+        <v>-9.5</v>
       </c>
       <c r="P194" s="31" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q194" s="31" t="n"/>
       <c r="R194" s="49" t="inlineStr">
@@ -21302,8 +21248,12 @@
           <t>⚡🧊</t>
         </is>
       </c>
-      <c r="O197" s="31" t="n"/>
-      <c r="P197" s="31" t="n"/>
+      <c r="O197" s="31" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="P197" s="31" t="n">
+        <v>13.7</v>
+      </c>
       <c r="Q197" s="31" t="n"/>
       <c r="R197" s="49" t="n"/>
       <c r="S197" s="22" t="inlineStr">
@@ -21525,10 +21475,10 @@
       </c>
       <c r="N199" s="2" t="n"/>
       <c r="O199" s="31" t="n">
-        <v>-5.2</v>
+        <v>-4.6</v>
       </c>
       <c r="P199" s="31" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
       <c r="Q199" s="31" t="n"/>
       <c r="R199" s="49" t="n"/>
@@ -21634,7 +21584,7 @@
       </c>
       <c r="N200" s="2" t="n"/>
       <c r="O200" s="31" t="n">
-        <v>-32.6</v>
+        <v>-28.4</v>
       </c>
       <c r="P200" s="31" t="n"/>
       <c r="Q200" s="31" t="n"/>
@@ -22198,13 +22148,13 @@
       </c>
       <c r="N206" s="2" t="n"/>
       <c r="O206" s="31" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P206" s="31" t="n">
-        <v>21</v>
+        <v>23.2</v>
       </c>
       <c r="Q206" s="31" t="n">
-        <v>18.52</v>
+        <v>18.66</v>
       </c>
       <c r="R206" s="49" t="n"/>
       <c r="S206" s="22" t="inlineStr">
@@ -22602,13 +22552,13 @@
       </c>
       <c r="N210" s="2" t="n"/>
       <c r="O210" s="31" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="P210" s="31" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="Q210" s="31" t="n">
-        <v>9.44</v>
+        <v>10.41</v>
       </c>
       <c r="R210" s="49" t="n"/>
       <c r="S210" s="22" t="inlineStr">
@@ -22812,13 +22762,13 @@
       </c>
       <c r="N212" s="2" t="n"/>
       <c r="O212" s="31" t="n">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="P212" s="31" t="n">
-        <v>13.9</v>
+        <v>11.5</v>
       </c>
       <c r="Q212" s="31" t="n">
-        <v>9.699999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="R212" s="49" t="n"/>
       <c r="S212" s="22" t="inlineStr">
@@ -23218,13 +23168,13 @@
       </c>
       <c r="N216" s="2" t="n"/>
       <c r="O216" s="31" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="P216" s="31" t="n">
-        <v>15</v>
+        <v>11.3</v>
       </c>
       <c r="Q216" s="31" t="n">
-        <v>9.710000000000001</v>
+        <v>6.59</v>
       </c>
       <c r="R216" s="49" t="n"/>
       <c r="S216" s="22" t="inlineStr">
@@ -23521,13 +23471,13 @@
       </c>
       <c r="N219" s="2" t="n"/>
       <c r="O219" s="31" t="n">
-        <v>13.9</v>
+        <v>10.2</v>
       </c>
       <c r="P219" s="31" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="Q219" s="31" t="n">
-        <v>15.31</v>
+        <v>13.68</v>
       </c>
       <c r="R219" s="49" t="n"/>
       <c r="S219" s="22" t="inlineStr">
@@ -23634,13 +23584,13 @@
       </c>
       <c r="N220" s="2" t="n"/>
       <c r="O220" s="31" t="n">
-        <v>8.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="P220" s="31" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="Q220" s="31" t="n">
-        <v>11.78</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="R220" s="49" t="n"/>
       <c r="S220" s="22" t="inlineStr">
@@ -24034,13 +23984,13 @@
         </is>
       </c>
       <c r="O224" s="31" t="n">
-        <v>-9.5</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="P224" s="31" t="n">
-        <v>15.4</v>
+        <v>13.7</v>
       </c>
       <c r="Q224" s="31" t="n">
-        <v>0.95</v>
+        <v>1.3</v>
       </c>
       <c r="R224" s="49" t="n"/>
       <c r="S224" s="22" t="inlineStr">
@@ -24225,9 +24175,7 @@
         </is>
       </c>
       <c r="N226" s="2" t="n"/>
-      <c r="O226" s="31" t="n">
-        <v>-9.800000000000001</v>
-      </c>
+      <c r="O226" s="31" t="n"/>
       <c r="P226" s="31" t="n"/>
       <c r="Q226" s="31" t="n"/>
       <c r="R226" s="49" t="n"/>
@@ -25340,8 +25288,12 @@
         </is>
       </c>
       <c r="N238" s="2" t="n"/>
-      <c r="O238" s="31" t="n"/>
-      <c r="P238" s="31" t="n"/>
+      <c r="O238" s="31" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="P238" s="31" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Q238" s="31" t="n"/>
       <c r="R238" s="49" t="n"/>
       <c r="S238" s="22" t="n"/>
@@ -26279,13 +26231,13 @@
       </c>
       <c r="N248" s="2" t="n"/>
       <c r="O248" s="31" t="n">
-        <v>-6.3</v>
+        <v>-1.1</v>
       </c>
       <c r="P248" s="31" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="Q248" s="31" t="n">
-        <v>0.21</v>
+        <v>2.1</v>
       </c>
       <c r="R248" s="49" t="n"/>
       <c r="S248" s="22" t="inlineStr">
@@ -26773,10 +26725,10 @@
       </c>
       <c r="N253" s="2" t="n"/>
       <c r="O253" s="31" t="n">
-        <v>-1</v>
+        <v>-1.7</v>
       </c>
       <c r="P253" s="31" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q253" s="31" t="n"/>
       <c r="R253" s="49" t="n"/>
@@ -27154,10 +27106,10 @@
       </c>
       <c r="N257" s="2" t="n"/>
       <c r="O257" s="31" t="n">
-        <v>-79.59999999999999</v>
+        <v>-79.8</v>
       </c>
       <c r="P257" s="31" t="n">
-        <v>-74.3</v>
+        <v>-73.3</v>
       </c>
       <c r="Q257" s="31" t="n"/>
       <c r="R257" s="49" t="n"/>
@@ -27254,7 +27206,9 @@
         </is>
       </c>
       <c r="N258" s="2" t="n"/>
-      <c r="O258" s="31" t="n"/>
+      <c r="O258" s="31" t="n">
+        <v>-81.40000000000001</v>
+      </c>
       <c r="P258" s="31" t="n"/>
       <c r="Q258" s="31" t="n"/>
       <c r="R258" s="49" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -830,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="728"/>
-    <col width="12.59765625" customWidth="1" style="5" min="729" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="729"/>
+    <col width="12.59765625" customWidth="1" style="5" min="730" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>12.39</v>
+        <v>13.22</v>
       </c>
       <c r="R2" s="49" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="49" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>22.2</v>
+        <v>17.6</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="49" t="inlineStr">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>-6.3</v>
+        <v>-5.2</v>
       </c>
       <c r="P6" s="31" t="n">
         <v>18.9</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>6.19</v>
+        <v>6.39</v>
       </c>
       <c r="R6" s="51" t="inlineStr">
         <is>
@@ -1691,13 +1691,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>12.34</v>
+        <v>11.03</v>
       </c>
       <c r="R8" s="49" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1804,13 +1804,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>12.25</v>
+        <v>14.43</v>
       </c>
       <c r="R9" s="49" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>-2.5</v>
+        <v>-0.9</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>21</v>
+        <v>17.9</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>9.35</v>
+        <v>9.08</v>
       </c>
       <c r="R10" s="49" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>-5.9</v>
+        <v>-5.2</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>18.6</v>
+        <v>17.1</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>7.06</v>
+        <v>7.36</v>
       </c>
       <c r="R11" s="49" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>-1.6</v>
+        <v>-0.2</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>21.1</v>
+        <v>20.1</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>8.42</v>
+        <v>9.51</v>
       </c>
       <c r="R12" s="49" t="inlineStr">
         <is>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>-3.6</v>
+        <v>-2.3</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>18.9</v>
+        <v>12.6</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>6.79</v>
+        <v>5.26</v>
       </c>
       <c r="R13" s="49" t="inlineStr">
         <is>
@@ -2397,13 +2397,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>20.7</v>
+        <v>22.1</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>12.7</v>
+        <v>13.86</v>
       </c>
       <c r="R14" s="49" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2518,13 +2518,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>-1.3</v>
+        <v>-2.7</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>12.7</v>
+        <v>8.15</v>
       </c>
       <c r="R15" s="49" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2628,15 +2628,9 @@
         </is>
       </c>
       <c r="N16" s="2" t="n"/>
-      <c r="O16" s="31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P16" s="31" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Q16" s="31" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="O16" s="31" t="n"/>
+      <c r="P16" s="31" t="n"/>
+      <c r="Q16" s="31" t="n"/>
       <c r="R16" s="49" t="n"/>
       <c r="S16" s="22" t="n"/>
       <c r="T16" s="35" t="n"/>
@@ -2825,7 +2819,7 @@
         </is>
       </c>
       <c r="O18" s="31" t="n">
-        <v>-10</v>
+        <v>-8.5</v>
       </c>
       <c r="P18" s="31" t="n"/>
       <c r="Q18" s="31" t="n"/>
@@ -9273,13 +9267,13 @@
         </is>
       </c>
       <c r="O88" s="31" t="n">
-        <v>2.6</v>
+        <v>-3.2</v>
       </c>
       <c r="P88" s="31" t="n">
-        <v>19.6</v>
+        <v>4</v>
       </c>
       <c r="Q88" s="31" t="n">
-        <v>7.65</v>
+        <v>0.39</v>
       </c>
       <c r="R88" s="49" t="inlineStr">
         <is>
@@ -9707,13 +9701,13 @@
         </is>
       </c>
       <c r="O92" s="31" t="n">
-        <v>-8.1</v>
+        <v>-4.8</v>
       </c>
       <c r="P92" s="31" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="Q92" s="31" t="n">
-        <v>1.27</v>
+        <v>2.75</v>
       </c>
       <c r="R92" s="49" t="n"/>
       <c r="S92" s="22" t="inlineStr">
@@ -9829,13 +9823,13 @@
         </is>
       </c>
       <c r="O93" s="31" t="n">
-        <v>-1.5</v>
+        <v>-5.2</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>3.46</v>
+        <v>2.86</v>
       </c>
       <c r="R93" s="49" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -10049,13 +10043,13 @@
         </is>
       </c>
       <c r="O95" s="31" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="P95" s="31" t="n">
-        <v>16</v>
+        <v>11.6</v>
       </c>
       <c r="Q95" s="31" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="R95" s="49" t="n"/>
       <c r="S95" s="22" t="inlineStr">
@@ -10269,13 +10263,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="31" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P97" s="31" t="n">
-        <v>22.2</v>
+        <v>18.7</v>
       </c>
       <c r="Q97" s="31" t="n">
-        <v>13.14</v>
+        <v>12.66</v>
       </c>
       <c r="R97" s="49" t="n"/>
       <c r="S97" s="22" t="inlineStr">
@@ -10497,13 +10491,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="31" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="P99" s="31" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="Q99" s="31" t="n">
-        <v>10.5</v>
+        <v>12.01</v>
       </c>
       <c r="R99" s="49" t="inlineStr">
         <is>
@@ -11021,9 +11015,15 @@
         </is>
       </c>
       <c r="N104" s="2" t="n"/>
-      <c r="O104" s="31" t="n"/>
-      <c r="P104" s="31" t="n"/>
-      <c r="Q104" s="31" t="n"/>
+      <c r="O104" s="31" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="P104" s="31" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Q104" s="31" t="n">
+        <v>12.53</v>
+      </c>
       <c r="R104" s="49" t="n"/>
       <c r="S104" s="22" t="inlineStr">
         <is>
@@ -11129,12 +11129,14 @@
       </c>
       <c r="N105" s="2" t="n"/>
       <c r="O105" s="31" t="n">
-        <v>15.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P105" s="31" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Q105" s="31" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="Q105" s="31" t="n">
+        <v>17.46</v>
+      </c>
       <c r="R105" s="49" t="n"/>
       <c r="S105" s="22" t="inlineStr">
         <is>
@@ -11363,12 +11365,14 @@
       </c>
       <c r="N107" s="2" t="n"/>
       <c r="O107" s="31" t="n">
-        <v>11.8</v>
+        <v>6.8</v>
       </c>
       <c r="P107" s="31" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Q107" s="31" t="n"/>
+        <v>21.5</v>
+      </c>
+      <c r="Q107" s="31" t="n">
+        <v>13.53</v>
+      </c>
       <c r="R107" s="49" t="n"/>
       <c r="S107" s="22" t="inlineStr">
         <is>
@@ -11486,12 +11490,14 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="31" t="n">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="P108" s="31" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Q108" s="31" t="n"/>
+        <v>17.9</v>
+      </c>
+      <c r="Q108" s="31" t="n">
+        <v>11.85</v>
+      </c>
       <c r="R108" s="49" t="n"/>
       <c r="S108" s="22" t="inlineStr">
         <is>
@@ -11822,9 +11828,15 @@
         </is>
       </c>
       <c r="N111" s="2" t="n"/>
-      <c r="O111" s="31" t="n"/>
-      <c r="P111" s="31" t="n"/>
-      <c r="Q111" s="31" t="n"/>
+      <c r="O111" s="31" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="P111" s="31" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q111" s="31" t="n">
+        <v>2.23</v>
+      </c>
       <c r="R111" s="49" t="n"/>
       <c r="S111" s="22" t="inlineStr">
         <is>
@@ -11929,9 +11941,15 @@
         </is>
       </c>
       <c r="N112" s="2" t="n"/>
-      <c r="O112" s="31" t="n"/>
-      <c r="P112" s="31" t="n"/>
-      <c r="Q112" s="31" t="n"/>
+      <c r="O112" s="31" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="P112" s="31" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Q112" s="31" t="n">
+        <v>1.67</v>
+      </c>
       <c r="R112" s="49" t="n"/>
       <c r="S112" s="22" t="inlineStr">
         <is>
@@ -12045,12 +12063,14 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="31" t="n">
-        <v>-6</v>
+        <v>-6.7</v>
       </c>
       <c r="P113" s="31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q113" s="31" t="n"/>
+        <v>12.9</v>
+      </c>
+      <c r="Q113" s="31" t="n">
+        <v>2.39</v>
+      </c>
       <c r="R113" s="49" t="n"/>
       <c r="S113" s="22" t="inlineStr">
         <is>
@@ -12263,13 +12283,13 @@
       </c>
       <c r="N115" s="2" t="n"/>
       <c r="O115" s="31" t="n">
-        <v>-7.6</v>
+        <v>-5.1</v>
       </c>
       <c r="P115" s="31" t="n">
-        <v>11.5</v>
+        <v>13.1</v>
       </c>
       <c r="Q115" s="31" t="n">
-        <v>1.78</v>
+        <v>3.88</v>
       </c>
       <c r="R115" s="49" t="n"/>
       <c r="S115" s="22" t="n"/>
@@ -12388,12 +12408,14 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>-8.699999999999999</v>
+        <v>-7.1</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q116" s="31" t="n"/>
+        <v>12.1</v>
+      </c>
+      <c r="Q116" s="31" t="n">
+        <v>2.08</v>
+      </c>
       <c r="R116" s="49" t="n"/>
       <c r="S116" s="22" t="inlineStr">
         <is>
@@ -13680,12 +13702,14 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="Q128" s="31" t="n"/>
+        <v>36.1</v>
+      </c>
+      <c r="Q128" s="31" t="n">
+        <v>28.82</v>
+      </c>
       <c r="R128" s="49" t="n"/>
       <c r="S128" s="22" t="inlineStr">
         <is>
@@ -13795,12 +13819,14 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>18.3</v>
+        <v>19.6</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="Q129" s="31" t="n"/>
+        <v>28.5</v>
+      </c>
+      <c r="Q129" s="31" t="n">
+        <v>23.84</v>
+      </c>
       <c r="R129" s="49" t="n"/>
       <c r="S129" s="22" t="inlineStr">
         <is>
@@ -14021,12 +14047,14 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="Q131" s="31" t="n"/>
+        <v>23.6</v>
+      </c>
+      <c r="Q131" s="31" t="n">
+        <v>15.69</v>
+      </c>
       <c r="R131" s="49" t="n"/>
       <c r="S131" s="22" t="inlineStr">
         <is>
@@ -14144,12 +14172,14 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="31" t="n">
-        <v>21</v>
+        <v>18.9</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="Q132" s="31" t="n"/>
+        <v>30.6</v>
+      </c>
+      <c r="Q132" s="31" t="n">
+        <v>24.1</v>
+      </c>
       <c r="R132" s="49" t="n"/>
       <c r="S132" s="22" t="inlineStr">
         <is>
@@ -14255,12 +14285,14 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>16.3</v>
+        <v>10.9</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Q133" s="31" t="n"/>
+        <v>25.5</v>
+      </c>
+      <c r="Q133" s="31" t="n">
+        <v>17.21</v>
+      </c>
       <c r="R133" s="49" t="n"/>
       <c r="S133" s="22" t="inlineStr">
         <is>
@@ -14374,12 +14406,14 @@
       </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="31" t="n">
-        <v>16.5</v>
+        <v>17.1</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Q134" s="31" t="n"/>
+        <v>23.1</v>
+      </c>
+      <c r="Q134" s="31" t="n">
+        <v>19.35</v>
+      </c>
       <c r="R134" s="49" t="n"/>
       <c r="S134" s="22" t="inlineStr">
         <is>
@@ -14493,12 +14527,14 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="31" t="n">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="P135" s="31" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="Q135" s="31" t="n"/>
+        <v>22.3</v>
+      </c>
+      <c r="Q135" s="31" t="n">
+        <v>11.9</v>
+      </c>
       <c r="R135" s="49" t="n"/>
       <c r="S135" s="22" t="inlineStr">
         <is>
@@ -14612,12 +14648,14 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="Q136" s="31" t="n"/>
+        <v>27.9</v>
+      </c>
+      <c r="Q136" s="31" t="n">
+        <v>24.16</v>
+      </c>
       <c r="R136" s="49" t="n"/>
       <c r="S136" s="22" t="inlineStr">
         <is>
@@ -14727,12 +14765,14 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q137" s="31" t="n"/>
+        <v>25.9</v>
+      </c>
+      <c r="Q137" s="31" t="n">
+        <v>22.49</v>
+      </c>
       <c r="R137" s="49" t="n"/>
       <c r="S137" s="22" t="inlineStr">
         <is>
@@ -14842,12 +14882,14 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="Q138" s="31" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="Q138" s="31" t="n">
+        <v>20.81</v>
+      </c>
       <c r="R138" s="49" t="n"/>
       <c r="S138" s="22" t="inlineStr">
         <is>
@@ -15064,12 +15106,14 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="Q140" s="31" t="n"/>
+        <v>29.1</v>
+      </c>
+      <c r="Q140" s="31" t="n">
+        <v>24.73</v>
+      </c>
       <c r="R140" s="49" t="n"/>
       <c r="S140" s="22" t="inlineStr">
         <is>
@@ -15182,9 +15226,11 @@
         <v>25.4</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="Q141" s="31" t="n"/>
+        <v>32.1</v>
+      </c>
+      <c r="Q141" s="31" t="n">
+        <v>28.18</v>
+      </c>
       <c r="R141" s="49" t="n"/>
       <c r="S141" s="22" t="inlineStr">
         <is>
@@ -15294,12 +15340,14 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="31" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="P142" s="31" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="Q142" s="31" t="n"/>
+        <v>25.6</v>
+      </c>
+      <c r="Q142" s="31" t="n">
+        <v>23.95</v>
+      </c>
       <c r="R142" s="49" t="n"/>
       <c r="S142" s="22" t="inlineStr">
         <is>
@@ -15409,12 +15457,14 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="Q143" s="31" t="n"/>
+        <v>28.1</v>
+      </c>
+      <c r="Q143" s="31" t="n">
+        <v>24.77</v>
+      </c>
       <c r="R143" s="49" t="n"/>
       <c r="S143" s="22" t="inlineStr">
         <is>
@@ -15524,12 +15574,14 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="Q144" s="31" t="n"/>
+        <v>29.9</v>
+      </c>
+      <c r="Q144" s="31" t="n">
+        <v>26.29</v>
+      </c>
       <c r="R144" s="49" t="n"/>
       <c r="S144" s="22" t="inlineStr">
         <is>
@@ -15742,12 +15794,14 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="31" t="n">
-        <v>26.5</v>
+        <v>24.6</v>
       </c>
       <c r="P146" s="31" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="Q146" s="31" t="n"/>
+        <v>31.2</v>
+      </c>
+      <c r="Q146" s="31" t="n">
+        <v>27.4</v>
+      </c>
       <c r="R146" s="49" t="n"/>
       <c r="S146" s="22" t="inlineStr">
         <is>
@@ -15857,12 +15911,14 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="Q147" s="31" t="n"/>
+        <v>33.9</v>
+      </c>
+      <c r="Q147" s="31" t="n">
+        <v>29.24</v>
+      </c>
       <c r="R147" s="49" t="n"/>
       <c r="S147" s="22" t="inlineStr">
         <is>
@@ -16174,12 +16230,14 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="Q150" s="31" t="n"/>
+        <v>30.2</v>
+      </c>
+      <c r="Q150" s="31" t="n">
+        <v>28.34</v>
+      </c>
       <c r="R150" s="49" t="n"/>
       <c r="S150" s="22" t="inlineStr">
         <is>
@@ -16281,12 +16339,14 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="Q151" s="31" t="n"/>
+        <v>35.2</v>
+      </c>
+      <c r="Q151" s="31" t="n">
+        <v>29.91</v>
+      </c>
       <c r="R151" s="49" t="n"/>
       <c r="S151" s="22" t="inlineStr">
         <is>
@@ -16396,12 +16456,14 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>14.1</v>
+        <v>15.7</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="Q152" s="31" t="n"/>
+        <v>26.9</v>
+      </c>
+      <c r="Q152" s="31" t="n">
+        <v>20.76</v>
+      </c>
       <c r="R152" s="49" t="n"/>
       <c r="S152" s="22" t="inlineStr">
         <is>
@@ -16511,12 +16573,14 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="31" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="P153" s="31" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="Q153" s="31" t="n"/>
+        <v>31.1</v>
+      </c>
+      <c r="Q153" s="31" t="n">
+        <v>24.95</v>
+      </c>
       <c r="R153" s="49" t="n"/>
       <c r="S153" s="22" t="inlineStr">
         <is>
@@ -16626,12 +16690,14 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>23.1</v>
+        <v>22.3</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="Q154" s="31" t="n"/>
+        <v>26.8</v>
+      </c>
+      <c r="Q154" s="31" t="n">
+        <v>23.79</v>
+      </c>
       <c r="R154" s="49" t="n"/>
       <c r="S154" s="22" t="inlineStr">
         <is>
@@ -16832,12 +16898,14 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="31" t="n">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
       <c r="P156" s="31" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q156" s="31" t="n"/>
+        <v>28.2</v>
+      </c>
+      <c r="Q156" s="31" t="n">
+        <v>23.2</v>
+      </c>
       <c r="R156" s="49" t="n"/>
       <c r="S156" s="22" t="inlineStr">
         <is>
@@ -16951,12 +17019,14 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="31" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="P157" s="31" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Q157" s="31" t="n"/>
+        <v>22.2</v>
+      </c>
+      <c r="Q157" s="31" t="n">
+        <v>14.86</v>
+      </c>
       <c r="R157" s="49" t="n"/>
       <c r="S157" s="22" t="inlineStr">
         <is>
@@ -17537,14 +17607,12 @@
       </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="31" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="P163" s="31" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q163" s="31" t="n">
-        <v>2.89</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="Q163" s="31" t="n"/>
       <c r="R163" s="49" t="n"/>
       <c r="S163" s="22" t="inlineStr">
         <is>
@@ -17654,13 +17722,13 @@
         </is>
       </c>
       <c r="O164" s="31" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="P164" s="31" t="n">
-        <v>11.9</v>
+        <v>10</v>
       </c>
       <c r="Q164" s="31" t="n">
-        <v>5.04</v>
+        <v>3.75</v>
       </c>
       <c r="R164" s="49" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -17767,13 +17835,13 @@
       </c>
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="31" t="n">
-        <v>20.4</v>
+        <v>19.7</v>
       </c>
       <c r="P165" s="31" t="n">
-        <v>28.2</v>
+        <v>29.7</v>
       </c>
       <c r="Q165" s="31" t="n">
-        <v>23.51</v>
+        <v>24.25</v>
       </c>
       <c r="R165" s="49" t="n"/>
       <c r="S165" s="22" t="inlineStr">
@@ -17872,13 +17940,13 @@
       </c>
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="31" t="n">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
       <c r="P166" s="31" t="n">
-        <v>29.4</v>
+        <v>29.9</v>
       </c>
       <c r="Q166" s="31" t="n">
-        <v>26.49</v>
+        <v>25.73</v>
       </c>
       <c r="R166" s="49" t="n"/>
       <c r="S166" s="22" t="inlineStr">
@@ -17981,13 +18049,13 @@
       </c>
       <c r="N167" s="2" t="n"/>
       <c r="O167" s="31" t="n">
-        <v>13.3</v>
+        <v>9.9</v>
       </c>
       <c r="P167" s="31" t="n">
-        <v>20.3</v>
+        <v>25.3</v>
       </c>
       <c r="Q167" s="31" t="n">
-        <v>16.1</v>
+        <v>16.56</v>
       </c>
       <c r="R167" s="49" t="n"/>
       <c r="S167" s="22" t="inlineStr">
@@ -18225,13 +18293,13 @@
         </is>
       </c>
       <c r="O169" s="31" t="n">
-        <v>-1.7</v>
+        <v>-2.7</v>
       </c>
       <c r="P169" s="31" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Q169" s="31" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="R169" s="49" t="n"/>
       <c r="S169" s="22" t="inlineStr">
@@ -18346,13 +18414,13 @@
       </c>
       <c r="N170" s="2" t="n"/>
       <c r="O170" s="31" t="n">
-        <v>-0.3</v>
+        <v>-2.2</v>
       </c>
       <c r="P170" s="31" t="n">
-        <v>18</v>
+        <v>16.8</v>
       </c>
       <c r="Q170" s="31" t="n">
-        <v>8.15</v>
+        <v>6.18</v>
       </c>
       <c r="R170" s="49" t="n"/>
       <c r="S170" s="22" t="inlineStr">
@@ -18467,13 +18535,13 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="31" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="P171" s="31" t="n">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="Q171" s="31" t="n">
-        <v>24.31</v>
+        <v>23.53</v>
       </c>
       <c r="R171" s="49" t="n"/>
       <c r="S171" s="22" t="inlineStr">
@@ -18580,13 +18648,13 @@
       </c>
       <c r="N172" s="2" t="n"/>
       <c r="O172" s="31" t="n">
-        <v>22.4</v>
+        <v>20.9</v>
       </c>
       <c r="P172" s="31" t="n">
-        <v>26</v>
+        <v>23.4</v>
       </c>
       <c r="Q172" s="31" t="n">
-        <v>23.74</v>
+        <v>22.21</v>
       </c>
       <c r="R172" s="49" t="n"/>
       <c r="S172" s="22" t="inlineStr">
@@ -18697,13 +18765,13 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="31" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="P173" s="31" t="n">
-        <v>36</v>
+        <v>37.1</v>
       </c>
       <c r="Q173" s="31" t="n">
-        <v>28.29</v>
+        <v>29.09</v>
       </c>
       <c r="R173" s="49" t="n"/>
       <c r="S173" s="22" t="inlineStr">
@@ -18810,13 +18878,13 @@
       </c>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="31" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="P174" s="31" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="Q174" s="31" t="n">
-        <v>15.75</v>
+        <v>15.83</v>
       </c>
       <c r="R174" s="49" t="n"/>
       <c r="S174" s="22" t="inlineStr">
@@ -19018,13 +19086,13 @@
         </is>
       </c>
       <c r="O176" s="31" t="n">
-        <v>-7.5</v>
+        <v>-6.3</v>
       </c>
       <c r="P176" s="31" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q176" s="31" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="R176" s="49" t="n"/>
       <c r="S176" s="22" t="inlineStr">
@@ -19126,12 +19194,8 @@
         </is>
       </c>
       <c r="N177" s="2" t="n"/>
-      <c r="O177" s="31" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="P177" s="31" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="O177" s="31" t="n"/>
+      <c r="P177" s="31" t="n"/>
       <c r="Q177" s="31" t="n"/>
       <c r="R177" s="49" t="n"/>
       <c r="S177" s="22" t="inlineStr">
@@ -19233,9 +19297,15 @@
         </is>
       </c>
       <c r="N178" s="2" t="n"/>
-      <c r="O178" s="31" t="n"/>
-      <c r="P178" s="31" t="n"/>
-      <c r="Q178" s="31" t="n"/>
+      <c r="O178" s="31" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="P178" s="31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q178" s="31" t="n">
+        <v>-3.2</v>
+      </c>
       <c r="R178" s="49" t="n"/>
       <c r="S178" s="22" t="n"/>
       <c r="T178" s="35" t="n"/>
@@ -19440,12 +19510,14 @@
       </c>
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="31" t="n">
-        <v>7.1</v>
+        <v>-0.3</v>
       </c>
       <c r="P180" s="31" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Q180" s="31" t="n"/>
+        <v>21.2</v>
+      </c>
+      <c r="Q180" s="31" t="n">
+        <v>9.890000000000001</v>
+      </c>
       <c r="R180" s="49" t="inlineStr">
         <is>
           <t>2010-01-05</t>
@@ -19551,7 +19623,7 @@
       </c>
       <c r="N181" s="2" t="n"/>
       <c r="O181" s="31" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="P181" s="31" t="n">
         <v>12</v>
@@ -19769,13 +19841,13 @@
         </is>
       </c>
       <c r="O183" s="31" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="P183" s="31" t="n">
-        <v>10.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q183" s="31" t="n">
-        <v>5.89</v>
+        <v>3.2</v>
       </c>
       <c r="R183" s="49" t="n"/>
       <c r="S183" s="22" t="inlineStr">
@@ -20704,14 +20776,12 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="31" t="n">
-        <v>-12.7</v>
+        <v>-12</v>
       </c>
       <c r="P192" s="31" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="Q192" s="31" t="n">
-        <v>-1.4</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="Q192" s="31" t="n"/>
       <c r="R192" s="49" t="n"/>
       <c r="S192" s="22" t="inlineStr">
         <is>
@@ -20817,10 +20887,10 @@
         </is>
       </c>
       <c r="O193" s="31" t="n">
-        <v>-8.1</v>
+        <v>-11.1</v>
       </c>
       <c r="P193" s="31" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="Q193" s="31" t="n"/>
       <c r="R193" s="49" t="n"/>
@@ -20928,10 +20998,10 @@
       </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="31" t="n">
-        <v>-9.5</v>
+        <v>-10</v>
       </c>
       <c r="P194" s="31" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="Q194" s="31" t="n"/>
       <c r="R194" s="49" t="inlineStr">
@@ -21249,10 +21319,10 @@
         </is>
       </c>
       <c r="O197" s="31" t="n">
-        <v>-3.9</v>
+        <v>0.8</v>
       </c>
       <c r="P197" s="31" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="Q197" s="31" t="n"/>
       <c r="R197" s="49" t="n"/>
@@ -21475,10 +21545,10 @@
       </c>
       <c r="N199" s="2" t="n"/>
       <c r="O199" s="31" t="n">
-        <v>-4.6</v>
+        <v>-1.7</v>
       </c>
       <c r="P199" s="31" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="Q199" s="31" t="n"/>
       <c r="R199" s="49" t="n"/>
@@ -21584,7 +21654,7 @@
       </c>
       <c r="N200" s="2" t="n"/>
       <c r="O200" s="31" t="n">
-        <v>-28.4</v>
+        <v>-23.3</v>
       </c>
       <c r="P200" s="31" t="n"/>
       <c r="Q200" s="31" t="n"/>
@@ -22148,13 +22218,13 @@
       </c>
       <c r="N206" s="2" t="n"/>
       <c r="O206" s="31" t="n">
-        <v>16.6</v>
+        <v>13.7</v>
       </c>
       <c r="P206" s="31" t="n">
-        <v>23.2</v>
+        <v>19.4</v>
       </c>
       <c r="Q206" s="31" t="n">
-        <v>18.66</v>
+        <v>16.95</v>
       </c>
       <c r="R206" s="49" t="n"/>
       <c r="S206" s="22" t="inlineStr">
@@ -22552,13 +22622,13 @@
       </c>
       <c r="N210" s="2" t="n"/>
       <c r="O210" s="31" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="P210" s="31" t="n">
-        <v>14.8</v>
+        <v>16.7</v>
       </c>
       <c r="Q210" s="31" t="n">
-        <v>10.41</v>
+        <v>10.2</v>
       </c>
       <c r="R210" s="49" t="n"/>
       <c r="S210" s="22" t="inlineStr">
@@ -22762,13 +22832,13 @@
       </c>
       <c r="N212" s="2" t="n"/>
       <c r="O212" s="31" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P212" s="31" t="n">
-        <v>11.5</v>
+        <v>12.6</v>
       </c>
       <c r="Q212" s="31" t="n">
-        <v>9.380000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="R212" s="49" t="n"/>
       <c r="S212" s="22" t="inlineStr">
@@ -23168,13 +23238,13 @@
       </c>
       <c r="N216" s="2" t="n"/>
       <c r="O216" s="31" t="n">
-        <v>4.7</v>
+        <v>-0.4</v>
       </c>
       <c r="P216" s="31" t="n">
-        <v>11.3</v>
+        <v>7.3</v>
       </c>
       <c r="Q216" s="31" t="n">
-        <v>6.59</v>
+        <v>4.19</v>
       </c>
       <c r="R216" s="49" t="n"/>
       <c r="S216" s="22" t="inlineStr">
@@ -23471,13 +23541,13 @@
       </c>
       <c r="N219" s="2" t="n"/>
       <c r="O219" s="31" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="P219" s="31" t="n">
-        <v>16.5</v>
+        <v>14.4</v>
       </c>
       <c r="Q219" s="31" t="n">
-        <v>13.68</v>
+        <v>12.64</v>
       </c>
       <c r="R219" s="49" t="n"/>
       <c r="S219" s="22" t="inlineStr">
@@ -23584,13 +23654,13 @@
       </c>
       <c r="N220" s="2" t="n"/>
       <c r="O220" s="31" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="P220" s="31" t="n">
-        <v>16.2</v>
+        <v>17.5</v>
       </c>
       <c r="Q220" s="31" t="n">
-        <v>9.619999999999999</v>
+        <v>11.57</v>
       </c>
       <c r="R220" s="49" t="n"/>
       <c r="S220" s="22" t="inlineStr">
@@ -23984,13 +24054,13 @@
         </is>
       </c>
       <c r="O224" s="31" t="n">
-        <v>-9.800000000000001</v>
+        <v>-11.8</v>
       </c>
       <c r="P224" s="31" t="n">
-        <v>13.7</v>
+        <v>12.8</v>
       </c>
       <c r="Q224" s="31" t="n">
-        <v>1.3</v>
+        <v>-0.68</v>
       </c>
       <c r="R224" s="49" t="n"/>
       <c r="S224" s="22" t="inlineStr">
@@ -24175,7 +24245,9 @@
         </is>
       </c>
       <c r="N226" s="2" t="n"/>
-      <c r="O226" s="31" t="n"/>
+      <c r="O226" s="31" t="n">
+        <v>-10.2</v>
+      </c>
       <c r="P226" s="31" t="n"/>
       <c r="Q226" s="31" t="n"/>
       <c r="R226" s="49" t="n"/>
@@ -25288,12 +25360,8 @@
         </is>
       </c>
       <c r="N238" s="2" t="n"/>
-      <c r="O238" s="31" t="n">
-        <v>-14.7</v>
-      </c>
-      <c r="P238" s="31" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="O238" s="31" t="n"/>
+      <c r="P238" s="31" t="n"/>
       <c r="Q238" s="31" t="n"/>
       <c r="R238" s="49" t="n"/>
       <c r="S238" s="22" t="n"/>
@@ -26231,13 +26299,13 @@
       </c>
       <c r="N248" s="2" t="n"/>
       <c r="O248" s="31" t="n">
-        <v>-1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="P248" s="31" t="n">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="Q248" s="31" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R248" s="49" t="n"/>
       <c r="S248" s="22" t="inlineStr">
@@ -26725,10 +26793,10 @@
       </c>
       <c r="N253" s="2" t="n"/>
       <c r="O253" s="31" t="n">
-        <v>-1.7</v>
+        <v>-4.5</v>
       </c>
       <c r="P253" s="31" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q253" s="31" t="n"/>
       <c r="R253" s="49" t="n"/>
@@ -27106,10 +27174,10 @@
       </c>
       <c r="N257" s="2" t="n"/>
       <c r="O257" s="31" t="n">
-        <v>-79.8</v>
+        <v>-78.2</v>
       </c>
       <c r="P257" s="31" t="n">
-        <v>-73.3</v>
+        <v>-72.3</v>
       </c>
       <c r="Q257" s="31" t="n"/>
       <c r="R257" s="49" t="n"/>
@@ -27206,9 +27274,7 @@
         </is>
       </c>
       <c r="N258" s="2" t="n"/>
-      <c r="O258" s="31" t="n">
-        <v>-81.40000000000001</v>
-      </c>
+      <c r="O258" s="31" t="n"/>
       <c r="P258" s="31" t="n"/>
       <c r="Q258" s="31" t="n"/>
       <c r="R258" s="49" t="n"/>
@@ -28198,8 +28264,12 @@
         </is>
       </c>
       <c r="N268" s="2" t="n"/>
-      <c r="O268" s="31" t="n"/>
-      <c r="P268" s="31" t="n"/>
+      <c r="O268" s="31" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="P268" s="31" t="n">
+        <v>12.2</v>
+      </c>
       <c r="Q268" s="31" t="n"/>
       <c r="R268" s="49" t="n"/>
       <c r="S268" s="22" t="inlineStr">
@@ -28301,9 +28371,15 @@
         </is>
       </c>
       <c r="N269" s="2" t="n"/>
-      <c r="O269" s="31" t="n"/>
-      <c r="P269" s="31" t="n"/>
-      <c r="Q269" s="31" t="n"/>
+      <c r="O269" s="31" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="P269" s="31" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q269" s="31" t="n">
+        <v>2.01</v>
+      </c>
       <c r="R269" s="49" t="n"/>
       <c r="S269" s="22" t="inlineStr">
         <is>
@@ -32285,8 +32361,12 @@
         </is>
       </c>
       <c r="N309" s="2" t="n"/>
-      <c r="O309" s="31" t="n"/>
-      <c r="P309" s="31" t="n"/>
+      <c r="O309" s="31" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="P309" s="31" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Q309" s="31" t="n"/>
       <c r="R309" s="49" t="n"/>
       <c r="S309" s="22" t="inlineStr">
@@ -32578,8 +32658,12 @@
         </is>
       </c>
       <c r="N312" s="2" t="n"/>
-      <c r="O312" s="31" t="n"/>
-      <c r="P312" s="31" t="n"/>
+      <c r="O312" s="31" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="P312" s="31" t="n">
+        <v>12.8</v>
+      </c>
       <c r="Q312" s="31" t="n"/>
       <c r="R312" s="49" t="n"/>
       <c r="S312" s="22" t="inlineStr">

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -830,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="729"/>
-    <col width="12.59765625" customWidth="1" style="5" min="730" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="731"/>
+    <col width="12.59765625" customWidth="1" style="5" min="732" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>22.6</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>13.22</v>
+        <v>11.16</v>
       </c>
       <c r="R2" s="49" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>21.5</v>
+        <v>17.4</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="49" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="49" t="inlineStr">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>-5.2</v>
+        <v>3.4</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>18.9</v>
+        <v>11.8</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>6.39</v>
+        <v>4.95</v>
       </c>
       <c r="R6" s="51" t="inlineStr">
         <is>
@@ -1691,13 +1691,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>20.4</v>
+        <v>14.8</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>11.03</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="R8" s="49" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1804,13 +1804,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>22.6</v>
+        <v>19.3</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>14.43</v>
+        <v>11.33</v>
       </c>
       <c r="R9" s="49" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>17.9</v>
+        <v>16.9</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>9.08</v>
+        <v>8</v>
       </c>
       <c r="R10" s="49" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>-5.2</v>
+        <v>-1.9</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>17.1</v>
+        <v>12.9</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>7.36</v>
+        <v>5.32</v>
       </c>
       <c r="R11" s="49" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>-0.2</v>
+        <v>3.1</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>20.1</v>
+        <v>11.9</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>9.51</v>
+        <v>7.74</v>
       </c>
       <c r="R12" s="49" t="inlineStr">
         <is>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>-2.3</v>
+        <v>-0.1</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>5.26</v>
+        <v>5.95</v>
       </c>
       <c r="R13" s="49" t="inlineStr">
         <is>
@@ -2397,13 +2397,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>22.1</v>
+        <v>12</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>13.86</v>
+        <v>7.6</v>
       </c>
       <c r="R14" s="49" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2518,13 +2518,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>-2.7</v>
+        <v>-4.4</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>20.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>8.15</v>
+        <v>3.59</v>
       </c>
       <c r="R15" s="49" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2818,9 +2818,7 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O18" s="31" t="n">
-        <v>-8.5</v>
-      </c>
+      <c r="O18" s="31" t="n"/>
       <c r="P18" s="31" t="n"/>
       <c r="Q18" s="31" t="n"/>
       <c r="R18" s="49" t="n"/>
@@ -4132,8 +4130,12 @@
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
-      <c r="O32" s="31" t="n"/>
-      <c r="P32" s="31" t="n"/>
+      <c r="O32" s="31" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="P32" s="31" t="n">
+        <v>6.7</v>
+      </c>
       <c r="Q32" s="31" t="n"/>
       <c r="R32" s="49" t="n"/>
       <c r="S32" s="22" t="n"/>
@@ -9267,13 +9269,13 @@
         </is>
       </c>
       <c r="O88" s="31" t="n">
-        <v>-3.2</v>
+        <v>-10.4</v>
       </c>
       <c r="P88" s="31" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="Q88" s="31" t="n">
-        <v>0.39</v>
+        <v>-1.86</v>
       </c>
       <c r="R88" s="49" t="inlineStr">
         <is>
@@ -9701,13 +9703,13 @@
         </is>
       </c>
       <c r="O92" s="31" t="n">
-        <v>-4.8</v>
+        <v>-6.6</v>
       </c>
       <c r="P92" s="31" t="n">
-        <v>13</v>
+        <v>15.4</v>
       </c>
       <c r="Q92" s="31" t="n">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="R92" s="49" t="n"/>
       <c r="S92" s="22" t="inlineStr">
@@ -9823,13 +9825,13 @@
         </is>
       </c>
       <c r="O93" s="31" t="n">
-        <v>-5.2</v>
+        <v>-7.1</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>12.2</v>
+        <v>15</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>2.86</v>
+        <v>3.21</v>
       </c>
       <c r="R93" s="49" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -10043,13 +10045,13 @@
         </is>
       </c>
       <c r="O95" s="31" t="n">
-        <v>4.4</v>
+        <v>-3</v>
       </c>
       <c r="P95" s="31" t="n">
-        <v>11.6</v>
+        <v>17.4</v>
       </c>
       <c r="Q95" s="31" t="n">
-        <v>7.7</v>
+        <v>5.49</v>
       </c>
       <c r="R95" s="49" t="n"/>
       <c r="S95" s="22" t="inlineStr">
@@ -10263,13 +10265,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="P97" s="31" t="n">
-        <v>18.7</v>
+        <v>19.3</v>
       </c>
       <c r="Q97" s="31" t="n">
-        <v>12.66</v>
+        <v>10.89</v>
       </c>
       <c r="R97" s="49" t="n"/>
       <c r="S97" s="22" t="inlineStr">
@@ -10491,13 +10493,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="31" t="n">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="P99" s="31" t="n">
-        <v>19.4</v>
+        <v>15.8</v>
       </c>
       <c r="Q99" s="31" t="n">
-        <v>12.01</v>
+        <v>9.07</v>
       </c>
       <c r="R99" s="49" t="inlineStr">
         <is>
@@ -11016,13 +11018,13 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="31" t="n">
-        <v>7.1</v>
+        <v>2.3</v>
       </c>
       <c r="P104" s="31" t="n">
-        <v>19.4</v>
+        <v>22</v>
       </c>
       <c r="Q104" s="31" t="n">
-        <v>12.53</v>
+        <v>13.05</v>
       </c>
       <c r="R104" s="49" t="n"/>
       <c r="S104" s="22" t="inlineStr">
@@ -11129,13 +11131,13 @@
       </c>
       <c r="N105" s="2" t="n"/>
       <c r="O105" s="31" t="n">
-        <v>9.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="P105" s="31" t="n">
-        <v>27</v>
+        <v>29.3</v>
       </c>
       <c r="Q105" s="31" t="n">
-        <v>17.46</v>
+        <v>21.32</v>
       </c>
       <c r="R105" s="49" t="n"/>
       <c r="S105" s="22" t="inlineStr">
@@ -11365,13 +11367,13 @@
       </c>
       <c r="N107" s="2" t="n"/>
       <c r="O107" s="31" t="n">
-        <v>6.8</v>
+        <v>16.1</v>
       </c>
       <c r="P107" s="31" t="n">
-        <v>21.5</v>
+        <v>26.3</v>
       </c>
       <c r="Q107" s="31" t="n">
-        <v>13.53</v>
+        <v>21.75</v>
       </c>
       <c r="R107" s="49" t="n"/>
       <c r="S107" s="22" t="inlineStr">
@@ -11490,13 +11492,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="31" t="n">
-        <v>5.9</v>
+        <v>12.2</v>
       </c>
       <c r="P108" s="31" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="Q108" s="31" t="n">
-        <v>11.85</v>
+        <v>14.01</v>
       </c>
       <c r="R108" s="49" t="n"/>
       <c r="S108" s="22" t="inlineStr">
@@ -11828,15 +11830,9 @@
         </is>
       </c>
       <c r="N111" s="2" t="n"/>
-      <c r="O111" s="31" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="P111" s="31" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q111" s="31" t="n">
-        <v>2.23</v>
-      </c>
+      <c r="O111" s="31" t="n"/>
+      <c r="P111" s="31" t="n"/>
+      <c r="Q111" s="31" t="n"/>
       <c r="R111" s="49" t="n"/>
       <c r="S111" s="22" t="inlineStr">
         <is>
@@ -11941,15 +11937,9 @@
         </is>
       </c>
       <c r="N112" s="2" t="n"/>
-      <c r="O112" s="31" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="P112" s="31" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="Q112" s="31" t="n">
-        <v>1.67</v>
-      </c>
+      <c r="O112" s="31" t="n"/>
+      <c r="P112" s="31" t="n"/>
+      <c r="Q112" s="31" t="n"/>
       <c r="R112" s="49" t="n"/>
       <c r="S112" s="22" t="inlineStr">
         <is>
@@ -12063,13 +12053,13 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="31" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="P113" s="31" t="n">
-        <v>12.9</v>
+        <v>16.5</v>
       </c>
       <c r="Q113" s="31" t="n">
-        <v>2.39</v>
+        <v>5.28</v>
       </c>
       <c r="R113" s="49" t="n"/>
       <c r="S113" s="22" t="inlineStr">
@@ -12282,15 +12272,9 @@
         </is>
       </c>
       <c r="N115" s="2" t="n"/>
-      <c r="O115" s="31" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="P115" s="31" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Q115" s="31" t="n">
-        <v>3.88</v>
-      </c>
+      <c r="O115" s="31" t="n"/>
+      <c r="P115" s="31" t="n"/>
+      <c r="Q115" s="31" t="n"/>
       <c r="R115" s="49" t="n"/>
       <c r="S115" s="22" t="n"/>
       <c r="T115" s="35" t="inlineStr">
@@ -12408,13 +12392,13 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>-7.1</v>
+        <v>-5.6</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>12.1</v>
+        <v>15.1</v>
       </c>
       <c r="Q116" s="31" t="n">
-        <v>2.08</v>
+        <v>4.27</v>
       </c>
       <c r="R116" s="49" t="n"/>
       <c r="S116" s="22" t="inlineStr">
@@ -13702,13 +13686,13 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>36.1</v>
+        <v>32.7</v>
       </c>
       <c r="Q128" s="31" t="n">
-        <v>28.82</v>
+        <v>26.15</v>
       </c>
       <c r="R128" s="49" t="n"/>
       <c r="S128" s="22" t="inlineStr">
@@ -13819,13 +13803,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>19.6</v>
+        <v>13.2</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>28.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q129" s="31" t="n">
-        <v>23.84</v>
+        <v>17.8</v>
       </c>
       <c r="R129" s="49" t="n"/>
       <c r="S129" s="22" t="inlineStr">
@@ -14047,13 +14031,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>23.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q131" s="31" t="n">
-        <v>15.69</v>
+        <v>17.24</v>
       </c>
       <c r="R131" s="49" t="n"/>
       <c r="S131" s="22" t="inlineStr">
@@ -14172,13 +14156,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="31" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="Q132" s="31" t="n">
-        <v>24.1</v>
+        <v>24.6</v>
       </c>
       <c r="R132" s="49" t="n"/>
       <c r="S132" s="22" t="inlineStr">
@@ -14285,13 +14269,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="Q133" s="31" t="n">
-        <v>17.21</v>
+        <v>18.04</v>
       </c>
       <c r="R133" s="49" t="n"/>
       <c r="S133" s="22" t="inlineStr">
@@ -14406,13 +14390,13 @@
       </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="31" t="n">
-        <v>17.1</v>
+        <v>12.9</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>23.1</v>
+        <v>28.9</v>
       </c>
       <c r="Q134" s="31" t="n">
-        <v>19.35</v>
+        <v>19.43</v>
       </c>
       <c r="R134" s="49" t="n"/>
       <c r="S134" s="22" t="inlineStr">
@@ -14527,13 +14511,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="31" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="P135" s="31" t="n">
-        <v>22.3</v>
+        <v>15.8</v>
       </c>
       <c r="Q135" s="31" t="n">
-        <v>11.9</v>
+        <v>10.58</v>
       </c>
       <c r="R135" s="49" t="n"/>
       <c r="S135" s="22" t="inlineStr">
@@ -14648,13 +14632,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
-        <v>21.4</v>
+        <v>18.8</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>27.9</v>
+        <v>33.2</v>
       </c>
       <c r="Q136" s="31" t="n">
-        <v>24.16</v>
+        <v>25.24</v>
       </c>
       <c r="R136" s="49" t="n"/>
       <c r="S136" s="22" t="inlineStr">
@@ -14765,13 +14749,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>20.8</v>
+        <v>18.6</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>25.9</v>
+        <v>30.3</v>
       </c>
       <c r="Q137" s="31" t="n">
-        <v>22.49</v>
+        <v>23.94</v>
       </c>
       <c r="R137" s="49" t="n"/>
       <c r="S137" s="22" t="inlineStr">
@@ -14882,13 +14866,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>25</v>
+        <v>25.7</v>
       </c>
       <c r="Q138" s="31" t="n">
-        <v>20.81</v>
+        <v>21.21</v>
       </c>
       <c r="R138" s="49" t="n"/>
       <c r="S138" s="22" t="inlineStr">
@@ -15106,13 +15090,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>22.4</v>
+        <v>21.2</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>29.1</v>
+        <v>26.5</v>
       </c>
       <c r="Q140" s="31" t="n">
-        <v>24.73</v>
+        <v>23.16</v>
       </c>
       <c r="R140" s="49" t="n"/>
       <c r="S140" s="22" t="inlineStr">
@@ -15223,13 +15207,13 @@
       </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="31" t="n">
-        <v>25.4</v>
+        <v>23.7</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>32.1</v>
+        <v>29.2</v>
       </c>
       <c r="Q141" s="31" t="n">
-        <v>28.18</v>
+        <v>25.69</v>
       </c>
       <c r="R141" s="49" t="n"/>
       <c r="S141" s="22" t="inlineStr">
@@ -15340,13 +15324,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="31" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="P142" s="31" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q142" s="31" t="n">
-        <v>23.95</v>
+        <v>23.13</v>
       </c>
       <c r="R142" s="49" t="n"/>
       <c r="S142" s="22" t="inlineStr">
@@ -15457,13 +15441,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>28.1</v>
+        <v>25.5</v>
       </c>
       <c r="Q143" s="31" t="n">
-        <v>24.77</v>
+        <v>24.06</v>
       </c>
       <c r="R143" s="49" t="n"/>
       <c r="S143" s="22" t="inlineStr">
@@ -15574,13 +15558,13 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="Q144" s="31" t="n">
-        <v>26.29</v>
+        <v>26.9</v>
       </c>
       <c r="R144" s="49" t="n"/>
       <c r="S144" s="22" t="inlineStr">
@@ -15794,13 +15778,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="31" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="P146" s="31" t="n">
-        <v>31.2</v>
+        <v>32</v>
       </c>
       <c r="Q146" s="31" t="n">
-        <v>27.4</v>
+        <v>27.69</v>
       </c>
       <c r="R146" s="49" t="n"/>
       <c r="S146" s="22" t="inlineStr">
@@ -15911,13 +15895,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="Q147" s="31" t="n">
-        <v>29.24</v>
+        <v>28.1</v>
       </c>
       <c r="R147" s="49" t="n"/>
       <c r="S147" s="22" t="inlineStr">
@@ -16230,13 +16214,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>25.5</v>
+        <v>25.1</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>30.2</v>
+        <v>31.5</v>
       </c>
       <c r="Q150" s="31" t="n">
-        <v>28.34</v>
+        <v>27.19</v>
       </c>
       <c r="R150" s="49" t="n"/>
       <c r="S150" s="22" t="inlineStr">
@@ -16339,13 +16323,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>25.2</v>
+        <v>24.7</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>35.2</v>
+        <v>32.9</v>
       </c>
       <c r="Q151" s="31" t="n">
-        <v>29.91</v>
+        <v>27.96</v>
       </c>
       <c r="R151" s="49" t="n"/>
       <c r="S151" s="22" t="inlineStr">
@@ -16456,10 +16440,10 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>26.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q152" s="31" t="n">
         <v>20.76</v>
@@ -16573,13 +16557,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="31" t="n">
-        <v>20.4</v>
+        <v>19.7</v>
       </c>
       <c r="P153" s="31" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="Q153" s="31" t="n">
-        <v>24.95</v>
+        <v>24.46</v>
       </c>
       <c r="R153" s="49" t="n"/>
       <c r="S153" s="22" t="inlineStr">
@@ -16690,13 +16674,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="Q154" s="31" t="n">
-        <v>23.79</v>
+        <v>23.53</v>
       </c>
       <c r="R154" s="49" t="n"/>
       <c r="S154" s="22" t="inlineStr">
@@ -16898,13 +16882,13 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="31" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P156" s="31" t="n">
-        <v>28.2</v>
+        <v>26.8</v>
       </c>
       <c r="Q156" s="31" t="n">
-        <v>23.2</v>
+        <v>22.53</v>
       </c>
       <c r="R156" s="49" t="n"/>
       <c r="S156" s="22" t="inlineStr">
@@ -17019,13 +17003,13 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="31" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P157" s="31" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="Q157" s="31" t="n">
-        <v>14.86</v>
+        <v>12.03</v>
       </c>
       <c r="R157" s="49" t="n"/>
       <c r="S157" s="22" t="inlineStr">
@@ -17607,12 +17591,14 @@
       </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="31" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P163" s="31" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Q163" s="31" t="n"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q163" s="31" t="n">
+        <v>2.28</v>
+      </c>
       <c r="R163" s="49" t="n"/>
       <c r="S163" s="22" t="inlineStr">
         <is>
@@ -17722,13 +17708,13 @@
         </is>
       </c>
       <c r="O164" s="31" t="n">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="P164" s="31" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q164" s="31" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="R164" s="49" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -17835,13 +17821,13 @@
       </c>
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="31" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="P165" s="31" t="n">
-        <v>29.7</v>
+        <v>31.4</v>
       </c>
       <c r="Q165" s="31" t="n">
-        <v>24.25</v>
+        <v>25.18</v>
       </c>
       <c r="R165" s="49" t="n"/>
       <c r="S165" s="22" t="inlineStr">
@@ -17940,13 +17926,13 @@
       </c>
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="31" t="n">
-        <v>22.9</v>
+        <v>24.5</v>
       </c>
       <c r="P166" s="31" t="n">
-        <v>29.9</v>
+        <v>28.7</v>
       </c>
       <c r="Q166" s="31" t="n">
-        <v>25.73</v>
+        <v>26.21</v>
       </c>
       <c r="R166" s="49" t="n"/>
       <c r="S166" s="22" t="inlineStr">
@@ -18049,13 +18035,13 @@
       </c>
       <c r="N167" s="2" t="n"/>
       <c r="O167" s="31" t="n">
-        <v>9.9</v>
+        <v>12.5</v>
       </c>
       <c r="P167" s="31" t="n">
-        <v>25.3</v>
+        <v>21.5</v>
       </c>
       <c r="Q167" s="31" t="n">
-        <v>16.56</v>
+        <v>16.65</v>
       </c>
       <c r="R167" s="49" t="n"/>
       <c r="S167" s="22" t="inlineStr">
@@ -18293,13 +18279,13 @@
         </is>
       </c>
       <c r="O169" s="31" t="n">
-        <v>-2.7</v>
+        <v>-3</v>
       </c>
       <c r="P169" s="31" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q169" s="31" t="n">
-        <v>1.66</v>
+        <v>-0.35</v>
       </c>
       <c r="R169" s="49" t="n"/>
       <c r="S169" s="22" t="inlineStr">
@@ -18414,13 +18400,13 @@
       </c>
       <c r="N170" s="2" t="n"/>
       <c r="O170" s="31" t="n">
-        <v>-2.2</v>
+        <v>-4.3</v>
       </c>
       <c r="P170" s="31" t="n">
-        <v>16.8</v>
+        <v>14.5</v>
       </c>
       <c r="Q170" s="31" t="n">
-        <v>6.18</v>
+        <v>3.44</v>
       </c>
       <c r="R170" s="49" t="n"/>
       <c r="S170" s="22" t="inlineStr">
@@ -18535,13 +18521,13 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="31" t="n">
-        <v>21.2</v>
+        <v>19.6</v>
       </c>
       <c r="P171" s="31" t="n">
-        <v>27.5</v>
+        <v>31.3</v>
       </c>
       <c r="Q171" s="31" t="n">
-        <v>23.53</v>
+        <v>25.05</v>
       </c>
       <c r="R171" s="49" t="n"/>
       <c r="S171" s="22" t="inlineStr">
@@ -18648,13 +18634,13 @@
       </c>
       <c r="N172" s="2" t="n"/>
       <c r="O172" s="31" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="P172" s="31" t="n">
-        <v>23.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q172" s="31" t="n">
-        <v>22.21</v>
+        <v>23.75</v>
       </c>
       <c r="R172" s="49" t="n"/>
       <c r="S172" s="22" t="inlineStr">
@@ -18765,13 +18751,13 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="31" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="P173" s="31" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="Q173" s="31" t="n">
-        <v>29.09</v>
+        <v>29.46</v>
       </c>
       <c r="R173" s="49" t="n"/>
       <c r="S173" s="22" t="inlineStr">
@@ -18878,13 +18864,13 @@
       </c>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="31" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="P174" s="31" t="n">
-        <v>20.2</v>
+        <v>16</v>
       </c>
       <c r="Q174" s="31" t="n">
-        <v>15.83</v>
+        <v>15.11</v>
       </c>
       <c r="R174" s="49" t="n"/>
       <c r="S174" s="22" t="inlineStr">
@@ -19086,13 +19072,13 @@
         </is>
       </c>
       <c r="O176" s="31" t="n">
-        <v>-6.3</v>
+        <v>-7.7</v>
       </c>
       <c r="P176" s="31" t="n">
-        <v>1.4</v>
+        <v>-1.7</v>
       </c>
       <c r="Q176" s="31" t="n">
-        <v>-3</v>
+        <v>-6.2</v>
       </c>
       <c r="R176" s="49" t="n"/>
       <c r="S176" s="22" t="inlineStr">
@@ -19194,9 +19180,15 @@
         </is>
       </c>
       <c r="N177" s="2" t="n"/>
-      <c r="O177" s="31" t="n"/>
-      <c r="P177" s="31" t="n"/>
-      <c r="Q177" s="31" t="n"/>
+      <c r="O177" s="31" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="P177" s="31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q177" s="31" t="n">
+        <v>-3.7</v>
+      </c>
       <c r="R177" s="49" t="n"/>
       <c r="S177" s="22" t="inlineStr">
         <is>
@@ -19297,15 +19289,9 @@
         </is>
       </c>
       <c r="N178" s="2" t="n"/>
-      <c r="O178" s="31" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="P178" s="31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q178" s="31" t="n">
-        <v>-3.2</v>
-      </c>
+      <c r="O178" s="31" t="n"/>
+      <c r="P178" s="31" t="n"/>
+      <c r="Q178" s="31" t="n"/>
       <c r="R178" s="49" t="n"/>
       <c r="S178" s="22" t="n"/>
       <c r="T178" s="35" t="n"/>
@@ -19510,13 +19496,13 @@
       </c>
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="31" t="n">
-        <v>-0.3</v>
+        <v>2.9</v>
       </c>
       <c r="P180" s="31" t="n">
-        <v>21.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q180" s="31" t="n">
-        <v>9.890000000000001</v>
+        <v>11.86</v>
       </c>
       <c r="R180" s="49" t="inlineStr">
         <is>
@@ -19623,10 +19609,10 @@
       </c>
       <c r="N181" s="2" t="n"/>
       <c r="O181" s="31" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="P181" s="31" t="n">
-        <v>12</v>
+        <v>15.1</v>
       </c>
       <c r="Q181" s="31" t="n"/>
       <c r="R181" s="49" t="n"/>
@@ -19729,8 +19715,12 @@
         </is>
       </c>
       <c r="N182" s="3" t="n"/>
-      <c r="O182" s="31" t="n"/>
-      <c r="P182" s="31" t="n"/>
+      <c r="O182" s="31" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="P182" s="31" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Q182" s="31" t="n"/>
       <c r="R182" s="49" t="n"/>
       <c r="S182" s="22" t="inlineStr">
@@ -19841,13 +19831,13 @@
         </is>
       </c>
       <c r="O183" s="31" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="P183" s="31" t="n">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q183" s="31" t="n">
-        <v>3.2</v>
+        <v>5.45</v>
       </c>
       <c r="R183" s="49" t="n"/>
       <c r="S183" s="22" t="inlineStr">
@@ -20776,10 +20766,10 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="31" t="n">
-        <v>-12</v>
+        <v>-10.1</v>
       </c>
       <c r="P192" s="31" t="n">
-        <v>13.7</v>
+        <v>18.2</v>
       </c>
       <c r="Q192" s="31" t="n"/>
       <c r="R192" s="49" t="n"/>
@@ -20887,10 +20877,10 @@
         </is>
       </c>
       <c r="O193" s="31" t="n">
-        <v>-11.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="P193" s="31" t="n">
-        <v>11.1</v>
+        <v>15.4</v>
       </c>
       <c r="Q193" s="31" t="n"/>
       <c r="R193" s="49" t="n"/>
@@ -20997,12 +20987,8 @@
         </is>
       </c>
       <c r="N194" s="2" t="n"/>
-      <c r="O194" s="31" t="n">
-        <v>-10</v>
-      </c>
-      <c r="P194" s="31" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="O194" s="31" t="n"/>
+      <c r="P194" s="31" t="n"/>
       <c r="Q194" s="31" t="n"/>
       <c r="R194" s="49" t="inlineStr">
         <is>
@@ -21319,10 +21305,10 @@
         </is>
       </c>
       <c r="O197" s="31" t="n">
-        <v>0.8</v>
+        <v>-3.2</v>
       </c>
       <c r="P197" s="31" t="n">
-        <v>13.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q197" s="31" t="n"/>
       <c r="R197" s="49" t="n"/>
@@ -21545,10 +21531,10 @@
       </c>
       <c r="N199" s="2" t="n"/>
       <c r="O199" s="31" t="n">
-        <v>-1.7</v>
+        <v>-5.9</v>
       </c>
       <c r="P199" s="31" t="n">
-        <v>18.8</v>
+        <v>14.3</v>
       </c>
       <c r="Q199" s="31" t="n"/>
       <c r="R199" s="49" t="n"/>
@@ -21654,7 +21640,7 @@
       </c>
       <c r="N200" s="2" t="n"/>
       <c r="O200" s="31" t="n">
-        <v>-23.3</v>
+        <v>-38.7</v>
       </c>
       <c r="P200" s="31" t="n"/>
       <c r="Q200" s="31" t="n"/>
@@ -22218,13 +22204,13 @@
       </c>
       <c r="N206" s="2" t="n"/>
       <c r="O206" s="31" t="n">
-        <v>13.7</v>
+        <v>15.5</v>
       </c>
       <c r="P206" s="31" t="n">
-        <v>19.4</v>
+        <v>21.1</v>
       </c>
       <c r="Q206" s="31" t="n">
-        <v>16.95</v>
+        <v>18.04</v>
       </c>
       <c r="R206" s="49" t="n"/>
       <c r="S206" s="22" t="inlineStr">
@@ -22622,13 +22608,13 @@
       </c>
       <c r="N210" s="2" t="n"/>
       <c r="O210" s="31" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="P210" s="31" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="Q210" s="31" t="n">
-        <v>10.2</v>
+        <v>6.84</v>
       </c>
       <c r="R210" s="49" t="n"/>
       <c r="S210" s="22" t="inlineStr">
@@ -22832,13 +22818,13 @@
       </c>
       <c r="N212" s="2" t="n"/>
       <c r="O212" s="31" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="P212" s="31" t="n">
-        <v>12.6</v>
+        <v>16.4</v>
       </c>
       <c r="Q212" s="31" t="n">
-        <v>10.81</v>
+        <v>10.45</v>
       </c>
       <c r="R212" s="49" t="n"/>
       <c r="S212" s="22" t="inlineStr">
@@ -23238,13 +23224,13 @@
       </c>
       <c r="N216" s="2" t="n"/>
       <c r="O216" s="31" t="n">
-        <v>-0.4</v>
+        <v>-2.1</v>
       </c>
       <c r="P216" s="31" t="n">
-        <v>7.3</v>
+        <v>15.3</v>
       </c>
       <c r="Q216" s="31" t="n">
-        <v>4.19</v>
+        <v>4.52</v>
       </c>
       <c r="R216" s="49" t="n"/>
       <c r="S216" s="22" t="inlineStr">
@@ -23541,13 +23527,13 @@
       </c>
       <c r="N219" s="2" t="n"/>
       <c r="O219" s="31" t="n">
-        <v>11.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P219" s="31" t="n">
-        <v>14.4</v>
+        <v>16.4</v>
       </c>
       <c r="Q219" s="31" t="n">
-        <v>12.64</v>
+        <v>12.36</v>
       </c>
       <c r="R219" s="49" t="n"/>
       <c r="S219" s="22" t="inlineStr">
@@ -23654,13 +23640,13 @@
       </c>
       <c r="N220" s="2" t="n"/>
       <c r="O220" s="31" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="P220" s="31" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="Q220" s="31" t="n">
-        <v>11.57</v>
+        <v>10.02</v>
       </c>
       <c r="R220" s="49" t="n"/>
       <c r="S220" s="22" t="inlineStr">
@@ -24054,13 +24040,13 @@
         </is>
       </c>
       <c r="O224" s="31" t="n">
-        <v>-11.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P224" s="31" t="n">
-        <v>12.8</v>
+        <v>14.9</v>
       </c>
       <c r="Q224" s="31" t="n">
-        <v>-0.68</v>
+        <v>4.55</v>
       </c>
       <c r="R224" s="49" t="n"/>
       <c r="S224" s="22" t="inlineStr">
@@ -24245,9 +24231,7 @@
         </is>
       </c>
       <c r="N226" s="2" t="n"/>
-      <c r="O226" s="31" t="n">
-        <v>-10.2</v>
-      </c>
+      <c r="O226" s="31" t="n"/>
       <c r="P226" s="31" t="n"/>
       <c r="Q226" s="31" t="n"/>
       <c r="R226" s="49" t="n"/>
@@ -26302,10 +26286,10 @@
         <v>-1.4</v>
       </c>
       <c r="P248" s="31" t="n">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="Q248" s="31" t="n">
-        <v>2.04</v>
+        <v>4.24</v>
       </c>
       <c r="R248" s="49" t="n"/>
       <c r="S248" s="22" t="inlineStr">
@@ -26793,7 +26777,7 @@
       </c>
       <c r="N253" s="2" t="n"/>
       <c r="O253" s="31" t="n">
-        <v>-4.5</v>
+        <v>-12.1</v>
       </c>
       <c r="P253" s="31" t="n">
         <v>1.8</v>
@@ -27174,10 +27158,10 @@
       </c>
       <c r="N257" s="2" t="n"/>
       <c r="O257" s="31" t="n">
-        <v>-78.2</v>
+        <v>-73.2</v>
       </c>
       <c r="P257" s="31" t="n">
-        <v>-72.3</v>
+        <v>-61.5</v>
       </c>
       <c r="Q257" s="31" t="n"/>
       <c r="R257" s="49" t="n"/>
@@ -28264,12 +28248,8 @@
         </is>
       </c>
       <c r="N268" s="2" t="n"/>
-      <c r="O268" s="31" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="P268" s="31" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="O268" s="31" t="n"/>
+      <c r="P268" s="31" t="n"/>
       <c r="Q268" s="31" t="n"/>
       <c r="R268" s="49" t="n"/>
       <c r="S268" s="22" t="inlineStr">
@@ -28372,13 +28352,13 @@
       </c>
       <c r="N269" s="2" t="n"/>
       <c r="O269" s="31" t="n">
-        <v>-6.6</v>
+        <v>-6.4</v>
       </c>
       <c r="P269" s="31" t="n">
-        <v>11.4</v>
+        <v>15.6</v>
       </c>
       <c r="Q269" s="31" t="n">
-        <v>2.01</v>
+        <v>4.19</v>
       </c>
       <c r="R269" s="49" t="n"/>
       <c r="S269" s="22" t="inlineStr">
@@ -32361,12 +32341,8 @@
         </is>
       </c>
       <c r="N309" s="2" t="n"/>
-      <c r="O309" s="31" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="P309" s="31" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="O309" s="31" t="n"/>
+      <c r="P309" s="31" t="n"/>
       <c r="Q309" s="31" t="n"/>
       <c r="R309" s="49" t="n"/>
       <c r="S309" s="22" t="inlineStr">
@@ -32658,12 +32634,8 @@
         </is>
       </c>
       <c r="N312" s="2" t="n"/>
-      <c r="O312" s="31" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="P312" s="31" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="O312" s="31" t="n"/>
+      <c r="P312" s="31" t="n"/>
       <c r="Q312" s="31" t="n"/>
       <c r="R312" s="49" t="n"/>
       <c r="S312" s="22" t="inlineStr">

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -830,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="731"/>
-    <col width="12.59765625" customWidth="1" style="5" min="732" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="732"/>
+    <col width="12.59765625" customWidth="1" style="5" min="733" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>11.16</v>
+        <v>12.08</v>
       </c>
       <c r="R2" s="49" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="49" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>17.4</v>
+        <v>13.3</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="49" t="inlineStr">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>3.4</v>
+        <v>-0.2</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>4.95</v>
+        <v>4.71</v>
       </c>
       <c r="R6" s="51" t="inlineStr">
         <is>
@@ -1691,13 +1691,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>2.9</v>
+        <v>-0.5</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>14.8</v>
+        <v>17.4</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>8.359999999999999</v>
+        <v>7.51</v>
       </c>
       <c r="R8" s="49" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1804,13 +1804,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>19.3</v>
+        <v>15.9</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>11.33</v>
+        <v>10.63</v>
       </c>
       <c r="R9" s="49" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>-1.3</v>
+        <v>2.5</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>16.9</v>
+        <v>22.9</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>8</v>
+        <v>7.68</v>
       </c>
       <c r="R10" s="49" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>-1.9</v>
+        <v>-3.4</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>12.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>5.32</v>
+        <v>4.99</v>
       </c>
       <c r="R11" s="49" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>11.9</v>
+        <v>15.9</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>7.74</v>
+        <v>8.24</v>
       </c>
       <c r="R12" s="49" t="inlineStr">
         <is>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>-0.1</v>
+        <v>2.2</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>13</v>
+        <v>12.2</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>5.95</v>
+        <v>6.29</v>
       </c>
       <c r="R13" s="49" t="inlineStr">
         <is>
@@ -2397,13 +2397,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>7.6</v>
+        <v>6.25</v>
       </c>
       <c r="R14" s="49" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2518,13 +2518,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>-4.4</v>
+        <v>0.8</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>10.8</v>
+        <v>6.4</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>3.59</v>
+        <v>4.15</v>
       </c>
       <c r="R15" s="49" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -4130,12 +4130,8 @@
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
-      <c r="O32" s="31" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="P32" s="31" t="n">
-        <v>6.7</v>
-      </c>
+      <c r="O32" s="31" t="n"/>
+      <c r="P32" s="31" t="n"/>
       <c r="Q32" s="31" t="n"/>
       <c r="R32" s="49" t="n"/>
       <c r="S32" s="22" t="n"/>
@@ -9269,13 +9265,13 @@
         </is>
       </c>
       <c r="O88" s="31" t="n">
-        <v>-10.4</v>
+        <v>-7.5</v>
       </c>
       <c r="P88" s="31" t="n">
-        <v>6.3</v>
+        <v>10.4</v>
       </c>
       <c r="Q88" s="31" t="n">
-        <v>-1.86</v>
+        <v>2.07</v>
       </c>
       <c r="R88" s="49" t="inlineStr">
         <is>
@@ -9703,13 +9699,13 @@
         </is>
       </c>
       <c r="O92" s="31" t="n">
-        <v>-6.6</v>
+        <v>-8.5</v>
       </c>
       <c r="P92" s="31" t="n">
-        <v>15.4</v>
+        <v>17</v>
       </c>
       <c r="Q92" s="31" t="n">
-        <v>3.54</v>
+        <v>2.96</v>
       </c>
       <c r="R92" s="49" t="n"/>
       <c r="S92" s="22" t="inlineStr">
@@ -9825,13 +9821,13 @@
         </is>
       </c>
       <c r="O93" s="31" t="n">
-        <v>-7.1</v>
+        <v>-7.9</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="R93" s="49" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -10045,13 +10041,13 @@
         </is>
       </c>
       <c r="O95" s="31" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="P95" s="31" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="Q95" s="31" t="n">
-        <v>5.49</v>
+        <v>4.99</v>
       </c>
       <c r="R95" s="49" t="n"/>
       <c r="S95" s="22" t="inlineStr">
@@ -10265,13 +10261,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="31" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="P97" s="31" t="n">
-        <v>19.3</v>
+        <v>20.4</v>
       </c>
       <c r="Q97" s="31" t="n">
-        <v>10.89</v>
+        <v>10.34</v>
       </c>
       <c r="R97" s="49" t="n"/>
       <c r="S97" s="22" t="inlineStr">
@@ -10493,13 +10489,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="31" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="P99" s="31" t="n">
-        <v>15.8</v>
+        <v>12.3</v>
       </c>
       <c r="Q99" s="31" t="n">
-        <v>9.07</v>
+        <v>7.22</v>
       </c>
       <c r="R99" s="49" t="inlineStr">
         <is>
@@ -11018,13 +11014,13 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="31" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="P104" s="31" t="n">
-        <v>22</v>
+        <v>18.6</v>
       </c>
       <c r="Q104" s="31" t="n">
-        <v>13.05</v>
+        <v>13.01</v>
       </c>
       <c r="R104" s="49" t="n"/>
       <c r="S104" s="22" t="inlineStr">
@@ -11131,13 +11127,13 @@
       </c>
       <c r="N105" s="2" t="n"/>
       <c r="O105" s="31" t="n">
-        <v>11.9</v>
+        <v>14.1</v>
       </c>
       <c r="P105" s="31" t="n">
-        <v>29.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q105" s="31" t="n">
-        <v>21.32</v>
+        <v>19.07</v>
       </c>
       <c r="R105" s="49" t="n"/>
       <c r="S105" s="22" t="inlineStr">
@@ -11367,13 +11363,13 @@
       </c>
       <c r="N107" s="2" t="n"/>
       <c r="O107" s="31" t="n">
-        <v>16.1</v>
+        <v>9.4</v>
       </c>
       <c r="P107" s="31" t="n">
-        <v>26.3</v>
+        <v>20</v>
       </c>
       <c r="Q107" s="31" t="n">
-        <v>21.75</v>
+        <v>14.34</v>
       </c>
       <c r="R107" s="49" t="n"/>
       <c r="S107" s="22" t="inlineStr">
@@ -11492,13 +11488,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="31" t="n">
-        <v>12.2</v>
+        <v>4.4</v>
       </c>
       <c r="P108" s="31" t="n">
-        <v>16.3</v>
+        <v>20.4</v>
       </c>
       <c r="Q108" s="31" t="n">
-        <v>14.01</v>
+        <v>13.26</v>
       </c>
       <c r="R108" s="49" t="n"/>
       <c r="S108" s="22" t="inlineStr">
@@ -12053,13 +12049,13 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="31" t="n">
-        <v>-4.8</v>
+        <v>-5.5</v>
       </c>
       <c r="P113" s="31" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Q113" s="31" t="n">
-        <v>5.28</v>
+        <v>4.27</v>
       </c>
       <c r="R113" s="49" t="n"/>
       <c r="S113" s="22" t="inlineStr">
@@ -12392,13 +12388,13 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>-5.6</v>
+        <v>-8.1</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>15.1</v>
+        <v>16.8</v>
       </c>
       <c r="Q116" s="31" t="n">
-        <v>4.27</v>
+        <v>3.7</v>
       </c>
       <c r="R116" s="49" t="n"/>
       <c r="S116" s="22" t="inlineStr">
@@ -13686,13 +13682,13 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>32.7</v>
+        <v>28.9</v>
       </c>
       <c r="Q128" s="31" t="n">
-        <v>26.15</v>
+        <v>24.69</v>
       </c>
       <c r="R128" s="49" t="n"/>
       <c r="S128" s="22" t="inlineStr">
@@ -13803,13 +13799,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="Q129" s="31" t="n">
-        <v>17.8</v>
+        <v>19.02</v>
       </c>
       <c r="R129" s="49" t="n"/>
       <c r="S129" s="22" t="inlineStr">
@@ -14031,13 +14027,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>9.5</v>
+        <v>13.6</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>25.5</v>
+        <v>23.1</v>
       </c>
       <c r="Q131" s="31" t="n">
-        <v>17.24</v>
+        <v>18.45</v>
       </c>
       <c r="R131" s="49" t="n"/>
       <c r="S131" s="22" t="inlineStr">
@@ -14156,13 +14152,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="31" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="Q132" s="31" t="n">
-        <v>24.6</v>
+        <v>21.36</v>
       </c>
       <c r="R132" s="49" t="n"/>
       <c r="S132" s="22" t="inlineStr">
@@ -14269,13 +14265,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>11</v>
+        <v>13.7</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="Q133" s="31" t="n">
-        <v>18.04</v>
+        <v>19.36</v>
       </c>
       <c r="R133" s="49" t="n"/>
       <c r="S133" s="22" t="inlineStr">
@@ -14390,13 +14386,13 @@
       </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="31" t="n">
-        <v>12.9</v>
+        <v>16.5</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>28.9</v>
+        <v>25</v>
       </c>
       <c r="Q134" s="31" t="n">
-        <v>19.43</v>
+        <v>20.09</v>
       </c>
       <c r="R134" s="49" t="n"/>
       <c r="S134" s="22" t="inlineStr">
@@ -14511,13 +14507,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="31" t="n">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="P135" s="31" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="Q135" s="31" t="n">
-        <v>10.58</v>
+        <v>11.14</v>
       </c>
       <c r="R135" s="49" t="n"/>
       <c r="S135" s="22" t="inlineStr">
@@ -14632,13 +14628,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
-        <v>18.8</v>
+        <v>21.5</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>33.2</v>
+        <v>30.8</v>
       </c>
       <c r="Q136" s="31" t="n">
-        <v>25.24</v>
+        <v>25.48</v>
       </c>
       <c r="R136" s="49" t="n"/>
       <c r="S136" s="22" t="inlineStr">
@@ -14749,13 +14745,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>18.6</v>
+        <v>20.7</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>30.3</v>
+        <v>24.9</v>
       </c>
       <c r="Q137" s="31" t="n">
-        <v>23.94</v>
+        <v>23.18</v>
       </c>
       <c r="R137" s="49" t="n"/>
       <c r="S137" s="22" t="inlineStr">
@@ -14866,13 +14862,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>18.2</v>
+        <v>20.3</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>25.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q138" s="31" t="n">
-        <v>21.21</v>
+        <v>22.13</v>
       </c>
       <c r="R138" s="49" t="n"/>
       <c r="S138" s="22" t="inlineStr">
@@ -15090,13 +15086,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>26.5</v>
+        <v>31.8</v>
       </c>
       <c r="Q140" s="31" t="n">
-        <v>23.16</v>
+        <v>25.5</v>
       </c>
       <c r="R140" s="49" t="n"/>
       <c r="S140" s="22" t="inlineStr">
@@ -15210,10 +15206,10 @@
         <v>23.7</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>29.2</v>
+        <v>33.7</v>
       </c>
       <c r="Q141" s="31" t="n">
-        <v>25.69</v>
+        <v>28.05</v>
       </c>
       <c r="R141" s="49" t="n"/>
       <c r="S141" s="22" t="inlineStr">
@@ -15324,13 +15320,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="31" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="P142" s="31" t="n">
-        <v>25.7</v>
+        <v>31</v>
       </c>
       <c r="Q142" s="31" t="n">
-        <v>23.13</v>
+        <v>25</v>
       </c>
       <c r="R142" s="49" t="n"/>
       <c r="S142" s="22" t="inlineStr">
@@ -15441,13 +15437,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="Q143" s="31" t="n">
-        <v>24.06</v>
+        <v>24.38</v>
       </c>
       <c r="R143" s="49" t="n"/>
       <c r="S143" s="22" t="inlineStr">
@@ -15558,13 +15554,13 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>24</v>
+        <v>24.7</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>30.5</v>
+        <v>31.1</v>
       </c>
       <c r="Q144" s="31" t="n">
-        <v>26.9</v>
+        <v>27.17</v>
       </c>
       <c r="R144" s="49" t="n"/>
       <c r="S144" s="22" t="inlineStr">
@@ -15778,13 +15774,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="31" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="P146" s="31" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="Q146" s="31" t="n">
-        <v>27.69</v>
+        <v>28.05</v>
       </c>
       <c r="R146" s="49" t="n"/>
       <c r="S146" s="22" t="inlineStr">
@@ -15895,13 +15891,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>25</v>
+        <v>25.7</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>33.4</v>
+        <v>33.8</v>
       </c>
       <c r="Q147" s="31" t="n">
-        <v>28.1</v>
+        <v>28.81</v>
       </c>
       <c r="R147" s="49" t="n"/>
       <c r="S147" s="22" t="inlineStr">
@@ -16214,13 +16210,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>25.1</v>
+        <v>25.5</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="Q150" s="31" t="n">
-        <v>27.19</v>
+        <v>28.45</v>
       </c>
       <c r="R150" s="49" t="n"/>
       <c r="S150" s="22" t="inlineStr">
@@ -16323,13 +16319,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>32.9</v>
+        <v>34.2</v>
       </c>
       <c r="Q151" s="31" t="n">
-        <v>27.96</v>
+        <v>28.8</v>
       </c>
       <c r="R151" s="49" t="n"/>
       <c r="S151" s="22" t="inlineStr">
@@ -16440,13 +16436,13 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>25.8</v>
+        <v>26.3</v>
       </c>
       <c r="Q152" s="31" t="n">
-        <v>20.76</v>
+        <v>19.96</v>
       </c>
       <c r="R152" s="49" t="n"/>
       <c r="S152" s="22" t="inlineStr">
@@ -16557,13 +16553,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="31" t="n">
-        <v>19.7</v>
+        <v>20.9</v>
       </c>
       <c r="P153" s="31" t="n">
-        <v>30.9</v>
+        <v>30</v>
       </c>
       <c r="Q153" s="31" t="n">
-        <v>24.46</v>
+        <v>24.81</v>
       </c>
       <c r="R153" s="49" t="n"/>
       <c r="S153" s="22" t="inlineStr">
@@ -16674,13 +16670,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>21.6</v>
+        <v>23.6</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>27.4</v>
+        <v>29.1</v>
       </c>
       <c r="Q154" s="31" t="n">
-        <v>23.53</v>
+        <v>25.55</v>
       </c>
       <c r="R154" s="49" t="n"/>
       <c r="S154" s="22" t="inlineStr">
@@ -16882,13 +16878,13 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="31" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="P156" s="31" t="n">
-        <v>26.8</v>
+        <v>22.1</v>
       </c>
       <c r="Q156" s="31" t="n">
-        <v>22.53</v>
+        <v>21.19</v>
       </c>
       <c r="R156" s="49" t="n"/>
       <c r="S156" s="22" t="inlineStr">
@@ -17003,13 +16999,13 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="31" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="P157" s="31" t="n">
-        <v>16.7</v>
+        <v>17.5</v>
       </c>
       <c r="Q157" s="31" t="n">
-        <v>12.03</v>
+        <v>12.21</v>
       </c>
       <c r="R157" s="49" t="n"/>
       <c r="S157" s="22" t="inlineStr">
@@ -17591,13 +17587,13 @@
       </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P163" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="Q163" s="31" t="n">
-        <v>2.28</v>
+        <v>1.33</v>
       </c>
       <c r="R163" s="49" t="n"/>
       <c r="S163" s="22" t="inlineStr">
@@ -17708,13 +17704,13 @@
         </is>
       </c>
       <c r="O164" s="31" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="P164" s="31" t="n">
-        <v>9.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="Q164" s="31" t="n">
-        <v>3.74</v>
+        <v>2.2</v>
       </c>
       <c r="R164" s="49" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -17821,13 +17817,13 @@
       </c>
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="P165" s="31" t="n">
-        <v>31.4</v>
+        <v>26.2</v>
       </c>
       <c r="Q165" s="31" t="n">
-        <v>25.18</v>
+        <v>22.29</v>
       </c>
       <c r="R165" s="49" t="n"/>
       <c r="S165" s="22" t="inlineStr">
@@ -17926,13 +17922,13 @@
       </c>
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="31" t="n">
-        <v>24.5</v>
+        <v>23.8</v>
       </c>
       <c r="P166" s="31" t="n">
-        <v>28.7</v>
+        <v>28</v>
       </c>
       <c r="Q166" s="31" t="n">
-        <v>26.21</v>
+        <v>25.73</v>
       </c>
       <c r="R166" s="49" t="n"/>
       <c r="S166" s="22" t="inlineStr">
@@ -18035,13 +18031,13 @@
       </c>
       <c r="N167" s="2" t="n"/>
       <c r="O167" s="31" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="P167" s="31" t="n">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="Q167" s="31" t="n">
-        <v>16.65</v>
+        <v>16</v>
       </c>
       <c r="R167" s="49" t="n"/>
       <c r="S167" s="22" t="inlineStr">
@@ -18279,13 +18275,13 @@
         </is>
       </c>
       <c r="O169" s="31" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="P169" s="31" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q169" s="31" t="n">
-        <v>-0.35</v>
+        <v>-0.46</v>
       </c>
       <c r="R169" s="49" t="n"/>
       <c r="S169" s="22" t="inlineStr">
@@ -18400,13 +18396,13 @@
       </c>
       <c r="N170" s="2" t="n"/>
       <c r="O170" s="31" t="n">
-        <v>-4.3</v>
+        <v>0.3</v>
       </c>
       <c r="P170" s="31" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="Q170" s="31" t="n">
-        <v>3.44</v>
+        <v>6.95</v>
       </c>
       <c r="R170" s="49" t="n"/>
       <c r="S170" s="22" t="inlineStr">
@@ -18521,13 +18517,13 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="31" t="n">
-        <v>19.6</v>
+        <v>21.4</v>
       </c>
       <c r="P171" s="31" t="n">
-        <v>31.3</v>
+        <v>27.2</v>
       </c>
       <c r="Q171" s="31" t="n">
-        <v>25.05</v>
+        <v>23.31</v>
       </c>
       <c r="R171" s="49" t="n"/>
       <c r="S171" s="22" t="inlineStr">
@@ -18634,13 +18630,13 @@
       </c>
       <c r="N172" s="2" t="n"/>
       <c r="O172" s="31" t="n">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="P172" s="31" t="n">
-        <v>27.1</v>
+        <v>28.4</v>
       </c>
       <c r="Q172" s="31" t="n">
-        <v>23.75</v>
+        <v>24.63</v>
       </c>
       <c r="R172" s="49" t="n"/>
       <c r="S172" s="22" t="inlineStr">
@@ -18751,13 +18747,13 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="31" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="P173" s="31" t="n">
-        <v>36.8</v>
+        <v>36</v>
       </c>
       <c r="Q173" s="31" t="n">
-        <v>29.46</v>
+        <v>28.96</v>
       </c>
       <c r="R173" s="49" t="n"/>
       <c r="S173" s="22" t="inlineStr">
@@ -18864,13 +18860,13 @@
       </c>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="31" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="P174" s="31" t="n">
-        <v>16</v>
+        <v>17.1</v>
       </c>
       <c r="Q174" s="31" t="n">
-        <v>15.11</v>
+        <v>15.41</v>
       </c>
       <c r="R174" s="49" t="n"/>
       <c r="S174" s="22" t="inlineStr">
@@ -19072,13 +19068,13 @@
         </is>
       </c>
       <c r="O176" s="31" t="n">
-        <v>-7.7</v>
+        <v>-10.8</v>
       </c>
       <c r="P176" s="31" t="n">
-        <v>-1.7</v>
+        <v>-0.9</v>
       </c>
       <c r="Q176" s="31" t="n">
-        <v>-6.2</v>
+        <v>-6.9</v>
       </c>
       <c r="R176" s="49" t="n"/>
       <c r="S176" s="22" t="inlineStr">
@@ -19180,15 +19176,9 @@
         </is>
       </c>
       <c r="N177" s="2" t="n"/>
-      <c r="O177" s="31" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="P177" s="31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q177" s="31" t="n">
-        <v>-3.7</v>
-      </c>
+      <c r="O177" s="31" t="n"/>
+      <c r="P177" s="31" t="n"/>
+      <c r="Q177" s="31" t="n"/>
       <c r="R177" s="49" t="n"/>
       <c r="S177" s="22" t="inlineStr">
         <is>
@@ -19496,13 +19486,13 @@
       </c>
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="31" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P180" s="31" t="n">
-        <v>23.3</v>
+        <v>16.8</v>
       </c>
       <c r="Q180" s="31" t="n">
-        <v>11.86</v>
+        <v>9.85</v>
       </c>
       <c r="R180" s="49" t="inlineStr">
         <is>
@@ -19609,10 +19599,10 @@
       </c>
       <c r="N181" s="2" t="n"/>
       <c r="O181" s="31" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="P181" s="31" t="n">
-        <v>15.1</v>
+        <v>10.9</v>
       </c>
       <c r="Q181" s="31" t="n"/>
       <c r="R181" s="49" t="n"/>
@@ -19716,10 +19706,10 @@
       </c>
       <c r="N182" s="3" t="n"/>
       <c r="O182" s="31" t="n">
-        <v>-4.8</v>
+        <v>-4.4</v>
       </c>
       <c r="P182" s="31" t="n">
-        <v>12.4</v>
+        <v>13.7</v>
       </c>
       <c r="Q182" s="31" t="n"/>
       <c r="R182" s="49" t="n"/>
@@ -19831,13 +19821,13 @@
         </is>
       </c>
       <c r="O183" s="31" t="n">
-        <v>3.4</v>
+        <v>-1</v>
       </c>
       <c r="P183" s="31" t="n">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="Q183" s="31" t="n">
-        <v>5.45</v>
+        <v>3.14</v>
       </c>
       <c r="R183" s="49" t="n"/>
       <c r="S183" s="22" t="inlineStr">
@@ -20766,10 +20756,10 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="31" t="n">
-        <v>-10.1</v>
+        <v>-10.8</v>
       </c>
       <c r="P192" s="31" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="Q192" s="31" t="n"/>
       <c r="R192" s="49" t="n"/>
@@ -20877,10 +20867,10 @@
         </is>
       </c>
       <c r="O193" s="31" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.4</v>
       </c>
       <c r="P193" s="31" t="n">
-        <v>15.4</v>
+        <v>16.3</v>
       </c>
       <c r="Q193" s="31" t="n"/>
       <c r="R193" s="49" t="n"/>
@@ -20987,8 +20977,12 @@
         </is>
       </c>
       <c r="N194" s="2" t="n"/>
-      <c r="O194" s="31" t="n"/>
-      <c r="P194" s="31" t="n"/>
+      <c r="O194" s="31" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="P194" s="31" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Q194" s="31" t="n"/>
       <c r="R194" s="49" t="inlineStr">
         <is>
@@ -21305,10 +21299,10 @@
         </is>
       </c>
       <c r="O197" s="31" t="n">
-        <v>-3.2</v>
+        <v>-4.7</v>
       </c>
       <c r="P197" s="31" t="n">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Q197" s="31" t="n"/>
       <c r="R197" s="49" t="n"/>
@@ -21531,10 +21525,10 @@
       </c>
       <c r="N199" s="2" t="n"/>
       <c r="O199" s="31" t="n">
-        <v>-5.9</v>
+        <v>1.5</v>
       </c>
       <c r="P199" s="31" t="n">
-        <v>14.3</v>
+        <v>12.3</v>
       </c>
       <c r="Q199" s="31" t="n"/>
       <c r="R199" s="49" t="n"/>
@@ -21640,7 +21634,7 @@
       </c>
       <c r="N200" s="2" t="n"/>
       <c r="O200" s="31" t="n">
-        <v>-38.7</v>
+        <v>-36.3</v>
       </c>
       <c r="P200" s="31" t="n"/>
       <c r="Q200" s="31" t="n"/>
@@ -22204,13 +22198,13 @@
       </c>
       <c r="N206" s="2" t="n"/>
       <c r="O206" s="31" t="n">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="P206" s="31" t="n">
-        <v>21.1</v>
+        <v>19.4</v>
       </c>
       <c r="Q206" s="31" t="n">
-        <v>18.04</v>
+        <v>15.14</v>
       </c>
       <c r="R206" s="49" t="n"/>
       <c r="S206" s="22" t="inlineStr">
@@ -22608,13 +22602,13 @@
       </c>
       <c r="N210" s="2" t="n"/>
       <c r="O210" s="31" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="P210" s="31" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="Q210" s="31" t="n">
-        <v>6.84</v>
+        <v>7.3</v>
       </c>
       <c r="R210" s="49" t="n"/>
       <c r="S210" s="22" t="inlineStr">
@@ -22818,13 +22812,13 @@
       </c>
       <c r="N212" s="2" t="n"/>
       <c r="O212" s="31" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="P212" s="31" t="n">
-        <v>16.4</v>
+        <v>18.2</v>
       </c>
       <c r="Q212" s="31" t="n">
-        <v>10.45</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="R212" s="49" t="n"/>
       <c r="S212" s="22" t="inlineStr">
@@ -23224,13 +23218,13 @@
       </c>
       <c r="N216" s="2" t="n"/>
       <c r="O216" s="31" t="n">
-        <v>-2.1</v>
+        <v>-3.2</v>
       </c>
       <c r="P216" s="31" t="n">
-        <v>15.3</v>
+        <v>17.1</v>
       </c>
       <c r="Q216" s="31" t="n">
-        <v>4.52</v>
+        <v>5.96</v>
       </c>
       <c r="R216" s="49" t="n"/>
       <c r="S216" s="22" t="inlineStr">
@@ -23527,13 +23521,13 @@
       </c>
       <c r="N219" s="2" t="n"/>
       <c r="O219" s="31" t="n">
-        <v>9.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="P219" s="31" t="n">
-        <v>16.4</v>
+        <v>17.9</v>
       </c>
       <c r="Q219" s="31" t="n">
-        <v>12.36</v>
+        <v>10.4</v>
       </c>
       <c r="R219" s="49" t="n"/>
       <c r="S219" s="22" t="inlineStr">
@@ -23640,13 +23634,13 @@
       </c>
       <c r="N220" s="2" t="n"/>
       <c r="O220" s="31" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="P220" s="31" t="n">
-        <v>16.9</v>
+        <v>18.3</v>
       </c>
       <c r="Q220" s="31" t="n">
-        <v>10.02</v>
+        <v>11.35</v>
       </c>
       <c r="R220" s="49" t="n"/>
       <c r="S220" s="22" t="inlineStr">
@@ -24040,14 +24034,12 @@
         </is>
       </c>
       <c r="O224" s="31" t="n">
-        <v>-8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="P224" s="31" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="Q224" s="31" t="n">
-        <v>4.55</v>
-      </c>
+        <v>12.2</v>
+      </c>
+      <c r="Q224" s="31" t="n"/>
       <c r="R224" s="49" t="n"/>
       <c r="S224" s="22" t="inlineStr">
         <is>
@@ -26283,13 +26275,13 @@
       </c>
       <c r="N248" s="2" t="n"/>
       <c r="O248" s="31" t="n">
-        <v>-1.4</v>
+        <v>2.6</v>
       </c>
       <c r="P248" s="31" t="n">
-        <v>9.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q248" s="31" t="n">
-        <v>4.24</v>
+        <v>5.28</v>
       </c>
       <c r="R248" s="49" t="n"/>
       <c r="S248" s="22" t="inlineStr">
@@ -26777,10 +26769,10 @@
       </c>
       <c r="N253" s="2" t="n"/>
       <c r="O253" s="31" t="n">
-        <v>-12.1</v>
+        <v>-7</v>
       </c>
       <c r="P253" s="31" t="n">
-        <v>1.8</v>
+        <v>10.5</v>
       </c>
       <c r="Q253" s="31" t="n"/>
       <c r="R253" s="49" t="n"/>
@@ -27158,10 +27150,10 @@
       </c>
       <c r="N257" s="2" t="n"/>
       <c r="O257" s="31" t="n">
-        <v>-73.2</v>
+        <v>-65.09999999999999</v>
       </c>
       <c r="P257" s="31" t="n">
-        <v>-61.5</v>
+        <v>-61.4</v>
       </c>
       <c r="Q257" s="31" t="n"/>
       <c r="R257" s="49" t="n"/>
@@ -28351,15 +28343,9 @@
         </is>
       </c>
       <c r="N269" s="2" t="n"/>
-      <c r="O269" s="31" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="P269" s="31" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="Q269" s="31" t="n">
-        <v>4.19</v>
-      </c>
+      <c r="O269" s="31" t="n"/>
+      <c r="P269" s="31" t="n"/>
+      <c r="Q269" s="31" t="n"/>
       <c r="R269" s="49" t="n"/>
       <c r="S269" s="22" t="inlineStr">
         <is>
@@ -32032,8 +32018,12 @@
         </is>
       </c>
       <c r="N306" s="2" t="n"/>
-      <c r="O306" s="31" t="n"/>
-      <c r="P306" s="31" t="n"/>
+      <c r="O306" s="31" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P306" s="31" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Q306" s="31" t="n"/>
       <c r="R306" s="49" t="n"/>
       <c r="S306" s="22" t="inlineStr">

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="极寒收集" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'站点信息和记录'!$A$1:$AI$405</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'站点信息和记录'!$A$1:$AI$406</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -804,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI405"/>
+  <dimension ref="A1:AI406"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.59765625" defaultRowHeight="20.25"/>
   <cols>
     <col width="4.59765625" customWidth="1" style="5" min="1" max="1"/>
@@ -830,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="732"/>
-    <col width="12.59765625" customWidth="1" style="5" min="733" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="740"/>
+    <col width="12.59765625" customWidth="1" style="5" min="741" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>6.4</v>
+        <v>-1.4</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>19.8</v>
+        <v>9.6</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>12.08</v>
+        <v>4.26</v>
       </c>
       <c r="R2" s="49" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>7.8</v>
+        <v>-2.1</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>16.7</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="49" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>4.7</v>
+        <v>-6.3</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>13.3</v>
+        <v>5.7</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="49" t="inlineStr">
@@ -1389,7 +1389,7 @@
       <c r="T5" s="35" t="n"/>
       <c r="U5" s="39" t="inlineStr">
         <is>
-          <t>伊德尔河 杭爱山</t>
+          <t>杭爱山</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>-0.2</v>
+        <v>-3</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>12.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>4.71</v>
+        <v>-0.29</v>
       </c>
       <c r="R6" s="51" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
       <c r="T6" s="35" t="n"/>
       <c r="U6" s="39" t="inlineStr">
         <is>
-          <t>扎布汗河 杭爱山</t>
+          <t>杭爱山</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1691,13 +1691,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>-0.5</v>
+        <v>1.1</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>17.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>7.51</v>
+        <v>4.15</v>
       </c>
       <c r="R8" s="49" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1804,13 +1804,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>15.9</v>
+        <v>11.1</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>10.63</v>
+        <v>6.7</v>
       </c>
       <c r="R9" s="49" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>2.5</v>
+        <v>-8.1</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>22.9</v>
+        <v>4</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>7.68</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="R10" s="49" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>-3.4</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>13.7</v>
+        <v>0.9</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>4.99</v>
+        <v>-2.92</v>
       </c>
       <c r="R11" s="49" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
       <c r="T11" s="35" t="n"/>
       <c r="U11" s="39" t="inlineStr">
         <is>
-          <t>扎布汗</t>
+          <t>杭爱山</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -2159,13 +2159,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>3</v>
+        <v>-3.8</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>15.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>8.24</v>
+        <v>-0.1</v>
       </c>
       <c r="R12" s="49" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
       <c r="T12" s="35" t="n"/>
       <c r="U12" s="39" t="inlineStr">
         <is>
-          <t>伊德尔河 杭爱山</t>
+          <t>杭爱山</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>2.2</v>
+        <v>-6.8</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>12.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>6.29</v>
+        <v>-2.76</v>
       </c>
       <c r="R13" s="49" t="inlineStr">
         <is>
@@ -2397,13 +2397,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>6.25</v>
+        <v>3.04</v>
       </c>
       <c r="R14" s="49" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2518,13 +2518,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>0.8</v>
+        <v>-1.8</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>4.15</v>
+        <v>1.12</v>
       </c>
       <c r="R15" s="49" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2535,7 +2535,7 @@
       <c r="T15" s="35" t="n"/>
       <c r="U15" s="39" t="inlineStr">
         <is>
-          <t>乌兰巴托郊县&lt;br&gt;Налайх</t>
+          <t>乌兰巴托郊县&lt;br&gt;Налайх / Terelj</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       <c r="T16" s="35" t="n"/>
       <c r="U16" s="39" t="inlineStr">
         <is>
-          <t>乌兰巴托机场</t>
+          <t>乌兰巴托机场&lt;br&gt;Buyant-Ukhaa</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -4494,9 +4494,15 @@
         </is>
       </c>
       <c r="N36" s="2" t="n"/>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="31" t="n"/>
+      <c r="O36" s="31" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="P36" s="31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q36" s="31" t="n">
+        <v>-0.75</v>
+      </c>
       <c r="R36" s="49" t="n"/>
       <c r="S36" s="22" t="n"/>
       <c r="T36" s="35" t="n"/>
@@ -4783,9 +4789,15 @@
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
-      <c r="O39" s="31" t="n"/>
-      <c r="P39" s="31" t="n"/>
-      <c r="Q39" s="31" t="n"/>
+      <c r="O39" s="31" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="P39" s="31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q39" s="31" t="n">
+        <v>-3.17</v>
+      </c>
       <c r="R39" s="49" t="n"/>
       <c r="S39" s="22" t="n"/>
       <c r="T39" s="35" t="n"/>
@@ -6949,7 +6961,7 @@
       <c r="T63" s="35" t="n"/>
       <c r="U63" s="39" t="inlineStr">
         <is>
-          <t>伊德尔河&lt;br&gt;扎布汗</t>
+          <t>扎布汗</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
@@ -9165,7 +9177,7 @@
       <c r="T87" s="35" t="n"/>
       <c r="U87" s="39" t="inlineStr">
         <is>
-          <t>布列亚河 布列亚山</t>
+          <t>布列亚山</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
@@ -9265,13 +9277,13 @@
         </is>
       </c>
       <c r="O88" s="31" t="n">
-        <v>-7.5</v>
+        <v>-2.9</v>
       </c>
       <c r="P88" s="31" t="n">
-        <v>10.4</v>
+        <v>14.4</v>
       </c>
       <c r="Q88" s="31" t="n">
-        <v>2.07</v>
+        <v>5.46</v>
       </c>
       <c r="R88" s="49" t="inlineStr">
         <is>
@@ -9699,13 +9711,13 @@
         </is>
       </c>
       <c r="O92" s="31" t="n">
-        <v>-8.5</v>
+        <v>-5.9</v>
       </c>
       <c r="P92" s="31" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="Q92" s="31" t="n">
-        <v>2.96</v>
+        <v>2.18</v>
       </c>
       <c r="R92" s="49" t="n"/>
       <c r="S92" s="22" t="inlineStr">
@@ -9716,7 +9728,7 @@
       <c r="T92" s="35" t="n"/>
       <c r="U92" s="39" t="inlineStr">
         <is>
-          <t>卡连加河&lt;br&gt;外贝加尔</t>
+          <t>外贝加尔</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
@@ -9821,13 +9833,13 @@
         </is>
       </c>
       <c r="O93" s="31" t="n">
-        <v>-7.9</v>
+        <v>-6.5</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>16.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>2.96</v>
+        <v>-0.46</v>
       </c>
       <c r="R93" s="49" t="n"/>
       <c r="S93" s="22" t="inlineStr">
@@ -9838,7 +9850,7 @@
       <c r="T93" s="35" t="n"/>
       <c r="U93" s="39" t="inlineStr">
         <is>
-          <t>卡连加河&lt;br&gt;外贝加尔</t>
+          <t>外贝加尔</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
@@ -10041,13 +10053,13 @@
         </is>
       </c>
       <c r="O95" s="31" t="n">
-        <v>-3.5</v>
+        <v>-2.9</v>
       </c>
       <c r="P95" s="31" t="n">
-        <v>17.5</v>
+        <v>6.7</v>
       </c>
       <c r="Q95" s="31" t="n">
-        <v>4.99</v>
+        <v>1.35</v>
       </c>
       <c r="R95" s="49" t="n"/>
       <c r="S95" s="22" t="inlineStr">
@@ -10165,7 +10177,7 @@
       <c r="T96" s="35" t="n"/>
       <c r="U96" s="39" t="inlineStr">
         <is>
-          <t>小叶尼塞河&lt;br&gt;图瓦</t>
+          <t>图瓦</t>
         </is>
       </c>
       <c r="V96" s="2" t="inlineStr">
@@ -10261,13 +10273,13 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="31" t="n">
-        <v>2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="P97" s="31" t="n">
-        <v>20.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q97" s="31" t="n">
-        <v>10.34</v>
+        <v>3.52</v>
       </c>
       <c r="R97" s="49" t="n"/>
       <c r="S97" s="22" t="inlineStr">
@@ -10489,13 +10501,13 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="31" t="n">
-        <v>4.3</v>
+        <v>-4.5</v>
       </c>
       <c r="P99" s="31" t="n">
-        <v>12.3</v>
+        <v>7.5</v>
       </c>
       <c r="Q99" s="31" t="n">
-        <v>7.22</v>
+        <v>1.6</v>
       </c>
       <c r="R99" s="49" t="inlineStr">
         <is>
@@ -10720,7 +10732,7 @@
       <c r="T101" s="35" t="n"/>
       <c r="U101" s="39" t="inlineStr">
         <is>
-          <t>额尔齐斯河支流&lt;br&gt;阿尔泰山</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
@@ -10823,7 +10835,7 @@
       <c r="T102" s="35" t="n"/>
       <c r="U102" s="39" t="inlineStr">
         <is>
-          <t>额尔齐斯河支流&lt;br&gt;东哈萨克斯坦州</t>
+          <t>东哈萨克斯坦州</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
@@ -11014,13 +11026,13 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="31" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="P104" s="31" t="n">
-        <v>18.6</v>
+        <v>11.8</v>
       </c>
       <c r="Q104" s="31" t="n">
-        <v>13.01</v>
+        <v>7.09</v>
       </c>
       <c r="R104" s="49" t="n"/>
       <c r="S104" s="22" t="inlineStr">
@@ -11127,13 +11139,13 @@
       </c>
       <c r="N105" s="2" t="n"/>
       <c r="O105" s="31" t="n">
-        <v>14.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P105" s="31" t="n">
-        <v>24.4</v>
+        <v>21.1</v>
       </c>
       <c r="Q105" s="31" t="n">
-        <v>19.07</v>
+        <v>13.5</v>
       </c>
       <c r="R105" s="49" t="n"/>
       <c r="S105" s="22" t="inlineStr">
@@ -11363,13 +11375,13 @@
       </c>
       <c r="N107" s="2" t="n"/>
       <c r="O107" s="31" t="n">
-        <v>9.4</v>
+        <v>6.5</v>
       </c>
       <c r="P107" s="31" t="n">
         <v>20</v>
       </c>
       <c r="Q107" s="31" t="n">
-        <v>14.34</v>
+        <v>13.22</v>
       </c>
       <c r="R107" s="49" t="n"/>
       <c r="S107" s="22" t="inlineStr">
@@ -11488,13 +11500,13 @@
       </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="31" t="n">
-        <v>4.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P108" s="31" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="Q108" s="31" t="n">
-        <v>13.26</v>
+        <v>13.89</v>
       </c>
       <c r="R108" s="49" t="n"/>
       <c r="S108" s="22" t="inlineStr">
@@ -12049,13 +12061,13 @@
       </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="31" t="n">
-        <v>-5.5</v>
+        <v>-1.1</v>
       </c>
       <c r="P113" s="31" t="n">
-        <v>17</v>
+        <v>15.3</v>
       </c>
       <c r="Q113" s="31" t="n">
-        <v>4.27</v>
+        <v>5.41</v>
       </c>
       <c r="R113" s="49" t="n"/>
       <c r="S113" s="22" t="inlineStr">
@@ -12388,13 +12400,13 @@
         </is>
       </c>
       <c r="O116" s="31" t="n">
-        <v>-8.1</v>
+        <v>-2.2</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="Q116" s="31" t="n">
-        <v>3.7</v>
+        <v>7.29</v>
       </c>
       <c r="R116" s="49" t="n"/>
       <c r="S116" s="22" t="inlineStr">
@@ -13682,13 +13694,13 @@
       </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="31" t="n">
-        <v>20.2</v>
+        <v>17.7</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>28.9</v>
+        <v>32</v>
       </c>
       <c r="Q128" s="31" t="n">
-        <v>24.69</v>
+        <v>24.29</v>
       </c>
       <c r="R128" s="49" t="n"/>
       <c r="S128" s="22" t="inlineStr">
@@ -13799,13 +13811,13 @@
       </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="31" t="n">
-        <v>15.3</v>
+        <v>13</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>24.1</v>
+        <v>22.6</v>
       </c>
       <c r="Q129" s="31" t="n">
-        <v>19.02</v>
+        <v>17.54</v>
       </c>
       <c r="R129" s="49" t="n"/>
       <c r="S129" s="22" t="inlineStr">
@@ -14027,13 +14039,13 @@
       </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="31" t="n">
-        <v>13.6</v>
+        <v>4.9</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>23.1</v>
+        <v>20.4</v>
       </c>
       <c r="Q131" s="31" t="n">
-        <v>18.45</v>
+        <v>11.45</v>
       </c>
       <c r="R131" s="49" t="n"/>
       <c r="S131" s="22" t="inlineStr">
@@ -14152,13 +14164,13 @@
       </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="31" t="n">
-        <v>19.1</v>
+        <v>15.4</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>26</v>
+        <v>25.2</v>
       </c>
       <c r="Q132" s="31" t="n">
-        <v>21.36</v>
+        <v>20.19</v>
       </c>
       <c r="R132" s="49" t="n"/>
       <c r="S132" s="22" t="inlineStr">
@@ -14265,13 +14277,13 @@
       </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="31" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>25.1</v>
+        <v>27.3</v>
       </c>
       <c r="Q133" s="31" t="n">
-        <v>19.36</v>
+        <v>18.55</v>
       </c>
       <c r="R133" s="49" t="n"/>
       <c r="S133" s="22" t="inlineStr">
@@ -14386,13 +14398,13 @@
       </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="31" t="n">
-        <v>16.5</v>
+        <v>15.1</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>25</v>
+        <v>22.3</v>
       </c>
       <c r="Q134" s="31" t="n">
-        <v>20.09</v>
+        <v>18.54</v>
       </c>
       <c r="R134" s="49" t="n"/>
       <c r="S134" s="22" t="inlineStr">
@@ -14507,13 +14519,13 @@
       </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="31" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="P135" s="31" t="n">
-        <v>17.7</v>
+        <v>14.4</v>
       </c>
       <c r="Q135" s="31" t="n">
-        <v>11.14</v>
+        <v>9.51</v>
       </c>
       <c r="R135" s="49" t="n"/>
       <c r="S135" s="22" t="inlineStr">
@@ -14628,13 +14640,13 @@
       </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="31" t="n">
-        <v>21.5</v>
+        <v>20.2</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>30.8</v>
+        <v>28.4</v>
       </c>
       <c r="Q136" s="31" t="n">
-        <v>25.48</v>
+        <v>23.57</v>
       </c>
       <c r="R136" s="49" t="n"/>
       <c r="S136" s="22" t="inlineStr">
@@ -14745,13 +14757,13 @@
       </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="31" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>24.9</v>
+        <v>21.9</v>
       </c>
       <c r="Q137" s="31" t="n">
-        <v>23.18</v>
+        <v>21.15</v>
       </c>
       <c r="R137" s="49" t="n"/>
       <c r="S137" s="22" t="inlineStr">
@@ -14862,13 +14874,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>20.3</v>
+        <v>19.6</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="Q138" s="31" t="n">
-        <v>22.13</v>
+        <v>20.65</v>
       </c>
       <c r="R138" s="49" t="n"/>
       <c r="S138" s="22" t="inlineStr">
@@ -15086,13 +15098,13 @@
       </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="31" t="n">
-        <v>20.5</v>
+        <v>23.6</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>31.8</v>
+        <v>32.1</v>
       </c>
       <c r="Q140" s="31" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="R140" s="49" t="n"/>
       <c r="S140" s="22" t="inlineStr">
@@ -15203,13 +15215,13 @@
       </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="31" t="n">
-        <v>23.7</v>
+        <v>26.4</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>33.7</v>
+        <v>35.7</v>
       </c>
       <c r="Q141" s="31" t="n">
-        <v>28.05</v>
+        <v>30.4</v>
       </c>
       <c r="R141" s="49" t="n"/>
       <c r="S141" s="22" t="inlineStr">
@@ -15320,13 +15332,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="31" t="n">
-        <v>20.6</v>
+        <v>22.3</v>
       </c>
       <c r="P142" s="31" t="n">
-        <v>31</v>
+        <v>24.7</v>
       </c>
       <c r="Q142" s="31" t="n">
-        <v>25</v>
+        <v>23.26</v>
       </c>
       <c r="R142" s="49" t="n"/>
       <c r="S142" s="22" t="inlineStr">
@@ -15437,13 +15449,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>23.1</v>
+        <v>19.4</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>25.8</v>
+        <v>23.4</v>
       </c>
       <c r="Q143" s="31" t="n">
-        <v>24.38</v>
+        <v>22.04</v>
       </c>
       <c r="R143" s="49" t="n"/>
       <c r="S143" s="22" t="inlineStr">
@@ -15554,13 +15566,13 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>31.1</v>
+        <v>28.4</v>
       </c>
       <c r="Q144" s="31" t="n">
-        <v>27.17</v>
+        <v>25.6</v>
       </c>
       <c r="R144" s="49" t="n"/>
       <c r="S144" s="22" t="inlineStr">
@@ -15774,13 +15786,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="31" t="n">
-        <v>24.8</v>
+        <v>27</v>
       </c>
       <c r="P146" s="31" t="n">
-        <v>33.4</v>
+        <v>37.1</v>
       </c>
       <c r="Q146" s="31" t="n">
-        <v>28.05</v>
+        <v>30.62</v>
       </c>
       <c r="R146" s="49" t="n"/>
       <c r="S146" s="22" t="inlineStr">
@@ -15891,13 +15903,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>33.8</v>
+        <v>35.5</v>
       </c>
       <c r="Q147" s="31" t="n">
-        <v>28.81</v>
+        <v>29.56</v>
       </c>
       <c r="R147" s="49" t="n"/>
       <c r="S147" s="22" t="inlineStr">
@@ -16210,13 +16222,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>25.5</v>
+        <v>27.7</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="Q150" s="31" t="n">
-        <v>28.45</v>
+        <v>29.75</v>
       </c>
       <c r="R150" s="49" t="n"/>
       <c r="S150" s="22" t="inlineStr">
@@ -16319,13 +16331,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="Q151" s="31" t="n">
-        <v>28.8</v>
+        <v>29.04</v>
       </c>
       <c r="R151" s="49" t="n"/>
       <c r="S151" s="22" t="inlineStr">
@@ -16436,13 +16448,13 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>14.8</v>
+        <v>19.5</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>26.3</v>
+        <v>27.2</v>
       </c>
       <c r="Q152" s="31" t="n">
-        <v>19.96</v>
+        <v>22.21</v>
       </c>
       <c r="R152" s="49" t="n"/>
       <c r="S152" s="22" t="inlineStr">
@@ -16553,13 +16565,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="31" t="n">
-        <v>20.9</v>
+        <v>22.3</v>
       </c>
       <c r="P153" s="31" t="n">
-        <v>30</v>
+        <v>30.4</v>
       </c>
       <c r="Q153" s="31" t="n">
-        <v>24.81</v>
+        <v>25.43</v>
       </c>
       <c r="R153" s="49" t="n"/>
       <c r="S153" s="22" t="inlineStr">
@@ -16670,13 +16682,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>29.1</v>
+        <v>27.9</v>
       </c>
       <c r="Q154" s="31" t="n">
-        <v>25.55</v>
+        <v>25.49</v>
       </c>
       <c r="R154" s="49" t="n"/>
       <c r="S154" s="22" t="inlineStr">
@@ -16878,13 +16890,13 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="31" t="n">
-        <v>20.6</v>
+        <v>21.3</v>
       </c>
       <c r="P156" s="31" t="n">
-        <v>22.1</v>
+        <v>24.5</v>
       </c>
       <c r="Q156" s="31" t="n">
-        <v>21.19</v>
+        <v>22.77</v>
       </c>
       <c r="R156" s="49" t="n"/>
       <c r="S156" s="22" t="inlineStr">
@@ -16999,13 +17011,13 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="31" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P157" s="31" t="n">
-        <v>17.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q157" s="31" t="n">
-        <v>12.21</v>
+        <v>15.12</v>
       </c>
       <c r="R157" s="49" t="n"/>
       <c r="S157" s="22" t="inlineStr">
@@ -17587,13 +17599,13 @@
       </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="31" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="P163" s="31" t="n">
-        <v>3.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q163" s="31" t="n">
-        <v>1.33</v>
+        <v>6.64</v>
       </c>
       <c r="R163" s="49" t="n"/>
       <c r="S163" s="22" t="inlineStr">
@@ -17704,13 +17716,13 @@
         </is>
       </c>
       <c r="O164" s="31" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="P164" s="31" t="n">
-        <v>6.7</v>
+        <v>14.3</v>
       </c>
       <c r="Q164" s="31" t="n">
-        <v>2.2</v>
+        <v>5.93</v>
       </c>
       <c r="R164" s="49" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -17784,8 +17796,10 @@
         <v>164</v>
       </c>
       <c r="B165" s="2" t="n"/>
-      <c r="C165" s="44" t="n">
-        <v>54517</v>
+      <c r="C165" s="44" t="inlineStr">
+        <is>
+          <t>54527</t>
+        </is>
       </c>
       <c r="D165" s="2" t="n"/>
       <c r="E165" s="4" t="n">
@@ -17817,13 +17831,13 @@
       </c>
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="31" t="n">
-        <v>20</v>
+        <v>16.9</v>
       </c>
       <c r="P165" s="31" t="n">
-        <v>26.2</v>
+        <v>25.7</v>
       </c>
       <c r="Q165" s="31" t="n">
-        <v>22.29</v>
+        <v>21.53</v>
       </c>
       <c r="R165" s="49" t="n"/>
       <c r="S165" s="22" t="inlineStr">
@@ -17834,7 +17848,7 @@
       <c r="T165" s="35" t="n"/>
       <c r="U165" s="39" t="inlineStr">
         <is>
-          <t>东丽</t>
+          <t>西青</t>
         </is>
       </c>
       <c r="V165" s="2" t="inlineStr">
@@ -17922,13 +17936,13 @@
       </c>
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="31" t="n">
-        <v>23.8</v>
+        <v>24.2</v>
       </c>
       <c r="P166" s="31" t="n">
-        <v>28</v>
+        <v>26.9</v>
       </c>
       <c r="Q166" s="31" t="n">
-        <v>25.73</v>
+        <v>25.63</v>
       </c>
       <c r="R166" s="49" t="n"/>
       <c r="S166" s="22" t="inlineStr">
@@ -18031,13 +18045,13 @@
       </c>
       <c r="N167" s="2" t="n"/>
       <c r="O167" s="31" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="P167" s="31" t="n">
-        <v>20.5</v>
+        <v>24</v>
       </c>
       <c r="Q167" s="31" t="n">
-        <v>16</v>
+        <v>16.16</v>
       </c>
       <c r="R167" s="49" t="n"/>
       <c r="S167" s="22" t="inlineStr">
@@ -18275,13 +18289,13 @@
         </is>
       </c>
       <c r="O169" s="31" t="n">
-        <v>-3.5</v>
+        <v>-0.3</v>
       </c>
       <c r="P169" s="31" t="n">
-        <v>4.4</v>
+        <v>9.1</v>
       </c>
       <c r="Q169" s="31" t="n">
-        <v>-0.46</v>
+        <v>3.51</v>
       </c>
       <c r="R169" s="49" t="n"/>
       <c r="S169" s="22" t="inlineStr">
@@ -18396,13 +18410,13 @@
       </c>
       <c r="N170" s="2" t="n"/>
       <c r="O170" s="31" t="n">
-        <v>0.3</v>
+        <v>-4</v>
       </c>
       <c r="P170" s="31" t="n">
-        <v>14.6</v>
+        <v>13.1</v>
       </c>
       <c r="Q170" s="31" t="n">
-        <v>6.95</v>
+        <v>4.08</v>
       </c>
       <c r="R170" s="49" t="n"/>
       <c r="S170" s="22" t="inlineStr">
@@ -18517,13 +18531,13 @@
       </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="31" t="n">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
       <c r="P171" s="31" t="n">
-        <v>27.2</v>
+        <v>23.4</v>
       </c>
       <c r="Q171" s="31" t="n">
-        <v>23.31</v>
+        <v>21.54</v>
       </c>
       <c r="R171" s="49" t="n"/>
       <c r="S171" s="22" t="inlineStr">
@@ -18630,13 +18644,13 @@
       </c>
       <c r="N172" s="2" t="n"/>
       <c r="O172" s="31" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="P172" s="31" t="n">
-        <v>28.4</v>
+        <v>23</v>
       </c>
       <c r="Q172" s="31" t="n">
-        <v>24.63</v>
+        <v>21.53</v>
       </c>
       <c r="R172" s="49" t="n"/>
       <c r="S172" s="22" t="inlineStr">
@@ -18747,13 +18761,13 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="31" t="n">
-        <v>23.1</v>
+        <v>27.5</v>
       </c>
       <c r="P173" s="31" t="n">
-        <v>36</v>
+        <v>37.2</v>
       </c>
       <c r="Q173" s="31" t="n">
-        <v>28.96</v>
+        <v>31.4</v>
       </c>
       <c r="R173" s="49" t="n"/>
       <c r="S173" s="22" t="inlineStr">
@@ -18860,13 +18874,13 @@
       </c>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="31" t="n">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="P174" s="31" t="n">
-        <v>17.1</v>
+        <v>18.6</v>
       </c>
       <c r="Q174" s="31" t="n">
-        <v>15.41</v>
+        <v>16.81</v>
       </c>
       <c r="R174" s="49" t="n"/>
       <c r="S174" s="22" t="inlineStr">
@@ -19068,13 +19082,13 @@
         </is>
       </c>
       <c r="O176" s="31" t="n">
-        <v>-10.8</v>
+        <v>-6.3</v>
       </c>
       <c r="P176" s="31" t="n">
-        <v>-0.9</v>
+        <v>1</v>
       </c>
       <c r="Q176" s="31" t="n">
-        <v>-6.9</v>
+        <v>-2.7</v>
       </c>
       <c r="R176" s="49" t="n"/>
       <c r="S176" s="22" t="inlineStr">
@@ -19176,8 +19190,12 @@
         </is>
       </c>
       <c r="N177" s="2" t="n"/>
-      <c r="O177" s="31" t="n"/>
-      <c r="P177" s="31" t="n"/>
+      <c r="O177" s="31" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="P177" s="31" t="n">
+        <v>2.5</v>
+      </c>
       <c r="Q177" s="31" t="n"/>
       <c r="R177" s="49" t="n"/>
       <c r="S177" s="22" t="inlineStr">
@@ -19486,14 +19504,12 @@
       </c>
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="31" t="n">
-        <v>3.5</v>
+        <v>-4.5</v>
       </c>
       <c r="P180" s="31" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Q180" s="31" t="n">
-        <v>9.85</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="Q180" s="31" t="n"/>
       <c r="R180" s="49" t="inlineStr">
         <is>
           <t>2010-01-05</t>
@@ -19511,7 +19527,7 @@
       </c>
       <c r="U180" s="39" t="inlineStr">
         <is>
-          <t>河北围场</t>
+          <t>河北围场 坝上</t>
         </is>
       </c>
       <c r="V180" s="2" t="inlineStr">
@@ -19599,10 +19615,10 @@
       </c>
       <c r="N181" s="2" t="n"/>
       <c r="O181" s="31" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="P181" s="31" t="n">
-        <v>10.9</v>
+        <v>10</v>
       </c>
       <c r="Q181" s="31" t="n"/>
       <c r="R181" s="49" t="n"/>
@@ -19706,10 +19722,10 @@
       </c>
       <c r="N182" s="3" t="n"/>
       <c r="O182" s="31" t="n">
-        <v>-4.4</v>
+        <v>-4.5</v>
       </c>
       <c r="P182" s="31" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="Q182" s="31" t="n"/>
       <c r="R182" s="49" t="n"/>
@@ -19821,13 +19837,13 @@
         </is>
       </c>
       <c r="O183" s="31" t="n">
-        <v>-1</v>
+        <v>-5.2</v>
       </c>
       <c r="P183" s="31" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="Q183" s="31" t="n">
-        <v>3.14</v>
+        <v>-2.83</v>
       </c>
       <c r="R183" s="49" t="n"/>
       <c r="S183" s="22" t="inlineStr">
@@ -20242,8 +20258,12 @@
         </is>
       </c>
       <c r="N187" s="2" t="n"/>
-      <c r="O187" s="31" t="n"/>
-      <c r="P187" s="31" t="n"/>
+      <c r="O187" s="31" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="P187" s="31" t="n">
+        <v>17.3</v>
+      </c>
       <c r="Q187" s="31" t="n"/>
       <c r="R187" s="49" t="n"/>
       <c r="S187" s="22" t="inlineStr">
@@ -20664,7 +20684,7 @@
       <c r="T191" s="35" t="n"/>
       <c r="U191" s="42" t="inlineStr">
         <is>
-          <t>陈巴尔虎旗</t>
+          <t>呼伦贝尔陈旗</t>
         </is>
       </c>
       <c r="V191" s="2" t="inlineStr">
@@ -20756,10 +20776,10 @@
       </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="31" t="n">
-        <v>-10.8</v>
+        <v>-8.6</v>
       </c>
       <c r="P192" s="31" t="n">
-        <v>20</v>
+        <v>16.2</v>
       </c>
       <c r="Q192" s="31" t="n"/>
       <c r="R192" s="49" t="n"/>
@@ -20867,10 +20887,10 @@
         </is>
       </c>
       <c r="O193" s="31" t="n">
-        <v>-9.4</v>
+        <v>-0.1</v>
       </c>
       <c r="P193" s="31" t="n">
-        <v>16.3</v>
+        <v>15.8</v>
       </c>
       <c r="Q193" s="31" t="n"/>
       <c r="R193" s="49" t="n"/>
@@ -20978,10 +20998,10 @@
       </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="31" t="n">
-        <v>-7.9</v>
+        <v>-0.4</v>
       </c>
       <c r="P194" s="31" t="n">
-        <v>17.1</v>
+        <v>16.4</v>
       </c>
       <c r="Q194" s="31" t="n"/>
       <c r="R194" s="49" t="inlineStr">
@@ -21299,10 +21319,10 @@
         </is>
       </c>
       <c r="O197" s="31" t="n">
-        <v>-4.7</v>
+        <v>-1</v>
       </c>
       <c r="P197" s="31" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q197" s="31" t="n"/>
       <c r="R197" s="49" t="n"/>
@@ -21525,10 +21545,10 @@
       </c>
       <c r="N199" s="2" t="n"/>
       <c r="O199" s="31" t="n">
-        <v>1.5</v>
+        <v>-6.5</v>
       </c>
       <c r="P199" s="31" t="n">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q199" s="31" t="n"/>
       <c r="R199" s="49" t="n"/>
@@ -21634,7 +21654,7 @@
       </c>
       <c r="N200" s="2" t="n"/>
       <c r="O200" s="31" t="n">
-        <v>-36.3</v>
+        <v>-34.5</v>
       </c>
       <c r="P200" s="31" t="n"/>
       <c r="Q200" s="31" t="n"/>
@@ -22013,7 +22033,7 @@
       <c r="T204" s="35" t="n"/>
       <c r="U204" s="39" t="inlineStr">
         <is>
-          <t>谢列姆贾河&lt;br&gt;阿穆尔州</t>
+          <t>谢列姆贾河&lt;br&gt;阿穆尔 无人监测站</t>
         </is>
       </c>
       <c r="V204" s="2" t="inlineStr">
@@ -22198,13 +22218,13 @@
       </c>
       <c r="N206" s="2" t="n"/>
       <c r="O206" s="31" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="P206" s="31" t="n">
-        <v>19.4</v>
+        <v>16.1</v>
       </c>
       <c r="Q206" s="31" t="n">
-        <v>15.14</v>
+        <v>12.85</v>
       </c>
       <c r="R206" s="49" t="n"/>
       <c r="S206" s="22" t="inlineStr">
@@ -22602,13 +22622,13 @@
       </c>
       <c r="N210" s="2" t="n"/>
       <c r="O210" s="31" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="P210" s="31" t="n">
-        <v>16.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q210" s="31" t="n">
-        <v>7.3</v>
+        <v>4.94</v>
       </c>
       <c r="R210" s="49" t="n"/>
       <c r="S210" s="22" t="inlineStr">
@@ -22619,7 +22639,7 @@
       <c r="T210" s="35" t="n"/>
       <c r="U210" s="39" t="inlineStr">
         <is>
-          <t>贝加尔湖&lt;br&gt;色楞格河 乌达河</t>
+          <t>贝加尔湖&lt;br&gt;色楞格河</t>
         </is>
       </c>
       <c r="V210" s="2" t="inlineStr">
@@ -22812,13 +22832,13 @@
       </c>
       <c r="N212" s="2" t="n"/>
       <c r="O212" s="31" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="P212" s="31" t="n">
-        <v>18.2</v>
+        <v>6.7</v>
       </c>
       <c r="Q212" s="31" t="n">
-        <v>8.289999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="R212" s="49" t="n"/>
       <c r="S212" s="22" t="inlineStr">
@@ -23218,13 +23238,13 @@
       </c>
       <c r="N216" s="2" t="n"/>
       <c r="O216" s="31" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="P216" s="31" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="Q216" s="31" t="n">
-        <v>5.96</v>
+        <v>2.94</v>
       </c>
       <c r="R216" s="49" t="n"/>
       <c r="S216" s="22" t="inlineStr">
@@ -23235,7 +23255,7 @@
       <c r="T216" s="35" t="n"/>
       <c r="U216" s="39" t="inlineStr">
         <is>
-          <t>音果达河</t>
+          <t>外贝加尔</t>
         </is>
       </c>
       <c r="V216" s="2" t="inlineStr">
@@ -23340,7 +23360,7 @@
       <c r="T217" s="35" t="n"/>
       <c r="U217" s="39" t="inlineStr">
         <is>
-          <t>石勒喀河支流&lt;br&gt;外贝加尔</t>
+          <t>外贝加尔</t>
         </is>
       </c>
       <c r="V217" s="2" t="inlineStr">
@@ -23521,13 +23541,13 @@
       </c>
       <c r="N219" s="2" t="n"/>
       <c r="O219" s="31" t="n">
-        <v>3.1</v>
+        <v>-1.6</v>
       </c>
       <c r="P219" s="31" t="n">
-        <v>17.9</v>
+        <v>11.6</v>
       </c>
       <c r="Q219" s="31" t="n">
-        <v>10.4</v>
+        <v>5.65</v>
       </c>
       <c r="R219" s="49" t="n"/>
       <c r="S219" s="22" t="inlineStr">
@@ -23634,13 +23654,13 @@
       </c>
       <c r="N220" s="2" t="n"/>
       <c r="O220" s="31" t="n">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="P220" s="31" t="n">
-        <v>18.3</v>
+        <v>9</v>
       </c>
       <c r="Q220" s="31" t="n">
-        <v>11.35</v>
+        <v>4.46</v>
       </c>
       <c r="R220" s="49" t="n"/>
       <c r="S220" s="22" t="inlineStr">
@@ -23756,11 +23776,7 @@
       <c r="R221" s="49" t="n"/>
       <c r="S221" s="22" t="n"/>
       <c r="T221" s="35" t="n"/>
-      <c r="U221" s="39" t="inlineStr">
-        <is>
-          <t>小阿纽伊河</t>
-        </is>
-      </c>
+      <c r="U221" s="39" t="n"/>
       <c r="V221" s="2" t="inlineStr">
         <is>
           <t>楚科奇</t>
@@ -24034,12 +24050,14 @@
         </is>
       </c>
       <c r="O224" s="31" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="P224" s="31" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q224" s="31" t="n"/>
+        <v>5.9</v>
+      </c>
+      <c r="Q224" s="31" t="n">
+        <v>2.86</v>
+      </c>
       <c r="R224" s="49" t="n"/>
       <c r="S224" s="22" t="inlineStr">
         <is>
@@ -24049,7 +24067,7 @@
       <c r="T224" s="35" t="n"/>
       <c r="U224" s="39" t="inlineStr">
         <is>
-          <t>通古斯卡河支流&lt;br&gt;克拉斯诺亚尔斯克</t>
+          <t>克拉斯诺亚尔斯克</t>
         </is>
       </c>
       <c r="V224" s="2" t="inlineStr">
@@ -24332,7 +24350,7 @@
       <c r="T227" s="35" t="n"/>
       <c r="U227" s="39" t="inlineStr">
         <is>
-          <t>赫塔河&lt;br&gt;克拉斯诺亚尔斯克</t>
+          <t>克拉斯诺亚尔斯克</t>
         </is>
       </c>
       <c r="V227" s="2" t="inlineStr">
@@ -24973,7 +24991,7 @@
       <c r="T234" s="35" t="n"/>
       <c r="U234" s="39" t="inlineStr">
         <is>
-          <t>马尔哈河&lt;br&gt;萨哈</t>
+          <t>萨哈</t>
         </is>
       </c>
       <c r="V234" s="2" t="inlineStr">
@@ -26275,13 +26293,13 @@
       </c>
       <c r="N248" s="2" t="n"/>
       <c r="O248" s="31" t="n">
-        <v>2.6</v>
+        <v>-12.1</v>
       </c>
       <c r="P248" s="31" t="n">
-        <v>8.699999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="Q248" s="31" t="n">
-        <v>5.28</v>
+        <v>-5.7</v>
       </c>
       <c r="R248" s="49" t="n"/>
       <c r="S248" s="22" t="inlineStr">
@@ -26292,7 +26310,7 @@
       <c r="T248" s="35" t="n"/>
       <c r="U248" s="39" t="inlineStr">
         <is>
-          <t>奥伊米亚康&lt;br&gt;萨哈</t>
+          <t>因迪吉尔卡河&lt;br&gt;萨哈 奥伊米亚康</t>
         </is>
       </c>
       <c r="V248" s="2" t="inlineStr">
@@ -26769,10 +26787,10 @@
       </c>
       <c r="N253" s="2" t="n"/>
       <c r="O253" s="31" t="n">
-        <v>-7</v>
+        <v>-9.1</v>
       </c>
       <c r="P253" s="31" t="n">
-        <v>10.5</v>
+        <v>16.8</v>
       </c>
       <c r="Q253" s="31" t="n"/>
       <c r="R253" s="49" t="n"/>
@@ -26784,7 +26802,7 @@
       <c r="T253" s="35" t="n"/>
       <c r="U253" s="39" t="inlineStr">
         <is>
-          <t>外兴安岭&lt;br&gt;萨哈</t>
+          <t>外兴安岭&lt;br&gt;萨哈 无人监测站</t>
         </is>
       </c>
       <c r="V253" s="2" t="inlineStr">
@@ -27150,10 +27168,10 @@
       </c>
       <c r="N257" s="2" t="n"/>
       <c r="O257" s="31" t="n">
-        <v>-65.09999999999999</v>
+        <v>-76.3</v>
       </c>
       <c r="P257" s="31" t="n">
-        <v>-61.4</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="Q257" s="31" t="n"/>
       <c r="R257" s="49" t="n"/>
@@ -27349,7 +27367,7 @@
       <c r="T259" s="35" t="n"/>
       <c r="U259" s="39" t="inlineStr">
         <is>
-          <t>哈萨克斯坦首都</t>
+          <t>世界第二冷首都</t>
         </is>
       </c>
       <c r="V259" s="2" t="inlineStr">
@@ -28658,7 +28676,7 @@
       <c r="T272" s="35" t="n"/>
       <c r="U272" s="39" t="inlineStr">
         <is>
-          <t>黑龙江&lt;br&gt;小兴安岭</t>
+          <t>黑龙江 小兴安岭</t>
         </is>
       </c>
       <c r="V272" s="2" t="inlineStr">
@@ -31729,7 +31747,7 @@
       <c r="T303" s="35" t="n"/>
       <c r="U303" s="39" t="inlineStr">
         <is>
-          <t>鄂伦春自治旗</t>
+          <t>鄂伦春</t>
         </is>
       </c>
       <c r="V303" s="2" t="inlineStr">
@@ -31832,7 +31850,7 @@
       <c r="T304" s="35" t="n"/>
       <c r="U304" s="39" t="inlineStr">
         <is>
-          <t>鄂伦春自治旗</t>
+          <t>鄂伦春</t>
         </is>
       </c>
       <c r="V304" s="2" t="inlineStr">
@@ -31931,7 +31949,7 @@
       <c r="T305" s="35" t="n"/>
       <c r="U305" s="39" t="inlineStr">
         <is>
-          <t>鄂伦春自治旗</t>
+          <t>鄂伦春</t>
         </is>
       </c>
       <c r="V305" s="2" t="inlineStr">
@@ -32019,10 +32037,10 @@
       </c>
       <c r="N306" s="2" t="n"/>
       <c r="O306" s="31" t="n">
-        <v>-9</v>
+        <v>-7.6</v>
       </c>
       <c r="P306" s="31" t="n">
-        <v>16.4</v>
+        <v>14.7</v>
       </c>
       <c r="Q306" s="31" t="n"/>
       <c r="R306" s="49" t="n"/>
@@ -32424,7 +32442,7 @@
       <c r="L310" s="3" t="n"/>
       <c r="M310" s="14" t="inlineStr">
         <is>
-          <t>根河敖乡</t>
+          <t>敖乡</t>
         </is>
       </c>
       <c r="N310" s="2" t="n"/>
@@ -32440,7 +32458,7 @@
       <c r="T310" s="35" t="n"/>
       <c r="U310" s="39" t="inlineStr">
         <is>
-          <t>敖鲁古雅乡</t>
+          <t>根河敖鲁古雅乡</t>
         </is>
       </c>
       <c r="V310" s="2" t="inlineStr">
@@ -32915,9 +32933,15 @@
         </is>
       </c>
       <c r="N315" s="2" t="n"/>
-      <c r="O315" s="31" t="n"/>
-      <c r="P315" s="31" t="n"/>
-      <c r="Q315" s="31" t="n"/>
+      <c r="O315" s="31" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="P315" s="31" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Q315" s="31" t="n">
+        <v>4.13</v>
+      </c>
       <c r="R315" s="49" t="n"/>
       <c r="S315" s="22" t="inlineStr">
         <is>
@@ -33970,7 +33994,7 @@
       <c r="T326" s="35" t="n"/>
       <c r="U326" s="39" t="inlineStr">
         <is>
-          <t>锡林郭勒盟</t>
+          <t>锡林郭勒</t>
         </is>
       </c>
       <c r="V326" s="2" t="inlineStr">
@@ -34758,9 +34782,15 @@
         </is>
       </c>
       <c r="N334" s="2" t="n"/>
-      <c r="O334" s="31" t="n"/>
-      <c r="P334" s="31" t="n"/>
-      <c r="Q334" s="31" t="n"/>
+      <c r="O334" s="31" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="P334" s="31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q334" s="31" t="n">
+        <v>-9.9</v>
+      </c>
       <c r="R334" s="49" t="n"/>
       <c r="S334" s="22" t="n"/>
       <c r="T334" s="35" t="n"/>
@@ -34826,17 +34856,17 @@
       <c r="E335" s="4" t="n"/>
       <c r="F335" s="37" t="inlineStr">
         <is>
-          <t>U7502</t>
+          <t>U7801</t>
         </is>
       </c>
       <c r="G335" s="28" t="n">
-        <v>31.0958</v>
+        <v>30.594</v>
       </c>
       <c r="H335" s="28" t="n">
-        <v>81.36969999999999</v>
+        <v>82.473</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>5642</v>
+        <v>5047</v>
       </c>
       <c r="J335" s="26" t="n">
         <v>12</v>
@@ -34849,7 +34879,7 @@
       <c r="L335" s="2" t="n"/>
       <c r="M335" s="14" t="inlineStr">
         <is>
-          <t>冈仁波齐3</t>
+          <t>普兰马攸木</t>
         </is>
       </c>
       <c r="N335" s="2" t="n"/>
@@ -34861,7 +34891,7 @@
       <c r="T335" s="35" t="n"/>
       <c r="U335" s="39" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>西藏阿里&lt;br&gt;(交通)</t>
         </is>
       </c>
       <c r="V335" s="2" t="inlineStr">
@@ -34908,7 +34938,11 @@
         </is>
       </c>
       <c r="AG335" s="4" t="n"/>
-      <c r="AH335" s="2" t="n"/>
+      <c r="AH335" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AI335" s="2" t="n"/>
     </row>
     <row r="336" ht="24" customHeight="1" s="54">
@@ -34921,12 +34955,18 @@
       <c r="E336" s="4" t="n"/>
       <c r="F336" s="37" t="inlineStr">
         <is>
-          <t>U7101</t>
-        </is>
-      </c>
-      <c r="G336" s="28" t="n"/>
-      <c r="H336" s="28" t="n"/>
-      <c r="I336" s="2" t="n"/>
+          <t>U7502</t>
+        </is>
+      </c>
+      <c r="G336" s="28" t="n">
+        <v>31.0958</v>
+      </c>
+      <c r="H336" s="28" t="n">
+        <v>81.36969999999999</v>
+      </c>
+      <c r="I336" s="2" t="n">
+        <v>5642</v>
+      </c>
       <c r="J336" s="26" t="n">
         <v>12</v>
       </c>
@@ -34938,7 +34978,7 @@
       <c r="L336" s="2" t="n"/>
       <c r="M336" s="14" t="inlineStr">
         <is>
-          <t>冈仁波齐4</t>
+          <t>冈仁波齐3</t>
         </is>
       </c>
       <c r="N336" s="2" t="n"/>
@@ -35005,25 +35045,17 @@
         <v>336</v>
       </c>
       <c r="B337" s="2" t="n"/>
-      <c r="C337" s="44" t="inlineStr">
-        <is>
-          <t>55026</t>
-        </is>
-      </c>
+      <c r="C337" s="44" t="n"/>
       <c r="D337" s="2" t="n"/>
-      <c r="E337" s="4" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F337" s="37" t="n"/>
-      <c r="G337" s="28" t="n">
-        <v>34.4264</v>
-      </c>
-      <c r="H337" s="28" t="n">
-        <v>80.3861</v>
-      </c>
-      <c r="I337" s="2" t="n">
-        <v>5188.6</v>
-      </c>
+      <c r="E337" s="4" t="n"/>
+      <c r="F337" s="37" t="inlineStr">
+        <is>
+          <t>U7101</t>
+        </is>
+      </c>
+      <c r="G337" s="28" t="n"/>
+      <c r="H337" s="28" t="n"/>
+      <c r="I337" s="2" t="n"/>
       <c r="J337" s="26" t="n">
         <v>12</v>
       </c>
@@ -35035,7 +35067,7 @@
       <c r="L337" s="2" t="n"/>
       <c r="M337" s="14" t="inlineStr">
         <is>
-          <t>松西</t>
+          <t>冈仁波齐4</t>
         </is>
       </c>
       <c r="N337" s="2" t="n"/>
@@ -35071,8 +35103,16 @@
         </is>
       </c>
       <c r="Z337" s="4" t="n"/>
-      <c r="AA337" s="2" t="n"/>
-      <c r="AB337" s="2" t="n"/>
+      <c r="AA337" s="2" t="inlineStr">
+        <is>
+          <t>阿里地区</t>
+        </is>
+      </c>
+      <c r="AB337" s="2" t="inlineStr">
+        <is>
+          <t>普兰县</t>
+        </is>
+      </c>
       <c r="AC337" s="2" t="n"/>
       <c r="AD337" s="2" t="n"/>
       <c r="AE337" s="2" t="inlineStr">
@@ -35094,26 +35134,24 @@
         <v>337</v>
       </c>
       <c r="B338" s="2" t="n"/>
-      <c r="C338" s="44" t="n">
-        <v>45007</v>
-      </c>
-      <c r="D338" s="2" t="inlineStr">
-        <is>
-          <t>Hong_Kong_(airport)</t>
-        </is>
-      </c>
+      <c r="C338" s="44" t="inlineStr">
+        <is>
+          <t>55026</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="n"/>
       <c r="E338" s="4" t="n">
         <v>99999</v>
       </c>
       <c r="F338" s="37" t="n"/>
       <c r="G338" s="28" t="n">
-        <v>22.308919</v>
+        <v>34.4264</v>
       </c>
       <c r="H338" s="28" t="n">
-        <v>113.914603</v>
+        <v>80.3861</v>
       </c>
       <c r="I338" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>5188.6</v>
       </c>
       <c r="J338" s="26" t="n">
         <v>12</v>
@@ -35123,10 +35161,10 @@
           <t>🇨🇳</t>
         </is>
       </c>
-      <c r="L338" s="3" t="n"/>
+      <c r="L338" s="2" t="n"/>
       <c r="M338" s="14" t="inlineStr">
         <is>
-          <t>香港</t>
+          <t>松西</t>
         </is>
       </c>
       <c r="N338" s="2" t="n"/>
@@ -35136,13 +35174,21 @@
       <c r="R338" s="49" t="n"/>
       <c r="S338" s="22" t="n"/>
       <c r="T338" s="35" t="n"/>
-      <c r="U338" s="39" t="n"/>
+      <c r="U338" s="39" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
       <c r="V338" s="2" t="inlineStr">
         <is>
-          <t>香港</t>
-        </is>
-      </c>
-      <c r="W338" s="4" t="n"/>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="W338" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="X338" s="4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -35177,22 +35223,26 @@
         <v>338</v>
       </c>
       <c r="B339" s="2" t="n"/>
-      <c r="C339" s="44" t="n"/>
-      <c r="D339" s="2" t="n"/>
-      <c r="E339" s="4" t="n"/>
-      <c r="F339" s="37" t="inlineStr">
-        <is>
-          <t>Y6758</t>
-        </is>
-      </c>
+      <c r="C339" s="44" t="n">
+        <v>45007</v>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Hong_Kong_(airport)</t>
+        </is>
+      </c>
+      <c r="E339" s="4" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F339" s="37" t="n"/>
       <c r="G339" s="28" t="n">
-        <v>48.0197</v>
+        <v>22.308919</v>
       </c>
       <c r="H339" s="28" t="n">
-        <v>87.5517</v>
+        <v>113.914603</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>1194</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="J339" s="26" t="n">
         <v>12</v>
@@ -35202,10 +35252,10 @@
           <t>🇨🇳</t>
         </is>
       </c>
-      <c r="L339" s="2" t="n"/>
+      <c r="L339" s="3" t="n"/>
       <c r="M339" s="14" t="inlineStr">
         <is>
-          <t>齐背岭水库</t>
+          <t>香港</t>
         </is>
       </c>
       <c r="N339" s="2" t="n"/>
@@ -35213,27 +35263,15 @@
       <c r="P339" s="31" t="n"/>
       <c r="Q339" s="31" t="n"/>
       <c r="R339" s="49" t="n"/>
-      <c r="S339" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="S339" s="22" t="n"/>
       <c r="T339" s="35" t="n"/>
-      <c r="U339" s="39" t="inlineStr">
-        <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
+      <c r="U339" s="39" t="n"/>
       <c r="V339" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="W339" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="W339" s="4" t="n"/>
       <c r="X339" s="4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -35245,16 +35283,8 @@
         </is>
       </c>
       <c r="Z339" s="4" t="n"/>
-      <c r="AA339" s="2" t="inlineStr">
-        <is>
-          <t>阿勒泰地区</t>
-        </is>
-      </c>
-      <c r="AB339" s="2" t="inlineStr">
-        <is>
-          <t>阿勒泰市</t>
-        </is>
-      </c>
+      <c r="AA339" s="2" t="n"/>
+      <c r="AB339" s="2" t="n"/>
       <c r="AC339" s="2" t="n"/>
       <c r="AD339" s="2" t="n"/>
       <c r="AE339" s="2" t="inlineStr">
@@ -35268,11 +35298,7 @@
         </is>
       </c>
       <c r="AG339" s="4" t="n"/>
-      <c r="AH339" s="2" t="inlineStr">
-        <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
+      <c r="AH339" s="2" t="n"/>
       <c r="AI339" s="2" t="n"/>
     </row>
     <row r="340" ht="24" customHeight="1" s="54">
@@ -35285,17 +35311,17 @@
       <c r="E340" s="4" t="n"/>
       <c r="F340" s="37" t="inlineStr">
         <is>
-          <t>Y5315</t>
+          <t>Y6758</t>
         </is>
       </c>
       <c r="G340" s="28" t="n">
-        <v>48.7217</v>
+        <v>48.0197</v>
       </c>
       <c r="H340" s="28" t="n">
-        <v>87.03060000000001</v>
+        <v>87.5517</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>1367</v>
+        <v>1194</v>
       </c>
       <c r="J340" s="26" t="n">
         <v>12</v>
@@ -35305,10 +35331,10 @@
           <t>🇨🇳</t>
         </is>
       </c>
-      <c r="L340" s="3" t="n"/>
+      <c r="L340" s="2" t="n"/>
       <c r="M340" s="14" t="inlineStr">
         <is>
-          <t>喀纳斯</t>
+          <t>齐背岭水库</t>
         </is>
       </c>
       <c r="N340" s="2" t="n"/>
@@ -35355,14 +35381,10 @@
       </c>
       <c r="AB340" s="2" t="inlineStr">
         <is>
-          <t>布尔津县</t>
-        </is>
-      </c>
-      <c r="AC340" s="2" t="inlineStr">
-        <is>
-          <t>禾木喀纳斯蒙古族乡</t>
-        </is>
-      </c>
+          <t>阿勒泰市</t>
+        </is>
+      </c>
+      <c r="AC340" s="2" t="n"/>
       <c r="AD340" s="2" t="n"/>
       <c r="AE340" s="2" t="inlineStr">
         <is>
@@ -35380,11 +35402,7 @@
           <t>阿尔泰山</t>
         </is>
       </c>
-      <c r="AI340" s="2" t="inlineStr">
-        <is>
-          <t>非定居点</t>
-        </is>
-      </c>
+      <c r="AI340" s="2" t="n"/>
     </row>
     <row r="341" ht="24" customHeight="1" s="54">
       <c r="A341" s="2" t="n">
@@ -35396,17 +35414,17 @@
       <c r="E341" s="4" t="n"/>
       <c r="F341" s="37" t="inlineStr">
         <is>
-          <t>Y5322</t>
+          <t>Y5315</t>
         </is>
       </c>
       <c r="G341" s="28" t="n">
-        <v>48.5842</v>
+        <v>48.7217</v>
       </c>
       <c r="H341" s="28" t="n">
-        <v>87.45780000000001</v>
+        <v>87.03060000000001</v>
       </c>
       <c r="I341" s="2" t="n">
-        <v>1223</v>
+        <v>1367</v>
       </c>
       <c r="J341" s="26" t="n">
         <v>12</v>
@@ -35419,14 +35437,10 @@
       <c r="L341" s="3" t="n"/>
       <c r="M341" s="14" t="inlineStr">
         <is>
-          <t>禾木村</t>
-        </is>
-      </c>
-      <c r="N341" s="23" t="inlineStr">
-        <is>
-          <t>❄️</t>
-        </is>
-      </c>
+          <t>喀纳斯</t>
+        </is>
+      </c>
+      <c r="N341" s="2" t="n"/>
       <c r="O341" s="31" t="n"/>
       <c r="P341" s="31" t="n"/>
       <c r="Q341" s="31" t="n"/>
@@ -35495,29 +35509,33 @@
           <t>阿尔泰山</t>
         </is>
       </c>
-      <c r="AI341" s="2" t="n"/>
+      <c r="AI341" s="2" t="inlineStr">
+        <is>
+          <t>非定居点</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="24" customHeight="1" s="54">
       <c r="A342" s="2" t="n">
         <v>341</v>
       </c>
       <c r="B342" s="2" t="n"/>
-      <c r="C342" s="44" t="n">
-        <v>51068</v>
-      </c>
+      <c r="C342" s="44" t="n"/>
       <c r="D342" s="2" t="n"/>
-      <c r="E342" s="4" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F342" s="37" t="n"/>
+      <c r="E342" s="4" t="n"/>
+      <c r="F342" s="37" t="inlineStr">
+        <is>
+          <t>Y5322</t>
+        </is>
+      </c>
       <c r="G342" s="28" t="n">
-        <v>47.125</v>
+        <v>48.5842</v>
       </c>
       <c r="H342" s="28" t="n">
-        <v>87.48139999999999</v>
+        <v>87.45780000000001</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>497.1</v>
+        <v>1223</v>
       </c>
       <c r="J342" s="26" t="n">
         <v>12</v>
@@ -35527,13 +35545,17 @@
           <t>🇨🇳</t>
         </is>
       </c>
-      <c r="L342" s="2" t="n"/>
+      <c r="L342" s="3" t="n"/>
       <c r="M342" s="14" t="inlineStr">
         <is>
-          <t>福海</t>
-        </is>
-      </c>
-      <c r="N342" s="2" t="n"/>
+          <t>禾木村</t>
+        </is>
+      </c>
+      <c r="N342" s="23" t="inlineStr">
+        <is>
+          <t>❄️</t>
+        </is>
+      </c>
       <c r="O342" s="31" t="n"/>
       <c r="P342" s="31" t="n"/>
       <c r="Q342" s="31" t="n"/>
@@ -35546,7 +35568,7 @@
       <c r="T342" s="35" t="n"/>
       <c r="U342" s="39" t="inlineStr">
         <is>
-          <t>乌伦古湖</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V342" s="2" t="inlineStr">
@@ -35577,10 +35599,14 @@
       </c>
       <c r="AB342" s="2" t="inlineStr">
         <is>
-          <t>福海县</t>
-        </is>
-      </c>
-      <c r="AC342" s="2" t="n"/>
+          <t>布尔津县</t>
+        </is>
+      </c>
+      <c r="AC342" s="2" t="inlineStr">
+        <is>
+          <t>禾木喀纳斯蒙古族乡</t>
+        </is>
+      </c>
       <c r="AD342" s="2" t="n"/>
       <c r="AE342" s="2" t="inlineStr">
         <is>
@@ -35595,7 +35621,7 @@
       <c r="AG342" s="4" t="n"/>
       <c r="AH342" s="2" t="inlineStr">
         <is>
-          <t>乌伦古湖</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="AI342" s="2" t="n"/>
@@ -35605,22 +35631,22 @@
         <v>342</v>
       </c>
       <c r="B343" s="2" t="n"/>
-      <c r="C343" s="44" t="n"/>
+      <c r="C343" s="44" t="n">
+        <v>51068</v>
+      </c>
       <c r="D343" s="2" t="n"/>
-      <c r="E343" s="4" t="n"/>
-      <c r="F343" s="37" t="inlineStr">
-        <is>
-          <t>Y6770</t>
-        </is>
-      </c>
+      <c r="E343" s="4" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F343" s="37" t="n"/>
       <c r="G343" s="28" t="n">
-        <v>47.1681</v>
+        <v>47.125</v>
       </c>
       <c r="H343" s="28" t="n">
-        <v>90.0903</v>
+        <v>87.48139999999999</v>
       </c>
       <c r="I343" s="2" t="n">
-        <v>3084</v>
+        <v>497.1</v>
       </c>
       <c r="J343" s="26" t="n">
         <v>12</v>
@@ -35630,17 +35656,13 @@
           <t>🇨🇳</t>
         </is>
       </c>
-      <c r="L343" s="3" t="n"/>
+      <c r="L343" s="2" t="n"/>
       <c r="M343" s="14" t="inlineStr">
         <is>
-          <t>可可托海雪场</t>
-        </is>
-      </c>
-      <c r="N343" s="23" t="inlineStr">
-        <is>
-          <t>🧊</t>
-        </is>
-      </c>
+          <t>福海</t>
+        </is>
+      </c>
+      <c r="N343" s="2" t="n"/>
       <c r="O343" s="31" t="n"/>
       <c r="P343" s="31" t="n"/>
       <c r="Q343" s="31" t="n"/>
@@ -35653,7 +35675,7 @@
       <c r="T343" s="35" t="n"/>
       <c r="U343" s="39" t="inlineStr">
         <is>
-          <t>阿尔泰山</t>
+          <t>乌伦古湖</t>
         </is>
       </c>
       <c r="V343" s="2" t="inlineStr">
@@ -35684,7 +35706,7 @@
       </c>
       <c r="AB343" s="2" t="inlineStr">
         <is>
-          <t>富蕴县</t>
+          <t>福海县</t>
         </is>
       </c>
       <c r="AC343" s="2" t="n"/>
@@ -35702,14 +35724,10 @@
       <c r="AG343" s="4" t="n"/>
       <c r="AH343" s="2" t="inlineStr">
         <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
-      <c r="AI343" s="2" t="inlineStr">
-        <is>
-          <t>非定居点</t>
-        </is>
-      </c>
+          <t>乌伦古湖</t>
+        </is>
+      </c>
+      <c r="AI343" s="2" t="n"/>
     </row>
     <row r="344" ht="24" customHeight="1" s="54">
       <c r="A344" s="2" t="n">
@@ -35721,17 +35739,17 @@
       <c r="E344" s="4" t="n"/>
       <c r="F344" s="37" t="inlineStr">
         <is>
-          <t>Y5316</t>
+          <t>Y6770</t>
         </is>
       </c>
       <c r="G344" s="28" t="n">
-        <v>47.1381</v>
+        <v>47.1681</v>
       </c>
       <c r="H344" s="28" t="n">
-        <v>85.5975</v>
+        <v>90.0903</v>
       </c>
       <c r="I344" s="2" t="n">
-        <v>2914</v>
+        <v>3084</v>
       </c>
       <c r="J344" s="26" t="n">
         <v>12</v>
@@ -35741,13 +35759,17 @@
           <t>🇨🇳</t>
         </is>
       </c>
-      <c r="L344" s="2" t="n"/>
+      <c r="L344" s="3" t="n"/>
       <c r="M344" s="14" t="inlineStr">
         <is>
-          <t>吉木乃冰川</t>
-        </is>
-      </c>
-      <c r="N344" s="23" t="n"/>
+          <t>可可托海雪场</t>
+        </is>
+      </c>
+      <c r="N344" s="23" t="inlineStr">
+        <is>
+          <t>🧊</t>
+        </is>
+      </c>
       <c r="O344" s="31" t="n"/>
       <c r="P344" s="31" t="n"/>
       <c r="Q344" s="31" t="n"/>
@@ -35760,7 +35782,7 @@
       <c r="T344" s="35" t="n"/>
       <c r="U344" s="39" t="inlineStr">
         <is>
-          <t>阿勒泰</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V344" s="2" t="inlineStr">
@@ -35791,7 +35813,7 @@
       </c>
       <c r="AB344" s="2" t="inlineStr">
         <is>
-          <t>吉木乃县</t>
+          <t>富蕴县</t>
         </is>
       </c>
       <c r="AC344" s="2" t="n"/>
@@ -35807,8 +35829,16 @@
         </is>
       </c>
       <c r="AG344" s="4" t="n"/>
-      <c r="AH344" s="2" t="n"/>
-      <c r="AI344" s="2" t="n"/>
+      <c r="AH344" s="2" t="inlineStr">
+        <is>
+          <t>阿尔泰山</t>
+        </is>
+      </c>
+      <c r="AI344" s="2" t="inlineStr">
+        <is>
+          <t>非定居点</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="24" customHeight="1" s="54">
       <c r="A345" s="2" t="n">
@@ -35820,17 +35850,17 @@
       <c r="E345" s="4" t="n"/>
       <c r="F345" s="37" t="inlineStr">
         <is>
-          <t>Y5347</t>
+          <t>Y5316</t>
         </is>
       </c>
       <c r="G345" s="28" t="n">
-        <v>46.1772</v>
+        <v>47.1381</v>
       </c>
       <c r="H345" s="28" t="n">
-        <v>90.5356</v>
+        <v>85.5975</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>1071.1</v>
+        <v>2914</v>
       </c>
       <c r="J345" s="26" t="n">
         <v>12</v>
@@ -35843,10 +35873,10 @@
       <c r="L345" s="2" t="n"/>
       <c r="M345" s="14" t="inlineStr">
         <is>
-          <t>塔克什肯镇</t>
-        </is>
-      </c>
-      <c r="N345" s="2" t="n"/>
+          <t>吉木乃冰川</t>
+        </is>
+      </c>
+      <c r="N345" s="23" t="n"/>
       <c r="O345" s="31" t="n"/>
       <c r="P345" s="31" t="n"/>
       <c r="Q345" s="31" t="n"/>
@@ -35859,7 +35889,7 @@
       <c r="T345" s="35" t="n"/>
       <c r="U345" s="39" t="inlineStr">
         <is>
-          <t>阿尔泰山</t>
+          <t>阿勒泰</t>
         </is>
       </c>
       <c r="V345" s="2" t="inlineStr">
@@ -35890,7 +35920,7 @@
       </c>
       <c r="AB345" s="2" t="inlineStr">
         <is>
-          <t>青河县</t>
+          <t>吉木乃县</t>
         </is>
       </c>
       <c r="AC345" s="2" t="n"/>
@@ -35906,42 +35936,30 @@
         </is>
       </c>
       <c r="AG345" s="4" t="n"/>
-      <c r="AH345" s="2" t="inlineStr">
-        <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
+      <c r="AH345" s="2" t="n"/>
       <c r="AI345" s="2" t="n"/>
     </row>
     <row r="346" ht="24" customHeight="1" s="54">
       <c r="A346" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="B346" s="2" t="inlineStr">
-        <is>
-          <t>ogimet</t>
-        </is>
-      </c>
-      <c r="C346" s="44" t="n">
-        <v>51087</v>
-      </c>
-      <c r="D346" s="2" t="inlineStr">
-        <is>
-          <t>Kueerqisi</t>
-        </is>
-      </c>
-      <c r="E346" s="4" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F346" s="37" t="n"/>
+      <c r="B346" s="2" t="n"/>
+      <c r="C346" s="44" t="n"/>
+      <c r="D346" s="2" t="n"/>
+      <c r="E346" s="4" t="n"/>
+      <c r="F346" s="37" t="inlineStr">
+        <is>
+          <t>Y5347</t>
+        </is>
+      </c>
       <c r="G346" s="28" t="n">
-        <v>47.02</v>
+        <v>46.1772</v>
       </c>
       <c r="H346" s="28" t="n">
-        <v>89.5</v>
+        <v>90.5356</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>860.4</v>
+        <v>1071.1</v>
       </c>
       <c r="J346" s="26" t="n">
         <v>12</v>
@@ -35954,7 +35972,7 @@
       <c r="L346" s="2" t="n"/>
       <c r="M346" s="14" t="inlineStr">
         <is>
-          <t>富蕴</t>
+          <t>塔克什肯镇</t>
         </is>
       </c>
       <c r="N346" s="2" t="n"/>
@@ -35962,11 +35980,15 @@
       <c r="P346" s="31" t="n"/>
       <c r="Q346" s="31" t="n"/>
       <c r="R346" s="49" t="n"/>
-      <c r="S346" s="22" t="n"/>
+      <c r="S346" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T346" s="35" t="n"/>
       <c r="U346" s="39" t="inlineStr">
         <is>
-          <t>额尔齐斯河&lt;br&gt;阿尔泰山</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V346" s="2" t="inlineStr">
@@ -35995,7 +36017,11 @@
           <t>阿勒泰地区</t>
         </is>
       </c>
-      <c r="AB346" s="2" t="n"/>
+      <c r="AB346" s="2" t="inlineStr">
+        <is>
+          <t>青河县</t>
+        </is>
+      </c>
       <c r="AC346" s="2" t="n"/>
       <c r="AD346" s="2" t="n"/>
       <c r="AE346" s="2" t="inlineStr">
@@ -36020,16 +36046,32 @@
       <c r="A347" s="2" t="n">
         <v>346</v>
       </c>
-      <c r="B347" s="2" t="n"/>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
       <c r="C347" s="44" t="n">
-        <v>51058</v>
-      </c>
-      <c r="D347" s="2" t="n"/>
-      <c r="E347" s="4" t="n"/>
+        <v>51087</v>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Kueerqisi</t>
+        </is>
+      </c>
+      <c r="E347" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F347" s="37" t="n"/>
-      <c r="G347" s="28" t="n"/>
-      <c r="H347" s="28" t="n"/>
-      <c r="I347" s="2" t="n"/>
+      <c r="G347" s="28" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="H347" s="28" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="I347" s="2" t="n">
+        <v>860.4</v>
+      </c>
       <c r="J347" s="26" t="n">
         <v>12</v>
       </c>
@@ -36041,7 +36083,7 @@
       <c r="L347" s="2" t="n"/>
       <c r="M347" s="14" t="inlineStr">
         <is>
-          <t>阿克达拉</t>
+          <t>富蕴</t>
         </is>
       </c>
       <c r="N347" s="2" t="n"/>
@@ -36049,15 +36091,11 @@
       <c r="P347" s="31" t="n"/>
       <c r="Q347" s="31" t="n"/>
       <c r="R347" s="49" t="n"/>
-      <c r="S347" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="S347" s="22" t="n"/>
       <c r="T347" s="35" t="n"/>
       <c r="U347" s="39" t="inlineStr">
         <is>
-          <t>乌伦古湖</t>
+          <t>额尔齐斯河&lt;br&gt;阿尔泰山</t>
         </is>
       </c>
       <c r="V347" s="2" t="inlineStr">
@@ -36100,7 +36138,11 @@
         </is>
       </c>
       <c r="AG347" s="4" t="n"/>
-      <c r="AH347" s="2" t="n"/>
+      <c r="AH347" s="2" t="inlineStr">
+        <is>
+          <t>阿尔泰山</t>
+        </is>
+      </c>
       <c r="AI347" s="2" t="n"/>
     </row>
     <row r="348" ht="24" customHeight="1" s="54">
@@ -36109,22 +36151,14 @@
       </c>
       <c r="B348" s="2" t="n"/>
       <c r="C348" s="44" t="n">
-        <v>51060</v>
+        <v>51058</v>
       </c>
       <c r="D348" s="2" t="n"/>
-      <c r="E348" s="4" t="n">
-        <v>99999</v>
-      </c>
+      <c r="E348" s="4" t="n"/>
       <c r="F348" s="37" t="n"/>
-      <c r="G348" s="28" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="H348" s="28" t="n">
-        <v>86.87</v>
-      </c>
-      <c r="I348" s="2" t="n">
-        <v>473.9</v>
-      </c>
+      <c r="G348" s="28" t="n"/>
+      <c r="H348" s="28" t="n"/>
+      <c r="I348" s="2" t="n"/>
       <c r="J348" s="26" t="n">
         <v>12</v>
       </c>
@@ -36136,7 +36170,7 @@
       <c r="L348" s="2" t="n"/>
       <c r="M348" s="14" t="inlineStr">
         <is>
-          <t>布尔津</t>
+          <t>阿克达拉</t>
         </is>
       </c>
       <c r="N348" s="2" t="n"/>
@@ -36144,11 +36178,15 @@
       <c r="P348" s="31" t="n"/>
       <c r="Q348" s="31" t="n"/>
       <c r="R348" s="49" t="n"/>
-      <c r="S348" s="22" t="n"/>
+      <c r="S348" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T348" s="35" t="n"/>
       <c r="U348" s="39" t="inlineStr">
         <is>
-          <t>额尔齐斯河</t>
+          <t>乌伦古湖</t>
         </is>
       </c>
       <c r="V348" s="2" t="inlineStr">
@@ -36191,11 +36229,7 @@
         </is>
       </c>
       <c r="AG348" s="4" t="n"/>
-      <c r="AH348" s="2" t="inlineStr">
-        <is>
-          <t>额尔齐斯河</t>
-        </is>
-      </c>
+      <c r="AH348" s="2" t="n"/>
       <c r="AI348" s="2" t="n"/>
     </row>
     <row r="349" ht="24" customHeight="1" s="54">
@@ -36203,22 +36237,22 @@
         <v>348</v>
       </c>
       <c r="B349" s="2" t="n"/>
-      <c r="C349" s="44" t="n"/>
+      <c r="C349" s="44" t="n">
+        <v>51060</v>
+      </c>
       <c r="D349" s="2" t="n"/>
-      <c r="E349" s="4" t="n"/>
-      <c r="F349" s="37" t="inlineStr">
-        <is>
-          <t>Y5826</t>
-        </is>
-      </c>
+      <c r="E349" s="4" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F349" s="37" t="n"/>
       <c r="G349" s="28" t="n">
-        <v>42.716</v>
+        <v>47.7</v>
       </c>
       <c r="H349" s="28" t="n">
-        <v>84.27200000000001</v>
+        <v>86.87</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>2404.3</v>
+        <v>473.9</v>
       </c>
       <c r="J349" s="26" t="n">
         <v>12</v>
@@ -36231,7 +36265,7 @@
       <c r="L349" s="2" t="n"/>
       <c r="M349" s="14" t="inlineStr">
         <is>
-          <t>德尔比勒金牧场</t>
+          <t>布尔津</t>
         </is>
       </c>
       <c r="N349" s="2" t="n"/>
@@ -36243,7 +36277,7 @@
       <c r="T349" s="35" t="n"/>
       <c r="U349" s="39" t="inlineStr">
         <is>
-          <t>天山&lt;br&gt;巴音布鲁克</t>
+          <t>额尔齐斯河</t>
         </is>
       </c>
       <c r="V349" s="2" t="inlineStr">
@@ -36269,14 +36303,10 @@
       <c r="Z349" s="4" t="n"/>
       <c r="AA349" s="2" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
-        </is>
-      </c>
-      <c r="AB349" s="2" t="inlineStr">
-        <is>
-          <t>和静县</t>
-        </is>
-      </c>
+          <t>阿勒泰地区</t>
+        </is>
+      </c>
+      <c r="AB349" s="2" t="n"/>
       <c r="AC349" s="2" t="n"/>
       <c r="AD349" s="2" t="n"/>
       <c r="AE349" s="2" t="inlineStr">
@@ -36292,7 +36322,7 @@
       <c r="AG349" s="4" t="n"/>
       <c r="AH349" s="2" t="inlineStr">
         <is>
-          <t>天山</t>
+          <t>额尔齐斯河</t>
         </is>
       </c>
       <c r="AI349" s="2" t="n"/>
@@ -36302,22 +36332,22 @@
         <v>349</v>
       </c>
       <c r="B350" s="2" t="n"/>
-      <c r="C350" s="44" t="n">
-        <v>51337</v>
-      </c>
+      <c r="C350" s="44" t="n"/>
       <c r="D350" s="2" t="n"/>
-      <c r="E350" s="4" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F350" s="37" t="n"/>
+      <c r="E350" s="4" t="n"/>
+      <c r="F350" s="37" t="inlineStr">
+        <is>
+          <t>Y5826</t>
+        </is>
+      </c>
       <c r="G350" s="28" t="n">
-        <v>44.6028</v>
+        <v>42.716</v>
       </c>
       <c r="H350" s="28" t="n">
-        <v>81.3878</v>
+        <v>84.27200000000001</v>
       </c>
       <c r="I350" s="2" t="n">
-        <v>2100</v>
+        <v>2404.3</v>
       </c>
       <c r="J350" s="26" t="n">
         <v>12</v>
@@ -36327,10 +36357,10 @@
           <t>🇨🇳</t>
         </is>
       </c>
-      <c r="L350" s="3" t="n"/>
+      <c r="L350" s="2" t="n"/>
       <c r="M350" s="14" t="inlineStr">
         <is>
-          <t>赛里木湖</t>
+          <t>德尔比勒金牧场</t>
         </is>
       </c>
       <c r="N350" s="2" t="n"/>
@@ -36338,15 +36368,11 @@
       <c r="P350" s="31" t="n"/>
       <c r="Q350" s="31" t="n"/>
       <c r="R350" s="49" t="n"/>
-      <c r="S350" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="S350" s="22" t="n"/>
       <c r="T350" s="35" t="n"/>
       <c r="U350" s="39" t="inlineStr">
         <is>
-          <t>天山</t>
+          <t>天山&lt;br&gt;巴音布鲁克</t>
         </is>
       </c>
       <c r="V350" s="2" t="inlineStr">
@@ -36372,12 +36398,12 @@
       <c r="Z350" s="4" t="n"/>
       <c r="AA350" s="2" t="inlineStr">
         <is>
-          <t>博尔塔拉蒙古自治州</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="AB350" s="2" t="inlineStr">
         <is>
-          <t>博乐市</t>
+          <t>和静县</t>
         </is>
       </c>
       <c r="AC350" s="2" t="n"/>
@@ -36398,21 +36424,15 @@
           <t>天山</t>
         </is>
       </c>
-      <c r="AI350" s="2" t="inlineStr">
-        <is>
-          <t>非定居点</t>
-        </is>
-      </c>
+      <c r="AI350" s="2" t="n"/>
     </row>
     <row r="351" ht="24" customHeight="1" s="54">
       <c r="A351" s="2" t="n">
         <v>350</v>
       </c>
       <c r="B351" s="2" t="n"/>
-      <c r="C351" s="44" t="inlineStr">
-        <is>
-          <t>51701</t>
-        </is>
+      <c r="C351" s="44" t="n">
+        <v>51337</v>
       </c>
       <c r="D351" s="2" t="n"/>
       <c r="E351" s="4" t="n">
@@ -36420,13 +36440,13 @@
       </c>
       <c r="F351" s="37" t="n"/>
       <c r="G351" s="28" t="n">
-        <v>40.5122</v>
+        <v>44.6028</v>
       </c>
       <c r="H351" s="28" t="n">
-        <v>75.3914</v>
+        <v>81.3878</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>3470.2</v>
+        <v>2100</v>
       </c>
       <c r="J351" s="26" t="n">
         <v>12</v>
@@ -36436,10 +36456,10 @@
           <t>🇨🇳</t>
         </is>
       </c>
-      <c r="L351" s="2" t="n"/>
+      <c r="L351" s="3" t="n"/>
       <c r="M351" s="14" t="inlineStr">
         <is>
-          <t>吐尔尕特</t>
+          <t>赛里木湖</t>
         </is>
       </c>
       <c r="N351" s="2" t="n"/>
@@ -36481,12 +36501,12 @@
       <c r="Z351" s="4" t="n"/>
       <c r="AA351" s="2" t="inlineStr">
         <is>
-          <t>喀什地区</t>
+          <t>博尔塔拉蒙古自治州</t>
         </is>
       </c>
       <c r="AB351" s="2" t="inlineStr">
         <is>
-          <t>喀什市</t>
+          <t>博乐市</t>
         </is>
       </c>
       <c r="AC351" s="2" t="n"/>
@@ -36507,7 +36527,11 @@
           <t>天山</t>
         </is>
       </c>
-      <c r="AI351" s="2" t="n"/>
+      <c r="AI351" s="2" t="inlineStr">
+        <is>
+          <t>非定居点</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="24" customHeight="1" s="54">
       <c r="A352" s="2" t="n">
@@ -36516,7 +36540,7 @@
       <c r="B352" s="2" t="n"/>
       <c r="C352" s="44" t="inlineStr">
         <is>
-          <t>51572</t>
+          <t>51701</t>
         </is>
       </c>
       <c r="D352" s="2" t="n"/>
@@ -36525,13 +36549,13 @@
       </c>
       <c r="F352" s="37" t="n"/>
       <c r="G352" s="28" t="n">
-        <v>42.8908</v>
+        <v>40.5122</v>
       </c>
       <c r="H352" s="28" t="n">
-        <v>89.3056</v>
+        <v>75.3914</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>-48.8</v>
+        <v>3470.2</v>
       </c>
       <c r="J352" s="26" t="n">
         <v>12</v>
@@ -36544,7 +36568,7 @@
       <c r="L352" s="2" t="n"/>
       <c r="M352" s="14" t="inlineStr">
         <is>
-          <t>东坎</t>
+          <t>吐尔尕特</t>
         </is>
       </c>
       <c r="N352" s="2" t="n"/>
@@ -36552,11 +36576,15 @@
       <c r="P352" s="31" t="n"/>
       <c r="Q352" s="31" t="n"/>
       <c r="R352" s="49" t="n"/>
-      <c r="S352" s="22" t="n"/>
+      <c r="S352" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T352" s="35" t="n"/>
       <c r="U352" s="39" t="inlineStr">
         <is>
-          <t>吐鲁番</t>
+          <t>天山</t>
         </is>
       </c>
       <c r="V352" s="2" t="inlineStr">
@@ -36582,12 +36610,12 @@
       <c r="Z352" s="4" t="n"/>
       <c r="AA352" s="2" t="inlineStr">
         <is>
-          <t>吐鲁番市</t>
+          <t>喀什地区</t>
         </is>
       </c>
       <c r="AB352" s="2" t="inlineStr">
         <is>
-          <t>高昌区</t>
+          <t>喀什市</t>
         </is>
       </c>
       <c r="AC352" s="2" t="n"/>
@@ -36603,7 +36631,11 @@
         </is>
       </c>
       <c r="AG352" s="4" t="n"/>
-      <c r="AH352" s="2" t="n"/>
+      <c r="AH352" s="2" t="inlineStr">
+        <is>
+          <t>天山</t>
+        </is>
+      </c>
       <c r="AI352" s="2" t="n"/>
     </row>
     <row r="353" ht="24" customHeight="1" s="54">
@@ -36611,22 +36643,24 @@
         <v>352</v>
       </c>
       <c r="B353" s="2" t="n"/>
-      <c r="C353" s="44" t="n"/>
+      <c r="C353" s="44" t="inlineStr">
+        <is>
+          <t>51572</t>
+        </is>
+      </c>
       <c r="D353" s="2" t="n"/>
-      <c r="E353" s="4" t="n"/>
-      <c r="F353" s="37" t="inlineStr">
-        <is>
-          <t>Y8049</t>
-        </is>
-      </c>
+      <c r="E353" s="4" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F353" s="37" t="n"/>
       <c r="G353" s="28" t="n">
-        <v>42.6856</v>
+        <v>42.8908</v>
       </c>
       <c r="H353" s="28" t="n">
-        <v>89.0656</v>
+        <v>89.3056</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>-106.4</v>
+        <v>-48.8</v>
       </c>
       <c r="J353" s="26" t="n">
         <v>12</v>
@@ -36639,7 +36673,7 @@
       <c r="L353" s="2" t="n"/>
       <c r="M353" s="14" t="inlineStr">
         <is>
-          <t>新鑫盐矿</t>
+          <t>东坎</t>
         </is>
       </c>
       <c r="N353" s="2" t="n"/>
@@ -36711,17 +36745,17 @@
       <c r="E354" s="4" t="n"/>
       <c r="F354" s="37" t="inlineStr">
         <is>
-          <t>Y5774</t>
+          <t>Y8049</t>
         </is>
       </c>
       <c r="G354" s="28" t="n">
-        <v>42.9044</v>
+        <v>42.6856</v>
       </c>
       <c r="H354" s="28" t="n">
-        <v>89.4422</v>
+        <v>89.0656</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>-52</v>
+        <v>-106.4</v>
       </c>
       <c r="J354" s="26" t="n">
         <v>12</v>
@@ -36734,7 +36768,7 @@
       <c r="L354" s="2" t="n"/>
       <c r="M354" s="14" t="inlineStr">
         <is>
-          <t>三堡乡</t>
+          <t>新鑫盐矿</t>
         </is>
       </c>
       <c r="N354" s="2" t="n"/>
@@ -36801,24 +36835,22 @@
         <v>354</v>
       </c>
       <c r="B355" s="2" t="n"/>
-      <c r="C355" s="44" t="inlineStr">
-        <is>
-          <t>51571</t>
-        </is>
-      </c>
+      <c r="C355" s="44" t="n"/>
       <c r="D355" s="2" t="n"/>
-      <c r="E355" s="4" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F355" s="37" t="n"/>
+      <c r="E355" s="4" t="n"/>
+      <c r="F355" s="37" t="inlineStr">
+        <is>
+          <t>Y5774</t>
+        </is>
+      </c>
       <c r="G355" s="28" t="n">
-        <v>42.7669</v>
+        <v>42.9044</v>
       </c>
       <c r="H355" s="28" t="n">
-        <v>88.60080000000001</v>
+        <v>89.4422</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>43.9</v>
+        <v>-52</v>
       </c>
       <c r="J355" s="26" t="n">
         <v>12</v>
@@ -36831,7 +36863,7 @@
       <c r="L355" s="2" t="n"/>
       <c r="M355" s="14" t="inlineStr">
         <is>
-          <t>托克逊</t>
+          <t>三堡乡</t>
         </is>
       </c>
       <c r="N355" s="2" t="n"/>
@@ -36874,7 +36906,7 @@
       </c>
       <c r="AB355" s="2" t="inlineStr">
         <is>
-          <t>托克逊县</t>
+          <t>高昌区</t>
         </is>
       </c>
       <c r="AC355" s="2" t="n"/>
@@ -36900,7 +36932,7 @@
       <c r="B356" s="2" t="n"/>
       <c r="C356" s="44" t="inlineStr">
         <is>
-          <t>51468</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="D356" s="2" t="n"/>
@@ -36909,13 +36941,13 @@
       </c>
       <c r="F356" s="37" t="n"/>
       <c r="G356" s="28" t="n">
-        <v>43.1131</v>
+        <v>42.7669</v>
       </c>
       <c r="H356" s="28" t="n">
-        <v>86.84310000000001</v>
+        <v>88.60080000000001</v>
       </c>
       <c r="I356" s="2" t="n">
-        <v>3540.5</v>
+        <v>43.9</v>
       </c>
       <c r="J356" s="26" t="n">
         <v>12</v>
@@ -36928,7 +36960,7 @@
       <c r="L356" s="2" t="n"/>
       <c r="M356" s="14" t="inlineStr">
         <is>
-          <t>天山大西沟</t>
+          <t>托克逊</t>
         </is>
       </c>
       <c r="N356" s="2" t="n"/>
@@ -36936,15 +36968,11 @@
       <c r="P356" s="31" t="n"/>
       <c r="Q356" s="31" t="n"/>
       <c r="R356" s="49" t="n"/>
-      <c r="S356" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="S356" s="22" t="n"/>
       <c r="T356" s="35" t="n"/>
       <c r="U356" s="39" t="inlineStr">
         <is>
-          <t>天山</t>
+          <t>吐鲁番</t>
         </is>
       </c>
       <c r="V356" s="2" t="inlineStr">
@@ -36970,12 +36998,12 @@
       <c r="Z356" s="4" t="n"/>
       <c r="AA356" s="2" t="inlineStr">
         <is>
-          <t>乌鲁木齐市</t>
+          <t>吐鲁番市</t>
         </is>
       </c>
       <c r="AB356" s="2" t="inlineStr">
         <is>
-          <t>乌鲁木齐县</t>
+          <t>托克逊县</t>
         </is>
       </c>
       <c r="AC356" s="2" t="n"/>
@@ -36991,11 +37019,7 @@
         </is>
       </c>
       <c r="AG356" s="4" t="n"/>
-      <c r="AH356" s="2" t="inlineStr">
-        <is>
-          <t>天山</t>
-        </is>
-      </c>
+      <c r="AH356" s="2" t="n"/>
       <c r="AI356" s="2" t="n"/>
     </row>
     <row r="357" ht="24" customHeight="1" s="54">
@@ -37005,7 +37029,7 @@
       <c r="B357" s="2" t="n"/>
       <c r="C357" s="44" t="inlineStr">
         <is>
-          <t>56976</t>
+          <t>51468</t>
         </is>
       </c>
       <c r="D357" s="2" t="n"/>
@@ -37014,18 +37038,18 @@
       </c>
       <c r="F357" s="37" t="n"/>
       <c r="G357" s="28" t="n">
-        <v>23.2286</v>
+        <v>43.1131</v>
       </c>
       <c r="H357" s="28" t="n">
-        <v>102.8214</v>
+        <v>86.84310000000001</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>312.3</v>
+        <v>3540.5</v>
       </c>
       <c r="J357" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="K357" s="46" t="inlineStr">
+      <c r="K357" s="30" t="inlineStr">
         <is>
           <t>🇨🇳</t>
         </is>
@@ -37033,7 +37057,7 @@
       <c r="L357" s="2" t="n"/>
       <c r="M357" s="14" t="inlineStr">
         <is>
-          <t>元阳</t>
+          <t>天山大西沟</t>
         </is>
       </c>
       <c r="N357" s="2" t="n"/>
@@ -37049,12 +37073,12 @@
       <c r="T357" s="35" t="n"/>
       <c r="U357" s="39" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天山</t>
         </is>
       </c>
       <c r="V357" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="W357" s="4" t="inlineStr">
@@ -37075,12 +37099,12 @@
       <c r="Z357" s="4" t="n"/>
       <c r="AA357" s="2" t="inlineStr">
         <is>
-          <t>红河哈尼族彝族自治州</t>
+          <t>乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB357" s="2" t="inlineStr">
         <is>
-          <t>元阳县</t>
+          <t>乌鲁木齐县</t>
         </is>
       </c>
       <c r="AC357" s="2" t="n"/>
@@ -37096,7 +37120,11 @@
         </is>
       </c>
       <c r="AG357" s="4" t="n"/>
-      <c r="AH357" s="2" t="n"/>
+      <c r="AH357" s="2" t="inlineStr">
+        <is>
+          <t>天山</t>
+        </is>
+      </c>
       <c r="AI357" s="2" t="n"/>
     </row>
     <row r="358" ht="24" customHeight="1" s="54">
@@ -37106,7 +37134,7 @@
       <c r="B358" s="2" t="n"/>
       <c r="C358" s="44" t="inlineStr">
         <is>
-          <t>56673</t>
+          <t>56976</t>
         </is>
       </c>
       <c r="D358" s="2" t="n"/>
@@ -37115,18 +37143,18 @@
       </c>
       <c r="F358" s="37" t="n"/>
       <c r="G358" s="28" t="n">
-        <v>26.9181</v>
+        <v>23.2286</v>
       </c>
       <c r="H358" s="28" t="n">
-        <v>102.9267</v>
+        <v>102.8214</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>893.9</v>
+        <v>312.3</v>
       </c>
       <c r="J358" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="K358" s="30" t="inlineStr">
+      <c r="K358" s="46" t="inlineStr">
         <is>
           <t>🇨🇳</t>
         </is>
@@ -37134,7 +37162,7 @@
       <c r="L358" s="2" t="n"/>
       <c r="M358" s="14" t="inlineStr">
         <is>
-          <t>巧家</t>
+          <t>元阳</t>
         </is>
       </c>
       <c r="N358" s="2" t="n"/>
@@ -37176,12 +37204,12 @@
       <c r="Z358" s="4" t="n"/>
       <c r="AA358" s="2" t="inlineStr">
         <is>
-          <t>昭通市</t>
+          <t>红河哈尼族彝族自治州</t>
         </is>
       </c>
       <c r="AB358" s="2" t="inlineStr">
         <is>
-          <t>巧家县</t>
+          <t>元阳县</t>
         </is>
       </c>
       <c r="AC358" s="2" t="n"/>
@@ -37201,38 +37229,102 @@
       <c r="AI358" s="2" t="n"/>
     </row>
     <row r="359" ht="24" customHeight="1" s="54">
-      <c r="A359" s="13" t="n"/>
+      <c r="A359" s="2" t="n">
+        <v>358</v>
+      </c>
       <c r="B359" s="2" t="n"/>
-      <c r="C359" s="44" t="n"/>
+      <c r="C359" s="44" t="inlineStr">
+        <is>
+          <t>56673</t>
+        </is>
+      </c>
       <c r="D359" s="2" t="n"/>
-      <c r="E359" s="4" t="n"/>
+      <c r="E359" s="4" t="n">
+        <v>99999</v>
+      </c>
       <c r="F359" s="37" t="n"/>
-      <c r="G359" s="28" t="n"/>
-      <c r="H359" s="28" t="n"/>
-      <c r="I359" s="2" t="n"/>
-      <c r="J359" s="26" t="n"/>
-      <c r="K359" s="30" t="n"/>
+      <c r="G359" s="28" t="n">
+        <v>26.9181</v>
+      </c>
+      <c r="H359" s="28" t="n">
+        <v>102.9267</v>
+      </c>
+      <c r="I359" s="2" t="n">
+        <v>893.9</v>
+      </c>
+      <c r="J359" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K359" s="30" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L359" s="2" t="n"/>
-      <c r="M359" s="14" t="n"/>
+      <c r="M359" s="14" t="inlineStr">
+        <is>
+          <t>巧家</t>
+        </is>
+      </c>
       <c r="N359" s="2" t="n"/>
       <c r="O359" s="31" t="n"/>
       <c r="P359" s="31" t="n"/>
       <c r="Q359" s="31" t="n"/>
       <c r="R359" s="49" t="n"/>
-      <c r="S359" s="22" t="n"/>
+      <c r="S359" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T359" s="35" t="n"/>
-      <c r="U359" s="39" t="n"/>
-      <c r="V359" s="2" t="n"/>
-      <c r="W359" s="4" t="n"/>
-      <c r="X359" s="4" t="n"/>
-      <c r="Y359" s="4" t="n"/>
+      <c r="U359" s="39" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="V359" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="W359" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X359" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y359" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Z359" s="4" t="n"/>
-      <c r="AA359" s="2" t="n"/>
-      <c r="AB359" s="2" t="n"/>
+      <c r="AA359" s="2" t="inlineStr">
+        <is>
+          <t>昭通市</t>
+        </is>
+      </c>
+      <c r="AB359" s="2" t="inlineStr">
+        <is>
+          <t>巧家县</t>
+        </is>
+      </c>
       <c r="AC359" s="2" t="n"/>
       <c r="AD359" s="2" t="n"/>
-      <c r="AE359" s="2" t="n"/>
-      <c r="AF359" s="4" t="n"/>
+      <c r="AE359" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AF359" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AG359" s="4" t="n"/>
       <c r="AH359" s="2" t="n"/>
       <c r="AI359" s="2" t="n"/>
@@ -38728,7 +38820,7 @@
       <c r="H400" s="28" t="n"/>
       <c r="I400" s="2" t="n"/>
       <c r="J400" s="26" t="n"/>
-      <c r="K400" s="4" t="n"/>
+      <c r="K400" s="30" t="n"/>
       <c r="L400" s="2" t="n"/>
       <c r="M400" s="14" t="n"/>
       <c r="N400" s="2" t="n"/>
@@ -38903,9 +38995,7 @@
       <c r="AI404" s="2" t="n"/>
     </row>
     <row r="405" ht="24" customHeight="1" s="54">
-      <c r="A405" s="12" t="n">
-        <v>999</v>
-      </c>
+      <c r="A405" s="13" t="n"/>
       <c r="B405" s="2" t="n"/>
       <c r="C405" s="44" t="n"/>
       <c r="D405" s="2" t="n"/>
@@ -38919,11 +39009,7 @@
       <c r="L405" s="2" t="n"/>
       <c r="M405" s="14" t="n"/>
       <c r="N405" s="2" t="n"/>
-      <c r="O405" s="31" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
+      <c r="O405" s="31" t="n"/>
       <c r="P405" s="31" t="n"/>
       <c r="Q405" s="31" t="n"/>
       <c r="R405" s="49" t="n"/>
@@ -38945,15 +39031,58 @@
       <c r="AH405" s="2" t="n"/>
       <c r="AI405" s="2" t="n"/>
     </row>
+    <row r="406" ht="24" customHeight="1" s="54">
+      <c r="A406" s="12" t="n">
+        <v>999</v>
+      </c>
+      <c r="B406" s="2" t="n"/>
+      <c r="C406" s="44" t="n"/>
+      <c r="D406" s="2" t="n"/>
+      <c r="E406" s="4" t="n"/>
+      <c r="F406" s="37" t="n"/>
+      <c r="G406" s="28" t="n"/>
+      <c r="H406" s="28" t="n"/>
+      <c r="I406" s="2" t="n"/>
+      <c r="J406" s="26" t="n"/>
+      <c r="K406" s="4" t="n"/>
+      <c r="L406" s="2" t="n"/>
+      <c r="M406" s="14" t="n"/>
+      <c r="N406" s="2" t="n"/>
+      <c r="O406" s="31" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="P406" s="31" t="n"/>
+      <c r="Q406" s="31" t="n"/>
+      <c r="R406" s="49" t="n"/>
+      <c r="S406" s="22" t="n"/>
+      <c r="T406" s="35" t="n"/>
+      <c r="U406" s="39" t="n"/>
+      <c r="V406" s="2" t="n"/>
+      <c r="W406" s="4" t="n"/>
+      <c r="X406" s="4" t="n"/>
+      <c r="Y406" s="4" t="n"/>
+      <c r="Z406" s="4" t="n"/>
+      <c r="AA406" s="2" t="n"/>
+      <c r="AB406" s="2" t="n"/>
+      <c r="AC406" s="2" t="n"/>
+      <c r="AD406" s="2" t="n"/>
+      <c r="AE406" s="2" t="n"/>
+      <c r="AF406" s="4" t="n"/>
+      <c r="AG406" s="4" t="n"/>
+      <c r="AH406" s="2" t="n"/>
+      <c r="AI406" s="2" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <autoFilter ref="A1:AI405"/>
-  <conditionalFormatting sqref="A2:N405 R2:AI405">
+  <autoFilter ref="A1:AI406"/>
+  <conditionalFormatting sqref="A2:N406 R2:AI406">
     <cfRule type="expression" priority="4" dxfId="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:Q405">
+  <conditionalFormatting sqref="O2:Q406">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -841,8 +841,8 @@
     <col width="18.59765625" customWidth="1" style="8" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="5" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="8" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="5" min="34" max="750"/>
-    <col width="12.59765625" customWidth="1" style="5" min="751" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="5" min="34" max="752"/>
+    <col width="12.59765625" customWidth="1" style="5" min="753" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="11">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="O2" s="31" t="n">
-        <v>-3</v>
+        <v>0.1</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>16.2</v>
+        <v>13.8</v>
       </c>
       <c r="Q2" s="31" t="n">
-        <v>5.67</v>
+        <v>6.8</v>
       </c>
       <c r="R2" s="49" t="n"/>
       <c r="S2" s="22" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="O3" s="31" t="n">
-        <v>-2.6</v>
+        <v>-0.6</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>15.6</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="31" t="n"/>
       <c r="R3" s="49" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="O4" s="31" t="n">
-        <v>-7.8</v>
+        <v>0.8</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>14.7</v>
+        <v>15.3</v>
       </c>
       <c r="Q4" s="31" t="n"/>
       <c r="R4" s="49" t="inlineStr">
@@ -1392,12 +1392,8 @@
         </is>
       </c>
       <c r="N5" s="2" t="n"/>
-      <c r="O5" s="31" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="P5" s="31" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="O5" s="31" t="n"/>
+      <c r="P5" s="31" t="n"/>
       <c r="Q5" s="31" t="n"/>
       <c r="R5" s="49" t="n"/>
       <c r="S5" s="22" t="n"/>
@@ -1500,13 +1496,13 @@
         </is>
       </c>
       <c r="O6" s="31" t="n">
-        <v>-9.1</v>
+        <v>-7.1</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>9.6</v>
+        <v>15.6</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>-0.38</v>
+        <v>1.79</v>
       </c>
       <c r="R6" s="51" t="inlineStr">
         <is>
@@ -1611,10 +1607,10 @@
         </is>
       </c>
       <c r="O7" s="31" t="n">
-        <v>-10.1</v>
+        <v>-4.4</v>
       </c>
       <c r="P7" s="31" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q7" s="31" t="n"/>
       <c r="R7" s="49" t="n"/>
@@ -1720,13 +1716,13 @@
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="31" t="n">
-        <v>-8.199999999999999</v>
+        <v>-2.6</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>16.8</v>
+        <v>18.7</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>3.06</v>
+        <v>6.15</v>
       </c>
       <c r="R8" s="49" t="n"/>
       <c r="S8" s="22" t="inlineStr">
@@ -1833,13 +1829,13 @@
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="31" t="n">
-        <v>-1.3</v>
+        <v>3</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>14.5</v>
+        <v>13.1</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>6.04</v>
+        <v>7.22</v>
       </c>
       <c r="R9" s="49" t="n"/>
       <c r="S9" s="22" t="inlineStr">
@@ -1954,13 +1950,13 @@
         </is>
       </c>
       <c r="O10" s="31" t="n">
-        <v>-9.199999999999999</v>
+        <v>-3.9</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>13.1</v>
+        <v>15.5</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>1.32</v>
+        <v>4.58</v>
       </c>
       <c r="R10" s="49" t="n"/>
       <c r="S10" s="22" t="inlineStr">
@@ -2071,13 +2067,13 @@
         </is>
       </c>
       <c r="O11" s="31" t="n">
-        <v>-12.9</v>
+        <v>-6</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>8.4</v>
+        <v>14.4</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>-1.79</v>
+        <v>4</v>
       </c>
       <c r="R11" s="49" t="inlineStr">
         <is>
@@ -2188,13 +2184,13 @@
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="31" t="n">
-        <v>-8.300000000000001</v>
+        <v>-4.7</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>10.8</v>
+        <v>15.6</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>0.11</v>
+        <v>3.31</v>
       </c>
       <c r="R12" s="49" t="inlineStr">
         <is>
@@ -2309,13 +2305,13 @@
         </is>
       </c>
       <c r="O13" s="31" t="n">
-        <v>-9.9</v>
+        <v>-4.7</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>11.2</v>
+        <v>13.3</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>-0.41</v>
+        <v>3.04</v>
       </c>
       <c r="R13" s="49" t="inlineStr">
         <is>
@@ -2426,13 +2422,13 @@
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="31" t="n">
-        <v>-3.5</v>
+        <v>-1.9</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>11.9</v>
+        <v>14.7</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="R14" s="49" t="n"/>
       <c r="S14" s="22" t="inlineStr">
@@ -2547,13 +2543,13 @@
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="31" t="n">
-        <v>-10.4</v>
+        <v>-7.8</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>9.6</v>
+        <v>12.3</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>-0.91</v>
+        <v>1.81</v>
       </c>
       <c r="R15" s="49" t="n"/>
       <c r="S15" s="22" t="inlineStr">
@@ -2658,13 +2654,13 @@
       </c>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="31" t="n">
-        <v>-9.6</v>
+        <v>-6.7</v>
       </c>
       <c r="P16" s="31" t="n">
-        <v>12.2</v>
+        <v>14.8</v>
       </c>
       <c r="Q16" s="31" t="n">
-        <v>-0.05</v>
+        <v>2.86</v>
       </c>
       <c r="R16" s="49" t="n"/>
       <c r="S16" s="22" t="n"/>
@@ -2849,9 +2845,7 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O18" s="31" t="n">
-        <v>-13.2</v>
-      </c>
+      <c r="O18" s="31" t="n"/>
       <c r="P18" s="31" t="n"/>
       <c r="Q18" s="31" t="n"/>
       <c r="R18" s="49" t="n"/>
@@ -3042,13 +3036,13 @@
       </c>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="31" t="n">
-        <v>-10.6</v>
+        <v>-8.4</v>
       </c>
       <c r="P20" s="31" t="n">
-        <v>9</v>
+        <v>15.1</v>
       </c>
       <c r="Q20" s="31" t="n">
-        <v>-0.66</v>
+        <v>1.46</v>
       </c>
       <c r="R20" s="49" t="n"/>
       <c r="S20" s="22" t="n"/>
@@ -4161,12 +4155,8 @@
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
-      <c r="O32" s="31" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="P32" s="31" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="O32" s="31" t="n"/>
+      <c r="P32" s="31" t="n"/>
       <c r="Q32" s="31" t="n"/>
       <c r="R32" s="49" t="n"/>
       <c r="S32" s="22" t="n"/>
@@ -4907,15 +4897,9 @@
         </is>
       </c>
       <c r="N40" s="2" t="n"/>
-      <c r="O40" s="31" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="P40" s="31" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q40" s="31" t="n">
-        <v>-0.33</v>
-      </c>
+      <c r="O40" s="31" t="n"/>
+      <c r="P40" s="31" t="n"/>
+      <c r="Q40" s="31" t="n"/>
       <c r="R40" s="49" t="n"/>
       <c r="S40" s="22" t="n"/>
       <c r="T40" s="35" t="n"/>
@@ -7914,12 +7898,8 @@
         </is>
       </c>
       <c r="N73" s="2" t="n"/>
-      <c r="O73" s="31" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="P73" s="31" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="O73" s="31" t="n"/>
+      <c r="P73" s="31" t="n"/>
       <c r="Q73" s="31" t="n"/>
       <c r="R73" s="49" t="n"/>
       <c r="S73" s="22" t="n"/>
@@ -8092,9 +8072,7 @@
         </is>
       </c>
       <c r="N75" s="2" t="n"/>
-      <c r="O75" s="31" t="n">
-        <v>-7.9</v>
-      </c>
+      <c r="O75" s="31" t="n"/>
       <c r="P75" s="31" t="n"/>
       <c r="Q75" s="31" t="n"/>
       <c r="R75" s="49" t="n"/>
@@ -8921,12 +8899,8 @@
         </is>
       </c>
       <c r="N84" s="2" t="n"/>
-      <c r="O84" s="31" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="P84" s="31" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="O84" s="31" t="n"/>
+      <c r="P84" s="31" t="n"/>
       <c r="Q84" s="31" t="n"/>
       <c r="R84" s="49" t="n"/>
       <c r="S84" s="22" t="n"/>
@@ -9118,13 +9092,13 @@
       </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="31" t="n">
-        <v>-12.2</v>
+        <v>-7.9</v>
       </c>
       <c r="P86" s="31" t="n">
-        <v>10.9</v>
+        <v>14.3</v>
       </c>
       <c r="Q86" s="31" t="n">
-        <v>0.41</v>
+        <v>2.63</v>
       </c>
       <c r="R86" s="49" t="n"/>
       <c r="S86" s="22" t="n"/>
@@ -9386,12 +9360,8 @@
         </is>
       </c>
       <c r="N89" s="2" t="n"/>
-      <c r="O89" s="31" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="P89" s="31" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="O89" s="31" t="n"/>
+      <c r="P89" s="31" t="n"/>
       <c r="Q89" s="31" t="n"/>
       <c r="R89" s="49" t="n"/>
       <c r="S89" s="22" t="n"/>
@@ -9734,8 +9704,12 @@
         </is>
       </c>
       <c r="N93" s="2" t="n"/>
-      <c r="O93" s="31" t="n"/>
-      <c r="P93" s="31" t="n"/>
+      <c r="O93" s="31" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="P93" s="31" t="n">
+        <v>16.7</v>
+      </c>
       <c r="Q93" s="31" t="n"/>
       <c r="R93" s="49" t="n"/>
       <c r="S93" s="22" t="n"/>
@@ -10230,13 +10204,13 @@
         </is>
       </c>
       <c r="O98" s="31" t="n">
-        <v>-10.3</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="P98" s="31" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="Q98" s="31" t="n">
-        <v>-0.79</v>
+        <v>-0.17</v>
       </c>
       <c r="R98" s="49" t="inlineStr">
         <is>
@@ -10664,13 +10638,13 @@
         </is>
       </c>
       <c r="O102" s="31" t="n">
-        <v>-9.6</v>
+        <v>-1.4</v>
       </c>
       <c r="P102" s="31" t="n">
-        <v>13.1</v>
+        <v>11.9</v>
       </c>
       <c r="Q102" s="31" t="n">
-        <v>1.07</v>
+        <v>5.61</v>
       </c>
       <c r="R102" s="49" t="n"/>
       <c r="S102" s="22" t="inlineStr">
@@ -10786,13 +10760,13 @@
         </is>
       </c>
       <c r="O103" s="31" t="n">
-        <v>-8.199999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="P103" s="31" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="Q103" s="31" t="n">
-        <v>1.72</v>
+        <v>5.14</v>
       </c>
       <c r="R103" s="49" t="n"/>
       <c r="S103" s="22" t="inlineStr">
@@ -11006,13 +10980,13 @@
         </is>
       </c>
       <c r="O105" s="31" t="n">
-        <v>-7.9</v>
+        <v>-3</v>
       </c>
       <c r="P105" s="31" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="Q105" s="31" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.31</v>
       </c>
       <c r="R105" s="49" t="n"/>
       <c r="S105" s="22" t="inlineStr">
@@ -11226,13 +11200,13 @@
       </c>
       <c r="N107" s="2" t="n"/>
       <c r="O107" s="31" t="n">
-        <v>0.1</v>
+        <v>5.2</v>
       </c>
       <c r="P107" s="31" t="n">
-        <v>17.7</v>
+        <v>16.3</v>
       </c>
       <c r="Q107" s="31" t="n">
-        <v>6.91</v>
+        <v>9.77</v>
       </c>
       <c r="R107" s="49" t="n"/>
       <c r="S107" s="22" t="inlineStr">
@@ -11454,13 +11428,13 @@
       </c>
       <c r="N109" s="2" t="n"/>
       <c r="O109" s="31" t="n">
-        <v>-6.7</v>
+        <v>3.2</v>
       </c>
       <c r="P109" s="31" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="Q109" s="31" t="n">
-        <v>3.16</v>
+        <v>7.85</v>
       </c>
       <c r="R109" s="49" t="inlineStr">
         <is>
@@ -11979,13 +11953,13 @@
       </c>
       <c r="N114" s="2" t="n"/>
       <c r="O114" s="31" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="P114" s="31" t="n">
-        <v>11.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q114" s="31" t="n">
-        <v>5.96</v>
+        <v>3.34</v>
       </c>
       <c r="R114" s="49" t="n"/>
       <c r="S114" s="22" t="inlineStr">
@@ -12092,13 +12066,13 @@
       </c>
       <c r="N115" s="2" t="n"/>
       <c r="O115" s="31" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="P115" s="31" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="Q115" s="31" t="n">
-        <v>13.07</v>
+        <v>11.91</v>
       </c>
       <c r="R115" s="49" t="n"/>
       <c r="S115" s="22" t="inlineStr">
@@ -12328,13 +12302,13 @@
       </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="31" t="n">
-        <v>8.800000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="P117" s="31" t="n">
-        <v>11.8</v>
+        <v>17</v>
       </c>
       <c r="Q117" s="31" t="n">
-        <v>9.83</v>
+        <v>10.24</v>
       </c>
       <c r="R117" s="49" t="n"/>
       <c r="S117" s="22" t="inlineStr">
@@ -12453,13 +12427,13 @@
       </c>
       <c r="N118" s="2" t="n"/>
       <c r="O118" s="31" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="P118" s="31" t="n">
-        <v>16.3</v>
+        <v>17.6</v>
       </c>
       <c r="Q118" s="31" t="n">
-        <v>9.619999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="R118" s="49" t="n"/>
       <c r="S118" s="22" t="inlineStr">
@@ -12898,15 +12872,9 @@
         </is>
       </c>
       <c r="N122" s="2" t="n"/>
-      <c r="O122" s="31" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="P122" s="31" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Q122" s="31" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="O122" s="31" t="n"/>
+      <c r="P122" s="31" t="n"/>
+      <c r="Q122" s="31" t="n"/>
       <c r="R122" s="49" t="n"/>
       <c r="S122" s="22" t="inlineStr">
         <is>
@@ -13020,12 +12988,14 @@
       </c>
       <c r="N123" s="2" t="n"/>
       <c r="O123" s="31" t="n">
-        <v>-6.6</v>
+        <v>-2.8</v>
       </c>
       <c r="P123" s="31" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="Q123" s="31" t="n"/>
+        <v>14.9</v>
+      </c>
+      <c r="Q123" s="31" t="n">
+        <v>5.55</v>
+      </c>
       <c r="R123" s="49" t="n"/>
       <c r="S123" s="22" t="inlineStr">
         <is>
@@ -13238,13 +13208,13 @@
       </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="31" t="n">
-        <v>-8.5</v>
+        <v>-7.7</v>
       </c>
       <c r="P125" s="31" t="n">
         <v>12.7</v>
       </c>
       <c r="Q125" s="31" t="n">
-        <v>1.21</v>
+        <v>2.51</v>
       </c>
       <c r="R125" s="49" t="n"/>
       <c r="S125" s="22" t="n"/>
@@ -13363,13 +13333,13 @@
         </is>
       </c>
       <c r="O126" s="31" t="n">
-        <v>-11.3</v>
+        <v>-11.2</v>
       </c>
       <c r="P126" s="31" t="n">
-        <v>11.8</v>
+        <v>12.9</v>
       </c>
       <c r="Q126" s="31" t="n">
-        <v>0.49</v>
+        <v>1.69</v>
       </c>
       <c r="R126" s="49" t="n"/>
       <c r="S126" s="22" t="inlineStr">
@@ -13891,15 +13861,9 @@
         </is>
       </c>
       <c r="N131" s="2" t="n"/>
-      <c r="O131" s="31" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="P131" s="31" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Q131" s="31" t="n">
-        <v>3.53</v>
-      </c>
+      <c r="O131" s="31" t="n"/>
+      <c r="P131" s="31" t="n"/>
+      <c r="Q131" s="31" t="n"/>
       <c r="R131" s="49" t="n"/>
       <c r="S131" s="22" t="n"/>
       <c r="T131" s="35" t="n"/>
@@ -14111,9 +14075,15 @@
         </is>
       </c>
       <c r="N133" s="2" t="n"/>
-      <c r="O133" s="31" t="n"/>
-      <c r="P133" s="31" t="n"/>
-      <c r="Q133" s="31" t="n"/>
+      <c r="O133" s="31" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="P133" s="31" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Q133" s="31" t="n">
+        <v>2.95</v>
+      </c>
       <c r="R133" s="49" t="n"/>
       <c r="S133" s="22" t="n"/>
       <c r="T133" s="35" t="n"/>
@@ -14663,13 +14633,13 @@
       </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="31" t="n">
-        <v>18.7</v>
+        <v>15.6</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>29.5</v>
+        <v>29.9</v>
       </c>
       <c r="Q138" s="31" t="n">
-        <v>24.19</v>
+        <v>23.16</v>
       </c>
       <c r="R138" s="49" t="n"/>
       <c r="S138" s="22" t="inlineStr">
@@ -14780,13 +14750,13 @@
       </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="31" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="P139" s="31" t="n">
-        <v>23.4</v>
+        <v>21.1</v>
       </c>
       <c r="Q139" s="31" t="n">
-        <v>16.04</v>
+        <v>17.7</v>
       </c>
       <c r="R139" s="49" t="n"/>
       <c r="S139" s="22" t="inlineStr">
@@ -15008,13 +14978,13 @@
       </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="31" t="n">
-        <v>0.9</v>
+        <v>-1.6</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>14.3</v>
+        <v>18</v>
       </c>
       <c r="Q141" s="31" t="n">
-        <v>7.84</v>
+        <v>8.44</v>
       </c>
       <c r="R141" s="49" t="n"/>
       <c r="S141" s="22" t="inlineStr">
@@ -15133,13 +15103,13 @@
       </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="31" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="P142" s="31" t="n">
-        <v>21</v>
+        <v>23.9</v>
       </c>
       <c r="Q142" s="31" t="n">
-        <v>17.71</v>
+        <v>16.01</v>
       </c>
       <c r="R142" s="49" t="n"/>
       <c r="S142" s="22" t="inlineStr">
@@ -15246,13 +15216,13 @@
       </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="31" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P143" s="31" t="n">
-        <v>18.2</v>
+        <v>20.9</v>
       </c>
       <c r="Q143" s="31" t="n">
-        <v>10.34</v>
+        <v>11.28</v>
       </c>
       <c r="R143" s="49" t="n"/>
       <c r="S143" s="22" t="inlineStr">
@@ -15367,13 +15337,13 @@
       </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="31" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="P144" s="31" t="n">
-        <v>19.1</v>
+        <v>21.1</v>
       </c>
       <c r="Q144" s="31" t="n">
-        <v>12.54</v>
+        <v>11.15</v>
       </c>
       <c r="R144" s="49" t="n"/>
       <c r="S144" s="22" t="inlineStr">
@@ -15488,13 +15458,13 @@
       </c>
       <c r="N145" s="2" t="n"/>
       <c r="O145" s="31" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="P145" s="31" t="n">
-        <v>14.9</v>
+        <v>17.3</v>
       </c>
       <c r="Q145" s="31" t="n">
-        <v>8.4</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="R145" s="49" t="n"/>
       <c r="S145" s="22" t="inlineStr">
@@ -15609,13 +15579,13 @@
       </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="31" t="n">
-        <v>14.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P146" s="31" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="Q146" s="31" t="n">
-        <v>18.57</v>
+        <v>16.18</v>
       </c>
       <c r="R146" s="49" t="n"/>
       <c r="S146" s="22" t="inlineStr">
@@ -15726,13 +15696,13 @@
       </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="31" t="n">
-        <v>14.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P147" s="31" t="n">
-        <v>25</v>
+        <v>26.1</v>
       </c>
       <c r="Q147" s="31" t="n">
-        <v>19.07</v>
+        <v>17.41</v>
       </c>
       <c r="R147" s="49" t="n"/>
       <c r="S147" s="22" t="inlineStr">
@@ -15843,13 +15813,13 @@
       </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="31" t="n">
-        <v>12.5</v>
+        <v>10.7</v>
       </c>
       <c r="P148" s="31" t="n">
-        <v>21.6</v>
+        <v>25.1</v>
       </c>
       <c r="Q148" s="31" t="n">
-        <v>17.1</v>
+        <v>17.04</v>
       </c>
       <c r="R148" s="49" t="n"/>
       <c r="S148" s="22" t="inlineStr">
@@ -16067,13 +16037,13 @@
       </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="31" t="n">
-        <v>15.8</v>
+        <v>16.5</v>
       </c>
       <c r="P150" s="31" t="n">
-        <v>19.2</v>
+        <v>21.4</v>
       </c>
       <c r="Q150" s="31" t="n">
-        <v>17.2</v>
+        <v>18.5</v>
       </c>
       <c r="R150" s="49" t="n"/>
       <c r="S150" s="22" t="inlineStr">
@@ -16184,13 +16154,13 @@
       </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="31" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="P151" s="31" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="Q151" s="31" t="n">
-        <v>20.86</v>
+        <v>20.62</v>
       </c>
       <c r="R151" s="49" t="n"/>
       <c r="S151" s="22" t="inlineStr">
@@ -16301,13 +16271,13 @@
       </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="31" t="n">
-        <v>17.2</v>
+        <v>15.1</v>
       </c>
       <c r="P152" s="31" t="n">
-        <v>23.8</v>
+        <v>24.8</v>
       </c>
       <c r="Q152" s="31" t="n">
-        <v>19.82</v>
+        <v>19.75</v>
       </c>
       <c r="R152" s="49" t="n"/>
       <c r="S152" s="22" t="inlineStr">
@@ -16418,13 +16388,13 @@
       </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P153" s="31" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q153" s="31" t="n">
-        <v>19.1</v>
+        <v>18.29</v>
       </c>
       <c r="R153" s="49" t="n"/>
       <c r="S153" s="22" t="inlineStr">
@@ -16535,13 +16505,13 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="31" t="n">
-        <v>18.4</v>
+        <v>16.3</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>19.9</v>
+        <v>23.2</v>
       </c>
       <c r="Q154" s="31" t="n">
-        <v>19.06</v>
+        <v>19.76</v>
       </c>
       <c r="R154" s="49" t="n"/>
       <c r="S154" s="22" t="inlineStr">
@@ -16755,13 +16725,13 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="31" t="n">
-        <v>24.3</v>
+        <v>20.5</v>
       </c>
       <c r="P156" s="31" t="n">
-        <v>35.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q156" s="31" t="n">
-        <v>27.85</v>
+        <v>22.65</v>
       </c>
       <c r="R156" s="49" t="n"/>
       <c r="S156" s="22" t="inlineStr">
@@ -16872,13 +16842,13 @@
       </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="31" t="n">
-        <v>24.3</v>
+        <v>22.8</v>
       </c>
       <c r="P157" s="31" t="n">
-        <v>33.7</v>
+        <v>27.5</v>
       </c>
       <c r="Q157" s="31" t="n">
-        <v>27.3</v>
+        <v>24.61</v>
       </c>
       <c r="R157" s="49" t="n"/>
       <c r="S157" s="22" t="inlineStr">
@@ -17191,13 +17161,13 @@
       </c>
       <c r="N160" s="2" t="n"/>
       <c r="O160" s="31" t="n">
-        <v>26.5</v>
+        <v>23</v>
       </c>
       <c r="P160" s="31" t="n">
-        <v>32.9</v>
+        <v>30.3</v>
       </c>
       <c r="Q160" s="31" t="n">
-        <v>29.96</v>
+        <v>26.09</v>
       </c>
       <c r="R160" s="49" t="n"/>
       <c r="S160" s="22" t="inlineStr">
@@ -17300,13 +17270,13 @@
       </c>
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="31" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
       </c>
       <c r="P161" s="31" t="n">
-        <v>32.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q161" s="31" t="n">
-        <v>25.59</v>
+        <v>21.95</v>
       </c>
       <c r="R161" s="49" t="n"/>
       <c r="S161" s="22" t="inlineStr">
@@ -17417,13 +17387,13 @@
       </c>
       <c r="N162" s="2" t="n"/>
       <c r="O162" s="31" t="n">
-        <v>16.4</v>
+        <v>13.2</v>
       </c>
       <c r="P162" s="31" t="n">
-        <v>21.1</v>
+        <v>18.2</v>
       </c>
       <c r="Q162" s="31" t="n">
-        <v>18.29</v>
+        <v>14.74</v>
       </c>
       <c r="R162" s="49" t="n"/>
       <c r="S162" s="22" t="inlineStr">
@@ -17534,13 +17504,13 @@
       </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="31" t="n">
-        <v>14.4</v>
+        <v>11.8</v>
       </c>
       <c r="P163" s="31" t="n">
-        <v>17.4</v>
+        <v>15</v>
       </c>
       <c r="Q163" s="31" t="n">
-        <v>15.9</v>
+        <v>13.36</v>
       </c>
       <c r="R163" s="49" t="n"/>
       <c r="S163" s="22" t="inlineStr">
@@ -17651,13 +17621,13 @@
       </c>
       <c r="N164" s="2" t="n"/>
       <c r="O164" s="31" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P164" s="31" t="n">
-        <v>21.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q164" s="31" t="n">
-        <v>20.56</v>
+        <v>20.69</v>
       </c>
       <c r="R164" s="49" t="n"/>
       <c r="S164" s="22" t="inlineStr">
@@ -17859,13 +17829,13 @@
       </c>
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="31" t="n">
-        <v>19.3</v>
+        <v>17.5</v>
       </c>
       <c r="P166" s="31" t="n">
-        <v>25.7</v>
+        <v>20</v>
       </c>
       <c r="Q166" s="31" t="n">
-        <v>21.51</v>
+        <v>18.45</v>
       </c>
       <c r="R166" s="49" t="n"/>
       <c r="S166" s="22" t="inlineStr">
@@ -17980,13 +17950,13 @@
       </c>
       <c r="N167" s="2" t="n"/>
       <c r="O167" s="31" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="P167" s="31" t="n">
-        <v>16.3</v>
+        <v>15.2</v>
       </c>
       <c r="Q167" s="31" t="n">
-        <v>11.04</v>
+        <v>10.06</v>
       </c>
       <c r="R167" s="49" t="n"/>
       <c r="S167" s="22" t="inlineStr">
@@ -18183,9 +18153,15 @@
         </is>
       </c>
       <c r="N169" s="2" t="n"/>
-      <c r="O169" s="31" t="n"/>
-      <c r="P169" s="31" t="n"/>
-      <c r="Q169" s="31" t="n"/>
+      <c r="O169" s="31" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="P169" s="31" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="Q169" s="31" t="n">
+        <v>4.18</v>
+      </c>
       <c r="R169" s="49" t="n"/>
       <c r="S169" s="22" t="n"/>
       <c r="T169" s="35" t="n"/>
@@ -18568,13 +18544,13 @@
       </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="31" t="n">
-        <v>-2.8</v>
+        <v>-5</v>
       </c>
       <c r="P173" s="31" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q173" s="31" t="n">
-        <v>1.45</v>
+        <v>-2.19</v>
       </c>
       <c r="R173" s="49" t="n"/>
       <c r="S173" s="22" t="inlineStr">
@@ -18685,13 +18661,13 @@
         </is>
       </c>
       <c r="O174" s="31" t="n">
-        <v>-5.6</v>
+        <v>-4.4</v>
       </c>
       <c r="P174" s="31" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="Q174" s="31" t="n">
-        <v>-0.09</v>
+        <v>-1.78</v>
       </c>
       <c r="R174" s="49" t="n"/>
       <c r="S174" s="22" t="inlineStr">
@@ -18800,13 +18776,13 @@
       </c>
       <c r="N175" s="2" t="n"/>
       <c r="O175" s="31" t="n">
-        <v>12.6</v>
+        <v>5.7</v>
       </c>
       <c r="P175" s="31" t="n">
-        <v>21.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q175" s="31" t="n">
-        <v>16.86</v>
+        <v>14.84</v>
       </c>
       <c r="R175" s="49" t="n"/>
       <c r="S175" s="22" t="inlineStr">
@@ -18905,13 +18881,13 @@
       </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="31" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="P176" s="31" t="n">
-        <v>22.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q176" s="31" t="n">
-        <v>20.39</v>
+        <v>21.36</v>
       </c>
       <c r="R176" s="49" t="n"/>
       <c r="S176" s="22" t="inlineStr">
@@ -19014,13 +18990,13 @@
       </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="31" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="P177" s="31" t="n">
-        <v>18.7</v>
+        <v>22.2</v>
       </c>
       <c r="Q177" s="31" t="n">
-        <v>13.6</v>
+        <v>14.83</v>
       </c>
       <c r="R177" s="49" t="n"/>
       <c r="S177" s="22" t="inlineStr">
@@ -19258,13 +19234,13 @@
         </is>
       </c>
       <c r="O179" s="31" t="n">
-        <v>-5.4</v>
+        <v>-8</v>
       </c>
       <c r="P179" s="31" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="Q179" s="31" t="n">
-        <v>-2.15</v>
+        <v>-2.55</v>
       </c>
       <c r="R179" s="49" t="n"/>
       <c r="S179" s="22" t="inlineStr">
@@ -19379,13 +19355,13 @@
       </c>
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="31" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="P180" s="31" t="n">
-        <v>15</v>
+        <v>11.9</v>
       </c>
       <c r="Q180" s="31" t="n">
-        <v>3.64</v>
+        <v>4.44</v>
       </c>
       <c r="R180" s="49" t="n"/>
       <c r="S180" s="22" t="inlineStr">
@@ -19500,13 +19476,13 @@
       </c>
       <c r="N181" s="2" t="n"/>
       <c r="O181" s="31" t="n">
-        <v>14.2</v>
+        <v>8.1</v>
       </c>
       <c r="P181" s="31" t="n">
-        <v>23.1</v>
+        <v>26.5</v>
       </c>
       <c r="Q181" s="31" t="n">
-        <v>18.65</v>
+        <v>17.3</v>
       </c>
       <c r="R181" s="49" t="n"/>
       <c r="S181" s="22" t="inlineStr">
@@ -19613,13 +19589,13 @@
       </c>
       <c r="N182" s="2" t="n"/>
       <c r="O182" s="31" t="n">
-        <v>16.9</v>
+        <v>12.2</v>
       </c>
       <c r="P182" s="31" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q182" s="31" t="n">
-        <v>19.19</v>
+        <v>17.84</v>
       </c>
       <c r="R182" s="49" t="n"/>
       <c r="S182" s="22" t="inlineStr">
@@ -19730,13 +19706,13 @@
       </c>
       <c r="N183" s="2" t="n"/>
       <c r="O183" s="31" t="n">
-        <v>24.6</v>
+        <v>21.3</v>
       </c>
       <c r="P183" s="31" t="n">
-        <v>37</v>
+        <v>29.8</v>
       </c>
       <c r="Q183" s="31" t="n">
-        <v>29.48</v>
+        <v>23.36</v>
       </c>
       <c r="R183" s="49" t="n"/>
       <c r="S183" s="22" t="inlineStr">
@@ -19843,13 +19819,13 @@
       </c>
       <c r="N184" s="2" t="n"/>
       <c r="O184" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P184" s="31" t="n">
         <v>8.9</v>
       </c>
-      <c r="P184" s="31" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Q184" s="31" t="n">
-        <v>10.89</v>
+        <v>6.21</v>
       </c>
       <c r="R184" s="49" t="n"/>
       <c r="S184" s="22" t="inlineStr">
@@ -20046,12 +20022,8 @@
           <t>🔵</t>
         </is>
       </c>
-      <c r="O186" s="31" t="n">
-        <v>-11</v>
-      </c>
-      <c r="P186" s="31" t="n">
-        <v>-0.5</v>
-      </c>
+      <c r="O186" s="31" t="n"/>
+      <c r="P186" s="31" t="n"/>
       <c r="Q186" s="31" t="n"/>
       <c r="R186" s="49" t="n"/>
       <c r="S186" s="22" t="n"/>
@@ -20451,13 +20423,13 @@
       </c>
       <c r="N190" s="2" t="n"/>
       <c r="O190" s="31" t="n">
-        <v>-0.7</v>
+        <v>-5.9</v>
       </c>
       <c r="P190" s="31" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="Q190" s="31" t="n">
-        <v>1.2</v>
+        <v>2.23</v>
       </c>
       <c r="R190" s="49" t="inlineStr">
         <is>
@@ -20559,12 +20531,8 @@
         </is>
       </c>
       <c r="N191" s="2" t="n"/>
-      <c r="O191" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P191" s="31" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="O191" s="31" t="n"/>
+      <c r="P191" s="31" t="n"/>
       <c r="Q191" s="31" t="n"/>
       <c r="R191" s="49" t="n"/>
       <c r="S191" s="22" t="n"/>
@@ -20662,12 +20630,8 @@
         </is>
       </c>
       <c r="N192" s="3" t="n"/>
-      <c r="O192" s="31" t="n">
-        <v>-5</v>
-      </c>
-      <c r="P192" s="31" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="O192" s="31" t="n"/>
+      <c r="P192" s="31" t="n"/>
       <c r="Q192" s="31" t="n"/>
       <c r="R192" s="49" t="n"/>
       <c r="S192" s="22" t="n"/>
@@ -20774,13 +20738,13 @@
         </is>
       </c>
       <c r="O193" s="31" t="n">
-        <v>-4.3</v>
+        <v>-7.1</v>
       </c>
       <c r="P193" s="31" t="n">
-        <v>-0.8</v>
+        <v>-3</v>
       </c>
       <c r="Q193" s="31" t="n">
-        <v>-2.51</v>
+        <v>-4.83</v>
       </c>
       <c r="R193" s="49" t="n"/>
       <c r="S193" s="22" t="n"/>
@@ -20981,15 +20945,9 @@
         </is>
       </c>
       <c r="N195" s="2" t="n"/>
-      <c r="O195" s="31" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="P195" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q195" s="31" t="n">
-        <v>3.66</v>
-      </c>
+      <c r="O195" s="31" t="n"/>
+      <c r="P195" s="31" t="n"/>
+      <c r="Q195" s="31" t="n"/>
       <c r="R195" s="49" t="n"/>
       <c r="S195" s="22" t="n"/>
       <c r="T195" s="35" t="n"/>
@@ -21284,8 +21242,12 @@
         </is>
       </c>
       <c r="N198" s="2" t="n"/>
-      <c r="O198" s="31" t="n"/>
-      <c r="P198" s="31" t="n"/>
+      <c r="O198" s="31" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="P198" s="31" t="n">
+        <v>17</v>
+      </c>
       <c r="Q198" s="31" t="n"/>
       <c r="R198" s="49" t="n"/>
       <c r="S198" s="22" t="n"/>
@@ -21373,8 +21335,12 @@
         </is>
       </c>
       <c r="N199" s="2" t="n"/>
-      <c r="O199" s="31" t="n"/>
-      <c r="P199" s="31" t="n"/>
+      <c r="O199" s="31" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="P199" s="31" t="n">
+        <v>-2</v>
+      </c>
       <c r="Q199" s="31" t="n"/>
       <c r="R199" s="49" t="n"/>
       <c r="S199" s="22" t="n"/>
@@ -21678,12 +21644,8 @@
         </is>
       </c>
       <c r="N202" s="2" t="n"/>
-      <c r="O202" s="31" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="P202" s="31" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="O202" s="31" t="n"/>
+      <c r="P202" s="31" t="n"/>
       <c r="Q202" s="31" t="n"/>
       <c r="R202" s="49" t="n"/>
       <c r="S202" s="22" t="n"/>
@@ -21785,12 +21747,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O203" s="31" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="P203" s="31" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="O203" s="31" t="n"/>
+      <c r="P203" s="31" t="n"/>
       <c r="Q203" s="31" t="n"/>
       <c r="R203" s="49" t="n"/>
       <c r="S203" s="22" t="n"/>
@@ -21892,12 +21850,8 @@
         </is>
       </c>
       <c r="N204" s="2" t="n"/>
-      <c r="O204" s="31" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="P204" s="31" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="O204" s="31" t="n"/>
+      <c r="P204" s="31" t="n"/>
       <c r="Q204" s="31" t="n"/>
       <c r="R204" s="49" t="inlineStr">
         <is>
@@ -22201,12 +22155,8 @@
           <t>⚡🧊</t>
         </is>
       </c>
-      <c r="O207" s="31" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="P207" s="31" t="n">
-        <v>9</v>
-      </c>
+      <c r="O207" s="31" t="n"/>
+      <c r="P207" s="31" t="n"/>
       <c r="Q207" s="31" t="n"/>
       <c r="R207" s="49" t="n"/>
       <c r="S207" s="22" t="n"/>
@@ -22419,12 +22369,8 @@
         </is>
       </c>
       <c r="N209" s="2" t="n"/>
-      <c r="O209" s="31" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="P209" s="31" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="O209" s="31" t="n"/>
+      <c r="P209" s="31" t="n"/>
       <c r="Q209" s="31" t="n"/>
       <c r="R209" s="49" t="n"/>
       <c r="S209" s="22" t="n"/>
@@ -22525,7 +22471,7 @@
       </c>
       <c r="N210" s="2" t="n"/>
       <c r="O210" s="31" t="n">
-        <v>-26.1</v>
+        <v>-37.5</v>
       </c>
       <c r="P210" s="31" t="n"/>
       <c r="Q210" s="31" t="n"/>
@@ -23093,13 +23039,13 @@
       </c>
       <c r="N216" s="2" t="n"/>
       <c r="O216" s="31" t="n">
-        <v>10.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P216" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q216" s="31" t="n">
-        <v>12.2</v>
+        <v>9.9</v>
       </c>
       <c r="R216" s="49" t="n"/>
       <c r="S216" s="22" t="inlineStr">
@@ -23497,13 +23443,13 @@
       </c>
       <c r="N220" s="2" t="n"/>
       <c r="O220" s="31" t="n">
-        <v>-4</v>
+        <v>5.3</v>
       </c>
       <c r="P220" s="31" t="n">
-        <v>15.7</v>
+        <v>16.4</v>
       </c>
       <c r="Q220" s="31" t="n">
-        <v>4.32</v>
+        <v>10.15</v>
       </c>
       <c r="R220" s="49" t="n"/>
       <c r="S220" s="22" t="inlineStr">
@@ -23707,13 +23653,13 @@
       </c>
       <c r="N222" s="2" t="n"/>
       <c r="O222" s="31" t="n">
-        <v>10.3</v>
+        <v>4.7</v>
       </c>
       <c r="P222" s="31" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="Q222" s="31" t="n">
-        <v>13.06</v>
+        <v>9.81</v>
       </c>
       <c r="R222" s="49" t="n"/>
       <c r="S222" s="22" t="inlineStr">
@@ -24113,13 +24059,13 @@
       </c>
       <c r="N226" s="2" t="n"/>
       <c r="O226" s="31" t="n">
-        <v>-3.6</v>
+        <v>4.7</v>
       </c>
       <c r="P226" s="31" t="n">
-        <v>15.4</v>
+        <v>13.5</v>
       </c>
       <c r="Q226" s="31" t="n">
-        <v>5.13</v>
+        <v>9.5</v>
       </c>
       <c r="R226" s="49" t="n"/>
       <c r="S226" s="22" t="inlineStr">
@@ -24416,13 +24362,13 @@
       </c>
       <c r="N229" s="2" t="n"/>
       <c r="O229" s="31" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="P229" s="31" t="n">
         <v>17.3</v>
       </c>
       <c r="Q229" s="31" t="n">
-        <v>12.89</v>
+        <v>11.2</v>
       </c>
       <c r="R229" s="49" t="n"/>
       <c r="S229" s="22" t="inlineStr">
@@ -24529,13 +24475,13 @@
       </c>
       <c r="N230" s="2" t="n"/>
       <c r="O230" s="31" t="n">
-        <v>-1.4</v>
+        <v>6.8</v>
       </c>
       <c r="P230" s="31" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="Q230" s="31" t="n">
-        <v>7.75</v>
+        <v>11.89</v>
       </c>
       <c r="R230" s="49" t="n"/>
       <c r="S230" s="22" t="inlineStr">
@@ -24925,14 +24871,12 @@
         </is>
       </c>
       <c r="O234" s="31" t="n">
-        <v>-4.6</v>
+        <v>-5.1</v>
       </c>
       <c r="P234" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q234" s="31" t="n">
-        <v>0.48</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q234" s="31" t="n"/>
       <c r="R234" s="49" t="n"/>
       <c r="S234" s="22" t="inlineStr">
         <is>
@@ -25583,9 +25527,15 @@
         </is>
       </c>
       <c r="N241" s="2" t="n"/>
-      <c r="O241" s="31" t="n"/>
-      <c r="P241" s="31" t="n"/>
-      <c r="Q241" s="31" t="n"/>
+      <c r="O241" s="31" t="n">
+        <v>-21.7</v>
+      </c>
+      <c r="P241" s="31" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="Q241" s="31" t="n">
+        <v>-13.67</v>
+      </c>
       <c r="R241" s="49" t="n"/>
       <c r="S241" s="22" t="n"/>
       <c r="T241" s="35" t="n"/>
@@ -27168,13 +27118,13 @@
       </c>
       <c r="N258" s="2" t="n"/>
       <c r="O258" s="31" t="n">
-        <v>-5.7</v>
+        <v>-14.7</v>
       </c>
       <c r="P258" s="31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q258" s="31" t="n">
-        <v>-2.43</v>
+        <v>-5.71</v>
       </c>
       <c r="R258" s="49" t="n"/>
       <c r="S258" s="22" t="inlineStr">
@@ -27662,10 +27612,10 @@
       </c>
       <c r="N263" s="2" t="n"/>
       <c r="O263" s="31" t="n">
-        <v>-6.6</v>
+        <v>-2.5</v>
       </c>
       <c r="P263" s="31" t="n">
-        <v>11.2</v>
+        <v>7</v>
       </c>
       <c r="Q263" s="31" t="n"/>
       <c r="R263" s="49" t="n"/>
@@ -28043,10 +27993,10 @@
       </c>
       <c r="N267" s="2" t="n"/>
       <c r="O267" s="31" t="n">
-        <v>-75.8</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="P267" s="31" t="n">
-        <v>-63.4</v>
+        <v>-50.8</v>
       </c>
       <c r="Q267" s="31" t="n"/>
       <c r="R267" s="49" t="n"/>
@@ -28143,7 +28093,9 @@
         </is>
       </c>
       <c r="N268" s="2" t="n"/>
-      <c r="O268" s="31" t="n"/>
+      <c r="O268" s="31" t="n">
+        <v>-76.3</v>
+      </c>
       <c r="P268" s="31" t="n"/>
       <c r="Q268" s="31" t="n"/>
       <c r="R268" s="49" t="n"/>
@@ -28235,13 +28187,13 @@
       </c>
       <c r="N269" s="2" t="n"/>
       <c r="O269" s="31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P269" s="31" t="n">
         <v>9.5</v>
       </c>
-      <c r="P269" s="31" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Q269" s="31" t="n">
-        <v>11.11</v>
+        <v>4.12</v>
       </c>
       <c r="R269" s="49" t="n"/>
       <c r="S269" s="22" t="inlineStr">
@@ -28353,9 +28305,15 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O270" s="31" t="n"/>
-      <c r="P270" s="31" t="n"/>
-      <c r="Q270" s="31" t="n"/>
+      <c r="O270" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P270" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q270" s="31" t="n">
+        <v>3.88</v>
+      </c>
       <c r="R270" s="49" t="n"/>
       <c r="S270" s="22" t="n"/>
       <c r="T270" s="35" t="n"/>
@@ -29219,13 +29177,13 @@
       </c>
       <c r="N279" s="2" t="n"/>
       <c r="O279" s="31" t="n">
-        <v>-8.6</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="P279" s="31" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="Q279" s="31" t="n">
-        <v>2.31</v>
+        <v>4.14</v>
       </c>
       <c r="R279" s="49" t="n"/>
       <c r="S279" s="22" t="n"/>
@@ -32775,12 +32733,8 @@
         </is>
       </c>
       <c r="N316" s="2" t="n"/>
-      <c r="O316" s="31" t="n">
-        <v>-11.7</v>
-      </c>
-      <c r="P316" s="31" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="O316" s="31" t="n"/>
+      <c r="P316" s="31" t="n"/>
       <c r="Q316" s="31" t="n"/>
       <c r="R316" s="49" t="n"/>
       <c r="S316" s="22" t="n"/>
@@ -34194,8 +34148,12 @@
         </is>
       </c>
       <c r="N331" s="2" t="n"/>
-      <c r="O331" s="31" t="n"/>
-      <c r="P331" s="31" t="n"/>
+      <c r="O331" s="31" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="P331" s="31" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Q331" s="31" t="n"/>
       <c r="R331" s="49" t="n"/>
       <c r="S331" s="22" t="n"/>
@@ -34753,13 +34711,13 @@
       </c>
       <c r="N337" s="2" t="n"/>
       <c r="O337" s="31" t="n">
-        <v>1.3</v>
+        <v>-3.8</v>
       </c>
       <c r="P337" s="31" t="n">
-        <v>7.5</v>
+        <v>13.2</v>
       </c>
       <c r="Q337" s="31" t="n">
-        <v>3.28</v>
+        <v>5.01</v>
       </c>
       <c r="R337" s="49" t="n"/>
       <c r="S337" s="22" t="n"/>
@@ -34850,13 +34808,13 @@
       </c>
       <c r="N338" s="2" t="n"/>
       <c r="O338" s="31" t="n">
-        <v>-6.4</v>
+        <v>-9.4</v>
       </c>
       <c r="P338" s="31" t="n">
-        <v>9.6</v>
+        <v>12.4</v>
       </c>
       <c r="Q338" s="31" t="n">
-        <v>1.83</v>
+        <v>0.99</v>
       </c>
       <c r="R338" s="49" t="n"/>
       <c r="S338" s="22" t="n"/>
@@ -34954,9 +34912,15 @@
         </is>
       </c>
       <c r="N339" s="2" t="n"/>
-      <c r="O339" s="31" t="n"/>
-      <c r="P339" s="31" t="n"/>
-      <c r="Q339" s="31" t="n"/>
+      <c r="O339" s="31" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="P339" s="31" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="Q339" s="31" t="n">
+        <v>0.7</v>
+      </c>
       <c r="R339" s="49" t="n"/>
       <c r="S339" s="22" t="n"/>
       <c r="T339" s="35" t="n"/>
@@ -35362,9 +35326,15 @@
         </is>
       </c>
       <c r="N343" s="2" t="n"/>
-      <c r="O343" s="31" t="n"/>
-      <c r="P343" s="31" t="n"/>
-      <c r="Q343" s="31" t="n"/>
+      <c r="O343" s="31" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="P343" s="31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="Q343" s="31" t="n">
+        <v>3.63</v>
+      </c>
       <c r="R343" s="49" t="n"/>
       <c r="S343" s="22" t="n"/>
       <c r="T343" s="35" t="n"/>
@@ -35562,9 +35532,15 @@
         </is>
       </c>
       <c r="N345" s="2" t="n"/>
-      <c r="O345" s="31" t="n"/>
-      <c r="P345" s="31" t="n"/>
-      <c r="Q345" s="31" t="n"/>
+      <c r="O345" s="31" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="P345" s="31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Q345" s="31" t="n">
+        <v>5.39</v>
+      </c>
       <c r="R345" s="49" t="n"/>
       <c r="S345" s="22" t="n"/>
       <c r="T345" s="35" t="n"/>
@@ -36044,12 +36020,8 @@
       <c r="O350" s="31" t="n">
         <v>-20.6</v>
       </c>
-      <c r="P350" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q350" s="31" t="n">
-        <v>-10.6</v>
-      </c>
+      <c r="P350" s="31" t="n"/>
+      <c r="Q350" s="31" t="n"/>
       <c r="R350" s="49" t="n"/>
       <c r="S350" s="22" t="n"/>
       <c r="T350" s="35" t="n"/>
@@ -36147,14 +36119,10 @@
       </c>
       <c r="N351" s="2" t="n"/>
       <c r="O351" s="31" t="n">
-        <v>-22.2</v>
-      </c>
-      <c r="P351" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Q351" s="31" t="n">
-        <v>-10.2</v>
-      </c>
+        <v>-24.1</v>
+      </c>
+      <c r="P351" s="31" t="n"/>
+      <c r="Q351" s="31" t="n"/>
       <c r="R351" s="49" t="n"/>
       <c r="S351" s="22" t="n"/>
       <c r="T351" s="35" t="n"/>
@@ -36252,14 +36220,10 @@
       </c>
       <c r="N352" s="2" t="n"/>
       <c r="O352" s="31" t="n">
-        <v>-19</v>
-      </c>
-      <c r="P352" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q352" s="31" t="n">
-        <v>-9</v>
-      </c>
+        <v>-20.8</v>
+      </c>
+      <c r="P352" s="31" t="n"/>
+      <c r="Q352" s="31" t="n"/>
       <c r="R352" s="49" t="n"/>
       <c r="S352" s="22" t="n"/>
       <c r="T352" s="35" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AB3E0D-6155-48A5-BEC0-C353198ADBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987DE207-FF74-4267-9C5B-8B2DA6FA0CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="极寒收集" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">站点信息和记录!$A$1:$AI$425</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">站点信息和记录!$A$1:$AI$426</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4848" uniqueCount="1217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4863" uniqueCount="1227">
   <si>
     <t>id</t>
   </si>
@@ -3680,6 +3680,46 @@
   </si>
   <si>
     <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>↓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>⚡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>▼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海坨山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A1490</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北京延庆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北京</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>延庆区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>竞速训练1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4415,7 +4455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI425"/>
+  <dimension ref="A1:AI426"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="20.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.59765625" style="5" customWidth="1"/>
@@ -11915,7 +11955,7 @@
         <v>261</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>262</v>
+        <v>1219</v>
       </c>
       <c r="O102" s="31">
         <v>-7.4</v>
@@ -12743,7 +12783,7 @@
         <v>305</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>306</v>
+        <v>1217</v>
       </c>
       <c r="O112" s="31"/>
       <c r="P112" s="31"/>
@@ -13918,9 +13958,7 @@
       <c r="M126" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="N126" s="2" t="s">
-        <v>262</v>
-      </c>
+      <c r="N126" s="2"/>
       <c r="O126" s="31">
         <v>-9.3000000000000007</v>
       </c>
@@ -14005,9 +14043,7 @@
       <c r="M127" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="N127" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="31"/>
       <c r="P127" s="31"/>
       <c r="Q127" s="31"/>
@@ -17529,7 +17565,9 @@
       <c r="M169" s="14" t="s">
         <v>583</v>
       </c>
-      <c r="N169" s="2"/>
+      <c r="N169" s="2" t="s">
+        <v>1217</v>
+      </c>
       <c r="O169" s="31">
         <v>-4.7</v>
       </c>
@@ -20054,7 +20092,7 @@
         <v>714</v>
       </c>
       <c r="N201" s="3" t="s">
-        <v>50</v>
+        <v>1218</v>
       </c>
       <c r="O201" s="31"/>
       <c r="P201" s="31"/>
@@ -20128,7 +20166,9 @@
       <c r="M202" s="14" t="s">
         <v>717</v>
       </c>
-      <c r="N202" s="2"/>
+      <c r="N202" s="3" t="s">
+        <v>1218</v>
+      </c>
       <c r="O202" s="31"/>
       <c r="P202" s="31"/>
       <c r="Q202" s="31"/>
@@ -20204,7 +20244,7 @@
         <v>718</v>
       </c>
       <c r="N203" s="3" t="s">
-        <v>50</v>
+        <v>1219</v>
       </c>
       <c r="O203" s="31"/>
       <c r="P203" s="31"/>
@@ -20280,7 +20320,9 @@
       <c r="M204" s="14" t="s">
         <v>721</v>
       </c>
-      <c r="N204" s="2"/>
+      <c r="N204" s="2" t="s">
+        <v>1217</v>
+      </c>
       <c r="O204" s="31"/>
       <c r="P204" s="31"/>
       <c r="Q204" s="31"/>
@@ -20581,7 +20623,7 @@
         <v>730</v>
       </c>
       <c r="N208" s="3" t="s">
-        <v>306</v>
+        <v>1217</v>
       </c>
       <c r="O208" s="31"/>
       <c r="P208" s="31"/>
@@ -27050,9 +27092,7 @@
       <c r="M296" s="14" t="s">
         <v>1007</v>
       </c>
-      <c r="N296" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="N296" s="2"/>
       <c r="O296" s="31"/>
       <c r="P296" s="31"/>
       <c r="Q296" s="31"/>
@@ -30249,7 +30289,9 @@
       <c r="M341" s="14" t="s">
         <v>1095</v>
       </c>
-      <c r="N341" s="2"/>
+      <c r="N341" s="3" t="s">
+        <v>1218</v>
+      </c>
       <c r="O341" s="31">
         <v>-7</v>
       </c>
@@ -30403,7 +30445,9 @@
       <c r="M343" s="14" t="s">
         <v>1103</v>
       </c>
-      <c r="N343" s="2"/>
+      <c r="N343" s="2" t="s">
+        <v>1217</v>
+      </c>
       <c r="O343" s="31">
         <v>-7.2</v>
       </c>
@@ -30846,24 +30890,20 @@
         <v>347</v>
       </c>
       <c r="B349" s="2"/>
-      <c r="C349" s="44">
-        <v>58968</v>
-      </c>
-      <c r="D349" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E349" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F349" s="37"/>
+      <c r="C349" s="44"/>
+      <c r="D349" s="2"/>
+      <c r="E349" s="4"/>
+      <c r="F349" s="37" t="s">
+        <v>1221</v>
+      </c>
       <c r="G349" s="28">
-        <v>25.033333299999999</v>
+        <v>40.555999999999997</v>
       </c>
       <c r="H349" s="28">
-        <v>121.51666659999999</v>
+        <v>115.79300000000001</v>
       </c>
       <c r="I349" s="2">
-        <v>9</v>
+        <v>1798</v>
       </c>
       <c r="J349" s="26">
         <v>12</v>
@@ -30871,32 +30911,38 @@
       <c r="K349" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="L349" s="3"/>
+      <c r="L349" s="2"/>
       <c r="M349" s="14" t="s">
-        <v>1124</v>
+        <v>1220</v>
       </c>
       <c r="N349" s="2"/>
       <c r="O349" s="31"/>
       <c r="P349" s="31"/>
       <c r="Q349" s="31"/>
-      <c r="R349" s="49"/>
+      <c r="R349" s="49" t="s">
+        <v>1222</v>
+      </c>
       <c r="S349" s="22"/>
       <c r="T349" s="35"/>
       <c r="U349" s="39" t="s">
-        <v>1125</v>
+        <v>1223</v>
       </c>
       <c r="V349" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="W349" s="4"/>
+        <v>1224</v>
+      </c>
+      <c r="W349" s="4" t="s">
+        <v>1216</v>
+      </c>
       <c r="X349" s="4" t="s">
-        <v>40</v>
+        <v>1216</v>
       </c>
       <c r="Y349" s="4" t="s">
-        <v>40</v>
+        <v>1216</v>
       </c>
       <c r="Z349" s="4"/>
-      <c r="AA349" s="2"/>
+      <c r="AA349" s="2" t="s">
+        <v>1225</v>
+      </c>
       <c r="AB349" s="2"/>
       <c r="AC349" s="2"/>
       <c r="AD349" s="2"/>
@@ -30908,27 +30954,33 @@
       </c>
       <c r="AG349" s="4"/>
       <c r="AH349" s="2"/>
-      <c r="AI349" s="2"/>
+      <c r="AI349" s="2" t="s">
+        <v>1226</v>
+      </c>
     </row>
     <row r="350" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A350" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B350" s="2"/>
-      <c r="C350" s="44"/>
-      <c r="D350" s="2"/>
-      <c r="E350" s="4"/>
-      <c r="F350" s="37" t="s">
-        <v>1126</v>
-      </c>
+      <c r="C350" s="44">
+        <v>58968</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E350" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F350" s="37"/>
       <c r="G350" s="28">
-        <v>31.134</v>
+        <v>25.033333299999999</v>
       </c>
       <c r="H350" s="28">
-        <v>82.221999999999994</v>
+        <v>121.51666659999999</v>
       </c>
       <c r="I350" s="2">
-        <v>5170</v>
+        <v>9</v>
       </c>
       <c r="J350" s="26">
         <v>12</v>
@@ -30936,9 +30988,9 @@
       <c r="K350" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="L350" s="2"/>
+      <c r="L350" s="3"/>
       <c r="M350" s="14" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="N350" s="2"/>
       <c r="O350" s="31"/>
@@ -30948,14 +31000,12 @@
       <c r="S350" s="22"/>
       <c r="T350" s="35"/>
       <c r="U350" s="39" t="s">
-        <v>576</v>
+        <v>1125</v>
       </c>
       <c r="V350" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="W350" s="4" t="s">
-        <v>40</v>
-      </c>
+        <v>1125</v>
+      </c>
+      <c r="W350" s="4"/>
       <c r="X350" s="4" t="s">
         <v>40</v>
       </c>
@@ -30963,12 +31013,8 @@
         <v>40</v>
       </c>
       <c r="Z350" s="4"/>
-      <c r="AA350" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AB350" s="2" t="s">
-        <v>1129</v>
-      </c>
+      <c r="AA350" s="2"/>
+      <c r="AB350" s="2"/>
       <c r="AC350" s="2"/>
       <c r="AD350" s="2"/>
       <c r="AE350" s="2" t="s">
@@ -30983,23 +31029,23 @@
     </row>
     <row r="351" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A351" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B351" s="2"/>
       <c r="C351" s="44"/>
       <c r="D351" s="2"/>
       <c r="E351" s="4"/>
       <c r="F351" s="37" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="G351" s="28">
-        <v>30.975999999999999</v>
+        <v>31.134</v>
       </c>
       <c r="H351" s="28">
-        <v>80.953000000000003</v>
+        <v>82.221999999999994</v>
       </c>
       <c r="I351" s="2">
-        <v>4526</v>
+        <v>5170</v>
       </c>
       <c r="J351" s="26">
         <v>12</v>
@@ -31009,7 +31055,7 @@
       </c>
       <c r="L351" s="2"/>
       <c r="M351" s="14" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="N351" s="2"/>
       <c r="O351" s="31"/>
@@ -31019,7 +31065,7 @@
       <c r="S351" s="22"/>
       <c r="T351" s="35"/>
       <c r="U351" s="39" t="s">
-        <v>1132</v>
+        <v>576</v>
       </c>
       <c r="V351" s="2" t="s">
         <v>576</v>
@@ -31038,7 +31084,7 @@
         <v>1128</v>
       </c>
       <c r="AB351" s="2" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="AC351" s="2"/>
       <c r="AD351" s="2"/>
@@ -31049,30 +31095,28 @@
         <v>325</v>
       </c>
       <c r="AG351" s="4"/>
-      <c r="AH351" s="2" t="s">
-        <v>600</v>
-      </c>
+      <c r="AH351" s="2"/>
       <c r="AI351" s="2"/>
     </row>
     <row r="352" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A352" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B352" s="2"/>
       <c r="C352" s="44"/>
       <c r="D352" s="2"/>
       <c r="E352" s="4"/>
       <c r="F352" s="37" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="G352" s="28">
-        <v>30.594000000000001</v>
+        <v>30.975999999999999</v>
       </c>
       <c r="H352" s="28">
-        <v>82.472999999999999</v>
+        <v>80.953000000000003</v>
       </c>
       <c r="I352" s="2">
-        <v>5047</v>
+        <v>4526</v>
       </c>
       <c r="J352" s="26">
         <v>12</v>
@@ -31082,19 +31126,17 @@
       </c>
       <c r="L352" s="2"/>
       <c r="M352" s="14" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="N352" s="2"/>
-      <c r="O352" s="31">
-        <v>-24.1</v>
-      </c>
+      <c r="O352" s="31"/>
       <c r="P352" s="31"/>
       <c r="Q352" s="31"/>
       <c r="R352" s="49"/>
       <c r="S352" s="22"/>
       <c r="T352" s="35"/>
       <c r="U352" s="39" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="V352" s="2" t="s">
         <v>576</v>
@@ -31113,7 +31155,7 @@
         <v>1128</v>
       </c>
       <c r="AB352" s="2" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="AC352" s="2"/>
       <c r="AD352" s="2"/>
@@ -31131,23 +31173,23 @@
     </row>
     <row r="353" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A353" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B353" s="2"/>
       <c r="C353" s="44"/>
       <c r="D353" s="2"/>
       <c r="E353" s="4"/>
       <c r="F353" s="37" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="G353" s="28">
-        <v>30.591000000000001</v>
+        <v>30.594000000000001</v>
       </c>
       <c r="H353" s="28">
-        <v>82.474999999999994</v>
+        <v>82.472999999999999</v>
       </c>
       <c r="I353" s="2">
-        <v>5039.2</v>
+        <v>5047</v>
       </c>
       <c r="J353" s="26">
         <v>12</v>
@@ -31157,11 +31199,11 @@
       </c>
       <c r="L353" s="2"/>
       <c r="M353" s="14" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="N353" s="2"/>
       <c r="O353" s="31">
-        <v>-21.1</v>
+        <v>-24.1</v>
       </c>
       <c r="P353" s="31"/>
       <c r="Q353" s="31"/>
@@ -31169,7 +31211,7 @@
       <c r="S353" s="22"/>
       <c r="T353" s="35"/>
       <c r="U353" s="39" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="V353" s="2" t="s">
         <v>576</v>
@@ -31206,23 +31248,23 @@
     </row>
     <row r="354" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A354" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B354" s="2"/>
       <c r="C354" s="44"/>
       <c r="D354" s="2"/>
       <c r="E354" s="4"/>
       <c r="F354" s="37" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="G354" s="28">
-        <v>31.095800000000001</v>
+        <v>30.591000000000001</v>
       </c>
       <c r="H354" s="28">
-        <v>81.369699999999995</v>
+        <v>82.474999999999994</v>
       </c>
       <c r="I354" s="2">
-        <v>5642</v>
+        <v>5039.2</v>
       </c>
       <c r="J354" s="26">
         <v>12</v>
@@ -31232,17 +31274,19 @@
       </c>
       <c r="L354" s="2"/>
       <c r="M354" s="14" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="N354" s="2"/>
-      <c r="O354" s="31"/>
+      <c r="O354" s="31">
+        <v>-21.1</v>
+      </c>
       <c r="P354" s="31"/>
       <c r="Q354" s="31"/>
       <c r="R354" s="49"/>
       <c r="S354" s="22"/>
       <c r="T354" s="35"/>
       <c r="U354" s="39" t="s">
-        <v>576</v>
+        <v>1132</v>
       </c>
       <c r="V354" s="2" t="s">
         <v>576</v>
@@ -31272,23 +31316,31 @@
         <v>325</v>
       </c>
       <c r="AG354" s="4"/>
-      <c r="AH354" s="2"/>
+      <c r="AH354" s="2" t="s">
+        <v>600</v>
+      </c>
       <c r="AI354" s="2"/>
     </row>
     <row r="355" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A355" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B355" s="2"/>
       <c r="C355" s="44"/>
       <c r="D355" s="2"/>
       <c r="E355" s="4"/>
       <c r="F355" s="37" t="s">
-        <v>1142</v>
-      </c>
-      <c r="G355" s="28"/>
-      <c r="H355" s="28"/>
-      <c r="I355" s="2"/>
+        <v>1140</v>
+      </c>
+      <c r="G355" s="28">
+        <v>31.095800000000001</v>
+      </c>
+      <c r="H355" s="28">
+        <v>81.369699999999995</v>
+      </c>
+      <c r="I355" s="2">
+        <v>5642</v>
+      </c>
       <c r="J355" s="26">
         <v>12</v>
       </c>
@@ -31297,7 +31349,7 @@
       </c>
       <c r="L355" s="2"/>
       <c r="M355" s="14" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="N355" s="2"/>
       <c r="O355" s="31"/>
@@ -31342,26 +31394,18 @@
     </row>
     <row r="356" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A356" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B356" s="2"/>
-      <c r="C356" s="44" t="s">
-        <v>1144</v>
-      </c>
+      <c r="C356" s="44"/>
       <c r="D356" s="2"/>
-      <c r="E356" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F356" s="37"/>
-      <c r="G356" s="28">
-        <v>34.426400000000001</v>
-      </c>
-      <c r="H356" s="28">
-        <v>80.386099999999999</v>
-      </c>
-      <c r="I356" s="2">
-        <v>5188.6000000000004</v>
-      </c>
+      <c r="E356" s="4"/>
+      <c r="F356" s="37" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G356" s="28"/>
+      <c r="H356" s="28"/>
+      <c r="I356" s="2"/>
       <c r="J356" s="26">
         <v>12</v>
       </c>
@@ -31370,7 +31414,7 @@
       </c>
       <c r="L356" s="2"/>
       <c r="M356" s="14" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="N356" s="2"/>
       <c r="O356" s="31"/>
@@ -31395,8 +31439,12 @@
         <v>40</v>
       </c>
       <c r="Z356" s="4"/>
-      <c r="AA356" s="2"/>
-      <c r="AB356" s="2"/>
+      <c r="AA356" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AB356" s="2" t="s">
+        <v>1137</v>
+      </c>
       <c r="AC356" s="2"/>
       <c r="AD356" s="2"/>
       <c r="AE356" s="2" t="s">
@@ -31411,29 +31459,25 @@
     </row>
     <row r="357" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A357" s="2">
-        <v>355</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>109</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="B357" s="2"/>
       <c r="C357" s="44" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D357" s="2" t="s">
-        <v>1147</v>
-      </c>
+        <v>1144</v>
+      </c>
+      <c r="D357" s="2"/>
       <c r="E357" s="4">
         <v>99999</v>
       </c>
       <c r="F357" s="37"/>
       <c r="G357" s="28">
-        <v>28.654199999999999</v>
+        <v>34.426400000000001</v>
       </c>
       <c r="H357" s="28">
-        <v>87.1203</v>
+        <v>80.386099999999999</v>
       </c>
       <c r="I357" s="2">
-        <v>4322</v>
+        <v>5188.6000000000004</v>
       </c>
       <c r="J357" s="26">
         <v>12</v>
@@ -31443,7 +31487,7 @@
       </c>
       <c r="L357" s="2"/>
       <c r="M357" s="14" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="N357" s="2"/>
       <c r="O357" s="31"/>
@@ -31468,12 +31512,8 @@
         <v>40</v>
       </c>
       <c r="Z357" s="4"/>
-      <c r="AA357" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AB357" s="2" t="s">
-        <v>1150</v>
-      </c>
+      <c r="AA357" s="2"/>
+      <c r="AB357" s="2"/>
       <c r="AC357" s="2"/>
       <c r="AD357" s="2"/>
       <c r="AE357" s="2" t="s">
@@ -31483,34 +31523,34 @@
         <v>325</v>
       </c>
       <c r="AG357" s="4"/>
-      <c r="AH357" s="2" t="s">
-        <v>600</v>
-      </c>
+      <c r="AH357" s="2"/>
       <c r="AI357" s="2"/>
     </row>
     <row r="358" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A358" s="2">
-        <v>356</v>
-      </c>
-      <c r="B358" s="2"/>
-      <c r="C358" s="44">
-        <v>45007</v>
+        <v>355</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C358" s="44" t="s">
+        <v>1146</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="E358" s="4">
         <v>99999</v>
       </c>
       <c r="F358" s="37"/>
       <c r="G358" s="28">
-        <v>22.308918999999999</v>
+        <v>28.654199999999999</v>
       </c>
       <c r="H358" s="28">
-        <v>113.914603</v>
+        <v>87.1203</v>
       </c>
       <c r="I358" s="2">
-        <v>8.5299999999999994</v>
+        <v>4322</v>
       </c>
       <c r="J358" s="26">
         <v>12</v>
@@ -31518,9 +31558,9 @@
       <c r="K358" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="L358" s="3"/>
+      <c r="L358" s="2"/>
       <c r="M358" s="14" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="N358" s="2"/>
       <c r="O358" s="31"/>
@@ -31529,11 +31569,15 @@
       <c r="R358" s="49"/>
       <c r="S358" s="22"/>
       <c r="T358" s="35"/>
-      <c r="U358" s="39"/>
+      <c r="U358" s="39" t="s">
+        <v>576</v>
+      </c>
       <c r="V358" s="2" t="s">
-        <v>1152</v>
-      </c>
-      <c r="W358" s="4"/>
+        <v>576</v>
+      </c>
+      <c r="W358" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="X358" s="4" t="s">
         <v>40</v>
       </c>
@@ -31541,8 +31585,12 @@
         <v>40</v>
       </c>
       <c r="Z358" s="4"/>
-      <c r="AA358" s="2"/>
-      <c r="AB358" s="2"/>
+      <c r="AA358" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AB358" s="2" t="s">
+        <v>1150</v>
+      </c>
       <c r="AC358" s="2"/>
       <c r="AD358" s="2"/>
       <c r="AE358" s="2" t="s">
@@ -31552,28 +31600,34 @@
         <v>325</v>
       </c>
       <c r="AG358" s="4"/>
-      <c r="AH358" s="2"/>
+      <c r="AH358" s="2" t="s">
+        <v>600</v>
+      </c>
       <c r="AI358" s="2"/>
     </row>
     <row r="359" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A359" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B359" s="2"/>
-      <c r="C359" s="44"/>
-      <c r="D359" s="2"/>
-      <c r="E359" s="4"/>
-      <c r="F359" s="37" t="s">
-        <v>1153</v>
-      </c>
+      <c r="C359" s="44">
+        <v>45007</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E359" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F359" s="37"/>
       <c r="G359" s="28">
-        <v>48.0197</v>
+        <v>22.308918999999999</v>
       </c>
       <c r="H359" s="28">
-        <v>87.551699999999997</v>
+        <v>113.914603</v>
       </c>
       <c r="I359" s="2">
-        <v>1194</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="J359" s="26">
         <v>12</v>
@@ -31581,9 +31635,9 @@
       <c r="K359" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="L359" s="2"/>
+      <c r="L359" s="3"/>
       <c r="M359" s="14" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="N359" s="2"/>
       <c r="O359" s="31"/>
@@ -31592,15 +31646,11 @@
       <c r="R359" s="49"/>
       <c r="S359" s="22"/>
       <c r="T359" s="35"/>
-      <c r="U359" s="39" t="s">
-        <v>122</v>
-      </c>
+      <c r="U359" s="39"/>
       <c r="V359" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="W359" s="4" t="s">
-        <v>40</v>
-      </c>
+        <v>1152</v>
+      </c>
+      <c r="W359" s="4"/>
       <c r="X359" s="4" t="s">
         <v>40</v>
       </c>
@@ -31608,12 +31658,8 @@
         <v>40</v>
       </c>
       <c r="Z359" s="4"/>
-      <c r="AA359" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="AB359" s="2" t="s">
-        <v>414</v>
-      </c>
+      <c r="AA359" s="2"/>
+      <c r="AB359" s="2"/>
       <c r="AC359" s="2"/>
       <c r="AD359" s="2"/>
       <c r="AE359" s="2" t="s">
@@ -31623,30 +31669,28 @@
         <v>325</v>
       </c>
       <c r="AG359" s="4"/>
-      <c r="AH359" s="2" t="s">
-        <v>122</v>
-      </c>
+      <c r="AH359" s="2"/>
       <c r="AI359" s="2"/>
     </row>
     <row r="360" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A360" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B360" s="2"/>
       <c r="C360" s="44"/>
       <c r="D360" s="2"/>
       <c r="E360" s="4"/>
       <c r="F360" s="37" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G360" s="28">
-        <v>48.721699999999998</v>
+        <v>48.0197</v>
       </c>
       <c r="H360" s="28">
-        <v>87.030600000000007</v>
+        <v>87.551699999999997</v>
       </c>
       <c r="I360" s="2">
-        <v>1367</v>
+        <v>1194</v>
       </c>
       <c r="J360" s="26">
         <v>12</v>
@@ -31654,9 +31698,9 @@
       <c r="K360" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="L360" s="3"/>
+      <c r="L360" s="2"/>
       <c r="M360" s="14" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="N360" s="2"/>
       <c r="O360" s="31"/>
@@ -31685,11 +31729,9 @@
         <v>409</v>
       </c>
       <c r="AB360" s="2" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AC360" s="2" t="s">
-        <v>1158</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="AC360" s="2"/>
       <c r="AD360" s="2"/>
       <c r="AE360" s="2" t="s">
         <v>324</v>
@@ -31701,29 +31743,27 @@
       <c r="AH360" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AI360" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="AI360" s="2"/>
     </row>
     <row r="361" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A361" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B361" s="2"/>
       <c r="C361" s="44"/>
       <c r="D361" s="2"/>
       <c r="E361" s="4"/>
       <c r="F361" s="37" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="G361" s="28">
-        <v>48.584200000000003</v>
+        <v>48.721699999999998</v>
       </c>
       <c r="H361" s="28">
-        <v>87.457800000000006</v>
+        <v>87.030600000000007</v>
       </c>
       <c r="I361" s="2">
-        <v>1223</v>
+        <v>1367</v>
       </c>
       <c r="J361" s="26">
         <v>12</v>
@@ -31733,11 +31773,9 @@
       </c>
       <c r="L361" s="3"/>
       <c r="M361" s="14" t="s">
-        <v>1160</v>
-      </c>
-      <c r="N361" s="23" t="s">
-        <v>1161</v>
-      </c>
+        <v>1156</v>
+      </c>
+      <c r="N361" s="2"/>
       <c r="O361" s="31"/>
       <c r="P361" s="31"/>
       <c r="Q361" s="31"/>
@@ -31780,29 +31818,29 @@
       <c r="AH361" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AI361" s="2"/>
+      <c r="AI361" s="2" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="362" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A362" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B362" s="2"/>
-      <c r="C362" s="44">
-        <v>51068</v>
-      </c>
+      <c r="C362" s="44"/>
       <c r="D362" s="2"/>
-      <c r="E362" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F362" s="37"/>
+      <c r="E362" s="4"/>
+      <c r="F362" s="37" t="s">
+        <v>1159</v>
+      </c>
       <c r="G362" s="28">
-        <v>47.125</v>
+        <v>48.584200000000003</v>
       </c>
       <c r="H362" s="28">
-        <v>87.481399999999994</v>
+        <v>87.457800000000006</v>
       </c>
       <c r="I362" s="2">
-        <v>497.1</v>
+        <v>1223</v>
       </c>
       <c r="J362" s="26">
         <v>12</v>
@@ -31810,11 +31848,13 @@
       <c r="K362" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="L362" s="2"/>
+      <c r="L362" s="3"/>
       <c r="M362" s="14" t="s">
-        <v>1162</v>
-      </c>
-      <c r="N362" s="2"/>
+        <v>1160</v>
+      </c>
+      <c r="N362" s="23" t="s">
+        <v>1161</v>
+      </c>
       <c r="O362" s="31"/>
       <c r="P362" s="31"/>
       <c r="Q362" s="31"/>
@@ -31822,7 +31862,7 @@
       <c r="S362" s="22"/>
       <c r="T362" s="35"/>
       <c r="U362" s="39" t="s">
-        <v>1163</v>
+        <v>122</v>
       </c>
       <c r="V362" s="2" t="s">
         <v>404</v>
@@ -31841,9 +31881,11 @@
         <v>409</v>
       </c>
       <c r="AB362" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AC362" s="2"/>
+        <v>1157</v>
+      </c>
+      <c r="AC362" s="2" t="s">
+        <v>1158</v>
+      </c>
       <c r="AD362" s="2"/>
       <c r="AE362" s="2" t="s">
         <v>324</v>
@@ -31853,29 +31895,31 @@
       </c>
       <c r="AG362" s="4"/>
       <c r="AH362" s="2" t="s">
-        <v>1163</v>
+        <v>122</v>
       </c>
       <c r="AI362" s="2"/>
     </row>
     <row r="363" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A363" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B363" s="2"/>
-      <c r="C363" s="44"/>
+      <c r="C363" s="44">
+        <v>51068</v>
+      </c>
       <c r="D363" s="2"/>
-      <c r="E363" s="4"/>
-      <c r="F363" s="37" t="s">
-        <v>1165</v>
-      </c>
+      <c r="E363" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F363" s="37"/>
       <c r="G363" s="28">
-        <v>47.168100000000003</v>
+        <v>47.125</v>
       </c>
       <c r="H363" s="28">
-        <v>90.090299999999999</v>
+        <v>87.481399999999994</v>
       </c>
       <c r="I363" s="2">
-        <v>3084</v>
+        <v>497.1</v>
       </c>
       <c r="J363" s="26">
         <v>12</v>
@@ -31883,13 +31927,11 @@
       <c r="K363" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="L363" s="3"/>
+      <c r="L363" s="2"/>
       <c r="M363" s="14" t="s">
-        <v>1166</v>
-      </c>
-      <c r="N363" s="23" t="s">
-        <v>101</v>
-      </c>
+        <v>1162</v>
+      </c>
+      <c r="N363" s="2"/>
       <c r="O363" s="31"/>
       <c r="P363" s="31"/>
       <c r="Q363" s="31"/>
@@ -31897,7 +31939,7 @@
       <c r="S363" s="22"/>
       <c r="T363" s="35"/>
       <c r="U363" s="39" t="s">
-        <v>122</v>
+        <v>1163</v>
       </c>
       <c r="V363" s="2" t="s">
         <v>404</v>
@@ -31916,7 +31958,7 @@
         <v>409</v>
       </c>
       <c r="AB363" s="2" t="s">
-        <v>732</v>
+        <v>1164</v>
       </c>
       <c r="AC363" s="2"/>
       <c r="AD363" s="2"/>
@@ -31928,31 +31970,29 @@
       </c>
       <c r="AG363" s="4"/>
       <c r="AH363" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI363" s="2" t="s">
-        <v>650</v>
-      </c>
+        <v>1163</v>
+      </c>
+      <c r="AI363" s="2"/>
     </row>
     <row r="364" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A364" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B364" s="2"/>
       <c r="C364" s="44"/>
       <c r="D364" s="2"/>
       <c r="E364" s="4"/>
       <c r="F364" s="37" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="G364" s="28">
-        <v>47.138100000000001</v>
+        <v>47.168100000000003</v>
       </c>
       <c r="H364" s="28">
-        <v>85.597499999999997</v>
+        <v>90.090299999999999</v>
       </c>
       <c r="I364" s="2">
-        <v>2914</v>
+        <v>3084</v>
       </c>
       <c r="J364" s="26">
         <v>12</v>
@@ -31960,11 +32000,13 @@
       <c r="K364" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="L364" s="2"/>
+      <c r="L364" s="3"/>
       <c r="M364" s="14" t="s">
-        <v>1168</v>
-      </c>
-      <c r="N364" s="23"/>
+        <v>1166</v>
+      </c>
+      <c r="N364" s="23" t="s">
+        <v>101</v>
+      </c>
       <c r="O364" s="31"/>
       <c r="P364" s="31"/>
       <c r="Q364" s="31"/>
@@ -31972,7 +32014,7 @@
       <c r="S364" s="22"/>
       <c r="T364" s="35"/>
       <c r="U364" s="39" t="s">
-        <v>412</v>
+        <v>122</v>
       </c>
       <c r="V364" s="2" t="s">
         <v>404</v>
@@ -31991,7 +32033,7 @@
         <v>409</v>
       </c>
       <c r="AB364" s="2" t="s">
-        <v>1169</v>
+        <v>732</v>
       </c>
       <c r="AC364" s="2"/>
       <c r="AD364" s="2"/>
@@ -32002,28 +32044,32 @@
         <v>325</v>
       </c>
       <c r="AG364" s="4"/>
-      <c r="AH364" s="2"/>
-      <c r="AI364" s="2"/>
+      <c r="AH364" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI364" s="2" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="365" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A365" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B365" s="2"/>
       <c r="C365" s="44"/>
       <c r="D365" s="2"/>
       <c r="E365" s="4"/>
       <c r="F365" s="37" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="G365" s="28">
-        <v>46.177199999999999</v>
+        <v>47.138100000000001</v>
       </c>
       <c r="H365" s="28">
-        <v>90.535600000000002</v>
+        <v>85.597499999999997</v>
       </c>
       <c r="I365" s="2">
-        <v>1071.0999999999999</v>
+        <v>2914</v>
       </c>
       <c r="J365" s="26">
         <v>12</v>
@@ -32033,9 +32079,9 @@
       </c>
       <c r="L365" s="2"/>
       <c r="M365" s="14" t="s">
-        <v>1171</v>
-      </c>
-      <c r="N365" s="2"/>
+        <v>1168</v>
+      </c>
+      <c r="N365" s="23"/>
       <c r="O365" s="31"/>
       <c r="P365" s="31"/>
       <c r="Q365" s="31"/>
@@ -32043,7 +32089,7 @@
       <c r="S365" s="22"/>
       <c r="T365" s="35"/>
       <c r="U365" s="39" t="s">
-        <v>122</v>
+        <v>412</v>
       </c>
       <c r="V365" s="2" t="s">
         <v>404</v>
@@ -32062,7 +32108,7 @@
         <v>409</v>
       </c>
       <c r="AB365" s="2" t="s">
-        <v>410</v>
+        <v>1169</v>
       </c>
       <c r="AC365" s="2"/>
       <c r="AD365" s="2"/>
@@ -32073,36 +32119,28 @@
         <v>325</v>
       </c>
       <c r="AG365" s="4"/>
-      <c r="AH365" s="2" t="s">
-        <v>122</v>
-      </c>
+      <c r="AH365" s="2"/>
       <c r="AI365" s="2"/>
     </row>
     <row r="366" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A366" s="2">
-        <v>364</v>
-      </c>
-      <c r="B366" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C366" s="44">
-        <v>51087</v>
-      </c>
-      <c r="D366" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E366" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F366" s="37"/>
+        <v>363</v>
+      </c>
+      <c r="B366" s="2"/>
+      <c r="C366" s="44"/>
+      <c r="D366" s="2"/>
+      <c r="E366" s="4"/>
+      <c r="F366" s="37" t="s">
+        <v>1170</v>
+      </c>
       <c r="G366" s="28">
-        <v>47.02</v>
+        <v>46.177199999999999</v>
       </c>
       <c r="H366" s="28">
-        <v>89.5</v>
+        <v>90.535600000000002</v>
       </c>
       <c r="I366" s="2">
-        <v>860.4</v>
+        <v>1071.0999999999999</v>
       </c>
       <c r="J366" s="26">
         <v>12</v>
@@ -32112,7 +32150,7 @@
       </c>
       <c r="L366" s="2"/>
       <c r="M366" s="14" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="N366" s="2"/>
       <c r="O366" s="31"/>
@@ -32122,7 +32160,7 @@
       <c r="S366" s="22"/>
       <c r="T366" s="35"/>
       <c r="U366" s="39" t="s">
-        <v>1174</v>
+        <v>122</v>
       </c>
       <c r="V366" s="2" t="s">
         <v>404</v>
@@ -32140,7 +32178,9 @@
       <c r="AA366" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="AB366" s="2"/>
+      <c r="AB366" s="2" t="s">
+        <v>410</v>
+      </c>
       <c r="AC366" s="2"/>
       <c r="AD366" s="2"/>
       <c r="AE366" s="2" t="s">
@@ -32157,18 +32197,30 @@
     </row>
     <row r="367" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A367" s="2">
-        <v>365</v>
-      </c>
-      <c r="B367" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="C367" s="44">
-        <v>51058</v>
-      </c>
-      <c r="D367" s="2"/>
-      <c r="E367" s="4"/>
+        <v>51087</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E367" s="4">
+        <v>99999</v>
+      </c>
       <c r="F367" s="37"/>
-      <c r="G367" s="28"/>
-      <c r="H367" s="28"/>
-      <c r="I367" s="2"/>
+      <c r="G367" s="28">
+        <v>47.02</v>
+      </c>
+      <c r="H367" s="28">
+        <v>89.5</v>
+      </c>
+      <c r="I367" s="2">
+        <v>860.4</v>
+      </c>
       <c r="J367" s="26">
         <v>12</v>
       </c>
@@ -32177,7 +32229,7 @@
       </c>
       <c r="L367" s="2"/>
       <c r="M367" s="14" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="N367" s="2"/>
       <c r="O367" s="31"/>
@@ -32187,7 +32239,7 @@
       <c r="S367" s="22"/>
       <c r="T367" s="35"/>
       <c r="U367" s="39" t="s">
-        <v>1163</v>
+        <v>1174</v>
       </c>
       <c r="V367" s="2" t="s">
         <v>404</v>
@@ -32215,31 +32267,25 @@
         <v>325</v>
       </c>
       <c r="AG367" s="4"/>
-      <c r="AH367" s="2"/>
+      <c r="AH367" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="AI367" s="2"/>
     </row>
     <row r="368" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A368" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B368" s="2"/>
       <c r="C368" s="44">
-        <v>51060</v>
+        <v>51058</v>
       </c>
       <c r="D368" s="2"/>
-      <c r="E368" s="4">
-        <v>99999</v>
-      </c>
+      <c r="E368" s="4"/>
       <c r="F368" s="37"/>
-      <c r="G368" s="28">
-        <v>47.7</v>
-      </c>
-      <c r="H368" s="28">
-        <v>86.87</v>
-      </c>
-      <c r="I368" s="2">
-        <v>473.9</v>
-      </c>
+      <c r="G368" s="28"/>
+      <c r="H368" s="28"/>
+      <c r="I368" s="2"/>
       <c r="J368" s="26">
         <v>12</v>
       </c>
@@ -32248,7 +32294,7 @@
       </c>
       <c r="L368" s="2"/>
       <c r="M368" s="14" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="N368" s="2"/>
       <c r="O368" s="31"/>
@@ -32258,7 +32304,7 @@
       <c r="S368" s="22"/>
       <c r="T368" s="35"/>
       <c r="U368" s="39" t="s">
-        <v>1177</v>
+        <v>1163</v>
       </c>
       <c r="V368" s="2" t="s">
         <v>404</v>
@@ -32286,30 +32332,30 @@
         <v>325</v>
       </c>
       <c r="AG368" s="4"/>
-      <c r="AH368" s="2" t="s">
-        <v>1177</v>
-      </c>
+      <c r="AH368" s="2"/>
       <c r="AI368" s="2"/>
     </row>
     <row r="369" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A369" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B369" s="2"/>
-      <c r="C369" s="44"/>
+      <c r="C369" s="44">
+        <v>51060</v>
+      </c>
       <c r="D369" s="2"/>
-      <c r="E369" s="4"/>
-      <c r="F369" s="37" t="s">
-        <v>1178</v>
-      </c>
+      <c r="E369" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F369" s="37"/>
       <c r="G369" s="28">
-        <v>42.716000000000001</v>
+        <v>47.7</v>
       </c>
       <c r="H369" s="28">
-        <v>84.272000000000006</v>
+        <v>86.87</v>
       </c>
       <c r="I369" s="2">
-        <v>2404.3000000000002</v>
+        <v>473.9</v>
       </c>
       <c r="J369" s="26">
         <v>12</v>
@@ -32319,7 +32365,7 @@
       </c>
       <c r="L369" s="2"/>
       <c r="M369" s="14" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="N369" s="2"/>
       <c r="O369" s="31"/>
@@ -32329,7 +32375,7 @@
       <c r="S369" s="22"/>
       <c r="T369" s="35"/>
       <c r="U369" s="39" t="s">
-        <v>683</v>
+        <v>1177</v>
       </c>
       <c r="V369" s="2" t="s">
         <v>404</v>
@@ -32345,11 +32391,9 @@
       </c>
       <c r="Z369" s="4"/>
       <c r="AA369" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="AB369" s="2" t="s">
-        <v>630</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="AB369" s="2"/>
       <c r="AC369" s="2"/>
       <c r="AD369" s="2"/>
       <c r="AE369" s="2" t="s">
@@ -32360,31 +32404,29 @@
       </c>
       <c r="AG369" s="4"/>
       <c r="AH369" s="2" t="s">
-        <v>403</v>
+        <v>1177</v>
       </c>
       <c r="AI369" s="2"/>
     </row>
     <row r="370" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A370" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B370" s="2"/>
-      <c r="C370" s="44">
-        <v>51337</v>
-      </c>
+      <c r="C370" s="44"/>
       <c r="D370" s="2"/>
-      <c r="E370" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F370" s="37"/>
+      <c r="E370" s="4"/>
+      <c r="F370" s="37" t="s">
+        <v>1178</v>
+      </c>
       <c r="G370" s="28">
-        <v>44.602800000000002</v>
+        <v>42.716000000000001</v>
       </c>
       <c r="H370" s="28">
-        <v>81.387799999999999</v>
+        <v>84.272000000000006</v>
       </c>
       <c r="I370" s="2">
-        <v>2100</v>
+        <v>2404.3000000000002</v>
       </c>
       <c r="J370" s="26">
         <v>12</v>
@@ -32392,9 +32434,9 @@
       <c r="K370" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="L370" s="3"/>
+      <c r="L370" s="2"/>
       <c r="M370" s="14" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="N370" s="2"/>
       <c r="O370" s="31"/>
@@ -32404,7 +32446,7 @@
       <c r="S370" s="22"/>
       <c r="T370" s="35"/>
       <c r="U370" s="39" t="s">
-        <v>403</v>
+        <v>683</v>
       </c>
       <c r="V370" s="2" t="s">
         <v>404</v>
@@ -32420,10 +32462,10 @@
       </c>
       <c r="Z370" s="4"/>
       <c r="AA370" s="2" t="s">
-        <v>1181</v>
+        <v>629</v>
       </c>
       <c r="AB370" s="2" t="s">
-        <v>1182</v>
+        <v>630</v>
       </c>
       <c r="AC370" s="2"/>
       <c r="AD370" s="2"/>
@@ -32437,17 +32479,15 @@
       <c r="AH370" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="AI370" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="AI370" s="2"/>
     </row>
     <row r="371" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A371" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B371" s="2"/>
-      <c r="C371" s="44" t="s">
-        <v>1183</v>
+      <c r="C371" s="44">
+        <v>51337</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" s="4">
@@ -32455,13 +32495,13 @@
       </c>
       <c r="F371" s="37"/>
       <c r="G371" s="28">
-        <v>40.5122</v>
+        <v>44.602800000000002</v>
       </c>
       <c r="H371" s="28">
-        <v>75.391400000000004</v>
+        <v>81.387799999999999</v>
       </c>
       <c r="I371" s="2">
-        <v>3470.2</v>
+        <v>2100</v>
       </c>
       <c r="J371" s="26">
         <v>12</v>
@@ -32469,9 +32509,9 @@
       <c r="K371" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="L371" s="2"/>
+      <c r="L371" s="3"/>
       <c r="M371" s="14" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="N371" s="2"/>
       <c r="O371" s="31"/>
@@ -32497,10 +32537,10 @@
       </c>
       <c r="Z371" s="4"/>
       <c r="AA371" s="2" t="s">
-        <v>662</v>
+        <v>1181</v>
       </c>
       <c r="AB371" s="2" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="AC371" s="2"/>
       <c r="AD371" s="2"/>
@@ -32514,15 +32554,17 @@
       <c r="AH371" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="AI371" s="2"/>
+      <c r="AI371" s="2" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="372" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A372" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B372" s="2"/>
       <c r="C372" s="44" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" s="4">
@@ -32530,13 +32572,13 @@
       </c>
       <c r="F372" s="37"/>
       <c r="G372" s="28">
-        <v>42.890799999999999</v>
+        <v>40.5122</v>
       </c>
       <c r="H372" s="28">
-        <v>89.305599999999998</v>
+        <v>75.391400000000004</v>
       </c>
       <c r="I372" s="2">
-        <v>-48.8</v>
+        <v>3470.2</v>
       </c>
       <c r="J372" s="26">
         <v>12</v>
@@ -32546,7 +32588,7 @@
       </c>
       <c r="L372" s="2"/>
       <c r="M372" s="14" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="N372" s="2"/>
       <c r="O372" s="31"/>
@@ -32556,7 +32598,7 @@
       <c r="S372" s="22"/>
       <c r="T372" s="35"/>
       <c r="U372" s="39" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="V372" s="2" t="s">
         <v>404</v>
@@ -32572,10 +32614,10 @@
       </c>
       <c r="Z372" s="4"/>
       <c r="AA372" s="2" t="s">
-        <v>419</v>
+        <v>662</v>
       </c>
       <c r="AB372" s="2" t="s">
-        <v>420</v>
+        <v>1185</v>
       </c>
       <c r="AC372" s="2"/>
       <c r="AD372" s="2"/>
@@ -32586,28 +32628,32 @@
         <v>325</v>
       </c>
       <c r="AG372" s="4"/>
-      <c r="AH372" s="2"/>
+      <c r="AH372" s="2" t="s">
+        <v>403</v>
+      </c>
       <c r="AI372" s="2"/>
     </row>
     <row r="373" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A373" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B373" s="2"/>
-      <c r="C373" s="44"/>
+      <c r="C373" s="44" t="s">
+        <v>1186</v>
+      </c>
       <c r="D373" s="2"/>
-      <c r="E373" s="4"/>
-      <c r="F373" s="37" t="s">
-        <v>1188</v>
-      </c>
+      <c r="E373" s="4">
+        <v>99999</v>
+      </c>
+      <c r="F373" s="37"/>
       <c r="G373" s="28">
-        <v>42.685600000000001</v>
+        <v>42.890799999999999</v>
       </c>
       <c r="H373" s="28">
-        <v>89.065600000000003</v>
+        <v>89.305599999999998</v>
       </c>
       <c r="I373" s="2">
-        <v>-106.4</v>
+        <v>-48.8</v>
       </c>
       <c r="J373" s="26">
         <v>12</v>
@@ -32617,7 +32663,7 @@
       </c>
       <c r="L373" s="2"/>
       <c r="M373" s="14" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="N373" s="2"/>
       <c r="O373" s="31"/>
@@ -32662,23 +32708,23 @@
     </row>
     <row r="374" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A374" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B374" s="2"/>
       <c r="C374" s="44"/>
       <c r="D374" s="2"/>
       <c r="E374" s="4"/>
       <c r="F374" s="37" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="G374" s="28">
-        <v>42.904400000000003</v>
+        <v>42.685600000000001</v>
       </c>
       <c r="H374" s="28">
-        <v>89.4422</v>
+        <v>89.065600000000003</v>
       </c>
       <c r="I374" s="2">
-        <v>-52</v>
+        <v>-106.4</v>
       </c>
       <c r="J374" s="26">
         <v>12</v>
@@ -32688,7 +32734,7 @@
       </c>
       <c r="L374" s="2"/>
       <c r="M374" s="14" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="N374" s="2"/>
       <c r="O374" s="31"/>
@@ -32733,25 +32779,23 @@
     </row>
     <row r="375" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A375" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B375" s="2"/>
-      <c r="C375" s="44" t="s">
-        <v>1192</v>
-      </c>
+      <c r="C375" s="44"/>
       <c r="D375" s="2"/>
-      <c r="E375" s="4">
-        <v>99999</v>
-      </c>
-      <c r="F375" s="37"/>
+      <c r="E375" s="4"/>
+      <c r="F375" s="37" t="s">
+        <v>1190</v>
+      </c>
       <c r="G375" s="28">
-        <v>42.7669</v>
+        <v>42.904400000000003</v>
       </c>
       <c r="H375" s="28">
-        <v>88.600800000000007</v>
+        <v>89.4422</v>
       </c>
       <c r="I375" s="2">
-        <v>43.9</v>
+        <v>-52</v>
       </c>
       <c r="J375" s="26">
         <v>12</v>
@@ -32761,7 +32805,7 @@
       </c>
       <c r="L375" s="2"/>
       <c r="M375" s="14" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="N375" s="2"/>
       <c r="O375" s="31"/>
@@ -32790,7 +32834,7 @@
         <v>419</v>
       </c>
       <c r="AB375" s="2" t="s">
-        <v>1194</v>
+        <v>420</v>
       </c>
       <c r="AC375" s="2"/>
       <c r="AD375" s="2"/>
@@ -32806,11 +32850,11 @@
     </row>
     <row r="376" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A376" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B376" s="2"/>
       <c r="C376" s="44" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" s="4">
@@ -32818,13 +32862,13 @@
       </c>
       <c r="F376" s="37"/>
       <c r="G376" s="28">
-        <v>43.113100000000003</v>
+        <v>42.7669</v>
       </c>
       <c r="H376" s="28">
-        <v>86.843100000000007</v>
+        <v>88.600800000000007</v>
       </c>
       <c r="I376" s="2">
-        <v>3540.5</v>
+        <v>43.9</v>
       </c>
       <c r="J376" s="26">
         <v>12</v>
@@ -32834,7 +32878,7 @@
       </c>
       <c r="L376" s="2"/>
       <c r="M376" s="14" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="N376" s="2"/>
       <c r="O376" s="31"/>
@@ -32844,7 +32888,7 @@
       <c r="S376" s="22"/>
       <c r="T376" s="35"/>
       <c r="U376" s="39" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="V376" s="2" t="s">
         <v>404</v>
@@ -32860,10 +32904,10 @@
       </c>
       <c r="Z376" s="4"/>
       <c r="AA376" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AB376" s="2" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="AC376" s="2"/>
       <c r="AD376" s="2"/>
@@ -32874,18 +32918,16 @@
         <v>325</v>
       </c>
       <c r="AG376" s="4"/>
-      <c r="AH376" s="2" t="s">
-        <v>403</v>
-      </c>
+      <c r="AH376" s="2"/>
       <c r="AI376" s="2"/>
     </row>
     <row r="377" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A377" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B377" s="2"/>
       <c r="C377" s="44" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" s="4">
@@ -32893,23 +32935,23 @@
       </c>
       <c r="F377" s="37"/>
       <c r="G377" s="28">
-        <v>23.2286</v>
+        <v>43.113100000000003</v>
       </c>
       <c r="H377" s="28">
-        <v>102.8214</v>
+        <v>86.843100000000007</v>
       </c>
       <c r="I377" s="2">
-        <v>312.3</v>
+        <v>3540.5</v>
       </c>
       <c r="J377" s="26">
         <v>12</v>
       </c>
-      <c r="K377" s="46" t="s">
+      <c r="K377" s="30" t="s">
         <v>319</v>
       </c>
       <c r="L377" s="2"/>
       <c r="M377" s="14" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="N377" s="2"/>
       <c r="O377" s="31"/>
@@ -32919,10 +32961,10 @@
       <c r="S377" s="22"/>
       <c r="T377" s="35"/>
       <c r="U377" s="39" t="s">
-        <v>547</v>
+        <v>403</v>
       </c>
       <c r="V377" s="2" t="s">
-        <v>547</v>
+        <v>404</v>
       </c>
       <c r="W377" s="4" t="s">
         <v>40</v>
@@ -32935,10 +32977,10 @@
       </c>
       <c r="Z377" s="4"/>
       <c r="AA377" s="2" t="s">
-        <v>1200</v>
+        <v>424</v>
       </c>
       <c r="AB377" s="2" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="AC377" s="2"/>
       <c r="AD377" s="2"/>
@@ -32949,16 +32991,18 @@
         <v>325</v>
       </c>
       <c r="AG377" s="4"/>
-      <c r="AH377" s="2"/>
+      <c r="AH377" s="2" t="s">
+        <v>403</v>
+      </c>
       <c r="AI377" s="2"/>
     </row>
     <row r="378" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A378" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B378" s="2"/>
       <c r="C378" s="44" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" s="4">
@@ -32966,23 +33010,23 @@
       </c>
       <c r="F378" s="37"/>
       <c r="G378" s="28">
-        <v>26.918099999999999</v>
+        <v>23.2286</v>
       </c>
       <c r="H378" s="28">
-        <v>102.9267</v>
+        <v>102.8214</v>
       </c>
       <c r="I378" s="2">
-        <v>893.9</v>
+        <v>312.3</v>
       </c>
       <c r="J378" s="26">
         <v>12</v>
       </c>
-      <c r="K378" s="30" t="s">
+      <c r="K378" s="46" t="s">
         <v>319</v>
       </c>
       <c r="L378" s="2"/>
       <c r="M378" s="14" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="N378" s="2"/>
       <c r="O378" s="31"/>
@@ -33008,10 +33052,10 @@
       </c>
       <c r="Z378" s="4"/>
       <c r="AA378" s="2" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="AB378" s="2" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="AC378" s="2"/>
       <c r="AD378" s="2"/>
@@ -33026,19 +33070,37 @@
       <c r="AI378" s="2"/>
     </row>
     <row r="379" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A379" s="13"/>
+      <c r="A379" s="2">
+        <v>376</v>
+      </c>
       <c r="B379" s="2"/>
-      <c r="C379" s="44"/>
+      <c r="C379" s="44" t="s">
+        <v>1202</v>
+      </c>
       <c r="D379" s="2"/>
-      <c r="E379" s="4"/>
+      <c r="E379" s="4">
+        <v>99999</v>
+      </c>
       <c r="F379" s="37"/>
-      <c r="G379" s="28"/>
-      <c r="H379" s="28"/>
-      <c r="I379" s="2"/>
-      <c r="J379" s="26"/>
-      <c r="K379" s="30"/>
+      <c r="G379" s="28">
+        <v>26.918099999999999</v>
+      </c>
+      <c r="H379" s="28">
+        <v>102.9267</v>
+      </c>
+      <c r="I379" s="2">
+        <v>893.9</v>
+      </c>
+      <c r="J379" s="26">
+        <v>12</v>
+      </c>
+      <c r="K379" s="30" t="s">
+        <v>319</v>
+      </c>
       <c r="L379" s="2"/>
-      <c r="M379" s="14"/>
+      <c r="M379" s="14" t="s">
+        <v>1203</v>
+      </c>
       <c r="N379" s="2"/>
       <c r="O379" s="31"/>
       <c r="P379" s="31"/>
@@ -33046,18 +33108,36 @@
       <c r="R379" s="49"/>
       <c r="S379" s="22"/>
       <c r="T379" s="35"/>
-      <c r="U379" s="39"/>
-      <c r="V379" s="2"/>
-      <c r="W379" s="4"/>
-      <c r="X379" s="4"/>
-      <c r="Y379" s="4"/>
+      <c r="U379" s="39" t="s">
+        <v>547</v>
+      </c>
+      <c r="V379" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="W379" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X379" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y379" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="Z379" s="4"/>
-      <c r="AA379" s="2"/>
-      <c r="AB379" s="2"/>
+      <c r="AA379" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="AB379" s="2" t="s">
+        <v>1205</v>
+      </c>
       <c r="AC379" s="2"/>
       <c r="AD379" s="2"/>
-      <c r="AE379" s="2"/>
-      <c r="AF379" s="4"/>
+      <c r="AE379" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="AF379" s="4" t="s">
+        <v>325</v>
+      </c>
       <c r="AG379" s="4"/>
       <c r="AH379" s="2"/>
       <c r="AI379" s="2"/>
@@ -34553,7 +34633,7 @@
       <c r="H420" s="28"/>
       <c r="I420" s="2"/>
       <c r="J420" s="26"/>
-      <c r="K420" s="4"/>
+      <c r="K420" s="30"/>
       <c r="L420" s="2"/>
       <c r="M420" s="14"/>
       <c r="N420" s="2"/>
@@ -34728,9 +34808,7 @@
       <c r="AI424" s="2"/>
     </row>
     <row r="425" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A425" s="12">
-        <v>999</v>
-      </c>
+      <c r="A425" s="13"/>
       <c r="B425" s="2"/>
       <c r="C425" s="44"/>
       <c r="D425" s="2"/>
@@ -34744,9 +34822,7 @@
       <c r="L425" s="2"/>
       <c r="M425" s="14"/>
       <c r="N425" s="2"/>
-      <c r="O425" s="31" t="s">
-        <v>1206</v>
-      </c>
+      <c r="O425" s="31"/>
       <c r="P425" s="31"/>
       <c r="Q425" s="31"/>
       <c r="R425" s="49"/>
@@ -34768,19 +34844,60 @@
       <c r="AH425" s="2"/>
       <c r="AI425" s="2"/>
     </row>
+    <row r="426" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A426" s="12">
+        <v>999</v>
+      </c>
+      <c r="B426" s="2"/>
+      <c r="C426" s="44"/>
+      <c r="D426" s="2"/>
+      <c r="E426" s="4"/>
+      <c r="F426" s="37"/>
+      <c r="G426" s="28"/>
+      <c r="H426" s="28"/>
+      <c r="I426" s="2"/>
+      <c r="J426" s="26"/>
+      <c r="K426" s="4"/>
+      <c r="L426" s="2"/>
+      <c r="M426" s="14"/>
+      <c r="N426" s="2"/>
+      <c r="O426" s="31" t="s">
+        <v>1206</v>
+      </c>
+      <c r="P426" s="31"/>
+      <c r="Q426" s="31"/>
+      <c r="R426" s="49"/>
+      <c r="S426" s="22"/>
+      <c r="T426" s="35"/>
+      <c r="U426" s="39"/>
+      <c r="V426" s="2"/>
+      <c r="W426" s="4"/>
+      <c r="X426" s="4"/>
+      <c r="Y426" s="4"/>
+      <c r="Z426" s="4"/>
+      <c r="AA426" s="2"/>
+      <c r="AB426" s="2"/>
+      <c r="AC426" s="2"/>
+      <c r="AD426" s="2"/>
+      <c r="AE426" s="2"/>
+      <c r="AF426" s="4"/>
+      <c r="AG426" s="4"/>
+      <c r="AH426" s="2"/>
+      <c r="AI426" s="2"/>
+    </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="O2:Q425" name="区域1"/>
+    <protectedRange sqref="O2:Q426" name="区域1"/>
   </protectedRanges>
-  <autoFilter ref="A1:AI425" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AI426" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:N425 R2:AI425">
+  <conditionalFormatting sqref="A2:N426 R2:AI426">
     <cfRule type="expression" dxfId="1" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:Q425">
+  <conditionalFormatting sqref="O2:Q426">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -841,8 +841,8 @@
     <col width="18.59765625" customWidth="1" style="7" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="4" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="7" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="4" min="34" max="758"/>
-    <col width="12.59765625" customWidth="1" style="4" min="759" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="4" min="34" max="760"/>
+    <col width="12.59765625" customWidth="1" style="4" min="761" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="10">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="O2" s="29" t="n">
-        <v>0.9</v>
+        <v>-2.4</v>
       </c>
       <c r="P2" s="29" t="n">
-        <v>15.4</v>
+        <v>13.8</v>
       </c>
       <c r="Q2" s="29" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="R2" s="46" t="n"/>
       <c r="S2" s="21" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="O3" s="29" t="n">
-        <v>0.8</v>
+        <v>-1.5</v>
       </c>
       <c r="P3" s="29" t="n">
-        <v>13.7</v>
+        <v>11.9</v>
       </c>
       <c r="Q3" s="29" t="n"/>
       <c r="R3" s="46" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="O4" s="29" t="n">
-        <v>-2.7</v>
+        <v>-3.2</v>
       </c>
       <c r="P4" s="29" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="Q4" s="29" t="n"/>
       <c r="R4" s="46" t="inlineStr">
@@ -1392,12 +1392,8 @@
         </is>
       </c>
       <c r="N5" s="52" t="n"/>
-      <c r="O5" s="29" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="P5" s="29" t="n">
-        <v>13</v>
-      </c>
+      <c r="O5" s="29" t="n"/>
+      <c r="P5" s="29" t="n"/>
       <c r="Q5" s="29" t="n"/>
       <c r="R5" s="46" t="n"/>
       <c r="S5" s="21" t="n"/>
@@ -1500,13 +1496,13 @@
         </is>
       </c>
       <c r="O6" s="29" t="n">
-        <v>-2.2</v>
+        <v>-6.2</v>
       </c>
       <c r="P6" s="29" t="n">
-        <v>13.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q6" s="29" t="n">
-        <v>4.49</v>
+        <v>0.98</v>
       </c>
       <c r="R6" s="48" t="inlineStr">
         <is>
@@ -1611,10 +1607,10 @@
         </is>
       </c>
       <c r="O7" s="29" t="n">
-        <v>-1.5</v>
+        <v>-3</v>
       </c>
       <c r="P7" s="29" t="n">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
       <c r="Q7" s="29" t="n"/>
       <c r="R7" s="46" t="n"/>
@@ -1720,13 +1716,13 @@
       </c>
       <c r="N8" s="52" t="n"/>
       <c r="O8" s="29" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>8.34</v>
+        <v>6.91</v>
       </c>
       <c r="R8" s="46" t="n"/>
       <c r="S8" s="21" t="inlineStr">
@@ -1833,13 +1829,13 @@
       </c>
       <c r="N9" s="52" t="n"/>
       <c r="O9" s="29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>6.91</v>
+        <v>7.81</v>
       </c>
       <c r="R9" s="46" t="n"/>
       <c r="S9" s="21" t="inlineStr">
@@ -1954,13 +1950,13 @@
         </is>
       </c>
       <c r="O10" s="29" t="n">
-        <v>-5.2</v>
+        <v>-3.7</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>12.2</v>
+        <v>9.9</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>3.94</v>
+        <v>4.54</v>
       </c>
       <c r="R10" s="46" t="n"/>
       <c r="S10" s="21" t="inlineStr">
@@ -2071,13 +2067,13 @@
         </is>
       </c>
       <c r="O11" s="29" t="n">
-        <v>-1.8</v>
+        <v>-5.5</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>9.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>5.33</v>
+        <v>1.6</v>
       </c>
       <c r="R11" s="46" t="inlineStr">
         <is>
@@ -2188,13 +2184,13 @@
       </c>
       <c r="N12" s="52" t="n"/>
       <c r="O12" s="29" t="n">
-        <v>-1.4</v>
+        <v>0.6</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>14.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>6.03</v>
+        <v>3.21</v>
       </c>
       <c r="R12" s="46" t="inlineStr">
         <is>
@@ -2309,13 +2305,13 @@
         </is>
       </c>
       <c r="O13" s="29" t="n">
-        <v>-1.8</v>
+        <v>-4</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>11.1</v>
+        <v>6.4</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>4.41</v>
+        <v>0.73</v>
       </c>
       <c r="R13" s="46" t="inlineStr">
         <is>
@@ -2426,13 +2422,13 @@
       </c>
       <c r="N14" s="52" t="n"/>
       <c r="O14" s="29" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="P14" s="29" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="Q14" s="29" t="n">
-        <v>10.34</v>
+        <v>10.3</v>
       </c>
       <c r="R14" s="46" t="n"/>
       <c r="S14" s="21" t="inlineStr">
@@ -2547,13 +2543,13 @@
       </c>
       <c r="N15" s="52" t="n"/>
       <c r="O15" s="29" t="n">
-        <v>-6.1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="29" t="n">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="29" t="n">
-        <v>5.25</v>
+        <v>6.34</v>
       </c>
       <c r="R15" s="46" t="n"/>
       <c r="S15" s="21" t="inlineStr">
@@ -2843,7 +2839,9 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O18" s="29" t="n"/>
+      <c r="O18" s="29" t="n">
+        <v>-7.9</v>
+      </c>
       <c r="P18" s="29" t="n"/>
       <c r="Q18" s="29" t="n"/>
       <c r="R18" s="46" t="n"/>
@@ -10186,13 +10184,13 @@
         </is>
       </c>
       <c r="O98" s="29" t="n">
-        <v>-11.7</v>
+        <v>-13.6</v>
       </c>
       <c r="P98" s="29" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q98" s="29" t="n">
-        <v>-4.41</v>
+        <v>-4.48</v>
       </c>
       <c r="R98" s="46" t="inlineStr">
         <is>
@@ -10616,13 +10614,13 @@
         </is>
       </c>
       <c r="O102" s="29" t="n">
-        <v>-4.6</v>
+        <v>-2.3</v>
       </c>
       <c r="P102" s="29" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="Q102" s="29" t="n">
-        <v>-0.99</v>
+        <v>1.61</v>
       </c>
       <c r="R102" s="46" t="n"/>
       <c r="S102" s="21" t="inlineStr">
@@ -10738,13 +10736,13 @@
         </is>
       </c>
       <c r="O103" s="29" t="n">
-        <v>-5</v>
+        <v>0.4</v>
       </c>
       <c r="P103" s="29" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q103" s="29" t="n">
-        <v>-0.64</v>
+        <v>1.55</v>
       </c>
       <c r="R103" s="46" t="n"/>
       <c r="S103" s="21" t="inlineStr">
@@ -10958,13 +10956,13 @@
         </is>
       </c>
       <c r="O105" s="29" t="n">
-        <v>2.2</v>
+        <v>-4</v>
       </c>
       <c r="P105" s="29" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="Q105" s="29" t="n">
-        <v>6.96</v>
+        <v>0.45</v>
       </c>
       <c r="R105" s="46" t="n"/>
       <c r="S105" s="21" t="inlineStr">
@@ -11178,13 +11176,13 @@
       </c>
       <c r="N107" s="52" t="n"/>
       <c r="O107" s="29" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="P107" s="29" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q107" s="29" t="n">
-        <v>6.19</v>
+        <v>6.01</v>
       </c>
       <c r="R107" s="46" t="n"/>
       <c r="S107" s="21" t="inlineStr">
@@ -11406,13 +11404,13 @@
       </c>
       <c r="N109" s="52" t="n"/>
       <c r="O109" s="29" t="n">
-        <v>-3.4</v>
+        <v>-7.9</v>
       </c>
       <c r="P109" s="29" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="Q109" s="29" t="n">
-        <v>1.4</v>
+        <v>-0.63</v>
       </c>
       <c r="R109" s="46" t="inlineStr">
         <is>
@@ -11931,13 +11929,13 @@
       </c>
       <c r="N114" s="52" t="n"/>
       <c r="O114" s="29" t="n">
-        <v>-5.4</v>
+        <v>-4.3</v>
       </c>
       <c r="P114" s="29" t="n">
-        <v>14.2</v>
+        <v>19.5</v>
       </c>
       <c r="Q114" s="29" t="n">
-        <v>4.89</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="R114" s="46" t="n"/>
       <c r="S114" s="21" t="inlineStr">
@@ -12044,13 +12042,13 @@
       </c>
       <c r="N115" s="52" t="n"/>
       <c r="O115" s="29" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P115" s="29" t="n">
-        <v>24.2</v>
+        <v>27</v>
       </c>
       <c r="Q115" s="29" t="n">
-        <v>13.81</v>
+        <v>17.4</v>
       </c>
       <c r="R115" s="46" t="n"/>
       <c r="S115" s="21" t="inlineStr">
@@ -12164,15 +12162,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O116" s="29" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="P116" s="29" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Q116" s="29" t="n">
-        <v>9.93</v>
-      </c>
+      <c r="O116" s="29" t="n"/>
+      <c r="P116" s="29" t="n"/>
+      <c r="Q116" s="29" t="n"/>
       <c r="R116" s="46" t="inlineStr">
         <is>
           <t>2001-01-13</t>
@@ -12286,13 +12278,13 @@
       </c>
       <c r="N117" s="52" t="n"/>
       <c r="O117" s="29" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="P117" s="29" t="n">
-        <v>21.7</v>
+        <v>23.1</v>
       </c>
       <c r="Q117" s="29" t="n">
-        <v>13.72</v>
+        <v>15.7</v>
       </c>
       <c r="R117" s="46" t="n"/>
       <c r="S117" s="21" t="inlineStr">
@@ -12411,13 +12403,13 @@
       </c>
       <c r="N118" s="52" t="n"/>
       <c r="O118" s="29" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P118" s="29" t="n">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="Q118" s="29" t="n">
-        <v>10.09</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="R118" s="46" t="n"/>
       <c r="S118" s="21" t="inlineStr">
@@ -12531,15 +12523,9 @@
         </is>
       </c>
       <c r="N119" s="52" t="n"/>
-      <c r="O119" s="29" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="P119" s="29" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q119" s="29" t="n">
-        <v>3.19</v>
-      </c>
+      <c r="O119" s="29" t="n"/>
+      <c r="P119" s="29" t="n"/>
+      <c r="Q119" s="29" t="n"/>
       <c r="R119" s="46" t="n"/>
       <c r="S119" s="21" t="inlineStr">
         <is>
@@ -12756,13 +12742,13 @@
       </c>
       <c r="N121" s="52" t="n"/>
       <c r="O121" s="29" t="n">
-        <v>-10</v>
+        <v>-13.1</v>
       </c>
       <c r="P121" s="29" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="Q121" s="29" t="n">
-        <v>-3.35</v>
+        <v>-3.08</v>
       </c>
       <c r="R121" s="46" t="n"/>
       <c r="S121" s="21" t="inlineStr">
@@ -12869,13 +12855,13 @@
       </c>
       <c r="N122" s="52" t="n"/>
       <c r="O122" s="29" t="n">
-        <v>-9.199999999999999</v>
+        <v>-12.1</v>
       </c>
       <c r="P122" s="29" t="n">
-        <v>5.1</v>
+        <v>9.5</v>
       </c>
       <c r="Q122" s="29" t="n">
-        <v>-2.71</v>
+        <v>-2.63</v>
       </c>
       <c r="R122" s="46" t="n"/>
       <c r="S122" s="21" t="inlineStr">
@@ -12990,13 +12976,13 @@
       </c>
       <c r="N123" s="52" t="n"/>
       <c r="O123" s="29" t="n">
-        <v>-11.4</v>
+        <v>-14.2</v>
       </c>
       <c r="P123" s="29" t="n">
-        <v>3.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q123" s="29" t="n">
-        <v>-5.31</v>
+        <v>-4.28</v>
       </c>
       <c r="R123" s="46" t="n"/>
       <c r="S123" s="21" t="inlineStr">
@@ -13107,13 +13093,13 @@
       </c>
       <c r="N124" s="52" t="n"/>
       <c r="O124" s="29" t="n">
-        <v>-11.1</v>
+        <v>-13.2</v>
       </c>
       <c r="P124" s="29" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q124" s="29" t="n">
-        <v>-4.35</v>
+        <v>-4</v>
       </c>
       <c r="R124" s="46" t="n"/>
       <c r="S124" s="21" t="n"/>
@@ -13331,13 +13317,13 @@
       </c>
       <c r="N126" s="52" t="n"/>
       <c r="O126" s="29" t="n">
-        <v>-7.3</v>
+        <v>-3.6</v>
       </c>
       <c r="P126" s="29" t="n">
-        <v>6.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q126" s="29" t="n">
-        <v>-0.76</v>
+        <v>2.74</v>
       </c>
       <c r="R126" s="46" t="n"/>
       <c r="S126" s="21" t="inlineStr">
@@ -14069,15 +14055,9 @@
         </is>
       </c>
       <c r="N133" s="52" t="n"/>
-      <c r="O133" s="29" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="P133" s="29" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Q133" s="29" t="n">
-        <v>9.029999999999999</v>
-      </c>
+      <c r="O133" s="29" t="n"/>
+      <c r="P133" s="29" t="n"/>
+      <c r="Q133" s="29" t="n"/>
       <c r="R133" s="46" t="n"/>
       <c r="S133" s="21" t="n"/>
       <c r="T133" s="33" t="n"/>
@@ -14182,15 +14162,9 @@
         </is>
       </c>
       <c r="N134" s="52" t="n"/>
-      <c r="O134" s="29" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P134" s="29" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="Q134" s="29" t="n">
-        <v>11.19</v>
-      </c>
+      <c r="O134" s="29" t="n"/>
+      <c r="P134" s="29" t="n"/>
+      <c r="Q134" s="29" t="n"/>
       <c r="R134" s="46" t="inlineStr">
         <is>
           <t>2002-12-25</t>
@@ -14299,15 +14273,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O135" s="29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P135" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q135" s="29" t="n">
-        <v>9.960000000000001</v>
-      </c>
+      <c r="O135" s="29" t="n"/>
+      <c r="P135" s="29" t="n"/>
+      <c r="Q135" s="29" t="n"/>
       <c r="R135" s="46" t="n"/>
       <c r="S135" s="21" t="n"/>
       <c r="T135" s="33" t="n"/>
@@ -14412,15 +14380,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O136" s="29" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="P136" s="29" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Q136" s="29" t="n">
-        <v>6.56</v>
-      </c>
+      <c r="O136" s="29" t="n"/>
+      <c r="P136" s="29" t="n"/>
+      <c r="Q136" s="29" t="n"/>
       <c r="R136" s="46" t="n"/>
       <c r="S136" s="21" t="n"/>
       <c r="T136" s="33" t="n"/>
@@ -14649,13 +14611,13 @@
       </c>
       <c r="N138" s="52" t="n"/>
       <c r="O138" s="29" t="n">
-        <v>19.6</v>
+        <v>16.9</v>
       </c>
       <c r="P138" s="29" t="n">
-        <v>27.7</v>
+        <v>26.2</v>
       </c>
       <c r="Q138" s="29" t="n">
-        <v>23.69</v>
+        <v>21.23</v>
       </c>
       <c r="R138" s="46" t="n"/>
       <c r="S138" s="21" t="inlineStr">
@@ -14766,13 +14728,13 @@
       </c>
       <c r="N139" s="52" t="n"/>
       <c r="O139" s="29" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
       </c>
       <c r="P139" s="29" t="n">
-        <v>15.8</v>
+        <v>16.3</v>
       </c>
       <c r="Q139" s="29" t="n">
-        <v>12.28</v>
+        <v>11.24</v>
       </c>
       <c r="R139" s="46" t="n"/>
       <c r="S139" s="21" t="inlineStr">
@@ -14994,13 +14956,13 @@
       </c>
       <c r="N141" s="52" t="n"/>
       <c r="O141" s="29" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="P141" s="29" t="n">
-        <v>22.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q141" s="29" t="n">
-        <v>12.25</v>
+        <v>13.41</v>
       </c>
       <c r="R141" s="46" t="n"/>
       <c r="S141" s="21" t="inlineStr">
@@ -15119,13 +15081,13 @@
       </c>
       <c r="N142" s="52" t="n"/>
       <c r="O142" s="29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P142" s="29" t="n">
-        <v>26.8</v>
+        <v>26.3</v>
       </c>
       <c r="Q142" s="29" t="n">
-        <v>17.01</v>
+        <v>17.35</v>
       </c>
       <c r="R142" s="46" t="n"/>
       <c r="S142" s="21" t="inlineStr">
@@ -15232,13 +15194,13 @@
       </c>
       <c r="N143" s="52" t="n"/>
       <c r="O143" s="29" t="n">
-        <v>5.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P143" s="29" t="n">
-        <v>26.9</v>
+        <v>25.4</v>
       </c>
       <c r="Q143" s="29" t="n">
-        <v>14.65</v>
+        <v>16.39</v>
       </c>
       <c r="R143" s="46" t="n"/>
       <c r="S143" s="21" t="inlineStr">
@@ -15353,13 +15315,13 @@
       </c>
       <c r="N144" s="52" t="n"/>
       <c r="O144" s="29" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P144" s="29" t="n">
-        <v>24.7</v>
+        <v>25.2</v>
       </c>
       <c r="Q144" s="29" t="n">
-        <v>13.03</v>
+        <v>13.49</v>
       </c>
       <c r="R144" s="46" t="n"/>
       <c r="S144" s="21" t="inlineStr">
@@ -15474,13 +15436,13 @@
       </c>
       <c r="N145" s="52" t="n"/>
       <c r="O145" s="29" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="P145" s="29" t="n">
-        <v>23.6</v>
+        <v>17.6</v>
       </c>
       <c r="Q145" s="29" t="n">
-        <v>11.61</v>
+        <v>11.1</v>
       </c>
       <c r="R145" s="46" t="n"/>
       <c r="S145" s="21" t="inlineStr">
@@ -15595,13 +15557,13 @@
       </c>
       <c r="N146" s="52" t="n"/>
       <c r="O146" s="29" t="n">
-        <v>13.1</v>
+        <v>17.7</v>
       </c>
       <c r="P146" s="29" t="n">
-        <v>29.8</v>
+        <v>28.1</v>
       </c>
       <c r="Q146" s="29" t="n">
-        <v>20.74</v>
+        <v>22.04</v>
       </c>
       <c r="R146" s="46" t="n"/>
       <c r="S146" s="21" t="inlineStr">
@@ -15712,13 +15674,13 @@
       </c>
       <c r="N147" s="52" t="n"/>
       <c r="O147" s="29" t="n">
-        <v>10.1</v>
+        <v>12.5</v>
       </c>
       <c r="P147" s="29" t="n">
-        <v>28.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q147" s="29" t="n">
-        <v>18.96</v>
+        <v>19.91</v>
       </c>
       <c r="R147" s="46" t="n"/>
       <c r="S147" s="21" t="inlineStr">
@@ -15829,13 +15791,13 @@
       </c>
       <c r="N148" s="52" t="n"/>
       <c r="O148" s="29" t="n">
-        <v>11.4</v>
+        <v>13</v>
       </c>
       <c r="P148" s="29" t="n">
         <v>26.5</v>
       </c>
       <c r="Q148" s="29" t="n">
-        <v>18.61</v>
+        <v>19.75</v>
       </c>
       <c r="R148" s="46" t="n"/>
       <c r="S148" s="21" t="inlineStr">
@@ -16053,13 +16015,13 @@
       </c>
       <c r="N150" s="52" t="n"/>
       <c r="O150" s="29" t="n">
-        <v>12.4</v>
+        <v>13.8</v>
       </c>
       <c r="P150" s="29" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="Q150" s="29" t="n">
-        <v>19.61</v>
+        <v>20.29</v>
       </c>
       <c r="R150" s="46" t="n"/>
       <c r="S150" s="21" t="inlineStr">
@@ -16170,13 +16132,13 @@
       </c>
       <c r="N151" s="52" t="n"/>
       <c r="O151" s="29" t="n">
-        <v>16</v>
+        <v>16.9</v>
       </c>
       <c r="P151" s="29" t="n">
-        <v>26.2</v>
+        <v>28.1</v>
       </c>
       <c r="Q151" s="29" t="n">
-        <v>20.46</v>
+        <v>21.95</v>
       </c>
       <c r="R151" s="46" t="n"/>
       <c r="S151" s="21" t="inlineStr">
@@ -16287,13 +16249,13 @@
       </c>
       <c r="N152" s="52" t="n"/>
       <c r="O152" s="29" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="P152" s="29" t="n">
-        <v>27.1</v>
+        <v>28</v>
       </c>
       <c r="Q152" s="29" t="n">
-        <v>18.65</v>
+        <v>18.96</v>
       </c>
       <c r="R152" s="46" t="n"/>
       <c r="S152" s="21" t="inlineStr">
@@ -16404,13 +16366,13 @@
       </c>
       <c r="N153" s="52" t="n"/>
       <c r="O153" s="29" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="P153" s="29" t="n">
-        <v>27.3</v>
+        <v>26.1</v>
       </c>
       <c r="Q153" s="29" t="n">
-        <v>18.81</v>
+        <v>19.25</v>
       </c>
       <c r="R153" s="46" t="n"/>
       <c r="S153" s="21" t="inlineStr">
@@ -16521,13 +16483,13 @@
       </c>
       <c r="N154" s="52" t="n"/>
       <c r="O154" s="29" t="n">
-        <v>12.1</v>
+        <v>13</v>
       </c>
       <c r="P154" s="29" t="n">
-        <v>26</v>
+        <v>26.9</v>
       </c>
       <c r="Q154" s="29" t="n">
-        <v>18.96</v>
+        <v>19.76</v>
       </c>
       <c r="R154" s="46" t="n"/>
       <c r="S154" s="21" t="inlineStr">
@@ -16741,13 +16703,13 @@
       </c>
       <c r="N156" s="52" t="n"/>
       <c r="O156" s="29" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="P156" s="29" t="n">
-        <v>27.3</v>
+        <v>27.8</v>
       </c>
       <c r="Q156" s="29" t="n">
-        <v>22.25</v>
+        <v>22.54</v>
       </c>
       <c r="R156" s="46" t="n"/>
       <c r="S156" s="21" t="inlineStr">
@@ -16858,13 +16820,13 @@
       </c>
       <c r="N157" s="52" t="n"/>
       <c r="O157" s="29" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P157" s="29" t="n">
-        <v>29.2</v>
+        <v>29.8</v>
       </c>
       <c r="Q157" s="29" t="n">
-        <v>23.31</v>
+        <v>23.15</v>
       </c>
       <c r="R157" s="46" t="n"/>
       <c r="S157" s="21" t="inlineStr">
@@ -17177,13 +17139,13 @@
       </c>
       <c r="N160" s="52" t="n"/>
       <c r="O160" s="29" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="P160" s="29" t="n">
-        <v>31.5</v>
+        <v>32.6</v>
       </c>
       <c r="Q160" s="29" t="n">
-        <v>26.89</v>
+        <v>28.04</v>
       </c>
       <c r="R160" s="46" t="n"/>
       <c r="S160" s="21" t="inlineStr">
@@ -17286,13 +17248,13 @@
       </c>
       <c r="N161" s="52" t="n"/>
       <c r="O161" s="29" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="P161" s="29" t="n">
-        <v>30.3</v>
+        <v>31.7</v>
       </c>
       <c r="Q161" s="29" t="n">
-        <v>24.66</v>
+        <v>25.05</v>
       </c>
       <c r="R161" s="46" t="n"/>
       <c r="S161" s="21" t="inlineStr">
@@ -17403,13 +17365,13 @@
       </c>
       <c r="N162" s="52" t="n"/>
       <c r="O162" s="29" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="P162" s="29" t="n">
-        <v>20.9</v>
+        <v>24.6</v>
       </c>
       <c r="Q162" s="29" t="n">
-        <v>15.18</v>
+        <v>17.25</v>
       </c>
       <c r="R162" s="46" t="n"/>
       <c r="S162" s="21" t="inlineStr">
@@ -17520,13 +17482,13 @@
       </c>
       <c r="N163" s="52" t="n"/>
       <c r="O163" s="29" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="P163" s="29" t="n">
-        <v>25.7</v>
+        <v>26.3</v>
       </c>
       <c r="Q163" s="29" t="n">
-        <v>18.38</v>
+        <v>19.48</v>
       </c>
       <c r="R163" s="46" t="n"/>
       <c r="S163" s="21" t="inlineStr">
@@ -17637,13 +17599,13 @@
       </c>
       <c r="N164" s="52" t="n"/>
       <c r="O164" s="29" t="n">
-        <v>18.3</v>
+        <v>21.4</v>
       </c>
       <c r="P164" s="29" t="n">
-        <v>29.3</v>
+        <v>27.7</v>
       </c>
       <c r="Q164" s="29" t="n">
-        <v>22.86</v>
+        <v>24.23</v>
       </c>
       <c r="R164" s="46" t="n"/>
       <c r="S164" s="21" t="inlineStr">
@@ -17845,13 +17807,13 @@
       </c>
       <c r="N166" s="52" t="n"/>
       <c r="O166" s="29" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="P166" s="29" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q166" s="29" t="n">
-        <v>19.51</v>
+        <v>20.78</v>
       </c>
       <c r="R166" s="46" t="n"/>
       <c r="S166" s="21" t="inlineStr">
@@ -17966,13 +17928,13 @@
       </c>
       <c r="N167" s="52" t="n"/>
       <c r="O167" s="29" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="P167" s="29" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="Q167" s="29" t="n">
-        <v>9.75</v>
+        <v>10.55</v>
       </c>
       <c r="R167" s="46" t="n"/>
       <c r="S167" s="21" t="inlineStr">
@@ -18173,15 +18135,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O169" s="29" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="P169" s="29" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="Q169" s="29" t="n">
-        <v>8.76</v>
-      </c>
+      <c r="O169" s="29" t="n"/>
+      <c r="P169" s="29" t="n"/>
+      <c r="Q169" s="29" t="n"/>
       <c r="R169" s="46" t="n"/>
       <c r="S169" s="21" t="n"/>
       <c r="T169" s="33" t="n"/>
@@ -18564,13 +18520,13 @@
       </c>
       <c r="N173" s="52" t="n"/>
       <c r="O173" s="29" t="n">
-        <v>-6.9</v>
+        <v>-4.2</v>
       </c>
       <c r="P173" s="29" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="Q173" s="29" t="n">
-        <v>-0.39</v>
+        <v>0.26</v>
       </c>
       <c r="R173" s="46" t="n"/>
       <c r="S173" s="21" t="inlineStr">
@@ -18677,13 +18633,13 @@
       </c>
       <c r="N174" s="52" t="n"/>
       <c r="O174" s="29" t="n">
-        <v>-7.5</v>
+        <v>-7.2</v>
       </c>
       <c r="P174" s="29" t="n">
-        <v>7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q174" s="29" t="n">
-        <v>-1.31</v>
+        <v>0.58</v>
       </c>
       <c r="R174" s="46" t="n"/>
       <c r="S174" s="21" t="inlineStr">
@@ -18792,13 +18748,13 @@
       </c>
       <c r="N175" s="52" t="n"/>
       <c r="O175" s="29" t="n">
-        <v>7.9</v>
+        <v>12.8</v>
       </c>
       <c r="P175" s="29" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="Q175" s="29" t="n">
-        <v>17.08</v>
+        <v>20.45</v>
       </c>
       <c r="R175" s="46" t="n"/>
       <c r="S175" s="21" t="inlineStr">
@@ -18897,13 +18853,13 @@
       </c>
       <c r="N176" s="52" t="n"/>
       <c r="O176" s="29" t="n">
-        <v>15.4</v>
+        <v>16.3</v>
       </c>
       <c r="P176" s="29" t="n">
         <v>27.1</v>
       </c>
       <c r="Q176" s="29" t="n">
-        <v>20.65</v>
+        <v>21.28</v>
       </c>
       <c r="R176" s="46" t="n"/>
       <c r="S176" s="21" t="inlineStr">
@@ -19006,13 +18962,13 @@
       </c>
       <c r="N177" s="52" t="n"/>
       <c r="O177" s="29" t="n">
-        <v>6.5</v>
+        <v>9.4</v>
       </c>
       <c r="P177" s="29" t="n">
-        <v>26.9</v>
+        <v>23.9</v>
       </c>
       <c r="Q177" s="29" t="n">
-        <v>15.59</v>
+        <v>15.88</v>
       </c>
       <c r="R177" s="46" t="n"/>
       <c r="S177" s="21" t="inlineStr">
@@ -19130,15 +19086,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O178" s="29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P178" s="29" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q178" s="29" t="n">
-        <v>9.550000000000001</v>
-      </c>
+      <c r="O178" s="29" t="n"/>
+      <c r="P178" s="29" t="n"/>
+      <c r="Q178" s="29" t="n"/>
       <c r="R178" s="46" t="inlineStr">
         <is>
           <t>1970-01-04</t>
@@ -19256,13 +19206,13 @@
         </is>
       </c>
       <c r="O179" s="29" t="n">
-        <v>-6</v>
+        <v>-3.5</v>
       </c>
       <c r="P179" s="29" t="n">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q179" s="29" t="n">
-        <v>-0.27</v>
+        <v>-1.03</v>
       </c>
       <c r="R179" s="46" t="n"/>
       <c r="S179" s="21" t="inlineStr">
@@ -19377,13 +19327,13 @@
       </c>
       <c r="N180" s="52" t="n"/>
       <c r="O180" s="29" t="n">
-        <v>-3.8</v>
+        <v>-7</v>
       </c>
       <c r="P180" s="29" t="n">
-        <v>6.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q180" s="29" t="n">
-        <v>1.56</v>
+        <v>-0.12</v>
       </c>
       <c r="R180" s="46" t="n"/>
       <c r="S180" s="21" t="inlineStr">
@@ -19498,13 +19448,13 @@
       </c>
       <c r="N181" s="52" t="n"/>
       <c r="O181" s="29" t="n">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="P181" s="29" t="n">
-        <v>28.2</v>
+        <v>29.2</v>
       </c>
       <c r="Q181" s="29" t="n">
-        <v>19.6</v>
+        <v>20.45</v>
       </c>
       <c r="R181" s="46" t="n"/>
       <c r="S181" s="21" t="inlineStr">
@@ -19614,10 +19564,10 @@
         <v>10.7</v>
       </c>
       <c r="P182" s="29" t="n">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="Q182" s="29" t="n">
-        <v>17.91</v>
+        <v>17.94</v>
       </c>
       <c r="R182" s="46" t="n"/>
       <c r="S182" s="21" t="inlineStr">
@@ -19728,13 +19678,13 @@
       </c>
       <c r="N183" s="52" t="n"/>
       <c r="O183" s="29" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="P183" s="29" t="n">
-        <v>32.2</v>
+        <v>33.7</v>
       </c>
       <c r="Q183" s="29" t="n">
-        <v>23.55</v>
+        <v>25.49</v>
       </c>
       <c r="R183" s="46" t="n"/>
       <c r="S183" s="21" t="inlineStr">
@@ -19841,13 +19791,13 @@
       </c>
       <c r="N184" s="52" t="n"/>
       <c r="O184" s="29" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="P184" s="29" t="n">
-        <v>13.9</v>
+        <v>16.3</v>
       </c>
       <c r="Q184" s="29" t="n">
-        <v>9.130000000000001</v>
+        <v>12.09</v>
       </c>
       <c r="R184" s="46" t="n"/>
       <c r="S184" s="21" t="inlineStr">
@@ -20044,15 +19994,9 @@
           <t>🔵</t>
         </is>
       </c>
-      <c r="O186" s="29" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="P186" s="29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q186" s="29" t="n">
-        <v>-7.5</v>
-      </c>
+      <c r="O186" s="29" t="n"/>
+      <c r="P186" s="29" t="n"/>
+      <c r="Q186" s="29" t="n"/>
       <c r="R186" s="46" t="n"/>
       <c r="S186" s="21" t="n"/>
       <c r="T186" s="33" t="n"/>
@@ -20150,13 +20094,13 @@
       </c>
       <c r="N187" s="52" t="n"/>
       <c r="O187" s="29" t="n">
-        <v>-7.7</v>
+        <v>-9.6</v>
       </c>
       <c r="P187" s="29" t="n">
-        <v>-1.4</v>
+        <v>-3.6</v>
       </c>
       <c r="Q187" s="29" t="n">
-        <v>-5.9</v>
+        <v>-8.1</v>
       </c>
       <c r="R187" s="46" t="n"/>
       <c r="S187" s="21" t="n"/>
@@ -20457,13 +20401,13 @@
         </is>
       </c>
       <c r="O190" s="29" t="n">
-        <v>-4.2</v>
+        <v>-1.3</v>
       </c>
       <c r="P190" s="29" t="n">
-        <v>20.4</v>
+        <v>22.2</v>
       </c>
       <c r="Q190" s="29" t="n">
-        <v>6.85</v>
+        <v>10</v>
       </c>
       <c r="R190" s="46" t="inlineStr">
         <is>
@@ -20566,10 +20510,10 @@
       </c>
       <c r="N191" s="52" t="n"/>
       <c r="O191" s="29" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="P191" s="29" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="Q191" s="29" t="n"/>
       <c r="R191" s="46" t="n"/>
@@ -20673,10 +20617,10 @@
         </is>
       </c>
       <c r="O192" s="29" t="n">
-        <v>-3.3</v>
+        <v>-5.8</v>
       </c>
       <c r="P192" s="29" t="n">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q192" s="29" t="n"/>
       <c r="R192" s="46" t="n"/>
@@ -20784,13 +20728,13 @@
         </is>
       </c>
       <c r="O193" s="29" t="n">
-        <v>-7.2</v>
+        <v>-2</v>
       </c>
       <c r="P193" s="29" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q193" s="29" t="n">
-        <v>-3.16</v>
+        <v>3</v>
       </c>
       <c r="R193" s="46" t="n"/>
       <c r="S193" s="21" t="n"/>
@@ -21288,12 +21232,8 @@
         </is>
       </c>
       <c r="N198" s="52" t="n"/>
-      <c r="O198" s="29" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="P198" s="29" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="O198" s="29" t="n"/>
+      <c r="P198" s="29" t="n"/>
       <c r="Q198" s="29" t="n"/>
       <c r="R198" s="46" t="n"/>
       <c r="S198" s="21" t="n"/>
@@ -21690,12 +21630,8 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="O202" s="29" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="P202" s="29" t="n">
-        <v>6.3</v>
-      </c>
+      <c r="O202" s="29" t="n"/>
+      <c r="P202" s="29" t="n"/>
       <c r="Q202" s="29" t="n"/>
       <c r="R202" s="46" t="n"/>
       <c r="S202" s="21" t="n"/>
@@ -21797,8 +21733,12 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="O203" s="29" t="n"/>
-      <c r="P203" s="29" t="n"/>
+      <c r="O203" s="29" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="P203" s="29" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="Q203" s="29" t="n"/>
       <c r="R203" s="46" t="n"/>
       <c r="S203" s="21" t="n"/>
@@ -21905,13 +21845,13 @@
         </is>
       </c>
       <c r="O204" s="29" t="n">
-        <v>-15.1</v>
+        <v>-18</v>
       </c>
       <c r="P204" s="29" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="Q204" s="29" t="n">
-        <v>-7.2</v>
+        <v>-4.5</v>
       </c>
       <c r="R204" s="46" t="inlineStr">
         <is>
@@ -22216,10 +22156,10 @@
         </is>
       </c>
       <c r="O207" s="29" t="n">
-        <v>-3</v>
+        <v>-9.9</v>
       </c>
       <c r="P207" s="29" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q207" s="29" t="n"/>
       <c r="R207" s="46" t="n"/>
@@ -22434,10 +22374,10 @@
       </c>
       <c r="N209" s="52" t="n"/>
       <c r="O209" s="29" t="n">
-        <v>-2.4</v>
+        <v>-5.6</v>
       </c>
       <c r="P209" s="29" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="Q209" s="29" t="n"/>
       <c r="R209" s="46" t="n"/>
@@ -22543,7 +22483,7 @@
         </is>
       </c>
       <c r="O210" s="29" t="n">
-        <v>-41</v>
+        <v>-36.5</v>
       </c>
       <c r="P210" s="29" t="n"/>
       <c r="Q210" s="29" t="n"/>
@@ -23119,13 +23059,13 @@
       </c>
       <c r="N216" s="52" t="n"/>
       <c r="O216" s="29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="P216" s="29" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="Q216" s="29" t="n">
-        <v>13.51</v>
+        <v>14.46</v>
       </c>
       <c r="R216" s="46" t="n"/>
       <c r="S216" s="21" t="inlineStr">
@@ -23523,13 +23463,13 @@
       </c>
       <c r="N220" s="52" t="n"/>
       <c r="O220" s="29" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="P220" s="29" t="n">
-        <v>13.2</v>
+        <v>7.6</v>
       </c>
       <c r="Q220" s="29" t="n">
-        <v>9.289999999999999</v>
+        <v>5</v>
       </c>
       <c r="R220" s="46" t="n"/>
       <c r="S220" s="21" t="inlineStr">
@@ -23733,13 +23673,13 @@
       </c>
       <c r="N222" s="52" t="n"/>
       <c r="O222" s="29" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="P222" s="29" t="n">
-        <v>10.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q222" s="29" t="n">
-        <v>7.76</v>
+        <v>4.81</v>
       </c>
       <c r="R222" s="46" t="n"/>
       <c r="S222" s="21" t="inlineStr">
@@ -24139,13 +24079,13 @@
       </c>
       <c r="N226" s="52" t="n"/>
       <c r="O226" s="29" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="P226" s="29" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q226" s="29" t="n">
-        <v>4.74</v>
+        <v>2.4</v>
       </c>
       <c r="R226" s="46" t="n"/>
       <c r="S226" s="21" t="inlineStr">
@@ -24446,13 +24386,13 @@
       </c>
       <c r="N229" s="52" t="n"/>
       <c r="O229" s="29" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P229" s="29" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="Q229" s="29" t="n">
-        <v>4.35</v>
+        <v>6.77</v>
       </c>
       <c r="R229" s="46" t="n"/>
       <c r="S229" s="21" t="inlineStr">
@@ -24559,13 +24499,13 @@
       </c>
       <c r="N230" s="52" t="n"/>
       <c r="O230" s="29" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="P230" s="29" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="Q230" s="29" t="n">
-        <v>7.56</v>
+        <v>5.65</v>
       </c>
       <c r="R230" s="46" t="n"/>
       <c r="S230" s="21" t="inlineStr">
@@ -25060,14 +25000,12 @@
         </is>
       </c>
       <c r="O235" s="29" t="n">
-        <v>-3.8</v>
+        <v>0.5</v>
       </c>
       <c r="P235" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q235" s="29" t="n">
-        <v>-1.18</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="Q235" s="29" t="n"/>
       <c r="R235" s="46" t="n"/>
       <c r="S235" s="21" t="inlineStr">
         <is>
@@ -26013,15 +25951,9 @@
         </is>
       </c>
       <c r="N245" s="52" t="n"/>
-      <c r="O245" s="29" t="n">
-        <v>-25.7</v>
-      </c>
-      <c r="P245" s="29" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Q245" s="29" t="n">
-        <v>-18.35</v>
-      </c>
+      <c r="O245" s="29" t="n"/>
+      <c r="P245" s="29" t="n"/>
+      <c r="Q245" s="29" t="n"/>
       <c r="R245" s="46" t="n"/>
       <c r="S245" s="21" t="n"/>
       <c r="T245" s="33" t="n"/>
@@ -27051,9 +26983,15 @@
         </is>
       </c>
       <c r="N256" s="52" t="n"/>
-      <c r="O256" s="29" t="n"/>
-      <c r="P256" s="29" t="n"/>
-      <c r="Q256" s="29" t="n"/>
+      <c r="O256" s="29" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="P256" s="29" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q256" s="29" t="n">
+        <v>-15.78</v>
+      </c>
       <c r="R256" s="46" t="n"/>
       <c r="S256" s="21" t="n"/>
       <c r="T256" s="33" t="n"/>
@@ -27430,13 +27368,13 @@
         </is>
       </c>
       <c r="O260" s="29" t="n">
-        <v>-5.3</v>
+        <v>-7.5</v>
       </c>
       <c r="P260" s="29" t="n">
-        <v>-0.4</v>
+        <v>-2.7</v>
       </c>
       <c r="Q260" s="29" t="n">
-        <v>-3.15</v>
+        <v>-4.86</v>
       </c>
       <c r="R260" s="46" t="n"/>
       <c r="S260" s="21" t="inlineStr">
@@ -27932,10 +27870,10 @@
         </is>
       </c>
       <c r="O265" s="29" t="n">
-        <v>-10</v>
+        <v>-7.6</v>
       </c>
       <c r="P265" s="29" t="n">
-        <v>-2.9</v>
+        <v>1.4</v>
       </c>
       <c r="Q265" s="29" t="n"/>
       <c r="R265" s="46" t="n"/>
@@ -28317,10 +28255,10 @@
         </is>
       </c>
       <c r="O269" s="29" t="n">
-        <v>-67.7</v>
+        <v>-56.7</v>
       </c>
       <c r="P269" s="29" t="n">
-        <v>-50.2</v>
+        <v>-51.6</v>
       </c>
       <c r="Q269" s="29" t="n"/>
       <c r="R269" s="46" t="n"/>
@@ -28513,13 +28451,13 @@
       </c>
       <c r="N271" s="52" t="n"/>
       <c r="O271" s="29" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="P271" s="29" t="n">
-        <v>11.2</v>
+        <v>13.2</v>
       </c>
       <c r="Q271" s="29" t="n">
-        <v>5.62</v>
+        <v>9.74</v>
       </c>
       <c r="R271" s="46" t="n"/>
       <c r="S271" s="21" t="inlineStr">
@@ -28632,13 +28570,13 @@
         </is>
       </c>
       <c r="O272" s="29" t="n">
-        <v>-5.3</v>
+        <v>-6.1</v>
       </c>
       <c r="P272" s="29" t="n">
-        <v>3.3</v>
+        <v>6.9</v>
       </c>
       <c r="Q272" s="29" t="n">
-        <v>-0.9399999999999999</v>
+        <v>2.01</v>
       </c>
       <c r="R272" s="46" t="n"/>
       <c r="S272" s="21" t="inlineStr">
@@ -29408,10 +29346,10 @@
       </c>
       <c r="N280" s="52" t="n"/>
       <c r="O280" s="29" t="n">
-        <v>-12.5</v>
+        <v>-15.6</v>
       </c>
       <c r="P280" s="29" t="n">
-        <v>7.3</v>
+        <v>10.2</v>
       </c>
       <c r="Q280" s="29" t="n"/>
       <c r="R280" s="46" t="n"/>
@@ -29511,13 +29449,13 @@
       </c>
       <c r="N281" s="52" t="n"/>
       <c r="O281" s="29" t="n">
-        <v>-10.1</v>
+        <v>-13.4</v>
       </c>
       <c r="P281" s="29" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="Q281" s="29" t="n">
-        <v>-2.19</v>
+        <v>-2.9</v>
       </c>
       <c r="R281" s="46" t="n"/>
       <c r="S281" s="21" t="n"/>
@@ -35040,15 +34978,9 @@
         </is>
       </c>
       <c r="N339" s="52" t="n"/>
-      <c r="O339" s="29" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="P339" s="29" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Q339" s="29" t="n">
-        <v>10.19</v>
-      </c>
+      <c r="O339" s="29" t="n"/>
+      <c r="P339" s="29" t="n"/>
+      <c r="Q339" s="29" t="n"/>
       <c r="R339" s="46" t="n"/>
       <c r="S339" s="21" t="n"/>
       <c r="T339" s="33" t="n"/>
@@ -35236,15 +35168,9 @@
         </is>
       </c>
       <c r="N341" s="52" t="n"/>
-      <c r="O341" s="29" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="P341" s="29" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q341" s="29" t="n">
-        <v>3.31</v>
-      </c>
+      <c r="O341" s="29" t="n"/>
+      <c r="P341" s="29" t="n"/>
+      <c r="Q341" s="29" t="n"/>
       <c r="R341" s="46" t="n"/>
       <c r="S341" s="21" t="n"/>
       <c r="T341" s="33" t="n"/>
@@ -35347,15 +35273,9 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O342" s="29" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="P342" s="29" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Q342" s="29" t="n">
-        <v>-0.71</v>
-      </c>
+      <c r="O342" s="29" t="n"/>
+      <c r="P342" s="29" t="n"/>
+      <c r="Q342" s="29" t="n"/>
       <c r="R342" s="46" t="n"/>
       <c r="S342" s="21" t="n"/>
       <c r="T342" s="33" t="n"/>
@@ -35868,15 +35788,9 @@
         </is>
       </c>
       <c r="N347" s="52" t="n"/>
-      <c r="O347" s="29" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="P347" s="29" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Q347" s="29" t="n">
-        <v>10.54</v>
-      </c>
+      <c r="O347" s="29" t="n"/>
+      <c r="P347" s="29" t="n"/>
+      <c r="Q347" s="29" t="n"/>
       <c r="R347" s="46" t="n"/>
       <c r="S347" s="21" t="n"/>
       <c r="T347" s="33" t="n"/>
@@ -36556,13 +36470,13 @@
       </c>
       <c r="N354" s="52" t="n"/>
       <c r="O354" s="29" t="n">
-        <v>-23.5</v>
+        <v>-13.1</v>
       </c>
       <c r="P354" s="29" t="n">
-        <v>3.9</v>
+        <v>-1.6</v>
       </c>
       <c r="Q354" s="29" t="n">
-        <v>-12.7</v>
+        <v>-6.8</v>
       </c>
       <c r="R354" s="46" t="n"/>
       <c r="S354" s="21" t="n"/>
@@ -36660,15 +36574,9 @@
         </is>
       </c>
       <c r="N355" s="52" t="n"/>
-      <c r="O355" s="29" t="n">
-        <v>-21.2</v>
-      </c>
-      <c r="P355" s="29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q355" s="29" t="n">
-        <v>-11.7</v>
-      </c>
+      <c r="O355" s="29" t="n"/>
+      <c r="P355" s="29" t="n"/>
+      <c r="Q355" s="29" t="n"/>
       <c r="R355" s="46" t="n"/>
       <c r="S355" s="21" t="n"/>
       <c r="T355" s="33" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -841,8 +841,8 @@
     <col width="18.59765625" customWidth="1" style="7" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="4" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="7" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="4" min="34" max="760"/>
-    <col width="12.59765625" customWidth="1" style="4" min="761" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="4" min="34" max="761"/>
+    <col width="12.59765625" customWidth="1" style="4" min="762" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="10">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="O2" s="29" t="n">
-        <v>-2.4</v>
+        <v>-0.9</v>
       </c>
       <c r="P2" s="29" t="n">
-        <v>13.8</v>
+        <v>14.7</v>
       </c>
       <c r="Q2" s="29" t="n">
-        <v>6.4</v>
+        <v>5.88</v>
       </c>
       <c r="R2" s="46" t="n"/>
       <c r="S2" s="21" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="O3" s="29" t="n">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
       <c r="P3" s="29" t="n">
-        <v>11.9</v>
+        <v>17.4</v>
       </c>
       <c r="Q3" s="29" t="n"/>
       <c r="R3" s="46" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="O4" s="29" t="n">
-        <v>-3.2</v>
+        <v>-4</v>
       </c>
       <c r="P4" s="29" t="n">
-        <v>10.9</v>
+        <v>15.4</v>
       </c>
       <c r="Q4" s="29" t="n"/>
       <c r="R4" s="46" t="inlineStr">
@@ -1392,8 +1392,12 @@
         </is>
       </c>
       <c r="N5" s="52" t="n"/>
-      <c r="O5" s="29" t="n"/>
-      <c r="P5" s="29" t="n"/>
+      <c r="O5" s="29" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="P5" s="29" t="n">
+        <v>11.1</v>
+      </c>
       <c r="Q5" s="29" t="n"/>
       <c r="R5" s="46" t="n"/>
       <c r="S5" s="21" t="n"/>
@@ -1496,13 +1500,13 @@
         </is>
       </c>
       <c r="O6" s="29" t="n">
-        <v>-6.2</v>
+        <v>-11.2</v>
       </c>
       <c r="P6" s="29" t="n">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="Q6" s="29" t="n">
-        <v>0.98</v>
+        <v>-1.8</v>
       </c>
       <c r="R6" s="48" t="inlineStr">
         <is>
@@ -1607,10 +1611,10 @@
         </is>
       </c>
       <c r="O7" s="29" t="n">
-        <v>-3</v>
+        <v>-10.3</v>
       </c>
       <c r="P7" s="29" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="Q7" s="29" t="n"/>
       <c r="R7" s="46" t="n"/>
@@ -1716,13 +1720,13 @@
       </c>
       <c r="N8" s="52" t="n"/>
       <c r="O8" s="29" t="n">
-        <v>0.1</v>
+        <v>-2.5</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>15.4</v>
+        <v>11.3</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>6.91</v>
+        <v>3.01</v>
       </c>
       <c r="R8" s="46" t="n"/>
       <c r="S8" s="21" t="inlineStr">
@@ -1829,13 +1833,13 @@
       </c>
       <c r="N9" s="52" t="n"/>
       <c r="O9" s="29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>12.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>7.81</v>
+        <v>5.13</v>
       </c>
       <c r="R9" s="46" t="n"/>
       <c r="S9" s="21" t="inlineStr">
@@ -1950,13 +1954,13 @@
         </is>
       </c>
       <c r="O10" s="29" t="n">
-        <v>-3.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>9.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>4.54</v>
+        <v>1.75</v>
       </c>
       <c r="R10" s="46" t="n"/>
       <c r="S10" s="21" t="inlineStr">
@@ -2067,13 +2071,13 @@
         </is>
       </c>
       <c r="O11" s="29" t="n">
-        <v>-5.5</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>5.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="R11" s="46" t="inlineStr">
         <is>
@@ -2184,13 +2188,13 @@
       </c>
       <c r="N12" s="52" t="n"/>
       <c r="O12" s="29" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="P12" s="29" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Q12" s="29" t="n">
         <v>0.6</v>
-      </c>
-      <c r="P12" s="29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q12" s="29" t="n">
-        <v>3.21</v>
       </c>
       <c r="R12" s="46" t="inlineStr">
         <is>
@@ -2305,13 +2309,13 @@
         </is>
       </c>
       <c r="O13" s="29" t="n">
-        <v>-4</v>
+        <v>-11.2</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>0.73</v>
+        <v>-2.16</v>
       </c>
       <c r="R13" s="46" t="inlineStr">
         <is>
@@ -2422,13 +2426,13 @@
       </c>
       <c r="N14" s="52" t="n"/>
       <c r="O14" s="29" t="n">
-        <v>6.6</v>
+        <v>-0.9</v>
       </c>
       <c r="P14" s="29" t="n">
-        <v>16.5</v>
+        <v>14.4</v>
       </c>
       <c r="Q14" s="29" t="n">
-        <v>10.3</v>
+        <v>6.41</v>
       </c>
       <c r="R14" s="46" t="n"/>
       <c r="S14" s="21" t="inlineStr">
@@ -2543,13 +2547,13 @@
       </c>
       <c r="N15" s="52" t="n"/>
       <c r="O15" s="29" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="P15" s="29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q15" s="29" t="n">
-        <v>6.34</v>
+        <v>1.21</v>
       </c>
       <c r="R15" s="46" t="n"/>
       <c r="S15" s="21" t="inlineStr">
@@ -2653,9 +2657,15 @@
         </is>
       </c>
       <c r="N16" s="52" t="n"/>
-      <c r="O16" s="29" t="n"/>
-      <c r="P16" s="29" t="n"/>
-      <c r="Q16" s="29" t="n"/>
+      <c r="O16" s="29" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="P16" s="29" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="Q16" s="29" t="n">
+        <v>3.93</v>
+      </c>
       <c r="R16" s="46" t="n"/>
       <c r="S16" s="21" t="n"/>
       <c r="T16" s="33" t="n"/>
@@ -2840,7 +2850,7 @@
         </is>
       </c>
       <c r="O18" s="29" t="n">
-        <v>-7.9</v>
+        <v>-12</v>
       </c>
       <c r="P18" s="29" t="n"/>
       <c r="Q18" s="29" t="n"/>
@@ -3031,9 +3041,15 @@
         </is>
       </c>
       <c r="N20" s="52" t="n"/>
-      <c r="O20" s="29" t="n"/>
-      <c r="P20" s="29" t="n"/>
-      <c r="Q20" s="29" t="n"/>
+      <c r="O20" s="29" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="P20" s="29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q20" s="29" t="n">
+        <v>-1.84</v>
+      </c>
       <c r="R20" s="46" t="n"/>
       <c r="S20" s="21" t="n"/>
       <c r="T20" s="33" t="n"/>
@@ -4234,8 +4250,12 @@
         </is>
       </c>
       <c r="N33" s="52" t="n"/>
-      <c r="O33" s="29" t="n"/>
-      <c r="P33" s="29" t="n"/>
+      <c r="O33" s="29" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="P33" s="29" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="Q33" s="29" t="n"/>
       <c r="R33" s="46" t="n"/>
       <c r="S33" s="21" t="n"/>
@@ -5328,8 +5348,12 @@
         </is>
       </c>
       <c r="N45" s="52" t="n"/>
-      <c r="O45" s="29" t="n"/>
-      <c r="P45" s="29" t="n"/>
+      <c r="O45" s="29" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="P45" s="29" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Q45" s="29" t="n"/>
       <c r="R45" s="46" t="n"/>
       <c r="S45" s="21" t="n"/>
@@ -7134,8 +7158,12 @@
         </is>
       </c>
       <c r="N65" s="52" t="n"/>
-      <c r="O65" s="29" t="n"/>
-      <c r="P65" s="29" t="n"/>
+      <c r="O65" s="29" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="P65" s="29" t="n">
+        <v>7.8</v>
+      </c>
       <c r="Q65" s="29" t="n"/>
       <c r="R65" s="46" t="n"/>
       <c r="S65" s="21" t="n"/>
@@ -10184,13 +10212,13 @@
         </is>
       </c>
       <c r="O98" s="29" t="n">
-        <v>-13.6</v>
+        <v>-17</v>
       </c>
       <c r="P98" s="29" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="Q98" s="29" t="n">
-        <v>-4.48</v>
+        <v>-5.74</v>
       </c>
       <c r="R98" s="46" t="inlineStr">
         <is>
@@ -10614,13 +10642,13 @@
         </is>
       </c>
       <c r="O102" s="29" t="n">
-        <v>-2.3</v>
+        <v>-3.5</v>
       </c>
       <c r="P102" s="29" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="Q102" s="29" t="n">
-        <v>1.61</v>
+        <v>0.04</v>
       </c>
       <c r="R102" s="46" t="n"/>
       <c r="S102" s="21" t="inlineStr">
@@ -10736,13 +10764,13 @@
         </is>
       </c>
       <c r="O103" s="29" t="n">
-        <v>0.4</v>
+        <v>-3.1</v>
       </c>
       <c r="P103" s="29" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="Q103" s="29" t="n">
-        <v>1.55</v>
+        <v>0.82</v>
       </c>
       <c r="R103" s="46" t="n"/>
       <c r="S103" s="21" t="inlineStr">
@@ -10956,13 +10984,13 @@
         </is>
       </c>
       <c r="O105" s="29" t="n">
-        <v>-4</v>
+        <v>-6.3</v>
       </c>
       <c r="P105" s="29" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="Q105" s="29" t="n">
-        <v>0.45</v>
+        <v>-1.01</v>
       </c>
       <c r="R105" s="46" t="n"/>
       <c r="S105" s="21" t="inlineStr">
@@ -11176,13 +11204,13 @@
       </c>
       <c r="N107" s="52" t="n"/>
       <c r="O107" s="29" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="P107" s="29" t="n">
-        <v>10.6</v>
+        <v>15.2</v>
       </c>
       <c r="Q107" s="29" t="n">
-        <v>6.01</v>
+        <v>5.79</v>
       </c>
       <c r="R107" s="46" t="n"/>
       <c r="S107" s="21" t="inlineStr">
@@ -11404,13 +11432,13 @@
       </c>
       <c r="N109" s="52" t="n"/>
       <c r="O109" s="29" t="n">
-        <v>-7.9</v>
+        <v>-0.8</v>
       </c>
       <c r="P109" s="29" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="Q109" s="29" t="n">
-        <v>-0.63</v>
+        <v>3.07</v>
       </c>
       <c r="R109" s="46" t="inlineStr">
         <is>
@@ -11929,13 +11957,13 @@
       </c>
       <c r="N114" s="52" t="n"/>
       <c r="O114" s="29" t="n">
-        <v>-4.3</v>
+        <v>5.1</v>
       </c>
       <c r="P114" s="29" t="n">
-        <v>19.5</v>
+        <v>20.6</v>
       </c>
       <c r="Q114" s="29" t="n">
-        <v>9.109999999999999</v>
+        <v>11.54</v>
       </c>
       <c r="R114" s="46" t="n"/>
       <c r="S114" s="21" t="inlineStr">
@@ -12042,13 +12070,13 @@
       </c>
       <c r="N115" s="52" t="n"/>
       <c r="O115" s="29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="P115" s="29" t="n">
-        <v>27</v>
+        <v>25.6</v>
       </c>
       <c r="Q115" s="29" t="n">
-        <v>17.4</v>
+        <v>17.07</v>
       </c>
       <c r="R115" s="46" t="n"/>
       <c r="S115" s="21" t="inlineStr">
@@ -12278,13 +12306,13 @@
       </c>
       <c r="N117" s="52" t="n"/>
       <c r="O117" s="29" t="n">
-        <v>9.5</v>
+        <v>7.6</v>
       </c>
       <c r="P117" s="29" t="n">
-        <v>23.1</v>
+        <v>20.6</v>
       </c>
       <c r="Q117" s="29" t="n">
-        <v>15.7</v>
+        <v>13.4</v>
       </c>
       <c r="R117" s="46" t="n"/>
       <c r="S117" s="21" t="inlineStr">
@@ -12403,13 +12431,13 @@
       </c>
       <c r="N118" s="52" t="n"/>
       <c r="O118" s="29" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P118" s="29" t="n">
-        <v>14.7</v>
+        <v>11.7</v>
       </c>
       <c r="Q118" s="29" t="n">
-        <v>8.279999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="R118" s="46" t="n"/>
       <c r="S118" s="21" t="inlineStr">
@@ -12741,15 +12769,9 @@
         </is>
       </c>
       <c r="N121" s="52" t="n"/>
-      <c r="O121" s="29" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="P121" s="29" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q121" s="29" t="n">
-        <v>-3.08</v>
-      </c>
+      <c r="O121" s="29" t="n"/>
+      <c r="P121" s="29" t="n"/>
+      <c r="Q121" s="29" t="n"/>
       <c r="R121" s="46" t="n"/>
       <c r="S121" s="21" t="inlineStr">
         <is>
@@ -12854,15 +12876,9 @@
         </is>
       </c>
       <c r="N122" s="52" t="n"/>
-      <c r="O122" s="29" t="n">
-        <v>-12.1</v>
-      </c>
-      <c r="P122" s="29" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Q122" s="29" t="n">
-        <v>-2.63</v>
-      </c>
+      <c r="O122" s="29" t="n"/>
+      <c r="P122" s="29" t="n"/>
+      <c r="Q122" s="29" t="n"/>
       <c r="R122" s="46" t="n"/>
       <c r="S122" s="21" t="inlineStr">
         <is>
@@ -12976,13 +12992,13 @@
       </c>
       <c r="N123" s="52" t="n"/>
       <c r="O123" s="29" t="n">
-        <v>-14.2</v>
+        <v>-5.2</v>
       </c>
       <c r="P123" s="29" t="n">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="Q123" s="29" t="n">
-        <v>-4.28</v>
+        <v>0.16</v>
       </c>
       <c r="R123" s="46" t="n"/>
       <c r="S123" s="21" t="inlineStr">
@@ -13092,15 +13108,9 @@
         </is>
       </c>
       <c r="N124" s="52" t="n"/>
-      <c r="O124" s="29" t="n">
-        <v>-13.2</v>
-      </c>
-      <c r="P124" s="29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q124" s="29" t="n">
-        <v>-4</v>
-      </c>
+      <c r="O124" s="29" t="n"/>
+      <c r="P124" s="29" t="n"/>
+      <c r="Q124" s="29" t="n"/>
       <c r="R124" s="46" t="n"/>
       <c r="S124" s="21" t="n"/>
       <c r="T124" s="33" t="n"/>
@@ -13317,13 +13327,13 @@
       </c>
       <c r="N126" s="52" t="n"/>
       <c r="O126" s="29" t="n">
-        <v>-3.6</v>
+        <v>-3.1</v>
       </c>
       <c r="P126" s="29" t="n">
-        <v>10.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q126" s="29" t="n">
-        <v>2.74</v>
+        <v>1.09</v>
       </c>
       <c r="R126" s="46" t="n"/>
       <c r="S126" s="21" t="inlineStr">
@@ -14611,13 +14621,13 @@
       </c>
       <c r="N138" s="52" t="n"/>
       <c r="O138" s="29" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="P138" s="29" t="n">
-        <v>26.2</v>
+        <v>27.2</v>
       </c>
       <c r="Q138" s="29" t="n">
-        <v>21.23</v>
+        <v>21.56</v>
       </c>
       <c r="R138" s="46" t="n"/>
       <c r="S138" s="21" t="inlineStr">
@@ -14728,13 +14738,13 @@
       </c>
       <c r="N139" s="52" t="n"/>
       <c r="O139" s="29" t="n">
-        <v>6.7</v>
+        <v>9.4</v>
       </c>
       <c r="P139" s="29" t="n">
-        <v>16.3</v>
+        <v>20.5</v>
       </c>
       <c r="Q139" s="29" t="n">
-        <v>11.24</v>
+        <v>14.24</v>
       </c>
       <c r="R139" s="46" t="n"/>
       <c r="S139" s="21" t="inlineStr">
@@ -14956,13 +14966,13 @@
       </c>
       <c r="N141" s="52" t="n"/>
       <c r="O141" s="29" t="n">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="P141" s="29" t="n">
-        <v>21.7</v>
+        <v>20.3</v>
       </c>
       <c r="Q141" s="29" t="n">
-        <v>13.41</v>
+        <v>13.4</v>
       </c>
       <c r="R141" s="46" t="n"/>
       <c r="S141" s="21" t="inlineStr">
@@ -15081,13 +15091,13 @@
       </c>
       <c r="N142" s="52" t="n"/>
       <c r="O142" s="29" t="n">
-        <v>9.699999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="P142" s="29" t="n">
         <v>26.3</v>
       </c>
       <c r="Q142" s="29" t="n">
-        <v>17.35</v>
+        <v>18.19</v>
       </c>
       <c r="R142" s="46" t="n"/>
       <c r="S142" s="21" t="inlineStr">
@@ -15194,13 +15204,13 @@
       </c>
       <c r="N143" s="52" t="n"/>
       <c r="O143" s="29" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="P143" s="29" t="n">
-        <v>25.4</v>
+        <v>19.7</v>
       </c>
       <c r="Q143" s="29" t="n">
-        <v>16.39</v>
+        <v>14.24</v>
       </c>
       <c r="R143" s="46" t="n"/>
       <c r="S143" s="21" t="inlineStr">
@@ -15315,13 +15325,13 @@
       </c>
       <c r="N144" s="52" t="n"/>
       <c r="O144" s="29" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="P144" s="29" t="n">
         <v>25.2</v>
       </c>
       <c r="Q144" s="29" t="n">
-        <v>13.49</v>
+        <v>14.2</v>
       </c>
       <c r="R144" s="46" t="n"/>
       <c r="S144" s="21" t="inlineStr">
@@ -15436,13 +15446,13 @@
       </c>
       <c r="N145" s="52" t="n"/>
       <c r="O145" s="29" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P145" s="29" t="n">
-        <v>17.6</v>
+        <v>13.8</v>
       </c>
       <c r="Q145" s="29" t="n">
-        <v>11.1</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="R145" s="46" t="n"/>
       <c r="S145" s="21" t="inlineStr">
@@ -15557,13 +15567,13 @@
       </c>
       <c r="N146" s="52" t="n"/>
       <c r="O146" s="29" t="n">
-        <v>17.7</v>
+        <v>16.1</v>
       </c>
       <c r="P146" s="29" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="Q146" s="29" t="n">
-        <v>22.04</v>
+        <v>21.6</v>
       </c>
       <c r="R146" s="46" t="n"/>
       <c r="S146" s="21" t="inlineStr">
@@ -15674,13 +15684,13 @@
       </c>
       <c r="N147" s="52" t="n"/>
       <c r="O147" s="29" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="P147" s="29" t="n">
-        <v>27.1</v>
+        <v>28.2</v>
       </c>
       <c r="Q147" s="29" t="n">
-        <v>19.91</v>
+        <v>19.88</v>
       </c>
       <c r="R147" s="46" t="n"/>
       <c r="S147" s="21" t="inlineStr">
@@ -15791,13 +15801,13 @@
       </c>
       <c r="N148" s="52" t="n"/>
       <c r="O148" s="29" t="n">
-        <v>13</v>
+        <v>14.1</v>
       </c>
       <c r="P148" s="29" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
       <c r="Q148" s="29" t="n">
-        <v>19.75</v>
+        <v>19.88</v>
       </c>
       <c r="R148" s="46" t="n"/>
       <c r="S148" s="21" t="inlineStr">
@@ -16015,13 +16025,13 @@
       </c>
       <c r="N150" s="52" t="n"/>
       <c r="O150" s="29" t="n">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="P150" s="29" t="n">
-        <v>27.5</v>
+        <v>28.7</v>
       </c>
       <c r="Q150" s="29" t="n">
-        <v>20.29</v>
+        <v>20.88</v>
       </c>
       <c r="R150" s="46" t="n"/>
       <c r="S150" s="21" t="inlineStr">
@@ -16132,13 +16142,13 @@
       </c>
       <c r="N151" s="52" t="n"/>
       <c r="O151" s="29" t="n">
-        <v>16.9</v>
+        <v>18</v>
       </c>
       <c r="P151" s="29" t="n">
-        <v>28.1</v>
+        <v>28.9</v>
       </c>
       <c r="Q151" s="29" t="n">
-        <v>21.95</v>
+        <v>23.07</v>
       </c>
       <c r="R151" s="46" t="n"/>
       <c r="S151" s="21" t="inlineStr">
@@ -16249,13 +16259,13 @@
       </c>
       <c r="N152" s="52" t="n"/>
       <c r="O152" s="29" t="n">
-        <v>11.6</v>
+        <v>13.7</v>
       </c>
       <c r="P152" s="29" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="Q152" s="29" t="n">
-        <v>18.96</v>
+        <v>20.3</v>
       </c>
       <c r="R152" s="46" t="n"/>
       <c r="S152" s="21" t="inlineStr">
@@ -16366,13 +16376,13 @@
       </c>
       <c r="N153" s="52" t="n"/>
       <c r="O153" s="29" t="n">
-        <v>12.8</v>
+        <v>16</v>
       </c>
       <c r="P153" s="29" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q153" s="29" t="n">
-        <v>19.25</v>
+        <v>20.57</v>
       </c>
       <c r="R153" s="46" t="n"/>
       <c r="S153" s="21" t="inlineStr">
@@ -16483,13 +16493,13 @@
       </c>
       <c r="N154" s="52" t="n"/>
       <c r="O154" s="29" t="n">
-        <v>13</v>
+        <v>15.6</v>
       </c>
       <c r="P154" s="29" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="Q154" s="29" t="n">
-        <v>19.76</v>
+        <v>21.38</v>
       </c>
       <c r="R154" s="46" t="n"/>
       <c r="S154" s="21" t="inlineStr">
@@ -16706,10 +16716,10 @@
         <v>19.1</v>
       </c>
       <c r="P156" s="29" t="n">
-        <v>27.8</v>
+        <v>29.5</v>
       </c>
       <c r="Q156" s="29" t="n">
-        <v>22.54</v>
+        <v>23.47</v>
       </c>
       <c r="R156" s="46" t="n"/>
       <c r="S156" s="21" t="inlineStr">
@@ -16820,13 +16830,13 @@
       </c>
       <c r="N157" s="52" t="n"/>
       <c r="O157" s="29" t="n">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="P157" s="29" t="n">
-        <v>29.8</v>
+        <v>31.7</v>
       </c>
       <c r="Q157" s="29" t="n">
-        <v>23.15</v>
+        <v>24.42</v>
       </c>
       <c r="R157" s="46" t="n"/>
       <c r="S157" s="21" t="inlineStr">
@@ -17139,13 +17149,13 @@
       </c>
       <c r="N160" s="52" t="n"/>
       <c r="O160" s="29" t="n">
-        <v>25.1</v>
+        <v>24.1</v>
       </c>
       <c r="P160" s="29" t="n">
-        <v>32.6</v>
+        <v>27.6</v>
       </c>
       <c r="Q160" s="29" t="n">
-        <v>28.04</v>
+        <v>25.36</v>
       </c>
       <c r="R160" s="46" t="n"/>
       <c r="S160" s="21" t="inlineStr">
@@ -17248,13 +17258,13 @@
       </c>
       <c r="N161" s="52" t="n"/>
       <c r="O161" s="29" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="P161" s="29" t="n">
-        <v>31.7</v>
+        <v>32.9</v>
       </c>
       <c r="Q161" s="29" t="n">
-        <v>25.05</v>
+        <v>26.16</v>
       </c>
       <c r="R161" s="46" t="n"/>
       <c r="S161" s="21" t="inlineStr">
@@ -17365,13 +17375,13 @@
       </c>
       <c r="N162" s="52" t="n"/>
       <c r="O162" s="29" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="P162" s="29" t="n">
-        <v>24.6</v>
+        <v>22.9</v>
       </c>
       <c r="Q162" s="29" t="n">
-        <v>17.25</v>
+        <v>16.66</v>
       </c>
       <c r="R162" s="46" t="n"/>
       <c r="S162" s="21" t="inlineStr">
@@ -17482,13 +17492,13 @@
       </c>
       <c r="N163" s="52" t="n"/>
       <c r="O163" s="29" t="n">
-        <v>12.9</v>
+        <v>14.5</v>
       </c>
       <c r="P163" s="29" t="n">
-        <v>26.3</v>
+        <v>27.6</v>
       </c>
       <c r="Q163" s="29" t="n">
-        <v>19.48</v>
+        <v>20.52</v>
       </c>
       <c r="R163" s="46" t="n"/>
       <c r="S163" s="21" t="inlineStr">
@@ -17599,13 +17609,13 @@
       </c>
       <c r="N164" s="52" t="n"/>
       <c r="O164" s="29" t="n">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
       <c r="P164" s="29" t="n">
-        <v>27.7</v>
+        <v>26.7</v>
       </c>
       <c r="Q164" s="29" t="n">
-        <v>24.23</v>
+        <v>23.61</v>
       </c>
       <c r="R164" s="46" t="n"/>
       <c r="S164" s="21" t="inlineStr">
@@ -17807,13 +17817,13 @@
       </c>
       <c r="N166" s="52" t="n"/>
       <c r="O166" s="29" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="P166" s="29" t="n">
-        <v>24.3</v>
+        <v>21.5</v>
       </c>
       <c r="Q166" s="29" t="n">
-        <v>20.78</v>
+        <v>19.81</v>
       </c>
       <c r="R166" s="46" t="n"/>
       <c r="S166" s="21" t="inlineStr">
@@ -17928,13 +17938,13 @@
       </c>
       <c r="N167" s="52" t="n"/>
       <c r="O167" s="29" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P167" s="29" t="n">
-        <v>17.9</v>
+        <v>14.4</v>
       </c>
       <c r="Q167" s="29" t="n">
-        <v>10.55</v>
+        <v>7.93</v>
       </c>
       <c r="R167" s="46" t="n"/>
       <c r="S167" s="21" t="inlineStr">
@@ -18520,14 +18530,12 @@
       </c>
       <c r="N173" s="52" t="n"/>
       <c r="O173" s="29" t="n">
-        <v>-4.2</v>
+        <v>-5.1</v>
       </c>
       <c r="P173" s="29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q173" s="29" t="n">
-        <v>0.26</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="Q173" s="29" t="n"/>
       <c r="R173" s="46" t="n"/>
       <c r="S173" s="21" t="inlineStr">
         <is>
@@ -18633,13 +18641,13 @@
       </c>
       <c r="N174" s="52" t="n"/>
       <c r="O174" s="29" t="n">
-        <v>-7.2</v>
+        <v>-5.9</v>
       </c>
       <c r="P174" s="29" t="n">
-        <v>9.699999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="Q174" s="29" t="n">
-        <v>0.58</v>
+        <v>-3.16</v>
       </c>
       <c r="R174" s="46" t="n"/>
       <c r="S174" s="21" t="inlineStr">
@@ -18748,13 +18756,13 @@
       </c>
       <c r="N175" s="52" t="n"/>
       <c r="O175" s="29" t="n">
-        <v>12.8</v>
+        <v>10.8</v>
       </c>
       <c r="P175" s="29" t="n">
-        <v>28.5</v>
+        <v>27</v>
       </c>
       <c r="Q175" s="29" t="n">
-        <v>20.45</v>
+        <v>19.15</v>
       </c>
       <c r="R175" s="46" t="n"/>
       <c r="S175" s="21" t="inlineStr">
@@ -18853,13 +18861,13 @@
       </c>
       <c r="N176" s="52" t="n"/>
       <c r="O176" s="29" t="n">
-        <v>16.3</v>
+        <v>18.1</v>
       </c>
       <c r="P176" s="29" t="n">
-        <v>27.1</v>
+        <v>26.5</v>
       </c>
       <c r="Q176" s="29" t="n">
-        <v>21.28</v>
+        <v>22.23</v>
       </c>
       <c r="R176" s="46" t="n"/>
       <c r="S176" s="21" t="inlineStr">
@@ -18962,13 +18970,13 @@
       </c>
       <c r="N177" s="52" t="n"/>
       <c r="O177" s="29" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P177" s="29" t="n">
-        <v>23.9</v>
+        <v>16.5</v>
       </c>
       <c r="Q177" s="29" t="n">
-        <v>15.88</v>
+        <v>12.25</v>
       </c>
       <c r="R177" s="46" t="n"/>
       <c r="S177" s="21" t="inlineStr">
@@ -19206,13 +19214,13 @@
         </is>
       </c>
       <c r="O179" s="29" t="n">
-        <v>-3.5</v>
+        <v>-9.6</v>
       </c>
       <c r="P179" s="29" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="Q179" s="29" t="n">
-        <v>-1.03</v>
+        <v>-4.25</v>
       </c>
       <c r="R179" s="46" t="n"/>
       <c r="S179" s="21" t="inlineStr">
@@ -19327,13 +19335,13 @@
       </c>
       <c r="N180" s="52" t="n"/>
       <c r="O180" s="29" t="n">
-        <v>-7</v>
+        <v>-6.6</v>
       </c>
       <c r="P180" s="29" t="n">
-        <v>8.300000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="Q180" s="29" t="n">
-        <v>-0.12</v>
+        <v>2.48</v>
       </c>
       <c r="R180" s="46" t="n"/>
       <c r="S180" s="21" t="inlineStr">
@@ -19448,13 +19456,13 @@
       </c>
       <c r="N181" s="52" t="n"/>
       <c r="O181" s="29" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="P181" s="29" t="n">
-        <v>29.2</v>
+        <v>27.2</v>
       </c>
       <c r="Q181" s="29" t="n">
-        <v>20.45</v>
+        <v>19.55</v>
       </c>
       <c r="R181" s="46" t="n"/>
       <c r="S181" s="21" t="inlineStr">
@@ -19561,13 +19569,13 @@
       </c>
       <c r="N182" s="52" t="n"/>
       <c r="O182" s="29" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="P182" s="29" t="n">
-        <v>26.6</v>
+        <v>27.4</v>
       </c>
       <c r="Q182" s="29" t="n">
-        <v>17.94</v>
+        <v>18.7</v>
       </c>
       <c r="R182" s="46" t="n"/>
       <c r="S182" s="21" t="inlineStr">
@@ -19678,13 +19686,13 @@
       </c>
       <c r="N183" s="52" t="n"/>
       <c r="O183" s="29" t="n">
-        <v>19.4</v>
+        <v>22.3</v>
       </c>
       <c r="P183" s="29" t="n">
-        <v>33.7</v>
+        <v>34.2</v>
       </c>
       <c r="Q183" s="29" t="n">
-        <v>25.49</v>
+        <v>27.31</v>
       </c>
       <c r="R183" s="46" t="n"/>
       <c r="S183" s="21" t="inlineStr">
@@ -19791,13 +19799,13 @@
       </c>
       <c r="N184" s="52" t="n"/>
       <c r="O184" s="29" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="P184" s="29" t="n">
-        <v>16.3</v>
+        <v>17</v>
       </c>
       <c r="Q184" s="29" t="n">
-        <v>12.09</v>
+        <v>12.7</v>
       </c>
       <c r="R184" s="46" t="n"/>
       <c r="S184" s="21" t="inlineStr">
@@ -20094,13 +20102,13 @@
       </c>
       <c r="N187" s="52" t="n"/>
       <c r="O187" s="29" t="n">
-        <v>-9.6</v>
+        <v>-12.6</v>
       </c>
       <c r="P187" s="29" t="n">
-        <v>-3.6</v>
+        <v>-2.1</v>
       </c>
       <c r="Q187" s="29" t="n">
-        <v>-8.1</v>
+        <v>-8.4</v>
       </c>
       <c r="R187" s="46" t="n"/>
       <c r="S187" s="21" t="n"/>
@@ -20198,9 +20206,15 @@
         </is>
       </c>
       <c r="N188" s="52" t="n"/>
-      <c r="O188" s="29" t="n"/>
-      <c r="P188" s="29" t="n"/>
-      <c r="Q188" s="29" t="n"/>
+      <c r="O188" s="29" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="P188" s="29" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="Q188" s="29" t="n">
+        <v>-11.2</v>
+      </c>
       <c r="R188" s="46" t="n"/>
       <c r="S188" s="21" t="n"/>
       <c r="T188" s="33" t="n"/>
@@ -20401,13 +20415,13 @@
         </is>
       </c>
       <c r="O190" s="29" t="n">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="P190" s="29" t="n">
-        <v>22.2</v>
+        <v>19.7</v>
       </c>
       <c r="Q190" s="29" t="n">
-        <v>10</v>
+        <v>9.34</v>
       </c>
       <c r="R190" s="46" t="inlineStr">
         <is>
@@ -20510,10 +20524,10 @@
       </c>
       <c r="N191" s="52" t="n"/>
       <c r="O191" s="29" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="P191" s="29" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="Q191" s="29" t="n"/>
       <c r="R191" s="46" t="n"/>
@@ -20617,10 +20631,10 @@
         </is>
       </c>
       <c r="O192" s="29" t="n">
-        <v>-5.8</v>
+        <v>-7.3</v>
       </c>
       <c r="P192" s="29" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="Q192" s="29" t="n"/>
       <c r="R192" s="46" t="n"/>
@@ -20728,13 +20742,13 @@
         </is>
       </c>
       <c r="O193" s="29" t="n">
-        <v>-2</v>
+        <v>2.6</v>
       </c>
       <c r="P193" s="29" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="Q193" s="29" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="R193" s="46" t="n"/>
       <c r="S193" s="21" t="n"/>
@@ -20935,9 +20949,15 @@
         </is>
       </c>
       <c r="N195" s="52" t="n"/>
-      <c r="O195" s="29" t="n"/>
-      <c r="P195" s="29" t="n"/>
-      <c r="Q195" s="29" t="n"/>
+      <c r="O195" s="29" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P195" s="29" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q195" s="29" t="n">
+        <v>-1.16</v>
+      </c>
       <c r="R195" s="46" t="n"/>
       <c r="S195" s="21" t="n"/>
       <c r="T195" s="33" t="n"/>
@@ -21630,8 +21650,12 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="O202" s="29" t="n"/>
-      <c r="P202" s="29" t="n"/>
+      <c r="O202" s="29" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="P202" s="29" t="n">
+        <v>4.2</v>
+      </c>
       <c r="Q202" s="29" t="n"/>
       <c r="R202" s="46" t="n"/>
       <c r="S202" s="21" t="n"/>
@@ -21734,10 +21758,10 @@
         </is>
       </c>
       <c r="O203" s="29" t="n">
-        <v>-15.6</v>
+        <v>-6</v>
       </c>
       <c r="P203" s="29" t="n">
-        <v>9.300000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="Q203" s="29" t="n"/>
       <c r="R203" s="46" t="n"/>
@@ -21845,14 +21869,12 @@
         </is>
       </c>
       <c r="O204" s="29" t="n">
-        <v>-18</v>
+        <v>-7.5</v>
       </c>
       <c r="P204" s="29" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q204" s="29" t="n">
-        <v>-4.5</v>
-      </c>
+        <v>6.1</v>
+      </c>
+      <c r="Q204" s="29" t="n"/>
       <c r="R204" s="46" t="inlineStr">
         <is>
           <t>2023-01-22</t>
@@ -22156,10 +22178,10 @@
         </is>
       </c>
       <c r="O207" s="29" t="n">
-        <v>-9.9</v>
+        <v>-5.7</v>
       </c>
       <c r="P207" s="29" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="Q207" s="29" t="n"/>
       <c r="R207" s="46" t="n"/>
@@ -22373,12 +22395,8 @@
         </is>
       </c>
       <c r="N209" s="52" t="n"/>
-      <c r="O209" s="29" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="P209" s="29" t="n">
-        <v>5.2</v>
-      </c>
+      <c r="O209" s="29" t="n"/>
+      <c r="P209" s="29" t="n"/>
       <c r="Q209" s="29" t="n"/>
       <c r="R209" s="46" t="n"/>
       <c r="S209" s="21" t="n"/>
@@ -22483,7 +22501,7 @@
         </is>
       </c>
       <c r="O210" s="29" t="n">
-        <v>-36.5</v>
+        <v>-45</v>
       </c>
       <c r="P210" s="29" t="n"/>
       <c r="Q210" s="29" t="n"/>
@@ -23059,13 +23077,13 @@
       </c>
       <c r="N216" s="52" t="n"/>
       <c r="O216" s="29" t="n">
-        <v>9.5</v>
+        <v>5.7</v>
       </c>
       <c r="P216" s="29" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="Q216" s="29" t="n">
-        <v>14.46</v>
+        <v>11.11</v>
       </c>
       <c r="R216" s="46" t="n"/>
       <c r="S216" s="21" t="inlineStr">
@@ -23463,13 +23481,13 @@
       </c>
       <c r="N220" s="52" t="n"/>
       <c r="O220" s="29" t="n">
-        <v>3</v>
+        <v>-0.6</v>
       </c>
       <c r="P220" s="29" t="n">
-        <v>7.6</v>
+        <v>12.3</v>
       </c>
       <c r="Q220" s="29" t="n">
-        <v>5</v>
+        <v>5.49</v>
       </c>
       <c r="R220" s="46" t="n"/>
       <c r="S220" s="21" t="inlineStr">
@@ -23673,13 +23691,13 @@
       </c>
       <c r="N222" s="52" t="n"/>
       <c r="O222" s="29" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="P222" s="29" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="Q222" s="29" t="n">
-        <v>4.81</v>
+        <v>8.59</v>
       </c>
       <c r="R222" s="46" t="n"/>
       <c r="S222" s="21" t="inlineStr">
@@ -24079,13 +24097,13 @@
       </c>
       <c r="N226" s="52" t="n"/>
       <c r="O226" s="29" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="P226" s="29" t="n">
-        <v>4.6</v>
+        <v>10.1</v>
       </c>
       <c r="Q226" s="29" t="n">
-        <v>2.4</v>
+        <v>4.31</v>
       </c>
       <c r="R226" s="46" t="n"/>
       <c r="S226" s="21" t="inlineStr">
@@ -24386,13 +24404,13 @@
       </c>
       <c r="N229" s="52" t="n"/>
       <c r="O229" s="29" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="P229" s="29" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q229" s="29" t="n">
-        <v>6.77</v>
+        <v>7.73</v>
       </c>
       <c r="R229" s="46" t="n"/>
       <c r="S229" s="21" t="inlineStr">
@@ -24499,13 +24517,13 @@
       </c>
       <c r="N230" s="52" t="n"/>
       <c r="O230" s="29" t="n">
-        <v>3</v>
+        <v>-0.9</v>
       </c>
       <c r="P230" s="29" t="n">
-        <v>8.4</v>
+        <v>12.9</v>
       </c>
       <c r="Q230" s="29" t="n">
-        <v>5.65</v>
+        <v>5.51</v>
       </c>
       <c r="R230" s="46" t="n"/>
       <c r="S230" s="21" t="inlineStr">
@@ -25000,10 +25018,10 @@
         </is>
       </c>
       <c r="O235" s="29" t="n">
-        <v>0.5</v>
+        <v>-2.4</v>
       </c>
       <c r="P235" s="29" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="Q235" s="29" t="n"/>
       <c r="R235" s="46" t="n"/>
@@ -26983,15 +27001,9 @@
         </is>
       </c>
       <c r="N256" s="52" t="n"/>
-      <c r="O256" s="29" t="n">
-        <v>-26.1</v>
-      </c>
-      <c r="P256" s="29" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q256" s="29" t="n">
-        <v>-15.78</v>
-      </c>
+      <c r="O256" s="29" t="n"/>
+      <c r="P256" s="29" t="n"/>
+      <c r="Q256" s="29" t="n"/>
       <c r="R256" s="46" t="n"/>
       <c r="S256" s="21" t="n"/>
       <c r="T256" s="33" t="n"/>
@@ -27368,13 +27380,13 @@
         </is>
       </c>
       <c r="O260" s="29" t="n">
-        <v>-7.5</v>
+        <v>-13.9</v>
       </c>
       <c r="P260" s="29" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="Q260" s="29" t="n">
-        <v>-4.86</v>
+        <v>-7.95</v>
       </c>
       <c r="R260" s="46" t="n"/>
       <c r="S260" s="21" t="inlineStr">
@@ -27870,10 +27882,10 @@
         </is>
       </c>
       <c r="O265" s="29" t="n">
-        <v>-7.6</v>
+        <v>-17.5</v>
       </c>
       <c r="P265" s="29" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="Q265" s="29" t="n"/>
       <c r="R265" s="46" t="n"/>
@@ -28255,10 +28267,10 @@
         </is>
       </c>
       <c r="O269" s="29" t="n">
-        <v>-56.7</v>
+        <v>-60.7</v>
       </c>
       <c r="P269" s="29" t="n">
-        <v>-51.6</v>
+        <v>-56.3</v>
       </c>
       <c r="Q269" s="29" t="n"/>
       <c r="R269" s="46" t="n"/>
@@ -28451,13 +28463,13 @@
       </c>
       <c r="N271" s="52" t="n"/>
       <c r="O271" s="29" t="n">
-        <v>7.3</v>
+        <v>5.1</v>
       </c>
       <c r="P271" s="29" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="Q271" s="29" t="n">
-        <v>9.74</v>
+        <v>8.32</v>
       </c>
       <c r="R271" s="46" t="n"/>
       <c r="S271" s="21" t="inlineStr">
@@ -28570,13 +28582,13 @@
         </is>
       </c>
       <c r="O272" s="29" t="n">
-        <v>-6.1</v>
+        <v>2.2</v>
       </c>
       <c r="P272" s="29" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="Q272" s="29" t="n">
-        <v>2.01</v>
+        <v>4.15</v>
       </c>
       <c r="R272" s="46" t="n"/>
       <c r="S272" s="21" t="inlineStr">
@@ -29345,12 +29357,8 @@
         </is>
       </c>
       <c r="N280" s="52" t="n"/>
-      <c r="O280" s="29" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="P280" s="29" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="O280" s="29" t="n"/>
+      <c r="P280" s="29" t="n"/>
       <c r="Q280" s="29" t="n"/>
       <c r="R280" s="46" t="n"/>
       <c r="S280" s="21" t="n"/>
@@ -29448,15 +29456,9 @@
         </is>
       </c>
       <c r="N281" s="52" t="n"/>
-      <c r="O281" s="29" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="P281" s="29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q281" s="29" t="n">
-        <v>-2.9</v>
-      </c>
+      <c r="O281" s="29" t="n"/>
+      <c r="P281" s="29" t="n"/>
+      <c r="Q281" s="29" t="n"/>
       <c r="R281" s="46" t="n"/>
       <c r="S281" s="21" t="n"/>
       <c r="T281" s="33" t="n"/>
@@ -33583,8 +33585,12 @@
         </is>
       </c>
       <c r="N324" s="52" t="n"/>
-      <c r="O324" s="29" t="n"/>
-      <c r="P324" s="29" t="n"/>
+      <c r="O324" s="29" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="P324" s="29" t="n">
+        <v>3.4</v>
+      </c>
       <c r="Q324" s="29" t="n"/>
       <c r="R324" s="46" t="n"/>
       <c r="S324" s="21" t="n"/>
@@ -35273,9 +35279,15 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O342" s="29" t="n"/>
-      <c r="P342" s="29" t="n"/>
-      <c r="Q342" s="29" t="n"/>
+      <c r="O342" s="29" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="P342" s="29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q342" s="29" t="n">
+        <v>-3.14</v>
+      </c>
       <c r="R342" s="46" t="n"/>
       <c r="S342" s="21" t="n"/>
       <c r="T342" s="33" t="n"/>
@@ -36275,9 +36287,15 @@
         </is>
       </c>
       <c r="N352" s="52" t="n"/>
-      <c r="O352" s="29" t="n"/>
-      <c r="P352" s="29" t="n"/>
-      <c r="Q352" s="29" t="n"/>
+      <c r="O352" s="29" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="P352" s="29" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="Q352" s="29" t="n">
+        <v>-10</v>
+      </c>
       <c r="R352" s="46" t="n"/>
       <c r="S352" s="21" t="n"/>
       <c r="T352" s="33" t="n"/>
@@ -36470,13 +36488,13 @@
       </c>
       <c r="N354" s="52" t="n"/>
       <c r="O354" s="29" t="n">
-        <v>-13.1</v>
+        <v>-23</v>
       </c>
       <c r="P354" s="29" t="n">
-        <v>-1.6</v>
+        <v>-0.3</v>
       </c>
       <c r="Q354" s="29" t="n">
-        <v>-6.8</v>
+        <v>-11.7</v>
       </c>
       <c r="R354" s="46" t="n"/>
       <c r="S354" s="21" t="n"/>
@@ -36574,9 +36592,15 @@
         </is>
       </c>
       <c r="N355" s="52" t="n"/>
-      <c r="O355" s="29" t="n"/>
-      <c r="P355" s="29" t="n"/>
-      <c r="Q355" s="29" t="n"/>
+      <c r="O355" s="29" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="P355" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q355" s="29" t="n">
+        <v>-10.5</v>
+      </c>
       <c r="R355" s="46" t="n"/>
       <c r="S355" s="21" t="n"/>
       <c r="T355" s="33" t="n"/>
@@ -38821,9 +38845,15 @@
         </is>
       </c>
       <c r="N378" s="52" t="n"/>
-      <c r="O378" s="29" t="n"/>
-      <c r="P378" s="29" t="n"/>
-      <c r="Q378" s="29" t="n"/>
+      <c r="O378" s="29" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="P378" s="29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q378" s="29" t="n">
+        <v>-2.75</v>
+      </c>
       <c r="R378" s="46" t="n"/>
       <c r="S378" s="21" t="n"/>
       <c r="T378" s="33" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -841,8 +841,8 @@
     <col width="18.59765625" customWidth="1" style="7" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="4" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="7" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="4" min="34" max="761"/>
-    <col width="12.59765625" customWidth="1" style="4" min="762" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="4" min="34" max="763"/>
+    <col width="12.59765625" customWidth="1" style="4" min="764" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="10">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="O2" s="29" t="n">
-        <v>-0.9</v>
+        <v>1.7</v>
       </c>
       <c r="P2" s="29" t="n">
-        <v>14.7</v>
+        <v>13</v>
       </c>
       <c r="Q2" s="29" t="n">
-        <v>5.88</v>
+        <v>6.34</v>
       </c>
       <c r="R2" s="46" t="n"/>
       <c r="S2" s="21" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="O3" s="29" t="n">
-        <v>-2</v>
+        <v>2.4</v>
       </c>
       <c r="P3" s="29" t="n">
-        <v>17.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q3" s="29" t="n"/>
       <c r="R3" s="46" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="O4" s="29" t="n">
-        <v>-4</v>
+        <v>1.7</v>
       </c>
       <c r="P4" s="29" t="n">
-        <v>15.4</v>
+        <v>12</v>
       </c>
       <c r="Q4" s="29" t="n"/>
       <c r="R4" s="46" t="inlineStr">
@@ -1392,12 +1392,8 @@
         </is>
       </c>
       <c r="N5" s="52" t="n"/>
-      <c r="O5" s="29" t="n">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="P5" s="29" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="O5" s="29" t="n"/>
+      <c r="P5" s="29" t="n"/>
       <c r="Q5" s="29" t="n"/>
       <c r="R5" s="46" t="n"/>
       <c r="S5" s="21" t="n"/>
@@ -1500,13 +1496,13 @@
         </is>
       </c>
       <c r="O6" s="29" t="n">
-        <v>-11.2</v>
+        <v>-5.2</v>
       </c>
       <c r="P6" s="29" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q6" s="29" t="n">
-        <v>-1.8</v>
+        <v>1.8</v>
       </c>
       <c r="R6" s="48" t="inlineStr">
         <is>
@@ -1611,10 +1607,10 @@
         </is>
       </c>
       <c r="O7" s="29" t="n">
-        <v>-10.3</v>
+        <v>-2.9</v>
       </c>
       <c r="P7" s="29" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q7" s="29" t="n"/>
       <c r="R7" s="46" t="n"/>
@@ -1720,13 +1716,13 @@
       </c>
       <c r="N8" s="52" t="n"/>
       <c r="O8" s="29" t="n">
-        <v>-2.5</v>
+        <v>-4.5</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>11.3</v>
+        <v>19.7</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>3.01</v>
+        <v>5.79</v>
       </c>
       <c r="R8" s="46" t="n"/>
       <c r="S8" s="21" t="inlineStr">
@@ -1833,13 +1829,13 @@
       </c>
       <c r="N9" s="52" t="n"/>
       <c r="O9" s="29" t="n">
-        <v>-1</v>
+        <v>3.1</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>10.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>5.13</v>
+        <v>7.3</v>
       </c>
       <c r="R9" s="46" t="n"/>
       <c r="S9" s="21" t="inlineStr">
@@ -1954,13 +1950,13 @@
         </is>
       </c>
       <c r="O10" s="29" t="n">
-        <v>-9.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>12.9</v>
+        <v>11.3</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>1.75</v>
+        <v>6.28</v>
       </c>
       <c r="R10" s="46" t="n"/>
       <c r="S10" s="21" t="inlineStr">
@@ -2071,13 +2067,13 @@
         </is>
       </c>
       <c r="O11" s="29" t="n">
-        <v>-9.699999999999999</v>
+        <v>-0.4</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>1.04</v>
+        <v>3.71</v>
       </c>
       <c r="R11" s="46" t="inlineStr">
         <is>
@@ -2188,13 +2184,13 @@
       </c>
       <c r="N12" s="52" t="n"/>
       <c r="O12" s="29" t="n">
-        <v>-7.7</v>
+        <v>-3</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>11.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>0.6</v>
+        <v>2.68</v>
       </c>
       <c r="R12" s="46" t="inlineStr">
         <is>
@@ -2309,13 +2305,13 @@
         </is>
       </c>
       <c r="O13" s="29" t="n">
-        <v>-11.2</v>
+        <v>-2.9</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>-2.16</v>
+        <v>1.84</v>
       </c>
       <c r="R13" s="46" t="inlineStr">
         <is>
@@ -2426,13 +2422,13 @@
       </c>
       <c r="N14" s="52" t="n"/>
       <c r="O14" s="29" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="P14" s="29" t="n">
-        <v>14.4</v>
+        <v>16.3</v>
       </c>
       <c r="Q14" s="29" t="n">
-        <v>6.41</v>
+        <v>7.1</v>
       </c>
       <c r="R14" s="46" t="n"/>
       <c r="S14" s="21" t="inlineStr">
@@ -2547,13 +2543,13 @@
       </c>
       <c r="N15" s="52" t="n"/>
       <c r="O15" s="29" t="n">
-        <v>-8.5</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="P15" s="29" t="n">
-        <v>12</v>
+        <v>14.3</v>
       </c>
       <c r="Q15" s="29" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="R15" s="46" t="n"/>
       <c r="S15" s="21" t="inlineStr">
@@ -2658,13 +2654,13 @@
       </c>
       <c r="N16" s="52" t="n"/>
       <c r="O16" s="29" t="n">
-        <v>-7.3</v>
+        <v>-8.4</v>
       </c>
       <c r="P16" s="29" t="n">
-        <v>14.7</v>
+        <v>16.6</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>3.93</v>
+        <v>3.05</v>
       </c>
       <c r="R16" s="46" t="n"/>
       <c r="S16" s="21" t="n"/>
@@ -2849,9 +2845,7 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O18" s="29" t="n">
-        <v>-12</v>
-      </c>
+      <c r="O18" s="29" t="n"/>
       <c r="P18" s="29" t="n"/>
       <c r="Q18" s="29" t="n"/>
       <c r="R18" s="46" t="n"/>
@@ -3041,15 +3035,9 @@
         </is>
       </c>
       <c r="N20" s="52" t="n"/>
-      <c r="O20" s="29" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="P20" s="29" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q20" s="29" t="n">
-        <v>-1.84</v>
-      </c>
+      <c r="O20" s="29" t="n"/>
+      <c r="P20" s="29" t="n"/>
+      <c r="Q20" s="29" t="n"/>
       <c r="R20" s="46" t="n"/>
       <c r="S20" s="21" t="n"/>
       <c r="T20" s="33" t="n"/>
@@ -4250,12 +4238,8 @@
         </is>
       </c>
       <c r="N33" s="52" t="n"/>
-      <c r="O33" s="29" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="P33" s="29" t="n">
-        <v>8.199999999999999</v>
-      </c>
+      <c r="O33" s="29" t="n"/>
+      <c r="P33" s="29" t="n"/>
       <c r="Q33" s="29" t="n"/>
       <c r="R33" s="46" t="n"/>
       <c r="S33" s="21" t="n"/>
@@ -5348,12 +5332,8 @@
         </is>
       </c>
       <c r="N45" s="52" t="n"/>
-      <c r="O45" s="29" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="P45" s="29" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="O45" s="29" t="n"/>
+      <c r="P45" s="29" t="n"/>
       <c r="Q45" s="29" t="n"/>
       <c r="R45" s="46" t="n"/>
       <c r="S45" s="21" t="n"/>
@@ -7158,12 +7138,8 @@
         </is>
       </c>
       <c r="N65" s="52" t="n"/>
-      <c r="O65" s="29" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="P65" s="29" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="O65" s="29" t="n"/>
+      <c r="P65" s="29" t="n"/>
       <c r="Q65" s="29" t="n"/>
       <c r="R65" s="46" t="n"/>
       <c r="S65" s="21" t="n"/>
@@ -9109,9 +9085,15 @@
         </is>
       </c>
       <c r="N86" s="52" t="n"/>
-      <c r="O86" s="29" t="n"/>
-      <c r="P86" s="29" t="n"/>
-      <c r="Q86" s="29" t="n"/>
+      <c r="O86" s="29" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="P86" s="29" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="Q86" s="29" t="n">
+        <v>2.53</v>
+      </c>
       <c r="R86" s="46" t="n"/>
       <c r="S86" s="21" t="n"/>
       <c r="T86" s="33" t="n"/>
@@ -10212,13 +10194,13 @@
         </is>
       </c>
       <c r="O98" s="29" t="n">
-        <v>-17</v>
+        <v>-14.9</v>
       </c>
       <c r="P98" s="29" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q98" s="29" t="n">
-        <v>-5.74</v>
+        <v>-3.66</v>
       </c>
       <c r="R98" s="46" t="inlineStr">
         <is>
@@ -10642,13 +10624,13 @@
         </is>
       </c>
       <c r="O102" s="29" t="n">
-        <v>-3.5</v>
+        <v>-6.3</v>
       </c>
       <c r="P102" s="29" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="Q102" s="29" t="n">
-        <v>0.04</v>
+        <v>-0.55</v>
       </c>
       <c r="R102" s="46" t="n"/>
       <c r="S102" s="21" t="inlineStr">
@@ -10764,13 +10746,13 @@
         </is>
       </c>
       <c r="O103" s="29" t="n">
-        <v>-3.1</v>
+        <v>-5.3</v>
       </c>
       <c r="P103" s="29" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="Q103" s="29" t="n">
-        <v>0.82</v>
+        <v>-0.71</v>
       </c>
       <c r="R103" s="46" t="n"/>
       <c r="S103" s="21" t="inlineStr">
@@ -10984,13 +10966,13 @@
         </is>
       </c>
       <c r="O105" s="29" t="n">
-        <v>-6.3</v>
+        <v>-8.1</v>
       </c>
       <c r="P105" s="29" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q105" s="29" t="n">
-        <v>-1.01</v>
+        <v>-1</v>
       </c>
       <c r="R105" s="46" t="n"/>
       <c r="S105" s="21" t="inlineStr">
@@ -11204,13 +11186,13 @@
       </c>
       <c r="N107" s="52" t="n"/>
       <c r="O107" s="29" t="n">
-        <v>-0.5</v>
+        <v>4.1</v>
       </c>
       <c r="P107" s="29" t="n">
-        <v>15.2</v>
+        <v>11.1</v>
       </c>
       <c r="Q107" s="29" t="n">
-        <v>5.79</v>
+        <v>6.74</v>
       </c>
       <c r="R107" s="46" t="n"/>
       <c r="S107" s="21" t="inlineStr">
@@ -11432,13 +11414,13 @@
       </c>
       <c r="N109" s="52" t="n"/>
       <c r="O109" s="29" t="n">
-        <v>-0.8</v>
+        <v>-4.7</v>
       </c>
       <c r="P109" s="29" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q109" s="29" t="n">
-        <v>3.07</v>
+        <v>-0.79</v>
       </c>
       <c r="R109" s="46" t="inlineStr">
         <is>
@@ -11957,13 +11939,13 @@
       </c>
       <c r="N114" s="52" t="n"/>
       <c r="O114" s="29" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="P114" s="29" t="n">
-        <v>20.6</v>
+        <v>18.6</v>
       </c>
       <c r="Q114" s="29" t="n">
-        <v>11.54</v>
+        <v>8.34</v>
       </c>
       <c r="R114" s="46" t="n"/>
       <c r="S114" s="21" t="inlineStr">
@@ -12070,14 +12052,12 @@
       </c>
       <c r="N115" s="52" t="n"/>
       <c r="O115" s="29" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="P115" s="29" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="Q115" s="29" t="n">
-        <v>17.07</v>
-      </c>
+        <v>21.5</v>
+      </c>
+      <c r="Q115" s="29" t="n"/>
       <c r="R115" s="46" t="n"/>
       <c r="S115" s="21" t="inlineStr">
         <is>
@@ -12306,13 +12286,13 @@
       </c>
       <c r="N117" s="52" t="n"/>
       <c r="O117" s="29" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="P117" s="29" t="n">
-        <v>20.6</v>
+        <v>17.7</v>
       </c>
       <c r="Q117" s="29" t="n">
-        <v>13.4</v>
+        <v>11.87</v>
       </c>
       <c r="R117" s="46" t="n"/>
       <c r="S117" s="21" t="inlineStr">
@@ -12431,13 +12411,13 @@
       </c>
       <c r="N118" s="52" t="n"/>
       <c r="O118" s="29" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P118" s="29" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
       <c r="Q118" s="29" t="n">
-        <v>7.3</v>
+        <v>7.59</v>
       </c>
       <c r="R118" s="46" t="n"/>
       <c r="S118" s="21" t="inlineStr">
@@ -12992,13 +12972,13 @@
       </c>
       <c r="N123" s="52" t="n"/>
       <c r="O123" s="29" t="n">
-        <v>-5.2</v>
+        <v>-4.8</v>
       </c>
       <c r="P123" s="29" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="Q123" s="29" t="n">
-        <v>0.16</v>
+        <v>1.42</v>
       </c>
       <c r="R123" s="46" t="n"/>
       <c r="S123" s="21" t="inlineStr">
@@ -13108,9 +13088,15 @@
         </is>
       </c>
       <c r="N124" s="52" t="n"/>
-      <c r="O124" s="29" t="n"/>
-      <c r="P124" s="29" t="n"/>
-      <c r="Q124" s="29" t="n"/>
+      <c r="O124" s="29" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="P124" s="29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q124" s="29" t="n">
+        <v>-0.31</v>
+      </c>
       <c r="R124" s="46" t="n"/>
       <c r="S124" s="21" t="n"/>
       <c r="T124" s="33" t="n"/>
@@ -13327,13 +13313,13 @@
       </c>
       <c r="N126" s="52" t="n"/>
       <c r="O126" s="29" t="n">
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
       <c r="P126" s="29" t="n">
-        <v>4.1</v>
+        <v>10.3</v>
       </c>
       <c r="Q126" s="29" t="n">
-        <v>1.09</v>
+        <v>3.29</v>
       </c>
       <c r="R126" s="46" t="n"/>
       <c r="S126" s="21" t="inlineStr">
@@ -14621,13 +14607,13 @@
       </c>
       <c r="N138" s="52" t="n"/>
       <c r="O138" s="29" t="n">
-        <v>16.7</v>
+        <v>15.1</v>
       </c>
       <c r="P138" s="29" t="n">
-        <v>27.2</v>
+        <v>28.2</v>
       </c>
       <c r="Q138" s="29" t="n">
-        <v>21.56</v>
+        <v>21.66</v>
       </c>
       <c r="R138" s="46" t="n"/>
       <c r="S138" s="21" t="inlineStr">
@@ -14738,13 +14724,13 @@
       </c>
       <c r="N139" s="52" t="n"/>
       <c r="O139" s="29" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="P139" s="29" t="n">
-        <v>20.5</v>
+        <v>17.7</v>
       </c>
       <c r="Q139" s="29" t="n">
-        <v>14.24</v>
+        <v>13.4</v>
       </c>
       <c r="R139" s="46" t="n"/>
       <c r="S139" s="21" t="inlineStr">
@@ -14966,13 +14952,13 @@
       </c>
       <c r="N141" s="52" t="n"/>
       <c r="O141" s="29" t="n">
-        <v>7.7</v>
+        <v>3.5</v>
       </c>
       <c r="P141" s="29" t="n">
-        <v>20.3</v>
+        <v>19.3</v>
       </c>
       <c r="Q141" s="29" t="n">
-        <v>13.4</v>
+        <v>11.86</v>
       </c>
       <c r="R141" s="46" t="n"/>
       <c r="S141" s="21" t="inlineStr">
@@ -15091,13 +15077,13 @@
       </c>
       <c r="N142" s="52" t="n"/>
       <c r="O142" s="29" t="n">
-        <v>10.7</v>
+        <v>13.8</v>
       </c>
       <c r="P142" s="29" t="n">
-        <v>26.3</v>
+        <v>26.6</v>
       </c>
       <c r="Q142" s="29" t="n">
-        <v>18.19</v>
+        <v>18.85</v>
       </c>
       <c r="R142" s="46" t="n"/>
       <c r="S142" s="21" t="inlineStr">
@@ -15204,13 +15190,13 @@
       </c>
       <c r="N143" s="52" t="n"/>
       <c r="O143" s="29" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="P143" s="29" t="n">
-        <v>19.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q143" s="29" t="n">
-        <v>14.24</v>
+        <v>12.4</v>
       </c>
       <c r="R143" s="46" t="n"/>
       <c r="S143" s="21" t="inlineStr">
@@ -15325,13 +15311,13 @@
       </c>
       <c r="N144" s="52" t="n"/>
       <c r="O144" s="29" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="P144" s="29" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q144" s="29" t="n">
-        <v>14.2</v>
+        <v>14.83</v>
       </c>
       <c r="R144" s="46" t="n"/>
       <c r="S144" s="21" t="inlineStr">
@@ -15446,13 +15432,13 @@
       </c>
       <c r="N145" s="52" t="n"/>
       <c r="O145" s="29" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="P145" s="29" t="n">
-        <v>13.8</v>
+        <v>17</v>
       </c>
       <c r="Q145" s="29" t="n">
-        <v>9.109999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R145" s="46" t="n"/>
       <c r="S145" s="21" t="inlineStr">
@@ -15567,13 +15553,13 @@
       </c>
       <c r="N146" s="52" t="n"/>
       <c r="O146" s="29" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="P146" s="29" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="Q146" s="29" t="n">
-        <v>21.6</v>
+        <v>21.41</v>
       </c>
       <c r="R146" s="46" t="n"/>
       <c r="S146" s="21" t="inlineStr">
@@ -15684,13 +15670,13 @@
       </c>
       <c r="N147" s="52" t="n"/>
       <c r="O147" s="29" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="P147" s="29" t="n">
-        <v>28.2</v>
+        <v>29.9</v>
       </c>
       <c r="Q147" s="29" t="n">
-        <v>19.88</v>
+        <v>21.44</v>
       </c>
       <c r="R147" s="46" t="n"/>
       <c r="S147" s="21" t="inlineStr">
@@ -15801,13 +15787,13 @@
       </c>
       <c r="N148" s="52" t="n"/>
       <c r="O148" s="29" t="n">
-        <v>14.1</v>
+        <v>17.1</v>
       </c>
       <c r="P148" s="29" t="n">
-        <v>26.7</v>
+        <v>25.9</v>
       </c>
       <c r="Q148" s="29" t="n">
-        <v>19.88</v>
+        <v>21.29</v>
       </c>
       <c r="R148" s="46" t="n"/>
       <c r="S148" s="21" t="inlineStr">
@@ -16025,13 +16011,13 @@
       </c>
       <c r="N150" s="52" t="n"/>
       <c r="O150" s="29" t="n">
-        <v>14.5</v>
+        <v>17.3</v>
       </c>
       <c r="P150" s="29" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="Q150" s="29" t="n">
-        <v>20.88</v>
+        <v>22.71</v>
       </c>
       <c r="R150" s="46" t="n"/>
       <c r="S150" s="21" t="inlineStr">
@@ -16142,13 +16128,13 @@
       </c>
       <c r="N151" s="52" t="n"/>
       <c r="O151" s="29" t="n">
-        <v>18</v>
+        <v>19.7</v>
       </c>
       <c r="P151" s="29" t="n">
-        <v>28.9</v>
+        <v>29.8</v>
       </c>
       <c r="Q151" s="29" t="n">
-        <v>23.07</v>
+        <v>24.55</v>
       </c>
       <c r="R151" s="46" t="n"/>
       <c r="S151" s="21" t="inlineStr">
@@ -16259,13 +16245,13 @@
       </c>
       <c r="N152" s="52" t="n"/>
       <c r="O152" s="29" t="n">
-        <v>13.7</v>
+        <v>15.7</v>
       </c>
       <c r="P152" s="29" t="n">
-        <v>28.7</v>
+        <v>30.3</v>
       </c>
       <c r="Q152" s="29" t="n">
-        <v>20.3</v>
+        <v>22.29</v>
       </c>
       <c r="R152" s="46" t="n"/>
       <c r="S152" s="21" t="inlineStr">
@@ -16376,13 +16362,13 @@
       </c>
       <c r="N153" s="52" t="n"/>
       <c r="O153" s="29" t="n">
-        <v>16</v>
+        <v>17.2</v>
       </c>
       <c r="P153" s="29" t="n">
-        <v>26.2</v>
+        <v>27.6</v>
       </c>
       <c r="Q153" s="29" t="n">
-        <v>20.57</v>
+        <v>21.75</v>
       </c>
       <c r="R153" s="46" t="n"/>
       <c r="S153" s="21" t="inlineStr">
@@ -16493,13 +16479,13 @@
       </c>
       <c r="N154" s="52" t="n"/>
       <c r="O154" s="29" t="n">
-        <v>15.6</v>
+        <v>16.6</v>
       </c>
       <c r="P154" s="29" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="Q154" s="29" t="n">
-        <v>21.38</v>
+        <v>21.75</v>
       </c>
       <c r="R154" s="46" t="n"/>
       <c r="S154" s="21" t="inlineStr">
@@ -16713,13 +16699,13 @@
       </c>
       <c r="N156" s="52" t="n"/>
       <c r="O156" s="29" t="n">
-        <v>19.1</v>
+        <v>20.5</v>
       </c>
       <c r="P156" s="29" t="n">
-        <v>29.5</v>
+        <v>30.9</v>
       </c>
       <c r="Q156" s="29" t="n">
-        <v>23.47</v>
+        <v>24.48</v>
       </c>
       <c r="R156" s="46" t="n"/>
       <c r="S156" s="21" t="inlineStr">
@@ -16830,13 +16816,13 @@
       </c>
       <c r="N157" s="52" t="n"/>
       <c r="O157" s="29" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="P157" s="29" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="Q157" s="29" t="n">
-        <v>24.42</v>
+        <v>25.12</v>
       </c>
       <c r="R157" s="46" t="n"/>
       <c r="S157" s="21" t="inlineStr">
@@ -17152,10 +17138,10 @@
         <v>24.1</v>
       </c>
       <c r="P160" s="29" t="n">
-        <v>27.6</v>
+        <v>32.7</v>
       </c>
       <c r="Q160" s="29" t="n">
-        <v>25.36</v>
+        <v>27.57</v>
       </c>
       <c r="R160" s="46" t="n"/>
       <c r="S160" s="21" t="inlineStr">
@@ -17258,13 +17244,13 @@
       </c>
       <c r="N161" s="52" t="n"/>
       <c r="O161" s="29" t="n">
-        <v>20</v>
+        <v>21.7</v>
       </c>
       <c r="P161" s="29" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="Q161" s="29" t="n">
-        <v>26.16</v>
+        <v>27.32</v>
       </c>
       <c r="R161" s="46" t="n"/>
       <c r="S161" s="21" t="inlineStr">
@@ -17375,13 +17361,13 @@
       </c>
       <c r="N162" s="52" t="n"/>
       <c r="O162" s="29" t="n">
-        <v>11.7</v>
+        <v>14.2</v>
       </c>
       <c r="P162" s="29" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="Q162" s="29" t="n">
-        <v>16.66</v>
+        <v>18.28</v>
       </c>
       <c r="R162" s="46" t="n"/>
       <c r="S162" s="21" t="inlineStr">
@@ -17492,13 +17478,13 @@
       </c>
       <c r="N163" s="52" t="n"/>
       <c r="O163" s="29" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="P163" s="29" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="Q163" s="29" t="n">
-        <v>20.52</v>
+        <v>20.89</v>
       </c>
       <c r="R163" s="46" t="n"/>
       <c r="S163" s="21" t="inlineStr">
@@ -17609,13 +17595,13 @@
       </c>
       <c r="N164" s="52" t="n"/>
       <c r="O164" s="29" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="P164" s="29" t="n">
-        <v>26.7</v>
+        <v>23.7</v>
       </c>
       <c r="Q164" s="29" t="n">
-        <v>23.61</v>
+        <v>22.5</v>
       </c>
       <c r="R164" s="46" t="n"/>
       <c r="S164" s="21" t="inlineStr">
@@ -17817,13 +17803,13 @@
       </c>
       <c r="N166" s="52" t="n"/>
       <c r="O166" s="29" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="P166" s="29" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="Q166" s="29" t="n">
-        <v>19.81</v>
+        <v>18.34</v>
       </c>
       <c r="R166" s="46" t="n"/>
       <c r="S166" s="21" t="inlineStr">
@@ -17938,13 +17924,13 @@
       </c>
       <c r="N167" s="52" t="n"/>
       <c r="O167" s="29" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="P167" s="29" t="n">
-        <v>14.4</v>
+        <v>12.6</v>
       </c>
       <c r="Q167" s="29" t="n">
-        <v>7.93</v>
+        <v>7.91</v>
       </c>
       <c r="R167" s="46" t="n"/>
       <c r="S167" s="21" t="inlineStr">
@@ -18530,12 +18516,14 @@
       </c>
       <c r="N173" s="52" t="n"/>
       <c r="O173" s="29" t="n">
-        <v>-5.1</v>
+        <v>-5.4</v>
       </c>
       <c r="P173" s="29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q173" s="29" t="n"/>
+        <v>4.5</v>
+      </c>
+      <c r="Q173" s="29" t="n">
+        <v>-1.69</v>
+      </c>
       <c r="R173" s="46" t="n"/>
       <c r="S173" s="21" t="inlineStr">
         <is>
@@ -18641,13 +18629,13 @@
       </c>
       <c r="N174" s="52" t="n"/>
       <c r="O174" s="29" t="n">
-        <v>-5.9</v>
+        <v>-8.5</v>
       </c>
       <c r="P174" s="29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q174" s="29" t="n">
-        <v>-3.16</v>
+        <v>-2.9</v>
       </c>
       <c r="R174" s="46" t="n"/>
       <c r="S174" s="21" t="inlineStr">
@@ -18756,13 +18744,13 @@
       </c>
       <c r="N175" s="52" t="n"/>
       <c r="O175" s="29" t="n">
-        <v>10.8</v>
+        <v>12.7</v>
       </c>
       <c r="P175" s="29" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="Q175" s="29" t="n">
-        <v>19.15</v>
+        <v>19.34</v>
       </c>
       <c r="R175" s="46" t="n"/>
       <c r="S175" s="21" t="inlineStr">
@@ -18861,13 +18849,13 @@
       </c>
       <c r="N176" s="52" t="n"/>
       <c r="O176" s="29" t="n">
-        <v>18.1</v>
+        <v>19.7</v>
       </c>
       <c r="P176" s="29" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="Q176" s="29" t="n">
-        <v>22.23</v>
+        <v>22.86</v>
       </c>
       <c r="R176" s="46" t="n"/>
       <c r="S176" s="21" t="inlineStr">
@@ -18970,13 +18958,13 @@
       </c>
       <c r="N177" s="52" t="n"/>
       <c r="O177" s="29" t="n">
-        <v>8.699999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="P177" s="29" t="n">
-        <v>16.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q177" s="29" t="n">
-        <v>12.25</v>
+        <v>11.79</v>
       </c>
       <c r="R177" s="46" t="n"/>
       <c r="S177" s="21" t="inlineStr">
@@ -19214,13 +19202,13 @@
         </is>
       </c>
       <c r="O179" s="29" t="n">
-        <v>-9.6</v>
+        <v>-8.5</v>
       </c>
       <c r="P179" s="29" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="Q179" s="29" t="n">
-        <v>-4.25</v>
+        <v>-2.19</v>
       </c>
       <c r="R179" s="46" t="n"/>
       <c r="S179" s="21" t="inlineStr">
@@ -19335,13 +19323,13 @@
       </c>
       <c r="N180" s="52" t="n"/>
       <c r="O180" s="29" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="P180" s="29" t="n">
-        <v>11.6</v>
+        <v>10.4</v>
       </c>
       <c r="Q180" s="29" t="n">
-        <v>2.48</v>
+        <v>4.34</v>
       </c>
       <c r="R180" s="46" t="n"/>
       <c r="S180" s="21" t="inlineStr">
@@ -19456,14 +19444,12 @@
       </c>
       <c r="N181" s="52" t="n"/>
       <c r="O181" s="29" t="n">
-        <v>12.1</v>
+        <v>13.6</v>
       </c>
       <c r="P181" s="29" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Q181" s="29" t="n">
-        <v>19.55</v>
-      </c>
+        <v>27.4</v>
+      </c>
+      <c r="Q181" s="29" t="n"/>
       <c r="R181" s="46" t="n"/>
       <c r="S181" s="21" t="inlineStr">
         <is>
@@ -19569,13 +19555,13 @@
       </c>
       <c r="N182" s="52" t="n"/>
       <c r="O182" s="29" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="P182" s="29" t="n">
-        <v>27.4</v>
+        <v>28.5</v>
       </c>
       <c r="Q182" s="29" t="n">
-        <v>18.7</v>
+        <v>19.83</v>
       </c>
       <c r="R182" s="46" t="n"/>
       <c r="S182" s="21" t="inlineStr">
@@ -19686,13 +19672,13 @@
       </c>
       <c r="N183" s="52" t="n"/>
       <c r="O183" s="29" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="P183" s="29" t="n">
-        <v>34.2</v>
+        <v>34.7</v>
       </c>
       <c r="Q183" s="29" t="n">
-        <v>27.31</v>
+        <v>27.58</v>
       </c>
       <c r="R183" s="46" t="n"/>
       <c r="S183" s="21" t="inlineStr">
@@ -19799,13 +19785,13 @@
       </c>
       <c r="N184" s="52" t="n"/>
       <c r="O184" s="29" t="n">
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="P184" s="29" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="Q184" s="29" t="n">
-        <v>12.7</v>
+        <v>12.69</v>
       </c>
       <c r="R184" s="46" t="n"/>
       <c r="S184" s="21" t="inlineStr">
@@ -20101,15 +20087,9 @@
         </is>
       </c>
       <c r="N187" s="52" t="n"/>
-      <c r="O187" s="29" t="n">
-        <v>-12.6</v>
-      </c>
-      <c r="P187" s="29" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="Q187" s="29" t="n">
-        <v>-8.4</v>
-      </c>
+      <c r="O187" s="29" t="n"/>
+      <c r="P187" s="29" t="n"/>
+      <c r="Q187" s="29" t="n"/>
       <c r="R187" s="46" t="n"/>
       <c r="S187" s="21" t="n"/>
       <c r="T187" s="33" t="n"/>
@@ -20206,15 +20186,9 @@
         </is>
       </c>
       <c r="N188" s="52" t="n"/>
-      <c r="O188" s="29" t="n">
-        <v>-18.4</v>
-      </c>
-      <c r="P188" s="29" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="Q188" s="29" t="n">
-        <v>-11.2</v>
-      </c>
+      <c r="O188" s="29" t="n"/>
+      <c r="P188" s="29" t="n"/>
+      <c r="Q188" s="29" t="n"/>
       <c r="R188" s="46" t="n"/>
       <c r="S188" s="21" t="n"/>
       <c r="T188" s="33" t="n"/>
@@ -20415,14 +20389,12 @@
         </is>
       </c>
       <c r="O190" s="29" t="n">
-        <v>-0.1</v>
+        <v>2.3</v>
       </c>
       <c r="P190" s="29" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Q190" s="29" t="n">
-        <v>9.34</v>
-      </c>
+        <v>14.5</v>
+      </c>
+      <c r="Q190" s="29" t="n"/>
       <c r="R190" s="46" t="inlineStr">
         <is>
           <t>2010-01-05</t>
@@ -20523,12 +20495,8 @@
         </is>
       </c>
       <c r="N191" s="52" t="n"/>
-      <c r="O191" s="29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P191" s="29" t="n">
-        <v>10</v>
-      </c>
+      <c r="O191" s="29" t="n"/>
+      <c r="P191" s="29" t="n"/>
       <c r="Q191" s="29" t="n"/>
       <c r="R191" s="46" t="n"/>
       <c r="S191" s="21" t="n"/>
@@ -20630,12 +20598,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O192" s="29" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="P192" s="29" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="O192" s="29" t="n"/>
+      <c r="P192" s="29" t="n"/>
       <c r="Q192" s="29" t="n"/>
       <c r="R192" s="46" t="n"/>
       <c r="S192" s="21" t="n"/>
@@ -20742,13 +20706,13 @@
         </is>
       </c>
       <c r="O193" s="29" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="P193" s="29" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="Q193" s="29" t="n">
-        <v>5.1</v>
+        <v>3.68</v>
       </c>
       <c r="R193" s="46" t="n"/>
       <c r="S193" s="21" t="n"/>
@@ -20950,13 +20914,13 @@
       </c>
       <c r="N195" s="52" t="n"/>
       <c r="O195" s="29" t="n">
-        <v>-10</v>
+        <v>-8.1</v>
       </c>
       <c r="P195" s="29" t="n">
-        <v>8.300000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="Q195" s="29" t="n">
-        <v>-1.16</v>
+        <v>1.25</v>
       </c>
       <c r="R195" s="46" t="n"/>
       <c r="S195" s="21" t="n"/>
@@ -21650,12 +21614,8 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="O202" s="29" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="P202" s="29" t="n">
-        <v>4.2</v>
-      </c>
+      <c r="O202" s="29" t="n"/>
+      <c r="P202" s="29" t="n"/>
       <c r="Q202" s="29" t="n"/>
       <c r="R202" s="46" t="n"/>
       <c r="S202" s="21" t="n"/>
@@ -21757,12 +21717,8 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="O203" s="29" t="n">
-        <v>-6</v>
-      </c>
-      <c r="P203" s="29" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="O203" s="29" t="n"/>
+      <c r="P203" s="29" t="n"/>
       <c r="Q203" s="29" t="n"/>
       <c r="R203" s="46" t="n"/>
       <c r="S203" s="21" t="n"/>
@@ -21868,12 +21824,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O204" s="29" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="P204" s="29" t="n">
-        <v>6.1</v>
-      </c>
+      <c r="O204" s="29" t="n"/>
+      <c r="P204" s="29" t="n"/>
       <c r="Q204" s="29" t="n"/>
       <c r="R204" s="46" t="inlineStr">
         <is>
@@ -22177,12 +22129,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O207" s="29" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="P207" s="29" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="O207" s="29" t="n"/>
+      <c r="P207" s="29" t="n"/>
       <c r="Q207" s="29" t="n"/>
       <c r="R207" s="46" t="n"/>
       <c r="S207" s="21" t="n"/>
@@ -22501,7 +22449,7 @@
         </is>
       </c>
       <c r="O210" s="29" t="n">
-        <v>-45</v>
+        <v>-45.5</v>
       </c>
       <c r="P210" s="29" t="n"/>
       <c r="Q210" s="29" t="n"/>
@@ -23077,13 +23025,13 @@
       </c>
       <c r="N216" s="52" t="n"/>
       <c r="O216" s="29" t="n">
-        <v>5.7</v>
+        <v>12.8</v>
       </c>
       <c r="P216" s="29" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="Q216" s="29" t="n">
-        <v>11.11</v>
+        <v>14.49</v>
       </c>
       <c r="R216" s="46" t="n"/>
       <c r="S216" s="21" t="inlineStr">
@@ -23481,13 +23429,13 @@
       </c>
       <c r="N220" s="52" t="n"/>
       <c r="O220" s="29" t="n">
-        <v>-0.6</v>
+        <v>-2.1</v>
       </c>
       <c r="P220" s="29" t="n">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="Q220" s="29" t="n">
-        <v>5.49</v>
+        <v>3.89</v>
       </c>
       <c r="R220" s="46" t="n"/>
       <c r="S220" s="21" t="inlineStr">
@@ -23691,13 +23639,13 @@
       </c>
       <c r="N222" s="52" t="n"/>
       <c r="O222" s="29" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="P222" s="29" t="n">
-        <v>11</v>
+        <v>8.1</v>
       </c>
       <c r="Q222" s="29" t="n">
-        <v>8.59</v>
+        <v>6</v>
       </c>
       <c r="R222" s="46" t="n"/>
       <c r="S222" s="21" t="inlineStr">
@@ -24097,13 +24045,13 @@
       </c>
       <c r="N226" s="52" t="n"/>
       <c r="O226" s="29" t="n">
-        <v>1.7</v>
+        <v>-2.4</v>
       </c>
       <c r="P226" s="29" t="n">
-        <v>10.1</v>
+        <v>12.5</v>
       </c>
       <c r="Q226" s="29" t="n">
-        <v>4.31</v>
+        <v>4.28</v>
       </c>
       <c r="R226" s="46" t="n"/>
       <c r="S226" s="21" t="inlineStr">
@@ -24404,13 +24352,13 @@
       </c>
       <c r="N229" s="52" t="n"/>
       <c r="O229" s="29" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="P229" s="29" t="n">
-        <v>9.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="Q229" s="29" t="n">
-        <v>7.73</v>
+        <v>4.29</v>
       </c>
       <c r="R229" s="46" t="n"/>
       <c r="S229" s="21" t="inlineStr">
@@ -24517,13 +24465,13 @@
       </c>
       <c r="N230" s="52" t="n"/>
       <c r="O230" s="29" t="n">
-        <v>-0.9</v>
+        <v>2.9</v>
       </c>
       <c r="P230" s="29" t="n">
-        <v>12.9</v>
+        <v>8</v>
       </c>
       <c r="Q230" s="29" t="n">
-        <v>5.51</v>
+        <v>5.44</v>
       </c>
       <c r="R230" s="46" t="n"/>
       <c r="S230" s="21" t="inlineStr">
@@ -25018,12 +24966,14 @@
         </is>
       </c>
       <c r="O235" s="29" t="n">
-        <v>-2.4</v>
+        <v>1.3</v>
       </c>
       <c r="P235" s="29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q235" s="29" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="Q235" s="29" t="n">
+        <v>2.67</v>
+      </c>
       <c r="R235" s="46" t="n"/>
       <c r="S235" s="21" t="inlineStr">
         <is>
@@ -27001,9 +26951,15 @@
         </is>
       </c>
       <c r="N256" s="52" t="n"/>
-      <c r="O256" s="29" t="n"/>
-      <c r="P256" s="29" t="n"/>
-      <c r="Q256" s="29" t="n"/>
+      <c r="O256" s="29" t="n">
+        <v>-24</v>
+      </c>
+      <c r="P256" s="29" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="Q256" s="29" t="n">
+        <v>-16.73</v>
+      </c>
       <c r="R256" s="46" t="n"/>
       <c r="S256" s="21" t="n"/>
       <c r="T256" s="33" t="n"/>
@@ -27380,13 +27336,13 @@
         </is>
       </c>
       <c r="O260" s="29" t="n">
-        <v>-13.9</v>
+        <v>-15.1</v>
       </c>
       <c r="P260" s="29" t="n">
-        <v>-2.6</v>
+        <v>-3.5</v>
       </c>
       <c r="Q260" s="29" t="n">
-        <v>-7.95</v>
+        <v>-7.3</v>
       </c>
       <c r="R260" s="46" t="n"/>
       <c r="S260" s="21" t="inlineStr">
@@ -27882,10 +27838,10 @@
         </is>
       </c>
       <c r="O265" s="29" t="n">
-        <v>-17.5</v>
+        <v>-19.5</v>
       </c>
       <c r="P265" s="29" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q265" s="29" t="n"/>
       <c r="R265" s="46" t="n"/>
@@ -28267,10 +28223,10 @@
         </is>
       </c>
       <c r="O269" s="29" t="n">
-        <v>-60.7</v>
+        <v>-65.8</v>
       </c>
       <c r="P269" s="29" t="n">
-        <v>-56.3</v>
+        <v>-52.5</v>
       </c>
       <c r="Q269" s="29" t="n"/>
       <c r="R269" s="46" t="n"/>
@@ -28463,13 +28419,13 @@
       </c>
       <c r="N271" s="52" t="n"/>
       <c r="O271" s="29" t="n">
-        <v>5.1</v>
+        <v>-0.5</v>
       </c>
       <c r="P271" s="29" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="Q271" s="29" t="n">
-        <v>8.32</v>
+        <v>5.72</v>
       </c>
       <c r="R271" s="46" t="n"/>
       <c r="S271" s="21" t="inlineStr">
@@ -28582,13 +28538,13 @@
         </is>
       </c>
       <c r="O272" s="29" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="P272" s="29" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="Q272" s="29" t="n">
-        <v>4.15</v>
+        <v>3.05</v>
       </c>
       <c r="R272" s="46" t="n"/>
       <c r="S272" s="21" t="inlineStr">
@@ -33585,12 +33541,8 @@
         </is>
       </c>
       <c r="N324" s="52" t="n"/>
-      <c r="O324" s="29" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="P324" s="29" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="O324" s="29" t="n"/>
+      <c r="P324" s="29" t="n"/>
       <c r="Q324" s="29" t="n"/>
       <c r="R324" s="46" t="n"/>
       <c r="S324" s="21" t="n"/>
@@ -34426,8 +34378,12 @@
         </is>
       </c>
       <c r="N333" s="52" t="n"/>
-      <c r="O333" s="29" t="n"/>
-      <c r="P333" s="29" t="n"/>
+      <c r="O333" s="29" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="P333" s="29" t="n">
+        <v>14.7</v>
+      </c>
       <c r="Q333" s="29" t="n"/>
       <c r="R333" s="46" t="n"/>
       <c r="S333" s="21" t="n"/>
@@ -35075,9 +35031,15 @@
         </is>
       </c>
       <c r="N340" s="52" t="n"/>
-      <c r="O340" s="29" t="n"/>
-      <c r="P340" s="29" t="n"/>
-      <c r="Q340" s="29" t="n"/>
+      <c r="O340" s="29" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P340" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q340" s="29" t="n">
+        <v>0.57</v>
+      </c>
       <c r="R340" s="46" t="n"/>
       <c r="S340" s="21" t="n"/>
       <c r="T340" s="33" t="n"/>
@@ -35174,9 +35136,15 @@
         </is>
       </c>
       <c r="N341" s="52" t="n"/>
-      <c r="O341" s="29" t="n"/>
-      <c r="P341" s="29" t="n"/>
-      <c r="Q341" s="29" t="n"/>
+      <c r="O341" s="29" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="P341" s="29" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Q341" s="29" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="R341" s="46" t="n"/>
       <c r="S341" s="21" t="n"/>
       <c r="T341" s="33" t="n"/>
@@ -35279,15 +35247,9 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O342" s="29" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="P342" s="29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q342" s="29" t="n">
-        <v>-3.14</v>
-      </c>
+      <c r="O342" s="29" t="n"/>
+      <c r="P342" s="29" t="n"/>
+      <c r="Q342" s="29" t="n"/>
       <c r="R342" s="46" t="n"/>
       <c r="S342" s="21" t="n"/>
       <c r="T342" s="33" t="n"/>
@@ -36287,15 +36249,9 @@
         </is>
       </c>
       <c r="N352" s="52" t="n"/>
-      <c r="O352" s="29" t="n">
-        <v>-16.6</v>
-      </c>
-      <c r="P352" s="29" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="Q352" s="29" t="n">
-        <v>-10</v>
-      </c>
+      <c r="O352" s="29" t="n"/>
+      <c r="P352" s="29" t="n"/>
+      <c r="Q352" s="29" t="n"/>
       <c r="R352" s="46" t="n"/>
       <c r="S352" s="21" t="n"/>
       <c r="T352" s="33" t="n"/>
@@ -36487,15 +36443,9 @@
         </is>
       </c>
       <c r="N354" s="52" t="n"/>
-      <c r="O354" s="29" t="n">
-        <v>-23</v>
-      </c>
-      <c r="P354" s="29" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="Q354" s="29" t="n">
-        <v>-11.7</v>
-      </c>
+      <c r="O354" s="29" t="n"/>
+      <c r="P354" s="29" t="n"/>
+      <c r="Q354" s="29" t="n"/>
       <c r="R354" s="46" t="n"/>
       <c r="S354" s="21" t="n"/>
       <c r="T354" s="33" t="n"/>
@@ -36592,15 +36542,9 @@
         </is>
       </c>
       <c r="N355" s="52" t="n"/>
-      <c r="O355" s="29" t="n">
-        <v>-19.7</v>
-      </c>
-      <c r="P355" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q355" s="29" t="n">
-        <v>-10.5</v>
-      </c>
+      <c r="O355" s="29" t="n"/>
+      <c r="P355" s="29" t="n"/>
+      <c r="Q355" s="29" t="n"/>
       <c r="R355" s="46" t="n"/>
       <c r="S355" s="21" t="n"/>
       <c r="T355" s="33" t="n"/>
@@ -38845,15 +38789,9 @@
         </is>
       </c>
       <c r="N378" s="52" t="n"/>
-      <c r="O378" s="29" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="P378" s="29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q378" s="29" t="n">
-        <v>-2.75</v>
-      </c>
+      <c r="O378" s="29" t="n"/>
+      <c r="P378" s="29" t="n"/>
+      <c r="Q378" s="29" t="n"/>
       <c r="R378" s="46" t="n"/>
       <c r="S378" s="21" t="n"/>
       <c r="T378" s="33" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -830,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="7" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="4" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="7" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="4" min="34" max="771"/>
-    <col width="12.59765625" customWidth="1" style="4" min="772" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="4" min="34" max="773"/>
+    <col width="12.59765625" customWidth="1" style="4" min="774" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="10">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="29" t="n">
-        <v>-1.8</v>
+        <v>0.1</v>
       </c>
       <c r="P2" s="29" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" s="29" t="n">
-        <v>3.04</v>
+        <v>2.21</v>
       </c>
       <c r="R2" s="45" t="n"/>
       <c r="S2" s="21" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="29" t="n">
-        <v>1.4</v>
+        <v>-0.5</v>
       </c>
       <c r="P3" s="29" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" s="29" t="n"/>
       <c r="R3" s="45" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="29" t="n">
-        <v>-2.3</v>
+        <v>-4.4</v>
       </c>
       <c r="P4" s="29" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q4" s="29" t="n"/>
       <c r="R4" s="45" t="inlineStr">
@@ -1381,8 +1381,12 @@
         </is>
       </c>
       <c r="N5" s="51" t="n"/>
-      <c r="O5" s="29" t="n"/>
-      <c r="P5" s="29" t="n"/>
+      <c r="O5" s="29" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P5" s="29" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="Q5" s="29" t="n"/>
       <c r="R5" s="45" t="n"/>
       <c r="S5" s="21" t="n"/>
@@ -1485,13 +1489,13 @@
         </is>
       </c>
       <c r="O6" s="29" t="n">
-        <v>-5.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="P6" s="29" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" s="29" t="n">
-        <v>-0.75</v>
+        <v>-4.39</v>
       </c>
       <c r="R6" s="47" t="inlineStr">
         <is>
@@ -1596,10 +1600,10 @@
         </is>
       </c>
       <c r="O7" s="29" t="n">
-        <v>-6</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="P7" s="29" t="n">
-        <v>2.5</v>
+        <v>-1.7</v>
       </c>
       <c r="Q7" s="29" t="n"/>
       <c r="R7" s="45" t="n"/>
@@ -1705,13 +1709,13 @@
       </c>
       <c r="N8" s="51" t="n"/>
       <c r="O8" s="29" t="n">
-        <v>-3.7</v>
+        <v>-2.4</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>10.2</v>
+        <v>5.1</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="R8" s="45" t="n"/>
       <c r="S8" s="21" t="inlineStr">
@@ -1818,13 +1822,13 @@
       </c>
       <c r="N9" s="51" t="n"/>
       <c r="O9" s="29" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>3.63</v>
+        <v>1.06</v>
       </c>
       <c r="R9" s="45" t="n"/>
       <c r="S9" s="21" t="inlineStr">
@@ -1939,13 +1943,13 @@
         </is>
       </c>
       <c r="O10" s="29" t="n">
-        <v>-1.7</v>
+        <v>-10.2</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>0.35</v>
+        <v>-4.63</v>
       </c>
       <c r="R10" s="45" t="n"/>
       <c r="S10" s="21" t="inlineStr">
@@ -2056,13 +2060,13 @@
         </is>
       </c>
       <c r="O11" s="29" t="n">
-        <v>-6.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>-2.49</v>
+        <v>-4.38</v>
       </c>
       <c r="R11" s="45" t="inlineStr">
         <is>
@@ -2173,13 +2177,13 @@
       </c>
       <c r="N12" s="51" t="n"/>
       <c r="O12" s="29" t="n">
-        <v>-0.9</v>
+        <v>-9</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>5.9</v>
+        <v>-0.1</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>0.99</v>
+        <v>-4.29</v>
       </c>
       <c r="R12" s="45" t="inlineStr">
         <is>
@@ -2294,13 +2298,13 @@
         </is>
       </c>
       <c r="O13" s="29" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>4.7</v>
+        <v>-1.6</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>-2.24</v>
+        <v>-5.19</v>
       </c>
       <c r="R13" s="45" t="inlineStr">
         <is>
@@ -2411,13 +2415,13 @@
       </c>
       <c r="N14" s="51" t="n"/>
       <c r="O14" s="29" t="n">
-        <v>-2.9</v>
+        <v>-3.5</v>
       </c>
       <c r="P14" s="29" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q14" s="29" t="n">
-        <v>2.04</v>
+        <v>-0.26</v>
       </c>
       <c r="R14" s="45" t="n"/>
       <c r="S14" s="21" t="inlineStr">
@@ -2528,13 +2532,13 @@
       </c>
       <c r="N15" s="51" t="n"/>
       <c r="O15" s="29" t="n">
-        <v>-8.199999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="P15" s="29" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" s="29" t="n">
-        <v>-2.41</v>
+        <v>-3.84</v>
       </c>
       <c r="R15" s="45" t="n"/>
       <c r="S15" s="21" t="inlineStr">
@@ -2639,13 +2643,13 @@
       </c>
       <c r="N16" s="51" t="n"/>
       <c r="O16" s="29" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.7</v>
       </c>
       <c r="P16" s="29" t="n">
-        <v>8.300000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>-0.74</v>
+        <v>-1.59</v>
       </c>
       <c r="R16" s="45" t="n"/>
       <c r="S16" s="21" t="n"/>
@@ -4223,8 +4227,12 @@
         </is>
       </c>
       <c r="N33" s="51" t="n"/>
-      <c r="O33" s="29" t="n"/>
-      <c r="P33" s="29" t="n"/>
+      <c r="O33" s="29" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="P33" s="29" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="Q33" s="29" t="n"/>
       <c r="R33" s="45" t="n"/>
       <c r="S33" s="21" t="n"/>
@@ -4587,9 +4595,15 @@
         </is>
       </c>
       <c r="N37" s="51" t="n"/>
-      <c r="O37" s="29" t="n"/>
-      <c r="P37" s="29" t="n"/>
-      <c r="Q37" s="29" t="n"/>
+      <c r="O37" s="29" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="P37" s="29" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="Q37" s="29" t="n">
+        <v>-6.46</v>
+      </c>
       <c r="R37" s="45" t="n"/>
       <c r="S37" s="21" t="n"/>
       <c r="T37" s="33" t="n"/>
@@ -4777,8 +4791,12 @@
         </is>
       </c>
       <c r="N39" s="51" t="n"/>
-      <c r="O39" s="29" t="n"/>
-      <c r="P39" s="29" t="n"/>
+      <c r="O39" s="29" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="P39" s="29" t="n">
+        <v>-4.7</v>
+      </c>
       <c r="Q39" s="29" t="n"/>
       <c r="R39" s="45" t="n"/>
       <c r="S39" s="21" t="n"/>
@@ -4876,9 +4894,15 @@
         </is>
       </c>
       <c r="N40" s="51" t="n"/>
-      <c r="O40" s="29" t="n"/>
-      <c r="P40" s="29" t="n"/>
-      <c r="Q40" s="29" t="n"/>
+      <c r="O40" s="29" t="n">
+        <v>-13</v>
+      </c>
+      <c r="P40" s="29" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q40" s="29" t="n">
+        <v>-8.1</v>
+      </c>
       <c r="R40" s="45" t="n"/>
       <c r="S40" s="21" t="n"/>
       <c r="T40" s="33" t="n"/>
@@ -4965,9 +4989,15 @@
         </is>
       </c>
       <c r="N41" s="51" t="n"/>
-      <c r="O41" s="29" t="n"/>
-      <c r="P41" s="29" t="n"/>
-      <c r="Q41" s="29" t="n"/>
+      <c r="O41" s="29" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="P41" s="29" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="Q41" s="29" t="n">
+        <v>-7.44</v>
+      </c>
       <c r="R41" s="45" t="n"/>
       <c r="S41" s="21" t="n"/>
       <c r="T41" s="33" t="n"/>
@@ -9422,12 +9452,8 @@
         </is>
       </c>
       <c r="N90" s="51" t="n"/>
-      <c r="O90" s="29" t="n">
-        <v>-10.8</v>
-      </c>
-      <c r="P90" s="29" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="O90" s="29" t="n"/>
+      <c r="P90" s="29" t="n"/>
       <c r="Q90" s="29" t="n"/>
       <c r="R90" s="45" t="n"/>
       <c r="S90" s="21" t="n"/>
@@ -10177,13 +10203,13 @@
         </is>
       </c>
       <c r="O98" s="29" t="n">
-        <v>-2.2</v>
+        <v>-6.8</v>
       </c>
       <c r="P98" s="29" t="n">
-        <v>1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="Q98" s="29" t="n">
-        <v>-0.67</v>
+        <v>-3.29</v>
       </c>
       <c r="R98" s="45" t="inlineStr">
         <is>
@@ -10607,13 +10633,13 @@
         </is>
       </c>
       <c r="O102" s="29" t="n">
-        <v>-13.9</v>
+        <v>-10.8</v>
       </c>
       <c r="P102" s="29" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q102" s="29" t="n">
-        <v>-6.08</v>
+        <v>-4.38</v>
       </c>
       <c r="R102" s="45" t="n"/>
       <c r="S102" s="21" t="inlineStr">
@@ -10729,13 +10755,13 @@
         </is>
       </c>
       <c r="O103" s="29" t="n">
-        <v>-12</v>
+        <v>-7.3</v>
       </c>
       <c r="P103" s="29" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="29" t="n">
-        <v>-5.7</v>
+        <v>-3.5</v>
       </c>
       <c r="R103" s="45" t="n"/>
       <c r="S103" s="21" t="inlineStr">
@@ -10949,13 +10975,13 @@
         </is>
       </c>
       <c r="O105" s="29" t="n">
-        <v>-1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="P105" s="29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q105" s="29" t="n">
-        <v>1.14</v>
+        <v>0.12</v>
       </c>
       <c r="R105" s="45" t="n"/>
       <c r="S105" s="21" t="inlineStr">
@@ -11169,13 +11195,13 @@
       </c>
       <c r="N107" s="51" t="n"/>
       <c r="O107" s="29" t="n">
-        <v>0.8</v>
+        <v>-1.8</v>
       </c>
       <c r="P107" s="29" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="Q107" s="29" t="n">
-        <v>3.56</v>
+        <v>1.99</v>
       </c>
       <c r="R107" s="45" t="n"/>
       <c r="S107" s="21" t="inlineStr">
@@ -11397,13 +11423,13 @@
       </c>
       <c r="N109" s="51" t="n"/>
       <c r="O109" s="29" t="n">
-        <v>-0.7</v>
+        <v>-6.2</v>
       </c>
       <c r="P109" s="29" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q109" s="29" t="n">
-        <v>2.02</v>
+        <v>-3.24</v>
       </c>
       <c r="R109" s="45" t="inlineStr">
         <is>
@@ -11922,13 +11948,13 @@
       </c>
       <c r="N114" s="51" t="n"/>
       <c r="O114" s="29" t="n">
-        <v>-4.3</v>
+        <v>-3.2</v>
       </c>
       <c r="P114" s="29" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="Q114" s="29" t="n">
-        <v>1.18</v>
+        <v>1.65</v>
       </c>
       <c r="R114" s="45" t="n"/>
       <c r="S114" s="21" t="inlineStr">
@@ -12035,13 +12061,13 @@
       </c>
       <c r="N115" s="51" t="n"/>
       <c r="O115" s="29" t="n">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
       <c r="P115" s="29" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q115" s="29" t="n">
-        <v>9.619999999999999</v>
+        <v>14.16</v>
       </c>
       <c r="R115" s="45" t="n"/>
       <c r="S115" s="21" t="inlineStr">
@@ -12271,13 +12297,13 @@
       </c>
       <c r="N117" s="51" t="n"/>
       <c r="O117" s="29" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="P117" s="29" t="n">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q117" s="29" t="n">
-        <v>6.22</v>
+        <v>5.59</v>
       </c>
       <c r="R117" s="45" t="n"/>
       <c r="S117" s="21" t="inlineStr">
@@ -12396,13 +12422,13 @@
       </c>
       <c r="N118" s="51" t="n"/>
       <c r="O118" s="29" t="n">
-        <v>2.6</v>
+        <v>-1.3</v>
       </c>
       <c r="P118" s="29" t="n">
-        <v>8.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q118" s="29" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="R118" s="45" t="n"/>
       <c r="S118" s="21" t="inlineStr">
@@ -12957,13 +12983,13 @@
       </c>
       <c r="N123" s="51" t="n"/>
       <c r="O123" s="29" t="n">
-        <v>-5.2</v>
+        <v>-12</v>
       </c>
       <c r="P123" s="29" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="Q123" s="29" t="n">
-        <v>-0.14</v>
+        <v>-3.76</v>
       </c>
       <c r="R123" s="45" t="n"/>
       <c r="S123" s="21" t="inlineStr">
@@ -13176,9 +13202,15 @@
         </is>
       </c>
       <c r="N125" s="51" t="n"/>
-      <c r="O125" s="29" t="n"/>
-      <c r="P125" s="29" t="n"/>
-      <c r="Q125" s="29" t="n"/>
+      <c r="O125" s="29" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="P125" s="29" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q125" s="29" t="n">
+        <v>-4.21</v>
+      </c>
       <c r="R125" s="45" t="n"/>
       <c r="S125" s="21" t="n"/>
       <c r="T125" s="33" t="inlineStr">
@@ -13292,13 +13324,13 @@
       </c>
       <c r="N126" s="51" t="n"/>
       <c r="O126" s="29" t="n">
-        <v>-11.3</v>
+        <v>-14.6</v>
       </c>
       <c r="P126" s="29" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q126" s="29" t="n">
-        <v>-4.15</v>
+        <v>-5.09</v>
       </c>
       <c r="R126" s="45" t="n"/>
       <c r="S126" s="21" t="inlineStr">
@@ -14030,15 +14062,9 @@
         </is>
       </c>
       <c r="N133" s="51" t="n"/>
-      <c r="O133" s="29" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="P133" s="29" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Q133" s="29" t="n">
-        <v>1.88</v>
-      </c>
+      <c r="O133" s="29" t="n"/>
+      <c r="P133" s="29" t="n"/>
+      <c r="Q133" s="29" t="n"/>
       <c r="R133" s="45" t="n"/>
       <c r="S133" s="21" t="n"/>
       <c r="T133" s="33" t="n"/>
@@ -14592,13 +14618,13 @@
       </c>
       <c r="N138" s="51" t="n"/>
       <c r="O138" s="29" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="P138" s="29" t="n">
-        <v>27.6</v>
+        <v>25.4</v>
       </c>
       <c r="Q138" s="29" t="n">
-        <v>21.73</v>
+        <v>20.96</v>
       </c>
       <c r="R138" s="45" t="n"/>
       <c r="S138" s="21" t="inlineStr">
@@ -14709,13 +14735,13 @@
       </c>
       <c r="N139" s="51" t="n"/>
       <c r="O139" s="29" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="P139" s="29" t="n">
-        <v>17.2</v>
+        <v>13.2</v>
       </c>
       <c r="Q139" s="29" t="n">
-        <v>12.8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R139" s="45" t="n"/>
       <c r="S139" s="21" t="inlineStr">
@@ -14937,13 +14963,13 @@
       </c>
       <c r="N141" s="51" t="n"/>
       <c r="O141" s="29" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="P141" s="29" t="n">
         <v>17.6</v>
       </c>
       <c r="Q141" s="29" t="n">
-        <v>7.47</v>
+        <v>9.01</v>
       </c>
       <c r="R141" s="45" t="n"/>
       <c r="S141" s="21" t="inlineStr">
@@ -15062,13 +15088,13 @@
       </c>
       <c r="N142" s="51" t="n"/>
       <c r="O142" s="29" t="n">
-        <v>6.3</v>
+        <v>9.1</v>
       </c>
       <c r="P142" s="29" t="n">
-        <v>21.9</v>
+        <v>27.2</v>
       </c>
       <c r="Q142" s="29" t="n">
-        <v>13.62</v>
+        <v>17.03</v>
       </c>
       <c r="R142" s="45" t="n"/>
       <c r="S142" s="21" t="inlineStr">
@@ -15175,13 +15201,13 @@
       </c>
       <c r="N143" s="51" t="n"/>
       <c r="O143" s="29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P143" s="29" t="n">
-        <v>23.4</v>
+        <v>17.2</v>
       </c>
       <c r="Q143" s="29" t="n">
-        <v>12.69</v>
+        <v>11.03</v>
       </c>
       <c r="R143" s="45" t="n"/>
       <c r="S143" s="21" t="inlineStr">
@@ -15296,13 +15322,13 @@
       </c>
       <c r="N144" s="51" t="n"/>
       <c r="O144" s="29" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="P144" s="29" t="n">
-        <v>24.1</v>
+        <v>24.6</v>
       </c>
       <c r="Q144" s="29" t="n">
-        <v>13.14</v>
+        <v>14.65</v>
       </c>
       <c r="R144" s="45" t="n"/>
       <c r="S144" s="21" t="inlineStr">
@@ -15417,13 +15443,13 @@
       </c>
       <c r="N145" s="51" t="n"/>
       <c r="O145" s="29" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="P145" s="29" t="n">
-        <v>18.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q145" s="29" t="n">
-        <v>8.56</v>
+        <v>4.56</v>
       </c>
       <c r="R145" s="45" t="n"/>
       <c r="S145" s="21" t="inlineStr">
@@ -15538,13 +15564,13 @@
       </c>
       <c r="N146" s="51" t="n"/>
       <c r="O146" s="29" t="n">
-        <v>11.8</v>
+        <v>20.1</v>
       </c>
       <c r="P146" s="29" t="n">
-        <v>24.9</v>
+        <v>28.2</v>
       </c>
       <c r="Q146" s="29" t="n">
-        <v>18.59</v>
+        <v>23.16</v>
       </c>
       <c r="R146" s="45" t="n"/>
       <c r="S146" s="21" t="inlineStr">
@@ -15655,13 +15681,13 @@
       </c>
       <c r="N147" s="51" t="n"/>
       <c r="O147" s="29" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="P147" s="29" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="Q147" s="29" t="n">
-        <v>19.93</v>
+        <v>21.04</v>
       </c>
       <c r="R147" s="45" t="n"/>
       <c r="S147" s="21" t="inlineStr">
@@ -15772,13 +15798,13 @@
       </c>
       <c r="N148" s="51" t="n"/>
       <c r="O148" s="29" t="n">
-        <v>12.4</v>
+        <v>14.6</v>
       </c>
       <c r="P148" s="29" t="n">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
       <c r="Q148" s="29" t="n">
-        <v>18.24</v>
+        <v>19.29</v>
       </c>
       <c r="R148" s="45" t="n"/>
       <c r="S148" s="21" t="inlineStr">
@@ -15996,13 +16022,13 @@
       </c>
       <c r="N150" s="51" t="n"/>
       <c r="O150" s="29" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="P150" s="29" t="n">
-        <v>24.8</v>
+        <v>21</v>
       </c>
       <c r="Q150" s="29" t="n">
-        <v>21.15</v>
+        <v>19.5</v>
       </c>
       <c r="R150" s="45" t="n"/>
       <c r="S150" s="21" t="inlineStr">
@@ -16113,13 +16139,13 @@
       </c>
       <c r="N151" s="51" t="n"/>
       <c r="O151" s="29" t="n">
-        <v>19.8</v>
+        <v>20.7</v>
       </c>
       <c r="P151" s="29" t="n">
-        <v>27.8</v>
+        <v>24.5</v>
       </c>
       <c r="Q151" s="29" t="n">
-        <v>23.85</v>
+        <v>21.94</v>
       </c>
       <c r="R151" s="45" t="n"/>
       <c r="S151" s="21" t="inlineStr">
@@ -16230,13 +16256,13 @@
       </c>
       <c r="N152" s="51" t="n"/>
       <c r="O152" s="29" t="n">
-        <v>14.1</v>
+        <v>18.9</v>
       </c>
       <c r="P152" s="29" t="n">
-        <v>26</v>
+        <v>22.1</v>
       </c>
       <c r="Q152" s="29" t="n">
-        <v>20.04</v>
+        <v>20.01</v>
       </c>
       <c r="R152" s="45" t="n"/>
       <c r="S152" s="21" t="inlineStr">
@@ -16347,13 +16373,13 @@
       </c>
       <c r="N153" s="51" t="n"/>
       <c r="O153" s="29" t="n">
-        <v>14.8</v>
+        <v>17.6</v>
       </c>
       <c r="P153" s="29" t="n">
-        <v>24.5</v>
+        <v>22.2</v>
       </c>
       <c r="Q153" s="29" t="n">
-        <v>19.94</v>
+        <v>19.75</v>
       </c>
       <c r="R153" s="45" t="n"/>
       <c r="S153" s="21" t="inlineStr">
@@ -16464,13 +16490,13 @@
       </c>
       <c r="N154" s="51" t="n"/>
       <c r="O154" s="29" t="n">
-        <v>19.6</v>
+        <v>17.8</v>
       </c>
       <c r="P154" s="29" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="Q154" s="29" t="n">
-        <v>22.51</v>
+        <v>21.26</v>
       </c>
       <c r="R154" s="45" t="n"/>
       <c r="S154" s="21" t="inlineStr">
@@ -16684,13 +16710,13 @@
       </c>
       <c r="N156" s="51" t="n"/>
       <c r="O156" s="29" t="n">
-        <v>24.1</v>
+        <v>22.3</v>
       </c>
       <c r="P156" s="29" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="Q156" s="29" t="n">
-        <v>25.21</v>
+        <v>24.68</v>
       </c>
       <c r="R156" s="45" t="n"/>
       <c r="S156" s="21" t="inlineStr">
@@ -16801,13 +16827,13 @@
       </c>
       <c r="N157" s="51" t="n"/>
       <c r="O157" s="29" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="P157" s="29" t="n">
-        <v>32.7</v>
+        <v>30.8</v>
       </c>
       <c r="Q157" s="29" t="n">
-        <v>26.49</v>
+        <v>26.3</v>
       </c>
       <c r="R157" s="45" t="n"/>
       <c r="S157" s="21" t="inlineStr">
@@ -17120,13 +17146,13 @@
       </c>
       <c r="N160" s="51" t="n"/>
       <c r="O160" s="29" t="n">
-        <v>25.9</v>
+        <v>25.2</v>
       </c>
       <c r="P160" s="29" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="Q160" s="29" t="n">
-        <v>28.79</v>
+        <v>28.01</v>
       </c>
       <c r="R160" s="45" t="n"/>
       <c r="S160" s="21" t="inlineStr">
@@ -17229,13 +17255,13 @@
       </c>
       <c r="N161" s="51" t="n"/>
       <c r="O161" s="29" t="n">
-        <v>23.2</v>
+        <v>24.1</v>
       </c>
       <c r="P161" s="29" t="n">
-        <v>34.6</v>
+        <v>32.2</v>
       </c>
       <c r="Q161" s="29" t="n">
-        <v>28.66</v>
+        <v>28.09</v>
       </c>
       <c r="R161" s="45" t="n"/>
       <c r="S161" s="21" t="inlineStr">
@@ -17346,13 +17372,13 @@
       </c>
       <c r="N162" s="51" t="n"/>
       <c r="O162" s="29" t="n">
-        <v>15.9</v>
+        <v>15.6</v>
       </c>
       <c r="P162" s="29" t="n">
-        <v>20.8</v>
+        <v>24.2</v>
       </c>
       <c r="Q162" s="29" t="n">
-        <v>17.25</v>
+        <v>18.95</v>
       </c>
       <c r="R162" s="45" t="n"/>
       <c r="S162" s="21" t="inlineStr">
@@ -17463,13 +17489,13 @@
       </c>
       <c r="N163" s="51" t="n"/>
       <c r="O163" s="29" t="n">
-        <v>17.3</v>
+        <v>19.1</v>
       </c>
       <c r="P163" s="29" t="n">
-        <v>24.9</v>
+        <v>25.9</v>
       </c>
       <c r="Q163" s="29" t="n">
-        <v>19.97</v>
+        <v>21.51</v>
       </c>
       <c r="R163" s="45" t="n"/>
       <c r="S163" s="21" t="inlineStr">
@@ -17583,10 +17609,10 @@
         <v>21.1</v>
       </c>
       <c r="P164" s="29" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q164" s="29" t="n">
-        <v>22.54</v>
+        <v>22.71</v>
       </c>
       <c r="R164" s="45" t="n"/>
       <c r="S164" s="21" t="inlineStr">
@@ -17788,13 +17814,13 @@
       </c>
       <c r="N166" s="51" t="n"/>
       <c r="O166" s="29" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="P166" s="29" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="Q166" s="29" t="n">
-        <v>21.45</v>
+        <v>20.14</v>
       </c>
       <c r="R166" s="45" t="n"/>
       <c r="S166" s="21" t="inlineStr">
@@ -17909,13 +17935,13 @@
       </c>
       <c r="N167" s="51" t="n"/>
       <c r="O167" s="29" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P167" s="29" t="n">
-        <v>17.7</v>
+        <v>18.4</v>
       </c>
       <c r="Q167" s="29" t="n">
-        <v>8.91</v>
+        <v>9.4</v>
       </c>
       <c r="R167" s="45" t="n"/>
       <c r="S167" s="21" t="inlineStr">
@@ -18116,15 +18142,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O169" s="29" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="P169" s="29" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="Q169" s="29" t="n">
-        <v>5.33</v>
-      </c>
+      <c r="O169" s="29" t="n"/>
+      <c r="P169" s="29" t="n"/>
+      <c r="Q169" s="29" t="n"/>
       <c r="R169" s="45" t="n"/>
       <c r="S169" s="21" t="n"/>
       <c r="T169" s="33" t="n"/>
@@ -18507,13 +18527,13 @@
       </c>
       <c r="N173" s="51" t="n"/>
       <c r="O173" s="29" t="n">
-        <v>-4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="P173" s="29" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="Q173" s="29" t="n">
-        <v>-1.59</v>
+        <v>-1.06</v>
       </c>
       <c r="R173" s="45" t="n"/>
       <c r="S173" s="21" t="inlineStr">
@@ -18620,13 +18640,13 @@
       </c>
       <c r="N174" s="51" t="n"/>
       <c r="O174" s="29" t="n">
-        <v>-3.1</v>
+        <v>-6.5</v>
       </c>
       <c r="P174" s="29" t="n">
-        <v>4.5</v>
+        <v>6.9</v>
       </c>
       <c r="Q174" s="29" t="n">
-        <v>-1.21</v>
+        <v>-0.9</v>
       </c>
       <c r="R174" s="45" t="n"/>
       <c r="S174" s="21" t="inlineStr">
@@ -18735,13 +18755,13 @@
       </c>
       <c r="N175" s="51" t="n"/>
       <c r="O175" s="29" t="n">
-        <v>6.4</v>
+        <v>11.3</v>
       </c>
       <c r="P175" s="29" t="n">
-        <v>23.7</v>
+        <v>26.3</v>
       </c>
       <c r="Q175" s="29" t="n">
-        <v>14.61</v>
+        <v>17.45</v>
       </c>
       <c r="R175" s="45" t="n"/>
       <c r="S175" s="21" t="inlineStr">
@@ -18840,13 +18860,13 @@
       </c>
       <c r="N176" s="51" t="n"/>
       <c r="O176" s="29" t="n">
-        <v>19.6</v>
+        <v>18.4</v>
       </c>
       <c r="P176" s="29" t="n">
-        <v>25</v>
+        <v>23.7</v>
       </c>
       <c r="Q176" s="29" t="n">
-        <v>21.9</v>
+        <v>20.89</v>
       </c>
       <c r="R176" s="45" t="n"/>
       <c r="S176" s="21" t="inlineStr">
@@ -18949,13 +18969,13 @@
       </c>
       <c r="N177" s="51" t="n"/>
       <c r="O177" s="29" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="P177" s="29" t="n">
-        <v>21.9</v>
+        <v>18</v>
       </c>
       <c r="Q177" s="29" t="n">
-        <v>12.9</v>
+        <v>10.91</v>
       </c>
       <c r="R177" s="45" t="n"/>
       <c r="S177" s="21" t="inlineStr">
@@ -19193,12 +19213,14 @@
         </is>
       </c>
       <c r="O179" s="29" t="n">
-        <v>-5.9</v>
+        <v>-8.5</v>
       </c>
       <c r="P179" s="29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q179" s="29" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="Q179" s="29" t="n">
+        <v>-2.98</v>
+      </c>
       <c r="R179" s="45" t="n"/>
       <c r="S179" s="21" t="inlineStr">
         <is>
@@ -19312,13 +19334,13 @@
       </c>
       <c r="N180" s="51" t="n"/>
       <c r="O180" s="29" t="n">
-        <v>-5.3</v>
+        <v>-0.8</v>
       </c>
       <c r="P180" s="29" t="n">
-        <v>10.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q180" s="29" t="n">
-        <v>2.55</v>
+        <v>1.49</v>
       </c>
       <c r="R180" s="45" t="n"/>
       <c r="S180" s="21" t="inlineStr">
@@ -19433,13 +19455,13 @@
       </c>
       <c r="N181" s="51" t="n"/>
       <c r="O181" s="29" t="n">
-        <v>10.1</v>
+        <v>12.7</v>
       </c>
       <c r="P181" s="29" t="n">
-        <v>25.1</v>
+        <v>27.5</v>
       </c>
       <c r="Q181" s="29" t="n">
-        <v>16.98</v>
+        <v>19.06</v>
       </c>
       <c r="R181" s="45" t="n"/>
       <c r="S181" s="21" t="inlineStr">
@@ -19546,13 +19568,13 @@
       </c>
       <c r="N182" s="51" t="n"/>
       <c r="O182" s="29" t="n">
-        <v>11.4</v>
+        <v>16.7</v>
       </c>
       <c r="P182" s="29" t="n">
-        <v>25.6</v>
+        <v>22.2</v>
       </c>
       <c r="Q182" s="29" t="n">
-        <v>18.51</v>
+        <v>19.46</v>
       </c>
       <c r="R182" s="45" t="n"/>
       <c r="S182" s="21" t="inlineStr">
@@ -19663,13 +19685,13 @@
       </c>
       <c r="N183" s="51" t="n"/>
       <c r="O183" s="29" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="P183" s="29" t="n">
-        <v>35.8</v>
+        <v>32.2</v>
       </c>
       <c r="Q183" s="29" t="n">
-        <v>27.96</v>
+        <v>26.11</v>
       </c>
       <c r="R183" s="45" t="n"/>
       <c r="S183" s="21" t="inlineStr">
@@ -19776,13 +19798,13 @@
       </c>
       <c r="N184" s="51" t="n"/>
       <c r="O184" s="29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P184" s="29" t="n">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="Q184" s="29" t="n">
-        <v>10.75</v>
+        <v>11.98</v>
       </c>
       <c r="R184" s="45" t="n"/>
       <c r="S184" s="21" t="inlineStr">
@@ -19979,15 +20001,9 @@
           <t>🔵</t>
         </is>
       </c>
-      <c r="O186" s="29" t="n">
-        <v>-13.7</v>
-      </c>
-      <c r="P186" s="29" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="Q186" s="29" t="n">
-        <v>-8.300000000000001</v>
-      </c>
+      <c r="O186" s="29" t="n"/>
+      <c r="P186" s="29" t="n"/>
+      <c r="Q186" s="29" t="n"/>
       <c r="R186" s="45" t="n"/>
       <c r="S186" s="21" t="n"/>
       <c r="T186" s="33" t="n"/>
@@ -20084,8 +20100,12 @@
         </is>
       </c>
       <c r="N187" s="51" t="n"/>
-      <c r="O187" s="29" t="n"/>
-      <c r="P187" s="29" t="n"/>
+      <c r="O187" s="29" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="P187" s="29" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="Q187" s="29" t="n"/>
       <c r="R187" s="45" t="n"/>
       <c r="S187" s="21" t="n"/>
@@ -20386,13 +20406,13 @@
         </is>
       </c>
       <c r="O190" s="29" t="n">
-        <v>-9.5</v>
+        <v>-6.3</v>
       </c>
       <c r="P190" s="29" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="Q190" s="29" t="n">
-        <v>1.64</v>
+        <v>2.13</v>
       </c>
       <c r="R190" s="45" t="inlineStr">
         <is>
@@ -20495,10 +20515,10 @@
       </c>
       <c r="N191" s="51" t="n"/>
       <c r="O191" s="29" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="P191" s="29" t="n">
-        <v>16.1</v>
+        <v>13.6</v>
       </c>
       <c r="Q191" s="29" t="n"/>
       <c r="R191" s="45" t="n"/>
@@ -20709,13 +20729,13 @@
         </is>
       </c>
       <c r="O193" s="29" t="n">
-        <v>-12.2</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P193" s="29" t="n">
-        <v>-8.300000000000001</v>
+        <v>-3.2</v>
       </c>
       <c r="Q193" s="29" t="n">
-        <v>-10.19</v>
+        <v>-5.65</v>
       </c>
       <c r="R193" s="45" t="n"/>
       <c r="S193" s="21" t="n"/>
@@ -21213,12 +21233,8 @@
         </is>
       </c>
       <c r="N198" s="51" t="n"/>
-      <c r="O198" s="29" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="P198" s="29" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="O198" s="29" t="n"/>
+      <c r="P198" s="29" t="n"/>
       <c r="Q198" s="29" t="n"/>
       <c r="R198" s="45" t="n"/>
       <c r="S198" s="21" t="n"/>
@@ -21512,12 +21528,8 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O201" s="29" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="P201" s="29" t="n">
-        <v>4.4</v>
-      </c>
+      <c r="O201" s="29" t="n"/>
+      <c r="P201" s="29" t="n"/>
       <c r="Q201" s="29" t="n"/>
       <c r="R201" s="45" t="n"/>
       <c r="S201" s="21" t="n"/>
@@ -21620,10 +21632,10 @@
         </is>
       </c>
       <c r="O202" s="29" t="n">
-        <v>-13.9</v>
+        <v>-16.7</v>
       </c>
       <c r="P202" s="29" t="n">
-        <v>3.8</v>
+        <v>8.9</v>
       </c>
       <c r="Q202" s="29" t="n"/>
       <c r="R202" s="45" t="n"/>
@@ -21727,10 +21739,10 @@
         </is>
       </c>
       <c r="O203" s="29" t="n">
-        <v>-7.8</v>
+        <v>-15.9</v>
       </c>
       <c r="P203" s="29" t="n">
-        <v>3.9</v>
+        <v>6.9</v>
       </c>
       <c r="Q203" s="29" t="n"/>
       <c r="R203" s="45" t="n"/>
@@ -21837,8 +21849,12 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O204" s="29" t="n"/>
-      <c r="P204" s="29" t="n"/>
+      <c r="O204" s="29" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="P204" s="29" t="n">
+        <v>6</v>
+      </c>
       <c r="Q204" s="29" t="n"/>
       <c r="R204" s="45" t="inlineStr">
         <is>
@@ -22143,10 +22159,10 @@
         </is>
       </c>
       <c r="O207" s="29" t="n">
-        <v>-5.7</v>
+        <v>-12.9</v>
       </c>
       <c r="P207" s="29" t="n">
-        <v>-0.4</v>
+        <v>-2.1</v>
       </c>
       <c r="Q207" s="29" t="n"/>
       <c r="R207" s="45" t="n"/>
@@ -22465,7 +22481,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O210" s="29" t="n"/>
+      <c r="O210" s="29" t="n">
+        <v>-42.7</v>
+      </c>
       <c r="P210" s="29" t="n"/>
       <c r="Q210" s="29" t="n"/>
       <c r="R210" s="45" t="n"/>
@@ -22556,9 +22574,7 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O211" s="29" t="n">
-        <v>-33.1</v>
-      </c>
+      <c r="O211" s="29" t="n"/>
       <c r="P211" s="29" t="n"/>
       <c r="Q211" s="29" t="n"/>
       <c r="R211" s="45" t="n"/>
@@ -23042,13 +23058,13 @@
       </c>
       <c r="N216" s="51" t="n"/>
       <c r="O216" s="29" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="P216" s="29" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="Q216" s="29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.41</v>
       </c>
       <c r="R216" s="45" t="n"/>
       <c r="S216" s="21" t="inlineStr">
@@ -23449,10 +23465,10 @@
         <v>0.2</v>
       </c>
       <c r="P220" s="29" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="Q220" s="29" t="n">
-        <v>3.04</v>
+        <v>2.58</v>
       </c>
       <c r="R220" s="45" t="n"/>
       <c r="S220" s="21" t="inlineStr">
@@ -23656,13 +23672,13 @@
       </c>
       <c r="N222" s="51" t="n"/>
       <c r="O222" s="29" t="n">
-        <v>0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="P222" s="29" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="Q222" s="29" t="n">
-        <v>2.2</v>
+        <v>0.91</v>
       </c>
       <c r="R222" s="45" t="n"/>
       <c r="S222" s="21" t="inlineStr">
@@ -24062,13 +24078,13 @@
       </c>
       <c r="N226" s="51" t="n"/>
       <c r="O226" s="29" t="n">
-        <v>-9.6</v>
+        <v>-2.7</v>
       </c>
       <c r="P226" s="29" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q226" s="29" t="n">
-        <v>-3.71</v>
+        <v>0.54</v>
       </c>
       <c r="R226" s="45" t="n"/>
       <c r="S226" s="21" t="inlineStr">
@@ -24369,13 +24385,13 @@
       </c>
       <c r="N229" s="51" t="n"/>
       <c r="O229" s="29" t="n">
-        <v>-2.2</v>
+        <v>-0.1</v>
       </c>
       <c r="P229" s="29" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="Q229" s="29" t="n">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="R229" s="45" t="n"/>
       <c r="S229" s="21" t="inlineStr">
@@ -24482,13 +24498,13 @@
       </c>
       <c r="N230" s="51" t="n"/>
       <c r="O230" s="29" t="n">
-        <v>1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="P230" s="29" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="Q230" s="29" t="n">
-        <v>4.92</v>
+        <v>2.04</v>
       </c>
       <c r="R230" s="45" t="n"/>
       <c r="S230" s="21" t="inlineStr">
@@ -24983,10 +24999,10 @@
         </is>
       </c>
       <c r="O235" s="29" t="n">
-        <v>-1.5</v>
+        <v>-2.2</v>
       </c>
       <c r="P235" s="29" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="Q235" s="29" t="n"/>
       <c r="R235" s="45" t="n"/>
@@ -27343,13 +27359,13 @@
       </c>
       <c r="N260" s="51" t="n"/>
       <c r="O260" s="29" t="n">
-        <v>-27.8</v>
+        <v>-28.2</v>
       </c>
       <c r="P260" s="29" t="n">
-        <v>-11.3</v>
+        <v>-11</v>
       </c>
       <c r="Q260" s="29" t="n">
-        <v>-20.98</v>
+        <v>-20.96</v>
       </c>
       <c r="R260" s="45" t="n"/>
       <c r="S260" s="21" t="n"/>
@@ -27444,13 +27460,13 @@
         </is>
       </c>
       <c r="O261" s="29" t="n">
-        <v>-11.9</v>
+        <v>-25.1</v>
       </c>
       <c r="P261" s="29" t="n">
-        <v>-7.8</v>
+        <v>-10.7</v>
       </c>
       <c r="Q261" s="29" t="n">
-        <v>-9.91</v>
+        <v>-18.45</v>
       </c>
       <c r="R261" s="45" t="n"/>
       <c r="S261" s="21" t="inlineStr">
@@ -27946,10 +27962,10 @@
         </is>
       </c>
       <c r="O266" s="29" t="n">
-        <v>-17.7</v>
+        <v>-23.3</v>
       </c>
       <c r="P266" s="29" t="n">
-        <v>-4.3</v>
+        <v>-4.1</v>
       </c>
       <c r="Q266" s="29" t="n"/>
       <c r="R266" s="45" t="n"/>
@@ -28331,10 +28347,10 @@
         </is>
       </c>
       <c r="O270" s="29" t="n">
-        <v>-63.3</v>
+        <v>-68.5</v>
       </c>
       <c r="P270" s="29" t="n">
-        <v>-52.8</v>
+        <v>-55.9</v>
       </c>
       <c r="Q270" s="29" t="n"/>
       <c r="R270" s="45" t="n"/>
@@ -28527,13 +28543,13 @@
       </c>
       <c r="N272" s="51" t="n"/>
       <c r="O272" s="29" t="n">
-        <v>5.8</v>
+        <v>-2.4</v>
       </c>
       <c r="P272" s="29" t="n">
-        <v>16.6</v>
+        <v>10</v>
       </c>
       <c r="Q272" s="29" t="n">
-        <v>10.01</v>
+        <v>2.79</v>
       </c>
       <c r="R272" s="45" t="n"/>
       <c r="S272" s="21" t="inlineStr">
@@ -28743,13 +28759,13 @@
         </is>
       </c>
       <c r="O274" s="29" t="n">
-        <v>-2.7</v>
+        <v>-3.9</v>
       </c>
       <c r="P274" s="29" t="n">
-        <v>2.2</v>
+        <v>-0.5</v>
       </c>
       <c r="Q274" s="29" t="n">
-        <v>-0.18</v>
+        <v>-2.55</v>
       </c>
       <c r="R274" s="45" t="n"/>
       <c r="S274" s="21" t="inlineStr">
@@ -29617,9 +29633,15 @@
         </is>
       </c>
       <c r="N283" s="51" t="n"/>
-      <c r="O283" s="29" t="n"/>
-      <c r="P283" s="29" t="n"/>
-      <c r="Q283" s="29" t="n"/>
+      <c r="O283" s="29" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="P283" s="29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Q283" s="29" t="n">
+        <v>-3.1</v>
+      </c>
       <c r="R283" s="45" t="n"/>
       <c r="S283" s="21" t="n"/>
       <c r="T283" s="33" t="n"/>
@@ -33304,7 +33326,7 @@
           <t>呼伦贝尔市</t>
         </is>
       </c>
-      <c r="AB321" s="3" t="inlineStr">
+      <c r="AB321" s="26" t="inlineStr">
         <is>
           <t>根河市</t>
         </is>
@@ -33746,8 +33768,12 @@
         </is>
       </c>
       <c r="N326" s="51" t="n"/>
-      <c r="O326" s="29" t="n"/>
-      <c r="P326" s="29" t="n"/>
+      <c r="O326" s="29" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="P326" s="29" t="n">
+        <v>5.8</v>
+      </c>
       <c r="Q326" s="29" t="n"/>
       <c r="R326" s="45" t="n"/>
       <c r="S326" s="21" t="n"/>
@@ -34025,15 +34051,9 @@
         </is>
       </c>
       <c r="N329" s="51" t="n"/>
-      <c r="O329" s="29" t="n">
-        <v>-11.2</v>
-      </c>
-      <c r="P329" s="29" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Q329" s="29" t="n">
-        <v>-1.96</v>
-      </c>
+      <c r="O329" s="29" t="n"/>
+      <c r="P329" s="29" t="n"/>
+      <c r="Q329" s="29" t="n"/>
       <c r="R329" s="45" t="n"/>
       <c r="S329" s="21" t="n"/>
       <c r="T329" s="33" t="n"/>
@@ -35238,12 +35258,8 @@
         </is>
       </c>
       <c r="N342" s="51" t="n"/>
-      <c r="O342" s="29" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="P342" s="29" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="O342" s="29" t="n"/>
+      <c r="P342" s="29" t="n"/>
       <c r="Q342" s="29" t="n"/>
       <c r="R342" s="45" t="n"/>
       <c r="S342" s="21" t="n"/>
@@ -35640,12 +35656,8 @@
         </is>
       </c>
       <c r="N346" s="51" t="n"/>
-      <c r="O346" s="29" t="n">
-        <v>-15.4</v>
-      </c>
-      <c r="P346" s="29" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="O346" s="29" t="n"/>
+      <c r="P346" s="29" t="n"/>
       <c r="Q346" s="29" t="n"/>
       <c r="R346" s="45" t="n"/>
       <c r="S346" s="21" t="n"/>
@@ -36847,13 +36859,13 @@
       </c>
       <c r="N358" s="51" t="n"/>
       <c r="O358" s="29" t="n">
-        <v>-21.7</v>
+        <v>-23.7</v>
       </c>
       <c r="P358" s="29" t="n">
-        <v>1.5</v>
+        <v>-0.4</v>
       </c>
       <c r="Q358" s="29" t="n">
-        <v>-13</v>
+        <v>-12.6</v>
       </c>
       <c r="R358" s="45" t="n"/>
       <c r="S358" s="21" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="极寒收集" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'站点信息和记录'!$A$1:$AI$435</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'站点信息和记录'!$A$1:$AI$436</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\ &quot;年&quot;\ m\ &quot;月&quot;\ d\ &quot;日&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -168,14 +168,6 @@
       <family val="3"/>
       <color theme="0"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <family val="1"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -812,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI435"/>
+  <dimension ref="A1:AI436"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.59765625" defaultRowHeight="20.25"/>
   <cols>
     <col width="4.59765625" customWidth="1" style="4" min="1" max="1"/>
@@ -838,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="7" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="4" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="7" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="4" min="34" max="774"/>
-    <col width="12.59765625" customWidth="1" style="4" min="775" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="4" min="34" max="777"/>
+    <col width="12.59765625" customWidth="1" style="4" min="778" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="10">
@@ -1073,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="29" t="n">
-        <v>-6.4</v>
+        <v>-8</v>
       </c>
       <c r="P2" s="29" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" s="29" t="n">
-        <v>-0.58</v>
+        <v>-2.44</v>
       </c>
       <c r="R2" s="45" t="n"/>
       <c r="S2" s="21" t="inlineStr">
@@ -1180,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="29" t="n">
-        <v>-4.8</v>
+        <v>-10.7</v>
       </c>
       <c r="P3" s="29" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" s="29" t="n"/>
       <c r="R3" s="45" t="inlineStr">
@@ -1289,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="29" t="n">
-        <v>-7</v>
+        <v>-19.4</v>
       </c>
       <c r="P4" s="29" t="n">
-        <v>-2.6</v>
+        <v>-5.5</v>
       </c>
       <c r="Q4" s="29" t="n"/>
       <c r="R4" s="45" t="inlineStr">
@@ -1493,13 +1485,13 @@
         </is>
       </c>
       <c r="O6" s="29" t="n">
-        <v>-10.1</v>
+        <v>-20.9</v>
       </c>
       <c r="P6" s="29" t="n">
-        <v>-1.2</v>
+        <v>-7.5</v>
       </c>
       <c r="Q6" s="29" t="n">
-        <v>-6.8</v>
+        <v>-13.99</v>
       </c>
       <c r="R6" s="47" t="inlineStr">
         <is>
@@ -1604,10 +1596,10 @@
         </is>
       </c>
       <c r="O7" s="29" t="n">
-        <v>-5.9</v>
+        <v>-17</v>
       </c>
       <c r="P7" s="29" t="n">
-        <v>-2.6</v>
+        <v>-5.1</v>
       </c>
       <c r="Q7" s="29" t="n"/>
       <c r="R7" s="45" t="n"/>
@@ -1713,13 +1705,13 @@
       </c>
       <c r="N8" s="51" t="n"/>
       <c r="O8" s="29" t="n">
-        <v>-5.8</v>
+        <v>-4.9</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>-0.3</v>
+        <v>1.1</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>-2.18</v>
+        <v>-2.34</v>
       </c>
       <c r="R8" s="45" t="n"/>
       <c r="S8" s="21" t="inlineStr">
@@ -1826,13 +1818,13 @@
       </c>
       <c r="N9" s="51" t="n"/>
       <c r="O9" s="29" t="n">
-        <v>-7.2</v>
+        <v>-9.4</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>-2.55</v>
+        <v>-4.96</v>
       </c>
       <c r="R9" s="45" t="n"/>
       <c r="S9" s="21" t="inlineStr">
@@ -1947,12 +1939,14 @@
         </is>
       </c>
       <c r="O10" s="29" t="n">
-        <v>-6</v>
+        <v>-21.4</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="Q10" s="29" t="n"/>
+        <v>-5</v>
+      </c>
+      <c r="Q10" s="29" t="n">
+        <v>-12.29</v>
+      </c>
       <c r="R10" s="45" t="n"/>
       <c r="S10" s="21" t="inlineStr">
         <is>
@@ -2062,13 +2056,13 @@
         </is>
       </c>
       <c r="O11" s="29" t="n">
-        <v>-14.6</v>
+        <v>-25.7</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>-9.550000000000001</v>
+        <v>-16.78</v>
       </c>
       <c r="R11" s="45" t="inlineStr">
         <is>
@@ -2179,13 +2173,13 @@
       </c>
       <c r="N12" s="51" t="n"/>
       <c r="O12" s="29" t="n">
-        <v>-7.8</v>
+        <v>-15.3</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>-3.3</v>
+        <v>-5.8</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>-5.4</v>
+        <v>-10.79</v>
       </c>
       <c r="R12" s="45" t="inlineStr">
         <is>
@@ -2300,13 +2294,13 @@
         </is>
       </c>
       <c r="O13" s="29" t="n">
-        <v>-6.8</v>
+        <v>-16.9</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>-3.2</v>
+        <v>-4.4</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>-5.59</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="R13" s="45" t="inlineStr">
         <is>
@@ -2417,13 +2411,13 @@
       </c>
       <c r="N14" s="51" t="n"/>
       <c r="O14" s="29" t="n">
-        <v>-2.5</v>
+        <v>-6.3</v>
       </c>
       <c r="P14" s="29" t="n">
-        <v>7.1</v>
+        <v>-1.8</v>
       </c>
       <c r="Q14" s="29" t="n">
-        <v>0.91</v>
+        <v>-4.26</v>
       </c>
       <c r="R14" s="45" t="n"/>
       <c r="S14" s="21" t="inlineStr">
@@ -2534,13 +2528,13 @@
       </c>
       <c r="N15" s="51" t="n"/>
       <c r="O15" s="29" t="n">
-        <v>-7.1</v>
+        <v>-9</v>
       </c>
       <c r="P15" s="29" t="n">
-        <v>3.2</v>
+        <v>-2.6</v>
       </c>
       <c r="Q15" s="29" t="n">
-        <v>-2.49</v>
+        <v>-5.45</v>
       </c>
       <c r="R15" s="45" t="n"/>
       <c r="S15" s="21" t="inlineStr">
@@ -2645,13 +2639,13 @@
       </c>
       <c r="N16" s="51" t="n"/>
       <c r="O16" s="29" t="n">
-        <v>-6.6</v>
+        <v>-10.4</v>
       </c>
       <c r="P16" s="29" t="n">
-        <v>8</v>
+        <v>-0.6</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>1.2</v>
+        <v>-4.4</v>
       </c>
       <c r="R16" s="45" t="n"/>
       <c r="S16" s="21" t="n"/>
@@ -3769,10 +3763,10 @@
       </c>
       <c r="N28" s="51" t="n"/>
       <c r="O28" s="29" t="n">
-        <v>-16</v>
+        <v>-19.1</v>
       </c>
       <c r="P28" s="29" t="n">
-        <v>-8.5</v>
+        <v>-0.8</v>
       </c>
       <c r="Q28" s="29" t="n"/>
       <c r="R28" s="45" t="n"/>
@@ -4318,8 +4312,12 @@
         </is>
       </c>
       <c r="N34" s="51" t="n"/>
-      <c r="O34" s="29" t="n"/>
-      <c r="P34" s="29" t="n"/>
+      <c r="O34" s="29" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="P34" s="29" t="n">
+        <v>-5.4</v>
+      </c>
       <c r="Q34" s="29" t="n"/>
       <c r="R34" s="45" t="n"/>
       <c r="S34" s="21" t="n"/>
@@ -6065,15 +6063,9 @@
         </is>
       </c>
       <c r="N53" s="51" t="n"/>
-      <c r="O53" s="29" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="P53" s="29" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="Q53" s="29" t="n">
-        <v>-7.99</v>
-      </c>
+      <c r="O53" s="29" t="n"/>
+      <c r="P53" s="29" t="n"/>
+      <c r="Q53" s="29" t="n"/>
       <c r="R53" s="45" t="n"/>
       <c r="S53" s="21" t="n"/>
       <c r="T53" s="33" t="n"/>
@@ -6123,7 +6115,7 @@
     </row>
     <row r="54" ht="24" customHeight="1" s="54">
       <c r="A54" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="41" t="n"/>
@@ -6212,7 +6204,7 @@
     </row>
     <row r="55" ht="24" customHeight="1" s="54">
       <c r="A55" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="41" t="n"/>
@@ -6301,7 +6293,7 @@
     </row>
     <row r="56" ht="24" customHeight="1" s="54">
       <c r="A56" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
@@ -6402,7 +6394,7 @@
     </row>
     <row r="57" ht="24" customHeight="1" s="54">
       <c r="A57" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="41" t="n"/>
@@ -6491,7 +6483,7 @@
     </row>
     <row r="58" ht="24" customHeight="1" s="54">
       <c r="A58" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="41" t="n"/>
@@ -6576,7 +6568,7 @@
     </row>
     <row r="59" ht="24" customHeight="1" s="54">
       <c r="A59" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="41" t="n"/>
@@ -6661,7 +6653,7 @@
     </row>
     <row r="60" ht="24" customHeight="1" s="54">
       <c r="A60" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="41" t="n"/>
@@ -6750,7 +6742,7 @@
     </row>
     <row r="61" ht="24" customHeight="1" s="54">
       <c r="A61" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="41" t="n"/>
@@ -6839,7 +6831,7 @@
     </row>
     <row r="62" ht="24" customHeight="1" s="54">
       <c r="A62" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
@@ -6942,7 +6934,7 @@
     </row>
     <row r="63" ht="24" customHeight="1" s="54">
       <c r="A63" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="41" t="n"/>
@@ -7031,7 +7023,7 @@
     </row>
     <row r="64" ht="24" customHeight="1" s="54">
       <c r="A64" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="41" t="n"/>
@@ -7120,7 +7112,7 @@
     </row>
     <row r="65" ht="24" customHeight="1" s="54">
       <c r="A65" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="41" t="n"/>
@@ -7205,7 +7197,7 @@
     </row>
     <row r="66" ht="24" customHeight="1" s="54">
       <c r="A66" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="41" t="n"/>
@@ -7239,10 +7231,10 @@
       </c>
       <c r="N66" s="51" t="n"/>
       <c r="O66" s="29" t="n">
-        <v>-16.6</v>
+        <v>-23.6</v>
       </c>
       <c r="P66" s="29" t="n">
-        <v>-3.2</v>
+        <v>-10.9</v>
       </c>
       <c r="Q66" s="29" t="n"/>
       <c r="R66" s="45" t="n"/>
@@ -7298,7 +7290,7 @@
     </row>
     <row r="67" ht="24" customHeight="1" s="54">
       <c r="A67" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="41" t="n"/>
@@ -7331,8 +7323,12 @@
         </is>
       </c>
       <c r="N67" s="51" t="n"/>
-      <c r="O67" s="29" t="n"/>
-      <c r="P67" s="29" t="n"/>
+      <c r="O67" s="29" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="P67" s="29" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="Q67" s="29" t="n"/>
       <c r="R67" s="45" t="n"/>
       <c r="S67" s="21" t="n"/>
@@ -7387,7 +7383,7 @@
     </row>
     <row r="68" ht="24" customHeight="1" s="54">
       <c r="A68" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="41" t="n"/>
@@ -7476,7 +7472,7 @@
     </row>
     <row r="69" ht="24" customHeight="1" s="54">
       <c r="A69" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="41" t="n"/>
@@ -7571,7 +7567,7 @@
     </row>
     <row r="70" ht="24" customHeight="1" s="54">
       <c r="A70" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="41" t="n"/>
@@ -7660,7 +7656,7 @@
     </row>
     <row r="71" ht="24" customHeight="1" s="54">
       <c r="A71" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="41" t="n"/>
@@ -7693,12 +7689,8 @@
         </is>
       </c>
       <c r="N71" s="51" t="n"/>
-      <c r="O71" s="29" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="P71" s="29" t="n">
-        <v>-3.6</v>
-      </c>
+      <c r="O71" s="29" t="n"/>
+      <c r="P71" s="29" t="n"/>
       <c r="Q71" s="29" t="n"/>
       <c r="R71" s="45" t="n"/>
       <c r="S71" s="21" t="n"/>
@@ -7757,7 +7749,7 @@
     </row>
     <row r="72" ht="24" customHeight="1" s="54">
       <c r="A72" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="41" t="n"/>
@@ -7790,15 +7782,9 @@
         </is>
       </c>
       <c r="N72" s="51" t="n"/>
-      <c r="O72" s="29" t="n">
-        <v>-12.1</v>
-      </c>
-      <c r="P72" s="29" t="n">
-        <v>-8</v>
-      </c>
-      <c r="Q72" s="29" t="n">
-        <v>-10.45</v>
-      </c>
+      <c r="O72" s="29" t="n"/>
+      <c r="P72" s="29" t="n"/>
+      <c r="Q72" s="29" t="n"/>
       <c r="R72" s="45" t="n"/>
       <c r="S72" s="21" t="n"/>
       <c r="T72" s="33" t="n"/>
@@ -7852,7 +7838,7 @@
     </row>
     <row r="73" ht="24" customHeight="1" s="54">
       <c r="A73" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
@@ -7953,7 +7939,7 @@
     </row>
     <row r="74" ht="24" customHeight="1" s="54">
       <c r="A74" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="41" t="n"/>
@@ -7986,12 +7972,8 @@
         </is>
       </c>
       <c r="N74" s="51" t="n"/>
-      <c r="O74" s="29" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="P74" s="29" t="n">
-        <v>-7.1</v>
-      </c>
+      <c r="O74" s="29" t="n"/>
+      <c r="P74" s="29" t="n"/>
       <c r="Q74" s="29" t="n"/>
       <c r="R74" s="45" t="n"/>
       <c r="S74" s="21" t="n"/>
@@ -8050,7 +8032,7 @@
     </row>
     <row r="75" ht="24" customHeight="1" s="54">
       <c r="A75" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
@@ -8153,7 +8135,7 @@
     </row>
     <row r="76" ht="24" customHeight="1" s="54">
       <c r="A76" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="41" t="n"/>
@@ -8240,7 +8222,7 @@
     </row>
     <row r="77" ht="24" customHeight="1" s="54">
       <c r="A77" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
@@ -8339,7 +8321,7 @@
     </row>
     <row r="78" ht="24" customHeight="1" s="54">
       <c r="A78" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="41" t="n"/>
@@ -8428,7 +8410,7 @@
     </row>
     <row r="79" ht="24" customHeight="1" s="54">
       <c r="A79" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="41" t="n"/>
@@ -8517,7 +8499,7 @@
     </row>
     <row r="80" ht="24" customHeight="1" s="54">
       <c r="A80" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="41" t="n"/>
@@ -8606,7 +8588,7 @@
     </row>
     <row r="81" ht="24" customHeight="1" s="54">
       <c r="A81" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="41" t="n"/>
@@ -8695,7 +8677,7 @@
     </row>
     <row r="82" ht="24" customHeight="1" s="54">
       <c r="A82" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
@@ -8796,7 +8778,7 @@
     </row>
     <row r="83" ht="24" customHeight="1" s="54">
       <c r="A83" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="41" t="n"/>
@@ -8885,7 +8867,7 @@
     </row>
     <row r="84" ht="24" customHeight="1" s="54">
       <c r="A84" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="41" t="n"/>
@@ -8974,7 +8956,7 @@
     </row>
     <row r="85" ht="24" customHeight="1" s="54">
       <c r="A85" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
@@ -9077,7 +9059,7 @@
     </row>
     <row r="86" ht="24" customHeight="1" s="54">
       <c r="A86" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="41" t="n"/>
@@ -9166,7 +9148,7 @@
     </row>
     <row r="87" ht="24" customHeight="1" s="54">
       <c r="A87" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="41" t="n"/>
@@ -9255,7 +9237,7 @@
     </row>
     <row r="88" ht="24" customHeight="1" s="54">
       <c r="A88" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="41" t="n"/>
@@ -9344,7 +9326,7 @@
     </row>
     <row r="89" ht="24" customHeight="1" s="54">
       <c r="A89" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="41" t="n"/>
@@ -9433,7 +9415,7 @@
     </row>
     <row r="90" ht="24" customHeight="1" s="54">
       <c r="A90" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
@@ -9536,7 +9518,7 @@
     </row>
     <row r="91" ht="24" customHeight="1" s="54">
       <c r="A91" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="41" t="n"/>
@@ -9625,7 +9607,7 @@
     </row>
     <row r="92" ht="24" customHeight="1" s="54">
       <c r="A92" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="41" t="n"/>
@@ -9710,7 +9692,7 @@
     </row>
     <row r="93" ht="24" customHeight="1" s="54">
       <c r="A93" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="41" t="n"/>
@@ -9799,7 +9781,7 @@
     </row>
     <row r="94" ht="24" customHeight="1" s="54">
       <c r="A94" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B94" s="2" t="n"/>
       <c r="C94" s="41" t="n"/>
@@ -9884,7 +9866,7 @@
     </row>
     <row r="95" ht="24" customHeight="1" s="54">
       <c r="A95" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="41" t="n"/>
@@ -9969,7 +9951,7 @@
     </row>
     <row r="96" ht="24" customHeight="1" s="54">
       <c r="A96" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="41" t="n"/>
@@ -10054,7 +10036,7 @@
     </row>
     <row r="97" ht="24" customHeight="1" s="54">
       <c r="A97" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="41" t="n"/>
@@ -10139,7 +10121,7 @@
     </row>
     <row r="98" ht="24" customHeight="1" s="54">
       <c r="A98" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
@@ -10238,7 +10220,7 @@
     </row>
     <row r="99" ht="24" customHeight="1" s="54">
       <c r="A99" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="41" t="n"/>
@@ -10325,7 +10307,7 @@
     </row>
     <row r="100" ht="24" customHeight="1" s="54">
       <c r="A100" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
@@ -10428,7 +10410,7 @@
     </row>
     <row r="101" ht="24" customHeight="1" s="54">
       <c r="A101" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
@@ -10535,7 +10517,7 @@
     </row>
     <row r="102" ht="24" customHeight="1" s="54">
       <c r="A102" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
@@ -10583,13 +10565,13 @@
         </is>
       </c>
       <c r="O102" s="29" t="n">
-        <v>-15.5</v>
+        <v>-12.2</v>
       </c>
       <c r="P102" s="29" t="n">
-        <v>-0.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q102" s="29" t="n">
-        <v>-6.84</v>
+        <v>-3.33</v>
       </c>
       <c r="R102" s="45" t="inlineStr">
         <is>
@@ -10656,7 +10638,7 @@
     </row>
     <row r="103" ht="24" customHeight="1" s="54">
       <c r="A103" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
@@ -10759,7 +10741,7 @@
     </row>
     <row r="104" ht="24" customHeight="1" s="54">
       <c r="A104" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
@@ -10862,7 +10844,7 @@
     </row>
     <row r="105" ht="24" customHeight="1" s="54">
       <c r="A105" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
@@ -10965,7 +10947,7 @@
     </row>
     <row r="106" ht="24" customHeight="1" s="54">
       <c r="A106" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
@@ -11013,13 +10995,13 @@
         </is>
       </c>
       <c r="O106" s="29" t="n">
-        <v>-7.9</v>
+        <v>-8.1</v>
       </c>
       <c r="P106" s="29" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q106" s="29" t="n">
-        <v>-2.67</v>
+        <v>-2.99</v>
       </c>
       <c r="R106" s="45" t="n"/>
       <c r="S106" s="21" t="inlineStr">
@@ -11087,7 +11069,7 @@
     </row>
     <row r="107" ht="24" customHeight="1" s="54">
       <c r="A107" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
@@ -11135,13 +11117,13 @@
         </is>
       </c>
       <c r="O107" s="29" t="n">
-        <v>-10.7</v>
+        <v>-7</v>
       </c>
       <c r="P107" s="29" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="Q107" s="29" t="n">
-        <v>-3.73</v>
+        <v>-2.33</v>
       </c>
       <c r="R107" s="45" t="n"/>
       <c r="S107" s="21" t="inlineStr">
@@ -11204,7 +11186,7 @@
     </row>
     <row r="108" ht="24" customHeight="1" s="54">
       <c r="A108" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
@@ -11307,7 +11289,7 @@
     </row>
     <row r="109" ht="24" customHeight="1" s="54">
       <c r="A109" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
@@ -11355,13 +11337,13 @@
         </is>
       </c>
       <c r="O109" s="29" t="n">
-        <v>-10.1</v>
+        <v>-4.4</v>
       </c>
       <c r="P109" s="29" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q109" s="29" t="n">
-        <v>-4.49</v>
+        <v>-1.21</v>
       </c>
       <c r="R109" s="45" t="n"/>
       <c r="S109" s="21" t="inlineStr">
@@ -11424,7 +11406,7 @@
     </row>
     <row r="110" ht="24" customHeight="1" s="54">
       <c r="A110" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
@@ -11531,7 +11513,7 @@
     </row>
     <row r="111" ht="24" customHeight="1" s="54">
       <c r="A111" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
@@ -11575,13 +11557,13 @@
       </c>
       <c r="N111" s="51" t="n"/>
       <c r="O111" s="29" t="n">
-        <v>-6</v>
+        <v>-5.4</v>
       </c>
       <c r="P111" s="29" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="Q111" s="29" t="n">
-        <v>-0.24</v>
+        <v>-1.2</v>
       </c>
       <c r="R111" s="45" t="n"/>
       <c r="S111" s="21" t="inlineStr">
@@ -11652,7 +11634,7 @@
     </row>
     <row r="112" ht="24" customHeight="1" s="54">
       <c r="A112" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
@@ -11759,7 +11741,7 @@
     </row>
     <row r="113" ht="24" customHeight="1" s="54">
       <c r="A113" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
@@ -11803,13 +11785,13 @@
       </c>
       <c r="N113" s="51" t="n"/>
       <c r="O113" s="29" t="n">
-        <v>-11.4</v>
+        <v>-13.3</v>
       </c>
       <c r="P113" s="29" t="n">
-        <v>-5.7</v>
+        <v>-7.2</v>
       </c>
       <c r="Q113" s="29" t="n">
-        <v>-8.26</v>
+        <v>-10.7</v>
       </c>
       <c r="R113" s="45" t="inlineStr">
         <is>
@@ -11876,7 +11858,7 @@
     </row>
     <row r="114" ht="24" customHeight="1" s="54">
       <c r="A114" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
@@ -11979,7 +11961,7 @@
     </row>
     <row r="115" ht="24" customHeight="1" s="54">
       <c r="A115" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
@@ -12082,7 +12064,7 @@
     </row>
     <row r="116" ht="24" customHeight="1" s="54">
       <c r="A116" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
@@ -12185,7 +12167,7 @@
     </row>
     <row r="117" ht="24" customHeight="1" s="54">
       <c r="A117" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
@@ -12284,7 +12266,7 @@
     </row>
     <row r="118" ht="24" customHeight="1" s="54">
       <c r="A118" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
@@ -12328,13 +12310,13 @@
       </c>
       <c r="N118" s="51" t="n"/>
       <c r="O118" s="29" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="P118" s="29" t="n">
-        <v>10.3</v>
+        <v>16.2</v>
       </c>
       <c r="Q118" s="29" t="n">
-        <v>4.49</v>
+        <v>7.91</v>
       </c>
       <c r="R118" s="45" t="n"/>
       <c r="S118" s="21" t="inlineStr">
@@ -12397,7 +12379,7 @@
     </row>
     <row r="119" ht="24" customHeight="1" s="54">
       <c r="A119" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
@@ -12441,13 +12423,13 @@
       </c>
       <c r="N119" s="51" t="n"/>
       <c r="O119" s="29" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="P119" s="29" t="n">
-        <v>18.1</v>
+        <v>26.3</v>
       </c>
       <c r="Q119" s="29" t="n">
-        <v>10.18</v>
+        <v>14.56</v>
       </c>
       <c r="R119" s="45" t="n"/>
       <c r="S119" s="21" t="inlineStr">
@@ -12522,7 +12504,7 @@
     </row>
     <row r="120" ht="24" customHeight="1" s="54">
       <c r="A120" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B120" s="2" t="n"/>
       <c r="C120" s="41" t="n">
@@ -12633,7 +12615,7 @@
     </row>
     <row r="121" ht="24" customHeight="1" s="54">
       <c r="A121" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
@@ -12677,13 +12659,13 @@
       </c>
       <c r="N121" s="51" t="n"/>
       <c r="O121" s="29" t="n">
-        <v>-0.2</v>
+        <v>0.8</v>
       </c>
       <c r="P121" s="29" t="n">
-        <v>13.6</v>
+        <v>18.2</v>
       </c>
       <c r="Q121" s="29" t="n">
-        <v>6.12</v>
+        <v>10.11</v>
       </c>
       <c r="R121" s="45" t="n"/>
       <c r="S121" s="21" t="inlineStr">
@@ -12758,7 +12740,7 @@
     </row>
     <row r="122" ht="24" customHeight="1" s="54">
       <c r="A122" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
@@ -12802,13 +12784,13 @@
       </c>
       <c r="N122" s="51" t="n"/>
       <c r="O122" s="29" t="n">
-        <v>1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="P122" s="29" t="n">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="Q122" s="29" t="n">
-        <v>6.65</v>
+        <v>6.96</v>
       </c>
       <c r="R122" s="45" t="n"/>
       <c r="S122" s="21" t="inlineStr">
@@ -12887,7 +12869,7 @@
     </row>
     <row r="123" ht="24" customHeight="1" s="54">
       <c r="A123" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B123" s="2" t="n"/>
       <c r="C123" s="41" t="n">
@@ -12994,7 +12976,7 @@
     </row>
     <row r="124" ht="24" customHeight="1" s="54">
       <c r="A124" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
@@ -13105,7 +13087,7 @@
     </row>
     <row r="125" ht="24" customHeight="1" s="54">
       <c r="A125" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B125" s="2" t="n"/>
       <c r="C125" s="41" t="n">
@@ -13212,7 +13194,7 @@
     </row>
     <row r="126" ht="24" customHeight="1" s="54">
       <c r="A126" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B126" s="2" t="n"/>
       <c r="C126" s="41" t="n">
@@ -13319,7 +13301,7 @@
     </row>
     <row r="127" ht="24" customHeight="1" s="54">
       <c r="A127" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
@@ -13363,13 +13345,13 @@
       </c>
       <c r="N127" s="51" t="n"/>
       <c r="O127" s="29" t="n">
-        <v>-10.2</v>
+        <v>-9.5</v>
       </c>
       <c r="P127" s="29" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q127" s="29" t="n">
-        <v>-2.52</v>
+        <v>-3.29</v>
       </c>
       <c r="R127" s="45" t="n"/>
       <c r="S127" s="21" t="inlineStr">
@@ -13444,7 +13426,7 @@
     </row>
     <row r="128" ht="24" customHeight="1" s="54">
       <c r="A128" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B128" s="2" t="n"/>
       <c r="C128" s="41" t="n">
@@ -13547,7 +13529,7 @@
     </row>
     <row r="129" ht="24" customHeight="1" s="54">
       <c r="A129" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B129" s="2" t="n"/>
       <c r="C129" s="41" t="n">
@@ -13654,7 +13636,7 @@
     </row>
     <row r="130" ht="24" customHeight="1" s="54">
       <c r="A130" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
@@ -13698,13 +13680,13 @@
       </c>
       <c r="N130" s="51" t="n"/>
       <c r="O130" s="29" t="n">
-        <v>-10.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="P130" s="29" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="Q130" s="29" t="n">
-        <v>-2.99</v>
+        <v>-3.31</v>
       </c>
       <c r="R130" s="45" t="n"/>
       <c r="S130" s="21" t="inlineStr">
@@ -13775,7 +13757,7 @@
     </row>
     <row r="131" ht="24" customHeight="1" s="54">
       <c r="A131" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="41" t="n">
@@ -13878,7 +13860,7 @@
     </row>
     <row r="132" ht="24" customHeight="1" s="54">
       <c r="A132" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B132" s="2" t="n"/>
       <c r="C132" s="41" t="n">
@@ -13977,7 +13959,7 @@
     </row>
     <row r="133" ht="24" customHeight="1" s="54">
       <c r="A133" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
@@ -14088,7 +14070,7 @@
     </row>
     <row r="134" ht="24" customHeight="1" s="54">
       <c r="A134" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B134" s="2" t="n"/>
       <c r="C134" s="41" t="n">
@@ -14187,7 +14169,7 @@
     </row>
     <row r="135" ht="24" customHeight="1" s="54">
       <c r="A135" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="41" t="n">
@@ -14290,7 +14272,7 @@
     </row>
     <row r="136" ht="24" customHeight="1" s="54">
       <c r="A136" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
@@ -14401,7 +14383,7 @@
     </row>
     <row r="137" ht="24" customHeight="1" s="54">
       <c r="A137" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="41" t="n">
@@ -14500,7 +14482,7 @@
     </row>
     <row r="138" ht="24" customHeight="1" s="54">
       <c r="A138" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
@@ -14615,7 +14597,7 @@
     </row>
     <row r="139" ht="24" customHeight="1" s="54">
       <c r="A139" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B139" s="2" t="n"/>
       <c r="C139" s="41" t="n">
@@ -14722,7 +14704,7 @@
     </row>
     <row r="140" ht="24" customHeight="1" s="54">
       <c r="A140" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B140" s="2" t="n"/>
       <c r="C140" s="41" t="n">
@@ -14829,7 +14811,7 @@
     </row>
     <row r="141" ht="24" customHeight="1" s="54">
       <c r="A141" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
@@ -14948,7 +14930,7 @@
     </row>
     <row r="142" ht="24" customHeight="1" s="54">
       <c r="A142" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
@@ -14992,14 +14974,12 @@
       </c>
       <c r="N142" s="51" t="n"/>
       <c r="O142" s="29" t="n">
-        <v>13.3</v>
+        <v>6.6</v>
       </c>
       <c r="P142" s="29" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Q142" s="29" t="n">
-        <v>16.02</v>
-      </c>
+        <v>14.1</v>
+      </c>
+      <c r="Q142" s="29" t="n"/>
       <c r="R142" s="45" t="n"/>
       <c r="S142" s="21" t="inlineStr">
         <is>
@@ -15065,7 +15045,7 @@
     </row>
     <row r="143" ht="24" customHeight="1" s="54">
       <c r="A143" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
@@ -15109,13 +15089,13 @@
       </c>
       <c r="N143" s="51" t="n"/>
       <c r="O143" s="29" t="n">
-        <v>-0.3</v>
+        <v>-2.2</v>
       </c>
       <c r="P143" s="29" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="Q143" s="29" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="R143" s="45" t="n"/>
       <c r="S143" s="21" t="inlineStr">
@@ -15190,7 +15170,7 @@
     </row>
     <row r="144" ht="24" customHeight="1" s="54">
       <c r="A144" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="41" t="n">
@@ -15293,7 +15273,7 @@
     </row>
     <row r="145" ht="24" customHeight="1" s="54">
       <c r="A145" s="2" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
@@ -15337,13 +15317,13 @@
       </c>
       <c r="N145" s="51" t="n"/>
       <c r="O145" s="29" t="n">
-        <v>7.9</v>
+        <v>3.6</v>
       </c>
       <c r="P145" s="29" t="n">
-        <v>15.4</v>
+        <v>11.8</v>
       </c>
       <c r="Q145" s="29" t="n">
-        <v>11.28</v>
+        <v>8.1</v>
       </c>
       <c r="R145" s="45" t="n"/>
       <c r="S145" s="21" t="inlineStr">
@@ -15418,7 +15398,7 @@
     </row>
     <row r="146" ht="24" customHeight="1" s="54">
       <c r="A146" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
@@ -15462,13 +15442,13 @@
       </c>
       <c r="N146" s="51" t="n"/>
       <c r="O146" s="29" t="n">
-        <v>11.7</v>
+        <v>13.5</v>
       </c>
       <c r="P146" s="29" t="n">
-        <v>19.3</v>
+        <v>17.3</v>
       </c>
       <c r="Q146" s="29" t="n">
-        <v>16.02</v>
+        <v>15.74</v>
       </c>
       <c r="R146" s="45" t="n"/>
       <c r="S146" s="21" t="inlineStr">
@@ -15531,7 +15511,7 @@
     </row>
     <row r="147" ht="24" customHeight="1" s="54">
       <c r="A147" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
@@ -15575,13 +15555,13 @@
       </c>
       <c r="N147" s="51" t="n"/>
       <c r="O147" s="29" t="n">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="P147" s="29" t="n">
-        <v>18.6</v>
+        <v>14</v>
       </c>
       <c r="Q147" s="29" t="n">
-        <v>12.5</v>
+        <v>9.35</v>
       </c>
       <c r="R147" s="45" t="n"/>
       <c r="S147" s="21" t="inlineStr">
@@ -15652,7 +15632,7 @@
     </row>
     <row r="148" ht="24" customHeight="1" s="54">
       <c r="A148" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
@@ -15696,13 +15676,13 @@
       </c>
       <c r="N148" s="51" t="n"/>
       <c r="O148" s="29" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="P148" s="29" t="n">
-        <v>22</v>
+        <v>14.8</v>
       </c>
       <c r="Q148" s="29" t="n">
-        <v>16.01</v>
+        <v>12.39</v>
       </c>
       <c r="R148" s="45" t="n"/>
       <c r="S148" s="21" t="inlineStr">
@@ -15773,7 +15753,7 @@
     </row>
     <row r="149" ht="24" customHeight="1" s="54">
       <c r="A149" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
@@ -15817,13 +15797,13 @@
       </c>
       <c r="N149" s="51" t="n"/>
       <c r="O149" s="29" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="P149" s="29" t="n">
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q149" s="29" t="n">
-        <v>6.5</v>
+        <v>4.72</v>
       </c>
       <c r="R149" s="45" t="n"/>
       <c r="S149" s="21" t="inlineStr">
@@ -15894,7 +15874,7 @@
     </row>
     <row r="150" ht="24" customHeight="1" s="54">
       <c r="A150" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
@@ -15938,13 +15918,13 @@
       </c>
       <c r="N150" s="51" t="n"/>
       <c r="O150" s="29" t="n">
-        <v>16.2</v>
+        <v>19.8</v>
       </c>
       <c r="P150" s="29" t="n">
-        <v>28.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q150" s="29" t="n">
-        <v>22.25</v>
+        <v>21.27</v>
       </c>
       <c r="R150" s="45" t="n"/>
       <c r="S150" s="21" t="inlineStr">
@@ -16011,7 +15991,7 @@
     </row>
     <row r="151" ht="24" customHeight="1" s="54">
       <c r="A151" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
@@ -16055,13 +16035,13 @@
       </c>
       <c r="N151" s="51" t="n"/>
       <c r="O151" s="29" t="n">
-        <v>17.4</v>
+        <v>16.6</v>
       </c>
       <c r="P151" s="29" t="n">
-        <v>21.2</v>
+        <v>19.7</v>
       </c>
       <c r="Q151" s="29" t="n">
-        <v>19.73</v>
+        <v>17.8</v>
       </c>
       <c r="R151" s="45" t="n"/>
       <c r="S151" s="21" t="inlineStr">
@@ -16128,7 +16108,7 @@
     </row>
     <row r="152" ht="24" customHeight="1" s="54">
       <c r="A152" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
@@ -16172,13 +16152,13 @@
       </c>
       <c r="N152" s="51" t="n"/>
       <c r="O152" s="29" t="n">
-        <v>15.2</v>
+        <v>13.7</v>
       </c>
       <c r="P152" s="29" t="n">
-        <v>24.4</v>
+        <v>18.9</v>
       </c>
       <c r="Q152" s="29" t="n">
-        <v>19.41</v>
+        <v>16.16</v>
       </c>
       <c r="R152" s="45" t="n"/>
       <c r="S152" s="21" t="inlineStr">
@@ -16249,7 +16229,7 @@
     </row>
     <row r="153" ht="24" customHeight="1" s="54">
       <c r="A153" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
@@ -16352,7 +16332,7 @@
     </row>
     <row r="154" ht="24" customHeight="1" s="54">
       <c r="A154" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
@@ -16396,13 +16376,13 @@
       </c>
       <c r="N154" s="51" t="n"/>
       <c r="O154" s="29" t="n">
-        <v>19.7</v>
+        <v>20.9</v>
       </c>
       <c r="P154" s="29" t="n">
-        <v>29.5</v>
+        <v>32.9</v>
       </c>
       <c r="Q154" s="29" t="n">
-        <v>23.03</v>
+        <v>26.5</v>
       </c>
       <c r="R154" s="45" t="n"/>
       <c r="S154" s="21" t="inlineStr">
@@ -16469,7 +16449,7 @@
     </row>
     <row r="155" ht="24" customHeight="1" s="54">
       <c r="A155" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
@@ -16513,13 +16493,13 @@
       </c>
       <c r="N155" s="51" t="n"/>
       <c r="O155" s="29" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="P155" s="29" t="n">
-        <v>27.8</v>
+        <v>33.1</v>
       </c>
       <c r="Q155" s="29" t="n">
-        <v>23.41</v>
+        <v>26.75</v>
       </c>
       <c r="R155" s="45" t="n"/>
       <c r="S155" s="21" t="inlineStr">
@@ -16586,7 +16566,7 @@
     </row>
     <row r="156" ht="24" customHeight="1" s="54">
       <c r="A156" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
@@ -16630,13 +16610,13 @@
       </c>
       <c r="N156" s="51" t="n"/>
       <c r="O156" s="29" t="n">
-        <v>19.8</v>
+        <v>21.6</v>
       </c>
       <c r="P156" s="29" t="n">
-        <v>23.7</v>
+        <v>31.3</v>
       </c>
       <c r="Q156" s="29" t="n">
-        <v>21.48</v>
+        <v>25.16</v>
       </c>
       <c r="R156" s="45" t="n"/>
       <c r="S156" s="21" t="inlineStr">
@@ -16703,7 +16683,7 @@
     </row>
     <row r="157" ht="24" customHeight="1" s="54">
       <c r="A157" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
@@ -16747,13 +16727,13 @@
       </c>
       <c r="N157" s="51" t="n"/>
       <c r="O157" s="29" t="n">
-        <v>19.2</v>
+        <v>20.9</v>
       </c>
       <c r="P157" s="29" t="n">
-        <v>24.9</v>
+        <v>28</v>
       </c>
       <c r="Q157" s="29" t="n">
-        <v>21.51</v>
+        <v>23.46</v>
       </c>
       <c r="R157" s="45" t="n"/>
       <c r="S157" s="21" t="inlineStr">
@@ -16820,7 +16800,7 @@
     </row>
     <row r="158" ht="24" customHeight="1" s="54">
       <c r="A158" s="2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
@@ -16864,13 +16844,13 @@
       </c>
       <c r="N158" s="51" t="n"/>
       <c r="O158" s="29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="P158" s="29" t="n">
-        <v>26.2</v>
+        <v>31.3</v>
       </c>
       <c r="Q158" s="29" t="n">
-        <v>22.16</v>
+        <v>24.34</v>
       </c>
       <c r="R158" s="45" t="n"/>
       <c r="S158" s="21" t="inlineStr">
@@ -16937,7 +16917,7 @@
     </row>
     <row r="159" ht="24" customHeight="1" s="54">
       <c r="A159" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
@@ -17040,7 +17020,7 @@
     </row>
     <row r="160" ht="24" customHeight="1" s="54">
       <c r="A160" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
@@ -17084,13 +17064,13 @@
       </c>
       <c r="N160" s="51" t="n"/>
       <c r="O160" s="29" t="n">
-        <v>20.9</v>
+        <v>23.6</v>
       </c>
       <c r="P160" s="29" t="n">
-        <v>31</v>
+        <v>26.9</v>
       </c>
       <c r="Q160" s="29" t="n">
-        <v>24.85</v>
+        <v>24.99</v>
       </c>
       <c r="R160" s="45" t="n"/>
       <c r="S160" s="21" t="inlineStr">
@@ -17157,7 +17137,7 @@
     </row>
     <row r="161" ht="24" customHeight="1" s="54">
       <c r="A161" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
@@ -17201,13 +17181,13 @@
       </c>
       <c r="N161" s="51" t="n"/>
       <c r="O161" s="29" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="P161" s="29" t="n">
-        <v>31.5</v>
+        <v>31.9</v>
       </c>
       <c r="Q161" s="29" t="n">
-        <v>26.07</v>
+        <v>26.7</v>
       </c>
       <c r="R161" s="45" t="n"/>
       <c r="S161" s="21" t="inlineStr">
@@ -17274,7 +17254,7 @@
     </row>
     <row r="162" ht="24" customHeight="1" s="54">
       <c r="A162" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
@@ -17377,7 +17357,7 @@
     </row>
     <row r="163" ht="24" customHeight="1" s="54">
       <c r="A163" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
@@ -17476,7 +17456,7 @@
     </row>
     <row r="164" ht="24" customHeight="1" s="54">
       <c r="A164" s="2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
@@ -17520,13 +17500,13 @@
       </c>
       <c r="N164" s="51" t="n"/>
       <c r="O164" s="29" t="n">
-        <v>24.8</v>
+        <v>25.6</v>
       </c>
       <c r="P164" s="29" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="Q164" s="29" t="n">
-        <v>27.44</v>
+        <v>28.46</v>
       </c>
       <c r="R164" s="45" t="n"/>
       <c r="S164" s="21" t="inlineStr">
@@ -17585,7 +17565,7 @@
     </row>
     <row r="165" ht="24" customHeight="1" s="54">
       <c r="A165" s="2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
@@ -17629,13 +17609,13 @@
       </c>
       <c r="N165" s="51" t="n"/>
       <c r="O165" s="29" t="n">
-        <v>22.8</v>
+        <v>23.4</v>
       </c>
       <c r="P165" s="29" t="n">
-        <v>31.5</v>
+        <v>29.8</v>
       </c>
       <c r="Q165" s="29" t="n">
-        <v>26.9</v>
+        <v>25.71</v>
       </c>
       <c r="R165" s="45" t="n"/>
       <c r="S165" s="21" t="inlineStr">
@@ -17702,7 +17682,7 @@
     </row>
     <row r="166" ht="24" customHeight="1" s="54">
       <c r="A166" s="2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
@@ -17746,13 +17726,13 @@
       </c>
       <c r="N166" s="51" t="n"/>
       <c r="O166" s="29" t="n">
-        <v>13.8</v>
+        <v>14.2</v>
       </c>
       <c r="P166" s="29" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q166" s="29" t="n">
-        <v>18.65</v>
+        <v>18.58</v>
       </c>
       <c r="R166" s="45" t="n"/>
       <c r="S166" s="21" t="inlineStr">
@@ -17819,7 +17799,7 @@
     </row>
     <row r="167" ht="24" customHeight="1" s="54">
       <c r="A167" s="2" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
@@ -17863,13 +17843,13 @@
       </c>
       <c r="N167" s="51" t="n"/>
       <c r="O167" s="29" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="P167" s="29" t="n">
-        <v>26</v>
+        <v>28.9</v>
       </c>
       <c r="Q167" s="29" t="n">
-        <v>22.39</v>
+        <v>23.15</v>
       </c>
       <c r="R167" s="45" t="n"/>
       <c r="S167" s="21" t="inlineStr">
@@ -17936,7 +17916,7 @@
     </row>
     <row r="168" ht="24" customHeight="1" s="54">
       <c r="A168" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
@@ -17980,13 +17960,13 @@
       </c>
       <c r="N168" s="51" t="n"/>
       <c r="O168" s="29" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="P168" s="29" t="n">
-        <v>25.2</v>
+        <v>26.6</v>
       </c>
       <c r="Q168" s="29" t="n">
-        <v>22.48</v>
+        <v>23.15</v>
       </c>
       <c r="R168" s="45" t="n"/>
       <c r="S168" s="21" t="inlineStr">
@@ -18049,7 +18029,7 @@
     </row>
     <row r="169" ht="24" customHeight="1" s="54">
       <c r="A169" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B169" s="2" t="n"/>
       <c r="C169" s="41" t="n">
@@ -18144,7 +18124,7 @@
     </row>
     <row r="170" ht="24" customHeight="1" s="54">
       <c r="A170" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
@@ -18188,13 +18168,13 @@
       </c>
       <c r="N170" s="51" t="n"/>
       <c r="O170" s="29" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="P170" s="29" t="n">
-        <v>21.5</v>
+        <v>23.9</v>
       </c>
       <c r="Q170" s="29" t="n">
-        <v>19.4</v>
+        <v>20.35</v>
       </c>
       <c r="R170" s="45" t="n"/>
       <c r="S170" s="21" t="inlineStr">
@@ -18265,7 +18245,7 @@
     </row>
     <row r="171" ht="24" customHeight="1" s="54">
       <c r="A171" s="2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
@@ -18309,14 +18289,12 @@
       </c>
       <c r="N171" s="51" t="n"/>
       <c r="O171" s="29" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="P171" s="29" t="n">
         <v>19.2</v>
       </c>
-      <c r="Q171" s="29" t="n">
-        <v>10.39</v>
-      </c>
+      <c r="Q171" s="29" t="n"/>
       <c r="R171" s="45" t="n"/>
       <c r="S171" s="21" t="inlineStr">
         <is>
@@ -18382,7 +18360,7 @@
     </row>
     <row r="172" ht="24" customHeight="1" s="54">
       <c r="A172" s="2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B172" s="2" t="n"/>
       <c r="C172" s="41" t="n">
@@ -18477,7 +18455,7 @@
     </row>
     <row r="173" ht="24" customHeight="1" s="54">
       <c r="A173" s="2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B173" s="2" t="n"/>
       <c r="C173" s="41" t="n">
@@ -18580,7 +18558,7 @@
     </row>
     <row r="174" ht="24" customHeight="1" s="54">
       <c r="A174" s="2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B174" s="2" t="n"/>
       <c r="C174" s="41" t="n">
@@ -18675,7 +18653,7 @@
     </row>
     <row r="175" ht="24" customHeight="1" s="54">
       <c r="A175" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B175" s="2" t="n"/>
       <c r="C175" s="41" t="n">
@@ -18770,7 +18748,7 @@
     </row>
     <row r="176" ht="24" customHeight="1" s="54">
       <c r="A176" s="2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B176" s="2" t="n"/>
       <c r="C176" s="41" t="n">
@@ -18865,7 +18843,7 @@
     </row>
     <row r="177" ht="24" customHeight="1" s="54">
       <c r="A177" s="2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B177" s="2" t="n"/>
       <c r="C177" s="41" t="n">
@@ -18901,13 +18879,13 @@
       </c>
       <c r="N177" s="51" t="n"/>
       <c r="O177" s="29" t="n">
-        <v>-2.5</v>
+        <v>-8.4</v>
       </c>
       <c r="P177" s="29" t="n">
         <v>4.8</v>
       </c>
       <c r="Q177" s="29" t="n">
-        <v>0.33</v>
+        <v>-2.41</v>
       </c>
       <c r="R177" s="45" t="n"/>
       <c r="S177" s="21" t="inlineStr">
@@ -18978,7 +18956,7 @@
     </row>
     <row r="178" ht="24" customHeight="1" s="54">
       <c r="A178" s="2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B178" s="2" t="n"/>
       <c r="C178" s="41" t="n">
@@ -19014,13 +18992,13 @@
       </c>
       <c r="N178" s="51" t="n"/>
       <c r="O178" s="29" t="n">
-        <v>-10</v>
+        <v>-14.8</v>
       </c>
       <c r="P178" s="29" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q178" s="29" t="n">
-        <v>-3.76</v>
+        <v>-6.81</v>
       </c>
       <c r="R178" s="45" t="n"/>
       <c r="S178" s="21" t="inlineStr">
@@ -19091,7 +19069,7 @@
     </row>
     <row r="179" ht="24" customHeight="1" s="54">
       <c r="A179" s="2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B179" s="2" t="n"/>
       <c r="C179" s="41" t="inlineStr">
@@ -19129,13 +19107,13 @@
       </c>
       <c r="N179" s="51" t="n"/>
       <c r="O179" s="29" t="n">
-        <v>12.6</v>
+        <v>17.2</v>
       </c>
       <c r="P179" s="29" t="n">
-        <v>22.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q179" s="29" t="n">
-        <v>17.21</v>
+        <v>18.75</v>
       </c>
       <c r="R179" s="45" t="n"/>
       <c r="S179" s="21" t="inlineStr">
@@ -19198,7 +19176,7 @@
     </row>
     <row r="180" ht="24" customHeight="1" s="54">
       <c r="A180" s="2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B180" s="2" t="n"/>
       <c r="C180" s="41" t="n">
@@ -19234,13 +19212,13 @@
       </c>
       <c r="N180" s="51" t="n"/>
       <c r="O180" s="29" t="n">
-        <v>21</v>
+        <v>21.9</v>
       </c>
       <c r="P180" s="29" t="n">
-        <v>25.7</v>
+        <v>28.8</v>
       </c>
       <c r="Q180" s="29" t="n">
-        <v>22.88</v>
+        <v>24.49</v>
       </c>
       <c r="R180" s="45" t="n"/>
       <c r="S180" s="21" t="inlineStr">
@@ -19307,7 +19285,7 @@
     </row>
     <row r="181" ht="24" customHeight="1" s="54">
       <c r="A181" s="2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B181" s="2" t="n"/>
       <c r="C181" s="41" t="n">
@@ -19343,13 +19321,13 @@
       </c>
       <c r="N181" s="51" t="n"/>
       <c r="O181" s="29" t="n">
-        <v>7.5</v>
+        <v>4.9</v>
       </c>
       <c r="P181" s="29" t="n">
-        <v>13.6</v>
+        <v>10.9</v>
       </c>
       <c r="Q181" s="29" t="n">
-        <v>10.33</v>
+        <v>7.95</v>
       </c>
       <c r="R181" s="45" t="n"/>
       <c r="S181" s="21" t="inlineStr">
@@ -19420,7 +19398,7 @@
     </row>
     <row r="182" ht="24" customHeight="1" s="54">
       <c r="A182" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
@@ -19539,7 +19517,7 @@
     </row>
     <row r="183" ht="24" customHeight="1" s="54">
       <c r="A183" s="2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
@@ -19587,13 +19565,13 @@
         </is>
       </c>
       <c r="O183" s="29" t="n">
-        <v>-6.2</v>
+        <v>-12</v>
       </c>
       <c r="P183" s="29" t="n">
-        <v>0.9</v>
+        <v>-3</v>
       </c>
       <c r="Q183" s="29" t="n">
-        <v>-3.29</v>
+        <v>-7.74</v>
       </c>
       <c r="R183" s="45" t="n"/>
       <c r="S183" s="21" t="inlineStr">
@@ -19664,7 +19642,7 @@
     </row>
     <row r="184" ht="24" customHeight="1" s="54">
       <c r="A184" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
@@ -19708,13 +19686,13 @@
       </c>
       <c r="N184" s="51" t="n"/>
       <c r="O184" s="29" t="n">
-        <v>-6.5</v>
+        <v>-20.1</v>
       </c>
       <c r="P184" s="29" t="n">
-        <v>0.9</v>
+        <v>-2.6</v>
       </c>
       <c r="Q184" s="29" t="n">
-        <v>-3.4</v>
+        <v>-10.67</v>
       </c>
       <c r="R184" s="45" t="n"/>
       <c r="S184" s="21" t="inlineStr">
@@ -19785,7 +19763,7 @@
     </row>
     <row r="185" ht="24" customHeight="1" s="54">
       <c r="A185" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
@@ -19829,13 +19807,13 @@
       </c>
       <c r="N185" s="51" t="n"/>
       <c r="O185" s="29" t="n">
-        <v>16.6</v>
+        <v>13</v>
       </c>
       <c r="P185" s="29" t="n">
-        <v>21.2</v>
+        <v>18.2</v>
       </c>
       <c r="Q185" s="29" t="n">
-        <v>18.38</v>
+        <v>15.14</v>
       </c>
       <c r="R185" s="45" t="n"/>
       <c r="S185" s="21" t="inlineStr">
@@ -19898,7 +19876,7 @@
     </row>
     <row r="186" ht="24" customHeight="1" s="54">
       <c r="A186" s="2" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
@@ -19942,13 +19920,13 @@
       </c>
       <c r="N186" s="51" t="n"/>
       <c r="O186" s="29" t="n">
-        <v>18.7</v>
+        <v>20.6</v>
       </c>
       <c r="P186" s="29" t="n">
-        <v>26.6</v>
+        <v>29.4</v>
       </c>
       <c r="Q186" s="29" t="n">
-        <v>22.18</v>
+        <v>24.49</v>
       </c>
       <c r="R186" s="45" t="n"/>
       <c r="S186" s="21" t="inlineStr">
@@ -20015,7 +19993,7 @@
     </row>
     <row r="187" ht="24" customHeight="1" s="54">
       <c r="A187" s="2" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
@@ -20059,13 +20037,13 @@
       </c>
       <c r="N187" s="51" t="n"/>
       <c r="O187" s="29" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="P187" s="29" t="n">
-        <v>34.5</v>
+        <v>33.9</v>
       </c>
       <c r="Q187" s="29" t="n">
-        <v>27.13</v>
+        <v>27.84</v>
       </c>
       <c r="R187" s="45" t="n"/>
       <c r="S187" s="21" t="inlineStr">
@@ -20128,7 +20106,7 @@
     </row>
     <row r="188" ht="24" customHeight="1" s="54">
       <c r="A188" s="2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
@@ -20172,13 +20150,13 @@
       </c>
       <c r="N188" s="51" t="n"/>
       <c r="O188" s="29" t="n">
-        <v>11.7</v>
+        <v>13</v>
       </c>
       <c r="P188" s="29" t="n">
-        <v>14.3</v>
+        <v>15.8</v>
       </c>
       <c r="Q188" s="29" t="n">
-        <v>13.23</v>
+        <v>14.34</v>
       </c>
       <c r="R188" s="45" t="n"/>
       <c r="S188" s="21" t="inlineStr">
@@ -20241,7 +20219,7 @@
     </row>
     <row r="189" ht="24" customHeight="1" s="54">
       <c r="A189" s="2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B189" s="2" t="n"/>
       <c r="C189" s="41" t="n"/>
@@ -20336,7 +20314,7 @@
     </row>
     <row r="190" ht="24" customHeight="1" s="54">
       <c r="A190" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B190" s="2" t="n"/>
       <c r="C190" s="41" t="n"/>
@@ -20376,14 +20354,12 @@
         </is>
       </c>
       <c r="O190" s="29" t="n">
-        <v>-16.5</v>
+        <v>-19</v>
       </c>
       <c r="P190" s="29" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="Q190" s="29" t="n">
-        <v>-12.9</v>
-      </c>
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="Q190" s="29" t="n"/>
       <c r="R190" s="45" t="n"/>
       <c r="S190" s="21" t="n"/>
       <c r="T190" s="33" t="n"/>
@@ -20445,7 +20421,7 @@
     </row>
     <row r="191" ht="24" customHeight="1" s="54">
       <c r="A191" s="2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B191" s="2" t="n"/>
       <c r="C191" s="41" t="n"/>
@@ -20480,15 +20456,9 @@
         </is>
       </c>
       <c r="N191" s="51" t="n"/>
-      <c r="O191" s="29" t="n">
-        <v>-15.1</v>
-      </c>
-      <c r="P191" s="29" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="Q191" s="29" t="n">
-        <v>-11.4</v>
-      </c>
+      <c r="O191" s="29" t="n"/>
+      <c r="P191" s="29" t="n"/>
+      <c r="Q191" s="29" t="n"/>
       <c r="R191" s="45" t="n"/>
       <c r="S191" s="21" t="n"/>
       <c r="T191" s="33" t="n"/>
@@ -20550,7 +20520,7 @@
     </row>
     <row r="192" ht="24" customHeight="1" s="54">
       <c r="A192" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B192" s="2" t="n"/>
       <c r="C192" s="41" t="n"/>
@@ -20649,7 +20619,7 @@
     </row>
     <row r="193" ht="24" customHeight="1" s="54">
       <c r="A193" s="2" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B193" s="2" t="n"/>
       <c r="C193" s="41" t="n"/>
@@ -20748,7 +20718,7 @@
     </row>
     <row r="194" ht="24" customHeight="1" s="54">
       <c r="A194" s="2" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B194" s="2" t="n"/>
       <c r="C194" s="41" t="n"/>
@@ -20788,13 +20758,13 @@
         </is>
       </c>
       <c r="O194" s="29" t="n">
-        <v>-6.1</v>
+        <v>3.9</v>
       </c>
       <c r="P194" s="29" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="Q194" s="29" t="n">
-        <v>0.79</v>
+        <v>5.95</v>
       </c>
       <c r="R194" s="45" t="inlineStr">
         <is>
@@ -20861,7 +20831,7 @@
     </row>
     <row r="195" ht="24" customHeight="1" s="54">
       <c r="A195" s="2" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B195" s="2" t="n"/>
       <c r="C195" s="41" t="n"/>
@@ -20897,10 +20867,10 @@
       </c>
       <c r="N195" s="51" t="n"/>
       <c r="O195" s="29" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="P195" s="29" t="n">
-        <v>13.2</v>
+        <v>9.9</v>
       </c>
       <c r="Q195" s="29" t="n"/>
       <c r="R195" s="45" t="n"/>
@@ -20964,7 +20934,7 @@
     </row>
     <row r="196" ht="24" customHeight="1" s="54">
       <c r="A196" s="2" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B196" s="2" t="n"/>
       <c r="C196" s="41" t="n"/>
@@ -21003,12 +20973,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O196" s="29" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="P196" s="29" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="O196" s="29" t="n"/>
+      <c r="P196" s="29" t="n"/>
       <c r="Q196" s="29" t="n"/>
       <c r="R196" s="45" t="n"/>
       <c r="S196" s="21" t="n"/>
@@ -21075,7 +21041,7 @@
     </row>
     <row r="197" ht="24" customHeight="1" s="54">
       <c r="A197" s="2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B197" s="2" t="n"/>
       <c r="C197" s="41" t="n">
@@ -21115,13 +21081,13 @@
         </is>
       </c>
       <c r="O197" s="29" t="n">
-        <v>-8.6</v>
+        <v>-2.6</v>
       </c>
       <c r="P197" s="29" t="n">
-        <v>-1.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q197" s="29" t="n">
-        <v>-5.38</v>
+        <v>0.75</v>
       </c>
       <c r="R197" s="45" t="n"/>
       <c r="S197" s="21" t="n"/>
@@ -21192,7 +21158,7 @@
     </row>
     <row r="198" ht="24" customHeight="1" s="54">
       <c r="A198" s="2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B198" s="2" t="n"/>
       <c r="C198" s="41" t="n"/>
@@ -21287,7 +21253,7 @@
     </row>
     <row r="199" ht="24" customHeight="1" s="54">
       <c r="A199" s="2" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B199" s="2" t="n"/>
       <c r="C199" s="41" t="n">
@@ -21386,7 +21352,7 @@
     </row>
     <row r="200" ht="24" customHeight="1" s="54">
       <c r="A200" s="2" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B200" s="2" t="n"/>
       <c r="C200" s="41" t="n"/>
@@ -21485,7 +21451,7 @@
     </row>
     <row r="201" ht="24" customHeight="1" s="54">
       <c r="A201" s="2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B201" s="2" t="n"/>
       <c r="C201" s="41" t="n"/>
@@ -21521,10 +21487,10 @@
       </c>
       <c r="N201" s="51" t="n"/>
       <c r="O201" s="29" t="n">
-        <v>-11.6</v>
+        <v>-10.3</v>
       </c>
       <c r="P201" s="29" t="n">
-        <v>11.1</v>
+        <v>7.4</v>
       </c>
       <c r="Q201" s="29" t="n"/>
       <c r="R201" s="45" t="n"/>
@@ -21588,7 +21554,7 @@
     </row>
     <row r="202" ht="24" customHeight="1" s="54">
       <c r="A202" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B202" s="2" t="n"/>
       <c r="C202" s="41" t="n"/>
@@ -21683,7 +21649,7 @@
     </row>
     <row r="203" ht="24" customHeight="1" s="54">
       <c r="A203" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B203" s="2" t="n"/>
       <c r="C203" s="41" t="n"/>
@@ -21776,7 +21742,7 @@
     </row>
     <row r="204" ht="24" customHeight="1" s="54">
       <c r="A204" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B204" s="2" t="n"/>
       <c r="C204" s="41" t="n">
@@ -21879,7 +21845,7 @@
     </row>
     <row r="205" ht="24" customHeight="1" s="54">
       <c r="A205" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B205" s="2" t="n"/>
       <c r="C205" s="41" t="n"/>
@@ -21982,7 +21948,7 @@
     </row>
     <row r="206" ht="24" customHeight="1" s="54">
       <c r="A206" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B206" s="2" t="n"/>
       <c r="C206" s="41" t="n"/>
@@ -22022,10 +21988,10 @@
         </is>
       </c>
       <c r="O206" s="29" t="n">
-        <v>-13.1</v>
+        <v>-14.6</v>
       </c>
       <c r="P206" s="29" t="n">
-        <v>7.4</v>
+        <v>-0.2</v>
       </c>
       <c r="Q206" s="29" t="n"/>
       <c r="R206" s="45" t="n"/>
@@ -22089,7 +22055,7 @@
     </row>
     <row r="207" ht="24" customHeight="1" s="54">
       <c r="A207" s="2" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B207" s="2" t="n"/>
       <c r="C207" s="41" t="n">
@@ -22129,10 +22095,10 @@
         </is>
       </c>
       <c r="O207" s="29" t="n">
-        <v>-16.3</v>
+        <v>-13.8</v>
       </c>
       <c r="P207" s="29" t="n">
-        <v>6.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q207" s="29" t="n"/>
       <c r="R207" s="45" t="n"/>
@@ -22200,7 +22166,7 @@
     </row>
     <row r="208" ht="24" customHeight="1" s="54">
       <c r="A208" s="2" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B208" s="2" t="n"/>
       <c r="C208" s="41" t="n"/>
@@ -22240,10 +22206,10 @@
         </is>
       </c>
       <c r="O208" s="29" t="n">
-        <v>-15.8</v>
+        <v>-12.4</v>
       </c>
       <c r="P208" s="29" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q208" s="29" t="n"/>
       <c r="R208" s="45" t="inlineStr">
@@ -22311,7 +22277,7 @@
     </row>
     <row r="209" ht="24" customHeight="1" s="54">
       <c r="A209" s="2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B209" s="2" t="n"/>
       <c r="C209" s="41" t="n"/>
@@ -22410,7 +22376,7 @@
     </row>
     <row r="210" ht="24" customHeight="1" s="54">
       <c r="A210" s="2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B210" s="2" t="n"/>
       <c r="C210" s="41" t="n">
@@ -22509,7 +22475,7 @@
     </row>
     <row r="211" ht="24" customHeight="1" s="54">
       <c r="A211" s="2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B211" s="2" t="n"/>
       <c r="C211" s="41" t="n"/>
@@ -22549,13 +22515,13 @@
         </is>
       </c>
       <c r="O211" s="29" t="n">
-        <v>-18.6</v>
+        <v>-28.8</v>
       </c>
       <c r="P211" s="29" t="n">
-        <v>-10.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="Q211" s="29" t="n">
-        <v>-13.2</v>
+        <v>-19</v>
       </c>
       <c r="R211" s="45" t="n"/>
       <c r="S211" s="21" t="n"/>
@@ -22622,7 +22588,7 @@
     </row>
     <row r="212" ht="24" customHeight="1" s="54">
       <c r="A212" s="2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B212" s="2" t="n"/>
       <c r="C212" s="41" t="n"/>
@@ -22733,7 +22699,7 @@
     </row>
     <row r="213" ht="24" customHeight="1" s="54">
       <c r="A213" s="2" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B213" s="2" t="n"/>
       <c r="C213" s="41" t="n"/>
@@ -22769,13 +22735,13 @@
       </c>
       <c r="N213" s="51" t="n"/>
       <c r="O213" s="29" t="n">
-        <v>-16.8</v>
+        <v>-21.7</v>
       </c>
       <c r="P213" s="29" t="n">
-        <v>-3.7</v>
+        <v>-4.2</v>
       </c>
       <c r="Q213" s="29" t="n">
-        <v>-9.9</v>
+        <v>-11.8</v>
       </c>
       <c r="R213" s="45" t="n"/>
       <c r="S213" s="21" t="n"/>
@@ -22838,7 +22804,7 @@
     </row>
     <row r="214" ht="24" customHeight="1" s="54">
       <c r="A214" s="2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B214" s="2" t="n"/>
       <c r="C214" s="41" t="inlineStr">
@@ -22879,9 +22845,7 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O214" s="29" t="n">
-        <v>-44.2</v>
-      </c>
+      <c r="O214" s="29" t="n"/>
       <c r="P214" s="29" t="n"/>
       <c r="Q214" s="29" t="n"/>
       <c r="R214" s="45" t="n"/>
@@ -22933,7 +22897,7 @@
     </row>
     <row r="215" ht="24" customHeight="1" s="54">
       <c r="A215" s="2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B215" s="2" t="n"/>
       <c r="C215" s="41" t="n"/>
@@ -22972,7 +22936,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O215" s="29" t="n"/>
+      <c r="O215" s="29" t="n">
+        <v>-44.6</v>
+      </c>
       <c r="P215" s="29" t="n"/>
       <c r="Q215" s="29" t="n"/>
       <c r="R215" s="45" t="n"/>
@@ -23024,7 +22990,7 @@
     </row>
     <row r="216" ht="24" customHeight="1" s="54">
       <c r="A216" s="2" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
@@ -23125,7 +23091,7 @@
     </row>
     <row r="217" ht="24" customHeight="1" s="54">
       <c r="A217" s="2" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B217" s="2" t="n"/>
       <c r="C217" s="41" t="inlineStr">
@@ -23222,7 +23188,7 @@
     </row>
     <row r="218" ht="24" customHeight="1" s="54">
       <c r="A218" s="2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B218" s="2" t="n"/>
       <c r="C218" s="41" t="inlineStr">
@@ -23319,7 +23285,7 @@
     </row>
     <row r="219" ht="24" customHeight="1" s="54">
       <c r="A219" s="2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B219" s="2" t="n"/>
       <c r="C219" s="41" t="inlineStr">
@@ -23412,7 +23378,7 @@
     </row>
     <row r="220" ht="24" customHeight="1" s="54">
       <c r="A220" s="2" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
@@ -23456,13 +23422,13 @@
       </c>
       <c r="N220" s="51" t="n"/>
       <c r="O220" s="29" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="P220" s="29" t="n">
         <v>14</v>
       </c>
       <c r="Q220" s="29" t="n">
-        <v>10.23</v>
+        <v>9.81</v>
       </c>
       <c r="R220" s="45" t="n"/>
       <c r="S220" s="21" t="inlineStr">
@@ -23525,7 +23491,7 @@
     </row>
     <row r="221" ht="24" customHeight="1" s="54">
       <c r="A221" s="2" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
@@ -23622,7 +23588,7 @@
     </row>
     <row r="222" ht="24" customHeight="1" s="54">
       <c r="A222" s="2" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
@@ -23719,7 +23685,7 @@
     </row>
     <row r="223" ht="24" customHeight="1" s="54">
       <c r="A223" s="2" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
@@ -23816,7 +23782,7 @@
     </row>
     <row r="224" ht="24" customHeight="1" s="54">
       <c r="A224" s="2" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
@@ -23860,13 +23826,13 @@
       </c>
       <c r="N224" s="51" t="n"/>
       <c r="O224" s="29" t="n">
-        <v>-4.2</v>
+        <v>-2.7</v>
       </c>
       <c r="P224" s="29" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="Q224" s="29" t="n">
-        <v>-1.45</v>
+        <v>0.29</v>
       </c>
       <c r="R224" s="45" t="n"/>
       <c r="S224" s="21" t="inlineStr">
@@ -23933,7 +23899,7 @@
     </row>
     <row r="225" ht="24" customHeight="1" s="54">
       <c r="A225" s="2" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B225" s="2" t="n"/>
       <c r="C225" s="41" t="inlineStr">
@@ -24026,7 +23992,7 @@
     </row>
     <row r="226" ht="24" customHeight="1" s="54">
       <c r="A226" s="2" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
@@ -24070,13 +24036,13 @@
       </c>
       <c r="N226" s="51" t="n"/>
       <c r="O226" s="29" t="n">
-        <v>-1.5</v>
+        <v>-4.7</v>
       </c>
       <c r="P226" s="29" t="n">
-        <v>0.4</v>
+        <v>-1.1</v>
       </c>
       <c r="Q226" s="29" t="n">
-        <v>-0.33</v>
+        <v>-2.69</v>
       </c>
       <c r="R226" s="45" t="n"/>
       <c r="S226" s="21" t="inlineStr">
@@ -24139,7 +24105,7 @@
     </row>
     <row r="227" ht="24" customHeight="1" s="54">
       <c r="A227" s="2" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
@@ -24240,7 +24206,7 @@
     </row>
     <row r="228" ht="24" customHeight="1" s="54">
       <c r="A228" s="2" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
@@ -24343,7 +24309,7 @@
     </row>
     <row r="229" ht="24" customHeight="1" s="54">
       <c r="A229" s="2" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B229" s="2" t="n"/>
       <c r="C229" s="41" t="inlineStr">
@@ -24432,7 +24398,7 @@
     </row>
     <row r="230" ht="24" customHeight="1" s="54">
       <c r="A230" s="2" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
@@ -24476,13 +24442,13 @@
       </c>
       <c r="N230" s="51" t="n"/>
       <c r="O230" s="29" t="n">
-        <v>-2.1</v>
+        <v>-1</v>
       </c>
       <c r="P230" s="29" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="Q230" s="29" t="n">
-        <v>2.08</v>
+        <v>-0.04</v>
       </c>
       <c r="R230" s="45" t="n"/>
       <c r="S230" s="21" t="inlineStr">
@@ -24545,7 +24511,7 @@
     </row>
     <row r="231" ht="24" customHeight="1" s="54">
       <c r="A231" s="2" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
@@ -24642,7 +24608,7 @@
     </row>
     <row r="232" ht="24" customHeight="1" s="54">
       <c r="A232" s="2" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B232" s="2" t="n"/>
       <c r="C232" s="41" t="inlineStr">
@@ -24739,7 +24705,7 @@
     </row>
     <row r="233" ht="24" customHeight="1" s="54">
       <c r="A233" s="2" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
@@ -24783,13 +24749,13 @@
       </c>
       <c r="N233" s="51" t="n"/>
       <c r="O233" s="29" t="n">
-        <v>-1.5</v>
+        <v>0.7</v>
       </c>
       <c r="P233" s="29" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q233" s="29" t="n">
-        <v>-0.06</v>
+        <v>1.74</v>
       </c>
       <c r="R233" s="45" t="n"/>
       <c r="S233" s="21" t="inlineStr">
@@ -24852,7 +24818,7 @@
     </row>
     <row r="234" ht="24" customHeight="1" s="54">
       <c r="A234" s="2" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
@@ -24896,13 +24862,13 @@
       </c>
       <c r="N234" s="51" t="n"/>
       <c r="O234" s="29" t="n">
-        <v>-1.8</v>
+        <v>-2.6</v>
       </c>
       <c r="P234" s="29" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q234" s="29" t="n">
-        <v>0.45</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R234" s="45" t="n"/>
       <c r="S234" s="21" t="inlineStr">
@@ -24969,7 +24935,7 @@
     </row>
     <row r="235" ht="24" customHeight="1" s="54">
       <c r="A235" s="2" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
@@ -25070,7 +25036,7 @@
     </row>
     <row r="236" ht="24" customHeight="1" s="54">
       <c r="A236" s="2" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
@@ -25165,7 +25131,7 @@
     </row>
     <row r="237" ht="24" customHeight="1" s="54">
       <c r="A237" s="2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
@@ -25260,7 +25226,7 @@
     </row>
     <row r="238" ht="24" customHeight="1" s="54">
       <c r="A238" s="2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B238" s="2" t="n"/>
       <c r="C238" s="41" t="inlineStr">
@@ -25349,7 +25315,7 @@
     </row>
     <row r="239" ht="24" customHeight="1" s="54">
       <c r="A239" s="2" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
@@ -25397,13 +25363,13 @@
         </is>
       </c>
       <c r="O239" s="29" t="n">
-        <v>-7.2</v>
+        <v>-4.8</v>
       </c>
       <c r="P239" s="29" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="Q239" s="29" t="n">
-        <v>-3.38</v>
+        <v>-1.44</v>
       </c>
       <c r="R239" s="45" t="n"/>
       <c r="S239" s="21" t="inlineStr">
@@ -25454,7 +25420,7 @@
     </row>
     <row r="240" ht="24" customHeight="1" s="54">
       <c r="A240" s="2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
@@ -25549,7 +25515,7 @@
     </row>
     <row r="241" ht="24" customHeight="1" s="54">
       <c r="A241" s="2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B241" s="2" t="n"/>
       <c r="C241" s="41" t="n">
@@ -25644,7 +25610,7 @@
     </row>
     <row r="242" ht="24" customHeight="1" s="54">
       <c r="A242" s="2" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
@@ -25737,7 +25703,7 @@
     </row>
     <row r="243" ht="24" customHeight="1" s="54">
       <c r="A243" s="2" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
@@ -25828,7 +25794,7 @@
     </row>
     <row r="244" ht="24" customHeight="1" s="54">
       <c r="A244" s="2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
@@ -25917,7 +25883,7 @@
     </row>
     <row r="245" ht="24" customHeight="1" s="54">
       <c r="A245" s="2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
@@ -26014,7 +25980,7 @@
     </row>
     <row r="246" ht="24" customHeight="1" s="54">
       <c r="A246" s="2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
@@ -26107,7 +26073,7 @@
     </row>
     <row r="247" ht="24" customHeight="1" s="54">
       <c r="A247" s="2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
@@ -26206,7 +26172,7 @@
     </row>
     <row r="248" ht="24" customHeight="1" s="54">
       <c r="A248" s="2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
@@ -26305,7 +26271,7 @@
     </row>
     <row r="249" ht="24" customHeight="1" s="54">
       <c r="A249" s="2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
@@ -26406,7 +26372,7 @@
     </row>
     <row r="250" ht="24" customHeight="1" s="54">
       <c r="A250" s="2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
@@ -26495,7 +26461,7 @@
     </row>
     <row r="251" ht="24" customHeight="1" s="54">
       <c r="A251" s="2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
@@ -26588,7 +26554,7 @@
     </row>
     <row r="252" ht="24" customHeight="1" s="54">
       <c r="A252" s="2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
@@ -26684,7 +26650,7 @@
     </row>
     <row r="253" ht="24" customHeight="1" s="54">
       <c r="A253" s="2" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
@@ -26775,7 +26741,7 @@
     </row>
     <row r="254" ht="24" customHeight="1" s="54">
       <c r="A254" s="2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
@@ -26870,7 +26836,7 @@
     </row>
     <row r="255" ht="24" customHeight="1" s="54">
       <c r="A255" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
@@ -26961,7 +26927,7 @@
     </row>
     <row r="256" ht="24" customHeight="1" s="54">
       <c r="A256" s="2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
@@ -27056,7 +27022,7 @@
     </row>
     <row r="257" ht="24" customHeight="1" s="54">
       <c r="A257" s="2" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
@@ -27151,7 +27117,7 @@
     </row>
     <row r="258" ht="24" customHeight="1" s="54">
       <c r="A258" s="2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
@@ -27244,7 +27210,7 @@
     </row>
     <row r="259" ht="24" customHeight="1" s="54">
       <c r="A259" s="2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
@@ -27337,7 +27303,7 @@
     </row>
     <row r="260" ht="24" customHeight="1" s="54">
       <c r="A260" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
@@ -27430,7 +27396,7 @@
     </row>
     <row r="261" ht="24" customHeight="1" s="54">
       <c r="A261" s="2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
@@ -27529,7 +27495,7 @@
     </row>
     <row r="262" ht="24" customHeight="1" s="54">
       <c r="A262" s="2" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
@@ -27622,7 +27588,7 @@
     </row>
     <row r="263" ht="24" customHeight="1" s="54">
       <c r="A263" s="2" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
@@ -27713,7 +27679,7 @@
     </row>
     <row r="264" ht="24" customHeight="1" s="54">
       <c r="A264" s="2" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
@@ -27806,7 +27772,7 @@
     </row>
     <row r="265" ht="24" customHeight="1" s="54">
       <c r="A265" s="2" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
@@ -27854,13 +27820,13 @@
         </is>
       </c>
       <c r="O265" s="29" t="n">
-        <v>-22.5</v>
+        <v>-20.6</v>
       </c>
       <c r="P265" s="29" t="n">
-        <v>-9</v>
+        <v>-4.8</v>
       </c>
       <c r="Q265" s="29" t="n">
-        <v>-16.2</v>
+        <v>-12.15</v>
       </c>
       <c r="R265" s="45" t="n"/>
       <c r="S265" s="21" t="inlineStr">
@@ -27920,7 +27886,7 @@
     </row>
     <row r="266" ht="24" customHeight="1" s="54">
       <c r="A266" s="2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
@@ -28019,7 +27985,7 @@
     </row>
     <row r="267" ht="24" customHeight="1" s="54">
       <c r="A267" s="2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
@@ -28118,7 +28084,7 @@
     </row>
     <row r="268" ht="24" customHeight="1" s="54">
       <c r="A268" s="2" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
@@ -28217,7 +28183,7 @@
     </row>
     <row r="269" ht="24" customHeight="1" s="54">
       <c r="A269" s="2" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
@@ -28308,7 +28274,7 @@
     </row>
     <row r="270" ht="24" customHeight="1" s="54">
       <c r="A270" s="2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
@@ -28356,10 +28322,10 @@
         </is>
       </c>
       <c r="O270" s="29" t="n">
-        <v>-21.9</v>
+        <v>-11.8</v>
       </c>
       <c r="P270" s="29" t="n">
-        <v>-1.5</v>
+        <v>-1.1</v>
       </c>
       <c r="Q270" s="29" t="n"/>
       <c r="R270" s="45" t="n"/>
@@ -28420,7 +28386,7 @@
     </row>
     <row r="271" ht="24" customHeight="1" s="54">
       <c r="A271" s="2" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B271" s="2" t="n"/>
       <c r="C271" s="41" t="inlineStr">
@@ -28509,7 +28475,7 @@
     </row>
     <row r="272" ht="24" customHeight="1" s="54">
       <c r="A272" s="2" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B272" s="2" t="n"/>
       <c r="C272" s="41" t="inlineStr">
@@ -28598,7 +28564,7 @@
     </row>
     <row r="273" ht="24" customHeight="1" s="54">
       <c r="A273" s="2" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
@@ -28693,7 +28659,7 @@
     </row>
     <row r="274" ht="24" customHeight="1" s="54">
       <c r="A274" s="2" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
@@ -28741,10 +28707,10 @@
         </is>
       </c>
       <c r="O274" s="29" t="n">
-        <v>-66.59999999999999</v>
+        <v>-58.4</v>
       </c>
       <c r="P274" s="29" t="n">
-        <v>-53.3</v>
+        <v>-51.1</v>
       </c>
       <c r="Q274" s="29" t="n"/>
       <c r="R274" s="45" t="n"/>
@@ -28796,7 +28762,7 @@
     </row>
     <row r="275" ht="24" customHeight="1" s="54">
       <c r="A275" s="2" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
@@ -28893,7 +28859,7 @@
     </row>
     <row r="276" ht="24" customHeight="1" s="54">
       <c r="A276" s="2" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
@@ -28937,13 +28903,13 @@
       </c>
       <c r="N276" s="51" t="n"/>
       <c r="O276" s="29" t="n">
-        <v>-2.3</v>
+        <v>1.1</v>
       </c>
       <c r="P276" s="29" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="Q276" s="29" t="n">
-        <v>3.31</v>
+        <v>5.44</v>
       </c>
       <c r="R276" s="45" t="n"/>
       <c r="S276" s="21" t="inlineStr">
@@ -29002,7 +28968,7 @@
     </row>
     <row r="277" ht="24" customHeight="1" s="54">
       <c r="A277" s="2" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
@@ -29103,7 +29069,7 @@
     </row>
     <row r="278" ht="24" customHeight="1" s="54">
       <c r="A278" s="2" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
@@ -29153,13 +29119,13 @@
         </is>
       </c>
       <c r="O278" s="29" t="n">
-        <v>-4.1</v>
+        <v>-3.7</v>
       </c>
       <c r="P278" s="29" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="Q278" s="29" t="n">
-        <v>-1.53</v>
+        <v>-1.29</v>
       </c>
       <c r="R278" s="45" t="n"/>
       <c r="S278" s="21" t="inlineStr">
@@ -29214,7 +29180,7 @@
     </row>
     <row r="279" ht="24" customHeight="1" s="54">
       <c r="A279" s="2" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B279" s="2" t="n"/>
       <c r="C279" s="41" t="n">
@@ -29301,7 +29267,7 @@
     </row>
     <row r="280" ht="24" customHeight="1" s="54">
       <c r="A280" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B280" s="2" t="n"/>
       <c r="C280" s="41" t="inlineStr">
@@ -29398,7 +29364,7 @@
     </row>
     <row r="281" ht="24" customHeight="1" s="54">
       <c r="A281" s="2" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B281" s="2" t="n"/>
       <c r="C281" s="41" t="inlineStr">
@@ -29495,7 +29461,7 @@
     </row>
     <row r="282" ht="24" customHeight="1" s="54">
       <c r="A282" s="2" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B282" s="2" t="n"/>
       <c r="C282" s="41" t="inlineStr">
@@ -29596,7 +29562,7 @@
     </row>
     <row r="283" ht="24" customHeight="1" s="54">
       <c r="A283" s="2" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B283" s="2" t="n"/>
       <c r="C283" s="41" t="n"/>
@@ -29695,7 +29661,7 @@
     </row>
     <row r="284" ht="24" customHeight="1" s="54">
       <c r="A284" s="2" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B284" s="2" t="n"/>
       <c r="C284" s="41" t="n"/>
@@ -29794,7 +29760,7 @@
     </row>
     <row r="285" ht="24" customHeight="1" s="54">
       <c r="A285" s="2" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B285" s="2" t="n"/>
       <c r="C285" s="41" t="n"/>
@@ -29893,7 +29859,7 @@
     </row>
     <row r="286" ht="24" customHeight="1" s="54">
       <c r="A286" s="2" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B286" s="2" t="n"/>
       <c r="C286" s="41" t="n"/>
@@ -29992,7 +29958,7 @@
     </row>
     <row r="287" ht="24" customHeight="1" s="54">
       <c r="A287" s="2" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B287" s="2" t="n"/>
       <c r="C287" s="41" t="n">
@@ -30027,15 +29993,9 @@
         </is>
       </c>
       <c r="N287" s="51" t="n"/>
-      <c r="O287" s="29" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="P287" s="29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Q287" s="29" t="n">
-        <v>-2.93</v>
-      </c>
+      <c r="O287" s="29" t="n"/>
+      <c r="P287" s="29" t="n"/>
+      <c r="Q287" s="29" t="n"/>
       <c r="R287" s="45" t="n"/>
       <c r="S287" s="21" t="n"/>
       <c r="T287" s="33" t="n"/>
@@ -30093,7 +30053,7 @@
     </row>
     <row r="288" ht="24" customHeight="1" s="54">
       <c r="A288" s="2" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B288" s="2" t="n"/>
       <c r="C288" s="41" t="n">
@@ -30188,7 +30148,7 @@
     </row>
     <row r="289" ht="24" customHeight="1" s="54">
       <c r="A289" s="2" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B289" s="2" t="n"/>
       <c r="C289" s="41" t="n">
@@ -30287,7 +30247,7 @@
     </row>
     <row r="290" ht="24" customHeight="1" s="54">
       <c r="A290" s="2" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
@@ -30396,7 +30356,7 @@
     </row>
     <row r="291" ht="24" customHeight="1" s="54">
       <c r="A291" s="2" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B291" s="2" t="n"/>
       <c r="C291" s="41" t="n"/>
@@ -30485,7 +30445,7 @@
     </row>
     <row r="292" ht="24" customHeight="1" s="54">
       <c r="A292" s="2" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B292" s="2" t="n"/>
       <c r="C292" s="41" t="n">
@@ -30584,7 +30544,7 @@
     </row>
     <row r="293" ht="24" customHeight="1" s="54">
       <c r="A293" s="2" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B293" s="2" t="n"/>
       <c r="C293" s="41" t="n">
@@ -30673,7 +30633,7 @@
     </row>
     <row r="294" ht="24" customHeight="1" s="54">
       <c r="A294" s="2" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B294" s="2" t="n"/>
       <c r="C294" s="41" t="n">
@@ -30772,7 +30732,7 @@
     </row>
     <row r="295" ht="24" customHeight="1" s="54">
       <c r="A295" s="2" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B295" s="2" t="n"/>
       <c r="C295" s="41" t="inlineStr">
@@ -30865,7 +30825,7 @@
     </row>
     <row r="296" ht="24" customHeight="1" s="54">
       <c r="A296" s="2" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B296" s="2" t="n"/>
       <c r="C296" s="41" t="n"/>
@@ -30960,7 +30920,7 @@
     </row>
     <row r="297" ht="24" customHeight="1" s="54">
       <c r="A297" s="2" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B297" s="2" t="n"/>
       <c r="C297" s="41" t="n">
@@ -31055,7 +31015,7 @@
     </row>
     <row r="298" ht="24" customHeight="1" s="54">
       <c r="A298" s="2" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B298" s="2" t="n"/>
       <c r="C298" s="41" t="n"/>
@@ -31144,7 +31104,7 @@
     </row>
     <row r="299" ht="24" customHeight="1" s="54">
       <c r="A299" s="2" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B299" s="2" t="n"/>
       <c r="C299" s="41" t="n"/>
@@ -31229,7 +31189,7 @@
     </row>
     <row r="300" ht="24" customHeight="1" s="54">
       <c r="A300" s="2" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
@@ -31328,7 +31288,7 @@
     </row>
     <row r="301" ht="24" customHeight="1" s="54">
       <c r="A301" s="2" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B301" s="2" t="n"/>
       <c r="C301" s="41" t="n">
@@ -31419,7 +31379,7 @@
     </row>
     <row r="302" ht="24" customHeight="1" s="54">
       <c r="A302" s="2" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B302" s="2" t="n"/>
       <c r="C302" s="41" t="n"/>
@@ -31518,7 +31478,7 @@
     </row>
     <row r="303" ht="24" customHeight="1" s="54">
       <c r="A303" s="2" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B303" s="2" t="n"/>
       <c r="C303" s="41" t="n"/>
@@ -31625,7 +31585,7 @@
     </row>
     <row r="304" ht="24" customHeight="1" s="54">
       <c r="A304" s="2" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B304" s="2" t="n"/>
       <c r="C304" s="41" t="n">
@@ -31724,7 +31684,7 @@
     </row>
     <row r="305" ht="24" customHeight="1" s="54">
       <c r="A305" s="2" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B305" s="2" t="n"/>
       <c r="C305" s="41" t="n"/>
@@ -31835,7 +31795,7 @@
     </row>
     <row r="306" ht="24" customHeight="1" s="54">
       <c r="A306" s="2" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B306" s="2" t="n"/>
       <c r="C306" s="41" t="n"/>
@@ -31934,7 +31894,7 @@
     </row>
     <row r="307" ht="24" customHeight="1" s="54">
       <c r="A307" s="2" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B307" s="2" t="n"/>
       <c r="C307" s="41" t="n"/>
@@ -32033,7 +31993,7 @@
     </row>
     <row r="308" ht="24" customHeight="1" s="54">
       <c r="A308" s="2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B308" s="2" t="n"/>
       <c r="C308" s="41" t="n"/>
@@ -32132,7 +32092,7 @@
     </row>
     <row r="309" ht="24" customHeight="1" s="54">
       <c r="A309" s="2" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B309" s="2" t="n"/>
       <c r="C309" s="41" t="n"/>
@@ -32231,7 +32191,7 @@
     </row>
     <row r="310" ht="24" customHeight="1" s="54">
       <c r="A310" s="2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B310" s="2" t="n"/>
       <c r="C310" s="41" t="n"/>
@@ -32320,7 +32280,7 @@
     </row>
     <row r="311" ht="24" customHeight="1" s="54">
       <c r="A311" s="2" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B311" s="2" t="n"/>
       <c r="C311" s="41" t="n"/>
@@ -32419,7 +32379,7 @@
     </row>
     <row r="312" ht="24" customHeight="1" s="54">
       <c r="A312" s="2" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B312" s="2" t="n"/>
       <c r="C312" s="41" t="n"/>
@@ -32512,7 +32472,7 @@
     </row>
     <row r="313" ht="24" customHeight="1" s="54">
       <c r="A313" s="2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B313" s="2" t="n"/>
       <c r="C313" s="41" t="n"/>
@@ -32601,7 +32561,7 @@
     </row>
     <row r="314" ht="24" customHeight="1" s="54">
       <c r="A314" s="2" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B314" s="2" t="n"/>
       <c r="C314" s="41" t="n"/>
@@ -32690,7 +32650,7 @@
     </row>
     <row r="315" ht="24" customHeight="1" s="54">
       <c r="A315" s="2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B315" s="2" t="n"/>
       <c r="C315" s="41" t="n"/>
@@ -32783,7 +32743,7 @@
     </row>
     <row r="316" ht="24" customHeight="1" s="54">
       <c r="A316" s="2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B316" s="2" t="n"/>
       <c r="C316" s="41" t="n"/>
@@ -32876,7 +32836,7 @@
     </row>
     <row r="317" ht="24" customHeight="1" s="54">
       <c r="A317" s="2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B317" s="2" t="n"/>
       <c r="C317" s="41" t="n"/>
@@ -32961,7 +32921,7 @@
     </row>
     <row r="318" ht="24" customHeight="1" s="54">
       <c r="A318" s="2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B318" s="2" t="n"/>
       <c r="C318" s="41" t="n"/>
@@ -33056,7 +33016,7 @@
     </row>
     <row r="319" ht="24" customHeight="1" s="54">
       <c r="A319" s="2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
@@ -33163,7 +33123,7 @@
     </row>
     <row r="320" ht="24" customHeight="1" s="54">
       <c r="A320" s="2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B320" s="2" t="n"/>
       <c r="C320" s="41" t="n">
@@ -33262,7 +33222,7 @@
     </row>
     <row r="321" ht="24" customHeight="1" s="54">
       <c r="A321" s="2" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B321" s="2" t="n"/>
       <c r="C321" s="41" t="n"/>
@@ -33359,7 +33319,7 @@
     </row>
     <row r="322" ht="24" customHeight="1" s="54">
       <c r="A322" s="2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B322" s="2" t="n"/>
       <c r="C322" s="41" t="n"/>
@@ -33454,7 +33414,7 @@
     </row>
     <row r="323" ht="24" customHeight="1" s="54">
       <c r="A323" s="2" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B323" s="2" t="n"/>
       <c r="C323" s="41" t="n"/>
@@ -33549,7 +33509,7 @@
     </row>
     <row r="324" ht="24" customHeight="1" s="54">
       <c r="A324" s="2" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B324" s="2" t="n"/>
       <c r="C324" s="41" t="n"/>
@@ -33648,7 +33608,7 @@
     </row>
     <row r="325" ht="24" customHeight="1" s="54">
       <c r="A325" s="2" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B325" s="2" t="n"/>
       <c r="C325" s="41" t="n"/>
@@ -33747,7 +33707,7 @@
     </row>
     <row r="326" ht="24" customHeight="1" s="54">
       <c r="A326" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B326" s="2" t="n"/>
       <c r="C326" s="41" t="n"/>
@@ -33846,7 +33806,7 @@
     </row>
     <row r="327" ht="24" customHeight="1" s="54">
       <c r="A327" s="2" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B327" s="2" t="n"/>
       <c r="C327" s="41" t="n"/>
@@ -33881,12 +33841,8 @@
         </is>
       </c>
       <c r="N327" s="51" t="n"/>
-      <c r="O327" s="29" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="P327" s="29" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="O327" s="29" t="n"/>
+      <c r="P327" s="29" t="n"/>
       <c r="Q327" s="29" t="n"/>
       <c r="R327" s="45" t="n"/>
       <c r="S327" s="21" t="n"/>
@@ -33949,7 +33905,7 @@
     </row>
     <row r="328" ht="24" customHeight="1" s="54">
       <c r="A328" s="2" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B328" s="2" t="n"/>
       <c r="C328" s="41" t="n"/>
@@ -34042,7 +33998,7 @@
     </row>
     <row r="329" ht="24" customHeight="1" s="54">
       <c r="A329" s="2" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B329" s="2" t="n"/>
       <c r="C329" s="41" t="n"/>
@@ -34131,7 +34087,7 @@
     </row>
     <row r="330" ht="24" customHeight="1" s="54">
       <c r="A330" s="2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B330" s="2" t="n"/>
       <c r="C330" s="41" t="n"/>
@@ -34166,8 +34122,12 @@
         </is>
       </c>
       <c r="N330" s="51" t="n"/>
-      <c r="O330" s="29" t="n"/>
-      <c r="P330" s="29" t="n"/>
+      <c r="O330" s="29" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="P330" s="29" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q330" s="29" t="n"/>
       <c r="R330" s="45" t="n"/>
       <c r="S330" s="21" t="n"/>
@@ -34230,7 +34190,7 @@
     </row>
     <row r="331" ht="24" customHeight="1" s="54">
       <c r="A331" s="2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B331" s="2" t="n"/>
       <c r="C331" s="41" t="n"/>
@@ -34319,7 +34279,7 @@
     </row>
     <row r="332" ht="24" customHeight="1" s="54">
       <c r="A332" s="2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B332" s="2" t="n"/>
       <c r="C332" s="41" t="n"/>
@@ -34408,7 +34368,7 @@
     </row>
     <row r="333" ht="24" customHeight="1" s="54">
       <c r="A333" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B333" s="2" t="n"/>
       <c r="C333" s="41" t="inlineStr">
@@ -34505,7 +34465,7 @@
     </row>
     <row r="334" ht="24" customHeight="1" s="54">
       <c r="A334" s="2" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B334" s="2" t="n"/>
       <c r="C334" s="41" t="n"/>
@@ -34600,7 +34560,7 @@
     </row>
     <row r="335" ht="24" customHeight="1" s="54">
       <c r="A335" s="2" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B335" s="2" t="n"/>
       <c r="C335" s="41" t="n">
@@ -34699,7 +34659,7 @@
     </row>
     <row r="336" ht="24" customHeight="1" s="54">
       <c r="A336" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B336" s="2" t="n"/>
       <c r="C336" s="41" t="n"/>
@@ -34784,7 +34744,7 @@
     </row>
     <row r="337" ht="24" customHeight="1" s="54">
       <c r="A337" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B337" s="2" t="n"/>
       <c r="C337" s="41" t="n"/>
@@ -34883,7 +34843,7 @@
     </row>
     <row r="338" ht="24" customHeight="1" s="54">
       <c r="A338" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B338" s="2" t="n"/>
       <c r="C338" s="41" t="n"/>
@@ -34968,7 +34928,7 @@
     </row>
     <row r="339" ht="24" customHeight="1" s="54">
       <c r="A339" s="2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B339" s="2" t="n"/>
       <c r="C339" s="41" t="n"/>
@@ -35063,7 +35023,7 @@
     </row>
     <row r="340" ht="24" customHeight="1" s="54">
       <c r="A340" s="2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B340" s="2" t="n"/>
       <c r="C340" s="41" t="n"/>
@@ -35148,7 +35108,7 @@
     </row>
     <row r="341" ht="24" customHeight="1" s="54">
       <c r="A341" s="2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B341" s="2" t="n"/>
       <c r="C341" s="41" t="n"/>
@@ -35233,7 +35193,7 @@
     </row>
     <row r="342" ht="24" customHeight="1" s="54">
       <c r="A342" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B342" s="2" t="n"/>
       <c r="C342" s="41" t="n"/>
@@ -35314,7 +35274,7 @@
     </row>
     <row r="343" ht="24" customHeight="1" s="54">
       <c r="A343" s="2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
@@ -35413,7 +35373,7 @@
     </row>
     <row r="344" ht="24" customHeight="1" s="54">
       <c r="A344" s="2" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
@@ -35516,7 +35476,7 @@
     </row>
     <row r="345" ht="24" customHeight="1" s="54">
       <c r="A345" s="2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
@@ -35617,7 +35577,7 @@
     </row>
     <row r="346" ht="24" customHeight="1" s="54">
       <c r="A346" s="2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B346" s="2" t="n"/>
       <c r="C346" s="41" t="n"/>
@@ -35712,7 +35672,7 @@
     </row>
     <row r="347" ht="24" customHeight="1" s="54">
       <c r="A347" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B347" s="2" t="n"/>
       <c r="C347" s="41" t="inlineStr">
@@ -35811,7 +35771,7 @@
     </row>
     <row r="348" ht="24" customHeight="1" s="54">
       <c r="A348" s="2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B348" s="2" t="n"/>
       <c r="C348" s="41" t="n">
@@ -35910,7 +35870,7 @@
     </row>
     <row r="349" ht="24" customHeight="1" s="54">
       <c r="A349" s="2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B349" s="2" t="n"/>
       <c r="C349" s="41" t="inlineStr">
@@ -36015,7 +35975,7 @@
     </row>
     <row r="350" ht="24" customHeight="1" s="54">
       <c r="A350" s="2" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B350" s="2" t="n"/>
       <c r="C350" s="41" t="n"/>
@@ -36023,17 +35983,17 @@
       <c r="E350" s="3" t="n"/>
       <c r="F350" s="35" t="inlineStr">
         <is>
-          <t>X2081</t>
+          <t>X2068</t>
         </is>
       </c>
       <c r="G350" s="26" t="n">
-        <v>38.184</v>
+        <v>35.904</v>
       </c>
       <c r="H350" s="26" t="n">
-        <v>97.59399999999999</v>
+        <v>93.404</v>
       </c>
       <c r="I350" s="2" t="n">
-        <v>4103</v>
+        <v>4396</v>
       </c>
       <c r="J350" s="24" t="n">
         <v>12</v>
@@ -36046,13 +36006,19 @@
       <c r="L350" s="51" t="n"/>
       <c r="M350" s="13" t="inlineStr">
         <is>
-          <t>哈拉湖</t>
+          <t>西王母瑶池</t>
         </is>
       </c>
       <c r="N350" s="51" t="n"/>
-      <c r="O350" s="29" t="n"/>
-      <c r="P350" s="29" t="n"/>
-      <c r="Q350" s="29" t="n"/>
+      <c r="O350" s="29" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="P350" s="29" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="Q350" s="29" t="n">
+        <v>-13.9</v>
+      </c>
       <c r="R350" s="45" t="n"/>
       <c r="S350" s="21" t="n"/>
       <c r="T350" s="33" t="n"/>
@@ -36089,7 +36055,7 @@
       </c>
       <c r="AB350" s="2" t="inlineStr">
         <is>
-          <t>德令哈市</t>
+          <t>格尔木市</t>
         </is>
       </c>
       <c r="AC350" s="2" t="n"/>
@@ -36114,7 +36080,7 @@
     </row>
     <row r="351" ht="24" customHeight="1" s="54">
       <c r="A351" s="2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B351" s="2" t="n"/>
       <c r="C351" s="41" t="n"/>
@@ -36122,17 +36088,17 @@
       <c r="E351" s="3" t="n"/>
       <c r="F351" s="35" t="inlineStr">
         <is>
-          <t>X7049</t>
+          <t>X2081</t>
         </is>
       </c>
       <c r="G351" s="26" t="n">
-        <v>33.62</v>
+        <v>38.184</v>
       </c>
       <c r="H351" s="26" t="n">
-        <v>97.197</v>
+        <v>97.59399999999999</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>4365.6</v>
+        <v>4103</v>
       </c>
       <c r="J351" s="24" t="n">
         <v>12</v>
@@ -36145,14 +36111,10 @@
       <c r="L351" s="51" t="n"/>
       <c r="M351" s="13" t="inlineStr">
         <is>
-          <t>珍秦永郎达</t>
-        </is>
-      </c>
-      <c r="N351" s="51" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
+          <t>哈拉湖</t>
+        </is>
+      </c>
+      <c r="N351" s="51" t="n"/>
       <c r="O351" s="29" t="n"/>
       <c r="P351" s="29" t="n"/>
       <c r="Q351" s="29" t="n"/>
@@ -36187,12 +36149,12 @@
       <c r="Z351" s="3" t="n"/>
       <c r="AA351" s="2" t="inlineStr">
         <is>
-          <t>玉树藏族自治州</t>
+          <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
       <c r="AB351" s="2" t="inlineStr">
         <is>
-          <t>称多县</t>
+          <t>德令哈市</t>
         </is>
       </c>
       <c r="AC351" s="2" t="n"/>
@@ -36213,43 +36175,29 @@
           <t>青藏高原</t>
         </is>
       </c>
-      <c r="AI351" s="2" t="inlineStr">
-        <is>
-          <t>竹节梁</t>
-        </is>
-      </c>
+      <c r="AI351" s="2" t="n"/>
     </row>
     <row r="352" ht="24" customHeight="1" s="54">
       <c r="A352" s="2" t="n">
-        <v>350</v>
-      </c>
-      <c r="B352" s="2" t="inlineStr">
-        <is>
-          <t>ogimet</t>
-        </is>
-      </c>
-      <c r="C352" s="41" t="inlineStr">
-        <is>
-          <t>56033</t>
-        </is>
-      </c>
-      <c r="D352" s="2" t="inlineStr">
-        <is>
-          <t>Machali</t>
-        </is>
-      </c>
-      <c r="E352" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F352" s="35" t="n"/>
+        <v>351</v>
+      </c>
+      <c r="B352" s="2" t="n"/>
+      <c r="C352" s="41" t="n"/>
+      <c r="D352" s="2" t="n"/>
+      <c r="E352" s="3" t="n"/>
+      <c r="F352" s="35" t="inlineStr">
+        <is>
+          <t>X7049</t>
+        </is>
+      </c>
       <c r="G352" s="26" t="n">
-        <v>34.9172</v>
+        <v>33.62</v>
       </c>
       <c r="H352" s="26" t="n">
-        <v>98.2158</v>
+        <v>97.197</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>4271.7</v>
+        <v>4365.6</v>
       </c>
       <c r="J352" s="24" t="n">
         <v>12</v>
@@ -36262,10 +36210,10 @@
       <c r="L352" s="51" t="n"/>
       <c r="M352" s="13" t="inlineStr">
         <is>
-          <t>玛多</t>
-        </is>
-      </c>
-      <c r="N352" s="53" t="inlineStr">
+          <t>珍秦永郎达</t>
+        </is>
+      </c>
+      <c r="N352" s="51" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -36304,12 +36252,12 @@
       <c r="Z352" s="3" t="n"/>
       <c r="AA352" s="2" t="inlineStr">
         <is>
-          <t>果洛藏族自治州</t>
+          <t>玉树藏族自治州</t>
         </is>
       </c>
       <c r="AB352" s="2" t="inlineStr">
         <is>
-          <t>玛多县</t>
+          <t>称多县</t>
         </is>
       </c>
       <c r="AC352" s="2" t="n"/>
@@ -36330,31 +36278,43 @@
           <t>青藏高原</t>
         </is>
       </c>
-      <c r="AI352" s="2" t="n"/>
+      <c r="AI352" s="2" t="inlineStr">
+        <is>
+          <t>竹节梁</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="24" customHeight="1" s="54">
       <c r="A353" s="2" t="n">
-        <v>351</v>
-      </c>
-      <c r="B353" s="2" t="n"/>
+        <v>352</v>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
       <c r="C353" s="41" t="inlineStr">
         <is>
-          <t>54301</t>
-        </is>
-      </c>
-      <c r="D353" s="2" t="n"/>
+          <t>56033</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>Machali</t>
+        </is>
+      </c>
       <c r="E353" s="3" t="n">
         <v>99999</v>
       </c>
       <c r="F353" s="35" t="n"/>
       <c r="G353" s="26" t="n">
-        <v>41.6719</v>
+        <v>34.9172</v>
       </c>
       <c r="H353" s="26" t="n">
-        <v>115.6531</v>
+        <v>98.2158</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>1409.6</v>
+        <v>4271.7</v>
       </c>
       <c r="J353" s="24" t="n">
         <v>12</v>
@@ -36367,10 +36327,14 @@
       <c r="L353" s="51" t="n"/>
       <c r="M353" s="13" t="inlineStr">
         <is>
-          <t>沽源</t>
-        </is>
-      </c>
-      <c r="N353" s="51" t="n"/>
+          <t>玛多</t>
+        </is>
+      </c>
+      <c r="N353" s="53" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
       <c r="O353" s="29" t="n"/>
       <c r="P353" s="29" t="n"/>
       <c r="Q353" s="29" t="n"/>
@@ -36379,12 +36343,12 @@
       <c r="T353" s="33" t="n"/>
       <c r="U353" s="37" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="V353" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="W353" s="3" t="inlineStr">
@@ -36405,12 +36369,12 @@
       <c r="Z353" s="3" t="n"/>
       <c r="AA353" s="2" t="inlineStr">
         <is>
-          <t>张家口市</t>
+          <t>果洛藏族自治州</t>
         </is>
       </c>
       <c r="AB353" s="2" t="inlineStr">
         <is>
-          <t>沽源县</t>
+          <t>玛多县</t>
         </is>
       </c>
       <c r="AC353" s="2" t="n"/>
@@ -36426,30 +36390,36 @@
         </is>
       </c>
       <c r="AG353" s="3" t="n"/>
-      <c r="AH353" s="2" t="n"/>
+      <c r="AH353" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AI353" s="2" t="n"/>
     </row>
     <row r="354" ht="24" customHeight="1" s="54">
       <c r="A354" s="2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B354" s="2" t="n"/>
-      <c r="C354" s="41" t="n"/>
+      <c r="C354" s="41" t="inlineStr">
+        <is>
+          <t>54301</t>
+        </is>
+      </c>
       <c r="D354" s="2" t="n"/>
-      <c r="E354" s="3" t="n"/>
-      <c r="F354" s="35" t="inlineStr">
-        <is>
-          <t>B5276</t>
-        </is>
-      </c>
+      <c r="E354" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F354" s="35" t="n"/>
       <c r="G354" s="26" t="n">
-        <v>39.7886</v>
+        <v>41.6719</v>
       </c>
       <c r="H354" s="26" t="n">
-        <v>112.8256</v>
+        <v>115.6531</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>1349</v>
+        <v>1409.6</v>
       </c>
       <c r="J354" s="24" t="n">
         <v>12</v>
@@ -36462,7 +36432,7 @@
       <c r="L354" s="51" t="n"/>
       <c r="M354" s="13" t="inlineStr">
         <is>
-          <t>(右玉)吴家窑</t>
+          <t>沽源</t>
         </is>
       </c>
       <c r="N354" s="51" t="n"/>
@@ -36474,12 +36444,12 @@
       <c r="T354" s="33" t="n"/>
       <c r="U354" s="37" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="V354" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="W354" s="3" t="inlineStr">
@@ -36500,12 +36470,12 @@
       <c r="Z354" s="3" t="n"/>
       <c r="AA354" s="2" t="inlineStr">
         <is>
-          <t>朔州市</t>
+          <t>张家口市</t>
         </is>
       </c>
       <c r="AB354" s="2" t="inlineStr">
         <is>
-          <t>怀仁市</t>
+          <t>沽源县</t>
         </is>
       </c>
       <c r="AC354" s="2" t="n"/>
@@ -36526,35 +36496,25 @@
     </row>
     <row r="355" ht="24" customHeight="1" s="54">
       <c r="A355" s="2" t="n">
-        <v>353</v>
-      </c>
-      <c r="B355" s="2" t="inlineStr">
-        <is>
-          <t>ogimet</t>
-        </is>
-      </c>
-      <c r="C355" s="41" t="inlineStr">
-        <is>
-          <t>53487</t>
-        </is>
-      </c>
-      <c r="D355" s="2" t="inlineStr">
-        <is>
-          <t>Datong</t>
-        </is>
-      </c>
-      <c r="E355" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F355" s="35" t="n"/>
+        <v>354</v>
+      </c>
+      <c r="B355" s="2" t="n"/>
+      <c r="C355" s="41" t="n"/>
+      <c r="D355" s="2" t="n"/>
+      <c r="E355" s="3" t="n"/>
+      <c r="F355" s="35" t="inlineStr">
+        <is>
+          <t>B5276</t>
+        </is>
+      </c>
       <c r="G355" s="26" t="n">
-        <v>40.0789</v>
+        <v>39.7886</v>
       </c>
       <c r="H355" s="26" t="n">
-        <v>113.4117</v>
+        <v>112.8256</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>1052.4</v>
+        <v>1349</v>
       </c>
       <c r="J355" s="24" t="n">
         <v>12</v>
@@ -36567,7 +36527,7 @@
       <c r="L355" s="51" t="n"/>
       <c r="M355" s="13" t="inlineStr">
         <is>
-          <t>大同</t>
+          <t>(右玉)吴家窑</t>
         </is>
       </c>
       <c r="N355" s="51" t="n"/>
@@ -36605,10 +36565,14 @@
       <c r="Z355" s="3" t="n"/>
       <c r="AA355" s="2" t="inlineStr">
         <is>
-          <t>大同市</t>
-        </is>
-      </c>
-      <c r="AB355" s="2" t="n"/>
+          <t>朔州市</t>
+        </is>
+      </c>
+      <c r="AB355" s="2" t="inlineStr">
+        <is>
+          <t>怀仁市</t>
+        </is>
+      </c>
       <c r="AC355" s="2" t="n"/>
       <c r="AD355" s="2" t="n"/>
       <c r="AE355" s="2" t="inlineStr">
@@ -36627,7 +36591,7 @@
     </row>
     <row r="356" ht="24" customHeight="1" s="54">
       <c r="A356" s="2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
@@ -36636,12 +36600,12 @@
       </c>
       <c r="C356" s="41" t="inlineStr">
         <is>
-          <t>53646</t>
+          <t>53487</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Yulin</t>
+          <t>Datong</t>
         </is>
       </c>
       <c r="E356" s="3" t="n">
@@ -36649,13 +36613,13 @@
       </c>
       <c r="F356" s="35" t="n"/>
       <c r="G356" s="26" t="n">
-        <v>38.2686</v>
+        <v>40.0789</v>
       </c>
       <c r="H356" s="26" t="n">
-        <v>109.7803</v>
+        <v>113.4117</v>
       </c>
       <c r="I356" s="2" t="n">
-        <v>1161.7</v>
+        <v>1052.4</v>
       </c>
       <c r="J356" s="24" t="n">
         <v>12</v>
@@ -36668,7 +36632,7 @@
       <c r="L356" s="51" t="n"/>
       <c r="M356" s="13" t="inlineStr">
         <is>
-          <t>榆林</t>
+          <t>大同</t>
         </is>
       </c>
       <c r="N356" s="51" t="n"/>
@@ -36680,12 +36644,12 @@
       <c r="T356" s="33" t="n"/>
       <c r="U356" s="37" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="V356" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="W356" s="3" t="inlineStr">
@@ -36706,7 +36670,7 @@
       <c r="Z356" s="3" t="n"/>
       <c r="AA356" s="2" t="inlineStr">
         <is>
-          <t>榆林市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="AB356" s="2" t="n"/>
@@ -36728,27 +36692,35 @@
     </row>
     <row r="357" ht="24" customHeight="1" s="54">
       <c r="A357" s="2" t="n">
-        <v>355</v>
-      </c>
-      <c r="B357" s="2" t="n"/>
+        <v>356</v>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
       <c r="C357" s="41" t="inlineStr">
         <is>
-          <t>56038</t>
-        </is>
-      </c>
-      <c r="D357" s="2" t="n"/>
+          <t>53646</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Yulin</t>
+        </is>
+      </c>
       <c r="E357" s="3" t="n">
         <v>99999</v>
       </c>
       <c r="F357" s="35" t="n"/>
       <c r="G357" s="26" t="n">
-        <v>32.9764</v>
+        <v>38.2686</v>
       </c>
       <c r="H357" s="26" t="n">
-        <v>98.09690000000001</v>
+        <v>109.7803</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>4181.2</v>
+        <v>1161.7</v>
       </c>
       <c r="J357" s="24" t="n">
         <v>12</v>
@@ -36761,28 +36733,24 @@
       <c r="L357" s="51" t="n"/>
       <c r="M357" s="13" t="inlineStr">
         <is>
-          <t>石渠</t>
+          <t>榆林</t>
         </is>
       </c>
       <c r="N357" s="51" t="n"/>
       <c r="O357" s="29" t="n"/>
       <c r="P357" s="29" t="n"/>
       <c r="Q357" s="29" t="n"/>
-      <c r="R357" s="45" t="inlineStr">
-        <is>
-          <t>1995-12-29</t>
-        </is>
-      </c>
+      <c r="R357" s="45" t="n"/>
       <c r="S357" s="21" t="n"/>
       <c r="T357" s="33" t="n"/>
       <c r="U357" s="37" t="inlineStr">
         <is>
-          <t>川西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="V357" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="W357" s="3" t="inlineStr">
@@ -36803,14 +36771,10 @@
       <c r="Z357" s="3" t="n"/>
       <c r="AA357" s="2" t="inlineStr">
         <is>
-          <t>甘孜藏族自治州</t>
-        </is>
-      </c>
-      <c r="AB357" s="2" t="inlineStr">
-        <is>
-          <t>石渠县</t>
-        </is>
-      </c>
+          <t>榆林市</t>
+        </is>
+      </c>
+      <c r="AB357" s="2" t="n"/>
       <c r="AC357" s="2" t="n"/>
       <c r="AD357" s="2" t="n"/>
       <c r="AE357" s="2" t="inlineStr">
@@ -36824,34 +36788,32 @@
         </is>
       </c>
       <c r="AG357" s="3" t="n"/>
-      <c r="AH357" s="2" t="inlineStr">
-        <is>
-          <t>青藏高原</t>
-        </is>
-      </c>
+      <c r="AH357" s="2" t="n"/>
       <c r="AI357" s="2" t="n"/>
     </row>
     <row r="358" ht="24" customHeight="1" s="54">
       <c r="A358" s="2" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B358" s="2" t="n"/>
-      <c r="C358" s="41" t="n"/>
+      <c r="C358" s="41" t="inlineStr">
+        <is>
+          <t>56038</t>
+        </is>
+      </c>
       <c r="D358" s="2" t="n"/>
-      <c r="E358" s="3" t="n"/>
-      <c r="F358" s="35" t="inlineStr">
-        <is>
-          <t>A1490</t>
-        </is>
-      </c>
+      <c r="E358" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F358" s="35" t="n"/>
       <c r="G358" s="26" t="n">
-        <v>40.556</v>
+        <v>32.9764</v>
       </c>
       <c r="H358" s="26" t="n">
-        <v>115.793</v>
+        <v>98.09690000000001</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>1798</v>
+        <v>4181.2</v>
       </c>
       <c r="J358" s="24" t="n">
         <v>12</v>
@@ -36864,32 +36826,28 @@
       <c r="L358" s="51" t="n"/>
       <c r="M358" s="13" t="inlineStr">
         <is>
-          <t>海坨山</t>
-        </is>
-      </c>
-      <c r="N358" s="51" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
+          <t>石渠</t>
+        </is>
+      </c>
+      <c r="N358" s="51" t="n"/>
       <c r="O358" s="29" t="n"/>
       <c r="P358" s="29" t="n"/>
       <c r="Q358" s="29" t="n"/>
       <c r="R358" s="45" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>1995-12-29</t>
         </is>
       </c>
       <c r="S358" s="21" t="n"/>
       <c r="T358" s="33" t="n"/>
       <c r="U358" s="37" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>川西</t>
         </is>
       </c>
       <c r="V358" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="W358" s="3" t="inlineStr">
@@ -36910,10 +36868,14 @@
       <c r="Z358" s="3" t="n"/>
       <c r="AA358" s="2" t="inlineStr">
         <is>
-          <t>延庆区</t>
-        </is>
-      </c>
-      <c r="AB358" s="2" t="n"/>
+          <t>甘孜藏族自治州</t>
+        </is>
+      </c>
+      <c r="AB358" s="2" t="inlineStr">
+        <is>
+          <t>石渠县</t>
+        </is>
+      </c>
       <c r="AC358" s="2" t="n"/>
       <c r="AD358" s="2" t="n"/>
       <c r="AE358" s="2" t="inlineStr">
@@ -36927,38 +36889,34 @@
         </is>
       </c>
       <c r="AG358" s="3" t="n"/>
-      <c r="AH358" s="2" t="n"/>
-      <c r="AI358" s="2" t="inlineStr">
-        <is>
-          <t>竞速训练1</t>
-        </is>
-      </c>
+      <c r="AH358" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
+      <c r="AI358" s="2" t="n"/>
     </row>
     <row r="359" ht="24" customHeight="1" s="54">
       <c r="A359" s="2" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B359" s="2" t="n"/>
-      <c r="C359" s="41" t="n">
-        <v>58968</v>
-      </c>
-      <c r="D359" s="2" t="inlineStr">
-        <is>
-          <t>Taipei</t>
-        </is>
-      </c>
-      <c r="E359" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F359" s="35" t="n"/>
+      <c r="C359" s="41" t="n"/>
+      <c r="D359" s="2" t="n"/>
+      <c r="E359" s="3" t="n"/>
+      <c r="F359" s="35" t="inlineStr">
+        <is>
+          <t>A1490</t>
+        </is>
+      </c>
       <c r="G359" s="26" t="n">
-        <v>25.0333333</v>
+        <v>40.556</v>
       </c>
       <c r="H359" s="26" t="n">
-        <v>121.5166666</v>
+        <v>115.793</v>
       </c>
       <c r="I359" s="2" t="n">
-        <v>9</v>
+        <v>1798</v>
       </c>
       <c r="J359" s="24" t="n">
         <v>12</v>
@@ -36971,27 +36929,39 @@
       <c r="L359" s="51" t="n"/>
       <c r="M359" s="13" t="inlineStr">
         <is>
-          <t>台北</t>
-        </is>
-      </c>
-      <c r="N359" s="51" t="n"/>
+          <t>海坨山</t>
+        </is>
+      </c>
+      <c r="N359" s="51" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
       <c r="O359" s="29" t="n"/>
       <c r="P359" s="29" t="n"/>
       <c r="Q359" s="29" t="n"/>
-      <c r="R359" s="45" t="n"/>
+      <c r="R359" s="45" t="inlineStr">
+        <is>
+          <t>2021-01-07</t>
+        </is>
+      </c>
       <c r="S359" s="21" t="n"/>
       <c r="T359" s="33" t="n"/>
       <c r="U359" s="37" t="inlineStr">
         <is>
-          <t>台湾</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="V359" s="2" t="inlineStr">
         <is>
-          <t>台湾</t>
-        </is>
-      </c>
-      <c r="W359" s="3" t="n"/>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="W359" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="X359" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -37003,7 +36973,11 @@
         </is>
       </c>
       <c r="Z359" s="3" t="n"/>
-      <c r="AA359" s="2" t="n"/>
+      <c r="AA359" s="2" t="inlineStr">
+        <is>
+          <t>延庆区</t>
+        </is>
+      </c>
       <c r="AB359" s="2" t="n"/>
       <c r="AC359" s="2" t="n"/>
       <c r="AD359" s="2" t="n"/>
@@ -37019,29 +36993,37 @@
       </c>
       <c r="AG359" s="3" t="n"/>
       <c r="AH359" s="2" t="n"/>
-      <c r="AI359" s="2" t="n"/>
+      <c r="AI359" s="2" t="inlineStr">
+        <is>
+          <t>竞速训练1</t>
+        </is>
+      </c>
     </row>
     <row r="360" ht="24" customHeight="1" s="54">
       <c r="A360" s="2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B360" s="2" t="n"/>
-      <c r="C360" s="41" t="n"/>
-      <c r="D360" s="2" t="n"/>
-      <c r="E360" s="3" t="n"/>
-      <c r="F360" s="35" t="inlineStr">
-        <is>
-          <t>U7073</t>
-        </is>
-      </c>
+      <c r="C360" s="41" t="n">
+        <v>58968</v>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="E360" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F360" s="35" t="n"/>
       <c r="G360" s="26" t="n">
-        <v>31.134</v>
+        <v>25.0333333</v>
       </c>
       <c r="H360" s="26" t="n">
-        <v>82.22199999999999</v>
+        <v>121.5166666</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>5170</v>
+        <v>9</v>
       </c>
       <c r="J360" s="24" t="n">
         <v>12</v>
@@ -37054,7 +37036,7 @@
       <c r="L360" s="51" t="n"/>
       <c r="M360" s="13" t="inlineStr">
         <is>
-          <t>(革吉)亚热却藏</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="N360" s="51" t="n"/>
@@ -37066,19 +37048,15 @@
       <c r="T360" s="33" t="n"/>
       <c r="U360" s="37" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>台湾</t>
         </is>
       </c>
       <c r="V360" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
-        </is>
-      </c>
-      <c r="W360" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>台湾</t>
+        </is>
+      </c>
+      <c r="W360" s="3" t="n"/>
       <c r="X360" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -37090,16 +37068,8 @@
         </is>
       </c>
       <c r="Z360" s="3" t="n"/>
-      <c r="AA360" s="2" t="inlineStr">
-        <is>
-          <t>阿里地区</t>
-        </is>
-      </c>
-      <c r="AB360" s="2" t="inlineStr">
-        <is>
-          <t>革吉县</t>
-        </is>
-      </c>
+      <c r="AA360" s="2" t="n"/>
+      <c r="AB360" s="2" t="n"/>
       <c r="AC360" s="2" t="n"/>
       <c r="AD360" s="2" t="n"/>
       <c r="AE360" s="2" t="inlineStr">
@@ -37118,7 +37088,7 @@
     </row>
     <row r="361" ht="24" customHeight="1" s="54">
       <c r="A361" s="2" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B361" s="2" t="n"/>
       <c r="C361" s="41" t="n"/>
@@ -37126,17 +37096,17 @@
       <c r="E361" s="3" t="n"/>
       <c r="F361" s="35" t="inlineStr">
         <is>
-          <t>U7031</t>
+          <t>U7073</t>
         </is>
       </c>
       <c r="G361" s="26" t="n">
-        <v>30.976</v>
+        <v>31.134</v>
       </c>
       <c r="H361" s="26" t="n">
-        <v>80.953</v>
+        <v>82.22199999999999</v>
       </c>
       <c r="I361" s="2" t="n">
-        <v>4526</v>
+        <v>5170</v>
       </c>
       <c r="J361" s="24" t="n">
         <v>12</v>
@@ -37149,7 +37119,7 @@
       <c r="L361" s="51" t="n"/>
       <c r="M361" s="13" t="inlineStr">
         <is>
-          <t>象泉河源头</t>
+          <t>(革吉)亚热却藏</t>
         </is>
       </c>
       <c r="N361" s="51" t="n"/>
@@ -37192,7 +37162,7 @@
       </c>
       <c r="AB361" s="2" t="inlineStr">
         <is>
-          <t>噶尔县</t>
+          <t>革吉县</t>
         </is>
       </c>
       <c r="AC361" s="2" t="n"/>
@@ -37208,16 +37178,12 @@
         </is>
       </c>
       <c r="AG361" s="3" t="n"/>
-      <c r="AH361" s="2" t="inlineStr">
-        <is>
-          <t>青藏高原</t>
-        </is>
-      </c>
+      <c r="AH361" s="2" t="n"/>
       <c r="AI361" s="2" t="n"/>
     </row>
     <row r="362" ht="24" customHeight="1" s="54">
       <c r="A362" s="2" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B362" s="2" t="n"/>
       <c r="C362" s="41" t="n"/>
@@ -37225,17 +37191,17 @@
       <c r="E362" s="3" t="n"/>
       <c r="F362" s="35" t="inlineStr">
         <is>
-          <t>U7801</t>
+          <t>U7031</t>
         </is>
       </c>
       <c r="G362" s="26" t="n">
-        <v>30.594</v>
+        <v>30.976</v>
       </c>
       <c r="H362" s="26" t="n">
-        <v>82.473</v>
+        <v>80.953</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>5047</v>
+        <v>4526</v>
       </c>
       <c r="J362" s="24" t="n">
         <v>12</v>
@@ -37248,25 +37214,19 @@
       <c r="L362" s="51" t="n"/>
       <c r="M362" s="13" t="inlineStr">
         <is>
-          <t>(普兰)马攸木</t>
+          <t>象泉河源头</t>
         </is>
       </c>
       <c r="N362" s="51" t="n"/>
-      <c r="O362" s="29" t="n">
-        <v>-21.6</v>
-      </c>
-      <c r="P362" s="29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q362" s="29" t="n">
-        <v>-9.800000000000001</v>
-      </c>
+      <c r="O362" s="29" t="n"/>
+      <c r="P362" s="29" t="n"/>
+      <c r="Q362" s="29" t="n"/>
       <c r="R362" s="45" t="n"/>
       <c r="S362" s="21" t="n"/>
       <c r="T362" s="33" t="n"/>
       <c r="U362" s="37" t="inlineStr">
         <is>
-          <t>(交通)</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="V362" s="2" t="inlineStr">
@@ -37297,7 +37257,7 @@
       </c>
       <c r="AB362" s="2" t="inlineStr">
         <is>
-          <t>普兰县</t>
+          <t>噶尔县</t>
         </is>
       </c>
       <c r="AC362" s="2" t="n"/>
@@ -37322,7 +37282,7 @@
     </row>
     <row r="363" ht="24" customHeight="1" s="54">
       <c r="A363" s="2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B363" s="2" t="n"/>
       <c r="C363" s="41" t="n"/>
@@ -37330,17 +37290,17 @@
       <c r="E363" s="3" t="n"/>
       <c r="F363" s="35" t="inlineStr">
         <is>
-          <t>U7014</t>
+          <t>U7801</t>
         </is>
       </c>
       <c r="G363" s="26" t="n">
-        <v>30.591</v>
+        <v>30.594</v>
       </c>
       <c r="H363" s="26" t="n">
-        <v>82.47499999999999</v>
+        <v>82.473</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>5039.2</v>
+        <v>5047</v>
       </c>
       <c r="J363" s="24" t="n">
         <v>12</v>
@@ -37353,19 +37313,25 @@
       <c r="L363" s="51" t="n"/>
       <c r="M363" s="13" t="inlineStr">
         <is>
-          <t>(普兰)马攸</t>
+          <t>(普兰)马攸木</t>
         </is>
       </c>
       <c r="N363" s="51" t="n"/>
-      <c r="O363" s="29" t="n"/>
-      <c r="P363" s="29" t="n"/>
-      <c r="Q363" s="29" t="n"/>
+      <c r="O363" s="29" t="n">
+        <v>-24.3</v>
+      </c>
+      <c r="P363" s="29" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Q363" s="29" t="n">
+        <v>-14.7</v>
+      </c>
       <c r="R363" s="45" t="n"/>
       <c r="S363" s="21" t="n"/>
       <c r="T363" s="33" t="n"/>
       <c r="U363" s="37" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>(交通)</t>
         </is>
       </c>
       <c r="V363" s="2" t="inlineStr">
@@ -37421,7 +37387,7 @@
     </row>
     <row r="364" ht="24" customHeight="1" s="54">
       <c r="A364" s="2" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B364" s="2" t="n"/>
       <c r="C364" s="41" t="n"/>
@@ -37429,17 +37395,17 @@
       <c r="E364" s="3" t="n"/>
       <c r="F364" s="35" t="inlineStr">
         <is>
-          <t>U7502</t>
+          <t>U7014</t>
         </is>
       </c>
       <c r="G364" s="26" t="n">
-        <v>31.0958</v>
+        <v>30.591</v>
       </c>
       <c r="H364" s="26" t="n">
-        <v>81.36969999999999</v>
+        <v>82.47499999999999</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>5642</v>
+        <v>5039.2</v>
       </c>
       <c r="J364" s="24" t="n">
         <v>12</v>
@@ -37452,7 +37418,7 @@
       <c r="L364" s="51" t="n"/>
       <c r="M364" s="13" t="inlineStr">
         <is>
-          <t>冈仁波齐3</t>
+          <t>(普兰)马攸</t>
         </is>
       </c>
       <c r="N364" s="51" t="n"/>
@@ -37511,12 +37477,16 @@
         </is>
       </c>
       <c r="AG364" s="3" t="n"/>
-      <c r="AH364" s="2" t="n"/>
+      <c r="AH364" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AI364" s="2" t="n"/>
     </row>
     <row r="365" ht="24" customHeight="1" s="54">
       <c r="A365" s="2" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B365" s="2" t="n"/>
       <c r="C365" s="41" t="n"/>
@@ -37524,12 +37494,18 @@
       <c r="E365" s="3" t="n"/>
       <c r="F365" s="35" t="inlineStr">
         <is>
-          <t>U7101</t>
-        </is>
-      </c>
-      <c r="G365" s="26" t="n"/>
-      <c r="H365" s="26" t="n"/>
-      <c r="I365" s="2" t="n"/>
+          <t>U7502</t>
+        </is>
+      </c>
+      <c r="G365" s="26" t="n">
+        <v>31.0958</v>
+      </c>
+      <c r="H365" s="26" t="n">
+        <v>81.36969999999999</v>
+      </c>
+      <c r="I365" s="2" t="n">
+        <v>5642</v>
+      </c>
       <c r="J365" s="24" t="n">
         <v>12</v>
       </c>
@@ -37541,7 +37517,7 @@
       <c r="L365" s="51" t="n"/>
       <c r="M365" s="13" t="inlineStr">
         <is>
-          <t>冈仁波齐4</t>
+          <t>冈仁波齐3</t>
         </is>
       </c>
       <c r="N365" s="51" t="n"/>
@@ -37605,28 +37581,20 @@
     </row>
     <row r="366" ht="24" customHeight="1" s="54">
       <c r="A366" s="2" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B366" s="2" t="n"/>
-      <c r="C366" s="41" t="inlineStr">
-        <is>
-          <t>55026</t>
-        </is>
-      </c>
+      <c r="C366" s="41" t="n"/>
       <c r="D366" s="2" t="n"/>
-      <c r="E366" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F366" s="35" t="n"/>
-      <c r="G366" s="26" t="n">
-        <v>34.4264</v>
-      </c>
-      <c r="H366" s="26" t="n">
-        <v>80.3861</v>
-      </c>
-      <c r="I366" s="2" t="n">
-        <v>5188.6</v>
-      </c>
+      <c r="E366" s="3" t="n"/>
+      <c r="F366" s="35" t="inlineStr">
+        <is>
+          <t>U7101</t>
+        </is>
+      </c>
+      <c r="G366" s="26" t="n"/>
+      <c r="H366" s="26" t="n"/>
+      <c r="I366" s="2" t="n"/>
       <c r="J366" s="24" t="n">
         <v>12</v>
       </c>
@@ -37638,7 +37606,7 @@
       <c r="L366" s="51" t="n"/>
       <c r="M366" s="13" t="inlineStr">
         <is>
-          <t>松西</t>
+          <t>冈仁波齐4</t>
         </is>
       </c>
       <c r="N366" s="51" t="n"/>
@@ -37674,8 +37642,16 @@
         </is>
       </c>
       <c r="Z366" s="3" t="n"/>
-      <c r="AA366" s="2" t="n"/>
-      <c r="AB366" s="2" t="n"/>
+      <c r="AA366" s="2" t="inlineStr">
+        <is>
+          <t>阿里地区</t>
+        </is>
+      </c>
+      <c r="AB366" s="2" t="inlineStr">
+        <is>
+          <t>普兰县</t>
+        </is>
+      </c>
       <c r="AC366" s="2" t="n"/>
       <c r="AD366" s="2" t="n"/>
       <c r="AE366" s="2" t="inlineStr">
@@ -37694,35 +37670,27 @@
     </row>
     <row r="367" ht="24" customHeight="1" s="54">
       <c r="A367" s="2" t="n">
-        <v>365</v>
-      </c>
-      <c r="B367" s="2" t="inlineStr">
-        <is>
-          <t>ogimet</t>
-        </is>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="B367" s="2" t="n"/>
       <c r="C367" s="41" t="inlineStr">
         <is>
-          <t>55664</t>
-        </is>
-      </c>
-      <c r="D367" s="2" t="inlineStr">
-        <is>
-          <t>Xegar</t>
-        </is>
-      </c>
+          <t>55026</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="n"/>
       <c r="E367" s="3" t="n">
         <v>99999</v>
       </c>
       <c r="F367" s="35" t="n"/>
       <c r="G367" s="26" t="n">
-        <v>28.6542</v>
+        <v>34.4264</v>
       </c>
       <c r="H367" s="26" t="n">
-        <v>87.1203</v>
+        <v>80.3861</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>4322</v>
+        <v>5188.6</v>
       </c>
       <c r="J367" s="24" t="n">
         <v>12</v>
@@ -37735,7 +37703,7 @@
       <c r="L367" s="51" t="n"/>
       <c r="M367" s="13" t="inlineStr">
         <is>
-          <t>定日</t>
+          <t>松西</t>
         </is>
       </c>
       <c r="N367" s="51" t="n"/>
@@ -37771,16 +37739,8 @@
         </is>
       </c>
       <c r="Z367" s="3" t="n"/>
-      <c r="AA367" s="2" t="inlineStr">
-        <is>
-          <t>日喀则市</t>
-        </is>
-      </c>
-      <c r="AB367" s="2" t="inlineStr">
-        <is>
-          <t>定日县</t>
-        </is>
-      </c>
+      <c r="AA367" s="2" t="n"/>
+      <c r="AB367" s="2" t="n"/>
       <c r="AC367" s="2" t="n"/>
       <c r="AD367" s="2" t="n"/>
       <c r="AE367" s="2" t="inlineStr">
@@ -37794,24 +37754,26 @@
         </is>
       </c>
       <c r="AG367" s="3" t="n"/>
-      <c r="AH367" s="2" t="inlineStr">
-        <is>
-          <t>青藏高原</t>
-        </is>
-      </c>
+      <c r="AH367" s="2" t="n"/>
       <c r="AI367" s="2" t="n"/>
     </row>
     <row r="368" ht="24" customHeight="1" s="54">
       <c r="A368" s="2" t="n">
-        <v>366</v>
-      </c>
-      <c r="B368" s="2" t="n"/>
-      <c r="C368" s="41" t="n">
-        <v>45007</v>
+        <v>367</v>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
+      <c r="C368" s="41" t="inlineStr">
+        <is>
+          <t>55664</t>
+        </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Hong_Kong_(airport)</t>
+          <t>Xegar</t>
         </is>
       </c>
       <c r="E368" s="3" t="n">
@@ -37819,13 +37781,13 @@
       </c>
       <c r="F368" s="35" t="n"/>
       <c r="G368" s="26" t="n">
-        <v>22.308919</v>
+        <v>28.6542</v>
       </c>
       <c r="H368" s="26" t="n">
-        <v>113.914603</v>
+        <v>87.1203</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>4322</v>
       </c>
       <c r="J368" s="24" t="n">
         <v>12</v>
@@ -37838,7 +37800,7 @@
       <c r="L368" s="51" t="n"/>
       <c r="M368" s="13" t="inlineStr">
         <is>
-          <t>香港</t>
+          <t>定日</t>
         </is>
       </c>
       <c r="N368" s="51" t="n"/>
@@ -37848,13 +37810,21 @@
       <c r="R368" s="45" t="n"/>
       <c r="S368" s="21" t="n"/>
       <c r="T368" s="33" t="n"/>
-      <c r="U368" s="37" t="n"/>
+      <c r="U368" s="37" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
       <c r="V368" s="2" t="inlineStr">
         <is>
-          <t>香港</t>
-        </is>
-      </c>
-      <c r="W368" s="3" t="n"/>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="W368" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="X368" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -37866,8 +37836,16 @@
         </is>
       </c>
       <c r="Z368" s="3" t="n"/>
-      <c r="AA368" s="2" t="n"/>
-      <c r="AB368" s="2" t="n"/>
+      <c r="AA368" s="2" t="inlineStr">
+        <is>
+          <t>日喀则市</t>
+        </is>
+      </c>
+      <c r="AB368" s="2" t="inlineStr">
+        <is>
+          <t>定日县</t>
+        </is>
+      </c>
       <c r="AC368" s="2" t="n"/>
       <c r="AD368" s="2" t="n"/>
       <c r="AE368" s="2" t="inlineStr">
@@ -37881,30 +37859,38 @@
         </is>
       </c>
       <c r="AG368" s="3" t="n"/>
-      <c r="AH368" s="2" t="n"/>
+      <c r="AH368" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AI368" s="2" t="n"/>
     </row>
     <row r="369" ht="24" customHeight="1" s="54">
       <c r="A369" s="2" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B369" s="2" t="n"/>
-      <c r="C369" s="41" t="n"/>
-      <c r="D369" s="2" t="n"/>
-      <c r="E369" s="3" t="n"/>
-      <c r="F369" s="35" t="inlineStr">
-        <is>
-          <t>Y6758</t>
-        </is>
-      </c>
+      <c r="C369" s="41" t="n">
+        <v>45007</v>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Hong_Kong_(airport)</t>
+        </is>
+      </c>
+      <c r="E369" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F369" s="35" t="n"/>
       <c r="G369" s="26" t="n">
-        <v>48.0197</v>
+        <v>22.308919</v>
       </c>
       <c r="H369" s="26" t="n">
-        <v>87.5517</v>
+        <v>113.914603</v>
       </c>
       <c r="I369" s="2" t="n">
-        <v>1194</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="J369" s="24" t="n">
         <v>12</v>
@@ -37917,7 +37903,7 @@
       <c r="L369" s="51" t="n"/>
       <c r="M369" s="13" t="inlineStr">
         <is>
-          <t>齐背岭水库</t>
+          <t>香港</t>
         </is>
       </c>
       <c r="N369" s="51" t="n"/>
@@ -37927,21 +37913,13 @@
       <c r="R369" s="45" t="n"/>
       <c r="S369" s="21" t="n"/>
       <c r="T369" s="33" t="n"/>
-      <c r="U369" s="37" t="inlineStr">
-        <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
+      <c r="U369" s="37" t="n"/>
       <c r="V369" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="W369" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="W369" s="3" t="n"/>
       <c r="X369" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -37953,16 +37931,8 @@
         </is>
       </c>
       <c r="Z369" s="3" t="n"/>
-      <c r="AA369" s="2" t="inlineStr">
-        <is>
-          <t>阿勒泰地区</t>
-        </is>
-      </c>
-      <c r="AB369" s="2" t="inlineStr">
-        <is>
-          <t>阿勒泰市</t>
-        </is>
-      </c>
+      <c r="AA369" s="2" t="n"/>
+      <c r="AB369" s="2" t="n"/>
       <c r="AC369" s="2" t="n"/>
       <c r="AD369" s="2" t="n"/>
       <c r="AE369" s="2" t="inlineStr">
@@ -37976,16 +37946,12 @@
         </is>
       </c>
       <c r="AG369" s="3" t="n"/>
-      <c r="AH369" s="2" t="inlineStr">
-        <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
+      <c r="AH369" s="2" t="n"/>
       <c r="AI369" s="2" t="n"/>
     </row>
     <row r="370" ht="24" customHeight="1" s="54">
       <c r="A370" s="2" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B370" s="2" t="n"/>
       <c r="C370" s="41" t="n"/>
@@ -37993,17 +37959,17 @@
       <c r="E370" s="3" t="n"/>
       <c r="F370" s="35" t="inlineStr">
         <is>
-          <t>Y5315</t>
+          <t>Y6758</t>
         </is>
       </c>
       <c r="G370" s="26" t="n">
-        <v>48.7217</v>
+        <v>48.0197</v>
       </c>
       <c r="H370" s="26" t="n">
-        <v>87.03060000000001</v>
+        <v>87.5517</v>
       </c>
       <c r="I370" s="2" t="n">
-        <v>1367</v>
+        <v>1194</v>
       </c>
       <c r="J370" s="24" t="n">
         <v>12</v>
@@ -38016,20 +37982,12 @@
       <c r="L370" s="51" t="n"/>
       <c r="M370" s="13" t="inlineStr">
         <is>
-          <t>喀纳斯</t>
-        </is>
-      </c>
-      <c r="N370" s="51" t="inlineStr">
-        <is>
-          <t>❄️</t>
-        </is>
-      </c>
-      <c r="O370" s="29" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="P370" s="29" t="n">
-        <v>1.6</v>
-      </c>
+          <t>齐背岭水库</t>
+        </is>
+      </c>
+      <c r="N370" s="51" t="n"/>
+      <c r="O370" s="29" t="n"/>
+      <c r="P370" s="29" t="n"/>
       <c r="Q370" s="29" t="n"/>
       <c r="R370" s="45" t="n"/>
       <c r="S370" s="21" t="n"/>
@@ -38067,14 +38025,10 @@
       </c>
       <c r="AB370" s="2" t="inlineStr">
         <is>
-          <t>布尔津县</t>
-        </is>
-      </c>
-      <c r="AC370" s="2" t="inlineStr">
-        <is>
-          <t>禾木喀纳斯蒙古族乡</t>
-        </is>
-      </c>
+          <t>阿勒泰市</t>
+        </is>
+      </c>
+      <c r="AC370" s="2" t="n"/>
       <c r="AD370" s="2" t="n"/>
       <c r="AE370" s="2" t="inlineStr">
         <is>
@@ -38092,15 +38046,11 @@
           <t>阿尔泰山</t>
         </is>
       </c>
-      <c r="AI370" s="2" t="inlineStr">
-        <is>
-          <t>非定居点</t>
-        </is>
-      </c>
+      <c r="AI370" s="2" t="n"/>
     </row>
     <row r="371" ht="24" customHeight="1" s="54">
       <c r="A371" s="2" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B371" s="2" t="n"/>
       <c r="C371" s="41" t="n"/>
@@ -38108,17 +38058,17 @@
       <c r="E371" s="3" t="n"/>
       <c r="F371" s="35" t="inlineStr">
         <is>
-          <t>Y5322</t>
+          <t>Y5315</t>
         </is>
       </c>
       <c r="G371" s="26" t="n">
-        <v>48.5842</v>
+        <v>48.7217</v>
       </c>
       <c r="H371" s="26" t="n">
-        <v>87.45780000000001</v>
+        <v>87.03060000000001</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>1223</v>
+        <v>1367</v>
       </c>
       <c r="J371" s="24" t="n">
         <v>12</v>
@@ -38131,7 +38081,7 @@
       <c r="L371" s="51" t="n"/>
       <c r="M371" s="13" t="inlineStr">
         <is>
-          <t>禾木村</t>
+          <t>喀纳斯</t>
         </is>
       </c>
       <c r="N371" s="51" t="inlineStr">
@@ -38139,8 +38089,12 @@
           <t>❄️</t>
         </is>
       </c>
-      <c r="O371" s="29" t="n"/>
-      <c r="P371" s="29" t="n"/>
+      <c r="O371" s="29" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="P371" s="29" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q371" s="29" t="n"/>
       <c r="R371" s="45" t="n"/>
       <c r="S371" s="21" t="n"/>
@@ -38203,29 +38157,33 @@
           <t>阿尔泰山</t>
         </is>
       </c>
-      <c r="AI371" s="2" t="n"/>
+      <c r="AI371" s="2" t="inlineStr">
+        <is>
+          <t>非定居点</t>
+        </is>
+      </c>
     </row>
     <row r="372" ht="24" customHeight="1" s="54">
       <c r="A372" s="2" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B372" s="2" t="n"/>
-      <c r="C372" s="41" t="n">
-        <v>51068</v>
-      </c>
+      <c r="C372" s="41" t="n"/>
       <c r="D372" s="2" t="n"/>
-      <c r="E372" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F372" s="35" t="n"/>
+      <c r="E372" s="3" t="n"/>
+      <c r="F372" s="35" t="inlineStr">
+        <is>
+          <t>Y5322</t>
+        </is>
+      </c>
       <c r="G372" s="26" t="n">
-        <v>47.125</v>
+        <v>48.5842</v>
       </c>
       <c r="H372" s="26" t="n">
-        <v>87.48139999999999</v>
+        <v>87.45780000000001</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>497.1</v>
+        <v>1223</v>
       </c>
       <c r="J372" s="24" t="n">
         <v>12</v>
@@ -38238,10 +38196,14 @@
       <c r="L372" s="51" t="n"/>
       <c r="M372" s="13" t="inlineStr">
         <is>
-          <t>福海</t>
-        </is>
-      </c>
-      <c r="N372" s="51" t="n"/>
+          <t>禾木村</t>
+        </is>
+      </c>
+      <c r="N372" s="51" t="inlineStr">
+        <is>
+          <t>❄️</t>
+        </is>
+      </c>
       <c r="O372" s="29" t="n"/>
       <c r="P372" s="29" t="n"/>
       <c r="Q372" s="29" t="n"/>
@@ -38250,7 +38212,7 @@
       <c r="T372" s="33" t="n"/>
       <c r="U372" s="37" t="inlineStr">
         <is>
-          <t>乌伦古湖</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V372" s="2" t="inlineStr">
@@ -38281,10 +38243,14 @@
       </c>
       <c r="AB372" s="2" t="inlineStr">
         <is>
-          <t>福海县</t>
-        </is>
-      </c>
-      <c r="AC372" s="2" t="n"/>
+          <t>布尔津县</t>
+        </is>
+      </c>
+      <c r="AC372" s="2" t="inlineStr">
+        <is>
+          <t>禾木喀纳斯蒙古族乡</t>
+        </is>
+      </c>
       <c r="AD372" s="2" t="n"/>
       <c r="AE372" s="2" t="inlineStr">
         <is>
@@ -38299,32 +38265,32 @@
       <c r="AG372" s="3" t="n"/>
       <c r="AH372" s="2" t="inlineStr">
         <is>
-          <t>乌伦古湖</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="AI372" s="2" t="n"/>
     </row>
     <row r="373" ht="24" customHeight="1" s="54">
       <c r="A373" s="2" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B373" s="2" t="n"/>
-      <c r="C373" s="41" t="n"/>
+      <c r="C373" s="41" t="n">
+        <v>51068</v>
+      </c>
       <c r="D373" s="2" t="n"/>
-      <c r="E373" s="3" t="n"/>
-      <c r="F373" s="35" t="inlineStr">
-        <is>
-          <t>Y6770</t>
-        </is>
-      </c>
+      <c r="E373" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F373" s="35" t="n"/>
       <c r="G373" s="26" t="n">
-        <v>47.1681</v>
+        <v>47.125</v>
       </c>
       <c r="H373" s="26" t="n">
-        <v>90.0903</v>
+        <v>87.48139999999999</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>3084</v>
+        <v>497.1</v>
       </c>
       <c r="J373" s="24" t="n">
         <v>12</v>
@@ -38337,7 +38303,7 @@
       <c r="L373" s="51" t="n"/>
       <c r="M373" s="13" t="inlineStr">
         <is>
-          <t>可可托海雪场</t>
+          <t>福海</t>
         </is>
       </c>
       <c r="N373" s="51" t="n"/>
@@ -38349,7 +38315,7 @@
       <c r="T373" s="33" t="n"/>
       <c r="U373" s="37" t="inlineStr">
         <is>
-          <t>阿尔泰山</t>
+          <t>乌伦古湖</t>
         </is>
       </c>
       <c r="V373" s="2" t="inlineStr">
@@ -38380,7 +38346,7 @@
       </c>
       <c r="AB373" s="2" t="inlineStr">
         <is>
-          <t>富蕴县</t>
+          <t>福海县</t>
         </is>
       </c>
       <c r="AC373" s="2" t="n"/>
@@ -38398,18 +38364,14 @@
       <c r="AG373" s="3" t="n"/>
       <c r="AH373" s="2" t="inlineStr">
         <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
-      <c r="AI373" s="2" t="inlineStr">
-        <is>
-          <t>非定居点</t>
-        </is>
-      </c>
+          <t>乌伦古湖</t>
+        </is>
+      </c>
+      <c r="AI373" s="2" t="n"/>
     </row>
     <row r="374" ht="24" customHeight="1" s="54">
       <c r="A374" s="2" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B374" s="2" t="n"/>
       <c r="C374" s="41" t="n"/>
@@ -38417,17 +38379,17 @@
       <c r="E374" s="3" t="n"/>
       <c r="F374" s="35" t="inlineStr">
         <is>
-          <t>Y5316</t>
+          <t>Y6770</t>
         </is>
       </c>
       <c r="G374" s="26" t="n">
-        <v>47.1381</v>
+        <v>47.1681</v>
       </c>
       <c r="H374" s="26" t="n">
-        <v>85.5975</v>
+        <v>90.0903</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>2914</v>
+        <v>3084</v>
       </c>
       <c r="J374" s="24" t="n">
         <v>12</v>
@@ -38440,19 +38402,25 @@
       <c r="L374" s="51" t="n"/>
       <c r="M374" s="13" t="inlineStr">
         <is>
-          <t>吉木乃冰川</t>
+          <t>可可托海雪场</t>
         </is>
       </c>
       <c r="N374" s="51" t="n"/>
-      <c r="O374" s="29" t="n"/>
-      <c r="P374" s="29" t="n"/>
-      <c r="Q374" s="29" t="n"/>
+      <c r="O374" s="29" t="n">
+        <v>-19</v>
+      </c>
+      <c r="P374" s="29" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="Q374" s="29" t="n">
+        <v>-15</v>
+      </c>
       <c r="R374" s="45" t="n"/>
       <c r="S374" s="21" t="n"/>
       <c r="T374" s="33" t="n"/>
       <c r="U374" s="37" t="inlineStr">
         <is>
-          <t>阿勒泰</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V374" s="2" t="inlineStr">
@@ -38483,7 +38451,7 @@
       </c>
       <c r="AB374" s="2" t="inlineStr">
         <is>
-          <t>吉木乃县</t>
+          <t>富蕴县</t>
         </is>
       </c>
       <c r="AC374" s="2" t="n"/>
@@ -38499,12 +38467,20 @@
         </is>
       </c>
       <c r="AG374" s="3" t="n"/>
-      <c r="AH374" s="2" t="n"/>
-      <c r="AI374" s="2" t="n"/>
+      <c r="AH374" s="2" t="inlineStr">
+        <is>
+          <t>阿尔泰山</t>
+        </is>
+      </c>
+      <c r="AI374" s="2" t="inlineStr">
+        <is>
+          <t>非定居点</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="24" customHeight="1" s="54">
       <c r="A375" s="2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B375" s="2" t="n"/>
       <c r="C375" s="41" t="n"/>
@@ -38512,17 +38488,17 @@
       <c r="E375" s="3" t="n"/>
       <c r="F375" s="35" t="inlineStr">
         <is>
-          <t>Y5347</t>
+          <t>Y5316</t>
         </is>
       </c>
       <c r="G375" s="26" t="n">
-        <v>46.1772</v>
+        <v>47.1381</v>
       </c>
       <c r="H375" s="26" t="n">
-        <v>90.5356</v>
+        <v>85.5975</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>1071.1</v>
+        <v>2914</v>
       </c>
       <c r="J375" s="24" t="n">
         <v>12</v>
@@ -38535,7 +38511,7 @@
       <c r="L375" s="51" t="n"/>
       <c r="M375" s="13" t="inlineStr">
         <is>
-          <t>塔克什肯镇</t>
+          <t>吉木乃冰川</t>
         </is>
       </c>
       <c r="N375" s="51" t="n"/>
@@ -38547,7 +38523,7 @@
       <c r="T375" s="33" t="n"/>
       <c r="U375" s="37" t="inlineStr">
         <is>
-          <t>阿尔泰山</t>
+          <t>阿勒泰</t>
         </is>
       </c>
       <c r="V375" s="2" t="inlineStr">
@@ -38578,7 +38554,7 @@
       </c>
       <c r="AB375" s="2" t="inlineStr">
         <is>
-          <t>青河县</t>
+          <t>吉木乃县</t>
         </is>
       </c>
       <c r="AC375" s="2" t="n"/>
@@ -38594,42 +38570,30 @@
         </is>
       </c>
       <c r="AG375" s="3" t="n"/>
-      <c r="AH375" s="2" t="inlineStr">
-        <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
+      <c r="AH375" s="2" t="n"/>
       <c r="AI375" s="2" t="n"/>
     </row>
     <row r="376" ht="24" customHeight="1" s="54">
       <c r="A376" s="2" t="n">
-        <v>374</v>
-      </c>
-      <c r="B376" s="2" t="inlineStr">
-        <is>
-          <t>ogimet</t>
-        </is>
-      </c>
-      <c r="C376" s="41" t="n">
-        <v>51087</v>
-      </c>
-      <c r="D376" s="2" t="inlineStr">
-        <is>
-          <t>Kueerqisi</t>
-        </is>
-      </c>
-      <c r="E376" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F376" s="35" t="n"/>
+        <v>375</v>
+      </c>
+      <c r="B376" s="2" t="n"/>
+      <c r="C376" s="41" t="n"/>
+      <c r="D376" s="2" t="n"/>
+      <c r="E376" s="3" t="n"/>
+      <c r="F376" s="35" t="inlineStr">
+        <is>
+          <t>Y5347</t>
+        </is>
+      </c>
       <c r="G376" s="26" t="n">
-        <v>47.02</v>
+        <v>46.1772</v>
       </c>
       <c r="H376" s="26" t="n">
-        <v>89.5</v>
+        <v>90.5356</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>860.4</v>
+        <v>1071.1</v>
       </c>
       <c r="J376" s="24" t="n">
         <v>12</v>
@@ -38642,7 +38606,7 @@
       <c r="L376" s="51" t="n"/>
       <c r="M376" s="13" t="inlineStr">
         <is>
-          <t>富蕴</t>
+          <t>塔克什肯镇</t>
         </is>
       </c>
       <c r="N376" s="51" t="n"/>
@@ -38654,7 +38618,7 @@
       <c r="T376" s="33" t="n"/>
       <c r="U376" s="37" t="inlineStr">
         <is>
-          <t>额尔齐斯河</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V376" s="2" t="inlineStr">
@@ -38683,7 +38647,11 @@
           <t>阿勒泰地区</t>
         </is>
       </c>
-      <c r="AB376" s="2" t="n"/>
+      <c r="AB376" s="2" t="inlineStr">
+        <is>
+          <t>青河县</t>
+        </is>
+      </c>
       <c r="AC376" s="2" t="n"/>
       <c r="AD376" s="2" t="n"/>
       <c r="AE376" s="2" t="inlineStr">
@@ -38706,18 +38674,34 @@
     </row>
     <row r="377" ht="24" customHeight="1" s="54">
       <c r="A377" s="2" t="n">
-        <v>375</v>
-      </c>
-      <c r="B377" s="2" t="n"/>
+        <v>376</v>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
       <c r="C377" s="41" t="n">
-        <v>51058</v>
-      </c>
-      <c r="D377" s="2" t="n"/>
-      <c r="E377" s="3" t="n"/>
+        <v>51087</v>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Kueerqisi</t>
+        </is>
+      </c>
+      <c r="E377" s="3" t="n">
+        <v>99999</v>
+      </c>
       <c r="F377" s="35" t="n"/>
-      <c r="G377" s="26" t="n"/>
-      <c r="H377" s="26" t="n"/>
-      <c r="I377" s="2" t="n"/>
+      <c r="G377" s="26" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="H377" s="26" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="I377" s="2" t="n">
+        <v>860.4</v>
+      </c>
       <c r="J377" s="24" t="n">
         <v>12</v>
       </c>
@@ -38729,7 +38713,7 @@
       <c r="L377" s="51" t="n"/>
       <c r="M377" s="13" t="inlineStr">
         <is>
-          <t>阿克达拉</t>
+          <t>富蕴</t>
         </is>
       </c>
       <c r="N377" s="51" t="n"/>
@@ -38741,7 +38725,7 @@
       <c r="T377" s="33" t="n"/>
       <c r="U377" s="37" t="inlineStr">
         <is>
-          <t>乌伦古湖</t>
+          <t>额尔齐斯河</t>
         </is>
       </c>
       <c r="V377" s="2" t="inlineStr">
@@ -38784,31 +38768,27 @@
         </is>
       </c>
       <c r="AG377" s="3" t="n"/>
-      <c r="AH377" s="2" t="n"/>
+      <c r="AH377" s="2" t="inlineStr">
+        <is>
+          <t>阿尔泰山</t>
+        </is>
+      </c>
       <c r="AI377" s="2" t="n"/>
     </row>
     <row r="378" ht="24" customHeight="1" s="54">
       <c r="A378" s="2" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B378" s="2" t="n"/>
       <c r="C378" s="41" t="n">
-        <v>51060</v>
+        <v>51058</v>
       </c>
       <c r="D378" s="2" t="n"/>
-      <c r="E378" s="3" t="n">
-        <v>99999</v>
-      </c>
+      <c r="E378" s="3" t="n"/>
       <c r="F378" s="35" t="n"/>
-      <c r="G378" s="26" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="H378" s="26" t="n">
-        <v>86.87</v>
-      </c>
-      <c r="I378" s="2" t="n">
-        <v>473.9</v>
-      </c>
+      <c r="G378" s="26" t="n"/>
+      <c r="H378" s="26" t="n"/>
+      <c r="I378" s="2" t="n"/>
       <c r="J378" s="24" t="n">
         <v>12</v>
       </c>
@@ -38820,7 +38800,7 @@
       <c r="L378" s="51" t="n"/>
       <c r="M378" s="13" t="inlineStr">
         <is>
-          <t>布尔津</t>
+          <t>阿克达拉</t>
         </is>
       </c>
       <c r="N378" s="51" t="n"/>
@@ -38832,7 +38812,7 @@
       <c r="T378" s="33" t="n"/>
       <c r="U378" s="37" t="inlineStr">
         <is>
-          <t>额尔齐斯河</t>
+          <t>乌伦古湖</t>
         </is>
       </c>
       <c r="V378" s="2" t="inlineStr">
@@ -38875,34 +38855,30 @@
         </is>
       </c>
       <c r="AG378" s="3" t="n"/>
-      <c r="AH378" s="2" t="inlineStr">
-        <is>
-          <t>额尔齐斯河</t>
-        </is>
-      </c>
+      <c r="AH378" s="2" t="n"/>
       <c r="AI378" s="2" t="n"/>
     </row>
     <row r="379" ht="24" customHeight="1" s="54">
       <c r="A379" s="2" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B379" s="2" t="n"/>
-      <c r="C379" s="41" t="n"/>
+      <c r="C379" s="41" t="n">
+        <v>51060</v>
+      </c>
       <c r="D379" s="2" t="n"/>
-      <c r="E379" s="3" t="n"/>
-      <c r="F379" s="35" t="inlineStr">
-        <is>
-          <t>Y5826</t>
-        </is>
-      </c>
+      <c r="E379" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F379" s="35" t="n"/>
       <c r="G379" s="26" t="n">
-        <v>42.716</v>
+        <v>47.7</v>
       </c>
       <c r="H379" s="26" t="n">
-        <v>84.27200000000001</v>
+        <v>86.87</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>2404.3</v>
+        <v>473.9</v>
       </c>
       <c r="J379" s="24" t="n">
         <v>12</v>
@@ -38915,7 +38891,7 @@
       <c r="L379" s="51" t="n"/>
       <c r="M379" s="13" t="inlineStr">
         <is>
-          <t>德尔比勒金牧场</t>
+          <t>布尔津</t>
         </is>
       </c>
       <c r="N379" s="51" t="n"/>
@@ -38927,7 +38903,7 @@
       <c r="T379" s="33" t="n"/>
       <c r="U379" s="37" t="inlineStr">
         <is>
-          <t>巴音布鲁克</t>
+          <t>额尔齐斯河</t>
         </is>
       </c>
       <c r="V379" s="2" t="inlineStr">
@@ -38953,14 +38929,10 @@
       <c r="Z379" s="3" t="n"/>
       <c r="AA379" s="2" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
-        </is>
-      </c>
-      <c r="AB379" s="2" t="inlineStr">
-        <is>
-          <t>和静县</t>
-        </is>
-      </c>
+          <t>阿勒泰地区</t>
+        </is>
+      </c>
+      <c r="AB379" s="2" t="n"/>
       <c r="AC379" s="2" t="n"/>
       <c r="AD379" s="2" t="n"/>
       <c r="AE379" s="2" t="inlineStr">
@@ -38976,32 +38948,32 @@
       <c r="AG379" s="3" t="n"/>
       <c r="AH379" s="2" t="inlineStr">
         <is>
-          <t>天山</t>
+          <t>额尔齐斯河</t>
         </is>
       </c>
       <c r="AI379" s="2" t="n"/>
     </row>
     <row r="380" ht="24" customHeight="1" s="54">
       <c r="A380" s="2" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B380" s="2" t="n"/>
-      <c r="C380" s="41" t="n">
-        <v>51337</v>
-      </c>
+      <c r="C380" s="41" t="n"/>
       <c r="D380" s="2" t="n"/>
-      <c r="E380" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F380" s="35" t="n"/>
+      <c r="E380" s="3" t="n"/>
+      <c r="F380" s="35" t="inlineStr">
+        <is>
+          <t>Y5826</t>
+        </is>
+      </c>
       <c r="G380" s="26" t="n">
-        <v>44.6028</v>
+        <v>42.716</v>
       </c>
       <c r="H380" s="26" t="n">
-        <v>81.3878</v>
+        <v>84.27200000000001</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>2100</v>
+        <v>2404.3</v>
       </c>
       <c r="J380" s="24" t="n">
         <v>12</v>
@@ -39014,7 +38986,7 @@
       <c r="L380" s="51" t="n"/>
       <c r="M380" s="13" t="inlineStr">
         <is>
-          <t>赛里木湖</t>
+          <t>德尔比勒金牧场</t>
         </is>
       </c>
       <c r="N380" s="51" t="n"/>
@@ -39026,7 +38998,7 @@
       <c r="T380" s="33" t="n"/>
       <c r="U380" s="37" t="inlineStr">
         <is>
-          <t>天山</t>
+          <t>巴音布鲁克</t>
         </is>
       </c>
       <c r="V380" s="2" t="inlineStr">
@@ -39052,12 +39024,12 @@
       <c r="Z380" s="3" t="n"/>
       <c r="AA380" s="2" t="inlineStr">
         <is>
-          <t>博尔塔拉蒙古自治州</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="AB380" s="2" t="inlineStr">
         <is>
-          <t>博乐市</t>
+          <t>和静县</t>
         </is>
       </c>
       <c r="AC380" s="2" t="n"/>
@@ -39078,21 +39050,15 @@
           <t>天山</t>
         </is>
       </c>
-      <c r="AI380" s="2" t="inlineStr">
-        <is>
-          <t>非定居点</t>
-        </is>
-      </c>
+      <c r="AI380" s="2" t="n"/>
     </row>
     <row r="381" ht="24" customHeight="1" s="54">
       <c r="A381" s="2" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B381" s="2" t="n"/>
-      <c r="C381" s="41" t="inlineStr">
-        <is>
-          <t>51701</t>
-        </is>
+      <c r="C381" s="41" t="n">
+        <v>51337</v>
       </c>
       <c r="D381" s="2" t="n"/>
       <c r="E381" s="3" t="n">
@@ -39100,13 +39066,13 @@
       </c>
       <c r="F381" s="35" t="n"/>
       <c r="G381" s="26" t="n">
-        <v>40.5122</v>
+        <v>44.6028</v>
       </c>
       <c r="H381" s="26" t="n">
-        <v>75.3914</v>
+        <v>81.3878</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>3470.2</v>
+        <v>2100</v>
       </c>
       <c r="J381" s="24" t="n">
         <v>12</v>
@@ -39119,7 +39085,7 @@
       <c r="L381" s="51" t="n"/>
       <c r="M381" s="13" t="inlineStr">
         <is>
-          <t>吐尔尕特</t>
+          <t>赛里木湖</t>
         </is>
       </c>
       <c r="N381" s="51" t="n"/>
@@ -39157,12 +39123,12 @@
       <c r="Z381" s="3" t="n"/>
       <c r="AA381" s="2" t="inlineStr">
         <is>
-          <t>喀什地区</t>
+          <t>博尔塔拉蒙古自治州</t>
         </is>
       </c>
       <c r="AB381" s="2" t="inlineStr">
         <is>
-          <t>喀什市</t>
+          <t>博乐市</t>
         </is>
       </c>
       <c r="AC381" s="2" t="n"/>
@@ -39183,16 +39149,20 @@
           <t>天山</t>
         </is>
       </c>
-      <c r="AI381" s="2" t="n"/>
+      <c r="AI381" s="2" t="inlineStr">
+        <is>
+          <t>非定居点</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="24" customHeight="1" s="54">
       <c r="A382" s="2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B382" s="2" t="n"/>
       <c r="C382" s="41" t="inlineStr">
         <is>
-          <t>51572</t>
+          <t>51701</t>
         </is>
       </c>
       <c r="D382" s="2" t="n"/>
@@ -39201,13 +39171,13 @@
       </c>
       <c r="F382" s="35" t="n"/>
       <c r="G382" s="26" t="n">
-        <v>42.8908</v>
+        <v>40.5122</v>
       </c>
       <c r="H382" s="26" t="n">
-        <v>89.3056</v>
+        <v>75.3914</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>-48.8</v>
+        <v>3470.2</v>
       </c>
       <c r="J382" s="24" t="n">
         <v>12</v>
@@ -39220,7 +39190,7 @@
       <c r="L382" s="51" t="n"/>
       <c r="M382" s="13" t="inlineStr">
         <is>
-          <t>东坎</t>
+          <t>吐尔尕特</t>
         </is>
       </c>
       <c r="N382" s="51" t="n"/>
@@ -39232,7 +39202,7 @@
       <c r="T382" s="33" t="n"/>
       <c r="U382" s="37" t="inlineStr">
         <is>
-          <t>吐鲁番</t>
+          <t>天山</t>
         </is>
       </c>
       <c r="V382" s="2" t="inlineStr">
@@ -39258,12 +39228,12 @@
       <c r="Z382" s="3" t="n"/>
       <c r="AA382" s="2" t="inlineStr">
         <is>
-          <t>吐鲁番市</t>
+          <t>喀什地区</t>
         </is>
       </c>
       <c r="AB382" s="2" t="inlineStr">
         <is>
-          <t>高昌区</t>
+          <t>喀什市</t>
         </is>
       </c>
       <c r="AC382" s="2" t="n"/>
@@ -39279,30 +39249,36 @@
         </is>
       </c>
       <c r="AG382" s="3" t="n"/>
-      <c r="AH382" s="2" t="n"/>
+      <c r="AH382" s="2" t="inlineStr">
+        <is>
+          <t>天山</t>
+        </is>
+      </c>
       <c r="AI382" s="2" t="n"/>
     </row>
     <row r="383" ht="24" customHeight="1" s="54">
       <c r="A383" s="2" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B383" s="2" t="n"/>
-      <c r="C383" s="41" t="n"/>
+      <c r="C383" s="41" t="inlineStr">
+        <is>
+          <t>51572</t>
+        </is>
+      </c>
       <c r="D383" s="2" t="n"/>
-      <c r="E383" s="3" t="n"/>
-      <c r="F383" s="35" t="inlineStr">
-        <is>
-          <t>Y8049</t>
-        </is>
-      </c>
+      <c r="E383" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F383" s="35" t="n"/>
       <c r="G383" s="26" t="n">
-        <v>42.6856</v>
+        <v>42.8908</v>
       </c>
       <c r="H383" s="26" t="n">
-        <v>89.0656</v>
+        <v>89.3056</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>-106.4</v>
+        <v>-48.8</v>
       </c>
       <c r="J383" s="24" t="n">
         <v>12</v>
@@ -39315,7 +39291,7 @@
       <c r="L383" s="51" t="n"/>
       <c r="M383" s="13" t="inlineStr">
         <is>
-          <t>新鑫盐矿</t>
+          <t>东坎</t>
         </is>
       </c>
       <c r="N383" s="51" t="n"/>
@@ -39379,7 +39355,7 @@
     </row>
     <row r="384" ht="24" customHeight="1" s="54">
       <c r="A384" s="2" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B384" s="2" t="n"/>
       <c r="C384" s="41" t="n"/>
@@ -39387,17 +39363,17 @@
       <c r="E384" s="3" t="n"/>
       <c r="F384" s="35" t="inlineStr">
         <is>
-          <t>Y5774</t>
+          <t>Y8049</t>
         </is>
       </c>
       <c r="G384" s="26" t="n">
-        <v>42.9044</v>
+        <v>42.6856</v>
       </c>
       <c r="H384" s="26" t="n">
-        <v>89.4422</v>
+        <v>89.0656</v>
       </c>
       <c r="I384" s="2" t="n">
-        <v>-52</v>
+        <v>-106.4</v>
       </c>
       <c r="J384" s="24" t="n">
         <v>12</v>
@@ -39410,7 +39386,7 @@
       <c r="L384" s="51" t="n"/>
       <c r="M384" s="13" t="inlineStr">
         <is>
-          <t>三堡乡</t>
+          <t>新鑫盐矿</t>
         </is>
       </c>
       <c r="N384" s="51" t="n"/>
@@ -39474,27 +39450,25 @@
     </row>
     <row r="385" ht="24" customHeight="1" s="54">
       <c r="A385" s="2" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B385" s="2" t="n"/>
-      <c r="C385" s="41" t="inlineStr">
-        <is>
-          <t>51571</t>
-        </is>
-      </c>
+      <c r="C385" s="41" t="n"/>
       <c r="D385" s="2" t="n"/>
-      <c r="E385" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F385" s="35" t="n"/>
+      <c r="E385" s="3" t="n"/>
+      <c r="F385" s="35" t="inlineStr">
+        <is>
+          <t>Y5774</t>
+        </is>
+      </c>
       <c r="G385" s="26" t="n">
-        <v>42.7669</v>
+        <v>42.9044</v>
       </c>
       <c r="H385" s="26" t="n">
-        <v>88.60080000000001</v>
+        <v>89.4422</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>43.9</v>
+        <v>-52</v>
       </c>
       <c r="J385" s="24" t="n">
         <v>12</v>
@@ -39507,7 +39481,7 @@
       <c r="L385" s="51" t="n"/>
       <c r="M385" s="13" t="inlineStr">
         <is>
-          <t>托克逊</t>
+          <t>三堡乡</t>
         </is>
       </c>
       <c r="N385" s="51" t="n"/>
@@ -39550,7 +39524,7 @@
       </c>
       <c r="AB385" s="2" t="inlineStr">
         <is>
-          <t>托克逊县</t>
+          <t>高昌区</t>
         </is>
       </c>
       <c r="AC385" s="2" t="n"/>
@@ -39571,12 +39545,12 @@
     </row>
     <row r="386" ht="24" customHeight="1" s="54">
       <c r="A386" s="2" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B386" s="2" t="n"/>
       <c r="C386" s="41" t="inlineStr">
         <is>
-          <t>51468</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="D386" s="2" t="n"/>
@@ -39585,13 +39559,13 @@
       </c>
       <c r="F386" s="35" t="n"/>
       <c r="G386" s="26" t="n">
-        <v>43.1131</v>
+        <v>42.7669</v>
       </c>
       <c r="H386" s="26" t="n">
-        <v>86.84310000000001</v>
+        <v>88.60080000000001</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>3540.5</v>
+        <v>43.9</v>
       </c>
       <c r="J386" s="24" t="n">
         <v>12</v>
@@ -39604,25 +39578,19 @@
       <c r="L386" s="51" t="n"/>
       <c r="M386" s="13" t="inlineStr">
         <is>
-          <t>天山大西沟</t>
+          <t>托克逊</t>
         </is>
       </c>
       <c r="N386" s="51" t="n"/>
-      <c r="O386" s="29" t="n">
-        <v>-15.8</v>
-      </c>
-      <c r="P386" s="29" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="Q386" s="29" t="n">
-        <v>-11.93</v>
-      </c>
+      <c r="O386" s="29" t="n"/>
+      <c r="P386" s="29" t="n"/>
+      <c r="Q386" s="29" t="n"/>
       <c r="R386" s="45" t="n"/>
       <c r="S386" s="21" t="n"/>
       <c r="T386" s="33" t="n"/>
       <c r="U386" s="37" t="inlineStr">
         <is>
-          <t>天山</t>
+          <t>吐鲁番</t>
         </is>
       </c>
       <c r="V386" s="2" t="inlineStr">
@@ -39648,12 +39616,12 @@
       <c r="Z386" s="3" t="n"/>
       <c r="AA386" s="2" t="inlineStr">
         <is>
-          <t>乌鲁木齐市</t>
+          <t>吐鲁番市</t>
         </is>
       </c>
       <c r="AB386" s="2" t="inlineStr">
         <is>
-          <t>乌鲁木齐县</t>
+          <t>托克逊县</t>
         </is>
       </c>
       <c r="AC386" s="2" t="n"/>
@@ -39669,21 +39637,17 @@
         </is>
       </c>
       <c r="AG386" s="3" t="n"/>
-      <c r="AH386" s="2" t="inlineStr">
-        <is>
-          <t>天山</t>
-        </is>
-      </c>
+      <c r="AH386" s="2" t="n"/>
       <c r="AI386" s="2" t="n"/>
     </row>
     <row r="387" ht="24" customHeight="1" s="54">
       <c r="A387" s="2" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B387" s="2" t="n"/>
       <c r="C387" s="41" t="inlineStr">
         <is>
-          <t>56976</t>
+          <t>51468</t>
         </is>
       </c>
       <c r="D387" s="2" t="n"/>
@@ -39692,18 +39656,18 @@
       </c>
       <c r="F387" s="35" t="n"/>
       <c r="G387" s="26" t="n">
-        <v>23.2286</v>
+        <v>43.1131</v>
       </c>
       <c r="H387" s="26" t="n">
-        <v>102.8214</v>
+        <v>86.84310000000001</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>312.3</v>
+        <v>3540.5</v>
       </c>
       <c r="J387" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="K387" s="43" t="inlineStr">
+      <c r="K387" s="28" t="inlineStr">
         <is>
           <t>🇨🇳</t>
         </is>
@@ -39711,24 +39675,30 @@
       <c r="L387" s="51" t="n"/>
       <c r="M387" s="13" t="inlineStr">
         <is>
-          <t>元阳</t>
+          <t>天山大西沟</t>
         </is>
       </c>
       <c r="N387" s="51" t="n"/>
-      <c r="O387" s="29" t="n"/>
-      <c r="P387" s="29" t="n"/>
-      <c r="Q387" s="29" t="n"/>
+      <c r="O387" s="29" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="P387" s="29" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q387" s="29" t="n">
+        <v>-8.710000000000001</v>
+      </c>
       <c r="R387" s="45" t="n"/>
       <c r="S387" s="21" t="n"/>
       <c r="T387" s="33" t="n"/>
       <c r="U387" s="37" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天山</t>
         </is>
       </c>
       <c r="V387" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="W387" s="3" t="inlineStr">
@@ -39749,12 +39719,12 @@
       <c r="Z387" s="3" t="n"/>
       <c r="AA387" s="2" t="inlineStr">
         <is>
-          <t>红河哈尼族彝族自治州</t>
+          <t>乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB387" s="2" t="inlineStr">
         <is>
-          <t>元阳县</t>
+          <t>乌鲁木齐县</t>
         </is>
       </c>
       <c r="AC387" s="2" t="n"/>
@@ -39770,17 +39740,21 @@
         </is>
       </c>
       <c r="AG387" s="3" t="n"/>
-      <c r="AH387" s="2" t="n"/>
+      <c r="AH387" s="2" t="inlineStr">
+        <is>
+          <t>天山</t>
+        </is>
+      </c>
       <c r="AI387" s="2" t="n"/>
     </row>
     <row r="388" ht="24" customHeight="1" s="54">
       <c r="A388" s="2" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B388" s="2" t="n"/>
       <c r="C388" s="41" t="inlineStr">
         <is>
-          <t>56673</t>
+          <t>56976</t>
         </is>
       </c>
       <c r="D388" s="2" t="n"/>
@@ -39789,18 +39763,18 @@
       </c>
       <c r="F388" s="35" t="n"/>
       <c r="G388" s="26" t="n">
-        <v>26.9181</v>
+        <v>23.2286</v>
       </c>
       <c r="H388" s="26" t="n">
-        <v>102.9267</v>
+        <v>102.8214</v>
       </c>
       <c r="I388" s="2" t="n">
-        <v>893.9</v>
+        <v>312.3</v>
       </c>
       <c r="J388" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="K388" s="28" t="inlineStr">
+      <c r="K388" s="43" t="inlineStr">
         <is>
           <t>🇨🇳</t>
         </is>
@@ -39808,7 +39782,7 @@
       <c r="L388" s="51" t="n"/>
       <c r="M388" s="13" t="inlineStr">
         <is>
-          <t>巧家</t>
+          <t>元阳</t>
         </is>
       </c>
       <c r="N388" s="51" t="n"/>
@@ -39846,12 +39820,12 @@
       <c r="Z388" s="3" t="n"/>
       <c r="AA388" s="2" t="inlineStr">
         <is>
-          <t>昭通市</t>
+          <t>红河哈尼族彝族自治州</t>
         </is>
       </c>
       <c r="AB388" s="2" t="inlineStr">
         <is>
-          <t>巧家县</t>
+          <t>元阳县</t>
         </is>
       </c>
       <c r="AC388" s="2" t="n"/>
@@ -39871,19 +39845,43 @@
       <c r="AI388" s="2" t="n"/>
     </row>
     <row r="389" ht="24" customHeight="1" s="54">
-      <c r="A389" s="12" t="n"/>
+      <c r="A389" s="2" t="n">
+        <v>388</v>
+      </c>
       <c r="B389" s="2" t="n"/>
-      <c r="C389" s="41" t="n"/>
+      <c r="C389" s="41" t="inlineStr">
+        <is>
+          <t>56673</t>
+        </is>
+      </c>
       <c r="D389" s="2" t="n"/>
-      <c r="E389" s="3" t="n"/>
+      <c r="E389" s="3" t="n">
+        <v>99999</v>
+      </c>
       <c r="F389" s="35" t="n"/>
-      <c r="G389" s="26" t="n"/>
-      <c r="H389" s="26" t="n"/>
-      <c r="I389" s="2" t="n"/>
-      <c r="J389" s="24" t="n"/>
-      <c r="K389" s="28" t="n"/>
+      <c r="G389" s="26" t="n">
+        <v>26.9181</v>
+      </c>
+      <c r="H389" s="26" t="n">
+        <v>102.9267</v>
+      </c>
+      <c r="I389" s="2" t="n">
+        <v>893.9</v>
+      </c>
+      <c r="J389" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="K389" s="28" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L389" s="51" t="n"/>
-      <c r="M389" s="13" t="n"/>
+      <c r="M389" s="13" t="inlineStr">
+        <is>
+          <t>巧家</t>
+        </is>
+      </c>
       <c r="N389" s="51" t="n"/>
       <c r="O389" s="29" t="n"/>
       <c r="P389" s="29" t="n"/>
@@ -39891,18 +39889,54 @@
       <c r="R389" s="45" t="n"/>
       <c r="S389" s="21" t="n"/>
       <c r="T389" s="33" t="n"/>
-      <c r="U389" s="37" t="n"/>
-      <c r="V389" s="2" t="n"/>
-      <c r="W389" s="3" t="n"/>
-      <c r="X389" s="3" t="n"/>
-      <c r="Y389" s="3" t="n"/>
+      <c r="U389" s="37" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="V389" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="W389" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X389" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y389" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Z389" s="3" t="n"/>
-      <c r="AA389" s="2" t="n"/>
-      <c r="AB389" s="2" t="n"/>
+      <c r="AA389" s="2" t="inlineStr">
+        <is>
+          <t>昭通市</t>
+        </is>
+      </c>
+      <c r="AB389" s="2" t="inlineStr">
+        <is>
+          <t>巧家县</t>
+        </is>
+      </c>
       <c r="AC389" s="2" t="n"/>
       <c r="AD389" s="2" t="n"/>
-      <c r="AE389" s="2" t="n"/>
-      <c r="AF389" s="3" t="n"/>
+      <c r="AE389" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AF389" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AG389" s="3" t="n"/>
       <c r="AH389" s="2" t="n"/>
       <c r="AI389" s="2" t="n"/>
@@ -41398,7 +41432,7 @@
       <c r="H430" s="26" t="n"/>
       <c r="I430" s="2" t="n"/>
       <c r="J430" s="24" t="n"/>
-      <c r="K430" s="3" t="n"/>
+      <c r="K430" s="28" t="n"/>
       <c r="L430" s="51" t="n"/>
       <c r="M430" s="13" t="n"/>
       <c r="N430" s="51" t="n"/>
@@ -41573,9 +41607,7 @@
       <c r="AI434" s="2" t="n"/>
     </row>
     <row r="435" ht="24" customHeight="1" s="54">
-      <c r="A435" s="11" t="n">
-        <v>999</v>
-      </c>
+      <c r="A435" s="12" t="n"/>
       <c r="B435" s="2" t="n"/>
       <c r="C435" s="41" t="n"/>
       <c r="D435" s="2" t="n"/>
@@ -41589,11 +41621,7 @@
       <c r="L435" s="51" t="n"/>
       <c r="M435" s="13" t="n"/>
       <c r="N435" s="51" t="n"/>
-      <c r="O435" s="29" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
+      <c r="O435" s="29" t="n"/>
       <c r="P435" s="29" t="n"/>
       <c r="Q435" s="29" t="n"/>
       <c r="R435" s="45" t="n"/>
@@ -41615,15 +41643,58 @@
       <c r="AH435" s="2" t="n"/>
       <c r="AI435" s="2" t="n"/>
     </row>
+    <row r="436" ht="24" customHeight="1" s="54">
+      <c r="A436" s="11" t="n">
+        <v>999</v>
+      </c>
+      <c r="B436" s="2" t="n"/>
+      <c r="C436" s="41" t="n"/>
+      <c r="D436" s="2" t="n"/>
+      <c r="E436" s="3" t="n"/>
+      <c r="F436" s="35" t="n"/>
+      <c r="G436" s="26" t="n"/>
+      <c r="H436" s="26" t="n"/>
+      <c r="I436" s="2" t="n"/>
+      <c r="J436" s="24" t="n"/>
+      <c r="K436" s="3" t="n"/>
+      <c r="L436" s="51" t="n"/>
+      <c r="M436" s="13" t="n"/>
+      <c r="N436" s="51" t="n"/>
+      <c r="O436" s="29" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="P436" s="29" t="n"/>
+      <c r="Q436" s="29" t="n"/>
+      <c r="R436" s="45" t="n"/>
+      <c r="S436" s="21" t="n"/>
+      <c r="T436" s="33" t="n"/>
+      <c r="U436" s="37" t="n"/>
+      <c r="V436" s="2" t="n"/>
+      <c r="W436" s="3" t="n"/>
+      <c r="X436" s="3" t="n"/>
+      <c r="Y436" s="3" t="n"/>
+      <c r="Z436" s="3" t="n"/>
+      <c r="AA436" s="2" t="n"/>
+      <c r="AB436" s="2" t="n"/>
+      <c r="AC436" s="2" t="n"/>
+      <c r="AD436" s="2" t="n"/>
+      <c r="AE436" s="2" t="n"/>
+      <c r="AF436" s="3" t="n"/>
+      <c r="AG436" s="3" t="n"/>
+      <c r="AH436" s="2" t="n"/>
+      <c r="AI436" s="2" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <autoFilter ref="A1:AI435"/>
-  <conditionalFormatting sqref="A2:N435 R2:AI435">
+  <autoFilter ref="A1:AI436"/>
+  <conditionalFormatting sqref="A2:N436 R2:AI436">
     <cfRule type="expression" priority="4" dxfId="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:Q435">
+  <conditionalFormatting sqref="O2:Q436">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -830,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="7" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="4" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="7" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="4" min="34" max="784"/>
-    <col width="12.59765625" customWidth="1" style="4" min="785" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="4" min="34" max="787"/>
+    <col width="12.59765625" customWidth="1" style="4" min="788" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="10">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="29" t="n">
-        <v>-9.5</v>
+        <v>-8</v>
       </c>
       <c r="P2" s="29" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="Q2" s="29" t="n">
-        <v>-3.85</v>
+        <v>-2.46</v>
       </c>
       <c r="R2" s="45" t="n"/>
       <c r="S2" s="21" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="29" t="n">
-        <v>-12.3</v>
+        <v>-6.1</v>
       </c>
       <c r="P3" s="29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q3" s="29" t="n"/>
       <c r="R3" s="45" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="29" t="n">
-        <v>-9.199999999999999</v>
+        <v>-15.7</v>
       </c>
       <c r="P4" s="29" t="n">
-        <v>3.1</v>
+        <v>-1</v>
       </c>
       <c r="Q4" s="29" t="n"/>
       <c r="R4" s="45" t="inlineStr">
@@ -1381,12 +1381,8 @@
         </is>
       </c>
       <c r="N5" s="51" t="n"/>
-      <c r="O5" s="29" t="n">
-        <v>-21</v>
-      </c>
-      <c r="P5" s="29" t="n">
-        <v>-6.8</v>
-      </c>
+      <c r="O5" s="29" t="n"/>
+      <c r="P5" s="29" t="n"/>
       <c r="Q5" s="29" t="n"/>
       <c r="R5" s="45" t="n"/>
       <c r="S5" s="21" t="n"/>
@@ -1489,13 +1485,13 @@
         </is>
       </c>
       <c r="O6" s="29" t="n">
-        <v>-25.7</v>
+        <v>-20.7</v>
       </c>
       <c r="P6" s="29" t="n">
-        <v>-7.5</v>
+        <v>-6.4</v>
       </c>
       <c r="Q6" s="29" t="n">
-        <v>-18.3</v>
+        <v>-14.29</v>
       </c>
       <c r="R6" s="47" t="inlineStr">
         <is>
@@ -1600,10 +1596,10 @@
         </is>
       </c>
       <c r="O7" s="29" t="n">
-        <v>-16.5</v>
+        <v>-12.5</v>
       </c>
       <c r="P7" s="29" t="n">
-        <v>1.8</v>
+        <v>-0.6</v>
       </c>
       <c r="Q7" s="29" t="n"/>
       <c r="R7" s="45" t="n"/>
@@ -1709,13 +1705,13 @@
       </c>
       <c r="N8" s="51" t="n"/>
       <c r="O8" s="29" t="n">
-        <v>-11.2</v>
+        <v>-3.9</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>-3.78</v>
+        <v>-0.51</v>
       </c>
       <c r="R8" s="45" t="n"/>
       <c r="S8" s="21" t="inlineStr">
@@ -1822,13 +1818,13 @@
       </c>
       <c r="N9" s="51" t="n"/>
       <c r="O9" s="29" t="n">
-        <v>-7.9</v>
+        <v>-5.7</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>-3.99</v>
+        <v>-0.88</v>
       </c>
       <c r="R9" s="45" t="n"/>
       <c r="S9" s="21" t="inlineStr">
@@ -1943,10 +1939,10 @@
         </is>
       </c>
       <c r="O10" s="29" t="n">
-        <v>-18.1</v>
+        <v>-15.2</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>-4.4</v>
+        <v>-5.4</v>
       </c>
       <c r="Q10" s="29" t="n">
         <v>-10.84</v>
@@ -2060,13 +2056,13 @@
         </is>
       </c>
       <c r="O11" s="29" t="n">
-        <v>-22.6</v>
+        <v>-13.3</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>2</v>
+        <v>-4.7</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>-3.28</v>
+        <v>-7.34</v>
       </c>
       <c r="R11" s="45" t="inlineStr">
         <is>
@@ -2177,13 +2173,13 @@
       </c>
       <c r="N12" s="51" t="n"/>
       <c r="O12" s="29" t="n">
-        <v>-20.6</v>
+        <v>-14.7</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>-7.1</v>
+        <v>-1.2</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>-14.69</v>
+        <v>-9.06</v>
       </c>
       <c r="R12" s="45" t="inlineStr">
         <is>
@@ -2298,13 +2294,13 @@
         </is>
       </c>
       <c r="O13" s="29" t="n">
-        <v>-18.9</v>
+        <v>-14</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>1.1</v>
+        <v>-0.5</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>-10.65</v>
+        <v>-8.59</v>
       </c>
       <c r="R13" s="45" t="inlineStr">
         <is>
@@ -2415,13 +2411,13 @@
       </c>
       <c r="N14" s="51" t="n"/>
       <c r="O14" s="29" t="n">
-        <v>-9.6</v>
+        <v>-6.9</v>
       </c>
       <c r="P14" s="29" t="n">
-        <v>9.4</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="29" t="n">
-        <v>-1.59</v>
+        <v>-3.26</v>
       </c>
       <c r="R14" s="45" t="n"/>
       <c r="S14" s="21" t="inlineStr">
@@ -2532,13 +2528,13 @@
       </c>
       <c r="N15" s="51" t="n"/>
       <c r="O15" s="29" t="n">
-        <v>-16.8</v>
+        <v>-11.2</v>
       </c>
       <c r="P15" s="29" t="n">
-        <v>5.6</v>
+        <v>-1.5</v>
       </c>
       <c r="Q15" s="29" t="n">
-        <v>-6.71</v>
+        <v>-4.99</v>
       </c>
       <c r="R15" s="45" t="n"/>
       <c r="S15" s="21" t="inlineStr">
@@ -2642,15 +2638,9 @@
         </is>
       </c>
       <c r="N16" s="51" t="n"/>
-      <c r="O16" s="29" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="P16" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q16" s="29" t="n">
-        <v>-4.61</v>
-      </c>
+      <c r="O16" s="29" t="n"/>
+      <c r="P16" s="29" t="n"/>
+      <c r="Q16" s="29" t="n"/>
       <c r="R16" s="45" t="n"/>
       <c r="S16" s="21" t="n"/>
       <c r="T16" s="33" t="n"/>
@@ -2834,7 +2824,9 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O18" s="29" t="n"/>
+      <c r="O18" s="29" t="n">
+        <v>-21.3</v>
+      </c>
       <c r="P18" s="29" t="n"/>
       <c r="Q18" s="29" t="n"/>
       <c r="R18" s="45" t="n"/>
@@ -3025,13 +3017,13 @@
       </c>
       <c r="N20" s="51" t="n"/>
       <c r="O20" s="29" t="n">
-        <v>-20.3</v>
+        <v>-21</v>
       </c>
       <c r="P20" s="29" t="n">
-        <v>0.3</v>
+        <v>-4.9</v>
       </c>
       <c r="Q20" s="29" t="n">
-        <v>-11.83</v>
+        <v>-12.86</v>
       </c>
       <c r="R20" s="45" t="n"/>
       <c r="S20" s="21" t="n"/>
@@ -8805,12 +8797,8 @@
         </is>
       </c>
       <c r="N83" s="51" t="n"/>
-      <c r="O83" s="29" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="P83" s="29" t="n">
-        <v>-0.4</v>
-      </c>
+      <c r="O83" s="29" t="n"/>
+      <c r="P83" s="29" t="n"/>
       <c r="Q83" s="29" t="n"/>
       <c r="R83" s="45" t="n"/>
       <c r="S83" s="21" t="n"/>
@@ -10563,13 +10551,13 @@
         </is>
       </c>
       <c r="O102" s="29" t="n">
-        <v>-6</v>
+        <v>-16.8</v>
       </c>
       <c r="P102" s="29" t="n">
-        <v>-2.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q102" s="29" t="n">
-        <v>-4.24</v>
+        <v>-7.93</v>
       </c>
       <c r="R102" s="45" t="inlineStr">
         <is>
@@ -10993,13 +10981,13 @@
         </is>
       </c>
       <c r="O106" s="29" t="n">
-        <v>-18.5</v>
+        <v>-3.2</v>
       </c>
       <c r="P106" s="29" t="n">
-        <v>3.2</v>
+        <v>-0.3</v>
       </c>
       <c r="Q106" s="29" t="n">
-        <v>-9.279999999999999</v>
+        <v>-1.58</v>
       </c>
       <c r="R106" s="45" t="n"/>
       <c r="S106" s="21" t="inlineStr">
@@ -11115,13 +11103,13 @@
         </is>
       </c>
       <c r="O107" s="29" t="n">
-        <v>-18.5</v>
+        <v>-5.3</v>
       </c>
       <c r="P107" s="29" t="n">
-        <v>3</v>
+        <v>-0.1</v>
       </c>
       <c r="Q107" s="29" t="n">
-        <v>-9.300000000000001</v>
+        <v>-1.91</v>
       </c>
       <c r="R107" s="45" t="n"/>
       <c r="S107" s="21" t="inlineStr">
@@ -11335,13 +11323,13 @@
         </is>
       </c>
       <c r="O109" s="29" t="n">
-        <v>-12.2</v>
+        <v>-5.6</v>
       </c>
       <c r="P109" s="29" t="n">
-        <v>9</v>
+        <v>2.1</v>
       </c>
       <c r="Q109" s="29" t="n">
-        <v>-3.89</v>
+        <v>-1.39</v>
       </c>
       <c r="R109" s="45" t="n"/>
       <c r="S109" s="21" t="inlineStr">
@@ -11555,13 +11543,13 @@
       </c>
       <c r="N111" s="51" t="n"/>
       <c r="O111" s="29" t="n">
-        <v>-6</v>
+        <v>-3.2</v>
       </c>
       <c r="P111" s="29" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="Q111" s="29" t="n">
-        <v>-1.04</v>
+        <v>0.5</v>
       </c>
       <c r="R111" s="45" t="n"/>
       <c r="S111" s="21" t="inlineStr">
@@ -11783,13 +11771,13 @@
       </c>
       <c r="N113" s="51" t="n"/>
       <c r="O113" s="29" t="n">
-        <v>-13.5</v>
+        <v>-12.6</v>
       </c>
       <c r="P113" s="29" t="n">
-        <v>-1.1</v>
+        <v>-2.9</v>
       </c>
       <c r="Q113" s="29" t="n">
-        <v>-6.56</v>
+        <v>-8.35</v>
       </c>
       <c r="R113" s="45" t="inlineStr">
         <is>
@@ -12308,13 +12296,13 @@
       </c>
       <c r="N118" s="51" t="n"/>
       <c r="O118" s="29" t="n">
-        <v>-5.4</v>
+        <v>-2.5</v>
       </c>
       <c r="P118" s="29" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="Q118" s="29" t="n">
-        <v>-1.86</v>
+        <v>2.86</v>
       </c>
       <c r="R118" s="45" t="n"/>
       <c r="S118" s="21" t="inlineStr">
@@ -12421,13 +12409,13 @@
       </c>
       <c r="N119" s="51" t="n"/>
       <c r="O119" s="29" t="n">
-        <v>-0.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P119" s="29" t="n">
-        <v>9.9</v>
+        <v>16.9</v>
       </c>
       <c r="Q119" s="29" t="n">
-        <v>5.08</v>
+        <v>12.29</v>
       </c>
       <c r="R119" s="45" t="n"/>
       <c r="S119" s="21" t="inlineStr">
@@ -12657,13 +12645,13 @@
       </c>
       <c r="N121" s="51" t="n"/>
       <c r="O121" s="29" t="n">
-        <v>-1.9</v>
+        <v>6.6</v>
       </c>
       <c r="P121" s="29" t="n">
-        <v>5.4</v>
+        <v>15.9</v>
       </c>
       <c r="Q121" s="29" t="n">
-        <v>2.26</v>
+        <v>11.24</v>
       </c>
       <c r="R121" s="45" t="n"/>
       <c r="S121" s="21" t="inlineStr">
@@ -12782,13 +12770,13 @@
       </c>
       <c r="N122" s="51" t="n"/>
       <c r="O122" s="29" t="n">
-        <v>-1.8</v>
+        <v>7.7</v>
       </c>
       <c r="P122" s="29" t="n">
-        <v>4.4</v>
+        <v>16.1</v>
       </c>
       <c r="Q122" s="29" t="n">
-        <v>1.62</v>
+        <v>11.41</v>
       </c>
       <c r="R122" s="45" t="n"/>
       <c r="S122" s="21" t="inlineStr">
@@ -13343,13 +13331,13 @@
       </c>
       <c r="N127" s="51" t="n"/>
       <c r="O127" s="29" t="n">
-        <v>-16.2</v>
+        <v>-6</v>
       </c>
       <c r="P127" s="29" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="Q127" s="29" t="n">
-        <v>-7.06</v>
+        <v>1.17</v>
       </c>
       <c r="R127" s="45" t="n"/>
       <c r="S127" s="21" t="inlineStr">
@@ -13678,13 +13666,13 @@
       </c>
       <c r="N130" s="51" t="n"/>
       <c r="O130" s="29" t="n">
-        <v>-10</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="P130" s="29" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="Q130" s="29" t="n">
-        <v>-4.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R130" s="45" t="n"/>
       <c r="S130" s="21" t="inlineStr">
@@ -14416,15 +14404,9 @@
         </is>
       </c>
       <c r="N137" s="51" t="n"/>
-      <c r="O137" s="29" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="P137" s="29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q137" s="29" t="n">
-        <v>-1.71</v>
-      </c>
+      <c r="O137" s="29" t="n"/>
+      <c r="P137" s="29" t="n"/>
+      <c r="Q137" s="29" t="n"/>
       <c r="R137" s="45" t="n"/>
       <c r="S137" s="21" t="n"/>
       <c r="T137" s="33" t="n"/>
@@ -14978,13 +14960,13 @@
       </c>
       <c r="N142" s="51" t="n"/>
       <c r="O142" s="29" t="n">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="P142" s="29" t="n">
-        <v>16.7</v>
+        <v>17.7</v>
       </c>
       <c r="Q142" s="29" t="n">
-        <v>10.8</v>
+        <v>13.14</v>
       </c>
       <c r="R142" s="45" t="n"/>
       <c r="S142" s="21" t="inlineStr">
@@ -15095,13 +15077,13 @@
       </c>
       <c r="N143" s="51" t="n"/>
       <c r="O143" s="29" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="P143" s="29" t="n">
-        <v>10.9</v>
+        <v>4</v>
       </c>
       <c r="Q143" s="29" t="n">
-        <v>6.31</v>
+        <v>0.79</v>
       </c>
       <c r="R143" s="45" t="n"/>
       <c r="S143" s="21" t="inlineStr">
@@ -15323,13 +15305,13 @@
       </c>
       <c r="N145" s="51" t="n"/>
       <c r="O145" s="29" t="n">
-        <v>-7.3</v>
+        <v>1.5</v>
       </c>
       <c r="P145" s="29" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q145" s="29" t="n">
-        <v>-0.19</v>
+        <v>6.94</v>
       </c>
       <c r="R145" s="45" t="n"/>
       <c r="S145" s="21" t="inlineStr">
@@ -15448,13 +15430,13 @@
       </c>
       <c r="N146" s="51" t="n"/>
       <c r="O146" s="29" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="P146" s="29" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="Q146" s="29" t="n">
-        <v>10.22</v>
+        <v>11.96</v>
       </c>
       <c r="R146" s="45" t="n"/>
       <c r="S146" s="21" t="inlineStr">
@@ -15561,13 +15543,13 @@
       </c>
       <c r="N147" s="51" t="n"/>
       <c r="O147" s="29" t="n">
-        <v>-3</v>
+        <v>3.7</v>
       </c>
       <c r="P147" s="29" t="n">
-        <v>14.1</v>
+        <v>19</v>
       </c>
       <c r="Q147" s="29" t="n">
-        <v>3.96</v>
+        <v>10.28</v>
       </c>
       <c r="R147" s="45" t="n"/>
       <c r="S147" s="21" t="inlineStr">
@@ -15682,13 +15664,13 @@
       </c>
       <c r="N148" s="51" t="n"/>
       <c r="O148" s="29" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="P148" s="29" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="Q148" s="29" t="n">
-        <v>6.56</v>
+        <v>11.6</v>
       </c>
       <c r="R148" s="45" t="n"/>
       <c r="S148" s="21" t="inlineStr">
@@ -15803,13 +15785,13 @@
       </c>
       <c r="N149" s="51" t="n"/>
       <c r="O149" s="29" t="n">
-        <v>-2.8</v>
+        <v>-1.7</v>
       </c>
       <c r="P149" s="29" t="n">
-        <v>13.8</v>
+        <v>20.5</v>
       </c>
       <c r="Q149" s="29" t="n">
-        <v>3.58</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="R149" s="45" t="n"/>
       <c r="S149" s="21" t="inlineStr">
@@ -15924,13 +15906,13 @@
       </c>
       <c r="N150" s="51" t="n"/>
       <c r="O150" s="29" t="n">
-        <v>5.6</v>
+        <v>10.9</v>
       </c>
       <c r="P150" s="29" t="n">
-        <v>16</v>
+        <v>21.4</v>
       </c>
       <c r="Q150" s="29" t="n">
-        <v>10.68</v>
+        <v>15.08</v>
       </c>
       <c r="R150" s="45" t="n"/>
       <c r="S150" s="21" t="inlineStr">
@@ -16041,13 +16023,13 @@
       </c>
       <c r="N151" s="51" t="n"/>
       <c r="O151" s="29" t="n">
-        <v>10.6</v>
+        <v>12.9</v>
       </c>
       <c r="P151" s="29" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="Q151" s="29" t="n">
-        <v>15.42</v>
+        <v>15.65</v>
       </c>
       <c r="R151" s="45" t="n"/>
       <c r="S151" s="21" t="inlineStr">
@@ -16161,10 +16143,10 @@
         <v>6.5</v>
       </c>
       <c r="P152" s="29" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="Q152" s="29" t="n">
-        <v>11.9</v>
+        <v>12.05</v>
       </c>
       <c r="R152" s="45" t="n"/>
       <c r="S152" s="21" t="inlineStr">
@@ -16382,13 +16364,13 @@
       </c>
       <c r="N154" s="51" t="n"/>
       <c r="O154" s="29" t="n">
-        <v>15.3</v>
+        <v>14.2</v>
       </c>
       <c r="P154" s="29" t="n">
-        <v>19</v>
+        <v>16.8</v>
       </c>
       <c r="Q154" s="29" t="n">
-        <v>16.64</v>
+        <v>14.96</v>
       </c>
       <c r="R154" s="45" t="n"/>
       <c r="S154" s="21" t="inlineStr">
@@ -16499,13 +16481,13 @@
       </c>
       <c r="N155" s="51" t="n"/>
       <c r="O155" s="29" t="n">
-        <v>18.1</v>
+        <v>16.6</v>
       </c>
       <c r="P155" s="29" t="n">
-        <v>22.9</v>
+        <v>25.3</v>
       </c>
       <c r="Q155" s="29" t="n">
-        <v>20.15</v>
+        <v>20.66</v>
       </c>
       <c r="R155" s="45" t="n"/>
       <c r="S155" s="21" t="inlineStr">
@@ -16616,13 +16598,13 @@
       </c>
       <c r="N156" s="51" t="n"/>
       <c r="O156" s="29" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="P156" s="29" t="n">
         <v>20.2</v>
       </c>
       <c r="Q156" s="29" t="n">
-        <v>17.24</v>
+        <v>17.02</v>
       </c>
       <c r="R156" s="45" t="n"/>
       <c r="S156" s="21" t="inlineStr">
@@ -16733,13 +16715,13 @@
       </c>
       <c r="N157" s="51" t="n"/>
       <c r="O157" s="29" t="n">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
       <c r="P157" s="29" t="n">
-        <v>19.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q157" s="29" t="n">
-        <v>16.86</v>
+        <v>17.71</v>
       </c>
       <c r="R157" s="45" t="n"/>
       <c r="S157" s="21" t="inlineStr">
@@ -16850,13 +16832,13 @@
       </c>
       <c r="N158" s="51" t="n"/>
       <c r="O158" s="29" t="n">
-        <v>18.1</v>
+        <v>16.2</v>
       </c>
       <c r="P158" s="29" t="n">
-        <v>22.8</v>
+        <v>20.4</v>
       </c>
       <c r="Q158" s="29" t="n">
-        <v>19.36</v>
+        <v>18</v>
       </c>
       <c r="R158" s="45" t="n"/>
       <c r="S158" s="21" t="inlineStr">
@@ -17070,13 +17052,13 @@
       </c>
       <c r="N160" s="51" t="n"/>
       <c r="O160" s="29" t="n">
-        <v>24.3</v>
+        <v>20.4</v>
       </c>
       <c r="P160" s="29" t="n">
-        <v>32</v>
+        <v>28.6</v>
       </c>
       <c r="Q160" s="29" t="n">
-        <v>26.54</v>
+        <v>24.46</v>
       </c>
       <c r="R160" s="45" t="n"/>
       <c r="S160" s="21" t="inlineStr">
@@ -17187,13 +17169,13 @@
       </c>
       <c r="N161" s="51" t="n"/>
       <c r="O161" s="29" t="n">
-        <v>22.5</v>
+        <v>20.6</v>
       </c>
       <c r="P161" s="29" t="n">
-        <v>33.9</v>
+        <v>31.2</v>
       </c>
       <c r="Q161" s="29" t="n">
-        <v>27.24</v>
+        <v>25.01</v>
       </c>
       <c r="R161" s="45" t="n"/>
       <c r="S161" s="21" t="inlineStr">
@@ -17506,13 +17488,13 @@
       </c>
       <c r="N164" s="51" t="n"/>
       <c r="O164" s="29" t="n">
-        <v>26.2</v>
+        <v>24.8</v>
       </c>
       <c r="P164" s="29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q164" s="29" t="n">
-        <v>28.35</v>
+        <v>28.17</v>
       </c>
       <c r="R164" s="45" t="n"/>
       <c r="S164" s="21" t="inlineStr">
@@ -17615,13 +17597,13 @@
       </c>
       <c r="N165" s="51" t="n"/>
       <c r="O165" s="29" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="P165" s="29" t="n">
-        <v>33.6</v>
+        <v>33.3</v>
       </c>
       <c r="Q165" s="29" t="n">
-        <v>27.45</v>
+        <v>27.2</v>
       </c>
       <c r="R165" s="45" t="n"/>
       <c r="S165" s="21" t="inlineStr">
@@ -17732,13 +17714,13 @@
       </c>
       <c r="N166" s="51" t="n"/>
       <c r="O166" s="29" t="n">
-        <v>15.5</v>
+        <v>13.9</v>
       </c>
       <c r="P166" s="29" t="n">
-        <v>22.4</v>
+        <v>26.9</v>
       </c>
       <c r="Q166" s="29" t="n">
-        <v>18.14</v>
+        <v>19.52</v>
       </c>
       <c r="R166" s="45" t="n"/>
       <c r="S166" s="21" t="inlineStr">
@@ -17849,13 +17831,13 @@
       </c>
       <c r="N167" s="51" t="n"/>
       <c r="O167" s="29" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
       <c r="P167" s="29" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="Q167" s="29" t="n">
-        <v>13.34</v>
+        <v>13.85</v>
       </c>
       <c r="R167" s="45" t="n"/>
       <c r="S167" s="21" t="inlineStr">
@@ -17966,13 +17948,13 @@
       </c>
       <c r="N168" s="51" t="n"/>
       <c r="O168" s="29" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="P168" s="29" t="n">
-        <v>23</v>
+        <v>21.4</v>
       </c>
       <c r="Q168" s="29" t="n">
-        <v>20.62</v>
+        <v>19.2</v>
       </c>
       <c r="R168" s="45" t="n"/>
       <c r="S168" s="21" t="inlineStr">
@@ -18174,13 +18156,13 @@
       </c>
       <c r="N170" s="51" t="n"/>
       <c r="O170" s="29" t="n">
-        <v>15.2</v>
+        <v>12.8</v>
       </c>
       <c r="P170" s="29" t="n">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="Q170" s="29" t="n">
-        <v>17.55</v>
+        <v>15.82</v>
       </c>
       <c r="R170" s="45" t="n"/>
       <c r="S170" s="21" t="inlineStr">
@@ -18298,10 +18280,10 @@
         <v>1.9</v>
       </c>
       <c r="P171" s="29" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="Q171" s="29" t="n">
-        <v>8.75</v>
+        <v>8.26</v>
       </c>
       <c r="R171" s="45" t="n"/>
       <c r="S171" s="21" t="inlineStr">
@@ -18502,15 +18484,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O173" s="29" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="P173" s="29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Q173" s="29" t="n">
-        <v>-1.7</v>
-      </c>
+      <c r="O173" s="29" t="n"/>
+      <c r="P173" s="29" t="n"/>
+      <c r="Q173" s="29" t="n"/>
       <c r="R173" s="45" t="n"/>
       <c r="S173" s="21" t="n"/>
       <c r="T173" s="33" t="n"/>
@@ -18893,14 +18869,12 @@
       </c>
       <c r="N177" s="51" t="n"/>
       <c r="O177" s="29" t="n">
-        <v>-6.7</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P177" s="29" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q177" s="29" t="n">
-        <v>-0.77</v>
-      </c>
+        <v>4.7</v>
+      </c>
+      <c r="Q177" s="29" t="n"/>
       <c r="R177" s="45" t="n"/>
       <c r="S177" s="21" t="inlineStr">
         <is>
@@ -19006,13 +18980,13 @@
       </c>
       <c r="N178" s="51" t="n"/>
       <c r="O178" s="29" t="n">
-        <v>-8.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="P178" s="29" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="Q178" s="29" t="n">
-        <v>-2.11</v>
+        <v>-2.03</v>
       </c>
       <c r="R178" s="45" t="n"/>
       <c r="S178" s="21" t="inlineStr">
@@ -19121,13 +19095,13 @@
       </c>
       <c r="N179" s="51" t="n"/>
       <c r="O179" s="29" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="P179" s="29" t="n">
-        <v>16.2</v>
+        <v>18.3</v>
       </c>
       <c r="Q179" s="29" t="n">
-        <v>9.640000000000001</v>
+        <v>12.73</v>
       </c>
       <c r="R179" s="45" t="n"/>
       <c r="S179" s="21" t="inlineStr">
@@ -19226,13 +19200,13 @@
       </c>
       <c r="N180" s="51" t="n"/>
       <c r="O180" s="29" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="P180" s="29" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="Q180" s="29" t="n">
-        <v>19.31</v>
+        <v>19.29</v>
       </c>
       <c r="R180" s="45" t="n"/>
       <c r="S180" s="21" t="inlineStr">
@@ -19335,13 +19309,13 @@
       </c>
       <c r="N181" s="51" t="n"/>
       <c r="O181" s="29" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="P181" s="29" t="n">
-        <v>15.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q181" s="29" t="n">
-        <v>6.66</v>
+        <v>10.74</v>
       </c>
       <c r="R181" s="45" t="n"/>
       <c r="S181" s="21" t="inlineStr">
@@ -19579,13 +19553,13 @@
         </is>
       </c>
       <c r="O183" s="29" t="n">
-        <v>-10.5</v>
+        <v>-11.1</v>
       </c>
       <c r="P183" s="29" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q183" s="29" t="n">
-        <v>-5.33</v>
+        <v>-4.88</v>
       </c>
       <c r="R183" s="45" t="n"/>
       <c r="S183" s="21" t="inlineStr">
@@ -19700,13 +19674,13 @@
       </c>
       <c r="N184" s="51" t="n"/>
       <c r="O184" s="29" t="n">
-        <v>-5.2</v>
+        <v>-8.5</v>
       </c>
       <c r="P184" s="29" t="n">
-        <v>1.6</v>
+        <v>-2.5</v>
       </c>
       <c r="Q184" s="29" t="n">
-        <v>-1.54</v>
+        <v>-5.05</v>
       </c>
       <c r="R184" s="45" t="n"/>
       <c r="S184" s="21" t="inlineStr">
@@ -19821,13 +19795,13 @@
       </c>
       <c r="N185" s="51" t="n"/>
       <c r="O185" s="29" t="n">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="P185" s="29" t="n">
-        <v>19.3</v>
+        <v>17.1</v>
       </c>
       <c r="Q185" s="29" t="n">
-        <v>12.06</v>
+        <v>11.7</v>
       </c>
       <c r="R185" s="45" t="n"/>
       <c r="S185" s="21" t="inlineStr">
@@ -19934,13 +19908,13 @@
       </c>
       <c r="N186" s="51" t="n"/>
       <c r="O186" s="29" t="n">
-        <v>12.5</v>
+        <v>14.7</v>
       </c>
       <c r="P186" s="29" t="n">
-        <v>18.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q186" s="29" t="n">
-        <v>16.13</v>
+        <v>17.01</v>
       </c>
       <c r="R186" s="45" t="n"/>
       <c r="S186" s="21" t="inlineStr">
@@ -20051,13 +20025,13 @@
       </c>
       <c r="N187" s="51" t="n"/>
       <c r="O187" s="29" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="P187" s="29" t="n">
-        <v>34</v>
+        <v>36.3</v>
       </c>
       <c r="Q187" s="29" t="n">
-        <v>27.01</v>
+        <v>28.43</v>
       </c>
       <c r="R187" s="45" t="n"/>
       <c r="S187" s="21" t="inlineStr">
@@ -20164,13 +20138,13 @@
       </c>
       <c r="N188" s="51" t="n"/>
       <c r="O188" s="29" t="n">
-        <v>5.3</v>
+        <v>10.1</v>
       </c>
       <c r="P188" s="29" t="n">
-        <v>14.4</v>
+        <v>18.6</v>
       </c>
       <c r="Q188" s="29" t="n">
-        <v>8.449999999999999</v>
+        <v>14.31</v>
       </c>
       <c r="R188" s="45" t="n"/>
       <c r="S188" s="21" t="inlineStr">
@@ -20367,9 +20341,15 @@
           <t>🔵</t>
         </is>
       </c>
-      <c r="O190" s="29" t="n"/>
-      <c r="P190" s="29" t="n"/>
-      <c r="Q190" s="29" t="n"/>
+      <c r="O190" s="29" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="P190" s="29" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="Q190" s="29" t="n">
+        <v>-10.3</v>
+      </c>
       <c r="R190" s="45" t="n"/>
       <c r="S190" s="21" t="n"/>
       <c r="T190" s="33" t="n"/>
@@ -20768,14 +20748,12 @@
         </is>
       </c>
       <c r="O194" s="29" t="n">
-        <v>-7.6</v>
+        <v>-3.9</v>
       </c>
       <c r="P194" s="29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q194" s="29" t="n">
-        <v>-3.3</v>
-      </c>
+        <v>11.6</v>
+      </c>
+      <c r="Q194" s="29" t="n"/>
       <c r="R194" s="45" t="inlineStr">
         <is>
           <t>2010-01-05</t>
@@ -20876,8 +20854,12 @@
         </is>
       </c>
       <c r="N195" s="51" t="n"/>
-      <c r="O195" s="29" t="n"/>
-      <c r="P195" s="29" t="n"/>
+      <c r="O195" s="29" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="P195" s="29" t="n">
+        <v>18</v>
+      </c>
       <c r="Q195" s="29" t="n"/>
       <c r="R195" s="45" t="n"/>
       <c r="S195" s="21" t="n"/>
@@ -20979,8 +20961,12 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O196" s="29" t="n"/>
-      <c r="P196" s="29" t="n"/>
+      <c r="O196" s="29" t="n">
+        <v>-11</v>
+      </c>
+      <c r="P196" s="29" t="n">
+        <v>-3.5</v>
+      </c>
       <c r="Q196" s="29" t="n"/>
       <c r="R196" s="45" t="n"/>
       <c r="S196" s="21" t="n"/>
@@ -21087,10 +21073,10 @@
         </is>
       </c>
       <c r="O197" s="29" t="n">
-        <v>-15.6</v>
+        <v>-4.2</v>
       </c>
       <c r="P197" s="29" t="n">
-        <v>-3.3</v>
+        <v>1.9</v>
       </c>
       <c r="Q197" s="29" t="n"/>
       <c r="R197" s="45" t="n"/>
@@ -21589,12 +21575,8 @@
         </is>
       </c>
       <c r="N202" s="51" t="n"/>
-      <c r="O202" s="29" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="P202" s="29" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="O202" s="29" t="n"/>
+      <c r="P202" s="29" t="n"/>
       <c r="Q202" s="29" t="n"/>
       <c r="R202" s="45" t="n"/>
       <c r="S202" s="21" t="n"/>
@@ -21682,12 +21664,8 @@
         </is>
       </c>
       <c r="N203" s="51" t="n"/>
-      <c r="O203" s="29" t="n">
-        <v>-16.2</v>
-      </c>
-      <c r="P203" s="29" t="n">
-        <v>-4</v>
-      </c>
+      <c r="O203" s="29" t="n"/>
+      <c r="P203" s="29" t="n"/>
       <c r="Q203" s="29" t="n"/>
       <c r="R203" s="45" t="n"/>
       <c r="S203" s="21" t="n"/>
@@ -21785,12 +21763,8 @@
         </is>
       </c>
       <c r="N204" s="51" t="n"/>
-      <c r="O204" s="29" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="P204" s="29" t="n">
-        <v>-4.7</v>
-      </c>
+      <c r="O204" s="29" t="n"/>
+      <c r="P204" s="29" t="n"/>
       <c r="Q204" s="29" t="n"/>
       <c r="R204" s="45" t="n"/>
       <c r="S204" s="21" t="n"/>
@@ -22209,8 +22183,12 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O208" s="29" t="n"/>
-      <c r="P208" s="29" t="n"/>
+      <c r="O208" s="29" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="P208" s="29" t="n">
+        <v>7.6</v>
+      </c>
       <c r="Q208" s="29" t="n"/>
       <c r="R208" s="45" t="inlineStr">
         <is>
@@ -22514,9 +22492,15 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O211" s="29" t="n"/>
-      <c r="P211" s="29" t="n"/>
-      <c r="Q211" s="29" t="n"/>
+      <c r="O211" s="29" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="P211" s="29" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="Q211" s="29" t="n">
+        <v>-14.6</v>
+      </c>
       <c r="R211" s="45" t="n"/>
       <c r="S211" s="21" t="n"/>
       <c r="T211" s="33" t="n"/>
@@ -22728,8 +22712,12 @@
         </is>
       </c>
       <c r="N213" s="51" t="n"/>
-      <c r="O213" s="29" t="n"/>
-      <c r="P213" s="29" t="n"/>
+      <c r="O213" s="29" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="P213" s="29" t="n">
+        <v>-4.5</v>
+      </c>
       <c r="Q213" s="29" t="n"/>
       <c r="R213" s="45" t="n"/>
       <c r="S213" s="21" t="n"/>
@@ -22834,7 +22822,7 @@
         </is>
       </c>
       <c r="O214" s="29" t="n">
-        <v>-41.9</v>
+        <v>-46.8</v>
       </c>
       <c r="P214" s="29" t="n"/>
       <c r="Q214" s="29" t="n"/>
@@ -22926,9 +22914,7 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O215" s="29" t="n">
-        <v>-44</v>
-      </c>
+      <c r="O215" s="29" t="n"/>
       <c r="P215" s="29" t="n"/>
       <c r="Q215" s="29" t="n"/>
       <c r="R215" s="45" t="n"/>
@@ -23699,13 +23685,13 @@
       </c>
       <c r="N223" s="51" t="n"/>
       <c r="O223" s="29" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="P223" s="29" t="n">
-        <v>12.3</v>
+        <v>13.2</v>
       </c>
       <c r="Q223" s="29" t="n">
-        <v>5.09</v>
+        <v>8.93</v>
       </c>
       <c r="R223" s="45" t="n"/>
       <c r="S223" s="21" t="inlineStr">
@@ -24103,13 +24089,13 @@
       </c>
       <c r="N227" s="51" t="n"/>
       <c r="O227" s="29" t="n">
-        <v>-8.4</v>
+        <v>-1</v>
       </c>
       <c r="P227" s="29" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q227" s="29" t="n">
-        <v>-2</v>
+        <v>0.93</v>
       </c>
       <c r="R227" s="45" t="n"/>
       <c r="S227" s="21" t="inlineStr">
@@ -24313,13 +24299,13 @@
       </c>
       <c r="N229" s="51" t="n"/>
       <c r="O229" s="29" t="n">
-        <v>0</v>
+        <v>-2.3</v>
       </c>
       <c r="P229" s="29" t="n">
-        <v>5.9</v>
+        <v>0.3</v>
       </c>
       <c r="Q229" s="29" t="n">
-        <v>3.41</v>
+        <v>-1.44</v>
       </c>
       <c r="R229" s="45" t="n"/>
       <c r="S229" s="21" t="inlineStr">
@@ -24719,13 +24705,13 @@
       </c>
       <c r="N233" s="51" t="n"/>
       <c r="O233" s="29" t="n">
-        <v>-11.3</v>
+        <v>-2.6</v>
       </c>
       <c r="P233" s="29" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q233" s="29" t="n">
-        <v>-4.58</v>
+        <v>-0.15</v>
       </c>
       <c r="R233" s="45" t="n"/>
       <c r="S233" s="21" t="inlineStr">
@@ -25313,13 +25299,13 @@
       </c>
       <c r="N239" s="51" t="n"/>
       <c r="O239" s="29" t="n">
-        <v>-0.3</v>
+        <v>-1.8</v>
       </c>
       <c r="P239" s="29" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q239" s="29" t="n">
-        <v>0.38</v>
+        <v>-0.78</v>
       </c>
       <c r="R239" s="45" t="n"/>
       <c r="S239" s="21" t="inlineStr">
@@ -25426,13 +25412,13 @@
       </c>
       <c r="N240" s="51" t="n"/>
       <c r="O240" s="29" t="n">
-        <v>0.4</v>
+        <v>-2</v>
       </c>
       <c r="P240" s="29" t="n">
-        <v>10.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q240" s="29" t="n">
-        <v>4.51</v>
+        <v>0.97</v>
       </c>
       <c r="R240" s="45" t="n"/>
       <c r="S240" s="21" t="inlineStr">
@@ -26404,14 +26390,12 @@
         </is>
       </c>
       <c r="O250" s="29" t="n">
-        <v>0.2</v>
+        <v>-6.2</v>
       </c>
       <c r="P250" s="29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q250" s="29" t="n">
-        <v>1.21</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="Q250" s="29" t="n"/>
       <c r="R250" s="45" t="n"/>
       <c r="S250" s="21" t="inlineStr">
         <is>
@@ -28959,15 +28943,9 @@
         </is>
       </c>
       <c r="N277" s="51" t="n"/>
-      <c r="O277" s="29" t="n">
-        <v>-26</v>
-      </c>
-      <c r="P277" s="29" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="Q277" s="29" t="n">
-        <v>-19.21</v>
-      </c>
+      <c r="O277" s="29" t="n"/>
+      <c r="P277" s="29" t="n"/>
+      <c r="Q277" s="29" t="n"/>
       <c r="R277" s="45" t="n"/>
       <c r="S277" s="21" t="n"/>
       <c r="T277" s="33" t="n"/>
@@ -29154,13 +29132,13 @@
         </is>
       </c>
       <c r="O279" s="29" t="n">
-        <v>-23</v>
+        <v>-26.8</v>
       </c>
       <c r="P279" s="29" t="n">
-        <v>-13.5</v>
+        <v>-12.5</v>
       </c>
       <c r="Q279" s="29" t="n">
-        <v>-18.75</v>
+        <v>-19.54</v>
       </c>
       <c r="R279" s="45" t="n"/>
       <c r="S279" s="21" t="inlineStr">
@@ -29656,10 +29634,10 @@
         </is>
       </c>
       <c r="O284" s="29" t="n">
-        <v>-18.3</v>
+        <v>-19.8</v>
       </c>
       <c r="P284" s="29" t="n">
-        <v>-3.3</v>
+        <v>-1.7</v>
       </c>
       <c r="Q284" s="29" t="n"/>
       <c r="R284" s="45" t="n"/>
@@ -30041,10 +30019,10 @@
         </is>
       </c>
       <c r="O288" s="29" t="n">
-        <v>-57.1</v>
+        <v>-60.3</v>
       </c>
       <c r="P288" s="29" t="n">
-        <v>-47.1</v>
+        <v>-48.4</v>
       </c>
       <c r="Q288" s="29" t="n"/>
       <c r="R288" s="45" t="n"/>
@@ -30237,13 +30215,13 @@
       </c>
       <c r="N290" s="51" t="n"/>
       <c r="O290" s="29" t="n">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="P290" s="29" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="Q290" s="29" t="n">
-        <v>3.73</v>
+        <v>0.88</v>
       </c>
       <c r="R290" s="45" t="n"/>
       <c r="S290" s="21" t="inlineStr">
@@ -30453,13 +30431,13 @@
         </is>
       </c>
       <c r="O292" s="29" t="n">
-        <v>-1.3</v>
+        <v>-1.9</v>
       </c>
       <c r="P292" s="29" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q292" s="29" t="n">
-        <v>1</v>
+        <v>0.21</v>
       </c>
       <c r="R292" s="45" t="n"/>
       <c r="S292" s="21" t="inlineStr">
@@ -35175,12 +35153,8 @@
         </is>
       </c>
       <c r="N341" s="51" t="n"/>
-      <c r="O341" s="29" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="P341" s="29" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="O341" s="29" t="n"/>
+      <c r="P341" s="29" t="n"/>
       <c r="Q341" s="29" t="n"/>
       <c r="R341" s="45" t="n"/>
       <c r="S341" s="21" t="n"/>
@@ -35272,8 +35246,12 @@
         </is>
       </c>
       <c r="N342" s="51" t="n"/>
-      <c r="O342" s="29" t="n"/>
-      <c r="P342" s="29" t="n"/>
+      <c r="O342" s="29" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="P342" s="29" t="n">
+        <v>4.9</v>
+      </c>
       <c r="Q342" s="29" t="n"/>
       <c r="R342" s="45" t="n"/>
       <c r="S342" s="21" t="n"/>
@@ -37041,15 +37019,9 @@
         </is>
       </c>
       <c r="N361" s="51" t="n"/>
-      <c r="O361" s="29" t="n">
-        <v>-13</v>
-      </c>
-      <c r="P361" s="29" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Q361" s="29" t="n">
-        <v>-3.68</v>
-      </c>
+      <c r="O361" s="29" t="n"/>
+      <c r="P361" s="29" t="n"/>
+      <c r="Q361" s="29" t="n"/>
       <c r="R361" s="45" t="n"/>
       <c r="S361" s="21" t="n"/>
       <c r="T361" s="33" t="n"/>
@@ -37251,9 +37223,15 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O363" s="29" t="n"/>
-      <c r="P363" s="29" t="n"/>
-      <c r="Q363" s="29" t="n"/>
+      <c r="O363" s="29" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="P363" s="29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q363" s="29" t="n">
+        <v>-4.05</v>
+      </c>
       <c r="R363" s="45" t="n"/>
       <c r="S363" s="21" t="n"/>
       <c r="T363" s="33" t="n"/>
@@ -37970,15 +37948,9 @@
         </is>
       </c>
       <c r="N370" s="51" t="n"/>
-      <c r="O370" s="29" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="P370" s="29" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="Q370" s="29" t="n">
-        <v>-0.31</v>
-      </c>
+      <c r="O370" s="29" t="n"/>
+      <c r="P370" s="29" t="n"/>
+      <c r="Q370" s="29" t="n"/>
       <c r="R370" s="45" t="n"/>
       <c r="S370" s="21" t="n"/>
       <c r="T370" s="33" t="n"/>
@@ -38657,9 +38629,15 @@
         </is>
       </c>
       <c r="N377" s="51" t="n"/>
-      <c r="O377" s="29" t="n"/>
-      <c r="P377" s="29" t="n"/>
-      <c r="Q377" s="29" t="n"/>
+      <c r="O377" s="29" t="n">
+        <v>-27.7</v>
+      </c>
+      <c r="P377" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q377" s="29" t="n">
+        <v>-16.8</v>
+      </c>
       <c r="R377" s="45" t="n"/>
       <c r="S377" s="21" t="n"/>
       <c r="T377" s="33" t="n"/>
@@ -39736,9 +39714,15 @@
         </is>
       </c>
       <c r="N388" s="51" t="n"/>
-      <c r="O388" s="29" t="n"/>
-      <c r="P388" s="29" t="n"/>
-      <c r="Q388" s="29" t="n"/>
+      <c r="O388" s="29" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="P388" s="29" t="n">
+        <v>-14</v>
+      </c>
+      <c r="Q388" s="29" t="n">
+        <v>-15.4</v>
+      </c>
       <c r="R388" s="45" t="n"/>
       <c r="S388" s="21" t="n"/>
       <c r="T388" s="33" t="n"/>
@@ -39839,9 +39823,15 @@
         </is>
       </c>
       <c r="N389" s="51" t="n"/>
-      <c r="O389" s="29" t="n"/>
-      <c r="P389" s="29" t="n"/>
-      <c r="Q389" s="29" t="n"/>
+      <c r="O389" s="29" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="P389" s="29" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="Q389" s="29" t="n">
+        <v>-15.3</v>
+      </c>
       <c r="R389" s="45" t="n"/>
       <c r="S389" s="21" t="n"/>
       <c r="T389" s="33" t="n"/>
@@ -41003,9 +40993,15 @@
         </is>
       </c>
       <c r="N401" s="51" t="n"/>
-      <c r="O401" s="29" t="n"/>
-      <c r="P401" s="29" t="n"/>
-      <c r="Q401" s="29" t="n"/>
+      <c r="O401" s="29" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="P401" s="29" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q401" s="29" t="n">
+        <v>-10.09</v>
+      </c>
       <c r="R401" s="45" t="n"/>
       <c r="S401" s="21" t="n"/>
       <c r="T401" s="33" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -830,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="7" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="4" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="7" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="4" min="34" max="787"/>
-    <col width="12.59765625" customWidth="1" style="4" min="788" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="4" min="34" max="789"/>
+    <col width="12.59765625" customWidth="1" style="4" min="790" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="10">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="29" t="n">
-        <v>-8</v>
+        <v>-9.4</v>
       </c>
       <c r="P2" s="29" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="Q2" s="29" t="n">
-        <v>-2.46</v>
+        <v>-3.79</v>
       </c>
       <c r="R2" s="45" t="n"/>
       <c r="S2" s="21" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="29" t="n">
-        <v>-6.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="P3" s="29" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="Q3" s="29" t="n"/>
       <c r="R3" s="45" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="29" t="n">
-        <v>-15.7</v>
+        <v>-20.4</v>
       </c>
       <c r="P4" s="29" t="n">
-        <v>-1</v>
+        <v>-6.5</v>
       </c>
       <c r="Q4" s="29" t="n"/>
       <c r="R4" s="45" t="inlineStr">
@@ -1381,8 +1381,12 @@
         </is>
       </c>
       <c r="N5" s="51" t="n"/>
-      <c r="O5" s="29" t="n"/>
-      <c r="P5" s="29" t="n"/>
+      <c r="O5" s="29" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="P5" s="29" t="n">
+        <v>-4.6</v>
+      </c>
       <c r="Q5" s="29" t="n"/>
       <c r="R5" s="45" t="n"/>
       <c r="S5" s="21" t="n"/>
@@ -1485,13 +1489,13 @@
         </is>
       </c>
       <c r="O6" s="29" t="n">
-        <v>-20.7</v>
+        <v>-20.6</v>
       </c>
       <c r="P6" s="29" t="n">
-        <v>-6.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="Q6" s="29" t="n">
-        <v>-14.29</v>
+        <v>-13.84</v>
       </c>
       <c r="R6" s="47" t="inlineStr">
         <is>
@@ -1596,10 +1600,10 @@
         </is>
       </c>
       <c r="O7" s="29" t="n">
-        <v>-12.5</v>
+        <v>-13.7</v>
       </c>
       <c r="P7" s="29" t="n">
-        <v>-0.6</v>
+        <v>-2.9</v>
       </c>
       <c r="Q7" s="29" t="n"/>
       <c r="R7" s="45" t="n"/>
@@ -1705,13 +1709,13 @@
       </c>
       <c r="N8" s="51" t="n"/>
       <c r="O8" s="29" t="n">
-        <v>-3.9</v>
+        <v>-12.1</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>-0.51</v>
+        <v>-4.9</v>
       </c>
       <c r="R8" s="45" t="n"/>
       <c r="S8" s="21" t="inlineStr">
@@ -1818,13 +1822,13 @@
       </c>
       <c r="N9" s="51" t="n"/>
       <c r="O9" s="29" t="n">
-        <v>-5.7</v>
+        <v>-7.4</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>-0.88</v>
+        <v>-2.58</v>
       </c>
       <c r="R9" s="45" t="n"/>
       <c r="S9" s="21" t="inlineStr">
@@ -1939,13 +1943,13 @@
         </is>
       </c>
       <c r="O10" s="29" t="n">
-        <v>-15.2</v>
+        <v>-21</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>-5.4</v>
+        <v>-7</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>-10.84</v>
+        <v>-14.54</v>
       </c>
       <c r="R10" s="45" t="n"/>
       <c r="S10" s="21" t="inlineStr">
@@ -2056,13 +2060,13 @@
         </is>
       </c>
       <c r="O11" s="29" t="n">
-        <v>-13.3</v>
+        <v>-22.2</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>-4.7</v>
+        <v>-6.4</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>-7.34</v>
+        <v>-14.74</v>
       </c>
       <c r="R11" s="45" t="inlineStr">
         <is>
@@ -2173,13 +2177,13 @@
       </c>
       <c r="N12" s="51" t="n"/>
       <c r="O12" s="29" t="n">
-        <v>-14.7</v>
+        <v>-18.5</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>-1.2</v>
+        <v>-3.2</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>-9.06</v>
+        <v>-12.54</v>
       </c>
       <c r="R12" s="45" t="inlineStr">
         <is>
@@ -2294,13 +2298,13 @@
         </is>
       </c>
       <c r="O13" s="29" t="n">
-        <v>-14</v>
+        <v>-12.9</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>-0.5</v>
+        <v>-3.8</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>-8.59</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="R13" s="45" t="inlineStr">
         <is>
@@ -2411,13 +2415,13 @@
       </c>
       <c r="N14" s="51" t="n"/>
       <c r="O14" s="29" t="n">
-        <v>-6.9</v>
+        <v>-11.1</v>
       </c>
       <c r="P14" s="29" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" s="29" t="n">
-        <v>-3.26</v>
+        <v>-5.56</v>
       </c>
       <c r="R14" s="45" t="n"/>
       <c r="S14" s="21" t="inlineStr">
@@ -2528,13 +2532,13 @@
       </c>
       <c r="N15" s="51" t="n"/>
       <c r="O15" s="29" t="n">
-        <v>-11.2</v>
+        <v>-20.5</v>
       </c>
       <c r="P15" s="29" t="n">
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="Q15" s="29" t="n">
-        <v>-4.99</v>
+        <v>-11.55</v>
       </c>
       <c r="R15" s="45" t="n"/>
       <c r="S15" s="21" t="inlineStr">
@@ -2638,9 +2642,15 @@
         </is>
       </c>
       <c r="N16" s="51" t="n"/>
-      <c r="O16" s="29" t="n"/>
-      <c r="P16" s="29" t="n"/>
-      <c r="Q16" s="29" t="n"/>
+      <c r="O16" s="29" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="P16" s="29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q16" s="29" t="n">
+        <v>-8.99</v>
+      </c>
       <c r="R16" s="45" t="n"/>
       <c r="S16" s="21" t="n"/>
       <c r="T16" s="33" t="n"/>
@@ -2824,9 +2834,7 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O18" s="29" t="n">
-        <v>-21.3</v>
-      </c>
+      <c r="O18" s="29" t="n"/>
       <c r="P18" s="29" t="n"/>
       <c r="Q18" s="29" t="n"/>
       <c r="R18" s="45" t="n"/>
@@ -3016,15 +3024,9 @@
         </is>
       </c>
       <c r="N20" s="51" t="n"/>
-      <c r="O20" s="29" t="n">
-        <v>-21</v>
-      </c>
-      <c r="P20" s="29" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="Q20" s="29" t="n">
-        <v>-12.86</v>
-      </c>
+      <c r="O20" s="29" t="n"/>
+      <c r="P20" s="29" t="n"/>
+      <c r="Q20" s="29" t="n"/>
       <c r="R20" s="45" t="n"/>
       <c r="S20" s="21" t="n"/>
       <c r="T20" s="33" t="n"/>
@@ -4878,9 +4880,15 @@
         </is>
       </c>
       <c r="N40" s="51" t="n"/>
-      <c r="O40" s="29" t="n"/>
-      <c r="P40" s="29" t="n"/>
-      <c r="Q40" s="29" t="n"/>
+      <c r="O40" s="29" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="P40" s="29" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q40" s="29" t="n">
+        <v>-13.61</v>
+      </c>
       <c r="R40" s="45" t="n"/>
       <c r="S40" s="21" t="n"/>
       <c r="T40" s="33" t="n"/>
@@ -10551,13 +10559,13 @@
         </is>
       </c>
       <c r="O102" s="29" t="n">
-        <v>-16.8</v>
+        <v>-2.4</v>
       </c>
       <c r="P102" s="29" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q102" s="29" t="n">
-        <v>-7.93</v>
+        <v>0.6</v>
       </c>
       <c r="R102" s="45" t="inlineStr">
         <is>
@@ -10981,13 +10989,13 @@
         </is>
       </c>
       <c r="O106" s="29" t="n">
-        <v>-3.2</v>
+        <v>-6</v>
       </c>
       <c r="P106" s="29" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="Q106" s="29" t="n">
-        <v>-1.58</v>
+        <v>-2.71</v>
       </c>
       <c r="R106" s="45" t="n"/>
       <c r="S106" s="21" t="inlineStr">
@@ -11103,13 +11111,13 @@
         </is>
       </c>
       <c r="O107" s="29" t="n">
-        <v>-5.3</v>
+        <v>-13.4</v>
       </c>
       <c r="P107" s="29" t="n">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="Q107" s="29" t="n">
-        <v>-1.91</v>
+        <v>-4.24</v>
       </c>
       <c r="R107" s="45" t="n"/>
       <c r="S107" s="21" t="inlineStr">
@@ -11323,13 +11331,13 @@
         </is>
       </c>
       <c r="O109" s="29" t="n">
-        <v>-5.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P109" s="29" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="Q109" s="29" t="n">
-        <v>-1.39</v>
+        <v>-4.66</v>
       </c>
       <c r="R109" s="45" t="n"/>
       <c r="S109" s="21" t="inlineStr">
@@ -11543,13 +11551,13 @@
       </c>
       <c r="N111" s="51" t="n"/>
       <c r="O111" s="29" t="n">
-        <v>-3.2</v>
+        <v>-2</v>
       </c>
       <c r="P111" s="29" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="Q111" s="29" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="R111" s="45" t="n"/>
       <c r="S111" s="21" t="inlineStr">
@@ -11771,13 +11779,13 @@
       </c>
       <c r="N113" s="51" t="n"/>
       <c r="O113" s="29" t="n">
-        <v>-12.6</v>
+        <v>-15</v>
       </c>
       <c r="P113" s="29" t="n">
-        <v>-2.9</v>
+        <v>-5.1</v>
       </c>
       <c r="Q113" s="29" t="n">
-        <v>-8.35</v>
+        <v>-11.33</v>
       </c>
       <c r="R113" s="45" t="inlineStr">
         <is>
@@ -12296,13 +12304,13 @@
       </c>
       <c r="N118" s="51" t="n"/>
       <c r="O118" s="29" t="n">
-        <v>-2.5</v>
+        <v>0.7</v>
       </c>
       <c r="P118" s="29" t="n">
-        <v>9.5</v>
+        <v>13.8</v>
       </c>
       <c r="Q118" s="29" t="n">
-        <v>2.86</v>
+        <v>5.83</v>
       </c>
       <c r="R118" s="45" t="n"/>
       <c r="S118" s="21" t="inlineStr">
@@ -12409,13 +12417,13 @@
       </c>
       <c r="N119" s="51" t="n"/>
       <c r="O119" s="29" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="P119" s="29" t="n">
         <v>16.9</v>
       </c>
       <c r="Q119" s="29" t="n">
-        <v>12.29</v>
+        <v>12.9</v>
       </c>
       <c r="R119" s="45" t="n"/>
       <c r="S119" s="21" t="inlineStr">
@@ -12645,13 +12653,13 @@
       </c>
       <c r="N121" s="51" t="n"/>
       <c r="O121" s="29" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="P121" s="29" t="n">
-        <v>15.9</v>
+        <v>14</v>
       </c>
       <c r="Q121" s="29" t="n">
-        <v>11.24</v>
+        <v>10.75</v>
       </c>
       <c r="R121" s="45" t="n"/>
       <c r="S121" s="21" t="inlineStr">
@@ -12770,13 +12778,13 @@
       </c>
       <c r="N122" s="51" t="n"/>
       <c r="O122" s="29" t="n">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
       <c r="P122" s="29" t="n">
-        <v>16.1</v>
+        <v>13.5</v>
       </c>
       <c r="Q122" s="29" t="n">
-        <v>11.41</v>
+        <v>10.46</v>
       </c>
       <c r="R122" s="45" t="n"/>
       <c r="S122" s="21" t="inlineStr">
@@ -13331,13 +13339,13 @@
       </c>
       <c r="N127" s="51" t="n"/>
       <c r="O127" s="29" t="n">
-        <v>-6</v>
+        <v>-0.7</v>
       </c>
       <c r="P127" s="29" t="n">
-        <v>7.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q127" s="29" t="n">
-        <v>1.17</v>
+        <v>0.95</v>
       </c>
       <c r="R127" s="45" t="n"/>
       <c r="S127" s="21" t="inlineStr">
@@ -13666,13 +13674,13 @@
       </c>
       <c r="N130" s="51" t="n"/>
       <c r="O130" s="29" t="n">
-        <v>-9.199999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="P130" s="29" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q130" s="29" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.62</v>
       </c>
       <c r="R130" s="45" t="n"/>
       <c r="S130" s="21" t="inlineStr">
@@ -14960,13 +14968,13 @@
       </c>
       <c r="N142" s="51" t="n"/>
       <c r="O142" s="29" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P142" s="29" t="n">
-        <v>17.7</v>
+        <v>14.1</v>
       </c>
       <c r="Q142" s="29" t="n">
-        <v>13.14</v>
+        <v>10.95</v>
       </c>
       <c r="R142" s="45" t="n"/>
       <c r="S142" s="21" t="inlineStr">
@@ -15077,13 +15085,13 @@
       </c>
       <c r="N143" s="51" t="n"/>
       <c r="O143" s="29" t="n">
-        <v>-0.7</v>
+        <v>-2.3</v>
       </c>
       <c r="P143" s="29" t="n">
-        <v>4</v>
+        <v>-0.3</v>
       </c>
       <c r="Q143" s="29" t="n">
-        <v>0.79</v>
+        <v>-1.43</v>
       </c>
       <c r="R143" s="45" t="n"/>
       <c r="S143" s="21" t="inlineStr">
@@ -15305,13 +15313,13 @@
       </c>
       <c r="N145" s="51" t="n"/>
       <c r="O145" s="29" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="P145" s="29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q145" s="29" t="n">
-        <v>6.94</v>
+        <v>7.92</v>
       </c>
       <c r="R145" s="45" t="n"/>
       <c r="S145" s="21" t="inlineStr">
@@ -15430,13 +15438,13 @@
       </c>
       <c r="N146" s="51" t="n"/>
       <c r="O146" s="29" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="P146" s="29" t="n">
-        <v>16.5</v>
+        <v>14.9</v>
       </c>
       <c r="Q146" s="29" t="n">
-        <v>11.96</v>
+        <v>12.63</v>
       </c>
       <c r="R146" s="45" t="n"/>
       <c r="S146" s="21" t="inlineStr">
@@ -15543,13 +15551,13 @@
       </c>
       <c r="N147" s="51" t="n"/>
       <c r="O147" s="29" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P147" s="29" t="n">
-        <v>19</v>
+        <v>11.8</v>
       </c>
       <c r="Q147" s="29" t="n">
-        <v>10.28</v>
+        <v>9.59</v>
       </c>
       <c r="R147" s="45" t="n"/>
       <c r="S147" s="21" t="inlineStr">
@@ -15664,13 +15672,13 @@
       </c>
       <c r="N148" s="51" t="n"/>
       <c r="O148" s="29" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
       <c r="P148" s="29" t="n">
-        <v>18.5</v>
+        <v>15.1</v>
       </c>
       <c r="Q148" s="29" t="n">
-        <v>11.6</v>
+        <v>10.41</v>
       </c>
       <c r="R148" s="45" t="n"/>
       <c r="S148" s="21" t="inlineStr">
@@ -15785,13 +15793,13 @@
       </c>
       <c r="N149" s="51" t="n"/>
       <c r="O149" s="29" t="n">
-        <v>-1.7</v>
+        <v>1.9</v>
       </c>
       <c r="P149" s="29" t="n">
-        <v>20.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q149" s="29" t="n">
-        <v>8.119999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="R149" s="45" t="n"/>
       <c r="S149" s="21" t="inlineStr">
@@ -15906,13 +15914,13 @@
       </c>
       <c r="N150" s="51" t="n"/>
       <c r="O150" s="29" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="P150" s="29" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="Q150" s="29" t="n">
-        <v>15.08</v>
+        <v>16.31</v>
       </c>
       <c r="R150" s="45" t="n"/>
       <c r="S150" s="21" t="inlineStr">
@@ -16023,13 +16031,13 @@
       </c>
       <c r="N151" s="51" t="n"/>
       <c r="O151" s="29" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="P151" s="29" t="n">
-        <v>19.9</v>
+        <v>18</v>
       </c>
       <c r="Q151" s="29" t="n">
-        <v>15.65</v>
+        <v>15.69</v>
       </c>
       <c r="R151" s="45" t="n"/>
       <c r="S151" s="21" t="inlineStr">
@@ -16140,13 +16148,13 @@
       </c>
       <c r="N152" s="51" t="n"/>
       <c r="O152" s="29" t="n">
-        <v>6.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P152" s="29" t="n">
-        <v>17.4</v>
+        <v>18.5</v>
       </c>
       <c r="Q152" s="29" t="n">
-        <v>12.05</v>
+        <v>13.08</v>
       </c>
       <c r="R152" s="45" t="n"/>
       <c r="S152" s="21" t="inlineStr">
@@ -16364,13 +16372,13 @@
       </c>
       <c r="N154" s="51" t="n"/>
       <c r="O154" s="29" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="P154" s="29" t="n">
-        <v>16.8</v>
+        <v>22</v>
       </c>
       <c r="Q154" s="29" t="n">
-        <v>14.96</v>
+        <v>17.46</v>
       </c>
       <c r="R154" s="45" t="n"/>
       <c r="S154" s="21" t="inlineStr">
@@ -16481,13 +16489,13 @@
       </c>
       <c r="N155" s="51" t="n"/>
       <c r="O155" s="29" t="n">
-        <v>16.6</v>
+        <v>18.9</v>
       </c>
       <c r="P155" s="29" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="Q155" s="29" t="n">
-        <v>20.66</v>
+        <v>21.25</v>
       </c>
       <c r="R155" s="45" t="n"/>
       <c r="S155" s="21" t="inlineStr">
@@ -16598,13 +16606,13 @@
       </c>
       <c r="N156" s="51" t="n"/>
       <c r="O156" s="29" t="n">
-        <v>15.1</v>
+        <v>12.9</v>
       </c>
       <c r="P156" s="29" t="n">
-        <v>20.2</v>
+        <v>22.8</v>
       </c>
       <c r="Q156" s="29" t="n">
-        <v>17.02</v>
+        <v>17.69</v>
       </c>
       <c r="R156" s="45" t="n"/>
       <c r="S156" s="21" t="inlineStr">
@@ -16715,13 +16723,13 @@
       </c>
       <c r="N157" s="51" t="n"/>
       <c r="O157" s="29" t="n">
-        <v>14.5</v>
+        <v>15.7</v>
       </c>
       <c r="P157" s="29" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q157" s="29" t="n">
-        <v>17.71</v>
+        <v>18.61</v>
       </c>
       <c r="R157" s="45" t="n"/>
       <c r="S157" s="21" t="inlineStr">
@@ -16832,13 +16840,13 @@
       </c>
       <c r="N158" s="51" t="n"/>
       <c r="O158" s="29" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="P158" s="29" t="n">
-        <v>20.4</v>
+        <v>18.7</v>
       </c>
       <c r="Q158" s="29" t="n">
-        <v>18</v>
+        <v>17.44</v>
       </c>
       <c r="R158" s="45" t="n"/>
       <c r="S158" s="21" t="inlineStr">
@@ -17052,13 +17060,13 @@
       </c>
       <c r="N160" s="51" t="n"/>
       <c r="O160" s="29" t="n">
-        <v>20.4</v>
+        <v>23.6</v>
       </c>
       <c r="P160" s="29" t="n">
-        <v>28.6</v>
+        <v>30.2</v>
       </c>
       <c r="Q160" s="29" t="n">
-        <v>24.46</v>
+        <v>26.16</v>
       </c>
       <c r="R160" s="45" t="n"/>
       <c r="S160" s="21" t="inlineStr">
@@ -17169,13 +17177,13 @@
       </c>
       <c r="N161" s="51" t="n"/>
       <c r="O161" s="29" t="n">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="P161" s="29" t="n">
-        <v>31.2</v>
+        <v>30.6</v>
       </c>
       <c r="Q161" s="29" t="n">
-        <v>25.01</v>
+        <v>24.93</v>
       </c>
       <c r="R161" s="45" t="n"/>
       <c r="S161" s="21" t="inlineStr">
@@ -17488,13 +17496,13 @@
       </c>
       <c r="N164" s="51" t="n"/>
       <c r="O164" s="29" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="P164" s="29" t="n">
-        <v>31</v>
+        <v>32.1</v>
       </c>
       <c r="Q164" s="29" t="n">
-        <v>28.17</v>
+        <v>28.24</v>
       </c>
       <c r="R164" s="45" t="n"/>
       <c r="S164" s="21" t="inlineStr">
@@ -17597,13 +17605,13 @@
       </c>
       <c r="N165" s="51" t="n"/>
       <c r="O165" s="29" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="P165" s="29" t="n">
-        <v>33.3</v>
+        <v>32.6</v>
       </c>
       <c r="Q165" s="29" t="n">
-        <v>27.2</v>
+        <v>27.01</v>
       </c>
       <c r="R165" s="45" t="n"/>
       <c r="S165" s="21" t="inlineStr">
@@ -17714,13 +17722,13 @@
       </c>
       <c r="N166" s="51" t="n"/>
       <c r="O166" s="29" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="P166" s="29" t="n">
-        <v>26.9</v>
+        <v>26</v>
       </c>
       <c r="Q166" s="29" t="n">
-        <v>19.52</v>
+        <v>19.1</v>
       </c>
       <c r="R166" s="45" t="n"/>
       <c r="S166" s="21" t="inlineStr">
@@ -17831,13 +17839,13 @@
       </c>
       <c r="N167" s="51" t="n"/>
       <c r="O167" s="29" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="P167" s="29" t="n">
-        <v>17.9</v>
+        <v>18.6</v>
       </c>
       <c r="Q167" s="29" t="n">
-        <v>13.85</v>
+        <v>15.7</v>
       </c>
       <c r="R167" s="45" t="n"/>
       <c r="S167" s="21" t="inlineStr">
@@ -17948,13 +17956,13 @@
       </c>
       <c r="N168" s="51" t="n"/>
       <c r="O168" s="29" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P168" s="29" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="Q168" s="29" t="n">
-        <v>19.2</v>
+        <v>19.93</v>
       </c>
       <c r="R168" s="45" t="n"/>
       <c r="S168" s="21" t="inlineStr">
@@ -18156,13 +18164,13 @@
       </c>
       <c r="N170" s="51" t="n"/>
       <c r="O170" s="29" t="n">
-        <v>12.8</v>
+        <v>15.9</v>
       </c>
       <c r="P170" s="29" t="n">
-        <v>18.6</v>
+        <v>19.3</v>
       </c>
       <c r="Q170" s="29" t="n">
-        <v>15.82</v>
+        <v>17.14</v>
       </c>
       <c r="R170" s="45" t="n"/>
       <c r="S170" s="21" t="inlineStr">
@@ -18277,13 +18285,13 @@
       </c>
       <c r="N171" s="51" t="n"/>
       <c r="O171" s="29" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="P171" s="29" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="Q171" s="29" t="n">
-        <v>8.26</v>
+        <v>7.96</v>
       </c>
       <c r="R171" s="45" t="n"/>
       <c r="S171" s="21" t="inlineStr">
@@ -18869,12 +18877,14 @@
       </c>
       <c r="N177" s="51" t="n"/>
       <c r="O177" s="29" t="n">
-        <v>-8.699999999999999</v>
+        <v>-7.9</v>
       </c>
       <c r="P177" s="29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Q177" s="29" t="n"/>
+        <v>5.2</v>
+      </c>
+      <c r="Q177" s="29" t="n">
+        <v>-1.11</v>
+      </c>
       <c r="R177" s="45" t="n"/>
       <c r="S177" s="21" t="inlineStr">
         <is>
@@ -18980,13 +18990,13 @@
       </c>
       <c r="N178" s="51" t="n"/>
       <c r="O178" s="29" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9</v>
       </c>
       <c r="P178" s="29" t="n">
         <v>6</v>
       </c>
       <c r="Q178" s="29" t="n">
-        <v>-2.03</v>
+        <v>-2.25</v>
       </c>
       <c r="R178" s="45" t="n"/>
       <c r="S178" s="21" t="inlineStr">
@@ -19095,13 +19105,13 @@
       </c>
       <c r="N179" s="51" t="n"/>
       <c r="O179" s="29" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="P179" s="29" t="n">
-        <v>18.3</v>
+        <v>19.3</v>
       </c>
       <c r="Q179" s="29" t="n">
-        <v>12.73</v>
+        <v>13.38</v>
       </c>
       <c r="R179" s="45" t="n"/>
       <c r="S179" s="21" t="inlineStr">
@@ -19200,13 +19210,13 @@
       </c>
       <c r="N180" s="51" t="n"/>
       <c r="O180" s="29" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P180" s="29" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="Q180" s="29" t="n">
-        <v>19.29</v>
+        <v>19.7</v>
       </c>
       <c r="R180" s="45" t="n"/>
       <c r="S180" s="21" t="inlineStr">
@@ -19309,13 +19319,13 @@
       </c>
       <c r="N181" s="51" t="n"/>
       <c r="O181" s="29" t="n">
-        <v>3.8</v>
+        <v>9.1</v>
       </c>
       <c r="P181" s="29" t="n">
-        <v>21.3</v>
+        <v>14</v>
       </c>
       <c r="Q181" s="29" t="n">
-        <v>10.74</v>
+        <v>10.55</v>
       </c>
       <c r="R181" s="45" t="n"/>
       <c r="S181" s="21" t="inlineStr">
@@ -19553,13 +19563,13 @@
         </is>
       </c>
       <c r="O183" s="29" t="n">
-        <v>-11.1</v>
+        <v>-9.9</v>
       </c>
       <c r="P183" s="29" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q183" s="29" t="n">
-        <v>-4.88</v>
+        <v>-4.58</v>
       </c>
       <c r="R183" s="45" t="n"/>
       <c r="S183" s="21" t="inlineStr">
@@ -19674,13 +19684,13 @@
       </c>
       <c r="N184" s="51" t="n"/>
       <c r="O184" s="29" t="n">
-        <v>-8.5</v>
+        <v>-14</v>
       </c>
       <c r="P184" s="29" t="n">
-        <v>-2.5</v>
+        <v>-6.8</v>
       </c>
       <c r="Q184" s="29" t="n">
-        <v>-5.05</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="R184" s="45" t="n"/>
       <c r="S184" s="21" t="inlineStr">
@@ -19795,13 +19805,13 @@
       </c>
       <c r="N185" s="51" t="n"/>
       <c r="O185" s="29" t="n">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P185" s="29" t="n">
-        <v>17.1</v>
+        <v>15</v>
       </c>
       <c r="Q185" s="29" t="n">
-        <v>11.7</v>
+        <v>12.16</v>
       </c>
       <c r="R185" s="45" t="n"/>
       <c r="S185" s="21" t="inlineStr">
@@ -19908,13 +19918,13 @@
       </c>
       <c r="N186" s="51" t="n"/>
       <c r="O186" s="29" t="n">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="P186" s="29" t="n">
-        <v>20.9</v>
+        <v>23.7</v>
       </c>
       <c r="Q186" s="29" t="n">
-        <v>17.01</v>
+        <v>18.26</v>
       </c>
       <c r="R186" s="45" t="n"/>
       <c r="S186" s="21" t="inlineStr">
@@ -20025,7 +20035,7 @@
       </c>
       <c r="N187" s="51" t="n"/>
       <c r="O187" s="29" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="P187" s="29" t="n">
         <v>36.3</v>
@@ -20138,13 +20148,13 @@
       </c>
       <c r="N188" s="51" t="n"/>
       <c r="O188" s="29" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="P188" s="29" t="n">
-        <v>18.6</v>
+        <v>14.5</v>
       </c>
       <c r="Q188" s="29" t="n">
-        <v>14.31</v>
+        <v>12.2</v>
       </c>
       <c r="R188" s="45" t="n"/>
       <c r="S188" s="21" t="inlineStr">
@@ -20342,13 +20352,13 @@
         </is>
       </c>
       <c r="O190" s="29" t="n">
-        <v>-18.5</v>
+        <v>-17.9</v>
       </c>
       <c r="P190" s="29" t="n">
-        <v>-3.9</v>
+        <v>-7.2</v>
       </c>
       <c r="Q190" s="29" t="n">
-        <v>-10.3</v>
+        <v>-12.8</v>
       </c>
       <c r="R190" s="45" t="n"/>
       <c r="S190" s="21" t="n"/>
@@ -20748,12 +20758,14 @@
         </is>
       </c>
       <c r="O194" s="29" t="n">
-        <v>-3.9</v>
+        <v>-2.7</v>
       </c>
       <c r="P194" s="29" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="Q194" s="29" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="Q194" s="29" t="n">
+        <v>2.63</v>
+      </c>
       <c r="R194" s="45" t="inlineStr">
         <is>
           <t>2010-01-05</t>
@@ -20855,10 +20867,10 @@
       </c>
       <c r="N195" s="51" t="n"/>
       <c r="O195" s="29" t="n">
-        <v>-0.7</v>
+        <v>0.3</v>
       </c>
       <c r="P195" s="29" t="n">
-        <v>18</v>
+        <v>16.1</v>
       </c>
       <c r="Q195" s="29" t="n"/>
       <c r="R195" s="45" t="n"/>
@@ -20962,12 +20974,14 @@
         </is>
       </c>
       <c r="O196" s="29" t="n">
-        <v>-11</v>
+        <v>-20.1</v>
       </c>
       <c r="P196" s="29" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="Q196" s="29" t="n"/>
+        <v>-6.6</v>
+      </c>
+      <c r="Q196" s="29" t="n">
+        <v>-12.2</v>
+      </c>
       <c r="R196" s="45" t="n"/>
       <c r="S196" s="21" t="n"/>
       <c r="T196" s="33" t="n"/>
@@ -21073,12 +21087,14 @@
         </is>
       </c>
       <c r="O197" s="29" t="n">
-        <v>-4.2</v>
+        <v>-1.9</v>
       </c>
       <c r="P197" s="29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q197" s="29" t="n"/>
+        <v>5.8</v>
+      </c>
+      <c r="Q197" s="29" t="n">
+        <v>1.31</v>
+      </c>
       <c r="R197" s="45" t="n"/>
       <c r="S197" s="21" t="n"/>
       <c r="T197" s="33" t="inlineStr">
@@ -21973,8 +21989,12 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="O206" s="29" t="n"/>
-      <c r="P206" s="29" t="n"/>
+      <c r="O206" s="29" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="P206" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="Q206" s="29" t="n"/>
       <c r="R206" s="45" t="n"/>
       <c r="S206" s="21" t="n"/>
@@ -22184,10 +22204,10 @@
         </is>
       </c>
       <c r="O208" s="29" t="n">
-        <v>-7.9</v>
+        <v>-1.7</v>
       </c>
       <c r="P208" s="29" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q208" s="29" t="n"/>
       <c r="R208" s="45" t="inlineStr">
@@ -22493,13 +22513,13 @@
         </is>
       </c>
       <c r="O211" s="29" t="n">
-        <v>-18.8</v>
+        <v>-33.1</v>
       </c>
       <c r="P211" s="29" t="n">
-        <v>-9.300000000000001</v>
+        <v>-13.3</v>
       </c>
       <c r="Q211" s="29" t="n">
-        <v>-14.6</v>
+        <v>-24.1</v>
       </c>
       <c r="R211" s="45" t="n"/>
       <c r="S211" s="21" t="n"/>
@@ -22713,12 +22733,14 @@
       </c>
       <c r="N213" s="51" t="n"/>
       <c r="O213" s="29" t="n">
-        <v>-10.1</v>
+        <v>-20.2</v>
       </c>
       <c r="P213" s="29" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="Q213" s="29" t="n"/>
+        <v>-7.2</v>
+      </c>
+      <c r="Q213" s="29" t="n">
+        <v>-12.8</v>
+      </c>
       <c r="R213" s="45" t="n"/>
       <c r="S213" s="21" t="n"/>
       <c r="T213" s="33" t="n"/>
@@ -22821,9 +22843,7 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O214" s="29" t="n">
-        <v>-46.8</v>
-      </c>
+      <c r="O214" s="29" t="n"/>
       <c r="P214" s="29" t="n"/>
       <c r="Q214" s="29" t="n"/>
       <c r="R214" s="45" t="n"/>
@@ -22914,7 +22934,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O215" s="29" t="n"/>
+      <c r="O215" s="29" t="n">
+        <v>-39.4</v>
+      </c>
       <c r="P215" s="29" t="n"/>
       <c r="Q215" s="29" t="n"/>
       <c r="R215" s="45" t="n"/>
@@ -23685,13 +23707,13 @@
       </c>
       <c r="N223" s="51" t="n"/>
       <c r="O223" s="29" t="n">
-        <v>5.5</v>
+        <v>10.7</v>
       </c>
       <c r="P223" s="29" t="n">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="Q223" s="29" t="n">
-        <v>8.93</v>
+        <v>13.05</v>
       </c>
       <c r="R223" s="45" t="n"/>
       <c r="S223" s="21" t="inlineStr">
@@ -24089,13 +24111,13 @@
       </c>
       <c r="N227" s="51" t="n"/>
       <c r="O227" s="29" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="P227" s="29" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q227" s="29" t="n">
-        <v>0.93</v>
+        <v>-1.2</v>
       </c>
       <c r="R227" s="45" t="n"/>
       <c r="S227" s="21" t="inlineStr">
@@ -24299,13 +24321,13 @@
       </c>
       <c r="N229" s="51" t="n"/>
       <c r="O229" s="29" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="P229" s="29" t="n">
         <v>-2.3</v>
       </c>
-      <c r="P229" s="29" t="n">
-        <v>0.3</v>
-      </c>
       <c r="Q229" s="29" t="n">
-        <v>-1.44</v>
+        <v>-3.95</v>
       </c>
       <c r="R229" s="45" t="n"/>
       <c r="S229" s="21" t="inlineStr">
@@ -24705,13 +24727,13 @@
       </c>
       <c r="N233" s="51" t="n"/>
       <c r="O233" s="29" t="n">
-        <v>-2.6</v>
+        <v>-3.4</v>
       </c>
       <c r="P233" s="29" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="Q233" s="29" t="n">
-        <v>-0.15</v>
+        <v>-1.14</v>
       </c>
       <c r="R233" s="45" t="n"/>
       <c r="S233" s="21" t="inlineStr">
@@ -25299,13 +25321,13 @@
       </c>
       <c r="N239" s="51" t="n"/>
       <c r="O239" s="29" t="n">
-        <v>-1.8</v>
+        <v>-3</v>
       </c>
       <c r="P239" s="29" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q239" s="29" t="n">
-        <v>-0.78</v>
+        <v>-1.59</v>
       </c>
       <c r="R239" s="45" t="n"/>
       <c r="S239" s="21" t="inlineStr">
@@ -25412,13 +25434,13 @@
       </c>
       <c r="N240" s="51" t="n"/>
       <c r="O240" s="29" t="n">
-        <v>-2</v>
+        <v>-1.6</v>
       </c>
       <c r="P240" s="29" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q240" s="29" t="n">
-        <v>0.97</v>
+        <v>-0.49</v>
       </c>
       <c r="R240" s="45" t="n"/>
       <c r="S240" s="21" t="inlineStr">
@@ -26390,7 +26412,7 @@
         </is>
       </c>
       <c r="O250" s="29" t="n">
-        <v>-6.2</v>
+        <v>-19.9</v>
       </c>
       <c r="P250" s="29" t="n">
         <v>-1</v>
@@ -29132,13 +29154,13 @@
         </is>
       </c>
       <c r="O279" s="29" t="n">
-        <v>-26.8</v>
+        <v>-23.3</v>
       </c>
       <c r="P279" s="29" t="n">
-        <v>-12.5</v>
+        <v>-12.9</v>
       </c>
       <c r="Q279" s="29" t="n">
-        <v>-19.54</v>
+        <v>-16.36</v>
       </c>
       <c r="R279" s="45" t="n"/>
       <c r="S279" s="21" t="inlineStr">
@@ -29634,11 +29656,9 @@
         </is>
       </c>
       <c r="O284" s="29" t="n">
-        <v>-19.8</v>
-      </c>
-      <c r="P284" s="29" t="n">
-        <v>-1.7</v>
-      </c>
+        <v>-15.5</v>
+      </c>
+      <c r="P284" s="29" t="n"/>
       <c r="Q284" s="29" t="n"/>
       <c r="R284" s="45" t="n"/>
       <c r="S284" s="21" t="inlineStr">
@@ -30019,7 +30039,7 @@
         </is>
       </c>
       <c r="O288" s="29" t="n">
-        <v>-60.3</v>
+        <v>-62.4</v>
       </c>
       <c r="P288" s="29" t="n">
         <v>-48.4</v>
@@ -30215,13 +30235,13 @@
       </c>
       <c r="N290" s="51" t="n"/>
       <c r="O290" s="29" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="P290" s="29" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q290" s="29" t="n">
-        <v>0.88</v>
+        <v>-0.68</v>
       </c>
       <c r="R290" s="45" t="n"/>
       <c r="S290" s="21" t="inlineStr">
@@ -30431,13 +30451,13 @@
         </is>
       </c>
       <c r="O292" s="29" t="n">
-        <v>-1.9</v>
+        <v>-1.7</v>
       </c>
       <c r="P292" s="29" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q292" s="29" t="n">
-        <v>0.21</v>
+        <v>1.43</v>
       </c>
       <c r="R292" s="45" t="n"/>
       <c r="S292" s="21" t="inlineStr">
@@ -35246,12 +35266,8 @@
         </is>
       </c>
       <c r="N342" s="51" t="n"/>
-      <c r="O342" s="29" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="P342" s="29" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="O342" s="29" t="n"/>
+      <c r="P342" s="29" t="n"/>
       <c r="Q342" s="29" t="n"/>
       <c r="R342" s="45" t="n"/>
       <c r="S342" s="21" t="n"/>
@@ -37223,15 +37239,9 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="O363" s="29" t="n">
-        <v>-12.1</v>
-      </c>
-      <c r="P363" s="29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q363" s="29" t="n">
-        <v>-4.05</v>
-      </c>
+      <c r="O363" s="29" t="n"/>
+      <c r="P363" s="29" t="n"/>
+      <c r="Q363" s="29" t="n"/>
       <c r="R363" s="45" t="n"/>
       <c r="S363" s="21" t="n"/>
       <c r="T363" s="33" t="n"/>
@@ -38630,13 +38640,13 @@
       </c>
       <c r="N377" s="51" t="n"/>
       <c r="O377" s="29" t="n">
-        <v>-27.7</v>
+        <v>-26.3</v>
       </c>
       <c r="P377" s="29" t="n">
-        <v>2</v>
+        <v>-1.4</v>
       </c>
       <c r="Q377" s="29" t="n">
-        <v>-16.8</v>
+        <v>-16.2</v>
       </c>
       <c r="R377" s="45" t="n"/>
       <c r="S377" s="21" t="n"/>
@@ -39715,13 +39725,13 @@
       </c>
       <c r="N388" s="51" t="n"/>
       <c r="O388" s="29" t="n">
-        <v>-16.6</v>
+        <v>-19.3</v>
       </c>
       <c r="P388" s="29" t="n">
-        <v>-14</v>
+        <v>-12.5</v>
       </c>
       <c r="Q388" s="29" t="n">
-        <v>-15.4</v>
+        <v>-16.8</v>
       </c>
       <c r="R388" s="45" t="n"/>
       <c r="S388" s="21" t="n"/>
@@ -39824,13 +39834,13 @@
       </c>
       <c r="N389" s="51" t="n"/>
       <c r="O389" s="29" t="n">
-        <v>-16.9</v>
+        <v>-22.4</v>
       </c>
       <c r="P389" s="29" t="n">
-        <v>-13.1</v>
+        <v>-16.2</v>
       </c>
       <c r="Q389" s="29" t="n">
-        <v>-15.3</v>
+        <v>-18.9</v>
       </c>
       <c r="R389" s="45" t="n"/>
       <c r="S389" s="21" t="n"/>
@@ -40994,13 +41004,13 @@
       </c>
       <c r="N401" s="51" t="n"/>
       <c r="O401" s="29" t="n">
-        <v>-11.9</v>
+        <v>-16.7</v>
       </c>
       <c r="P401" s="29" t="n">
-        <v>-5</v>
+        <v>-10.6</v>
       </c>
       <c r="Q401" s="29" t="n">
-        <v>-10.09</v>
+        <v>-14.59</v>
       </c>
       <c r="R401" s="45" t="n"/>
       <c r="S401" s="21" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -830,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="7" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="4" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="7" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="4" min="34" max="790"/>
-    <col width="12.59765625" customWidth="1" style="4" min="791" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="4" min="34" max="791"/>
+    <col width="12.59765625" customWidth="1" style="4" min="792" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="10">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="29" t="n">
-        <v>-10.9</v>
+        <v>-10.6</v>
       </c>
       <c r="P2" s="29" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q2" s="29" t="n">
-        <v>-4.7</v>
+        <v>-3.5</v>
       </c>
       <c r="R2" s="45" t="n"/>
       <c r="S2" s="21" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="29" t="n">
-        <v>-11.8</v>
+        <v>-11</v>
       </c>
       <c r="P3" s="29" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" s="29" t="n"/>
       <c r="R3" s="45" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="29" t="n">
-        <v>-21.1</v>
+        <v>-18.3</v>
       </c>
       <c r="P4" s="29" t="n">
-        <v>-6.6</v>
+        <v>-3.2</v>
       </c>
       <c r="Q4" s="29" t="n"/>
       <c r="R4" s="45" t="inlineStr">
@@ -1381,12 +1381,8 @@
         </is>
       </c>
       <c r="N5" s="51" t="n"/>
-      <c r="O5" s="29" t="n">
-        <v>-20</v>
-      </c>
-      <c r="P5" s="29" t="n">
-        <v>-4.8</v>
-      </c>
+      <c r="O5" s="29" t="n"/>
+      <c r="P5" s="29" t="n"/>
       <c r="Q5" s="29" t="n"/>
       <c r="R5" s="45" t="n"/>
       <c r="S5" s="21" t="n"/>
@@ -1489,13 +1485,13 @@
         </is>
       </c>
       <c r="O6" s="29" t="n">
-        <v>-24</v>
+        <v>-19.8</v>
       </c>
       <c r="P6" s="29" t="n">
-        <v>-10.2</v>
+        <v>-6.1</v>
       </c>
       <c r="Q6" s="29" t="n">
-        <v>-17.93</v>
+        <v>-12.01</v>
       </c>
       <c r="R6" s="47" t="inlineStr">
         <is>
@@ -1600,10 +1596,10 @@
         </is>
       </c>
       <c r="O7" s="29" t="n">
-        <v>-15.8</v>
+        <v>-12.3</v>
       </c>
       <c r="P7" s="29" t="n">
-        <v>-4.9</v>
+        <v>-5</v>
       </c>
       <c r="Q7" s="29" t="n"/>
       <c r="R7" s="45" t="n"/>
@@ -1709,13 +1705,13 @@
       </c>
       <c r="N8" s="51" t="n"/>
       <c r="O8" s="29" t="n">
-        <v>-10.1</v>
+        <v>-4.8</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>-4.01</v>
+        <v>-3.01</v>
       </c>
       <c r="R8" s="45" t="n"/>
       <c r="S8" s="21" t="inlineStr">
@@ -1822,13 +1818,13 @@
       </c>
       <c r="N9" s="51" t="n"/>
       <c r="O9" s="29" t="n">
-        <v>-9.1</v>
+        <v>-7.8</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>-2.86</v>
+        <v>-2.91</v>
       </c>
       <c r="R9" s="45" t="n"/>
       <c r="S9" s="21" t="inlineStr">
@@ -1943,13 +1939,13 @@
         </is>
       </c>
       <c r="O10" s="29" t="n">
-        <v>-20.5</v>
+        <v>-13.4</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>-3</v>
+        <v>-4.2</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>-10.73</v>
+        <v>-8.16</v>
       </c>
       <c r="R10" s="45" t="n"/>
       <c r="S10" s="21" t="inlineStr">
@@ -2060,13 +2056,13 @@
         </is>
       </c>
       <c r="O11" s="29" t="n">
-        <v>-24.7</v>
+        <v>-15.1</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>-7.5</v>
+        <v>-7</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>-15.45</v>
+        <v>-10.9</v>
       </c>
       <c r="R11" s="45" t="inlineStr">
         <is>
@@ -2177,13 +2173,13 @@
       </c>
       <c r="N12" s="51" t="n"/>
       <c r="O12" s="29" t="n">
-        <v>-19.6</v>
+        <v>-10.4</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>-4.6</v>
+        <v>-4.3</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>-12.43</v>
+        <v>-7.34</v>
       </c>
       <c r="R12" s="45" t="inlineStr">
         <is>
@@ -2298,13 +2294,13 @@
         </is>
       </c>
       <c r="O13" s="29" t="n">
-        <v>-16.2</v>
+        <v>-18</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>-3.9</v>
+        <v>-5</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>-11.2</v>
+        <v>-10.41</v>
       </c>
       <c r="R13" s="45" t="inlineStr">
         <is>
@@ -2415,13 +2411,13 @@
       </c>
       <c r="N14" s="51" t="n"/>
       <c r="O14" s="29" t="n">
-        <v>-10.7</v>
+        <v>-8.6</v>
       </c>
       <c r="P14" s="29" t="n">
-        <v>0.3</v>
+        <v>-3.2</v>
       </c>
       <c r="Q14" s="29" t="n">
-        <v>-5.44</v>
+        <v>-6.1</v>
       </c>
       <c r="R14" s="45" t="n"/>
       <c r="S14" s="21" t="inlineStr">
@@ -2532,13 +2528,13 @@
       </c>
       <c r="N15" s="51" t="n"/>
       <c r="O15" s="29" t="n">
-        <v>-19.4</v>
+        <v>-9.1</v>
       </c>
       <c r="P15" s="29" t="n">
-        <v>-2.7</v>
+        <v>-4.5</v>
       </c>
       <c r="Q15" s="29" t="n">
-        <v>-10.46</v>
+        <v>-7.08</v>
       </c>
       <c r="R15" s="45" t="n"/>
       <c r="S15" s="21" t="inlineStr">
@@ -2643,13 +2639,13 @@
       </c>
       <c r="N16" s="51" t="n"/>
       <c r="O16" s="29" t="n">
-        <v>-15.5</v>
+        <v>-13.2</v>
       </c>
       <c r="P16" s="29" t="n">
-        <v>1.1</v>
+        <v>-2.5</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>-6.99</v>
+        <v>-6.54</v>
       </c>
       <c r="R16" s="45" t="n"/>
       <c r="S16" s="21" t="n"/>
@@ -2834,9 +2830,7 @@
           <t>🧊</t>
         </is>
       </c>
-      <c r="O18" s="29" t="n">
-        <v>-25.7</v>
-      </c>
+      <c r="O18" s="29" t="n"/>
       <c r="P18" s="29" t="n"/>
       <c r="Q18" s="29" t="n"/>
       <c r="R18" s="45" t="n"/>
@@ -2925,9 +2919,15 @@
         </is>
       </c>
       <c r="N19" s="51" t="n"/>
-      <c r="O19" s="29" t="n"/>
-      <c r="P19" s="29" t="n"/>
-      <c r="Q19" s="29" t="n"/>
+      <c r="O19" s="29" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="P19" s="29" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Q19" s="29" t="n">
+        <v>-10.96</v>
+      </c>
       <c r="R19" s="45" t="n"/>
       <c r="S19" s="21" t="n"/>
       <c r="T19" s="33" t="n"/>
@@ -4314,8 +4314,12 @@
         </is>
       </c>
       <c r="N34" s="51" t="n"/>
-      <c r="O34" s="29" t="n"/>
-      <c r="P34" s="29" t="n"/>
+      <c r="O34" s="29" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="P34" s="29" t="n">
+        <v>-2.2</v>
+      </c>
       <c r="Q34" s="29" t="n"/>
       <c r="R34" s="45" t="n"/>
       <c r="S34" s="21" t="n"/>
@@ -4783,8 +4787,12 @@
         </is>
       </c>
       <c r="N39" s="51" t="n"/>
-      <c r="O39" s="29" t="n"/>
-      <c r="P39" s="29" t="n"/>
+      <c r="O39" s="29" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="P39" s="29" t="n">
+        <v>-9.199999999999999</v>
+      </c>
       <c r="Q39" s="29" t="n"/>
       <c r="R39" s="45" t="n"/>
       <c r="S39" s="21" t="n"/>
@@ -10555,13 +10563,13 @@
         </is>
       </c>
       <c r="O102" s="29" t="n">
-        <v>-6.6</v>
+        <v>-10.9</v>
       </c>
       <c r="P102" s="29" t="n">
-        <v>-2.2</v>
+        <v>-4.3</v>
       </c>
       <c r="Q102" s="29" t="n">
-        <v>-4.06</v>
+        <v>-7.82</v>
       </c>
       <c r="R102" s="45" t="inlineStr">
         <is>
@@ -10985,13 +10993,13 @@
         </is>
       </c>
       <c r="O106" s="29" t="n">
-        <v>-18.6</v>
+        <v>-18.3</v>
       </c>
       <c r="P106" s="29" t="n">
-        <v>-1.8</v>
+        <v>-3.6</v>
       </c>
       <c r="Q106" s="29" t="n">
-        <v>-9.5</v>
+        <v>-10.64</v>
       </c>
       <c r="R106" s="45" t="n"/>
       <c r="S106" s="21" t="inlineStr">
@@ -11107,13 +11115,13 @@
         </is>
       </c>
       <c r="O107" s="29" t="n">
-        <v>-19</v>
+        <v>-16.6</v>
       </c>
       <c r="P107" s="29" t="n">
-        <v>-2.9</v>
+        <v>-3.6</v>
       </c>
       <c r="Q107" s="29" t="n">
-        <v>-10.84</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="R107" s="45" t="n"/>
       <c r="S107" s="21" t="inlineStr">
@@ -11327,13 +11335,13 @@
         </is>
       </c>
       <c r="O109" s="29" t="n">
-        <v>-7.8</v>
+        <v>-7.5</v>
       </c>
       <c r="P109" s="29" t="n">
-        <v>0</v>
+        <v>-4.4</v>
       </c>
       <c r="Q109" s="29" t="n">
-        <v>-4.64</v>
+        <v>-5.8</v>
       </c>
       <c r="R109" s="45" t="n"/>
       <c r="S109" s="21" t="inlineStr">
@@ -11547,13 +11555,13 @@
       </c>
       <c r="N111" s="51" t="n"/>
       <c r="O111" s="29" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9.4</v>
       </c>
       <c r="P111" s="29" t="n">
-        <v>-0.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q111" s="29" t="n">
-        <v>-4.24</v>
+        <v>-4.38</v>
       </c>
       <c r="R111" s="45" t="n"/>
       <c r="S111" s="21" t="inlineStr">
@@ -11775,13 +11783,13 @@
       </c>
       <c r="N113" s="51" t="n"/>
       <c r="O113" s="29" t="n">
-        <v>-19.4</v>
+        <v>-18.1</v>
       </c>
       <c r="P113" s="29" t="n">
-        <v>-7.6</v>
+        <v>-6.7</v>
       </c>
       <c r="Q113" s="29" t="n">
-        <v>-13</v>
+        <v>-12.75</v>
       </c>
       <c r="R113" s="45" t="inlineStr">
         <is>
@@ -12300,13 +12308,13 @@
       </c>
       <c r="N118" s="51" t="n"/>
       <c r="O118" s="29" t="n">
-        <v>-2.3</v>
+        <v>-3.1</v>
       </c>
       <c r="P118" s="29" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q118" s="29" t="n">
-        <v>2.21</v>
+        <v>1.51</v>
       </c>
       <c r="R118" s="45" t="n"/>
       <c r="S118" s="21" t="inlineStr">
@@ -12413,13 +12421,13 @@
       </c>
       <c r="N119" s="51" t="n"/>
       <c r="O119" s="29" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="P119" s="29" t="n">
-        <v>17.1</v>
+        <v>14.1</v>
       </c>
       <c r="Q119" s="29" t="n">
-        <v>10.85</v>
+        <v>9.82</v>
       </c>
       <c r="R119" s="45" t="n"/>
       <c r="S119" s="21" t="inlineStr">
@@ -12649,13 +12657,13 @@
       </c>
       <c r="N121" s="51" t="n"/>
       <c r="O121" s="29" t="n">
-        <v>-2.3</v>
+        <v>1.1</v>
       </c>
       <c r="P121" s="29" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="Q121" s="29" t="n">
-        <v>5.76</v>
+        <v>6.5</v>
       </c>
       <c r="R121" s="45" t="n"/>
       <c r="S121" s="21" t="inlineStr">
@@ -12774,13 +12782,13 @@
       </c>
       <c r="N122" s="51" t="n"/>
       <c r="O122" s="29" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="P122" s="29" t="n">
-        <v>12.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q122" s="29" t="n">
-        <v>5.22</v>
+        <v>5.49</v>
       </c>
       <c r="R122" s="45" t="n"/>
       <c r="S122" s="21" t="inlineStr">
@@ -13335,13 +13343,13 @@
       </c>
       <c r="N127" s="51" t="n"/>
       <c r="O127" s="29" t="n">
-        <v>-6.7</v>
+        <v>-9.6</v>
       </c>
       <c r="P127" s="29" t="n">
-        <v>2.3</v>
+        <v>-0.6</v>
       </c>
       <c r="Q127" s="29" t="n">
-        <v>-2.24</v>
+        <v>-5.1</v>
       </c>
       <c r="R127" s="45" t="n"/>
       <c r="S127" s="21" t="inlineStr">
@@ -13554,9 +13562,15 @@
         </is>
       </c>
       <c r="N129" s="51" t="n"/>
-      <c r="O129" s="29" t="n"/>
-      <c r="P129" s="29" t="n"/>
-      <c r="Q129" s="29" t="n"/>
+      <c r="O129" s="29" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="P129" s="29" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="Q129" s="29" t="n">
+        <v>-9.35</v>
+      </c>
       <c r="R129" s="45" t="n"/>
       <c r="S129" s="21" t="n"/>
       <c r="T129" s="33" t="inlineStr">
@@ -13670,13 +13684,13 @@
       </c>
       <c r="N130" s="51" t="n"/>
       <c r="O130" s="29" t="n">
-        <v>-14.9</v>
+        <v>-18.9</v>
       </c>
       <c r="P130" s="29" t="n">
-        <v>0.3</v>
+        <v>-1.6</v>
       </c>
       <c r="Q130" s="29" t="n">
-        <v>-4.25</v>
+        <v>-8.9</v>
       </c>
       <c r="R130" s="45" t="n"/>
       <c r="S130" s="21" t="inlineStr">
@@ -14733,9 +14747,15 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O140" s="29" t="n"/>
-      <c r="P140" s="29" t="n"/>
-      <c r="Q140" s="29" t="n"/>
+      <c r="O140" s="29" t="n">
+        <v>-14</v>
+      </c>
+      <c r="P140" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q140" s="29" t="n">
+        <v>-7.83</v>
+      </c>
       <c r="R140" s="45" t="n"/>
       <c r="S140" s="21" t="n"/>
       <c r="T140" s="33" t="n"/>
@@ -14964,13 +14984,13 @@
       </c>
       <c r="N142" s="51" t="n"/>
       <c r="O142" s="29" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="P142" s="29" t="n">
-        <v>15.2</v>
+        <v>11.5</v>
       </c>
       <c r="Q142" s="29" t="n">
-        <v>9.720000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="R142" s="45" t="n"/>
       <c r="S142" s="21" t="inlineStr">
@@ -15081,13 +15101,13 @@
       </c>
       <c r="N143" s="51" t="n"/>
       <c r="O143" s="29" t="n">
-        <v>-3.9</v>
+        <v>-5.9</v>
       </c>
       <c r="P143" s="29" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q143" s="29" t="n">
-        <v>-1.8</v>
+        <v>-2.06</v>
       </c>
       <c r="R143" s="45" t="n"/>
       <c r="S143" s="21" t="inlineStr">
@@ -15309,13 +15329,13 @@
       </c>
       <c r="N145" s="51" t="n"/>
       <c r="O145" s="29" t="n">
-        <v>5.2</v>
+        <v>-0.3</v>
       </c>
       <c r="P145" s="29" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="Q145" s="29" t="n">
-        <v>6.94</v>
+        <v>4.11</v>
       </c>
       <c r="R145" s="45" t="n"/>
       <c r="S145" s="21" t="inlineStr">
@@ -15434,13 +15454,13 @@
       </c>
       <c r="N146" s="51" t="n"/>
       <c r="O146" s="29" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P146" s="29" t="n">
-        <v>13.7</v>
+        <v>19</v>
       </c>
       <c r="Q146" s="29" t="n">
-        <v>12.41</v>
+        <v>13</v>
       </c>
       <c r="R146" s="45" t="n"/>
       <c r="S146" s="21" t="inlineStr">
@@ -15547,13 +15567,13 @@
       </c>
       <c r="N147" s="51" t="n"/>
       <c r="O147" s="29" t="n">
-        <v>6.3</v>
+        <v>2.6</v>
       </c>
       <c r="P147" s="29" t="n">
-        <v>9.9</v>
+        <v>12.4</v>
       </c>
       <c r="Q147" s="29" t="n">
-        <v>7.78</v>
+        <v>7.46</v>
       </c>
       <c r="R147" s="45" t="n"/>
       <c r="S147" s="21" t="inlineStr">
@@ -15668,13 +15688,13 @@
       </c>
       <c r="N148" s="51" t="n"/>
       <c r="O148" s="29" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="P148" s="29" t="n">
-        <v>12.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q148" s="29" t="n">
-        <v>11.24</v>
+        <v>12.4</v>
       </c>
       <c r="R148" s="45" t="n"/>
       <c r="S148" s="21" t="inlineStr">
@@ -15789,13 +15809,13 @@
       </c>
       <c r="N149" s="51" t="n"/>
       <c r="O149" s="29" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="P149" s="29" t="n">
-        <v>12.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q149" s="29" t="n">
-        <v>5.05</v>
+        <v>4.48</v>
       </c>
       <c r="R149" s="45" t="n"/>
       <c r="S149" s="21" t="inlineStr">
@@ -15910,13 +15930,13 @@
       </c>
       <c r="N150" s="51" t="n"/>
       <c r="O150" s="29" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="P150" s="29" t="n">
-        <v>23.5</v>
+        <v>17.7</v>
       </c>
       <c r="Q150" s="29" t="n">
-        <v>17.84</v>
+        <v>13.61</v>
       </c>
       <c r="R150" s="45" t="n"/>
       <c r="S150" s="21" t="inlineStr">
@@ -16027,13 +16047,13 @@
       </c>
       <c r="N151" s="51" t="n"/>
       <c r="O151" s="29" t="n">
-        <v>15.3</v>
+        <v>14.2</v>
       </c>
       <c r="P151" s="29" t="n">
-        <v>19.4</v>
+        <v>17.5</v>
       </c>
       <c r="Q151" s="29" t="n">
-        <v>16.85</v>
+        <v>15.45</v>
       </c>
       <c r="R151" s="45" t="n"/>
       <c r="S151" s="21" t="inlineStr">
@@ -16144,13 +16164,13 @@
       </c>
       <c r="N152" s="51" t="n"/>
       <c r="O152" s="29" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="P152" s="29" t="n">
-        <v>15.6</v>
+        <v>13.8</v>
       </c>
       <c r="Q152" s="29" t="n">
-        <v>14.27</v>
+        <v>12.34</v>
       </c>
       <c r="R152" s="45" t="n"/>
       <c r="S152" s="21" t="inlineStr">
@@ -16368,13 +16388,13 @@
       </c>
       <c r="N154" s="51" t="n"/>
       <c r="O154" s="29" t="n">
-        <v>15.1</v>
+        <v>17.4</v>
       </c>
       <c r="P154" s="29" t="n">
-        <v>24.7</v>
+        <v>27.3</v>
       </c>
       <c r="Q154" s="29" t="n">
-        <v>19.5</v>
+        <v>21.91</v>
       </c>
       <c r="R154" s="45" t="n"/>
       <c r="S154" s="21" t="inlineStr">
@@ -16485,13 +16505,13 @@
       </c>
       <c r="N155" s="51" t="n"/>
       <c r="O155" s="29" t="n">
-        <v>20.6</v>
+        <v>19.3</v>
       </c>
       <c r="P155" s="29" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q155" s="29" t="n">
-        <v>22.89</v>
+        <v>23.11</v>
       </c>
       <c r="R155" s="45" t="n"/>
       <c r="S155" s="21" t="inlineStr">
@@ -16602,13 +16622,13 @@
       </c>
       <c r="N156" s="51" t="n"/>
       <c r="O156" s="29" t="n">
-        <v>17</v>
+        <v>15.7</v>
       </c>
       <c r="P156" s="29" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="Q156" s="29" t="n">
-        <v>20.94</v>
+        <v>20.5</v>
       </c>
       <c r="R156" s="45" t="n"/>
       <c r="S156" s="21" t="inlineStr">
@@ -16719,13 +16739,13 @@
       </c>
       <c r="N157" s="51" t="n"/>
       <c r="O157" s="29" t="n">
-        <v>18.3</v>
+        <v>13.7</v>
       </c>
       <c r="P157" s="29" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q157" s="29" t="n">
-        <v>20.23</v>
+        <v>19.01</v>
       </c>
       <c r="R157" s="45" t="n"/>
       <c r="S157" s="21" t="inlineStr">
@@ -16836,13 +16856,13 @@
       </c>
       <c r="N158" s="51" t="n"/>
       <c r="O158" s="29" t="n">
-        <v>18.6</v>
+        <v>15.5</v>
       </c>
       <c r="P158" s="29" t="n">
-        <v>24</v>
+        <v>25.8</v>
       </c>
       <c r="Q158" s="29" t="n">
-        <v>20.65</v>
+        <v>20.56</v>
       </c>
       <c r="R158" s="45" t="n"/>
       <c r="S158" s="21" t="inlineStr">
@@ -17056,13 +17076,13 @@
       </c>
       <c r="N160" s="51" t="n"/>
       <c r="O160" s="29" t="n">
-        <v>23</v>
+        <v>21.1</v>
       </c>
       <c r="P160" s="29" t="n">
-        <v>28.2</v>
+        <v>26.2</v>
       </c>
       <c r="Q160" s="29" t="n">
-        <v>24.93</v>
+        <v>22.35</v>
       </c>
       <c r="R160" s="45" t="n"/>
       <c r="S160" s="21" t="inlineStr">
@@ -17173,13 +17193,13 @@
       </c>
       <c r="N161" s="51" t="n"/>
       <c r="O161" s="29" t="n">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="P161" s="29" t="n">
-        <v>29.7</v>
+        <v>31.2</v>
       </c>
       <c r="Q161" s="29" t="n">
-        <v>24.3</v>
+        <v>24.11</v>
       </c>
       <c r="R161" s="45" t="n"/>
       <c r="S161" s="21" t="inlineStr">
@@ -17492,13 +17512,13 @@
       </c>
       <c r="N164" s="51" t="n"/>
       <c r="O164" s="29" t="n">
-        <v>26.3</v>
+        <v>24.8</v>
       </c>
       <c r="P164" s="29" t="n">
-        <v>31.8</v>
+        <v>33.1</v>
       </c>
       <c r="Q164" s="29" t="n">
-        <v>28.94</v>
+        <v>28.04</v>
       </c>
       <c r="R164" s="45" t="n"/>
       <c r="S164" s="21" t="inlineStr">
@@ -17601,13 +17621,13 @@
       </c>
       <c r="N165" s="51" t="n"/>
       <c r="O165" s="29" t="n">
-        <v>22.6</v>
+        <v>21.9</v>
       </c>
       <c r="P165" s="29" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="Q165" s="29" t="n">
-        <v>26.61</v>
+        <v>26.55</v>
       </c>
       <c r="R165" s="45" t="n"/>
       <c r="S165" s="21" t="inlineStr">
@@ -17718,13 +17738,13 @@
       </c>
       <c r="N166" s="51" t="n"/>
       <c r="O166" s="29" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="P166" s="29" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q166" s="29" t="n">
-        <v>18.86</v>
+        <v>17.84</v>
       </c>
       <c r="R166" s="45" t="n"/>
       <c r="S166" s="21" t="inlineStr">
@@ -17835,13 +17855,13 @@
       </c>
       <c r="N167" s="51" t="n"/>
       <c r="O167" s="29" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="P167" s="29" t="n">
-        <v>17.9</v>
+        <v>20.6</v>
       </c>
       <c r="Q167" s="29" t="n">
-        <v>16.15</v>
+        <v>17.43</v>
       </c>
       <c r="R167" s="45" t="n"/>
       <c r="S167" s="21" t="inlineStr">
@@ -17952,13 +17972,13 @@
       </c>
       <c r="N168" s="51" t="n"/>
       <c r="O168" s="29" t="n">
-        <v>18.8</v>
+        <v>19.9</v>
       </c>
       <c r="P168" s="29" t="n">
         <v>22.5</v>
       </c>
       <c r="Q168" s="29" t="n">
-        <v>20.62</v>
+        <v>21.06</v>
       </c>
       <c r="R168" s="45" t="n"/>
       <c r="S168" s="21" t="inlineStr">
@@ -18160,13 +18180,13 @@
       </c>
       <c r="N170" s="51" t="n"/>
       <c r="O170" s="29" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P170" s="29" t="n">
-        <v>23.5</v>
+        <v>20.1</v>
       </c>
       <c r="Q170" s="29" t="n">
-        <v>19.09</v>
+        <v>17.77</v>
       </c>
       <c r="R170" s="45" t="n"/>
       <c r="S170" s="21" t="inlineStr">
@@ -18281,13 +18301,13 @@
       </c>
       <c r="N171" s="51" t="n"/>
       <c r="O171" s="29" t="n">
-        <v>1.7</v>
+        <v>-1.1</v>
       </c>
       <c r="P171" s="29" t="n">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="Q171" s="29" t="n">
-        <v>8.380000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="R171" s="45" t="n"/>
       <c r="S171" s="21" t="inlineStr">
@@ -18873,13 +18893,13 @@
       </c>
       <c r="N177" s="51" t="n"/>
       <c r="O177" s="29" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="P177" s="29" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="Q177" s="29" t="n">
-        <v>-1.71</v>
+        <v>-2.36</v>
       </c>
       <c r="R177" s="45" t="n"/>
       <c r="S177" s="21" t="inlineStr">
@@ -18986,13 +19006,13 @@
       </c>
       <c r="N178" s="51" t="n"/>
       <c r="O178" s="29" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9</v>
       </c>
       <c r="P178" s="29" t="n">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="Q178" s="29" t="n">
-        <v>-1.46</v>
+        <v>-1.38</v>
       </c>
       <c r="R178" s="45" t="n"/>
       <c r="S178" s="21" t="inlineStr">
@@ -19101,13 +19121,13 @@
       </c>
       <c r="N179" s="51" t="n"/>
       <c r="O179" s="29" t="n">
-        <v>13.3</v>
+        <v>9.4</v>
       </c>
       <c r="P179" s="29" t="n">
-        <v>16.3</v>
+        <v>17.9</v>
       </c>
       <c r="Q179" s="29" t="n">
-        <v>14.7</v>
+        <v>13.09</v>
       </c>
       <c r="R179" s="45" t="n"/>
       <c r="S179" s="21" t="inlineStr">
@@ -19206,13 +19226,13 @@
       </c>
       <c r="N180" s="51" t="n"/>
       <c r="O180" s="29" t="n">
-        <v>19.7</v>
+        <v>16.3</v>
       </c>
       <c r="P180" s="29" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q180" s="29" t="n">
-        <v>20.69</v>
+        <v>19.74</v>
       </c>
       <c r="R180" s="45" t="n"/>
       <c r="S180" s="21" t="inlineStr">
@@ -19315,13 +19335,13 @@
       </c>
       <c r="N181" s="51" t="n"/>
       <c r="O181" s="29" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="P181" s="29" t="n">
-        <v>14.1</v>
+        <v>11.8</v>
       </c>
       <c r="Q181" s="29" t="n">
-        <v>9.390000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="R181" s="45" t="n"/>
       <c r="S181" s="21" t="inlineStr">
@@ -19559,13 +19579,13 @@
         </is>
       </c>
       <c r="O183" s="29" t="n">
-        <v>-10.9</v>
+        <v>-11</v>
       </c>
       <c r="P183" s="29" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="Q183" s="29" t="n">
-        <v>-5.18</v>
+        <v>-5.28</v>
       </c>
       <c r="R183" s="45" t="n"/>
       <c r="S183" s="21" t="inlineStr">
@@ -19680,13 +19700,13 @@
       </c>
       <c r="N184" s="51" t="n"/>
       <c r="O184" s="29" t="n">
-        <v>-20</v>
+        <v>-21.8</v>
       </c>
       <c r="P184" s="29" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8</v>
       </c>
       <c r="Q184" s="29" t="n">
-        <v>-13.74</v>
+        <v>-15.21</v>
       </c>
       <c r="R184" s="45" t="n"/>
       <c r="S184" s="21" t="inlineStr">
@@ -19801,13 +19821,13 @@
       </c>
       <c r="N185" s="51" t="n"/>
       <c r="O185" s="29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P185" s="29" t="n">
-        <v>12.9</v>
+        <v>15.7</v>
       </c>
       <c r="Q185" s="29" t="n">
-        <v>11.84</v>
+        <v>11.81</v>
       </c>
       <c r="R185" s="45" t="n"/>
       <c r="S185" s="21" t="inlineStr">
@@ -19914,13 +19934,13 @@
       </c>
       <c r="N186" s="51" t="n"/>
       <c r="O186" s="29" t="n">
-        <v>17</v>
+        <v>13.1</v>
       </c>
       <c r="P186" s="29" t="n">
-        <v>21.6</v>
+        <v>24.6</v>
       </c>
       <c r="Q186" s="29" t="n">
-        <v>18.85</v>
+        <v>18.6</v>
       </c>
       <c r="R186" s="45" t="n"/>
       <c r="S186" s="21" t="inlineStr">
@@ -20031,13 +20051,13 @@
       </c>
       <c r="N187" s="51" t="n"/>
       <c r="O187" s="29" t="n">
-        <v>21.7</v>
+        <v>22.7</v>
       </c>
       <c r="P187" s="29" t="n">
         <v>36.7</v>
       </c>
       <c r="Q187" s="29" t="n">
-        <v>27.95</v>
+        <v>28.54</v>
       </c>
       <c r="R187" s="45" t="n"/>
       <c r="S187" s="21" t="inlineStr">
@@ -20144,13 +20164,13 @@
       </c>
       <c r="N188" s="51" t="n"/>
       <c r="O188" s="29" t="n">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="P188" s="29" t="n">
-        <v>10.2</v>
+        <v>14.7</v>
       </c>
       <c r="Q188" s="29" t="n">
-        <v>9.41</v>
+        <v>10.73</v>
       </c>
       <c r="R188" s="45" t="n"/>
       <c r="S188" s="21" t="inlineStr">
@@ -20348,13 +20368,13 @@
         </is>
       </c>
       <c r="O190" s="29" t="n">
-        <v>-16.5</v>
+        <v>-16.4</v>
       </c>
       <c r="P190" s="29" t="n">
-        <v>-7.6</v>
+        <v>-7.3</v>
       </c>
       <c r="Q190" s="29" t="n">
-        <v>-12.7</v>
+        <v>-12.2</v>
       </c>
       <c r="R190" s="45" t="n"/>
       <c r="S190" s="21" t="n"/>
@@ -20754,13 +20774,13 @@
         </is>
       </c>
       <c r="O194" s="29" t="n">
-        <v>-0.6</v>
+        <v>-2.3</v>
       </c>
       <c r="P194" s="29" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="Q194" s="29" t="n">
-        <v>3.51</v>
+        <v>-0.03</v>
       </c>
       <c r="R194" s="45" t="inlineStr">
         <is>
@@ -20863,10 +20883,10 @@
       </c>
       <c r="N195" s="51" t="n"/>
       <c r="O195" s="29" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P195" s="29" t="n">
-        <v>14.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q195" s="29" t="n"/>
       <c r="R195" s="45" t="n"/>
@@ -20970,10 +20990,10 @@
         </is>
       </c>
       <c r="O196" s="29" t="n">
-        <v>-27.3</v>
+        <v>-28.8</v>
       </c>
       <c r="P196" s="29" t="n">
-        <v>-10.7</v>
+        <v>-9.9</v>
       </c>
       <c r="Q196" s="29" t="n"/>
       <c r="R196" s="45" t="n"/>
@@ -21081,13 +21101,13 @@
         </is>
       </c>
       <c r="O197" s="29" t="n">
-        <v>-3.6</v>
+        <v>-10.4</v>
       </c>
       <c r="P197" s="29" t="n">
-        <v>0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="Q197" s="29" t="n">
-        <v>-1.19</v>
+        <v>-5.23</v>
       </c>
       <c r="R197" s="45" t="n"/>
       <c r="S197" s="21" t="n"/>
@@ -21983,9 +22003,15 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="O206" s="29" t="n"/>
-      <c r="P206" s="29" t="n"/>
-      <c r="Q206" s="29" t="n"/>
+      <c r="O206" s="29" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="P206" s="29" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="Q206" s="29" t="n">
+        <v>-11.8</v>
+      </c>
       <c r="R206" s="45" t="n"/>
       <c r="S206" s="21" t="n"/>
       <c r="T206" s="33" t="n"/>
@@ -22087,10 +22113,10 @@
         </is>
       </c>
       <c r="O207" s="29" t="n">
-        <v>-9.4</v>
+        <v>-18.1</v>
       </c>
       <c r="P207" s="29" t="n">
-        <v>1.9</v>
+        <v>-0.4</v>
       </c>
       <c r="Q207" s="29" t="n"/>
       <c r="R207" s="45" t="n"/>
@@ -22197,8 +22223,12 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O208" s="29" t="n"/>
-      <c r="P208" s="29" t="n"/>
+      <c r="O208" s="29" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="P208" s="29" t="n">
+        <v>0.2</v>
+      </c>
       <c r="Q208" s="29" t="n"/>
       <c r="R208" s="45" t="inlineStr">
         <is>
@@ -22503,13 +22533,13 @@
         </is>
       </c>
       <c r="O211" s="29" t="n">
-        <v>-34.5</v>
+        <v>-30.6</v>
       </c>
       <c r="P211" s="29" t="n">
-        <v>-14.3</v>
+        <v>-8.4</v>
       </c>
       <c r="Q211" s="29" t="n">
-        <v>-28.2</v>
+        <v>-21.9</v>
       </c>
       <c r="R211" s="45" t="n"/>
       <c r="S211" s="21" t="n"/>
@@ -22616,13 +22646,13 @@
         </is>
       </c>
       <c r="O212" s="29" t="n">
-        <v>-19.9</v>
+        <v>-25.1</v>
       </c>
       <c r="P212" s="29" t="n">
-        <v>-4.4</v>
+        <v>-3.8</v>
       </c>
       <c r="Q212" s="29" t="n">
-        <v>-11</v>
+        <v>-18.2</v>
       </c>
       <c r="R212" s="45" t="inlineStr">
         <is>
@@ -22729,13 +22759,13 @@
       </c>
       <c r="N213" s="51" t="n"/>
       <c r="O213" s="29" t="n">
-        <v>-32.3</v>
+        <v>-27.5</v>
       </c>
       <c r="P213" s="29" t="n">
-        <v>-10.2</v>
+        <v>-6</v>
       </c>
       <c r="Q213" s="29" t="n">
-        <v>-23.5</v>
+        <v>-19.6</v>
       </c>
       <c r="R213" s="45" t="n"/>
       <c r="S213" s="21" t="n"/>
@@ -22840,7 +22870,7 @@
         </is>
       </c>
       <c r="O214" s="29" t="n">
-        <v>-45.1</v>
+        <v>-45.4</v>
       </c>
       <c r="P214" s="29" t="n"/>
       <c r="Q214" s="29" t="n"/>
@@ -22932,7 +22962,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O215" s="29" t="n"/>
+      <c r="O215" s="29" t="n">
+        <v>-46.6</v>
+      </c>
       <c r="P215" s="29" t="n"/>
       <c r="Q215" s="29" t="n"/>
       <c r="R215" s="45" t="n"/>
@@ -23703,13 +23735,13 @@
       </c>
       <c r="N223" s="51" t="n"/>
       <c r="O223" s="29" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="P223" s="29" t="n">
-        <v>14.2</v>
+        <v>10.4</v>
       </c>
       <c r="Q223" s="29" t="n">
-        <v>10.44</v>
+        <v>8.31</v>
       </c>
       <c r="R223" s="45" t="n"/>
       <c r="S223" s="21" t="inlineStr">
@@ -24107,13 +24139,13 @@
       </c>
       <c r="N227" s="51" t="n"/>
       <c r="O227" s="29" t="n">
-        <v>-5.7</v>
+        <v>-4.9</v>
       </c>
       <c r="P227" s="29" t="n">
-        <v>2.5</v>
+        <v>-0.5</v>
       </c>
       <c r="Q227" s="29" t="n">
-        <v>-2.21</v>
+        <v>-3.45</v>
       </c>
       <c r="R227" s="45" t="n"/>
       <c r="S227" s="21" t="inlineStr">
@@ -24317,13 +24349,13 @@
       </c>
       <c r="N229" s="51" t="n"/>
       <c r="O229" s="29" t="n">
-        <v>-4</v>
+        <v>-5.8</v>
       </c>
       <c r="P229" s="29" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="Q229" s="29" t="n">
-        <v>-2.44</v>
+        <v>-2.74</v>
       </c>
       <c r="R229" s="45" t="n"/>
       <c r="S229" s="21" t="inlineStr">
@@ -24723,13 +24755,13 @@
       </c>
       <c r="N233" s="51" t="n"/>
       <c r="O233" s="29" t="n">
-        <v>-6.7</v>
+        <v>-7.2</v>
       </c>
       <c r="P233" s="29" t="n">
-        <v>-0.5</v>
+        <v>-2.8</v>
       </c>
       <c r="Q233" s="29" t="n">
-        <v>-3.59</v>
+        <v>-5.26</v>
       </c>
       <c r="R233" s="45" t="n"/>
       <c r="S233" s="21" t="inlineStr">
@@ -25317,13 +25349,13 @@
       </c>
       <c r="N239" s="51" t="n"/>
       <c r="O239" s="29" t="n">
-        <v>-1.2</v>
+        <v>-0.4</v>
       </c>
       <c r="P239" s="29" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="Q239" s="29" t="n">
-        <v>-0.34</v>
+        <v>0.78</v>
       </c>
       <c r="R239" s="45" t="n"/>
       <c r="S239" s="21" t="inlineStr">
@@ -25430,13 +25462,13 @@
       </c>
       <c r="N240" s="51" t="n"/>
       <c r="O240" s="29" t="n">
-        <v>-7.2</v>
+        <v>-4.8</v>
       </c>
       <c r="P240" s="29" t="n">
-        <v>3.3</v>
+        <v>-0.4</v>
       </c>
       <c r="Q240" s="29" t="n">
-        <v>-2.26</v>
+        <v>-3.46</v>
       </c>
       <c r="R240" s="45" t="n"/>
       <c r="S240" s="21" t="inlineStr">
@@ -26408,13 +26440,13 @@
         </is>
       </c>
       <c r="O250" s="29" t="n">
-        <v>-14.6</v>
+        <v>-19</v>
       </c>
       <c r="P250" s="29" t="n">
-        <v>-8</v>
+        <v>-1.5</v>
       </c>
       <c r="Q250" s="29" t="n">
-        <v>-9.380000000000001</v>
+        <v>-9.59</v>
       </c>
       <c r="R250" s="45" t="n"/>
       <c r="S250" s="21" t="inlineStr">
@@ -28116,9 +28148,15 @@
         </is>
       </c>
       <c r="N268" s="51" t="n"/>
-      <c r="O268" s="29" t="n"/>
-      <c r="P268" s="29" t="n"/>
-      <c r="Q268" s="29" t="n"/>
+      <c r="O268" s="29" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="P268" s="29" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="Q268" s="29" t="n">
+        <v>-25.53</v>
+      </c>
       <c r="R268" s="45" t="n"/>
       <c r="S268" s="21" t="n"/>
       <c r="T268" s="33" t="n"/>
@@ -29152,13 +29190,13 @@
         </is>
       </c>
       <c r="O279" s="29" t="n">
-        <v>-16</v>
+        <v>-14.4</v>
       </c>
       <c r="P279" s="29" t="n">
-        <v>-12</v>
+        <v>-13.4</v>
       </c>
       <c r="Q279" s="29" t="n">
-        <v>-14.19</v>
+        <v>-13.75</v>
       </c>
       <c r="R279" s="45" t="n"/>
       <c r="S279" s="21" t="inlineStr">
@@ -29654,10 +29692,10 @@
         </is>
       </c>
       <c r="O284" s="29" t="n">
-        <v>-17</v>
+        <v>-19.7</v>
       </c>
       <c r="P284" s="29" t="n">
-        <v>-4.9</v>
+        <v>-4.7</v>
       </c>
       <c r="Q284" s="29" t="n"/>
       <c r="R284" s="45" t="n"/>
@@ -30039,10 +30077,10 @@
         </is>
       </c>
       <c r="O288" s="29" t="n">
-        <v>-62</v>
+        <v>-62.8</v>
       </c>
       <c r="P288" s="29" t="n">
-        <v>-49</v>
+        <v>-49.3</v>
       </c>
       <c r="Q288" s="29" t="n"/>
       <c r="R288" s="45" t="n"/>
@@ -30235,13 +30273,13 @@
       </c>
       <c r="N290" s="51" t="n"/>
       <c r="O290" s="29" t="n">
-        <v>-2.1</v>
+        <v>-0.6</v>
       </c>
       <c r="P290" s="29" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q290" s="29" t="n">
-        <v>1.13</v>
+        <v>3.34</v>
       </c>
       <c r="R290" s="45" t="n"/>
       <c r="S290" s="21" t="inlineStr">
@@ -30451,13 +30489,13 @@
         </is>
       </c>
       <c r="O292" s="29" t="n">
-        <v>-1.7</v>
+        <v>1</v>
       </c>
       <c r="P292" s="29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q292" s="29" t="n">
-        <v>1.1</v>
+        <v>2.85</v>
       </c>
       <c r="R292" s="45" t="n"/>
       <c r="S292" s="21" t="inlineStr">
@@ -34877,10 +34915,10 @@
       </c>
       <c r="N338" s="51" t="n"/>
       <c r="O338" s="29" t="n">
-        <v>-19.8</v>
+        <v>-21.5</v>
       </c>
       <c r="P338" s="29" t="n">
-        <v>1</v>
+        <v>-1.9</v>
       </c>
       <c r="Q338" s="29" t="n"/>
       <c r="R338" s="45" t="n"/>
@@ -38644,13 +38682,13 @@
       </c>
       <c r="N377" s="51" t="n"/>
       <c r="O377" s="29" t="n">
-        <v>-25.2</v>
+        <v>-28.4</v>
       </c>
       <c r="P377" s="29" t="n">
-        <v>-4.4</v>
+        <v>-3.7</v>
       </c>
       <c r="Q377" s="29" t="n">
-        <v>-15.8</v>
+        <v>-17.6</v>
       </c>
       <c r="R377" s="45" t="n"/>
       <c r="S377" s="21" t="n"/>
@@ -39527,14 +39565,12 @@
         </is>
       </c>
       <c r="O386" s="29" t="n">
-        <v>-19.1</v>
+        <v>-18.6</v>
       </c>
       <c r="P386" s="29" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="Q386" s="29" t="n">
-        <v>-11.9</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="Q386" s="29" t="n"/>
       <c r="R386" s="45" t="n"/>
       <c r="S386" s="21" t="n"/>
       <c r="T386" s="33" t="n"/>
@@ -39735,13 +39771,13 @@
       </c>
       <c r="N388" s="51" t="n"/>
       <c r="O388" s="29" t="n">
-        <v>-22</v>
+        <v>-17.3</v>
       </c>
       <c r="P388" s="29" t="n">
-        <v>-12.3</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="Q388" s="29" t="n">
-        <v>-18.6</v>
+        <v>-11.1</v>
       </c>
       <c r="R388" s="45" t="n"/>
       <c r="S388" s="21" t="n"/>
@@ -41007,15 +41043,9 @@
         </is>
       </c>
       <c r="N401" s="51" t="n"/>
-      <c r="O401" s="29" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="P401" s="29" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="Q401" s="29" t="n">
-        <v>-16.15</v>
-      </c>
+      <c r="O401" s="29" t="n"/>
+      <c r="P401" s="29" t="n"/>
+      <c r="Q401" s="29" t="n"/>
       <c r="R401" s="45" t="n"/>
       <c r="S401" s="21" t="n"/>
       <c r="T401" s="33" t="n"/>

--- a/气象/For_Python_站点信息和记录.xlsx
+++ b/气象/For_Python_站点信息和记录.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="极寒收集" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'站点信息和记录'!$A$1:$AI$450</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'站点信息和记录'!$A$1:$AI$451</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -804,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI450"/>
+  <dimension ref="A1:AI451"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.59765625" defaultRowHeight="20.25"/>
   <cols>
     <col width="4.59765625" customWidth="1" style="4" min="1" max="1"/>
@@ -830,8 +830,8 @@
     <col width="18.59765625" customWidth="1" style="7" min="26" max="26"/>
     <col width="12.59765625" customWidth="1" style="4" min="27" max="31"/>
     <col width="12.59765625" customWidth="1" style="7" min="32" max="33"/>
-    <col width="12.59765625" customWidth="1" style="4" min="34" max="791"/>
-    <col width="12.59765625" customWidth="1" style="4" min="792" max="16384"/>
+    <col width="12.59765625" customWidth="1" style="4" min="34" max="792"/>
+    <col width="12.59765625" customWidth="1" style="4" min="793" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customFormat="1" customHeight="1" s="10">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="O2" s="29" t="n">
-        <v>-10.6</v>
+        <v>-12.2</v>
       </c>
       <c r="P2" s="29" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q2" s="29" t="n">
-        <v>-3.5</v>
+        <v>-4.93</v>
       </c>
       <c r="R2" s="45" t="n"/>
       <c r="S2" s="21" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="O3" s="29" t="n">
-        <v>-11</v>
+        <v>-14.3</v>
       </c>
       <c r="P3" s="29" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="Q3" s="29" t="n"/>
       <c r="R3" s="45" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="O4" s="29" t="n">
-        <v>-18.3</v>
+        <v>-20.2</v>
       </c>
       <c r="P4" s="29" t="n">
-        <v>-3.2</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="Q4" s="29" t="n"/>
       <c r="R4" s="45" t="inlineStr">
@@ -1381,8 +1381,12 @@
         </is>
       </c>
       <c r="N5" s="51" t="n"/>
-      <c r="O5" s="29" t="n"/>
-      <c r="P5" s="29" t="n"/>
+      <c r="O5" s="29" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="P5" s="29" t="n">
+        <v>-8</v>
+      </c>
       <c r="Q5" s="29" t="n"/>
       <c r="R5" s="45" t="n"/>
       <c r="S5" s="21" t="n"/>
@@ -1485,13 +1489,13 @@
         </is>
       </c>
       <c r="O6" s="29" t="n">
-        <v>-19.8</v>
+        <v>-25.2</v>
       </c>
       <c r="P6" s="29" t="n">
-        <v>-6.1</v>
+        <v>-9.5</v>
       </c>
       <c r="Q6" s="29" t="n">
-        <v>-12.01</v>
+        <v>-18.13</v>
       </c>
       <c r="R6" s="47" t="inlineStr">
         <is>
@@ -1596,10 +1600,10 @@
         </is>
       </c>
       <c r="O7" s="29" t="n">
-        <v>-12.3</v>
+        <v>-19.2</v>
       </c>
       <c r="P7" s="29" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="Q7" s="29" t="n"/>
       <c r="R7" s="45" t="n"/>
@@ -1705,13 +1709,13 @@
       </c>
       <c r="N8" s="51" t="n"/>
       <c r="O8" s="29" t="n">
-        <v>-4.8</v>
+        <v>-14.1</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>-3.01</v>
+        <v>-7.15</v>
       </c>
       <c r="R8" s="45" t="n"/>
       <c r="S8" s="21" t="inlineStr">
@@ -1818,13 +1822,13 @@
       </c>
       <c r="N9" s="51" t="n"/>
       <c r="O9" s="29" t="n">
-        <v>-7.8</v>
+        <v>-8.9</v>
       </c>
       <c r="P9" s="29" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>-2.91</v>
+        <v>-4.01</v>
       </c>
       <c r="R9" s="45" t="n"/>
       <c r="S9" s="21" t="inlineStr">
@@ -1939,13 +1943,13 @@
         </is>
       </c>
       <c r="O10" s="29" t="n">
-        <v>-13.4</v>
+        <v>-24.8</v>
       </c>
       <c r="P10" s="29" t="n">
-        <v>-4.2</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>-8.16</v>
+        <v>-16.28</v>
       </c>
       <c r="R10" s="45" t="n"/>
       <c r="S10" s="21" t="inlineStr">
@@ -2056,13 +2060,13 @@
         </is>
       </c>
       <c r="O11" s="29" t="n">
-        <v>-15.1</v>
+        <v>-24.6</v>
       </c>
       <c r="P11" s="29" t="n">
-        <v>-7</v>
+        <v>-5.6</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>-10.9</v>
+        <v>-16.45</v>
       </c>
       <c r="R11" s="45" t="inlineStr">
         <is>
@@ -2173,13 +2177,13 @@
       </c>
       <c r="N12" s="51" t="n"/>
       <c r="O12" s="29" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>-4.3</v>
+        <v>-7.4</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>-7.34</v>
+        <v>-14.75</v>
       </c>
       <c r="R12" s="45" t="inlineStr">
         <is>
@@ -2294,13 +2298,13 @@
         </is>
       </c>
       <c r="O13" s="29" t="n">
-        <v>-18</v>
+        <v>-21.8</v>
       </c>
       <c r="P13" s="29" t="n">
-        <v>-5</v>
+        <v>-6.1</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>-10.41</v>
+        <v>-13.75</v>
       </c>
       <c r="R13" s="45" t="inlineStr">
         <is>
@@ -2411,13 +2415,13 @@
       </c>
       <c r="N14" s="51" t="n"/>
       <c r="O14" s="29" t="n">
-        <v>-8.6</v>
+        <v>-12</v>
       </c>
       <c r="P14" s="29" t="n">
-        <v>-3.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" s="29" t="n">
-        <v>-6.1</v>
+        <v>-6</v>
       </c>
       <c r="R14" s="45" t="n"/>
       <c r="S14" s="21" t="inlineStr">
@@ -2528,13 +2532,13 @@
       </c>
       <c r="N15" s="51" t="n"/>
       <c r="O15" s="29" t="n">
-        <v>-9.1</v>
+        <v>-15.2</v>
       </c>
       <c r="P15" s="29" t="n">
-        <v>-4.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q15" s="29" t="n">
-        <v>-7.08</v>
+        <v>-7.78</v>
       </c>
       <c r="R15" s="45" t="n"/>
       <c r="S15" s="21" t="inlineStr">
@@ -2639,13 +2643,13 @@
       </c>
       <c r="N16" s="51" t="n"/>
       <c r="O16" s="29" t="n">
-        <v>-13.2</v>
+        <v>-16.4</v>
       </c>
       <c r="P16" s="29" t="n">
-        <v>-2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>-6.54</v>
+        <v>-7.81</v>
       </c>
       <c r="R16" s="45" t="n"/>
       <c r="S16" s="21" t="n"/>
@@ -2919,15 +2923,9 @@
         </is>
       </c>
       <c r="N19" s="51" t="n"/>
-      <c r="O19" s="29" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="P19" s="29" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Q19" s="29" t="n">
-        <v>-10.96</v>
-      </c>
+      <c r="O19" s="29" t="n"/>
+      <c r="P19" s="29" t="n"/>
+      <c r="Q19" s="29" t="n"/>
       <c r="R19" s="45" t="n"/>
       <c r="S19" s="21" t="n"/>
       <c r="T19" s="33" t="n"/>
@@ -3026,9 +3024,15 @@
         </is>
       </c>
       <c r="N20" s="51" t="n"/>
-      <c r="O20" s="29" t="n"/>
-      <c r="P20" s="29" t="n"/>
-      <c r="Q20" s="29" t="n"/>
+      <c r="O20" s="29" t="n">
+        <v>-21.4</v>
+      </c>
+      <c r="P20" s="29" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Q20" s="29" t="n">
+        <v>-13.31</v>
+      </c>
       <c r="R20" s="45" t="n"/>
       <c r="S20" s="21" t="n"/>
       <c r="T20" s="33" t="n"/>
@@ -4314,12 +4318,8 @@
         </is>
       </c>
       <c r="N34" s="51" t="n"/>
-      <c r="O34" s="29" t="n">
-        <v>-21.9</v>
-      </c>
-      <c r="P34" s="29" t="n">
-        <v>-2.2</v>
-      </c>
+      <c r="O34" s="29" t="n"/>
+      <c r="P34" s="29" t="n"/>
       <c r="Q34" s="29" t="n"/>
       <c r="R34" s="45" t="n"/>
       <c r="S34" s="21" t="n"/>
@@ -4787,12 +4787,8 @@
         </is>
       </c>
       <c r="N39" s="51" t="n"/>
-      <c r="O39" s="29" t="n">
-        <v>-16.6</v>
-      </c>
-      <c r="P39" s="29" t="n">
-        <v>-9.199999999999999</v>
-      </c>
+      <c r="O39" s="29" t="n"/>
+      <c r="P39" s="29" t="n"/>
       <c r="Q39" s="29" t="n"/>
       <c r="R39" s="45" t="n"/>
       <c r="S39" s="21" t="n"/>
@@ -10563,13 +10559,13 @@
         </is>
       </c>
       <c r="O102" s="29" t="n">
-        <v>-10.9</v>
+        <v>-14.2</v>
       </c>
       <c r="P102" s="29" t="n">
-        <v>-4.3</v>
+        <v>-4</v>
       </c>
       <c r="Q102" s="29" t="n">
-        <v>-7.82</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="R102" s="45" t="inlineStr">
         <is>
@@ -10993,13 +10989,13 @@
         </is>
       </c>
       <c r="O106" s="29" t="n">
-        <v>-18.3</v>
+        <v>-23.6</v>
       </c>
       <c r="P106" s="29" t="n">
-        <v>-3.6</v>
+        <v>-7.1</v>
       </c>
       <c r="Q106" s="29" t="n">
-        <v>-10.64</v>
+        <v>-13.79</v>
       </c>
       <c r="R106" s="45" t="n"/>
       <c r="S106" s="21" t="inlineStr">
@@ -11115,13 +11111,13 @@
         </is>
       </c>
       <c r="O107" s="29" t="n">
-        <v>-16.6</v>
+        <v>-16.4</v>
       </c>
       <c r="P107" s="29" t="n">
-        <v>-3.6</v>
+        <v>-7.4</v>
       </c>
       <c r="Q107" s="29" t="n">
-        <v>-8.890000000000001</v>
+        <v>-11.67</v>
       </c>
       <c r="R107" s="45" t="n"/>
       <c r="S107" s="21" t="inlineStr">
@@ -11335,13 +11331,13 @@
         </is>
       </c>
       <c r="O109" s="29" t="n">
-        <v>-7.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P109" s="29" t="n">
-        <v>-4.4</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="29" t="n">
-        <v>-5.8</v>
+        <v>-4.08</v>
       </c>
       <c r="R109" s="45" t="n"/>
       <c r="S109" s="21" t="inlineStr">
@@ -11555,13 +11551,13 @@
       </c>
       <c r="N111" s="51" t="n"/>
       <c r="O111" s="29" t="n">
-        <v>-9.4</v>
+        <v>-10.9</v>
       </c>
       <c r="P111" s="29" t="n">
-        <v>2.1</v>
+        <v>-0.6</v>
       </c>
       <c r="Q111" s="29" t="n">
-        <v>-4.38</v>
+        <v>-5.59</v>
       </c>
       <c r="R111" s="45" t="n"/>
       <c r="S111" s="21" t="inlineStr">
@@ -11783,13 +11779,13 @@
       </c>
       <c r="N113" s="51" t="n"/>
       <c r="O113" s="29" t="n">
-        <v>-18.1</v>
+        <v>-19.3</v>
       </c>
       <c r="P113" s="29" t="n">
-        <v>-6.7</v>
+        <v>-5.6</v>
       </c>
       <c r="Q113" s="29" t="n">
-        <v>-12.75</v>
+        <v>-13.38</v>
       </c>
       <c r="R113" s="45" t="inlineStr">
         <is>
@@ -12308,13 +12304,13 @@
       </c>
       <c r="N118" s="51" t="n"/>
       <c r="O118" s="29" t="n">
-        <v>-3.1</v>
+        <v>-8.6</v>
       </c>
       <c r="P118" s="29" t="n">
-        <v>5.7</v>
+        <v>-0.1</v>
       </c>
       <c r="Q118" s="29" t="n">
-        <v>1.51</v>
+        <v>-4.51</v>
       </c>
       <c r="R118" s="45" t="n"/>
       <c r="S118" s="21" t="inlineStr">
@@ -12421,13 +12417,13 @@
       </c>
       <c r="N119" s="51" t="n"/>
       <c r="O119" s="29" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="P119" s="29" t="n">
-        <v>14.1</v>
+        <v>8.5</v>
       </c>
       <c r="Q119" s="29" t="n">
-        <v>9.82</v>
+        <v>5.65</v>
       </c>
       <c r="R119" s="45" t="n"/>
       <c r="S119" s="21" t="inlineStr">
@@ -12657,13 +12653,13 @@
       </c>
       <c r="N121" s="51" t="n"/>
       <c r="O121" s="29" t="n">
-        <v>1.1</v>
+        <v>-2.1</v>
       </c>
       <c r="P121" s="29" t="n">
-        <v>12.8</v>
+        <v>7.7</v>
       </c>
       <c r="Q121" s="29" t="n">
-        <v>6.5</v>
+        <v>2.06</v>
       </c>
       <c r="R121" s="45" t="n"/>
       <c r="S121" s="21" t="inlineStr">
@@ -12782,13 +12778,13 @@
       </c>
       <c r="N122" s="51" t="n"/>
       <c r="O122" s="29" t="n">
-        <v>1.2</v>
+        <v>-2</v>
       </c>
       <c r="P122" s="29" t="n">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="Q122" s="29" t="n">
-        <v>5.49</v>
+        <v>1.05</v>
       </c>
       <c r="R122" s="45" t="n"/>
       <c r="S122" s="21" t="inlineStr">
@@ -13343,13 +13339,13 @@
       </c>
       <c r="N127" s="51" t="n"/>
       <c r="O127" s="29" t="n">
-        <v>-9.6</v>
+        <v>-14.4</v>
       </c>
       <c r="P127" s="29" t="n">
-        <v>-0.6</v>
+        <v>-5.6</v>
       </c>
       <c r="Q127" s="29" t="n">
-        <v>-5.1</v>
+        <v>-9.81</v>
       </c>
       <c r="R127" s="45" t="n"/>
       <c r="S127" s="21" t="inlineStr">
@@ -13563,13 +13559,13 @@
       </c>
       <c r="N129" s="51" t="n"/>
       <c r="O129" s="29" t="n">
-        <v>-17.5</v>
+        <v>-18.5</v>
       </c>
       <c r="P129" s="29" t="n">
-        <v>-1.6</v>
+        <v>-6.4</v>
       </c>
       <c r="Q129" s="29" t="n">
-        <v>-9.35</v>
+        <v>-13.35</v>
       </c>
       <c r="R129" s="45" t="n"/>
       <c r="S129" s="21" t="n"/>
@@ -13684,13 +13680,13 @@
       </c>
       <c r="N130" s="51" t="n"/>
       <c r="O130" s="29" t="n">
-        <v>-18.9</v>
+        <v>-19.9</v>
       </c>
       <c r="P130" s="29" t="n">
-        <v>-1.6</v>
+        <v>-6.8</v>
       </c>
       <c r="Q130" s="29" t="n">
-        <v>-8.9</v>
+        <v>-12.81</v>
       </c>
       <c r="R130" s="45" t="n"/>
       <c r="S130" s="21" t="inlineStr">
@@ -14747,15 +14743,9 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O140" s="29" t="n">
-        <v>-14</v>
-      </c>
-      <c r="P140" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q140" s="29" t="n">
-        <v>-7.83</v>
-      </c>
+      <c r="O140" s="29" t="n"/>
+      <c r="P140" s="29" t="n"/>
+      <c r="Q140" s="29" t="n"/>
       <c r="R140" s="45" t="n"/>
       <c r="S140" s="21" t="n"/>
       <c r="T140" s="33" t="n"/>
@@ -14984,13 +14974,13 @@
       </c>
       <c r="N142" s="51" t="n"/>
       <c r="O142" s="29" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="P142" s="29" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q142" s="29" t="n">
-        <v>7.43</v>
+        <v>7.27</v>
       </c>
       <c r="R142" s="45" t="n"/>
       <c r="S142" s="21" t="inlineStr">
@@ -15101,13 +15091,13 @@
       </c>
       <c r="N143" s="51" t="n"/>
       <c r="O143" s="29" t="n">
-        <v>-5.9</v>
+        <v>-5</v>
       </c>
       <c r="P143" s="29" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q143" s="29" t="n">
-        <v>-2.06</v>
+        <v>-1.48</v>
       </c>
       <c r="R143" s="45" t="n"/>
       <c r="S143" s="21" t="inlineStr">
@@ -15329,13 +15319,13 @@
       </c>
       <c r="N145" s="51" t="n"/>
       <c r="O145" s="29" t="n">
-        <v>-0.3</v>
+        <v>-4.4</v>
       </c>
       <c r="P145" s="29" t="n">
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
       <c r="Q145" s="29" t="n">
-        <v>4.11</v>
+        <v>1.23</v>
       </c>
       <c r="R145" s="45" t="n"/>
       <c r="S145" s="21" t="inlineStr">
@@ -15454,13 +15444,13 @@
       </c>
       <c r="N146" s="51" t="n"/>
       <c r="O146" s="29" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="P146" s="29" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="Q146" s="29" t="n">
-        <v>13</v>
+        <v>11.97</v>
       </c>
       <c r="R146" s="45" t="n"/>
       <c r="S146" s="21" t="inlineStr">
@@ -15567,13 +15557,13 @@
       </c>
       <c r="N147" s="51" t="n"/>
       <c r="O147" s="29" t="n">
-        <v>2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="P147" s="29" t="n">
-        <v>12.4</v>
+        <v>11.9</v>
       </c>
       <c r="Q147" s="29" t="n">
-        <v>7.46</v>
+        <v>3.91</v>
       </c>
       <c r="R147" s="45" t="n"/>
       <c r="S147" s="21" t="inlineStr">
@@ -15688,13 +15678,13 @@
       </c>
       <c r="N148" s="51" t="n"/>
       <c r="O148" s="29" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="P148" s="29" t="n">
-        <v>17.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q148" s="29" t="n">
-        <v>12.4</v>
+        <v>8.08</v>
       </c>
       <c r="R148" s="45" t="n"/>
       <c r="S148" s="21" t="inlineStr">
@@ -15809,13 +15799,13 @@
       </c>
       <c r="N149" s="51" t="n"/>
       <c r="O149" s="29" t="n">
-        <v>1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="P149" s="29" t="n">
-        <v>9.699999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="Q149" s="29" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="R149" s="45" t="n"/>
       <c r="S149" s="21" t="inlineStr">
@@ -15930,13 +15920,13 @@
       </c>
       <c r="N150" s="51" t="n"/>
       <c r="O150" s="29" t="n">
-        <v>12</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P150" s="29" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="Q150" s="29" t="n">
-        <v>13.61</v>
+        <v>12.39</v>
       </c>
       <c r="R150" s="45" t="n"/>
       <c r="S150" s="21" t="inlineStr">
@@ -16047,13 +16037,13 @@
       </c>
       <c r="N151" s="51" t="n"/>
       <c r="O151" s="29" t="n">
-        <v>14.2</v>
+        <v>9.6</v>
       </c>
       <c r="P151" s="29" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Q151" s="29" t="n">
-        <v>15.45</v>
+        <v>15.16</v>
       </c>
       <c r="R151" s="45" t="n"/>
       <c r="S151" s="21" t="inlineStr">
@@ -16164,13 +16154,13 @@
       </c>
       <c r="N152" s="51" t="n"/>
       <c r="O152" s="29" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="P152" s="29" t="n">
-        <v>13.8</v>
+        <v>15.2</v>
       </c>
       <c r="Q152" s="29" t="n">
-        <v>12.34</v>
+        <v>12.26</v>
       </c>
       <c r="R152" s="45" t="n"/>
       <c r="S152" s="21" t="inlineStr">
@@ -16388,13 +16378,13 @@
       </c>
       <c r="N154" s="51" t="n"/>
       <c r="O154" s="29" t="n">
-        <v>17.4</v>
+        <v>16.1</v>
       </c>
       <c r="P154" s="29" t="n">
-        <v>27.3</v>
+        <v>23.8</v>
       </c>
       <c r="Q154" s="29" t="n">
-        <v>21.91</v>
+        <v>18.54</v>
       </c>
       <c r="R154" s="45" t="n"/>
       <c r="S154" s="21" t="inlineStr">
@@ -16505,13 +16495,13 @@
       </c>
       <c r="N155" s="51" t="n"/>
       <c r="O155" s="29" t="n">
-        <v>19.3</v>
+        <v>18.8</v>
       </c>
       <c r="P155" s="29" t="n">
-        <v>27.4</v>
+        <v>24.9</v>
       </c>
       <c r="Q155" s="29" t="n">
-        <v>23.11</v>
+        <v>21.61</v>
       </c>
       <c r="R155" s="45" t="n"/>
       <c r="S155" s="21" t="inlineStr">
@@ -16622,13 +16612,13 @@
       </c>
       <c r="N156" s="51" t="n"/>
       <c r="O156" s="29" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P156" s="29" t="n">
-        <v>25.7</v>
+        <v>21.1</v>
       </c>
       <c r="Q156" s="29" t="n">
-        <v>20.5</v>
+        <v>18.25</v>
       </c>
       <c r="R156" s="45" t="n"/>
       <c r="S156" s="21" t="inlineStr">
@@ -16739,13 +16729,13 @@
       </c>
       <c r="N157" s="51" t="n"/>
       <c r="O157" s="29" t="n">
-        <v>13.7</v>
+        <v>14.7</v>
       </c>
       <c r="P157" s="29" t="n">
-        <v>24.5</v>
+        <v>21.2</v>
       </c>
       <c r="Q157" s="29" t="n">
-        <v>19.01</v>
+        <v>18.05</v>
       </c>
       <c r="R157" s="45" t="n"/>
       <c r="S157" s="21" t="inlineStr">
@@ -16856,13 +16846,13 @@
       </c>
       <c r="N158" s="51" t="n"/>
       <c r="O158" s="29" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="P158" s="29" t="n">
-        <v>25.8</v>
+        <v>20.4</v>
       </c>
       <c r="Q158" s="29" t="n">
-        <v>20.56</v>
+        <v>18.49</v>
       </c>
       <c r="R158" s="45" t="n"/>
       <c r="S158" s="21" t="inlineStr">
@@ -17076,13 +17066,13 @@
       </c>
       <c r="N160" s="51" t="n"/>
       <c r="O160" s="29" t="n">
-        <v>21.1</v>
+        <v>19.6</v>
       </c>
       <c r="P160" s="29" t="n">
-        <v>26.2</v>
+        <v>28</v>
       </c>
       <c r="Q160" s="29" t="n">
-        <v>22.35</v>
+        <v>23.02</v>
       </c>
       <c r="R160" s="45" t="n"/>
       <c r="S160" s="21" t="inlineStr">
@@ -17193,13 +17183,13 @@
       </c>
       <c r="N161" s="51" t="n"/>
       <c r="O161" s="29" t="n">
-        <v>18.7</v>
+        <v>19.2</v>
       </c>
       <c r="P161" s="29" t="n">
-        <v>31.2</v>
+        <v>31.5</v>
       </c>
       <c r="Q161" s="29" t="n">
-        <v>24.11</v>
+        <v>24.61</v>
       </c>
       <c r="R161" s="45" t="n"/>
       <c r="S161" s="21" t="inlineStr">
@@ -17512,13 +17502,13 @@
       </c>
       <c r="N164" s="51" t="n"/>
       <c r="O164" s="29" t="n">
-        <v>24.8</v>
+        <v>25.4</v>
       </c>
       <c r="P164" s="29" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="Q164" s="29" t="n">
-        <v>28.04</v>
+        <v>27.9</v>
       </c>
       <c r="R164" s="45" t="n"/>
       <c r="S164" s="21" t="inlineStr">
@@ -17621,13 +17611,13 @@
       </c>
       <c r="N165" s="51" t="n"/>
       <c r="O165" s="29" t="n">
-        <v>21.9</v>
+        <v>22.5</v>
       </c>
       <c r="P165" s="29" t="n">
-        <v>32.2</v>
+        <v>31.5</v>
       </c>
       <c r="Q165" s="29" t="n">
-        <v>26.55</v>
+        <v>26.45</v>
       </c>
       <c r="R165" s="45" t="n"/>
       <c r="S165" s="21" t="inlineStr">
@@ -17738,13 +17728,13 @@
       </c>
       <c r="N166" s="51" t="n"/>
       <c r="O166" s="29" t="n">
-        <v>11.3</v>
+        <v>14.2</v>
       </c>
       <c r="P166" s="29" t="n">
-        <v>26.3</v>
+        <v>24.3</v>
       </c>
       <c r="Q166" s="29" t="n">
-        <v>17.84</v>
+        <v>18.91</v>
       </c>
       <c r="R166" s="45" t="n"/>
       <c r="S166" s="21" t="inlineStr">
@@ -17855,13 +17845,13 @@
       </c>
       <c r="N167" s="51" t="n"/>
       <c r="O167" s="29" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="P167" s="29" t="n">
-        <v>20.6</v>
+        <v>18.1</v>
       </c>
       <c r="Q167" s="29" t="n">
-        <v>17.43</v>
+        <v>16.26</v>
       </c>
       <c r="R167" s="45" t="n"/>
       <c r="S167" s="21" t="inlineStr">
@@ -17972,13 +17962,13 @@
       </c>
       <c r="N168" s="51" t="n"/>
       <c r="O168" s="29" t="n">
-        <v>19.9</v>
+        <v>16.7</v>
       </c>
       <c r="P168" s="29" t="n">
-        <v>22.5</v>
+        <v>19.8</v>
       </c>
       <c r="Q168" s="29" t="n">
-        <v>21.06</v>
+        <v>18.03</v>
       </c>
       <c r="R168" s="45" t="n"/>
       <c r="S168" s="21" t="inlineStr">
@@ -18180,13 +18170,13 @@
       </c>
       <c r="N170" s="51" t="n"/>
       <c r="O170" s="29" t="n">
-        <v>16.1</v>
+        <v>15.7</v>
       </c>
       <c r="P170" s="29" t="n">
-        <v>20.1</v>
+        <v>18.5</v>
       </c>
       <c r="Q170" s="29" t="n">
-        <v>17.77</v>
+        <v>16.6</v>
       </c>
       <c r="R170" s="45" t="n"/>
       <c r="S170" s="21" t="inlineStr">
@@ -18301,13 +18291,13 @@
       </c>
       <c r="N171" s="51" t="n"/>
       <c r="O171" s="29" t="n">
-        <v>-1.1</v>
+        <v>1.4</v>
       </c>
       <c r="P171" s="29" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="Q171" s="29" t="n">
-        <v>8.84</v>
+        <v>7.92</v>
       </c>
       <c r="R171" s="45" t="n"/>
       <c r="S171" s="21" t="inlineStr">
@@ -18893,14 +18883,12 @@
       </c>
       <c r="N177" s="51" t="n"/>
       <c r="O177" s="29" t="n">
-        <v>-9.6</v>
+        <v>-10</v>
       </c>
       <c r="P177" s="29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q177" s="29" t="n">
-        <v>-2.36</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="Q177" s="29" t="n"/>
       <c r="R177" s="45" t="n"/>
       <c r="S177" s="21" t="inlineStr">
         <is>
@@ -19006,13 +18994,13 @@
       </c>
       <c r="N178" s="51" t="n"/>
       <c r="O178" s="29" t="n">
-        <v>-9</v>
+        <v>-10.5</v>
       </c>
       <c r="P178" s="29" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="Q178" s="29" t="n">
-        <v>-1.38</v>
+        <v>-2.2</v>
       </c>
       <c r="R178" s="45" t="n"/>
       <c r="S178" s="21" t="inlineStr">
@@ -19121,13 +19109,13 @@
       </c>
       <c r="N179" s="51" t="n"/>
       <c r="O179" s="29" t="n">
-        <v>9.4</v>
+        <v>5.2</v>
       </c>
       <c r="P179" s="29" t="n">
-        <v>17.9</v>
+        <v>15.5</v>
       </c>
       <c r="Q179" s="29" t="n">
-        <v>13.09</v>
+        <v>11.41</v>
       </c>
       <c r="R179" s="45" t="n"/>
       <c r="S179" s="21" t="inlineStr">
@@ -19226,13 +19214,13 @@
       </c>
       <c r="N180" s="51" t="n"/>
       <c r="O180" s="29" t="n">
-        <v>16.3</v>
+        <v>17.5</v>
       </c>
       <c r="P180" s="29" t="n">
-        <v>23.9</v>
+        <v>21.5</v>
       </c>
       <c r="Q180" s="29" t="n">
-        <v>19.74</v>
+        <v>18.86</v>
       </c>
       <c r="R180" s="45" t="n"/>
       <c r="S180" s="21" t="inlineStr">
@@ -19335,13 +19323,13 @@
       </c>
       <c r="N181" s="51" t="n"/>
       <c r="O181" s="29" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="P181" s="29" t="n">
-        <v>11.8</v>
+        <v>16.8</v>
       </c>
       <c r="Q181" s="29" t="n">
-        <v>8.890000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="R181" s="45" t="n"/>
       <c r="S181" s="21" t="inlineStr">
@@ -19579,13 +19567,13 @@
         </is>
       </c>
       <c r="O183" s="29" t="n">
-        <v>-11</v>
+        <v>-12.3</v>
       </c>
       <c r="P183" s="29" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q183" s="29" t="n">
-        <v>-5.28</v>
+        <v>-4.56</v>
       </c>
       <c r="R183" s="45" t="n"/>
       <c r="S183" s="21" t="inlineStr">
@@ -19700,13 +19688,13 @@
       </c>
       <c r="N184" s="51" t="n"/>
       <c r="O184" s="29" t="n">
-        <v>-21.8</v>
+        <v>-16</v>
       </c>
       <c r="P184" s="29" t="n">
-        <v>-8</v>
+        <v>-4.3</v>
       </c>
       <c r="Q184" s="29" t="n">
-        <v>-15.21</v>
+        <v>-10.87</v>
       </c>
       <c r="R184" s="45" t="n"/>
       <c r="S184" s="21" t="inlineStr">
@@ -19821,13 +19809,13 @@
       </c>
       <c r="N185" s="51" t="n"/>
       <c r="O185" s="29" t="n">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="P185" s="29" t="n">
-        <v>15.7</v>
+        <v>17.8</v>
       </c>
       <c r="Q185" s="29" t="n">
-        <v>11.81</v>
+        <v>11.65</v>
       </c>
       <c r="R185" s="45" t="n"/>
       <c r="S185" s="21" t="inlineStr">
@@ -19934,14 +19922,12 @@
       </c>
       <c r="N186" s="51" t="n"/>
       <c r="O186" s="29" t="n">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="P186" s="29" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="Q186" s="29" t="n">
-        <v>18.6</v>
-      </c>
+        <v>20.9</v>
+      </c>
+      <c r="Q186" s="29" t="n"/>
       <c r="R186" s="45" t="n"/>
       <c r="S186" s="21" t="inlineStr">
         <is>
@@ -20051,13 +20037,13 @@
       </c>
       <c r="N187" s="51" t="n"/>
       <c r="O187" s="29" t="n">
-        <v>22.7</v>
+        <v>23.9</v>
       </c>
       <c r="P187" s="29" t="n">
-        <v>36.7</v>
+        <v>33.5</v>
       </c>
       <c r="Q187" s="29" t="n">
-        <v>28.54</v>
+        <v>28.46</v>
       </c>
       <c r="R187" s="45" t="n"/>
       <c r="S187" s="21" t="inlineStr">
@@ -20164,13 +20150,13 @@
       </c>
       <c r="N188" s="51" t="n"/>
       <c r="O188" s="29" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="P188" s="29" t="n">
-        <v>14.7</v>
+        <v>10.8</v>
       </c>
       <c r="Q188" s="29" t="n">
-        <v>10.73</v>
+        <v>7.23</v>
       </c>
       <c r="R188" s="45" t="n"/>
       <c r="S188" s="21" t="inlineStr">
@@ -20367,15 +20353,9 @@
           <t>🔵</t>
         </is>
       </c>
-      <c r="O190" s="29" t="n">
-        <v>-16.4</v>
-      </c>
-      <c r="P190" s="29" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="Q190" s="29" t="n">
-        <v>-12.2</v>
-      </c>
+      <c r="O190" s="29" t="n"/>
+      <c r="P190" s="29" t="n"/>
+      <c r="Q190" s="29" t="n"/>
       <c r="R190" s="45" t="n"/>
       <c r="S190" s="21" t="n"/>
       <c r="T190" s="33" t="n"/>
@@ -20774,13 +20754,13 @@
         </is>
       </c>
       <c r="O194" s="29" t="n">
-        <v>-2.3</v>
+        <v>-9</v>
       </c>
       <c r="P194" s="29" t="n">
-        <v>4.8</v>
+        <v>-0.8</v>
       </c>
       <c r="Q194" s="29" t="n">
-        <v>-0.03</v>
+        <v>-5.06</v>
       </c>
       <c r="R194" s="45" t="inlineStr">
         <is>
@@ -20883,10 +20863,10 @@
       </c>
       <c r="N195" s="51" t="n"/>
       <c r="O195" s="29" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="P195" s="29" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="Q195" s="29" t="n"/>
       <c r="R195" s="45" t="n"/>
@@ -20990,12 +20970,14 @@
         </is>
       </c>
       <c r="O196" s="29" t="n">
-        <v>-28.8</v>
+        <v>-24.5</v>
       </c>
       <c r="P196" s="29" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="Q196" s="29" t="n"/>
+        <v>-5.2</v>
+      </c>
+      <c r="Q196" s="29" t="n">
+        <v>-17.3</v>
+      </c>
       <c r="R196" s="45" t="n"/>
       <c r="S196" s="21" t="n"/>
       <c r="T196" s="33" t="n"/>
@@ -21101,14 +21083,12 @@
         </is>
       </c>
       <c r="O197" s="29" t="n">
-        <v>-10.4</v>
+        <v>-21.3</v>
       </c>
       <c r="P197" s="29" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q197" s="29" t="n">
-        <v>-5.23</v>
-      </c>
+        <v>-10.2</v>
+      </c>
+      <c r="Q197" s="29" t="n"/>
       <c r="R197" s="45" t="n"/>
       <c r="S197" s="21" t="n"/>
       <c r="T197" s="33" t="inlineStr">
@@ -22004,13 +21984,13 @@
         </is>
       </c>
       <c r="O206" s="29" t="n">
-        <v>-22.1</v>
+        <v>-23.9</v>
       </c>
       <c r="P206" s="29" t="n">
-        <v>-0.3</v>
+        <v>-7.1</v>
       </c>
       <c r="Q206" s="29" t="n">
-        <v>-11.8</v>
+        <v>-15.7</v>
       </c>
       <c r="R206" s="45" t="n"/>
       <c r="S206" s="21" t="n"/>
@@ -22113,10 +22093,10 @@
         </is>
       </c>
       <c r="O207" s="29" t="n">
-        <v>-18.1</v>
+        <v>-20.6</v>
       </c>
       <c r="P207" s="29" t="n">
-        <v>-0.4</v>
+        <v>-4.9</v>
       </c>
       <c r="Q207" s="29" t="n"/>
       <c r="R207" s="45" t="n"/>
@@ -22224,10 +22204,10 @@
         </is>
       </c>
       <c r="O208" s="29" t="n">
-        <v>-17.6</v>
+        <v>-21.2</v>
       </c>
       <c r="P208" s="29" t="n">
-        <v>0.2</v>
+        <v>-6.3</v>
       </c>
       <c r="Q208" s="29" t="n"/>
       <c r="R208" s="45" t="inlineStr">
@@ -22533,13 +22513,13 @@
         </is>
       </c>
       <c r="O211" s="29" t="n">
-        <v>-30.6</v>
+        <v>-27.3</v>
       </c>
       <c r="P211" s="29" t="n">
-        <v>-8.4</v>
+        <v>-8.6</v>
       </c>
       <c r="Q211" s="29" t="n">
-        <v>-21.9</v>
+        <v>-19.9</v>
       </c>
       <c r="R211" s="45" t="n"/>
       <c r="S211" s="21" t="n"/>
@@ -22646,14 +22626,12 @@
         </is>
       </c>
       <c r="O212" s="29" t="n">
-        <v>-25.1</v>
+        <v>-22</v>
       </c>
       <c r="P212" s="29" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="Q212" s="29" t="n">
-        <v>-18.2</v>
-      </c>
+        <v>-0.2</v>
+      </c>
+      <c r="Q212" s="29" t="n"/>
       <c r="R212" s="45" t="inlineStr">
         <is>
           <t>2024-02-18</t>
@@ -22759,13 +22737,13 @@
       </c>
       <c r="N213" s="51" t="n"/>
       <c r="O213" s="29" t="n">
-        <v>-27.5</v>
+        <v>-24.1</v>
       </c>
       <c r="P213" s="29" t="n">
-        <v>-6</v>
+        <v>-4.3</v>
       </c>
       <c r="Q213" s="29" t="n">
-        <v>-19.6</v>
+        <v>-17</v>
       </c>
       <c r="R213" s="45" t="n"/>
       <c r="S213" s="21" t="n"/>
@@ -22869,9 +22847,7 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="O214" s="29" t="n">
-        <v>-45.4</v>
-      </c>
+      <c r="O214" s="29" t="n"/>
       <c r="P214" s="29" t="n"/>
       <c r="Q214" s="29" t="n"/>
       <c r="R214" s="45" t="n"/>
@@ -22963,7 +22939,7 @@
         </is>
       </c>
       <c r="O215" s="29" t="n">
-        <v>-46.6</v>
+        <v>-45.7</v>
       </c>
       <c r="P215" s="29" t="n"/>
       <c r="Q215" s="29" t="n"/>
@@ -23735,13 +23711,13 @@
       </c>
       <c r="N223" s="51" t="n"/>
       <c r="O223" s="29" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="P223" s="29" t="n">
-        <v>10.4</v>
+        <v>8.9</v>
       </c>
       <c r="Q223" s="29" t="n">
-        <v>8.31</v>
+        <v>6.26</v>
       </c>
       <c r="R223" s="45" t="n"/>
       <c r="S223" s="21" t="inlineStr">
@@ -24139,13 +24115,13 @@
       </c>
       <c r="N227" s="51" t="n"/>
       <c r="O227" s="29" t="n">
-        <v>-4.9</v>
+        <v>-6.1</v>
       </c>
       <c r="P227" s="29" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="Q227" s="29" t="n">
-        <v>-3.45</v>
+        <v>-3.57</v>
       </c>
       <c r="R227" s="45" t="n"/>
       <c r="S227" s="21" t="inlineStr">
@@ -24349,13 +24325,13 @@
       </c>
       <c r="N229" s="51" t="n"/>
       <c r="O229" s="29" t="n">
-        <v>-5.8</v>
+        <v>0</v>
       </c>
       <c r="P229" s="29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q229" s="29" t="n">
-        <v>-2.74</v>
+        <v>1.2</v>
       </c>
       <c r="R229" s="45" t="n"/>
       <c r="S229" s="21" t="inlineStr">
@@ -24755,13 +24731,13 @@
       </c>
       <c r="N233" s="51" t="n"/>
       <c r="O233" s="29" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="P233" s="29" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="Q233" s="29" t="n">
         <v>-7.2</v>
-      </c>
-      <c r="P233" s="29" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="Q233" s="29" t="n">
-        <v>-5.26</v>
       </c>
       <c r="R233" s="45" t="n"/>
       <c r="S233" s="21" t="inlineStr">
@@ -25349,13 +25325,13 @@
       </c>
       <c r="N239" s="51" t="n"/>
       <c r="O239" s="29" t="n">
-        <v>-0.4</v>
+        <v>1</v>
       </c>
       <c r="P239" s="29" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="Q239" s="29" t="n">
-        <v>0.78</v>
+        <v>1.91</v>
       </c>
       <c r="R239" s="45" t="n"/>
       <c r="S239" s="21" t="inlineStr">
@@ -25462,13 +25438,13 @@
       </c>
       <c r="N240" s="51" t="n"/>
       <c r="O240" s="29" t="n">
-        <v>-4.8</v>
+        <v>-5.8</v>
       </c>
       <c r="P240" s="29" t="n">
-        <v>-0.4</v>
+        <v>3</v>
       </c>
       <c r="Q240" s="29" t="n">
-        <v>-3.46</v>
+        <v>-1.68</v>
       </c>
       <c r="R240" s="45" t="n"/>
       <c r="S240" s="21" t="inlineStr">
@@ -26440,13 +26416,13 @@
         </is>
       </c>
       <c r="O250" s="29" t="n">
-        <v>-19</v>
+        <v>-15.9</v>
       </c>
       <c r="P250" s="29" t="n">
-        <v>-1.5</v>
+        <v>-7</v>
       </c>
       <c r="Q250" s="29" t="n">
-        <v>-9.59</v>
+        <v>-10.24</v>
       </c>
       <c r="R250" s="45" t="n"/>
       <c r="S250" s="21" t="inlineStr">
@@ -28149,13 +28125,13 @@
       </c>
       <c r="N268" s="51" t="n"/>
       <c r="O268" s="29" t="n">
-        <v>-33.1</v>
+        <v>-33.8</v>
       </c>
       <c r="P268" s="29" t="n">
-        <v>-13.5</v>
+        <v>-15.2</v>
       </c>
       <c r="Q268" s="29" t="n">
-        <v>-25.53</v>
+        <v>-23</v>
       </c>
       <c r="R268" s="45" t="n"/>
       <c r="S268" s="21" t="n"/>
@@ -29190,13 +29166,13 @@
         </is>
       </c>
       <c r="O279" s="29" t="n">
-        <v>-14.4</v>
+        <v>-16.4</v>
       </c>
       <c r="P279" s="29" t="n">
-        <v>-13.4</v>
+        <v>-14</v>
       </c>
       <c r="Q279" s="29" t="n">
-        <v>-13.75</v>
+        <v>-15.19</v>
       </c>
       <c r="R279" s="45" t="n"/>
       <c r="S279" s="21" t="inlineStr">
@@ -29692,10 +29668,10 @@
         </is>
       </c>
       <c r="O284" s="29" t="n">
-        <v>-19.7</v>
+        <v>-24.2</v>
       </c>
       <c r="P284" s="29" t="n">
-        <v>-4.7</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="Q284" s="29" t="n"/>
       <c r="R284" s="45" t="n"/>
@@ -30077,10 +30053,10 @@
         </is>
       </c>
       <c r="O288" s="29" t="n">
-        <v>-62.8</v>
+        <v>-61.3</v>
       </c>
       <c r="P288" s="29" t="n">
-        <v>-49.3</v>
+        <v>-50.1</v>
       </c>
       <c r="Q288" s="29" t="n"/>
       <c r="R288" s="45" t="n"/>
@@ -30273,13 +30249,13 @@
       </c>
       <c r="N290" s="51" t="n"/>
       <c r="O290" s="29" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="P290" s="29" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q290" s="29" t="n">
-        <v>3.34</v>
+        <v>4.47</v>
       </c>
       <c r="R290" s="45" t="n"/>
       <c r="S290" s="21" t="inlineStr">
@@ -30489,13 +30465,13 @@
         </is>
       </c>
       <c r="O292" s="29" t="n">
-        <v>1</v>
+        <v>-1.9</v>
       </c>
       <c r="P292" s="29" t="n">
         <v>4.2</v>
       </c>
       <c r="Q292" s="29" t="n">
-        <v>2.85</v>
+        <v>1.49</v>
       </c>
       <c r="R292" s="45" t="n"/>
       <c r="S292" s="21" t="inlineStr">
@@ -34914,12 +34890,8 @@
         </is>
       </c>
       <c r="N338" s="51" t="n"/>
-      <c r="O338" s="29" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="P338" s="29" t="n">
-        <v>-1.9</v>
-      </c>
+      <c r="O338" s="29" t="n"/>
+      <c r="P338" s="29" t="n"/>
       <c r="Q338" s="29" t="n"/>
       <c r="R338" s="45" t="n"/>
       <c r="S338" s="21" t="n"/>
@@ -35308,8 +35280,12 @@
         </is>
       </c>
       <c r="N342" s="51" t="n"/>
-      <c r="O342" s="29" t="n"/>
-      <c r="P342" s="29" t="n"/>
+      <c r="O342" s="29" t="n">
+        <v>-22.3</v>
+      </c>
+      <c r="P342" s="29" t="n">
+        <v>-5.7</v>
+      </c>
       <c r="Q342" s="29" t="n"/>
       <c r="R342" s="45" t="n"/>
       <c r="S342" s="21" t="n"/>
@@ -35378,10 +35354,20 @@
       <c r="C343" s="41" t="n"/>
       <c r="D343" s="2" t="n"/>
       <c r="E343" s="3" t="n"/>
-      <c r="F343" s="35" t="n"/>
-      <c r="G343" s="26" t="n"/>
-      <c r="H343" s="26" t="n"/>
-      <c r="I343" s="2" t="n"/>
+      <c r="F343" s="35" t="inlineStr">
+        <is>
+          <t>C0063</t>
+        </is>
+      </c>
+      <c r="G343" s="26" t="n">
+        <v>51.693</v>
+      </c>
+      <c r="H343" s="26" t="n">
+        <v>121.859</v>
+      </c>
+      <c r="I343" s="2" t="n">
+        <v>687.6</v>
+      </c>
       <c r="J343" s="24" t="n">
         <v>12</v>
       </c>
@@ -35393,7 +35379,7 @@
       <c r="L343" s="51" t="n"/>
       <c r="M343" s="13" t="inlineStr">
         <is>
-          <t>阿龙山防火办</t>
+          <t>阿龙山</t>
         </is>
       </c>
       <c r="N343" s="51" t="n"/>
@@ -35467,20 +35453,10 @@
       <c r="C344" s="41" t="n"/>
       <c r="D344" s="2" t="n"/>
       <c r="E344" s="3" t="n"/>
-      <c r="F344" s="35" t="inlineStr">
-        <is>
-          <t>C0064</t>
-        </is>
-      </c>
-      <c r="G344" s="26" t="n">
-        <v>51.3308</v>
-      </c>
-      <c r="H344" s="26" t="n">
-        <v>121.5136</v>
-      </c>
-      <c r="I344" s="2" t="n">
-        <v>798.9</v>
-      </c>
+      <c r="F344" s="35" t="n"/>
+      <c r="G344" s="26" t="n"/>
+      <c r="H344" s="26" t="n"/>
+      <c r="I344" s="2" t="n"/>
       <c r="J344" s="24" t="n">
         <v>12</v>
       </c>
@@ -35492,7 +35468,7 @@
       <c r="L344" s="51" t="n"/>
       <c r="M344" s="13" t="inlineStr">
         <is>
-          <t>金河</t>
+          <t>阿龙山防火办</t>
         </is>
       </c>
       <c r="N344" s="51" t="n"/>
@@ -35568,12 +35544,18 @@
       <c r="E345" s="3" t="n"/>
       <c r="F345" s="35" t="inlineStr">
         <is>
-          <t>C0363</t>
-        </is>
-      </c>
-      <c r="G345" s="26" t="n"/>
-      <c r="H345" s="26" t="n"/>
-      <c r="I345" s="2" t="n"/>
+          <t>C0064</t>
+        </is>
+      </c>
+      <c r="G345" s="26" t="n">
+        <v>51.3308</v>
+      </c>
+      <c r="H345" s="26" t="n">
+        <v>121.5136</v>
+      </c>
+      <c r="I345" s="2" t="n">
+        <v>798.9</v>
+      </c>
       <c r="J345" s="24" t="n">
         <v>12</v>
       </c>
@@ -35585,7 +35567,7 @@
       <c r="L345" s="51" t="n"/>
       <c r="M345" s="13" t="inlineStr">
         <is>
-          <t>谢尔塔拉五队</t>
+          <t>金河</t>
         </is>
       </c>
       <c r="N345" s="51" t="n"/>
@@ -35597,7 +35579,7 @@
       <c r="T345" s="33" t="n"/>
       <c r="U345" s="37" t="inlineStr">
         <is>
-          <t>海拉尔</t>
+          <t>根河</t>
         </is>
       </c>
       <c r="V345" s="2" t="inlineStr">
@@ -35628,7 +35610,7 @@
       </c>
       <c r="AB345" s="2" t="inlineStr">
         <is>
-          <t>海拉尔区</t>
+          <t>根河市</t>
         </is>
       </c>
       <c r="AC345" s="2" t="n"/>
@@ -35644,7 +35626,11 @@
         </is>
       </c>
       <c r="AG345" s="3" t="n"/>
-      <c r="AH345" s="2" t="n"/>
+      <c r="AH345" s="2" t="inlineStr">
+        <is>
+          <t>大兴安岭</t>
+        </is>
+      </c>
       <c r="AI345" s="2" t="n"/>
     </row>
     <row r="346" ht="24" customHeight="1" s="54">
@@ -35657,7 +35643,7 @@
       <c r="E346" s="3" t="n"/>
       <c r="F346" s="35" t="inlineStr">
         <is>
-          <t>C0380</t>
+          <t>C0363</t>
         </is>
       </c>
       <c r="G346" s="26" t="n"/>
@@ -35674,7 +35660,7 @@
       <c r="L346" s="51" t="n"/>
       <c r="M346" s="13" t="inlineStr">
         <is>
-          <t>谢尔塔拉八队</t>
+          <t>谢尔塔拉五队</t>
         </is>
       </c>
       <c r="N346" s="51" t="n"/>
@@ -35741,25 +35727,17 @@
         <v>346</v>
       </c>
       <c r="B347" s="2" t="n"/>
-      <c r="C347" s="41" t="inlineStr">
-        <is>
-          <t>50514</t>
-        </is>
-      </c>
+      <c r="C347" s="41" t="n"/>
       <c r="D347" s="2" t="n"/>
-      <c r="E347" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F347" s="35" t="n"/>
-      <c r="G347" s="26" t="n">
-        <v>49.5817</v>
-      </c>
-      <c r="H347" s="26" t="n">
-        <v>117.3269</v>
-      </c>
-      <c r="I347" s="2" t="n">
-        <v>660.4</v>
-      </c>
+      <c r="E347" s="3" t="n"/>
+      <c r="F347" s="35" t="inlineStr">
+        <is>
+          <t>C0380</t>
+        </is>
+      </c>
+      <c r="G347" s="26" t="n"/>
+      <c r="H347" s="26" t="n"/>
+      <c r="I347" s="2" t="n"/>
       <c r="J347" s="24" t="n">
         <v>12</v>
       </c>
@@ -35771,7 +35749,7 @@
       <c r="L347" s="51" t="n"/>
       <c r="M347" s="13" t="inlineStr">
         <is>
-          <t>满洲里</t>
+          <t>谢尔塔拉八队</t>
         </is>
       </c>
       <c r="N347" s="51" t="n"/>
@@ -35783,7 +35761,7 @@
       <c r="T347" s="33" t="n"/>
       <c r="U347" s="37" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>海拉尔</t>
         </is>
       </c>
       <c r="V347" s="2" t="inlineStr">
@@ -35814,7 +35792,7 @@
       </c>
       <c r="AB347" s="2" t="inlineStr">
         <is>
-          <t>满洲里市</t>
+          <t>海拉尔区</t>
         </is>
       </c>
       <c r="AC347" s="2" t="n"/>
@@ -35838,22 +35816,24 @@
         <v>347</v>
       </c>
       <c r="B348" s="2" t="n"/>
-      <c r="C348" s="41" t="n"/>
+      <c r="C348" s="41" t="inlineStr">
+        <is>
+          <t>50514</t>
+        </is>
+      </c>
       <c r="D348" s="2" t="n"/>
-      <c r="E348" s="3" t="n"/>
-      <c r="F348" s="35" t="inlineStr">
-        <is>
-          <t>C0107</t>
-        </is>
-      </c>
+      <c r="E348" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F348" s="35" t="n"/>
       <c r="G348" s="26" t="n">
-        <v>49.6797</v>
+        <v>49.5817</v>
       </c>
       <c r="H348" s="26" t="n">
-        <v>116.8136</v>
+        <v>117.3269</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>710</v>
+        <v>660.4</v>
       </c>
       <c r="J348" s="24" t="n">
         <v>12</v>
@@ -35866,7 +35846,7 @@
       <c r="L348" s="51" t="n"/>
       <c r="M348" s="13" t="inlineStr">
         <is>
-          <t>新佰路克</t>
+          <t>满洲里</t>
         </is>
       </c>
       <c r="N348" s="51" t="n"/>
@@ -35878,7 +35858,7 @@
       <c r="T348" s="33" t="n"/>
       <c r="U348" s="37" t="inlineStr">
         <is>
-          <t>新巴尔虎右旗</t>
+          <t>呼伦贝尔</t>
         </is>
       </c>
       <c r="V348" s="2" t="inlineStr">
@@ -35909,7 +35889,7 @@
       </c>
       <c r="AB348" s="2" t="inlineStr">
         <is>
-          <t>新巴尔虎右旗</t>
+          <t>满洲里市</t>
         </is>
       </c>
       <c r="AC348" s="2" t="n"/>
@@ -35933,22 +35913,22 @@
         <v>348</v>
       </c>
       <c r="B349" s="2" t="n"/>
-      <c r="C349" s="41" t="n">
-        <v>50618</v>
-      </c>
+      <c r="C349" s="41" t="n"/>
       <c r="D349" s="2" t="n"/>
-      <c r="E349" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F349" s="35" t="n"/>
+      <c r="E349" s="3" t="n"/>
+      <c r="F349" s="35" t="inlineStr">
+        <is>
+          <t>C0107</t>
+        </is>
+      </c>
       <c r="G349" s="26" t="n">
-        <v>48.1864</v>
+        <v>49.6797</v>
       </c>
       <c r="H349" s="26" t="n">
-        <v>118.2614</v>
+        <v>116.8136</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>622</v>
+        <v>710</v>
       </c>
       <c r="J349" s="24" t="n">
         <v>12</v>
@@ -35961,7 +35941,7 @@
       <c r="L349" s="51" t="n"/>
       <c r="M349" s="13" t="inlineStr">
         <is>
-          <t>新巴尔虎左旗</t>
+          <t>新佰路克</t>
         </is>
       </c>
       <c r="N349" s="51" t="n"/>
@@ -35973,7 +35953,7 @@
       <c r="T349" s="33" t="n"/>
       <c r="U349" s="37" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>新巴尔虎右旗</t>
         </is>
       </c>
       <c r="V349" s="2" t="inlineStr">
@@ -36004,7 +35984,7 @@
       </c>
       <c r="AB349" s="2" t="inlineStr">
         <is>
-          <t>新巴尔虎左旗</t>
+          <t>新巴尔虎右旗</t>
         </is>
       </c>
       <c r="AC349" s="2" t="n"/>
@@ -36020,11 +36000,7 @@
         </is>
       </c>
       <c r="AG349" s="3" t="n"/>
-      <c r="AH349" s="2" t="inlineStr">
-        <is>
-          <t>大兴安岭</t>
-        </is>
-      </c>
+      <c r="AH349" s="2" t="n"/>
       <c r="AI349" s="2" t="n"/>
     </row>
     <row r="350" ht="24" customHeight="1" s="54">
@@ -36032,13 +36008,23 @@
         <v>349</v>
       </c>
       <c r="B350" s="2" t="n"/>
-      <c r="C350" s="41" t="n"/>
+      <c r="C350" s="41" t="n">
+        <v>50618</v>
+      </c>
       <c r="D350" s="2" t="n"/>
-      <c r="E350" s="3" t="n"/>
+      <c r="E350" s="3" t="n">
+        <v>99999</v>
+      </c>
       <c r="F350" s="35" t="n"/>
-      <c r="G350" s="26" t="n"/>
-      <c r="H350" s="26" t="n"/>
-      <c r="I350" s="2" t="n"/>
+      <c r="G350" s="26" t="n">
+        <v>48.1864</v>
+      </c>
+      <c r="H350" s="26" t="n">
+        <v>118.2614</v>
+      </c>
+      <c r="I350" s="2" t="n">
+        <v>622</v>
+      </c>
       <c r="J350" s="24" t="n">
         <v>12</v>
       </c>
@@ -36050,7 +36036,7 @@
       <c r="L350" s="51" t="n"/>
       <c r="M350" s="13" t="inlineStr">
         <is>
-          <t>罕达盖</t>
+          <t>新巴尔虎左旗</t>
         </is>
       </c>
       <c r="N350" s="51" t="n"/>
@@ -36062,7 +36048,7 @@
       <c r="T350" s="33" t="n"/>
       <c r="U350" s="37" t="inlineStr">
         <is>
-          <t>新巴尔虎左旗</t>
+          <t>呼伦贝尔</t>
         </is>
       </c>
       <c r="V350" s="2" t="inlineStr">
@@ -36109,7 +36095,11 @@
         </is>
       </c>
       <c r="AG350" s="3" t="n"/>
-      <c r="AH350" s="2" t="n"/>
+      <c r="AH350" s="2" t="inlineStr">
+        <is>
+          <t>大兴安岭</t>
+        </is>
+      </c>
       <c r="AI350" s="2" t="n"/>
     </row>
     <row r="351" ht="24" customHeight="1" s="54">
@@ -36120,20 +36110,10 @@
       <c r="C351" s="41" t="n"/>
       <c r="D351" s="2" t="n"/>
       <c r="E351" s="3" t="n"/>
-      <c r="F351" s="35" t="inlineStr">
-        <is>
-          <t>C0022</t>
-        </is>
-      </c>
-      <c r="G351" s="26" t="n">
-        <v>50.6378</v>
-      </c>
-      <c r="H351" s="26" t="n">
-        <v>121.5664</v>
-      </c>
-      <c r="I351" s="2" t="n">
-        <v>733.8</v>
-      </c>
+      <c r="F351" s="35" t="n"/>
+      <c r="G351" s="26" t="n"/>
+      <c r="H351" s="26" t="n"/>
+      <c r="I351" s="2" t="n"/>
       <c r="J351" s="24" t="n">
         <v>12</v>
       </c>
@@ -36145,7 +36125,7 @@
       <c r="L351" s="51" t="n"/>
       <c r="M351" s="13" t="inlineStr">
         <is>
-          <t>伊图里河</t>
+          <t>罕达盖</t>
         </is>
       </c>
       <c r="N351" s="51" t="n"/>
@@ -36157,7 +36137,7 @@
       <c r="T351" s="33" t="n"/>
       <c r="U351" s="37" t="inlineStr">
         <is>
-          <t>牙克石</t>
+          <t>新巴尔虎左旗</t>
         </is>
       </c>
       <c r="V351" s="2" t="inlineStr">
@@ -36188,7 +36168,7 @@
       </c>
       <c r="AB351" s="2" t="inlineStr">
         <is>
-          <t>牙克石市</t>
+          <t>新巴尔虎左旗</t>
         </is>
       </c>
       <c r="AC351" s="2" t="n"/>
@@ -36204,11 +36184,7 @@
         </is>
       </c>
       <c r="AG351" s="3" t="n"/>
-      <c r="AH351" s="2" t="inlineStr">
-        <is>
-          <t>大兴安岭</t>
-        </is>
-      </c>
+      <c r="AH351" s="2" t="n"/>
       <c r="AI351" s="2" t="n"/>
     </row>
     <row r="352" ht="24" customHeight="1" s="54">
@@ -36219,10 +36195,20 @@
       <c r="C352" s="41" t="n"/>
       <c r="D352" s="2" t="n"/>
       <c r="E352" s="3" t="n"/>
-      <c r="F352" s="35" t="n"/>
-      <c r="G352" s="26" t="n"/>
-      <c r="H352" s="26" t="n"/>
-      <c r="I352" s="2" t="n"/>
+      <c r="F352" s="35" t="inlineStr">
+        <is>
+          <t>C0022</t>
+        </is>
+      </c>
+      <c r="G352" s="26" t="n">
+        <v>50.6378</v>
+      </c>
+      <c r="H352" s="26" t="n">
+        <v>121.5664</v>
+      </c>
+      <c r="I352" s="2" t="n">
+        <v>733.8</v>
+      </c>
       <c r="J352" s="24" t="n">
         <v>12</v>
       </c>
@@ -36234,7 +36220,7 @@
       <c r="L352" s="51" t="n"/>
       <c r="M352" s="13" t="inlineStr">
         <is>
-          <t>库都尔</t>
+          <t>伊图里河</t>
         </is>
       </c>
       <c r="N352" s="51" t="n"/>
@@ -36293,7 +36279,11 @@
         </is>
       </c>
       <c r="AG352" s="3" t="n"/>
-      <c r="AH352" s="2" t="n"/>
+      <c r="AH352" s="2" t="inlineStr">
+        <is>
+          <t>大兴安岭</t>
+        </is>
+      </c>
       <c r="AI352" s="2" t="n"/>
     </row>
     <row r="353" ht="24" customHeight="1" s="54">
@@ -36304,20 +36294,10 @@
       <c r="C353" s="41" t="n"/>
       <c r="D353" s="2" t="n"/>
       <c r="E353" s="3" t="n"/>
-      <c r="F353" s="35" t="inlineStr">
-        <is>
-          <t>C0316</t>
-        </is>
-      </c>
-      <c r="G353" s="26" t="n">
-        <v>49.0722</v>
-      </c>
-      <c r="H353" s="26" t="n">
-        <v>121.6139</v>
-      </c>
-      <c r="I353" s="2" t="n">
-        <v>775.4</v>
-      </c>
+      <c r="F353" s="35" t="n"/>
+      <c r="G353" s="26" t="n"/>
+      <c r="H353" s="26" t="n"/>
+      <c r="I353" s="2" t="n"/>
       <c r="J353" s="24" t="n">
         <v>12</v>
       </c>
@@ -36329,7 +36309,7 @@
       <c r="L353" s="51" t="n"/>
       <c r="M353" s="13" t="inlineStr">
         <is>
-          <t>扎敦水利枢纽</t>
+          <t>库都尔</t>
         </is>
       </c>
       <c r="N353" s="51" t="n"/>
@@ -36399,10 +36379,20 @@
       <c r="C354" s="41" t="n"/>
       <c r="D354" s="2" t="n"/>
       <c r="E354" s="3" t="n"/>
-      <c r="F354" s="35" t="n"/>
-      <c r="G354" s="26" t="n"/>
-      <c r="H354" s="26" t="n"/>
-      <c r="I354" s="2" t="n"/>
+      <c r="F354" s="35" t="inlineStr">
+        <is>
+          <t>C0316</t>
+        </is>
+      </c>
+      <c r="G354" s="26" t="n">
+        <v>49.0722</v>
+      </c>
+      <c r="H354" s="26" t="n">
+        <v>121.6139</v>
+      </c>
+      <c r="I354" s="2" t="n">
+        <v>775.4</v>
+      </c>
       <c r="J354" s="24" t="n">
         <v>12</v>
       </c>
@@ -36414,7 +36404,7 @@
       <c r="L354" s="51" t="n"/>
       <c r="M354" s="13" t="inlineStr">
         <is>
-          <t>恩和</t>
+          <t>扎敦水利枢纽</t>
         </is>
       </c>
       <c r="N354" s="51" t="n"/>
@@ -36426,7 +36416,7 @@
       <c r="T354" s="33" t="n"/>
       <c r="U354" s="37" t="inlineStr">
         <is>
-          <t>呼伦贝尔</t>
+          <t>牙克石</t>
         </is>
       </c>
       <c r="V354" s="2" t="inlineStr">
@@ -36455,7 +36445,11 @@
           <t>呼伦贝尔市</t>
         </is>
       </c>
-      <c r="AB354" s="2" t="n"/>
+      <c r="AB354" s="2" t="inlineStr">
+        <is>
+          <t>牙克石市</t>
+        </is>
+      </c>
       <c r="AC354" s="2" t="n"/>
       <c r="AD354" s="2" t="n"/>
       <c r="AE354" s="2" t="inlineStr">
@@ -36469,11 +36463,7 @@
         </is>
       </c>
       <c r="AG354" s="3" t="n"/>
-      <c r="AH354" s="2" t="inlineStr">
-        <is>
-          <t>大兴安岭</t>
-        </is>
-      </c>
+      <c r="AH354" s="2" t="n"/>
       <c r="AI354" s="2" t="n"/>
     </row>
     <row r="355" ht="24" customHeight="1" s="54">
@@ -36499,7 +36489,7 @@
       <c r="L355" s="51" t="n"/>
       <c r="M355" s="13" t="inlineStr">
         <is>
-          <t>辉河林场</t>
+          <t>恩和</t>
         </is>
       </c>
       <c r="N355" s="51" t="n"/>
@@ -36584,7 +36574,7 @@
       <c r="L356" s="51" t="n"/>
       <c r="M356" s="13" t="inlineStr">
         <is>
-          <t>西乌珠尔</t>
+          <t>辉河林场</t>
         </is>
       </c>
       <c r="N356" s="51" t="n"/>
@@ -36639,39 +36629,25 @@
         </is>
       </c>
       <c r="AG356" s="3" t="n"/>
-      <c r="AH356" s="2" t="n"/>
+      <c r="AH356" s="2" t="inlineStr">
+        <is>
+          <t>大兴安岭</t>
+        </is>
+      </c>
       <c r="AI356" s="2" t="n"/>
     </row>
     <row r="357" ht="24" customHeight="1" s="54">
       <c r="A357" s="2" t="n">
         <v>356</v>
       </c>
-      <c r="B357" s="2" t="inlineStr">
-        <is>
-          <t>ogimet</t>
-        </is>
-      </c>
-      <c r="C357" s="41" t="n">
-        <v>54012</v>
-      </c>
-      <c r="D357" s="2" t="inlineStr">
-        <is>
-          <t>Xiwuzhumuqin</t>
-        </is>
-      </c>
-      <c r="E357" s="3" t="n">
-        <v>99999</v>
-      </c>
+      <c r="B357" s="2" t="n"/>
+      <c r="C357" s="41" t="n"/>
+      <c r="D357" s="2" t="n"/>
+      <c r="E357" s="3" t="n"/>
       <c r="F357" s="35" t="n"/>
-      <c r="G357" s="26" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="H357" s="26" t="n">
-        <v>117.63</v>
-      </c>
-      <c r="I357" s="2" t="n">
-        <v>1001.7</v>
-      </c>
+      <c r="G357" s="26" t="n"/>
+      <c r="H357" s="26" t="n"/>
+      <c r="I357" s="2" t="n"/>
       <c r="J357" s="24" t="n">
         <v>12</v>
       </c>
@@ -36683,7 +36659,7 @@
       <c r="L357" s="51" t="n"/>
       <c r="M357" s="13" t="inlineStr">
         <is>
-          <t>西乌珠穆沁</t>
+          <t>西乌珠尔</t>
         </is>
       </c>
       <c r="N357" s="51" t="n"/>
@@ -36695,7 +36671,7 @@
       <c r="T357" s="33" t="n"/>
       <c r="U357" s="37" t="inlineStr">
         <is>
-          <t>锡林郭勒</t>
+          <t>呼伦贝尔</t>
         </is>
       </c>
       <c r="V357" s="2" t="inlineStr">
@@ -36721,7 +36697,7 @@
       <c r="Z357" s="3" t="n"/>
       <c r="AA357" s="2" t="inlineStr">
         <is>
-          <t>西乌珠穆沁旗</t>
+          <t>呼伦贝尔市</t>
         </is>
       </c>
       <c r="AB357" s="2" t="n"/>
@@ -36751,11 +36727,11 @@
         </is>
       </c>
       <c r="C358" s="41" t="n">
-        <v>53083</v>
+        <v>54012</v>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Narenbaola</t>
+          <t>Xiwuzhumuqin</t>
         </is>
       </c>
       <c r="E358" s="3" t="n">
@@ -36763,13 +36739,13 @@
       </c>
       <c r="F358" s="35" t="n"/>
       <c r="G358" s="26" t="n">
-        <v>44.6175</v>
+        <v>44.57</v>
       </c>
       <c r="H358" s="26" t="n">
-        <v>114.1522</v>
+        <v>117.63</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>1181.6</v>
+        <v>1001.7</v>
       </c>
       <c r="J358" s="24" t="n">
         <v>12</v>
@@ -36782,7 +36758,7 @@
       <c r="L358" s="51" t="n"/>
       <c r="M358" s="13" t="inlineStr">
         <is>
-          <t>那仁宝力格</t>
+          <t>西乌珠穆沁</t>
         </is>
       </c>
       <c r="N358" s="51" t="n"/>
@@ -36820,14 +36796,10 @@
       <c r="Z358" s="3" t="n"/>
       <c r="AA358" s="2" t="inlineStr">
         <is>
-          <t>锡林郭勒盟</t>
-        </is>
-      </c>
-      <c r="AB358" s="2" t="inlineStr">
-        <is>
-          <t>阿巴嘎旗</t>
-        </is>
-      </c>
+          <t>西乌珠穆沁旗</t>
+        </is>
+      </c>
+      <c r="AB358" s="2" t="n"/>
       <c r="AC358" s="2" t="n"/>
       <c r="AD358" s="2" t="n"/>
       <c r="AE358" s="2" t="inlineStr">
@@ -36853,14 +36825,12 @@
           <t>ogimet</t>
         </is>
       </c>
-      <c r="C359" s="41" t="inlineStr">
-        <is>
-          <t>54208</t>
-        </is>
+      <c r="C359" s="41" t="n">
+        <v>53083</v>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Duolunnao'er</t>
+          <t>Narenbaola</t>
         </is>
       </c>
       <c r="E359" s="3" t="n">
@@ -36868,13 +36838,13 @@
       </c>
       <c r="F359" s="35" t="n"/>
       <c r="G359" s="26" t="n">
-        <v>42.1939</v>
+        <v>44.6175</v>
       </c>
       <c r="H359" s="26" t="n">
-        <v>116.4664</v>
+        <v>114.1522</v>
       </c>
       <c r="I359" s="2" t="n">
-        <v>1245.5</v>
+        <v>1181.6</v>
       </c>
       <c r="J359" s="24" t="n">
         <v>12</v>
@@ -36887,7 +36857,7 @@
       <c r="L359" s="51" t="n"/>
       <c r="M359" s="13" t="inlineStr">
         <is>
-          <t>多伦</t>
+          <t>那仁宝力格</t>
         </is>
       </c>
       <c r="N359" s="51" t="n"/>
@@ -36928,7 +36898,11 @@
           <t>锡林郭勒盟</t>
         </is>
       </c>
-      <c r="AB359" s="2" t="n"/>
+      <c r="AB359" s="2" t="inlineStr">
+        <is>
+          <t>阿巴嘎旗</t>
+        </is>
+      </c>
       <c r="AC359" s="2" t="n"/>
       <c r="AD359" s="2" t="n"/>
       <c r="AE359" s="2" t="inlineStr">
@@ -36949,23 +36923,33 @@
       <c r="A360" s="2" t="n">
         <v>359</v>
       </c>
-      <c r="B360" s="2" t="n"/>
-      <c r="C360" s="41" t="n"/>
-      <c r="D360" s="2" t="n"/>
-      <c r="E360" s="3" t="n"/>
-      <c r="F360" s="35" t="inlineStr">
-        <is>
-          <t>C2227</t>
-        </is>
-      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
+      <c r="C360" s="41" t="inlineStr">
+        <is>
+          <t>54208</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Duolunnao'er</t>
+        </is>
+      </c>
+      <c r="E360" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F360" s="35" t="n"/>
       <c r="G360" s="26" t="n">
-        <v>42.423</v>
+        <v>42.1939</v>
       </c>
       <c r="H360" s="26" t="n">
-        <v>116.775</v>
+        <v>116.4664</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>1374.1</v>
+        <v>1245.5</v>
       </c>
       <c r="J360" s="24" t="n">
         <v>12</v>
@@ -36978,7 +36962,7 @@
       <c r="L360" s="51" t="n"/>
       <c r="M360" s="13" t="inlineStr">
         <is>
-          <t>姑娘湖</t>
+          <t>多伦</t>
         </is>
       </c>
       <c r="N360" s="51" t="n"/>
@@ -37019,11 +37003,7 @@
           <t>锡林郭勒盟</t>
         </is>
       </c>
-      <c r="AB360" s="2" t="inlineStr">
-        <is>
-          <t>多伦县</t>
-        </is>
-      </c>
+      <c r="AB360" s="2" t="n"/>
       <c r="AC360" s="2" t="n"/>
       <c r="AD360" s="2" t="n"/>
       <c r="AE360" s="2" t="inlineStr">
@@ -37045,22 +37025,22 @@
         <v>360</v>
       </c>
       <c r="B361" s="2" t="n"/>
-      <c r="C361" s="41" t="inlineStr">
-        <is>
-          <t>52633</t>
-        </is>
-      </c>
+      <c r="C361" s="41" t="n"/>
       <c r="D361" s="2" t="n"/>
       <c r="E361" s="3" t="n"/>
-      <c r="F361" s="35" t="n"/>
+      <c r="F361" s="35" t="inlineStr">
+        <is>
+          <t>C2227</t>
+        </is>
+      </c>
       <c r="G361" s="26" t="n">
-        <v>38.8086</v>
+        <v>42.423</v>
       </c>
       <c r="H361" s="26" t="n">
-        <v>98.4181</v>
+        <v>116.775</v>
       </c>
       <c r="I361" s="2" t="n">
-        <v>3364.3</v>
+        <v>1374.1</v>
       </c>
       <c r="J361" s="24" t="n">
         <v>12</v>
@@ -37073,7 +37053,7 @@
       <c r="L361" s="51" t="n"/>
       <c r="M361" s="13" t="inlineStr">
         <is>
-          <t>托勒</t>
+          <t>姑娘湖</t>
         </is>
       </c>
       <c r="N361" s="51" t="n"/>
@@ -37085,12 +37065,12 @@
       <c r="T361" s="33" t="n"/>
       <c r="U361" s="37" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>锡林郭勒</t>
         </is>
       </c>
       <c r="V361" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="W361" s="3" t="inlineStr">
@@ -37111,12 +37091,12 @@
       <c r="Z361" s="3" t="n"/>
       <c r="AA361" s="2" t="inlineStr">
         <is>
-          <t>海北藏族自治州</t>
+          <t>锡林郭勒盟</t>
         </is>
       </c>
       <c r="AB361" s="2" t="inlineStr">
         <is>
-          <t>祁连县</t>
+          <t>多伦县</t>
         </is>
       </c>
       <c r="AC361" s="2" t="n"/>
@@ -37132,11 +37112,7 @@
         </is>
       </c>
       <c r="AG361" s="3" t="n"/>
-      <c r="AH361" s="2" t="inlineStr">
-        <is>
-          <t>青藏高原</t>
-        </is>
-      </c>
+      <c r="AH361" s="2" t="n"/>
       <c r="AI361" s="2" t="n"/>
     </row>
     <row r="362" ht="24" customHeight="1" s="54">
@@ -37144,22 +37120,22 @@
         <v>361</v>
       </c>
       <c r="B362" s="2" t="n"/>
-      <c r="C362" s="41" t="n">
-        <v>52645</v>
+      <c r="C362" s="41" t="inlineStr">
+        <is>
+          <t>52633</t>
+        </is>
       </c>
       <c r="D362" s="2" t="n"/>
-      <c r="E362" s="3" t="n">
-        <v>99999</v>
-      </c>
+      <c r="E362" s="3" t="n"/>
       <c r="F362" s="35" t="n"/>
       <c r="G362" s="26" t="n">
-        <v>38.43</v>
+        <v>38.8086</v>
       </c>
       <c r="H362" s="26" t="n">
-        <v>99.59999999999999</v>
+        <v>98.4181</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>3314</v>
+        <v>3364.3</v>
       </c>
       <c r="J362" s="24" t="n">
         <v>12</v>
@@ -37172,7 +37148,7 @@
       <c r="L362" s="51" t="n"/>
       <c r="M362" s="13" t="inlineStr">
         <is>
-          <t>野牛沟</t>
+          <t>托勒</t>
         </is>
       </c>
       <c r="N362" s="51" t="n"/>
@@ -37243,10 +37219,8 @@
         <v>362</v>
       </c>
       <c r="B363" s="2" t="n"/>
-      <c r="C363" s="41" t="inlineStr">
-        <is>
-          <t>56001</t>
-        </is>
+      <c r="C363" s="41" t="n">
+        <v>52645</v>
       </c>
       <c r="D363" s="2" t="n"/>
       <c r="E363" s="3" t="n">
@@ -37254,13 +37228,13 @@
       </c>
       <c r="F363" s="35" t="n"/>
       <c r="G363" s="26" t="n">
-        <v>34.6333</v>
+        <v>38.43</v>
       </c>
       <c r="H363" s="26" t="n">
-        <v>92.8553</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>4770</v>
+        <v>3314</v>
       </c>
       <c r="J363" s="24" t="n">
         <v>12</v>
@@ -37273,14 +37247,10 @@
       <c r="L363" s="51" t="n"/>
       <c r="M363" s="13" t="inlineStr">
         <is>
-          <t>沱沱河</t>
-        </is>
-      </c>
-      <c r="N363" s="51" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
+          <t>野牛沟</t>
+        </is>
+      </c>
+      <c r="N363" s="51" t="n"/>
       <c r="O363" s="29" t="n"/>
       <c r="P363" s="29" t="n"/>
       <c r="Q363" s="29" t="n"/>
@@ -37315,12 +37285,12 @@
       <c r="Z363" s="3" t="n"/>
       <c r="AA363" s="2" t="inlineStr">
         <is>
-          <t>海西蒙古族藏族自治州</t>
+          <t>海北藏族自治州</t>
         </is>
       </c>
       <c r="AB363" s="2" t="inlineStr">
         <is>
-          <t>格尔木市</t>
+          <t>祁连县</t>
         </is>
       </c>
       <c r="AC363" s="2" t="n"/>
@@ -37348,22 +37318,24 @@
         <v>363</v>
       </c>
       <c r="B364" s="2" t="n"/>
-      <c r="C364" s="41" t="n"/>
+      <c r="C364" s="41" t="inlineStr">
+        <is>
+          <t>56001</t>
+        </is>
+      </c>
       <c r="D364" s="2" t="n"/>
-      <c r="E364" s="3" t="n"/>
-      <c r="F364" s="35" t="inlineStr">
-        <is>
-          <t>X2068</t>
-        </is>
-      </c>
+      <c r="E364" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F364" s="35" t="n"/>
       <c r="G364" s="26" t="n">
-        <v>35.904</v>
+        <v>34.6333</v>
       </c>
       <c r="H364" s="26" t="n">
-        <v>93.404</v>
+        <v>92.8553</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>4396</v>
+        <v>4770</v>
       </c>
       <c r="J364" s="24" t="n">
         <v>12</v>
@@ -37376,10 +37348,14 @@
       <c r="L364" s="51" t="n"/>
       <c r="M364" s="13" t="inlineStr">
         <is>
-          <t>西王母瑶池</t>
-        </is>
-      </c>
-      <c r="N364" s="51" t="n"/>
+          <t>沱沱河</t>
+        </is>
+      </c>
+      <c r="N364" s="51" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
       <c r="O364" s="29" t="n"/>
       <c r="P364" s="29" t="n"/>
       <c r="Q364" s="29" t="n"/>
@@ -37452,17 +37428,17 @@
       <c r="E365" s="3" t="n"/>
       <c r="F365" s="35" t="inlineStr">
         <is>
-          <t>X2081</t>
+          <t>X2068</t>
         </is>
       </c>
       <c r="G365" s="26" t="n">
-        <v>38.184</v>
+        <v>35.904</v>
       </c>
       <c r="H365" s="26" t="n">
-        <v>97.59399999999999</v>
+        <v>93.404</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>4103</v>
+        <v>4396</v>
       </c>
       <c r="J365" s="24" t="n">
         <v>12</v>
@@ -37475,7 +37451,7 @@
       <c r="L365" s="51" t="n"/>
       <c r="M365" s="13" t="inlineStr">
         <is>
-          <t>哈拉湖</t>
+          <t>西王母瑶池</t>
         </is>
       </c>
       <c r="N365" s="51" t="n"/>
@@ -37518,7 +37494,7 @@
       </c>
       <c r="AB365" s="2" t="inlineStr">
         <is>
-          <t>德令哈市</t>
+          <t>格尔木市</t>
         </is>
       </c>
       <c r="AC365" s="2" t="n"/>
@@ -37551,17 +37527,17 @@
       <c r="E366" s="3" t="n"/>
       <c r="F366" s="35" t="inlineStr">
         <is>
-          <t>X7049</t>
+          <t>X2081</t>
         </is>
       </c>
       <c r="G366" s="26" t="n">
-        <v>33.62</v>
+        <v>38.184</v>
       </c>
       <c r="H366" s="26" t="n">
-        <v>97.197</v>
+        <v>97.59399999999999</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>4365.6</v>
+        <v>4103</v>
       </c>
       <c r="J366" s="24" t="n">
         <v>12</v>
@@ -37574,14 +37550,10 @@
       <c r="L366" s="51" t="n"/>
       <c r="M366" s="13" t="inlineStr">
         <is>
-          <t>珍秦永郎达</t>
-        </is>
-      </c>
-      <c r="N366" s="51" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
+          <t>哈拉湖</t>
+        </is>
+      </c>
+      <c r="N366" s="51" t="n"/>
       <c r="O366" s="29" t="n"/>
       <c r="P366" s="29" t="n"/>
       <c r="Q366" s="29" t="n"/>
@@ -37616,12 +37588,12 @@
       <c r="Z366" s="3" t="n"/>
       <c r="AA366" s="2" t="inlineStr">
         <is>
-          <t>玉树藏族自治州</t>
+          <t>海西蒙古族藏族自治州</t>
         </is>
       </c>
       <c r="AB366" s="2" t="inlineStr">
         <is>
-          <t>称多县</t>
+          <t>德令哈市</t>
         </is>
       </c>
       <c r="AC366" s="2" t="n"/>
@@ -37642,43 +37614,29 @@
           <t>青藏高原</t>
         </is>
       </c>
-      <c r="AI366" s="2" t="inlineStr">
-        <is>
-          <t>竹节梁</t>
-        </is>
-      </c>
+      <c r="AI366" s="2" t="n"/>
     </row>
     <row r="367" ht="24" customHeight="1" s="54">
       <c r="A367" s="2" t="n">
         <v>366</v>
       </c>
-      <c r="B367" s="2" t="inlineStr">
-        <is>
-          <t>ogimet</t>
-        </is>
-      </c>
-      <c r="C367" s="41" t="inlineStr">
-        <is>
-          <t>56033</t>
-        </is>
-      </c>
-      <c r="D367" s="2" t="inlineStr">
-        <is>
-          <t>Machali</t>
-        </is>
-      </c>
-      <c r="E367" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F367" s="35" t="n"/>
+      <c r="B367" s="2" t="n"/>
+      <c r="C367" s="41" t="n"/>
+      <c r="D367" s="2" t="n"/>
+      <c r="E367" s="3" t="n"/>
+      <c r="F367" s="35" t="inlineStr">
+        <is>
+          <t>X7049</t>
+        </is>
+      </c>
       <c r="G367" s="26" t="n">
-        <v>34.9172</v>
+        <v>33.62</v>
       </c>
       <c r="H367" s="26" t="n">
-        <v>98.2158</v>
+        <v>97.197</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>4271.7</v>
+        <v>4365.6</v>
       </c>
       <c r="J367" s="24" t="n">
         <v>12</v>
@@ -37691,10 +37649,10 @@
       <c r="L367" s="51" t="n"/>
       <c r="M367" s="13" t="inlineStr">
         <is>
-          <t>玛多</t>
-        </is>
-      </c>
-      <c r="N367" s="53" t="inlineStr">
+          <t>珍秦永郎达</t>
+        </is>
+      </c>
+      <c r="N367" s="51" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -37733,12 +37691,12 @@
       <c r="Z367" s="3" t="n"/>
       <c r="AA367" s="2" t="inlineStr">
         <is>
-          <t>果洛藏族自治州</t>
+          <t>玉树藏族自治州</t>
         </is>
       </c>
       <c r="AB367" s="2" t="inlineStr">
         <is>
-          <t>玛多县</t>
+          <t>称多县</t>
         </is>
       </c>
       <c r="AC367" s="2" t="n"/>
@@ -37759,31 +37717,43 @@
           <t>青藏高原</t>
         </is>
       </c>
-      <c r="AI367" s="2" t="n"/>
+      <c r="AI367" s="2" t="inlineStr">
+        <is>
+          <t>竹节梁</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="24" customHeight="1" s="54">
       <c r="A368" s="2" t="n">
         <v>367</v>
       </c>
-      <c r="B368" s="2" t="n"/>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
       <c r="C368" s="41" t="inlineStr">
         <is>
-          <t>54301</t>
-        </is>
-      </c>
-      <c r="D368" s="2" t="n"/>
+          <t>56033</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Machali</t>
+        </is>
+      </c>
       <c r="E368" s="3" t="n">
         <v>99999</v>
       </c>
       <c r="F368" s="35" t="n"/>
       <c r="G368" s="26" t="n">
-        <v>41.6719</v>
+        <v>34.9172</v>
       </c>
       <c r="H368" s="26" t="n">
-        <v>115.6531</v>
+        <v>98.2158</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>1409.6</v>
+        <v>4271.7</v>
       </c>
       <c r="J368" s="24" t="n">
         <v>12</v>
@@ -37796,10 +37766,14 @@
       <c r="L368" s="51" t="n"/>
       <c r="M368" s="13" t="inlineStr">
         <is>
-          <t>沽源</t>
-        </is>
-      </c>
-      <c r="N368" s="51" t="n"/>
+          <t>玛多</t>
+        </is>
+      </c>
+      <c r="N368" s="53" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
       <c r="O368" s="29" t="n"/>
       <c r="P368" s="29" t="n"/>
       <c r="Q368" s="29" t="n"/>
@@ -37808,12 +37782,12 @@
       <c r="T368" s="33" t="n"/>
       <c r="U368" s="37" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="V368" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="W368" s="3" t="inlineStr">
@@ -37834,12 +37808,12 @@
       <c r="Z368" s="3" t="n"/>
       <c r="AA368" s="2" t="inlineStr">
         <is>
-          <t>张家口市</t>
+          <t>果洛藏族自治州</t>
         </is>
       </c>
       <c r="AB368" s="2" t="inlineStr">
         <is>
-          <t>沽源县</t>
+          <t>玛多县</t>
         </is>
       </c>
       <c r="AC368" s="2" t="n"/>
@@ -37855,7 +37829,11 @@
         </is>
       </c>
       <c r="AG368" s="3" t="n"/>
-      <c r="AH368" s="2" t="n"/>
+      <c r="AH368" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AI368" s="2" t="n"/>
     </row>
     <row r="369" ht="24" customHeight="1" s="54">
@@ -37863,22 +37841,24 @@
         <v>368</v>
       </c>
       <c r="B369" s="2" t="n"/>
-      <c r="C369" s="41" t="n"/>
+      <c r="C369" s="41" t="inlineStr">
+        <is>
+          <t>54301</t>
+        </is>
+      </c>
       <c r="D369" s="2" t="n"/>
-      <c r="E369" s="3" t="n"/>
-      <c r="F369" s="35" t="inlineStr">
-        <is>
-          <t>B5276</t>
-        </is>
-      </c>
+      <c r="E369" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F369" s="35" t="n"/>
       <c r="G369" s="26" t="n">
-        <v>39.7886</v>
+        <v>41.6719</v>
       </c>
       <c r="H369" s="26" t="n">
-        <v>112.8256</v>
+        <v>115.6531</v>
       </c>
       <c r="I369" s="2" t="n">
-        <v>1349</v>
+        <v>1409.6</v>
       </c>
       <c r="J369" s="24" t="n">
         <v>12</v>
@@ -37891,7 +37871,7 @@
       <c r="L369" s="51" t="n"/>
       <c r="M369" s="13" t="inlineStr">
         <is>
-          <t>(右玉)吴家窑</t>
+          <t>沽源</t>
         </is>
       </c>
       <c r="N369" s="51" t="n"/>
@@ -37903,12 +37883,12 @@
       <c r="T369" s="33" t="n"/>
       <c r="U369" s="37" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="V369" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="W369" s="3" t="inlineStr">
@@ -37929,12 +37909,12 @@
       <c r="Z369" s="3" t="n"/>
       <c r="AA369" s="2" t="inlineStr">
         <is>
-          <t>朔州市</t>
+          <t>张家口市</t>
         </is>
       </c>
       <c r="AB369" s="2" t="inlineStr">
         <is>
-          <t>怀仁市</t>
+          <t>沽源县</t>
         </is>
       </c>
       <c r="AC369" s="2" t="n"/>
@@ -37957,33 +37937,23 @@
       <c r="A370" s="2" t="n">
         <v>369</v>
       </c>
-      <c r="B370" s="2" t="inlineStr">
-        <is>
-          <t>ogimet</t>
-        </is>
-      </c>
-      <c r="C370" s="41" t="inlineStr">
-        <is>
-          <t>53487</t>
-        </is>
-      </c>
-      <c r="D370" s="2" t="inlineStr">
-        <is>
-          <t>Datong</t>
-        </is>
-      </c>
-      <c r="E370" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F370" s="35" t="n"/>
+      <c r="B370" s="2" t="n"/>
+      <c r="C370" s="41" t="n"/>
+      <c r="D370" s="2" t="n"/>
+      <c r="E370" s="3" t="n"/>
+      <c r="F370" s="35" t="inlineStr">
+        <is>
+          <t>B5276</t>
+        </is>
+      </c>
       <c r="G370" s="26" t="n">
-        <v>40.0789</v>
+        <v>39.7886</v>
       </c>
       <c r="H370" s="26" t="n">
-        <v>113.4117</v>
+        <v>112.8256</v>
       </c>
       <c r="I370" s="2" t="n">
-        <v>1052.4</v>
+        <v>1349</v>
       </c>
       <c r="J370" s="24" t="n">
         <v>12</v>
@@ -37996,7 +37966,7 @@
       <c r="L370" s="51" t="n"/>
       <c r="M370" s="13" t="inlineStr">
         <is>
-          <t>大同</t>
+          <t>(右玉)吴家窑</t>
         </is>
       </c>
       <c r="N370" s="51" t="n"/>
@@ -38034,10 +38004,14 @@
       <c r="Z370" s="3" t="n"/>
       <c r="AA370" s="2" t="inlineStr">
         <is>
-          <t>大同市</t>
-        </is>
-      </c>
-      <c r="AB370" s="2" t="n"/>
+          <t>朔州市</t>
+        </is>
+      </c>
+      <c r="AB370" s="2" t="inlineStr">
+        <is>
+          <t>怀仁市</t>
+        </is>
+      </c>
       <c r="AC370" s="2" t="n"/>
       <c r="AD370" s="2" t="n"/>
       <c r="AE370" s="2" t="inlineStr">
@@ -38065,12 +38039,12 @@
       </c>
       <c r="C371" s="41" t="inlineStr">
         <is>
-          <t>53646</t>
+          <t>53487</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Yulin</t>
+          <t>Datong</t>
         </is>
       </c>
       <c r="E371" s="3" t="n">
@@ -38078,13 +38052,13 @@
       </c>
       <c r="F371" s="35" t="n"/>
       <c r="G371" s="26" t="n">
-        <v>38.2686</v>
+        <v>40.0789</v>
       </c>
       <c r="H371" s="26" t="n">
-        <v>109.7803</v>
+        <v>113.4117</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>1161.7</v>
+        <v>1052.4</v>
       </c>
       <c r="J371" s="24" t="n">
         <v>12</v>
@@ -38097,7 +38071,7 @@
       <c r="L371" s="51" t="n"/>
       <c r="M371" s="13" t="inlineStr">
         <is>
-          <t>榆林</t>
+          <t>大同</t>
         </is>
       </c>
       <c r="N371" s="51" t="n"/>
@@ -38109,12 +38083,12 @@
       <c r="T371" s="33" t="n"/>
       <c r="U371" s="37" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="V371" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="W371" s="3" t="inlineStr">
@@ -38135,7 +38109,7 @@
       <c r="Z371" s="3" t="n"/>
       <c r="AA371" s="2" t="inlineStr">
         <is>
-          <t>榆林市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="AB371" s="2" t="n"/>
@@ -38159,25 +38133,33 @@
       <c r="A372" s="2" t="n">
         <v>371</v>
       </c>
-      <c r="B372" s="2" t="n"/>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
       <c r="C372" s="41" t="inlineStr">
         <is>
-          <t>56038</t>
-        </is>
-      </c>
-      <c r="D372" s="2" t="n"/>
+          <t>53646</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Yulin</t>
+        </is>
+      </c>
       <c r="E372" s="3" t="n">
         <v>99999</v>
       </c>
       <c r="F372" s="35" t="n"/>
       <c r="G372" s="26" t="n">
-        <v>32.9764</v>
+        <v>38.2686</v>
       </c>
       <c r="H372" s="26" t="n">
-        <v>98.09690000000001</v>
+        <v>109.7803</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>4181.2</v>
+        <v>1161.7</v>
       </c>
       <c r="J372" s="24" t="n">
         <v>12</v>
@@ -38190,28 +38172,24 @@
       <c r="L372" s="51" t="n"/>
       <c r="M372" s="13" t="inlineStr">
         <is>
-          <t>石渠</t>
+          <t>榆林</t>
         </is>
       </c>
       <c r="N372" s="51" t="n"/>
       <c r="O372" s="29" t="n"/>
       <c r="P372" s="29" t="n"/>
       <c r="Q372" s="29" t="n"/>
-      <c r="R372" s="45" t="inlineStr">
-        <is>
-          <t>1995-12-29</t>
-        </is>
-      </c>
+      <c r="R372" s="45" t="n"/>
       <c r="S372" s="21" t="n"/>
       <c r="T372" s="33" t="n"/>
       <c r="U372" s="37" t="inlineStr">
         <is>
-          <t>川西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="V372" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="W372" s="3" t="inlineStr">
@@ -38232,14 +38210,10 @@
       <c r="Z372" s="3" t="n"/>
       <c r="AA372" s="2" t="inlineStr">
         <is>
-          <t>甘孜藏族自治州</t>
-        </is>
-      </c>
-      <c r="AB372" s="2" t="inlineStr">
-        <is>
-          <t>石渠县</t>
-        </is>
-      </c>
+          <t>榆林市</t>
+        </is>
+      </c>
+      <c r="AB372" s="2" t="n"/>
       <c r="AC372" s="2" t="n"/>
       <c r="AD372" s="2" t="n"/>
       <c r="AE372" s="2" t="inlineStr">
@@ -38253,11 +38227,7 @@
         </is>
       </c>
       <c r="AG372" s="3" t="n"/>
-      <c r="AH372" s="2" t="inlineStr">
-        <is>
-          <t>青藏高原</t>
-        </is>
-      </c>
+      <c r="AH372" s="2" t="n"/>
       <c r="AI372" s="2" t="n"/>
     </row>
     <row r="373" ht="24" customHeight="1" s="54">
@@ -38265,22 +38235,24 @@
         <v>372</v>
       </c>
       <c r="B373" s="2" t="n"/>
-      <c r="C373" s="41" t="n"/>
+      <c r="C373" s="41" t="inlineStr">
+        <is>
+          <t>56038</t>
+        </is>
+      </c>
       <c r="D373" s="2" t="n"/>
-      <c r="E373" s="3" t="n"/>
-      <c r="F373" s="35" t="inlineStr">
-        <is>
-          <t>A1490</t>
-        </is>
-      </c>
+      <c r="E373" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F373" s="35" t="n"/>
       <c r="G373" s="26" t="n">
-        <v>40.556</v>
+        <v>32.9764</v>
       </c>
       <c r="H373" s="26" t="n">
-        <v>115.793</v>
+        <v>98.09690000000001</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>1798</v>
+        <v>4181.2</v>
       </c>
       <c r="J373" s="24" t="n">
         <v>12</v>
@@ -38293,32 +38265,28 @@
       <c r="L373" s="51" t="n"/>
       <c r="M373" s="13" t="inlineStr">
         <is>
-          <t>海坨山</t>
-        </is>
-      </c>
-      <c r="N373" s="51" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
+          <t>石渠</t>
+        </is>
+      </c>
+      <c r="N373" s="51" t="n"/>
       <c r="O373" s="29" t="n"/>
       <c r="P373" s="29" t="n"/>
       <c r="Q373" s="29" t="n"/>
       <c r="R373" s="45" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>1995-12-29</t>
         </is>
       </c>
       <c r="S373" s="21" t="n"/>
       <c r="T373" s="33" t="n"/>
       <c r="U373" s="37" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>川西</t>
         </is>
       </c>
       <c r="V373" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="W373" s="3" t="inlineStr">
@@ -38339,10 +38307,14 @@
       <c r="Z373" s="3" t="n"/>
       <c r="AA373" s="2" t="inlineStr">
         <is>
-          <t>延庆区</t>
-        </is>
-      </c>
-      <c r="AB373" s="2" t="n"/>
+          <t>甘孜藏族自治州</t>
+        </is>
+      </c>
+      <c r="AB373" s="2" t="inlineStr">
+        <is>
+          <t>石渠县</t>
+        </is>
+      </c>
       <c r="AC373" s="2" t="n"/>
       <c r="AD373" s="2" t="n"/>
       <c r="AE373" s="2" t="inlineStr">
@@ -38356,38 +38328,34 @@
         </is>
       </c>
       <c r="AG373" s="3" t="n"/>
-      <c r="AH373" s="2" t="n"/>
-      <c r="AI373" s="2" t="inlineStr">
-        <is>
-          <t>竞速训练1</t>
-        </is>
-      </c>
+      <c r="AH373" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
+      <c r="AI373" s="2" t="n"/>
     </row>
     <row r="374" ht="24" customHeight="1" s="54">
       <c r="A374" s="2" t="n">
         <v>373</v>
       </c>
       <c r="B374" s="2" t="n"/>
-      <c r="C374" s="41" t="n">
-        <v>58968</v>
-      </c>
-      <c r="D374" s="2" t="inlineStr">
-        <is>
-          <t>Taipei</t>
-        </is>
-      </c>
-      <c r="E374" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F374" s="35" t="n"/>
+      <c r="C374" s="41" t="n"/>
+      <c r="D374" s="2" t="n"/>
+      <c r="E374" s="3" t="n"/>
+      <c r="F374" s="35" t="inlineStr">
+        <is>
+          <t>A1490</t>
+        </is>
+      </c>
       <c r="G374" s="26" t="n">
-        <v>25.0333333</v>
+        <v>40.556</v>
       </c>
       <c r="H374" s="26" t="n">
-        <v>121.5166666</v>
+        <v>115.793</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>9</v>
+        <v>1798</v>
       </c>
       <c r="J374" s="24" t="n">
         <v>12</v>
@@ -38400,27 +38368,39 @@
       <c r="L374" s="51" t="n"/>
       <c r="M374" s="13" t="inlineStr">
         <is>
-          <t>台北</t>
-        </is>
-      </c>
-      <c r="N374" s="51" t="n"/>
+          <t>海坨山</t>
+        </is>
+      </c>
+      <c r="N374" s="51" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
       <c r="O374" s="29" t="n"/>
       <c r="P374" s="29" t="n"/>
       <c r="Q374" s="29" t="n"/>
-      <c r="R374" s="45" t="n"/>
+      <c r="R374" s="45" t="inlineStr">
+        <is>
+          <t>2021-01-07</t>
+        </is>
+      </c>
       <c r="S374" s="21" t="n"/>
       <c r="T374" s="33" t="n"/>
       <c r="U374" s="37" t="inlineStr">
         <is>
-          <t>台湾</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="V374" s="2" t="inlineStr">
         <is>
-          <t>台湾</t>
-        </is>
-      </c>
-      <c r="W374" s="3" t="n"/>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="W374" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="X374" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -38432,7 +38412,11 @@
         </is>
       </c>
       <c r="Z374" s="3" t="n"/>
-      <c r="AA374" s="2" t="n"/>
+      <c r="AA374" s="2" t="inlineStr">
+        <is>
+          <t>延庆区</t>
+        </is>
+      </c>
       <c r="AB374" s="2" t="n"/>
       <c r="AC374" s="2" t="n"/>
       <c r="AD374" s="2" t="n"/>
@@ -38448,29 +38432,37 @@
       </c>
       <c r="AG374" s="3" t="n"/>
       <c r="AH374" s="2" t="n"/>
-      <c r="AI374" s="2" t="n"/>
+      <c r="AI374" s="2" t="inlineStr">
+        <is>
+          <t>竞速训练1</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="24" customHeight="1" s="54">
       <c r="A375" s="2" t="n">
         <v>374</v>
       </c>
       <c r="B375" s="2" t="n"/>
-      <c r="C375" s="41" t="n"/>
-      <c r="D375" s="2" t="n"/>
-      <c r="E375" s="3" t="n"/>
-      <c r="F375" s="35" t="inlineStr">
-        <is>
-          <t>U7073</t>
-        </is>
-      </c>
+      <c r="C375" s="41" t="n">
+        <v>58968</v>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="E375" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F375" s="35" t="n"/>
       <c r="G375" s="26" t="n">
-        <v>31.134</v>
+        <v>25.0333333</v>
       </c>
       <c r="H375" s="26" t="n">
-        <v>82.22199999999999</v>
+        <v>121.5166666</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>5170</v>
+        <v>9</v>
       </c>
       <c r="J375" s="24" t="n">
         <v>12</v>
@@ -38483,7 +38475,7 @@
       <c r="L375" s="51" t="n"/>
       <c r="M375" s="13" t="inlineStr">
         <is>
-          <t>(革吉)亚热却藏</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="N375" s="51" t="n"/>
@@ -38495,19 +38487,15 @@
       <c r="T375" s="33" t="n"/>
       <c r="U375" s="37" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>台湾</t>
         </is>
       </c>
       <c r="V375" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
-        </is>
-      </c>
-      <c r="W375" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>台湾</t>
+        </is>
+      </c>
+      <c r="W375" s="3" t="n"/>
       <c r="X375" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -38519,16 +38507,8 @@
         </is>
       </c>
       <c r="Z375" s="3" t="n"/>
-      <c r="AA375" s="2" t="inlineStr">
-        <is>
-          <t>阿里地区</t>
-        </is>
-      </c>
-      <c r="AB375" s="2" t="inlineStr">
-        <is>
-          <t>革吉县</t>
-        </is>
-      </c>
+      <c r="AA375" s="2" t="n"/>
+      <c r="AB375" s="2" t="n"/>
       <c r="AC375" s="2" t="n"/>
       <c r="AD375" s="2" t="n"/>
       <c r="AE375" s="2" t="inlineStr">
@@ -38555,17 +38535,17 @@
       <c r="E376" s="3" t="n"/>
       <c r="F376" s="35" t="inlineStr">
         <is>
-          <t>U7031</t>
+          <t>U7073</t>
         </is>
       </c>
       <c r="G376" s="26" t="n">
-        <v>30.976</v>
+        <v>31.134</v>
       </c>
       <c r="H376" s="26" t="n">
-        <v>80.953</v>
+        <v>82.22199999999999</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>4526</v>
+        <v>5170</v>
       </c>
       <c r="J376" s="24" t="n">
         <v>12</v>
@@ -38578,7 +38558,7 @@
       <c r="L376" s="51" t="n"/>
       <c r="M376" s="13" t="inlineStr">
         <is>
-          <t>象泉河源头</t>
+          <t>(革吉)亚热却藏</t>
         </is>
       </c>
       <c r="N376" s="51" t="n"/>
@@ -38621,7 +38601,7 @@
       </c>
       <c r="AB376" s="2" t="inlineStr">
         <is>
-          <t>噶尔县</t>
+          <t>革吉县</t>
         </is>
       </c>
       <c r="AC376" s="2" t="n"/>
@@ -38637,11 +38617,7 @@
         </is>
       </c>
       <c r="AG376" s="3" t="n"/>
-      <c r="AH376" s="2" t="inlineStr">
-        <is>
-          <t>青藏高原</t>
-        </is>
-      </c>
+      <c r="AH376" s="2" t="n"/>
       <c r="AI376" s="2" t="n"/>
     </row>
     <row r="377" ht="24" customHeight="1" s="54">
@@ -38654,17 +38630,17 @@
       <c r="E377" s="3" t="n"/>
       <c r="F377" s="35" t="inlineStr">
         <is>
-          <t>U7801</t>
+          <t>U7031</t>
         </is>
       </c>
       <c r="G377" s="26" t="n">
-        <v>30.594</v>
+        <v>30.976</v>
       </c>
       <c r="H377" s="26" t="n">
-        <v>82.473</v>
+        <v>80.953</v>
       </c>
       <c r="I377" s="2" t="n">
-        <v>5047</v>
+        <v>4526</v>
       </c>
       <c r="J377" s="24" t="n">
         <v>12</v>
@@ -38677,25 +38653,19 @@
       <c r="L377" s="51" t="n"/>
       <c r="M377" s="13" t="inlineStr">
         <is>
-          <t>(普兰)马攸木</t>
+          <t>象泉河源头</t>
         </is>
       </c>
       <c r="N377" s="51" t="n"/>
-      <c r="O377" s="29" t="n">
-        <v>-28.4</v>
-      </c>
-      <c r="P377" s="29" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="Q377" s="29" t="n">
-        <v>-17.6</v>
-      </c>
+      <c r="O377" s="29" t="n"/>
+      <c r="P377" s="29" t="n"/>
+      <c r="Q377" s="29" t="n"/>
       <c r="R377" s="45" t="n"/>
       <c r="S377" s="21" t="n"/>
       <c r="T377" s="33" t="n"/>
       <c r="U377" s="37" t="inlineStr">
         <is>
-          <t>(交通)</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="V377" s="2" t="inlineStr">
@@ -38726,7 +38696,7 @@
       </c>
       <c r="AB377" s="2" t="inlineStr">
         <is>
-          <t>普兰县</t>
+          <t>噶尔县</t>
         </is>
       </c>
       <c r="AC377" s="2" t="n"/>
@@ -38759,17 +38729,17 @@
       <c r="E378" s="3" t="n"/>
       <c r="F378" s="35" t="inlineStr">
         <is>
-          <t>U7014</t>
+          <t>U7801</t>
         </is>
       </c>
       <c r="G378" s="26" t="n">
-        <v>30.591</v>
+        <v>30.594</v>
       </c>
       <c r="H378" s="26" t="n">
-        <v>82.47499999999999</v>
+        <v>82.473</v>
       </c>
       <c r="I378" s="2" t="n">
-        <v>5039.2</v>
+        <v>5047</v>
       </c>
       <c r="J378" s="24" t="n">
         <v>12</v>
@@ -38782,19 +38752,25 @@
       <c r="L378" s="51" t="n"/>
       <c r="M378" s="13" t="inlineStr">
         <is>
-          <t>(普兰)马攸</t>
+          <t>(普兰)马攸木</t>
         </is>
       </c>
       <c r="N378" s="51" t="n"/>
-      <c r="O378" s="29" t="n"/>
-      <c r="P378" s="29" t="n"/>
-      <c r="Q378" s="29" t="n"/>
+      <c r="O378" s="29" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="P378" s="29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q378" s="29" t="n">
+        <v>-16.8</v>
+      </c>
       <c r="R378" s="45" t="n"/>
       <c r="S378" s="21" t="n"/>
       <c r="T378" s="33" t="n"/>
       <c r="U378" s="37" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>(交通)</t>
         </is>
       </c>
       <c r="V378" s="2" t="inlineStr">
@@ -38858,17 +38834,17 @@
       <c r="E379" s="3" t="n"/>
       <c r="F379" s="35" t="inlineStr">
         <is>
-          <t>U7502</t>
+          <t>U7014</t>
         </is>
       </c>
       <c r="G379" s="26" t="n">
-        <v>31.0958</v>
+        <v>30.591</v>
       </c>
       <c r="H379" s="26" t="n">
-        <v>81.36969999999999</v>
+        <v>82.47499999999999</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>5642</v>
+        <v>5039.2</v>
       </c>
       <c r="J379" s="24" t="n">
         <v>12</v>
@@ -38881,7 +38857,7 @@
       <c r="L379" s="51" t="n"/>
       <c r="M379" s="13" t="inlineStr">
         <is>
-          <t>冈仁波齐3</t>
+          <t>(普兰)马攸</t>
         </is>
       </c>
       <c r="N379" s="51" t="n"/>
@@ -38940,7 +38916,11 @@
         </is>
       </c>
       <c r="AG379" s="3" t="n"/>
-      <c r="AH379" s="2" t="n"/>
+      <c r="AH379" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AI379" s="2" t="n"/>
     </row>
     <row r="380" ht="24" customHeight="1" s="54">
@@ -38953,12 +38933,18 @@
       <c r="E380" s="3" t="n"/>
       <c r="F380" s="35" t="inlineStr">
         <is>
-          <t>U7101</t>
-        </is>
-      </c>
-      <c r="G380" s="26" t="n"/>
-      <c r="H380" s="26" t="n"/>
-      <c r="I380" s="2" t="n"/>
+          <t>U7502</t>
+        </is>
+      </c>
+      <c r="G380" s="26" t="n">
+        <v>31.0958</v>
+      </c>
+      <c r="H380" s="26" t="n">
+        <v>81.36969999999999</v>
+      </c>
+      <c r="I380" s="2" t="n">
+        <v>5642</v>
+      </c>
       <c r="J380" s="24" t="n">
         <v>12</v>
       </c>
@@ -38970,7 +38956,7 @@
       <c r="L380" s="51" t="n"/>
       <c r="M380" s="13" t="inlineStr">
         <is>
-          <t>冈仁波齐4</t>
+          <t>冈仁波齐3</t>
         </is>
       </c>
       <c r="N380" s="51" t="n"/>
@@ -39037,25 +39023,17 @@
         <v>380</v>
       </c>
       <c r="B381" s="2" t="n"/>
-      <c r="C381" s="41" t="inlineStr">
-        <is>
-          <t>55026</t>
-        </is>
-      </c>
+      <c r="C381" s="41" t="n"/>
       <c r="D381" s="2" t="n"/>
-      <c r="E381" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F381" s="35" t="n"/>
-      <c r="G381" s="26" t="n">
-        <v>34.4264</v>
-      </c>
-      <c r="H381" s="26" t="n">
-        <v>80.3861</v>
-      </c>
-      <c r="I381" s="2" t="n">
-        <v>5188.6</v>
-      </c>
+      <c r="E381" s="3" t="n"/>
+      <c r="F381" s="35" t="inlineStr">
+        <is>
+          <t>U7101</t>
+        </is>
+      </c>
+      <c r="G381" s="26" t="n"/>
+      <c r="H381" s="26" t="n"/>
+      <c r="I381" s="2" t="n"/>
       <c r="J381" s="24" t="n">
         <v>12</v>
       </c>
@@ -39067,7 +39045,7 @@
       <c r="L381" s="51" t="n"/>
       <c r="M381" s="13" t="inlineStr">
         <is>
-          <t>松西</t>
+          <t>冈仁波齐4</t>
         </is>
       </c>
       <c r="N381" s="51" t="n"/>
@@ -39103,8 +39081,16 @@
         </is>
       </c>
       <c r="Z381" s="3" t="n"/>
-      <c r="AA381" s="2" t="n"/>
-      <c r="AB381" s="2" t="n"/>
+      <c r="AA381" s="2" t="inlineStr">
+        <is>
+          <t>阿里地区</t>
+        </is>
+      </c>
+      <c r="AB381" s="2" t="inlineStr">
+        <is>
+          <t>普兰县</t>
+        </is>
+      </c>
       <c r="AC381" s="2" t="n"/>
       <c r="AD381" s="2" t="n"/>
       <c r="AE381" s="2" t="inlineStr">
@@ -39125,33 +39111,25 @@
       <c r="A382" s="2" t="n">
         <v>381</v>
       </c>
-      <c r="B382" s="2" t="inlineStr">
-        <is>
-          <t>ogimet</t>
-        </is>
-      </c>
+      <c r="B382" s="2" t="n"/>
       <c r="C382" s="41" t="inlineStr">
         <is>
-          <t>55664</t>
-        </is>
-      </c>
-      <c r="D382" s="2" t="inlineStr">
-        <is>
-          <t>Xegar</t>
-        </is>
-      </c>
+          <t>55026</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="n"/>
       <c r="E382" s="3" t="n">
         <v>99999</v>
       </c>
       <c r="F382" s="35" t="n"/>
       <c r="G382" s="26" t="n">
-        <v>28.6542</v>
+        <v>34.4264</v>
       </c>
       <c r="H382" s="26" t="n">
-        <v>87.1203</v>
+        <v>80.3861</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>4322</v>
+        <v>5188.6</v>
       </c>
       <c r="J382" s="24" t="n">
         <v>12</v>
@@ -39164,7 +39142,7 @@
       <c r="L382" s="51" t="n"/>
       <c r="M382" s="13" t="inlineStr">
         <is>
-          <t>定日</t>
+          <t>松西</t>
         </is>
       </c>
       <c r="N382" s="51" t="n"/>
@@ -39200,16 +39178,8 @@
         </is>
       </c>
       <c r="Z382" s="3" t="n"/>
-      <c r="AA382" s="2" t="inlineStr">
-        <is>
-          <t>日喀则市</t>
-        </is>
-      </c>
-      <c r="AB382" s="2" t="inlineStr">
-        <is>
-          <t>定日县</t>
-        </is>
-      </c>
+      <c r="AA382" s="2" t="n"/>
+      <c r="AB382" s="2" t="n"/>
       <c r="AC382" s="2" t="n"/>
       <c r="AD382" s="2" t="n"/>
       <c r="AE382" s="2" t="inlineStr">
@@ -39223,24 +39193,26 @@
         </is>
       </c>
       <c r="AG382" s="3" t="n"/>
-      <c r="AH382" s="2" t="inlineStr">
-        <is>
-          <t>青藏高原</t>
-        </is>
-      </c>
+      <c r="AH382" s="2" t="n"/>
       <c r="AI382" s="2" t="n"/>
     </row>
     <row r="383" ht="24" customHeight="1" s="54">
       <c r="A383" s="2" t="n">
         <v>382</v>
       </c>
-      <c r="B383" s="2" t="n"/>
-      <c r="C383" s="41" t="n">
-        <v>45007</v>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
+      <c r="C383" s="41" t="inlineStr">
+        <is>
+          <t>55664</t>
+        </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>Hong_Kong_(airport)</t>
+          <t>Xegar</t>
         </is>
       </c>
       <c r="E383" s="3" t="n">
@@ -39248,13 +39220,13 @@
       </c>
       <c r="F383" s="35" t="n"/>
       <c r="G383" s="26" t="n">
-        <v>22.308919</v>
+        <v>28.6542</v>
       </c>
       <c r="H383" s="26" t="n">
-        <v>113.914603</v>
+        <v>87.1203</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>4322</v>
       </c>
       <c r="J383" s="24" t="n">
         <v>12</v>
@@ -39267,7 +39239,7 @@
       <c r="L383" s="51" t="n"/>
       <c r="M383" s="13" t="inlineStr">
         <is>
-          <t>香港</t>
+          <t>定日</t>
         </is>
       </c>
       <c r="N383" s="51" t="n"/>
@@ -39277,13 +39249,21 @@
       <c r="R383" s="45" t="n"/>
       <c r="S383" s="21" t="n"/>
       <c r="T383" s="33" t="n"/>
-      <c r="U383" s="37" t="n"/>
+      <c r="U383" s="37" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
       <c r="V383" s="2" t="inlineStr">
         <is>
-          <t>香港</t>
-        </is>
-      </c>
-      <c r="W383" s="3" t="n"/>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="W383" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="X383" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -39295,8 +39275,16 @@
         </is>
       </c>
       <c r="Z383" s="3" t="n"/>
-      <c r="AA383" s="2" t="n"/>
-      <c r="AB383" s="2" t="n"/>
+      <c r="AA383" s="2" t="inlineStr">
+        <is>
+          <t>日喀则市</t>
+        </is>
+      </c>
+      <c r="AB383" s="2" t="inlineStr">
+        <is>
+          <t>定日县</t>
+        </is>
+      </c>
       <c r="AC383" s="2" t="n"/>
       <c r="AD383" s="2" t="n"/>
       <c r="AE383" s="2" t="inlineStr">
@@ -39310,7 +39298,11 @@
         </is>
       </c>
       <c r="AG383" s="3" t="n"/>
-      <c r="AH383" s="2" t="n"/>
+      <c r="AH383" s="2" t="inlineStr">
+        <is>
+          <t>青藏高原</t>
+        </is>
+      </c>
       <c r="AI383" s="2" t="n"/>
     </row>
     <row r="384" ht="24" customHeight="1" s="54">
@@ -39318,22 +39310,26 @@
         <v>383</v>
       </c>
       <c r="B384" s="2" t="n"/>
-      <c r="C384" s="41" t="n"/>
-      <c r="D384" s="2" t="n"/>
-      <c r="E384" s="3" t="n"/>
-      <c r="F384" s="35" t="inlineStr">
-        <is>
-          <t>Y6758</t>
-        </is>
-      </c>
+      <c r="C384" s="41" t="n">
+        <v>45007</v>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Hong_Kong_(airport)</t>
+        </is>
+      </c>
+      <c r="E384" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F384" s="35" t="n"/>
       <c r="G384" s="26" t="n">
-        <v>48.0197</v>
+        <v>22.308919</v>
       </c>
       <c r="H384" s="26" t="n">
-        <v>87.5517</v>
+        <v>113.914603</v>
       </c>
       <c r="I384" s="2" t="n">
-        <v>1194</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="J384" s="24" t="n">
         <v>12</v>
@@ -39346,7 +39342,7 @@
       <c r="L384" s="51" t="n"/>
       <c r="M384" s="13" t="inlineStr">
         <is>
-          <t>齐背岭水库</t>
+          <t>香港</t>
         </is>
       </c>
       <c r="N384" s="51" t="n"/>
@@ -39356,21 +39352,13 @@
       <c r="R384" s="45" t="n"/>
       <c r="S384" s="21" t="n"/>
       <c r="T384" s="33" t="n"/>
-      <c r="U384" s="37" t="inlineStr">
-        <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
+      <c r="U384" s="37" t="n"/>
       <c r="V384" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="W384" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="W384" s="3" t="n"/>
       <c r="X384" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -39382,16 +39370,8 @@
         </is>
       </c>
       <c r="Z384" s="3" t="n"/>
-      <c r="AA384" s="2" t="inlineStr">
-        <is>
-          <t>阿勒泰地区</t>
-        </is>
-      </c>
-      <c r="AB384" s="2" t="inlineStr">
-        <is>
-          <t>阿勒泰市</t>
-        </is>
-      </c>
+      <c r="AA384" s="2" t="n"/>
+      <c r="AB384" s="2" t="n"/>
       <c r="AC384" s="2" t="n"/>
       <c r="AD384" s="2" t="n"/>
       <c r="AE384" s="2" t="inlineStr">
@@ -39405,11 +39385,7 @@
         </is>
       </c>
       <c r="AG384" s="3" t="n"/>
-      <c r="AH384" s="2" t="inlineStr">
-        <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
+      <c r="AH384" s="2" t="n"/>
       <c r="AI384" s="2" t="n"/>
     </row>
     <row r="385" ht="24" customHeight="1" s="54">
@@ -39422,17 +39398,17 @@
       <c r="E385" s="3" t="n"/>
       <c r="F385" s="35" t="inlineStr">
         <is>
-          <t>Y5315</t>
+          <t>Y6758</t>
         </is>
       </c>
       <c r="G385" s="26" t="n">
-        <v>48.7217</v>
+        <v>48.0197</v>
       </c>
       <c r="H385" s="26" t="n">
-        <v>87.03060000000001</v>
+        <v>87.5517</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>1367</v>
+        <v>1194</v>
       </c>
       <c r="J385" s="24" t="n">
         <v>12</v>
@@ -39445,14 +39421,10 @@
       <c r="L385" s="51" t="n"/>
       <c r="M385" s="13" t="inlineStr">
         <is>
-          <t>喀纳斯</t>
-        </is>
-      </c>
-      <c r="N385" s="51" t="inlineStr">
-        <is>
-          <t>❄️</t>
-        </is>
-      </c>
+          <t>齐背岭水库</t>
+        </is>
+      </c>
+      <c r="N385" s="51" t="n"/>
       <c r="O385" s="29" t="n"/>
       <c r="P385" s="29" t="n"/>
       <c r="Q385" s="29" t="n"/>
@@ -39492,14 +39464,10 @@
       </c>
       <c r="AB385" s="2" t="inlineStr">
         <is>
-          <t>布尔津县</t>
-        </is>
-      </c>
-      <c r="AC385" s="2" t="inlineStr">
-        <is>
-          <t>禾木喀纳斯蒙古族乡</t>
-        </is>
-      </c>
+          <t>阿勒泰市</t>
+        </is>
+      </c>
+      <c r="AC385" s="2" t="n"/>
       <c r="AD385" s="2" t="n"/>
       <c r="AE385" s="2" t="inlineStr">
         <is>
@@ -39517,11 +39485,7 @@
           <t>阿尔泰山</t>
         </is>
       </c>
-      <c r="AI385" s="2" t="inlineStr">
-        <is>
-          <t>非定居点</t>
-        </is>
-      </c>
+      <c r="AI385" s="2" t="n"/>
     </row>
     <row r="386" ht="24" customHeight="1" s="54">
       <c r="A386" s="2" t="n">
@@ -39533,17 +39497,17 @@
       <c r="E386" s="3" t="n"/>
       <c r="F386" s="35" t="inlineStr">
         <is>
-          <t>Y5322</t>
+          <t>Y5315</t>
         </is>
       </c>
       <c r="G386" s="26" t="n">
-        <v>48.5842</v>
+        <v>48.7217</v>
       </c>
       <c r="H386" s="26" t="n">
-        <v>87.45780000000001</v>
+        <v>87.03060000000001</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>1223</v>
+        <v>1367</v>
       </c>
       <c r="J386" s="24" t="n">
         <v>12</v>
@@ -39556,7 +39520,7 @@
       <c r="L386" s="51" t="n"/>
       <c r="M386" s="13" t="inlineStr">
         <is>
-          <t>禾木村</t>
+          <t>喀纳斯</t>
         </is>
       </c>
       <c r="N386" s="51" t="inlineStr">
@@ -39564,12 +39528,8 @@
           <t>❄️</t>
         </is>
       </c>
-      <c r="O386" s="29" t="n">
-        <v>-18.6</v>
-      </c>
-      <c r="P386" s="29" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="O386" s="29" t="n"/>
+      <c r="P386" s="29" t="n"/>
       <c r="Q386" s="29" t="n"/>
       <c r="R386" s="45" t="n"/>
       <c r="S386" s="21" t="n"/>
@@ -39632,29 +39592,33 @@
           <t>阿尔泰山</t>
         </is>
       </c>
-      <c r="AI386" s="2" t="n"/>
+      <c r="AI386" s="2" t="inlineStr">
+        <is>
+          <t>非定居点</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="24" customHeight="1" s="54">
       <c r="A387" s="2" t="n">
         <v>386</v>
       </c>
       <c r="B387" s="2" t="n"/>
-      <c r="C387" s="41" t="n">
-        <v>51068</v>
-      </c>
+      <c r="C387" s="41" t="n"/>
       <c r="D387" s="2" t="n"/>
-      <c r="E387" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F387" s="35" t="n"/>
+      <c r="E387" s="3" t="n"/>
+      <c r="F387" s="35" t="inlineStr">
+        <is>
+          <t>Y5322</t>
+        </is>
+      </c>
       <c r="G387" s="26" t="n">
-        <v>47.125</v>
+        <v>48.5842</v>
       </c>
       <c r="H387" s="26" t="n">
-        <v>87.48139999999999</v>
+        <v>87.45780000000001</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>497.1</v>
+        <v>1223</v>
       </c>
       <c r="J387" s="24" t="n">
         <v>12</v>
@@ -39667,19 +39631,27 @@
       <c r="L387" s="51" t="n"/>
       <c r="M387" s="13" t="inlineStr">
         <is>
-          <t>福海</t>
-        </is>
-      </c>
-      <c r="N387" s="51" t="n"/>
-      <c r="O387" s="29" t="n"/>
-      <c r="P387" s="29" t="n"/>
+          <t>禾木村</t>
+        </is>
+      </c>
+      <c r="N387" s="51" t="inlineStr">
+        <is>
+          <t>❄️</t>
+        </is>
+      </c>
+      <c r="O387" s="29" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="P387" s="29" t="n">
+        <v>3.2</v>
+      </c>
       <c r="Q387" s="29" t="n"/>
       <c r="R387" s="45" t="n"/>
       <c r="S387" s="21" t="n"/>
       <c r="T387" s="33" t="n"/>
       <c r="U387" s="37" t="inlineStr">
         <is>
-          <t>乌伦古湖</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V387" s="2" t="inlineStr">
@@ -39710,10 +39682,14 @@
       </c>
       <c r="AB387" s="2" t="inlineStr">
         <is>
-          <t>福海县</t>
-        </is>
-      </c>
-      <c r="AC387" s="2" t="n"/>
+          <t>布尔津县</t>
+        </is>
+      </c>
+      <c r="AC387" s="2" t="inlineStr">
+        <is>
+          <t>禾木喀纳斯蒙古族乡</t>
+        </is>
+      </c>
       <c r="AD387" s="2" t="n"/>
       <c r="AE387" s="2" t="inlineStr">
         <is>
@@ -39728,7 +39704,7 @@
       <c r="AG387" s="3" t="n"/>
       <c r="AH387" s="2" t="inlineStr">
         <is>
-          <t>乌伦古湖</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="AI387" s="2" t="n"/>
@@ -39738,22 +39714,22 @@
         <v>387</v>
       </c>
       <c r="B388" s="2" t="n"/>
-      <c r="C388" s="41" t="n"/>
+      <c r="C388" s="41" t="n">
+        <v>51068</v>
+      </c>
       <c r="D388" s="2" t="n"/>
-      <c r="E388" s="3" t="n"/>
-      <c r="F388" s="35" t="inlineStr">
-        <is>
-          <t>Y6770</t>
-        </is>
-      </c>
+      <c r="E388" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F388" s="35" t="n"/>
       <c r="G388" s="26" t="n">
-        <v>47.1681</v>
+        <v>47.125</v>
       </c>
       <c r="H388" s="26" t="n">
-        <v>90.0903</v>
+        <v>87.48139999999999</v>
       </c>
       <c r="I388" s="2" t="n">
-        <v>3084</v>
+        <v>497.1</v>
       </c>
       <c r="J388" s="24" t="n">
         <v>12</v>
@@ -39766,25 +39742,19 @@
       <c r="L388" s="51" t="n"/>
       <c r="M388" s="13" t="inlineStr">
         <is>
-          <t>可可托海滑雪场</t>
+          <t>福海</t>
         </is>
       </c>
       <c r="N388" s="51" t="n"/>
-      <c r="O388" s="29" t="n">
-        <v>-17.3</v>
-      </c>
-      <c r="P388" s="29" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="Q388" s="29" t="n">
-        <v>-11.1</v>
-      </c>
+      <c r="O388" s="29" t="n"/>
+      <c r="P388" s="29" t="n"/>
+      <c r="Q388" s="29" t="n"/>
       <c r="R388" s="45" t="n"/>
       <c r="S388" s="21" t="n"/>
       <c r="T388" s="33" t="n"/>
       <c r="U388" s="37" t="inlineStr">
         <is>
-          <t>山顶</t>
+          <t>乌伦古湖</t>
         </is>
       </c>
       <c r="V388" s="2" t="inlineStr">
@@ -39815,7 +39785,7 @@
       </c>
       <c r="AB388" s="2" t="inlineStr">
         <is>
-          <t>富蕴县</t>
+          <t>福海县</t>
         </is>
       </c>
       <c r="AC388" s="2" t="n"/>
@@ -39833,14 +39803,10 @@
       <c r="AG388" s="3" t="n"/>
       <c r="AH388" s="2" t="inlineStr">
         <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
-      <c r="AI388" s="2" t="inlineStr">
-        <is>
-          <t>非定居点</t>
-        </is>
-      </c>
+          <t>乌伦古湖</t>
+        </is>
+      </c>
+      <c r="AI388" s="2" t="n"/>
     </row>
     <row r="389" ht="24" customHeight="1" s="54">
       <c r="A389" s="2" t="n">
@@ -39852,17 +39818,17 @@
       <c r="E389" s="3" t="n"/>
       <c r="F389" s="35" t="inlineStr">
         <is>
-          <t>Y5316</t>
+          <t>Y6770</t>
         </is>
       </c>
       <c r="G389" s="26" t="n">
-        <v>47.1381</v>
+        <v>47.1681</v>
       </c>
       <c r="H389" s="26" t="n">
-        <v>85.5975</v>
+        <v>90.0903</v>
       </c>
       <c r="I389" s="2" t="n">
-        <v>2914</v>
+        <v>3084</v>
       </c>
       <c r="J389" s="24" t="n">
         <v>12</v>
@@ -39875,7 +39841,7 @@
       <c r="L389" s="51" t="n"/>
       <c r="M389" s="13" t="inlineStr">
         <is>
-          <t>吉木乃冰川</t>
+          <t>可可托海滑雪场</t>
         </is>
       </c>
       <c r="N389" s="51" t="n"/>
@@ -39887,7 +39853,7 @@
       <c r="T389" s="33" t="n"/>
       <c r="U389" s="37" t="inlineStr">
         <is>
-          <t>阿勒泰</t>
+          <t>山顶</t>
         </is>
       </c>
       <c r="V389" s="2" t="inlineStr">
@@ -39918,7 +39884,7 @@
       </c>
       <c r="AB389" s="2" t="inlineStr">
         <is>
-          <t>吉木乃县</t>
+          <t>富蕴县</t>
         </is>
       </c>
       <c r="AC389" s="2" t="n"/>
@@ -39934,8 +39900,16 @@
         </is>
       </c>
       <c r="AG389" s="3" t="n"/>
-      <c r="AH389" s="2" t="n"/>
-      <c r="AI389" s="2" t="n"/>
+      <c r="AH389" s="2" t="inlineStr">
+        <is>
+          <t>阿尔泰山</t>
+        </is>
+      </c>
+      <c r="AI389" s="2" t="inlineStr">
+        <is>
+          <t>非定居点</t>
+        </is>
+      </c>
     </row>
     <row r="390" ht="24" customHeight="1" s="54">
       <c r="A390" s="2" t="n">
@@ -39947,17 +39921,17 @@
       <c r="E390" s="3" t="n"/>
       <c r="F390" s="35" t="inlineStr">
         <is>
-          <t>Y5347</t>
+          <t>Y5316</t>
         </is>
       </c>
       <c r="G390" s="26" t="n">
-        <v>46.1772</v>
+        <v>47.1381</v>
       </c>
       <c r="H390" s="26" t="n">
-        <v>90.5356</v>
+        <v>85.5975</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>1071.1</v>
+        <v>2914</v>
       </c>
       <c r="J390" s="24" t="n">
         <v>12</v>
@@ -39970,7 +39944,7 @@
       <c r="L390" s="51" t="n"/>
       <c r="M390" s="13" t="inlineStr">
         <is>
-          <t>塔克什肯镇</t>
+          <t>吉木乃冰川</t>
         </is>
       </c>
       <c r="N390" s="51" t="n"/>
@@ -39982,7 +39956,7 @@
       <c r="T390" s="33" t="n"/>
       <c r="U390" s="37" t="inlineStr">
         <is>
-          <t>阿尔泰山</t>
+          <t>阿勒泰</t>
         </is>
       </c>
       <c r="V390" s="2" t="inlineStr">
@@ -40013,7 +39987,7 @@
       </c>
       <c r="AB390" s="2" t="inlineStr">
         <is>
-          <t>青河县</t>
+          <t>吉木乃县</t>
         </is>
       </c>
       <c r="AC390" s="2" t="n"/>
@@ -40029,42 +40003,30 @@
         </is>
       </c>
       <c r="AG390" s="3" t="n"/>
-      <c r="AH390" s="2" t="inlineStr">
-        <is>
-          <t>阿尔泰山</t>
-        </is>
-      </c>
+      <c r="AH390" s="2" t="n"/>
       <c r="AI390" s="2" t="n"/>
     </row>
     <row r="391" ht="24" customHeight="1" s="54">
       <c r="A391" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="B391" s="2" t="inlineStr">
-        <is>
-          <t>ogimet</t>
-        </is>
-      </c>
-      <c r="C391" s="41" t="n">
-        <v>51087</v>
-      </c>
-      <c r="D391" s="2" t="inlineStr">
-        <is>
-          <t>Kueerqisi</t>
-        </is>
-      </c>
-      <c r="E391" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F391" s="35" t="n"/>
+      <c r="B391" s="2" t="n"/>
+      <c r="C391" s="41" t="n"/>
+      <c r="D391" s="2" t="n"/>
+      <c r="E391" s="3" t="n"/>
+      <c r="F391" s="35" t="inlineStr">
+        <is>
+          <t>Y5347</t>
+        </is>
+      </c>
       <c r="G391" s="26" t="n">
-        <v>47.02</v>
+        <v>46.1772</v>
       </c>
       <c r="H391" s="26" t="n">
-        <v>89.5</v>
+        <v>90.5356</v>
       </c>
       <c r="I391" s="2" t="n">
-        <v>860.4</v>
+        <v>1071.1</v>
       </c>
       <c r="J391" s="24" t="n">
         <v>12</v>
@@ -40077,7 +40039,7 @@
       <c r="L391" s="51" t="n"/>
       <c r="M391" s="13" t="inlineStr">
         <is>
-          <t>富蕴</t>
+          <t>塔克什肯镇</t>
         </is>
       </c>
       <c r="N391" s="51" t="n"/>
@@ -40089,7 +40051,7 @@
       <c r="T391" s="33" t="n"/>
       <c r="U391" s="37" t="inlineStr">
         <is>
-          <t>额尔齐斯河</t>
+          <t>阿尔泰山</t>
         </is>
       </c>
       <c r="V391" s="2" t="inlineStr">
@@ -40118,7 +40080,11 @@
           <t>阿勒泰地区</t>
         </is>
       </c>
-      <c r="AB391" s="2" t="n"/>
+      <c r="AB391" s="2" t="inlineStr">
+        <is>
+          <t>青河县</t>
+        </is>
+      </c>
       <c r="AC391" s="2" t="n"/>
       <c r="AD391" s="2" t="n"/>
       <c r="AE391" s="2" t="inlineStr">
@@ -40143,16 +40109,32 @@
       <c r="A392" s="2" t="n">
         <v>391</v>
       </c>
-      <c r="B392" s="2" t="n"/>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>ogimet</t>
+        </is>
+      </c>
       <c r="C392" s="41" t="n">
-        <v>51058</v>
-      </c>
-      <c r="D392" s="2" t="n"/>
-      <c r="E392" s="3" t="n"/>
+        <v>51087</v>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Kueerqisi</t>
+        </is>
+      </c>
+      <c r="E392" s="3" t="n">
+        <v>99999</v>
+      </c>
       <c r="F392" s="35" t="n"/>
-      <c r="G392" s="26" t="n"/>
-      <c r="H392" s="26" t="n"/>
-      <c r="I392" s="2" t="n"/>
+      <c r="G392" s="26" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="H392" s="26" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="I392" s="2" t="n">
+        <v>860.4</v>
+      </c>
       <c r="J392" s="24" t="n">
         <v>12</v>
       </c>
@@ -40164,7 +40146,7 @@
       <c r="L392" s="51" t="n"/>
       <c r="M392" s="13" t="inlineStr">
         <is>
-          <t>阿克达拉</t>
+          <t>富蕴</t>
         </is>
       </c>
       <c r="N392" s="51" t="n"/>
@@ -40176,7 +40158,7 @@
       <c r="T392" s="33" t="n"/>
       <c r="U392" s="37" t="inlineStr">
         <is>
-          <t>乌伦古湖</t>
+          <t>额尔齐斯河</t>
         </is>
       </c>
       <c r="V392" s="2" t="inlineStr">
@@ -40219,7 +40201,11 @@
         </is>
       </c>
       <c r="AG392" s="3" t="n"/>
-      <c r="AH392" s="2" t="n"/>
+      <c r="AH392" s="2" t="inlineStr">
+        <is>
+          <t>阿尔泰山</t>
+        </is>
+      </c>
       <c r="AI392" s="2" t="n"/>
     </row>
     <row r="393" ht="24" customHeight="1" s="54">
@@ -40228,22 +40214,14 @@
       </c>
       <c r="B393" s="2" t="n"/>
       <c r="C393" s="41" t="n">
-        <v>51060</v>
+        <v>51058</v>
       </c>
       <c r="D393" s="2" t="n"/>
-      <c r="E393" s="3" t="n">
-        <v>99999</v>
-      </c>
+      <c r="E393" s="3" t="n"/>
       <c r="F393" s="35" t="n"/>
-      <c r="G393" s="26" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="H393" s="26" t="n">
-        <v>86.87</v>
-      </c>
-      <c r="I393" s="2" t="n">
-        <v>473.9</v>
-      </c>
+      <c r="G393" s="26" t="n"/>
+      <c r="H393" s="26" t="n"/>
+      <c r="I393" s="2" t="n"/>
       <c r="J393" s="24" t="n">
         <v>12</v>
       </c>
@@ -40255,7 +40233,7 @@
       <c r="L393" s="51" t="n"/>
       <c r="M393" s="13" t="inlineStr">
         <is>
-          <t>布尔津</t>
+          <t>阿克达拉</t>
         </is>
       </c>
       <c r="N393" s="51" t="n"/>
@@ -40267,7 +40245,7 @@
       <c r="T393" s="33" t="n"/>
       <c r="U393" s="37" t="inlineStr">
         <is>
-          <t>额尔齐斯河</t>
+          <t>乌伦古湖</t>
         </is>
       </c>
       <c r="V393" s="2" t="inlineStr">
@@ -40310,11 +40288,7 @@
         </is>
       </c>
       <c r="AG393" s="3" t="n"/>
-      <c r="AH393" s="2" t="inlineStr">
-        <is>
-          <t>额尔齐斯河</t>
-        </is>
-      </c>
+      <c r="AH393" s="2" t="n"/>
       <c r="AI393" s="2" t="n"/>
     </row>
     <row r="394" ht="24" customHeight="1" s="54">
@@ -40322,22 +40296,22 @@
         <v>393</v>
       </c>
       <c r="B394" s="2" t="n"/>
-      <c r="C394" s="41" t="n"/>
+      <c r="C394" s="41" t="n">
+        <v>51060</v>
+      </c>
       <c r="D394" s="2" t="n"/>
-      <c r="E394" s="3" t="n"/>
-      <c r="F394" s="35" t="inlineStr">
-        <is>
-          <t>Y5826</t>
-        </is>
-      </c>
+      <c r="E394" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F394" s="35" t="n"/>
       <c r="G394" s="26" t="n">
-        <v>42.716</v>
+        <v>47.7</v>
       </c>
       <c r="H394" s="26" t="n">
-        <v>84.27200000000001</v>
+        <v>86.87</v>
       </c>
       <c r="I394" s="2" t="n">
-        <v>2404.3</v>
+        <v>473.9</v>
       </c>
       <c r="J394" s="24" t="n">
         <v>12</v>
@@ -40350,7 +40324,7 @@
       <c r="L394" s="51" t="n"/>
       <c r="M394" s="13" t="inlineStr">
         <is>
-          <t>德尔比勒金牧场</t>
+          <t>布尔津</t>
         </is>
       </c>
       <c r="N394" s="51" t="n"/>
@@ -40362,7 +40336,7 @@
       <c r="T394" s="33" t="n"/>
       <c r="U394" s="37" t="inlineStr">
         <is>
-          <t>巴音布鲁克</t>
+          <t>额尔齐斯河</t>
         </is>
       </c>
       <c r="V394" s="2" t="inlineStr">
@@ -40388,14 +40362,10 @@
       <c r="Z394" s="3" t="n"/>
       <c r="AA394" s="2" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
-        </is>
-      </c>
-      <c r="AB394" s="2" t="inlineStr">
-        <is>
-          <t>和静县</t>
-        </is>
-      </c>
+          <t>阿勒泰地区</t>
+        </is>
+      </c>
+      <c r="AB394" s="2" t="n"/>
       <c r="AC394" s="2" t="n"/>
       <c r="AD394" s="2" t="n"/>
       <c r="AE394" s="2" t="inlineStr">
@@ -40411,7 +40381,7 @@
       <c r="AG394" s="3" t="n"/>
       <c r="AH394" s="2" t="inlineStr">
         <is>
-          <t>天山</t>
+          <t>额尔齐斯河</t>
         </is>
       </c>
       <c r="AI394" s="2" t="n"/>
@@ -40421,22 +40391,22 @@
         <v>394</v>
       </c>
       <c r="B395" s="2" t="n"/>
-      <c r="C395" s="41" t="n">
-        <v>51337</v>
-      </c>
+      <c r="C395" s="41" t="n"/>
       <c r="D395" s="2" t="n"/>
-      <c r="E395" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F395" s="35" t="n"/>
+      <c r="E395" s="3" t="n"/>
+      <c r="F395" s="35" t="inlineStr">
+        <is>
+          <t>Y5826</t>
+        </is>
+      </c>
       <c r="G395" s="26" t="n">
-        <v>44.6028</v>
+        <v>42.716</v>
       </c>
       <c r="H395" s="26" t="n">
-        <v>81.3878</v>
+        <v>84.27200000000001</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>2100</v>
+        <v>2404.3</v>
       </c>
       <c r="J395" s="24" t="n">
         <v>12</v>
@@ -40449,7 +40419,7 @@
       <c r="L395" s="51" t="n"/>
       <c r="M395" s="13" t="inlineStr">
         <is>
-          <t>赛里木湖</t>
+          <t>德尔比勒金牧场</t>
         </is>
       </c>
       <c r="N395" s="51" t="n"/>
@@ -40461,7 +40431,7 @@
       <c r="T395" s="33" t="n"/>
       <c r="U395" s="37" t="inlineStr">
         <is>
-          <t>天山</t>
+          <t>巴音布鲁克</t>
         </is>
       </c>
       <c r="V395" s="2" t="inlineStr">
@@ -40487,12 +40457,12 @@
       <c r="Z395" s="3" t="n"/>
       <c r="AA395" s="2" t="inlineStr">
         <is>
-          <t>博尔塔拉蒙古自治州</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="AB395" s="2" t="inlineStr">
         <is>
-          <t>博乐市</t>
+          <t>和静县</t>
         </is>
       </c>
       <c r="AC395" s="2" t="n"/>
@@ -40513,21 +40483,15 @@
           <t>天山</t>
         </is>
       </c>
-      <c r="AI395" s="2" t="inlineStr">
-        <is>
-          <t>非定居点</t>
-        </is>
-      </c>
+      <c r="AI395" s="2" t="n"/>
     </row>
     <row r="396" ht="24" customHeight="1" s="54">
       <c r="A396" s="2" t="n">
         <v>395</v>
       </c>
       <c r="B396" s="2" t="n"/>
-      <c r="C396" s="41" t="inlineStr">
-        <is>
-          <t>51701</t>
-        </is>
+      <c r="C396" s="41" t="n">
+        <v>51337</v>
       </c>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="3" t="n">
@@ -40535,13 +40499,13 @@
       </c>
       <c r="F396" s="35" t="n"/>
       <c r="G396" s="26" t="n">
-        <v>40.5122</v>
+        <v>44.6028</v>
       </c>
       <c r="H396" s="26" t="n">
-        <v>75.3914</v>
+        <v>81.3878</v>
       </c>
       <c r="I396" s="2" t="n">
-        <v>3470.2</v>
+        <v>2100</v>
       </c>
       <c r="J396" s="24" t="n">
         <v>12</v>
@@ -40554,7 +40518,7 @@
       <c r="L396" s="51" t="n"/>
       <c r="M396" s="13" t="inlineStr">
         <is>
-          <t>吐尔尕特</t>
+          <t>赛里木湖</t>
         </is>
       </c>
       <c r="N396" s="51" t="n"/>
@@ -40592,12 +40556,12 @@
       <c r="Z396" s="3" t="n"/>
       <c r="AA396" s="2" t="inlineStr">
         <is>
-          <t>喀什地区</t>
+          <t>博尔塔拉蒙古自治州</t>
         </is>
       </c>
       <c r="AB396" s="2" t="inlineStr">
         <is>
-          <t>喀什市</t>
+          <t>博乐市</t>
         </is>
       </c>
       <c r="AC396" s="2" t="n"/>
@@ -40618,7 +40582,11 @@
           <t>天山</t>
         </is>
       </c>
-      <c r="AI396" s="2" t="n"/>
+      <c r="AI396" s="2" t="inlineStr">
+        <is>
+          <t>非定居点</t>
+        </is>
+      </c>
     </row>
     <row r="397" ht="24" customHeight="1" s="54">
       <c r="A397" s="2" t="n">
@@ -40627,7 +40595,7 @@
       <c r="B397" s="2" t="n"/>
       <c r="C397" s="41" t="inlineStr">
         <is>
-          <t>51572</t>
+          <t>51701</t>
         </is>
       </c>
       <c r="D397" s="2" t="n"/>
@@ -40636,13 +40604,13 @@
       </c>
       <c r="F397" s="35" t="n"/>
       <c r="G397" s="26" t="n">
-        <v>42.8908</v>
+        <v>40.5122</v>
       </c>
       <c r="H397" s="26" t="n">
-        <v>89.3056</v>
+        <v>75.3914</v>
       </c>
       <c r="I397" s="2" t="n">
-        <v>-48.8</v>
+        <v>3470.2</v>
       </c>
       <c r="J397" s="24" t="n">
         <v>12</v>
@@ -40655,7 +40623,7 @@
       <c r="L397" s="51" t="n"/>
       <c r="M397" s="13" t="inlineStr">
         <is>
-          <t>东坎</t>
+          <t>吐尔尕特</t>
         </is>
       </c>
       <c r="N397" s="51" t="n"/>
@@ -40667,7 +40635,7 @@
       <c r="T397" s="33" t="n"/>
       <c r="U397" s="37" t="inlineStr">
         <is>
-          <t>吐鲁番</t>
+          <t>天山</t>
         </is>
       </c>
       <c r="V397" s="2" t="inlineStr">
@@ -40693,12 +40661,12 @@
       <c r="Z397" s="3" t="n"/>
       <c r="AA397" s="2" t="inlineStr">
         <is>
-          <t>吐鲁番市</t>
+          <t>喀什地区</t>
         </is>
       </c>
       <c r="AB397" s="2" t="inlineStr">
         <is>
-          <t>高昌区</t>
+          <t>喀什市</t>
         </is>
       </c>
       <c r="AC397" s="2" t="n"/>
@@ -40714,7 +40682,11 @@
         </is>
       </c>
       <c r="AG397" s="3" t="n"/>
-      <c r="AH397" s="2" t="n"/>
+      <c r="AH397" s="2" t="inlineStr">
+        <is>
+          <t>天山</t>
+        </is>
+      </c>
       <c r="AI397" s="2" t="n"/>
     </row>
     <row r="398" ht="24" customHeight="1" s="54">
@@ -40722,22 +40694,24 @@
         <v>397</v>
       </c>
       <c r="B398" s="2" t="n"/>
-      <c r="C398" s="41" t="n"/>
+      <c r="C398" s="41" t="inlineStr">
+        <is>
+          <t>51572</t>
+        </is>
+      </c>
       <c r="D398" s="2" t="n"/>
-      <c r="E398" s="3" t="n"/>
-      <c r="F398" s="35" t="inlineStr">
-        <is>
-          <t>Y8049</t>
-        </is>
-      </c>
+      <c r="E398" s="3" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F398" s="35" t="n"/>
       <c r="G398" s="26" t="n">
-        <v>42.6856</v>
+        <v>42.8908</v>
       </c>
       <c r="H398" s="26" t="n">
-        <v>89.0656</v>
+        <v>89.3056</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>-106.4</v>
+        <v>-48.8</v>
       </c>
       <c r="J398" s="24" t="n">
         <v>12</v>
@@ -40750,7 +40724,7 @@
       <c r="L398" s="51" t="n"/>
       <c r="M398" s="13" t="inlineStr">
         <is>
-          <t>新鑫盐矿</t>
+          <t>东坎</t>
         </is>
       </c>
       <c r="N398" s="51" t="n"/>
@@ -40822,17 +40796,17 @@
       <c r="E399" s="3" t="n"/>
       <c r="F399" s="35" t="inlineStr">
         <is>
-          <t>Y5774</t>
+          <t>Y8049</t>
         </is>
       </c>
       <c r="G399" s="26" t="n">
-        <v>42.9044</v>
+        <v>42.6856</v>
       </c>
       <c r="H399" s="26" t="n">
-        <v>89.4422</v>
+        <v>89.0656</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>-52</v>
+        <v>-106.4</v>
       </c>
       <c r="J399" s="24" t="n">
         <v>12</v>
@@ -40845,7 +40819,7 @@
       <c r="L399" s="51" t="n"/>
       <c r="M399" s="13" t="inlineStr">
         <is>
-          <t>三堡乡</t>
+          <t>新鑫盐矿</t>
         </is>
       </c>
       <c r="N399" s="51" t="n"/>
@@ -40912,24 +40886,22 @@
         <v>399</v>
       </c>
       <c r="B400" s="2" t="n"/>
-      <c r="C400" s="41" t="inlineStr">
-        <is>
-          <t>51571</t>
-        </is>
-      </c>
+      <c r="C400" s="41" t="n"/>
       <c r="D400" s="2" t="n"/>
-      <c r="E400" s="3" t="n">
-        <v>99999</v>
-      </c>
-      <c r="F400" s="35" t="n"/>
+      <c r="E400" s="3" t="n"/>
+      <c r="F400" s="35" t="inlineStr">
+        <is>
+          <t>Y5774</t>
+        </is>
+      </c>
       <c r="G400" s="26" t="n">
-        <v>42.7669</v>
+        <v>42.9044</v>
       </c>
       <c r="H400" s="26" t="n">
-        <v>88.60080000000001</v>
+        <v>89.4422</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>43.9</v>
+        <v>-52</v>
       </c>
       <c r="J400" s="24" t="n">
         <v>12</v>
@@ -40942,7 +40914,7 @@
       <c r="L400" s="51" t="n"/>
       <c r="M400" s="13" t="inlineStr">
         <is>
-          <t>托克逊</t>
+          <t>三堡乡</t>
         </is>
       </c>
       <c r="N400" s="51" t="n"/>
@@ -40985,7 +40957,7 @@
       </c>
       <c r="AB400" s="2" t="inlineStr">
         <is>
-          <t>托克逊县</t>
+          <t>高昌区</t>
         </is>
       </c>
       <c r="AC400" s="2" t="n"/>
@@ -41011,7 +40983,7 @@
       <c r="B401" s="2" t="n"/>
       <c r="C401" s="41" t="inlineStr">
         <is>
-          <t>51468</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="D401" s="2" t="n"/>
@@ -41020,13 +40992,13 @@
       </c>
       <c r="F401" s="35" t="n"/>
       <c r="G401" s="26" t="n">
-        <v>43.1131</v>
+        <v>42.7669</v>
       </c>
       <c r="H401" s="26" t="n">
-        <v>86.84310000000001</v>
+        <v>88.60080000000001</v>
       </c>
       <c r="I401" s="2" t="n">
-        <v>3540.5</v>
+        <v>43.9</v>
       </c>
       <c r="J401" s="24" t="n">
         <v>12</v>
@@ -41039,7 +41011,7 @@
       <c r="L401" s="51" t="n"/>
       <c r="M401" s="13" t="inlineStr">
         <is>
-          <t>天山大西沟</t>
+          <t>托克逊</t>
         </is>
       </c>
       <c r="N401" s="51" t="n"/>
@@ -41051,7 +41023,7 @@
       <c r="T401" s="33" t="n"/>
       <c r="U401" s="37" t="inlineStr">
         <is>
-          <t>天山</t>
+          <t>吐鲁番</t>
         </is>
       </c>
       <c r="V401" s="2" t="inlineStr">
@@ -41077,12 +41049,12 @@
       <c r="Z401" s="3" t="n"/>
       <c r="AA401" s="2" t="inlineStr">
         <is>
-          <t>乌鲁木齐市</t>
+          <t>吐鲁番市</t>
         </is>
       </c>
       <c r="AB401" s="2" t="inlineStr">
         <is>
-          <t>乌鲁木齐县</t>
+          <t>托克逊县</t>
         </is>
       </c>
       <c r="AC401" s="2" t="n"/>
@@ -41098,11 +41070,7 @@
         </is>
       </c>
       <c r="AG401" s="3" t="n"/>
-      <c r="AH401" s="2" t="inlineStr">
-        <is>
-          <t>天山</t>
-        </is>
-      </c>
+      <c r="AH401" s="2" t="n"/>
       <c r="AI401" s="2" t="n"/>
     </row>
     <row r="402" ht="24" customHeight="1" s="54">
@@ -41112,7 +41080,7 @@
       <c r="B402" s="2" t="n"/>
       <c r="C402" s="41" t="inlineStr">
         <is>
-          <t>56976</t>
+          <t>51468</t>
         </is>
       </c>
       <c r="D402" s="2" t="n"/>
@@ -41121,18 +41089,18 @@
       </c>
       <c r="F402" s="35" t="n"/>
       <c r="G402" s="26" t="n">
-        <v>23.2286</v>
+        <v>43.1131</v>
       </c>
       <c r="H402" s="26" t="n">
-        <v>102.8214</v>
+        <v>86.84310000000001</v>
       </c>
       <c r="I402" s="2" t="n">
-        <v>312.3</v>
+        <v>3540.5</v>
       </c>
       <c r="J402" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="K402" s="43" t="inlineStr">
+      <c r="K402" s="28" t="inlineStr">
         <is>
           <t>🇨🇳</t>
         </is>
@@ -41140,7 +41108,7 @@
       <c r="L402" s="51" t="n"/>
       <c r="M402" s="13" t="inlineStr">
         <is>
-          <t>元阳</t>
+          <t>天山大西沟</t>
         </is>
       </c>
       <c r="N402" s="51" t="n"/>
@@ -41152,12 +41120,12 @@
       <c r="T402" s="33" t="n"/>
       <c r="U402" s="37" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天山</t>
         </is>
       </c>
       <c r="V402" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="W402" s="3" t="inlineStr">
@@ -41178,12 +41146,12 @@
       <c r="Z402" s="3" t="n"/>
       <c r="AA402" s="2" t="inlineStr">
         <is>
-          <t>红河哈尼族彝族自治州</t>
+          <t>乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB402" s="2" t="inlineStr">
         <is>
-          <t>元阳县</t>
+          <t>乌鲁木齐县</t>
         </is>
       </c>
       <c r="AC402" s="2" t="n"/>
@@ -41199,7 +41167,11 @@
         </is>
       </c>
       <c r="AG402" s="3" t="n"/>
-      <c r="AH402" s="2" t="n"/>
+      <c r="AH402" s="2" t="inlineStr">
+        <is>
+          <t>天山</t>
+        </is>
+      </c>
       <c r="AI402" s="2" t="n"/>
     </row>
     <row r="403" ht="24" customHeight="1" s="54">
@@ -41209,7 +41181,7 @@
       <c r="B403" s="2" t="n"/>
       <c r="C403" s="41" t="inlineStr">
         <is>
-          <t>56673</t>
+          <t>56976</t>
         </is>
       </c>
       <c r="D403" s="2" t="n"/>
@@ -41218,18 +41190,18 @@
       </c>
       <c r="F403" s="35" t="n"/>
       <c r="G403" s="26" t="n">
-        <v>26.9181</v>
+        <v>23.2286</v>
       </c>
       <c r="H403" s="26" t="n">
-        <v>102.9267</v>
+        <v>102.8214</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>893.9</v>
+        <v>312.3</v>
       </c>
       <c r="J403" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="K403" s="28" t="inlineStr">
+      <c r="K403" s="43" t="inlineStr">
         <is>
           <t>🇨🇳</t>
         </is>
@@ -41237,7 +41209,7 @@
       <c r="L403" s="51" t="n"/>
       <c r="M403" s="13" t="inlineStr">
         <is>
-          <t>巧家</t>
+          <t>元阳</t>
         </is>
       </c>
       <c r="N403" s="51" t="n"/>
@@ -41275,12 +41247,12 @@
       <c r="Z403" s="3" t="n"/>
       <c r="AA403" s="2" t="inlineStr">
         <is>
-          <t>昭通市</t>
+          <t>红河哈尼族彝族自治州</t>
         </is>
       </c>
       <c r="AB403" s="2" t="inlineStr">
         <is>
-          <t>巧家县</t>
+          <t>元阳县</t>
         </is>
       </c>
       <c r="AC403" s="2" t="n"/>
@@ -41300,19 +41272,43 @@
       <c r="AI403" s="2" t="n"/>
     </row>
     <row r="404" ht="24" customHeight="1" s="54">
-      <c r="A404" s="12" t="n"/>
+      <c r="A404" s="2" t="n">
+        <v>403</v>
+      </c>
       <c r="B404" s="2" t="n"/>
-      <c r="C404" s="41" t="n"/>
+      <c r="C404" s="41" t="inlineStr">
+        <is>
+          <t>56673</t>
+        </is>
+      </c>
       <c r="D404" s="2" t="n"/>
-      <c r="E404" s="3" t="n"/>
+      <c r="E404" s="3" t="n">
+        <v>99999</v>
+      </c>
       <c r="F404" s="35" t="n"/>
-      <c r="G404" s="26" t="n"/>
-      <c r="H404" s="26" t="n"/>
-      <c r="I404" s="2" t="n"/>
-      <c r="J404" s="24" t="n"/>
-      <c r="K404" s="28" t="n"/>
+      <c r="G404" s="26" t="n">
+        <v>26.9181</v>
+      </c>
+      <c r="H404" s="26" t="n">
+        <v>102.9267</v>
+      </c>
+      <c r="I404" s="2" t="n">
+        <v>893.9</v>
+      </c>
+      <c r="J404" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="K404" s="28" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
       <c r="L404" s="51" t="n"/>
-      <c r="M404" s="13" t="n"/>
+      <c r="M404" s="13" t="inlineStr">
+        <is>
+          <t>巧家</t>
+        </is>
+      </c>
       <c r="N404" s="51" t="n"/>
       <c r="O404" s="29" t="n"/>
       <c r="P404" s="29" t="n"/>
@@ -41320,18 +41316,54 @@
       <c r="R404" s="45" t="n"/>
       <c r="S404" s="21" t="n"/>
       <c r="T404" s="33" t="n"/>
-      <c r="U404" s="37" t="n"/>
-      <c r="V404" s="2" t="n"/>
-      <c r="W404" s="3" t="n"/>
-      <c r="X404" s="3" t="n"/>
-      <c r="Y404" s="3" t="n"/>
+      <c r="U404" s="37" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="V404" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="W404" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X404" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y404" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="Z404" s="3" t="n"/>
-      <c r="AA404" s="2" t="n"/>
-      <c r="AB404" s="2" t="n"/>
+      <c r="AA404" s="2" t="inlineStr">
+        <is>
+          <t>昭通市</t>
+        </is>
+      </c>
+      <c r="AB404" s="2" t="inlineStr">
+        <is>
+          <t>巧家县</t>
+        </is>
+      </c>
       <c r="AC404" s="2" t="n"/>
       <c r="AD404" s="2" t="n"/>
-      <c r="AE404" s="2" t="n"/>
-      <c r="AF404" s="3" t="n"/>
+      <c r="AE404" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="AF404" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AG404" s="3" t="n"/>
       <c r="AH404" s="2" t="n"/>
       <c r="AI404" s="2" t="n"/>
@@ -42827,7 +42859,7 @@
       <c r="H445" s="26" t="n"/>
       <c r="I445" s="2" t="n"/>
       <c r="J445" s="24" t="n"/>
-      <c r="K445" s="3" t="n"/>
+      <c r="K445" s="28" t="n"/>
       <c r="L445" s="51" t="n"/>
       <c r="M445" s="13" t="n"/>
       <c r="N445" s="51" t="n"/>
@@ -43002,9 +43034,7 @@
       <c r="AI449" s="2" t="n"/>
     </row>
     <row r="450" ht="24" customHeight="1" s="54">
-      <c r="A450" s="11" t="n">
-        <v>999</v>
-      </c>
+      <c r="A450" s="12" t="n"/>
       <c r="B450" s="2" t="n"/>
       <c r="C450" s="41" t="n"/>
       <c r="D450" s="2" t="n"/>
@@ -43018,11 +43048,7 @@
       <c r="L450" s="51" t="n"/>
       <c r="M450" s="13" t="n"/>
       <c r="N450" s="51" t="n"/>
-      <c r="O450" s="29" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
+      <c r="O450" s="29" t="n"/>
       <c r="P450" s="29" t="n"/>
       <c r="Q450" s="29" t="n"/>
       <c r="R450" s="45" t="n"/>
@@ -43044,15 +43070,58 @@
       <c r="AH450" s="2" t="n"/>
       <c r="AI450" s="2" t="n"/>
     </row>
+    <row r="451" ht="24" customHeight="1" s="54">
+      <c r="A451" s="11" t="n">
+        <v>999</v>
+      </c>
+      <c r="B451" s="2" t="n"/>
+      <c r="C451" s="41" t="n"/>
+      <c r="D451" s="2" t="n"/>
+      <c r="E451" s="3" t="n"/>
+      <c r="F451" s="35" t="n"/>
+      <c r="G451" s="26" t="n"/>
+      <c r="H451" s="26" t="n"/>
+      <c r="I451" s="2" t="n"/>
+      <c r="J451" s="24" t="n"/>
+      <c r="K451" s="3" t="n"/>
+      <c r="L451" s="51" t="n"/>
+      <c r="M451" s="13" t="n"/>
+      <c r="N451" s="51" t="n"/>
+      <c r="O451" s="29" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="P451" s="29" t="n"/>
+      <c r="Q451" s="29" t="n"/>
+      <c r="R451" s="45" t="n"/>
+      <c r="S451" s="21" t="n"/>
+      <c r="T451" s="33" t="n"/>
+      <c r="U451" s="37" t="n"/>
+      <c r="V451" s="2" t="n"/>
+      <c r="W451" s="3" t="n"/>
+      <c r="X451" s="3" t="n"/>
+      <c r="Y451" s="3" t="n"/>
+      <c r="Z451" s="3" t="n"/>
+      <c r="AA451" s="2" t="n"/>
+      <c r="AB451" s="2" t="n"/>
+      <c r="AC451" s="2" t="n"/>
+      <c r="AD451" s="2" t="n"/>
+      <c r="AE451" s="2" t="n"/>
+      <c r="AF451" s="3" t="n"/>
+      <c r="AG451" s="3" t="n"/>
+      <c r="AH451" s="2" t="n"/>
+      <c r="AI451" s="2" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <autoFilter ref="A1:AI450"/>
-  <conditionalFormatting sqref="A2:N450 R2:AI450">
+  <autoFilter ref="A1:AI451"/>
+  <conditionalFormatting sqref="A2:N451 R2:AI451">
     <cfRule type="expression" priority="4" dxfId="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:Q450">
+  <conditionalFormatting sqref="O2:Q451">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
